--- a/data/metrics_dimensions_filled.xlsx
+++ b/data/metrics_dimensions_filled.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB3"/>
+  <dimension ref="A1:AB4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -484,94 +484,187 @@
     </row>
     <row r="3" xml:space="preserve">
       <c r="A3" t="str">
+        <v>EXP-001</v>
+      </c>
+      <c r="B3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Current market value of all pledged collateral securing a credit exposure, denominated in USD. At the facility level, aggregates across all collateral positions linked to the facility. At the counterparty level, applies the bank's participation percentage (bank_share_pct) to reflect only the bank's proportionate share of collateral coverage. Supports recovery analysis, secured lending assessment, and credit risk mitigation quantification. Data element: Current_valuation_USD. Sourced from L2 Atomic Layer (collateral_snapshot).
+</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Current Collateral Market Value</v>
+      </c>
+      <c r="D3" t="str" xml:space="preserve">
+        <v xml:space="preserve">For each active facility as of the most recent as_of_date, look up all collateral_snapshot records linked to that facility_id and SUM current_valuation_usd across all associated collateral positions.
+</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="J3" t="str" xml:space="preserve">
+        <v xml:space="preserve">For each active facility as of the most recent as_of_date, look up all collateral_snapshot records linked to that facility_id and SUM current_valuation_usd across all associated collateral positions.
+</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Current Collateral Market Value (facility)</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M3" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="N3" t="str" xml:space="preserve">
+        <v xml:space="preserve">For each counterparty, look up all active facilities via facility_master. For each facility, retrieve the bank's participation percentage (bank_share_pct) from facility_lender_allocation and the facility-level current_valuation_usd (summed across all collateral positions). Multiply collateral value by participation percentage to get the bank's attributable share, then SUM across all facilities for the counterparty. Formula: SUM(current_valuation_usd * bank_share_pct / 100) per counterparty_id.
+</v>
+      </c>
+      <c r="O3" t="str">
+        <v>Current Collateral Market Value (counterparty)</v>
+      </c>
+      <c r="P3" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R3" t="str" xml:space="preserve">
+        <v xml:space="preserve">For each L3 desk in enterprise_business_taxonomy, look up all active facilities with a matching lob_segment_id, retrieve their facility-level current collateral market value, and SUM across all facilities for the desk.
+</v>
+      </c>
+      <c r="S3" t="str">
+        <v>Current Collateral Market Value (desk)</v>
+      </c>
+      <c r="T3" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U3" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V3" t="str" xml:space="preserve">
+        <v xml:space="preserve">For each L2 portfolio segment, traverse enterprise_business_taxonomy from facility lob_segment_id (L3 desk) up to its parent_segment_id (L2 portfolio). SUM facility-level collateral market values across all facilities belonging to desks within the portfolio.
+</v>
+      </c>
+      <c r="W3" t="str">
+        <v>Current Collateral Market Value (portfolio)</v>
+      </c>
+      <c r="X3" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y3" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z3" t="str" xml:space="preserve">
+        <v xml:space="preserve">For each L1 business segment / department, traverse enterprise_business_taxonomy two levels up from the facility's lob_segment_id (L3 desk → L2 portfolio → L1 business segment). SUM facility-level collateral market values across all facilities within the segment.
+</v>
+      </c>
+      <c r="AA3" t="str">
+        <v>Current Collateral Market Value (business_segment)</v>
+      </c>
+      <c r="AB3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
+      <c r="A4" t="str">
         <v>PROF-108</v>
       </c>
-      <c r="B3" t="str" xml:space="preserve">
+      <c r="B4" t="str" xml:space="preserve">
         <v xml:space="preserve">Total interest cost incurred on funding sources attributable to the reporting unit during the period. At facility level, computed as the product of the committed amount, the bank's participation share, and the cost of funds rate. At higher rollup levels, aggregated as the sum of facility-level interest expense.
 </v>
       </c>
-      <c r="C3" t="str">
+      <c r="C4" t="str">
         <v>Interest Expense</v>
       </c>
-      <c r="D3" t="str">
+      <c r="D4" t="str">
         <v>committed_facility_amt × bank_share_pct × cost_of_funds_rate</v>
       </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v>Y</v>
-      </c>
-      <c r="I3" t="str">
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I4" t="str">
         <v>Calc</v>
       </c>
-      <c r="J3" t="str">
+      <c r="J4" t="str">
         <v>committed_facility_amt × bank_share_pct × cost_of_funds_rate</v>
       </c>
-      <c r="K3" t="str">
+      <c r="K4" t="str">
         <v>Interest Expense (facility)</v>
       </c>
-      <c r="L3" t="str">
-        <v>Y</v>
-      </c>
-      <c r="M3" t="str">
-        <v>Agg</v>
-      </c>
-      <c r="N3" t="str">
+      <c r="L4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M4" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N4" t="str">
         <v>SUM(Facility Interest Expense) per counterparty</v>
       </c>
-      <c r="O3" t="str">
+      <c r="O4" t="str">
         <v>Interest Expense (counterparty)</v>
       </c>
-      <c r="P3" t="str">
-        <v>Y</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>Agg</v>
-      </c>
-      <c r="R3" t="str">
+      <c r="P4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R4" t="str">
         <v>SUM(Facility Interest Expense) per L3 desk segment</v>
       </c>
-      <c r="S3" t="str">
+      <c r="S4" t="str">
         <v>Interest Expense (desk)</v>
       </c>
-      <c r="T3" t="str">
-        <v>Y</v>
-      </c>
-      <c r="U3" t="str">
-        <v>Agg</v>
-      </c>
-      <c r="V3" t="str">
+      <c r="T4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U4" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V4" t="str">
         <v>SUM(Facility Interest Expense) per L2 portfolio segment</v>
       </c>
-      <c r="W3" t="str">
+      <c r="W4" t="str">
         <v>Interest Expense (portfolio)</v>
       </c>
-      <c r="X3" t="str">
-        <v>Y</v>
-      </c>
-      <c r="Y3" t="str">
-        <v>Agg</v>
-      </c>
-      <c r="Z3" t="str">
+      <c r="X4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y4" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z4" t="str">
         <v>SUM(Facility Interest Expense) per L1 business segment (department)</v>
       </c>
-      <c r="AA3" t="str">
+      <c r="AA4" t="str">
         <v>Interest Expense (business_segment)</v>
       </c>
-      <c r="AB3" t="str">
+      <c r="AB4" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AB3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AB4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/metrics_dimensions_filled.xlsx
+++ b/data/metrics_dimensions_filled.xlsx
@@ -487,14 +487,14 @@
         <v>EXP-001</v>
       </c>
       <c r="B3" t="str" xml:space="preserve">
-        <v xml:space="preserve">Current market value of all pledged collateral securing a credit exposure, denominated in USD. At the facility level, aggregates across all collateral positions linked to the facility. At the counterparty level, applies the bank's participation percentage (bank_share_pct) to reflect only the bank's proportionate share of collateral coverage. Supports recovery analysis, secured lending assessment, and credit risk mitigation quantification. Data element: Current_valuation_USD. Sourced from L2 Atomic Layer (collateral_snapshot).
+        <v xml:space="preserve">Current market value of all pledged collateral securing a credit exposure, denominated in USD, reflecting the bank's proportionate share (bank_share_pct). At the facility level, aggregates current_valuation_usd across all collateral positions linked to the facility, weighted by the bank's participation percentage from the current lender allocation record. At higher rollup levels (counterparty, desk, portfolio, business segment), values are summed consistently using the same bank-share-weighted facility amounts, ensuring cross-level reconciliation. NOTE: This metric reports raw market value, not haircut-adjusted recognised value per Basel III CRE22 comprehensive approach. For regulatory CRM recognition, apply haircut_pct from collateral_snapshot. Data element: current_valuation_usd. Sourced from L2 Atomic Layer (collateral_snapshot).
 </v>
       </c>
       <c r="C3" t="str">
         <v>Current Collateral Market Value</v>
       </c>
       <c r="D3" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each active facility as of the most recent as_of_date, look up all collateral_snapshot records linked to that facility_id and SUM current_valuation_usd across all associated collateral positions.
+        <v xml:space="preserve">For each active facility, SUM current_valuation_usd across all collateral positions, weighted by the bank's current participation share. Formula: SUM(current_valuation_usd) * COALESCE(bank_share_pct, 100) / 100.
 </v>
       </c>
       <c r="E3" t="str">
@@ -510,10 +510,10 @@
         <v>Y</v>
       </c>
       <c r="I3" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="J3" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each active facility as of the most recent as_of_date, look up all collateral_snapshot records linked to that facility_id and SUM current_valuation_usd across all associated collateral positions.
+        <v xml:space="preserve">For each active facility, SUM current_valuation_usd across all collateral positions, weighted by the bank's current participation share. Formula: SUM(current_valuation_usd) * COALESCE(bank_share_pct, 100) / 100.
 </v>
       </c>
       <c r="K3" t="str">
@@ -523,10 +523,10 @@
         <v>Y</v>
       </c>
       <c r="M3" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="N3" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each counterparty, look up all active facilities via facility_master. For each facility, retrieve the bank's participation percentage (bank_share_pct) from facility_lender_allocation and the facility-level current_valuation_usd (summed across all collateral positions). Multiply collateral value by participation percentage to get the bank's attributable share, then SUM across all facilities for the counterparty. Formula: SUM(current_valuation_usd * bank_share_pct / 100) per counterparty_id.
+        <v xml:space="preserve">SUM of bank-share-weighted facility collateral values per counterparty. Formula: SUM(facility_collateral_mv * COALESCE(bank_share_pct, 100) / 100) grouped by counterparty_id.
 </v>
       </c>
       <c r="O3" t="str">
@@ -539,7 +539,7 @@
         <v>Agg</v>
       </c>
       <c r="R3" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each L3 desk in enterprise_business_taxonomy, look up all active facilities with a matching lob_segment_id, retrieve their facility-level current collateral market value, and SUM across all facilities for the desk.
+        <v xml:space="preserve">SUM of bank-share-weighted facility collateral values per L3 desk segment.
 </v>
       </c>
       <c r="S3" t="str">
@@ -552,7 +552,7 @@
         <v>Agg</v>
       </c>
       <c r="V3" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each L2 portfolio segment, traverse enterprise_business_taxonomy from facility lob_segment_id (L3 desk) up to its parent_segment_id (L2 portfolio). SUM facility-level collateral market values across all facilities belonging to desks within the portfolio.
+        <v xml:space="preserve">SUM of bank-share-weighted facility collateral values per L2 portfolio segment. Traverses enterprise_business_taxonomy: L3 desk → L2 portfolio (parent_segment_id).
 </v>
       </c>
       <c r="W3" t="str">
@@ -565,7 +565,7 @@
         <v>Agg</v>
       </c>
       <c r="Z3" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each L1 business segment / department, traverse enterprise_business_taxonomy two levels up from the facility's lob_segment_id (L3 desk → L2 portfolio → L1 business segment). SUM facility-level collateral market values across all facilities within the segment.
+        <v xml:space="preserve">SUM of bank-share-weighted facility collateral values per L1 business segment. Traverses enterprise_business_taxonomy: L3 desk → L2 portfolio → L1 segment.
 </v>
       </c>
       <c r="AA3" t="str">

--- a/data/metrics_dimensions_filled.xlsx
+++ b/data/metrics_dimensions_filled.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB4"/>
+  <dimension ref="A1:AB107"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -484,17 +484,17 @@
     </row>
     <row r="3" xml:space="preserve">
       <c r="A3" t="str">
-        <v>EXP-001</v>
+        <v>AMD-001</v>
       </c>
       <c r="B3" t="str" xml:space="preserve">
-        <v xml:space="preserve">Current market value of all pledged collateral securing a credit exposure, denominated in USD, reflecting the bank's proportionate share (bank_share_pct). At the facility level, aggregates current_valuation_usd across all collateral positions linked to the facility, weighted by the bank's participation percentage from the current lender allocation record. At higher rollup levels (counterparty, desk, portfolio, business segment), values are summed consistently using the same bank-share-weighted facility amounts, ensuring cross-level reconciliation. NOTE: This metric reports raw market value, not haircut-adjusted recognised value per Basel III CRE22 comprehensive approach. For regulatory CRM recognition, apply haircut_pct from collateral_snapshot. Data element: current_valuation_usd. Sourced from L2 Atomic Layer (collateral_snapshot).
+        <v xml:space="preserve">Date amendment became effective.
 </v>
       </c>
       <c r="C3" t="str">
-        <v>Current Collateral Market Value</v>
+        <v>Amendment Start Date</v>
       </c>
       <c r="D3" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each active facility, SUM current_valuation_usd across all collateral positions, weighted by the bank's current participation share. Formula: SUM(current_valuation_usd) * COALESCE(bank_share_pct, 100) / 100.
+        <v xml:space="preserve">Read effective_date from facility_master for each facility.
 </v>
       </c>
       <c r="E3" t="str">
@@ -510,14 +510,14 @@
         <v>Y</v>
       </c>
       <c r="I3" t="str">
-        <v>Calc</v>
+        <v>Raw</v>
       </c>
       <c r="J3" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each active facility, SUM current_valuation_usd across all collateral positions, weighted by the bank's current participation share. Formula: SUM(current_valuation_usd) * COALESCE(bank_share_pct, 100) / 100.
+        <v xml:space="preserve">Read effective_date from facility_master for each facility.
 </v>
       </c>
       <c r="K3" t="str">
-        <v>Current Collateral Market Value (facility)</v>
+        <v>Amendment Start Date (facility)</v>
       </c>
       <c r="L3" t="str">
         <v>Y</v>
@@ -526,11 +526,11 @@
         <v>Agg</v>
       </c>
       <c r="N3" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of bank-share-weighted facility collateral values per counterparty. Formula: SUM(facility_collateral_mv * COALESCE(bank_share_pct, 100) / 100) grouped by counterparty_id.
+        <v xml:space="preserve">Latest (MAX) effective_date per counterparty.
 </v>
       </c>
       <c r="O3" t="str">
-        <v>Current Collateral Market Value (counterparty)</v>
+        <v>Amendment Start Date (counterparty)</v>
       </c>
       <c r="P3" t="str">
         <v>Y</v>
@@ -539,11 +539,11 @@
         <v>Agg</v>
       </c>
       <c r="R3" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of bank-share-weighted facility collateral values per L3 desk segment.
+        <v xml:space="preserve">Latest (MAX) effective_date per L3 desk segment.
 </v>
       </c>
       <c r="S3" t="str">
-        <v>Current Collateral Market Value (desk)</v>
+        <v>Amendment Start Date (desk)</v>
       </c>
       <c r="T3" t="str">
         <v>Y</v>
@@ -552,11 +552,11 @@
         <v>Agg</v>
       </c>
       <c r="V3" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of bank-share-weighted facility collateral values per L2 portfolio segment. Traverses enterprise_business_taxonomy: L3 desk → L2 portfolio (parent_segment_id).
+        <v xml:space="preserve">Latest (MAX) effective_date per L2 portfolio segment.
 </v>
       </c>
       <c r="W3" t="str">
-        <v>Current Collateral Market Value (portfolio)</v>
+        <v>Amendment Start Date (portfolio)</v>
       </c>
       <c r="X3" t="str">
         <v>Y</v>
@@ -565,11 +565,11 @@
         <v>Agg</v>
       </c>
       <c r="Z3" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of bank-share-weighted facility collateral values per L1 business segment. Traverses enterprise_business_taxonomy: L3 desk → L2 portfolio → L1 segment.
+        <v xml:space="preserve">Latest (MAX) effective_date per L1 business segment.
 </v>
       </c>
       <c r="AA3" t="str">
-        <v>Current Collateral Market Value (business_segment)</v>
+        <v>Amendment Start Date (business_segment)</v>
       </c>
       <c r="AB3" t="str">
         <v/>
@@ -577,94 +577,9690 @@
     </row>
     <row r="4" xml:space="preserve">
       <c r="A4" t="str">
+        <v>AMD-002</v>
+      </c>
+      <c r="B4" t="str" xml:space="preserve">
+        <v xml:space="preserve">Status of amendment within the approval lifecycle.
+</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Amendment Status</v>
+      </c>
+      <c r="D4" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read amendment status flag for each active facility.
+</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J4" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read amendment status flag for each active facility.
+</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Amendment Status (facility)</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M4" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N4" t="str" xml:space="preserve">
+        <v xml:space="preserve">COUNT of facilities with amendment status per counterparty.
+</v>
+      </c>
+      <c r="O4" t="str">
+        <v>Amendment Status (counterparty)</v>
+      </c>
+      <c r="P4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R4" t="str" xml:space="preserve">
+        <v xml:space="preserve">COUNT of facilities with amendment status per L3 desk segment.
+</v>
+      </c>
+      <c r="S4" t="str">
+        <v>Amendment Status (desk)</v>
+      </c>
+      <c r="T4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U4" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V4" t="str" xml:space="preserve">
+        <v xml:space="preserve">COUNT of facilities with amendment status per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W4" t="str">
+        <v>Amendment Status (portfolio)</v>
+      </c>
+      <c r="X4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y4" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z4" t="str" xml:space="preserve">
+        <v xml:space="preserve">COUNT of facilities with amendment status per L1 business segment.
+</v>
+      </c>
+      <c r="AA4" t="str">
+        <v>Amendment Status (business_segment)</v>
+      </c>
+      <c r="AB4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
+      <c r="A5" t="str">
+        <v>AMD-003</v>
+      </c>
+      <c r="B5" t="str" xml:space="preserve">
+        <v xml:space="preserve">Type of contractual amendment (e.g., covenant reset, maturity extension).
+</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Amendment Type</v>
+      </c>
+      <c r="D5" t="str" xml:space="preserve">
+        <v xml:space="preserve">Direct lookup of amendment_type_code from amendment_type_dim.
+</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I5" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J5" t="str" xml:space="preserve">
+        <v xml:space="preserve">Direct lookup of amendment_type_code from amendment_type_dim.
+</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Amendment Type (facility)</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M5" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N5" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(facility-level amendment_type_code) per counterparty.
+</v>
+      </c>
+      <c r="O5" t="str">
+        <v>Amendment Type (counterparty)</v>
+      </c>
+      <c r="P5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q5" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R5" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level amendment_type_code per L3 desk segment.
+</v>
+      </c>
+      <c r="S5" t="str">
+        <v>Amendment Type (desk)</v>
+      </c>
+      <c r="T5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U5" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V5" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level amendment_type_code per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W5" t="str">
+        <v>Amendment Type (portfolio)</v>
+      </c>
+      <c r="X5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y5" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z5" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level amendment_type_code per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA5" t="str">
+        <v>Amendment Type (business_segment)</v>
+      </c>
+      <c r="AB5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6" t="str">
+        <v>AMD-004</v>
+      </c>
+      <c r="B6" t="str" xml:space="preserve">
+        <v xml:space="preserve">Indicator that facility agreement has undergone amendment. Portfolio KPI (% Facilities with Amendments) signals restructuring activity.
+</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Amendment ID</v>
+      </c>
+      <c r="D6" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read amendment_event_id from amendment_event for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I6" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J6" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read amendment_event_id from amendment_event for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Amendment ID (facility)</v>
+      </c>
+      <c r="L6" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M6" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N6" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(facility-level amendment_event_id) per counterparty.
+</v>
+      </c>
+      <c r="O6" t="str">
+        <v>Amendment ID (counterparty)</v>
+      </c>
+      <c r="P6" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q6" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R6" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level amendment_event_id per L3 desk segment.
+</v>
+      </c>
+      <c r="S6" t="str">
+        <v>Amendment ID (desk)</v>
+      </c>
+      <c r="T6" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U6" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V6" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level amendment_event_id per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W6" t="str">
+        <v>Amendment ID (portfolio)</v>
+      </c>
+      <c r="X6" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y6" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z6" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level amendment_event_id per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA6" t="str">
+        <v>Amendment ID (business_segment)</v>
+      </c>
+      <c r="AB6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7" xml:space="preserve">
+      <c r="A7" t="str">
+        <v>CAP-001</v>
+      </c>
+      <c r="B7" t="str" xml:space="preserve">
+        <v xml:space="preserve">Assesses capital buffer relative to risk (RWA); indicates solvency cushion and capacity to absorb losses and support growth.
+</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Capital Adequacy Ratio (%)</v>
+      </c>
+      <c r="D7" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read capital_adequacy_ratio_pct from lob_risk_ratio_summary for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J7" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read capital_adequacy_ratio_pct from lob_risk_ratio_summary for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Capital Adequacy Ratio (%) (facility)</v>
+      </c>
+      <c r="L7" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M7" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="N7" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(allocated_equity) / SUM(rwa) * 100.0 per counterparty.
+</v>
+      </c>
+      <c r="O7" t="str">
+        <v>Capital Adequacy Ratio (%) (counterparty)</v>
+      </c>
+      <c r="P7" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q7" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="R7" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(allocated_equity) / SUM(rwa) * 100.0 per L3 desk segment.
+</v>
+      </c>
+      <c r="S7" t="str">
+        <v>Capital Adequacy Ratio (%) (desk)</v>
+      </c>
+      <c r="T7" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U7" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="V7" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(allocated_equity) / SUM(rwa) * 100.0 per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W7" t="str">
+        <v>Capital Adequacy Ratio (%) (portfolio)</v>
+      </c>
+      <c r="X7" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y7" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="Z7" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(allocated_equity) / SUM(rwa) * 100.0 per L1 business segment.
+</v>
+      </c>
+      <c r="AA7" t="str">
+        <v>Capital Adequacy Ratio (%) (business_segment)</v>
+      </c>
+      <c r="AB7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8" xml:space="preserve">
+      <c r="A8" t="str">
+        <v>CAP-002</v>
+      </c>
+      <c r="B8" t="str" xml:space="preserve">
+        <v xml:space="preserve">Evaluates profitability per unit of risk (RWA); supports risk-adjusted performance comparisons, pricing, and capital allocation decisions.
+</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Return on RWA (%)</v>
+      </c>
+      <c r="D8" t="str" xml:space="preserve">
+        <v xml:space="preserve">Calculated return_on_rwa_pct per facility.
+</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="J8" t="str" xml:space="preserve">
+        <v xml:space="preserve">Calculated return_on_rwa_pct per facility.
+</v>
+      </c>
+      <c r="K8" t="str">
+        <v>Return on RWA (%) (facility)</v>
+      </c>
+      <c r="L8" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M8" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="N8" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(net_income) / SUM(rwa) * 100.0 per counterparty.
+</v>
+      </c>
+      <c r="O8" t="str">
+        <v>Return on RWA (%) (counterparty)</v>
+      </c>
+      <c r="P8" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q8" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="R8" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(net_income) / SUM(rwa) * 100.0 per L3 desk segment.
+</v>
+      </c>
+      <c r="S8" t="str">
+        <v>Return on RWA (%) (desk)</v>
+      </c>
+      <c r="T8" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U8" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="V8" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(net_income) / SUM(rwa) * 100.0 per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W8" t="str">
+        <v>Return on RWA (%) (portfolio)</v>
+      </c>
+      <c r="X8" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y8" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="Z8" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(net_income) / SUM(rwa) * 100.0 per L1 business segment.
+</v>
+      </c>
+      <c r="AA8" t="str">
+        <v>Return on RWA (%) (business_segment)</v>
+      </c>
+      <c r="AB8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
+      <c r="A9" t="str">
+        <v>CAP-003</v>
+      </c>
+      <c r="B9" t="str" xml:space="preserve">
+        <v xml:space="preserve">Regulatory risk weight percentage assigned to the exposure under the applicable capital framework (e.g., Basel standardized or IRB). Represents the proportion of exposure considered risk-weighted for capital adequacy purposes.
+</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Risk Weight (%)</v>
+      </c>
+      <c r="D9" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read risk_weight_pct from facility_risk_snapshot for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I9" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J9" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read risk_weight_pct from facility_risk_snapshot for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="K9" t="str">
+        <v>Risk Weight (%) (facility)</v>
+      </c>
+      <c r="L9" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M9" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="N9" t="str" xml:space="preserve">
+        <v xml:space="preserve">Exposure-weighted average risk_weight_pct per counterparty.
+</v>
+      </c>
+      <c r="O9" t="str">
+        <v>Risk Weight (%) (counterparty)</v>
+      </c>
+      <c r="P9" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q9" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="R9" t="str" xml:space="preserve">
+        <v xml:space="preserve">Exposure-weighted average risk_weight_pct per L3 desk segment.
+</v>
+      </c>
+      <c r="S9" t="str">
+        <v>Risk Weight (%) (desk)</v>
+      </c>
+      <c r="T9" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U9" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="V9" t="str" xml:space="preserve">
+        <v xml:space="preserve">Exposure-weighted average risk_weight_pct per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W9" t="str">
+        <v>Risk Weight (%) (portfolio)</v>
+      </c>
+      <c r="X9" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y9" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="Z9" t="str" xml:space="preserve">
+        <v xml:space="preserve">Exposure-weighted average risk_weight_pct per L1 business segment.
+</v>
+      </c>
+      <c r="AA9" t="str">
+        <v>Risk Weight (%) (business_segment)</v>
+      </c>
+      <c r="AB9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str">
+        <v>EXP-001</v>
+      </c>
+      <c r="B10" t="str" xml:space="preserve">
+        <v xml:space="preserve">Current market value of all pledged collateral securing a credit exposure, denominated in USD, reflecting the bank's proportionate share (bank_share_pct). At the facility level, aggregates current_valuation_usd across all collateral positions linked to the facility, weighted by the bank's participation percentage from the current lender allocation record. At higher rollup levels (counterparty, desk, portfolio, business segment), values are summed consistently using the same bank-share-weighted facility amounts, ensuring cross-level reconciliation. NOTE: This metric reports raw market value, not haircut-adjusted recognised value per Basel III CRE22 comprehensive approach. For regulatory CRM recognition, apply haircut_pct from collateral_snapshot. Data element: current_valuation_usd. Sourced from L2 Atomic Layer (collateral_snapshot).
+</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Current Collateral Market Value</v>
+      </c>
+      <c r="D10" t="str" xml:space="preserve">
+        <v xml:space="preserve">For each active facility, SUM current_valuation_usd across all collateral positions, weighted by the bank's current participation share. Formula: SUM(current_valuation_usd) * COALESCE(bank_share_pct, 100) / 100.
+</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I10" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="J10" t="str" xml:space="preserve">
+        <v xml:space="preserve">For each active facility, SUM current_valuation_usd across all collateral positions, weighted by the bank's current participation share. Formula: SUM(current_valuation_usd) * COALESCE(bank_share_pct, 100) / 100.
+</v>
+      </c>
+      <c r="K10" t="str">
+        <v>Current Collateral Market Value (facility)</v>
+      </c>
+      <c r="L10" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M10" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N10" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of bank-share-weighted facility collateral values per counterparty. Formula: SUM(facility_collateral_mv * COALESCE(bank_share_pct, 100) / 100) grouped by counterparty_id.
+</v>
+      </c>
+      <c r="O10" t="str">
+        <v>Current Collateral Market Value (counterparty)</v>
+      </c>
+      <c r="P10" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q10" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R10" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of bank-share-weighted facility collateral values per L3 desk segment.
+</v>
+      </c>
+      <c r="S10" t="str">
+        <v>Current Collateral Market Value (desk)</v>
+      </c>
+      <c r="T10" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U10" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V10" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of bank-share-weighted facility collateral values per L2 portfolio segment. Traverses enterprise_business_taxonomy: L3 desk → L2 portfolio (parent_segment_id).
+</v>
+      </c>
+      <c r="W10" t="str">
+        <v>Current Collateral Market Value (portfolio)</v>
+      </c>
+      <c r="X10" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y10" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z10" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of bank-share-weighted facility collateral values per L1 business segment. Traverses enterprise_business_taxonomy: L3 desk → L2 portfolio → L1 segment.
+</v>
+      </c>
+      <c r="AA10" t="str">
+        <v>Current Collateral Market Value (business_segment)</v>
+      </c>
+      <c r="AB10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11" xml:space="preserve">
+      <c r="A11" t="str">
+        <v>EXP-002</v>
+      </c>
+      <c r="B11" t="str" xml:space="preserve">
+        <v xml:space="preserve">Operating cash flow generated by borrower in millions USD. Primary indicator of repayment capacity. Cashflows are sourced based on line of business (At a counterparty level defined as CRE = NOI, all other LOBs = EBITDA, where within business heirarchy defined as Interest Income calculated at a facility level)
+</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Cashflow ($)</v>
+      </c>
+      <c r="D11" t="str" xml:space="preserve">
+        <v xml:space="preserve">[Facility Cashflow]==[Facility Interest Income w/ Bank Share]
+</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="J11" t="str" xml:space="preserve">
+        <v xml:space="preserve">[Facility Cashflow]==[Facility Interest Income w/ Bank Share]
+</v>
+      </c>
+      <c r="K11" t="str">
+        <v>Cashflow ($) (facility)</v>
+      </c>
+      <c r="L11" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M11" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N11" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level contractual_amt per counterparty.
+</v>
+      </c>
+      <c r="O11" t="str">
+        <v>Cashflow ($) (counterparty)</v>
+      </c>
+      <c r="P11" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q11" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R11" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level contractual_amt per L3 desk segment.
+</v>
+      </c>
+      <c r="S11" t="str">
+        <v>Cashflow ($) (desk)</v>
+      </c>
+      <c r="T11" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U11" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V11" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level contractual_amt per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W11" t="str">
+        <v>Cashflow ($) (portfolio)</v>
+      </c>
+      <c r="X11" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y11" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z11" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level contractual_amt per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA11" t="str">
+        <v>Cashflow ($) (business_segment)</v>
+      </c>
+      <c r="AB11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
+      <c r="A12" t="str">
+        <v>EXP-004</v>
+      </c>
+      <c r="B12" t="str" xml:space="preserve">
+        <v xml:space="preserve">Total approved committed credit amount in USD representing contractual lending capacity.
+</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Committed Exposure ($)</v>
+      </c>
+      <c r="D12" t="str" xml:space="preserve">
+        <v xml:space="preserve">For each Distinct([Facility ID]), WHEN IS(MAX(AS_OF_DATE) AND [Facility_Active_Flag]="Y", THEN [Committed_Facility_Amt]*[Bank_Share] == [Committed Exposure, Bank Share portion only]
+</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I12" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="J12" t="str" xml:space="preserve">
+        <v xml:space="preserve">For each Distinct([Facility ID]), WHEN IS(MAX(AS_OF_DATE) AND [Facility_Active_Flag]="Y", THEN [Committed_Facility_Amt]*[Bank_Share] == [Committed Exposure, Bank Share portion only]
+</v>
+      </c>
+      <c r="K12" t="str">
+        <v>Committed Exposure ($) (facility)</v>
+      </c>
+      <c r="L12" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M12" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N12" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level committed_facility_amt per counterparty.
+</v>
+      </c>
+      <c r="O12" t="str">
+        <v>Committed Exposure ($) (counterparty)</v>
+      </c>
+      <c r="P12" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q12" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R12" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level committed_facility_amt per L3 desk segment.
+</v>
+      </c>
+      <c r="S12" t="str">
+        <v>Committed Exposure ($) (desk)</v>
+      </c>
+      <c r="T12" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U12" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V12" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level committed_facility_amt per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W12" t="str">
+        <v>Committed Exposure ($) (portfolio)</v>
+      </c>
+      <c r="X12" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y12" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z12" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level committed_facility_amt per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA12" t="str">
+        <v>Committed Exposure ($) (business_segment)</v>
+      </c>
+      <c r="AB12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13" xml:space="preserve">
+      <c r="A13" t="str">
+        <v>EXP-005</v>
+      </c>
+      <c r="B13" t="str" xml:space="preserve">
+        <v xml:space="preserve">The portion of total funding-related expense (primarily interest expense on deposits, borrowings, and other funding sources) that is attributed to a specific exposure or portfolio for a given period
+</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Cost of Funds ($)</v>
+      </c>
+      <c r="D13" t="str" xml:space="preserve">
+        <v xml:space="preserve">Lookup Position_ID for each Facility_ID, Select bank_share from Facility_ID from Faciltiy Master THEN contract_amt * bank_share* Interest Rate = [Position Cost of Funds w/ Bank Share] (AKA Utilized Exposure * Interest Rate)  SUM([Position Interest Income w/ Bank Share] across all Position_IDs ==[Facility Cost of Funds w/ Bank Share]
+</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I13" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="J13" t="str" xml:space="preserve">
+        <v xml:space="preserve">Lookup Position_ID for each Facility_ID, Select bank_share from Facility_ID from Faciltiy Master THEN contract_amt * bank_share* Interest Rate = [Position Cost of Funds w/ Bank Share] (AKA Utilized Exposure * Interest Rate)  SUM([Position Interest Income w/ Bank Share] across all Position_IDs ==[Facility Cost of Funds w/ Bank Share]
+</v>
+      </c>
+      <c r="K13" t="str">
+        <v>Cost of Funds ($) (facility)</v>
+      </c>
+      <c r="L13" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M13" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N13" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level funded_amount per counterparty.
+</v>
+      </c>
+      <c r="O13" t="str">
+        <v>Cost of Funds ($) (counterparty)</v>
+      </c>
+      <c r="P13" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q13" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R13" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level funded_amount per L3 desk segment.
+</v>
+      </c>
+      <c r="S13" t="str">
+        <v>Cost of Funds ($) (desk)</v>
+      </c>
+      <c r="T13" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U13" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V13" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level funded_amount per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W13" t="str">
+        <v>Cost of Funds ($) (portfolio)</v>
+      </c>
+      <c r="X13" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y13" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z13" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level funded_amount per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA13" t="str">
+        <v>Cost of Funds ($) (business_segment)</v>
+      </c>
+      <c r="AB13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14" xml:space="preserve">
+      <c r="A14" t="str">
+        <v>EXP-006</v>
+      </c>
+      <c r="B14" t="str" xml:space="preserve">
+        <v xml:space="preserve">Exposure allocated to specific counterparty representing their share of the facility which the client can draw on. Concentration KPI measuring obligor dependency risk.
+</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Counterparty Share or Allocation (%)</v>
+      </c>
+      <c r="D14" t="str" xml:space="preserve">
+        <v xml:space="preserve">Direct lookup of allocation_pct from facility_counterparty_participation.
+</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I14" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J14" t="str" xml:space="preserve">
+        <v xml:space="preserve">Direct lookup of allocation_pct from facility_counterparty_participation.
+</v>
+      </c>
+      <c r="K14" t="str">
+        <v>Counterparty Share or Allocation (%) (facility)</v>
+      </c>
+      <c r="L14" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M14" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="N14" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read allocation_pct per counterparty.
+</v>
+      </c>
+      <c r="O14" t="str">
+        <v>Counterparty Share or Allocation (%) (counterparty)</v>
+      </c>
+      <c r="P14" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q14" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R14" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level allocation_pct per L3 desk segment.
+</v>
+      </c>
+      <c r="S14" t="str">
+        <v>Counterparty Share or Allocation (%) (desk)</v>
+      </c>
+      <c r="T14" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U14" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V14" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level allocation_pct per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W14" t="str">
+        <v>Counterparty Share or Allocation (%) (portfolio)</v>
+      </c>
+      <c r="X14" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y14" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z14" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level allocation_pct per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA14" t="str">
+        <v>Counterparty Share or Allocation (%) (business_segment)</v>
+      </c>
+      <c r="AB14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15" xml:space="preserve">
+      <c r="A15" t="str">
+        <v>EXP-007</v>
+      </c>
+      <c r="B15" t="str" xml:space="preserve">
+        <v xml:space="preserve">Flag identifying exposures requiring heightened monitoring due to elevated credit risk. Governance control used for enhanced monitoring, reserve consideration, and management reporting.
+</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Criticized Portfolios</v>
+      </c>
+      <c r="D15" t="str" xml:space="preserve">
+        <v xml:space="preserve">Binary flag: 1 if criticized rating (internal_risk_rating &gt;= 6), 0 otherwise.
+</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I15" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="J15" t="str" xml:space="preserve">
+        <v xml:space="preserve">Binary flag: 1 if criticized rating (internal_risk_rating &gt;= 6), 0 otherwise.
+</v>
+      </c>
+      <c r="K15" t="str">
+        <v>Criticized Portfolios (facility)</v>
+      </c>
+      <c r="L15" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M15" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="N15" t="str" xml:space="preserve">
+        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per counterparty.
+</v>
+      </c>
+      <c r="O15" t="str">
+        <v>Criticized Portfolios (counterparty)</v>
+      </c>
+      <c r="P15" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q15" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="R15" t="str" xml:space="preserve">
+        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per L3 desk.
+</v>
+      </c>
+      <c r="S15" t="str">
+        <v>Criticized Portfolios (desk)</v>
+      </c>
+      <c r="T15" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U15" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="V15" t="str" xml:space="preserve">
+        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per L2 portfolio.
+</v>
+      </c>
+      <c r="W15" t="str">
+        <v>Criticized Portfolios (portfolio)</v>
+      </c>
+      <c r="X15" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y15" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="Z15" t="str" xml:space="preserve">
+        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per L1 business segment.
+</v>
+      </c>
+      <c r="AA15" t="str">
+        <v>Criticized Portfolios (business_segment)</v>
+      </c>
+      <c r="AB15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16" xml:space="preserve">
+      <c r="A16" t="str">
+        <v>EXP-008</v>
+      </c>
+      <c r="B16" t="str" xml:space="preserve">
+        <v xml:space="preserve">Total exposure amount allocated across multiple legal entities. Supports intra-group concentration transparency.
+</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Cross Entity Exposure Amount</v>
+      </c>
+      <c r="D16" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(total_cross_entity_exposure_usd) per facility from counterparty_exposure_summary. Weighted by bank share percentage.
+</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I16" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="J16" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(total_cross_entity_exposure_usd) per facility from counterparty_exposure_summary. Weighted by bank share percentage.
+</v>
+      </c>
+      <c r="K16" t="str">
+        <v>Cross Entity Exposure Amount (facility)</v>
+      </c>
+      <c r="L16" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M16" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N16" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per counterparty.
+</v>
+      </c>
+      <c r="O16" t="str">
+        <v>Cross Entity Exposure Amount (counterparty)</v>
+      </c>
+      <c r="P16" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q16" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R16" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per L3 desk segment.
+</v>
+      </c>
+      <c r="S16" t="str">
+        <v>Cross Entity Exposure Amount (desk)</v>
+      </c>
+      <c r="T16" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U16" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V16" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W16" t="str">
+        <v>Cross Entity Exposure Amount (portfolio)</v>
+      </c>
+      <c r="X16" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y16" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z16" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA16" t="str">
+        <v>Cross Entity Exposure Amount (business_segment)</v>
+      </c>
+      <c r="AB16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17" xml:space="preserve">
+      <c r="A17" t="str">
+        <v>EXP-009</v>
+      </c>
+      <c r="B17" t="str" xml:space="preserve">
+        <v xml:space="preserve">Number of days outstanding payments is past due as grouped into 3 "buckets", 0-30 Days, 31-60 Days, 61-90+ Days. Used for staging classification and early credit deterioration monitoring.
+</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Days Payment Overdue Bucket</v>
+      </c>
+      <c r="D17" t="str" xml:space="preserve">
+        <v xml:space="preserve">For each Facility_ID lookup the Payments records in the Payment Lockbox table, For each payment record where [Payment_Due_Date] &gt; Today() IF ([Pmt_Applied] &lt;[Pmt_Due])&gt;=1, THEN Today() - [Payment_due_date] ==[Days Overdue] SELECT MAX ([Days Overdue] then lookup in Payments Overdue bucket)
+</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I17" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="J17" t="str" xml:space="preserve">
+        <v xml:space="preserve">For each Facility_ID lookup the Payments records in the Payment Lockbox table, For each payment record where [Payment_Due_Date] &gt; Today() IF ([Pmt_Applied] &lt;[Pmt_Due])&gt;=1, THEN Today() - [Payment_due_date] ==[Days Overdue] SELECT MAX ([Days Overdue] then lookup in Payments Overdue bucket)
+</v>
+      </c>
+      <c r="K17" t="str">
+        <v>Days Payment Overdue Bucket (facility)</v>
+      </c>
+      <c r="L17" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M17" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N17" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level dpd_bucket_code per counterparty.
+</v>
+      </c>
+      <c r="O17" t="str">
+        <v>Days Payment Overdue Bucket (counterparty)</v>
+      </c>
+      <c r="P17" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q17" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R17" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level dpd_bucket_code per L3 desk segment.
+</v>
+      </c>
+      <c r="S17" t="str">
+        <v>Days Payment Overdue Bucket (desk)</v>
+      </c>
+      <c r="T17" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U17" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V17" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level dpd_bucket_code per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W17" t="str">
+        <v>Days Payment Overdue Bucket (portfolio)</v>
+      </c>
+      <c r="X17" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y17" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z17" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level dpd_bucket_code per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA17" t="str">
+        <v>Days Payment Overdue Bucket (business_segment)</v>
+      </c>
+      <c r="AB17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18" xml:space="preserve">
+      <c r="A18" t="str">
+        <v>EXP-010</v>
+      </c>
+      <c r="B18" t="str" xml:space="preserve">
+        <v xml:space="preserve">Calculated as Count of Delinquent Loans / Total Loans × 100. Portfolio stress KPI measuring prevalence of past-due exposures.
+</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Delinquency Rate (%)</v>
+      </c>
+      <c r="D18" t="str" xml:space="preserve">
+        <v xml:space="preserve">Binary flag: 1 if delinquency (days_past_due &gt; 0), 0 otherwise.
+</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I18" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="J18" t="str" xml:space="preserve">
+        <v xml:space="preserve">Binary flag: 1 if delinquency (days_past_due &gt; 0), 0 otherwise.
+</v>
+      </c>
+      <c r="K18" t="str">
+        <v>Delinquency Rate (%) (facility)</v>
+      </c>
+      <c r="L18" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M18" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="N18" t="str" xml:space="preserve">
+        <v xml:space="preserve">Percentage of facilities with delinquency (days_past_due &gt; 0) per counterparty.
+</v>
+      </c>
+      <c r="O18" t="str">
+        <v>Delinquency Rate (%) (counterparty)</v>
+      </c>
+      <c r="P18" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q18" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="R18" t="str" xml:space="preserve">
+        <v xml:space="preserve">Percentage of facilities with delinquency (days_past_due &gt; 0) per L3 desk.
+</v>
+      </c>
+      <c r="S18" t="str">
+        <v>Delinquency Rate (%) (desk)</v>
+      </c>
+      <c r="T18" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U18" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="V18" t="str" xml:space="preserve">
+        <v xml:space="preserve">Percentage of facilities with delinquency (days_past_due &gt; 0) per L2 portfolio.
+</v>
+      </c>
+      <c r="W18" t="str">
+        <v>Delinquency Rate (%) (portfolio)</v>
+      </c>
+      <c r="X18" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y18" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="Z18" t="str" xml:space="preserve">
+        <v xml:space="preserve">Percentage of facilities with delinquency (days_past_due &gt; 0) per L1 business segment.
+</v>
+      </c>
+      <c r="AA18" t="str">
+        <v>Delinquency Rate (%) (business_segment)</v>
+      </c>
+      <c r="AB18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19" xml:space="preserve">
+      <c r="A19" t="str">
+        <v>EXP-011</v>
+      </c>
+      <c r="B19" t="str" xml:space="preserve">
+        <v xml:space="preserve">Indicator that exposure is past due. Used for credit monitoring, staging assessment, and early default identification.
+</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Delinquent Payment Flag</v>
+      </c>
+      <c r="D19" t="str" xml:space="preserve">
+        <v xml:space="preserve">For each Facility_ID lookup the Payments records in the Payment Lockbox table. For each payment record where Payment Due Date &gt; Today() IF(COUNT IF ([Pmt_Applied] &lt;[Pmt_Due])&gt;=1, then "Y", "N")
+</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I19" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="J19" t="str" xml:space="preserve">
+        <v xml:space="preserve">For each Facility_ID lookup the Payments records in the Payment Lockbox table. For each payment record where Payment Due Date &gt; Today() IF(COUNT IF ([Pmt_Applied] &lt;[Pmt_Due])&gt;=1, then "Y", "N")
+</v>
+      </c>
+      <c r="K19" t="str">
+        <v>Delinquent Payment Flag (facility)</v>
+      </c>
+      <c r="L19" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M19" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N19" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level delinquent_payment_flag per counterparty.
+</v>
+      </c>
+      <c r="O19" t="str">
+        <v>Delinquent Payment Flag (counterparty)</v>
+      </c>
+      <c r="P19" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q19" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R19" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level delinquent_payment_flag per L3 desk segment.
+</v>
+      </c>
+      <c r="S19" t="str">
+        <v>Delinquent Payment Flag (desk)</v>
+      </c>
+      <c r="T19" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U19" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V19" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level delinquent_payment_flag per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W19" t="str">
+        <v>Delinquent Payment Flag (portfolio)</v>
+      </c>
+      <c r="X19" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y19" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z19" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level delinquent_payment_flag per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA19" t="str">
+        <v>Delinquent Payment Flag (business_segment)</v>
+      </c>
+      <c r="AB19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20" xml:space="preserve">
+      <c r="A20" t="str">
+        <v>EXP-012</v>
+      </c>
+      <c r="B20" t="str" xml:space="preserve">
+        <v xml:space="preserve">Total outstanding exposure that is contractually past due in USD. Provides direct measurement of impaired balances and supports staging and loss forecasting analysis.
+</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Delinquent Amount ($)</v>
+      </c>
+      <c r="D20" t="str" xml:space="preserve">
+        <v xml:space="preserve">For each Facility_ID lookup the Payments records in the Payment Lockbox table. For each payment record where [Payment_Due_Date] &gt; Today() IF(COUNT IF ([Pmt_Applied] &lt;[Pmt_Due])&gt;=1, then [Payment_Amt_Due]+[Fee_Due]-[Payment Applied] == [Deliquent Payment Amount]) SUM([Deliquent Payment Amount] across all payment records where IS(Facility_ID))
+</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I20" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="J20" t="str" xml:space="preserve">
+        <v xml:space="preserve">For each Facility_ID lookup the Payments records in the Payment Lockbox table. For each payment record where [Payment_Due_Date] &gt; Today() IF(COUNT IF ([Pmt_Applied] &lt;[Pmt_Due])&gt;=1, then [Payment_Amt_Due]+[Fee_Due]-[Payment Applied] == [Deliquent Payment Amount]) SUM([Deliquent Payment Amount] across all payment records where IS(Facility_ID))
+</v>
+      </c>
+      <c r="K20" t="str">
+        <v>Delinquent Amount ($) (facility)</v>
+      </c>
+      <c r="L20" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M20" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N20" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level total_overdue_amt per counterparty.
+</v>
+      </c>
+      <c r="O20" t="str">
+        <v>Delinquent Amount ($) (counterparty)</v>
+      </c>
+      <c r="P20" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q20" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R20" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level total_overdue_amt per L3 desk segment.
+</v>
+      </c>
+      <c r="S20" t="str">
+        <v>Delinquent Amount ($) (desk)</v>
+      </c>
+      <c r="T20" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U20" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V20" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level total_overdue_amt per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W20" t="str">
+        <v>Delinquent Amount ($) (portfolio)</v>
+      </c>
+      <c r="X20" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y20" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z20" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level total_overdue_amt per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA20" t="str">
+        <v>Delinquent Amount ($) (business_segment)</v>
+      </c>
+      <c r="AB20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21" xml:space="preserve">
+      <c r="A21" t="str">
+        <v>EXP-013</v>
+      </c>
+      <c r="B21" t="str" xml:space="preserve">
+        <v xml:space="preserve">Derived indicator that the facility’s internal credit rating has worsened during the reporting period. Provides automated early deterioration signal supporting migration monitoring and risk escalation.
+</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Deteriorated Deal Flag</v>
+      </c>
+      <c r="D21" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read is_deteriorated from facility_detail_snapshot for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I21" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J21" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read is_deteriorated from facility_detail_snapshot for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="K21" t="str">
+        <v>Deteriorated Deal Flag (facility)</v>
+      </c>
+      <c r="L21" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M21" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N21" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level is_deteriorated per counterparty.
+</v>
+      </c>
+      <c r="O21" t="str">
+        <v>Deteriorated Deal Flag (counterparty)</v>
+      </c>
+      <c r="P21" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q21" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R21" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level is_deteriorated per L3 desk segment.
+</v>
+      </c>
+      <c r="S21" t="str">
+        <v>Deteriorated Deal Flag (desk)</v>
+      </c>
+      <c r="T21" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U21" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V21" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level is_deteriorated per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W21" t="str">
+        <v>Deteriorated Deal Flag (portfolio)</v>
+      </c>
+      <c r="X21" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y21" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z21" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level is_deteriorated per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA21" t="str">
+        <v>Deteriorated Deal Flag (business_segment)</v>
+      </c>
+      <c r="AB21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22" xml:space="preserve">
+      <c r="A22" t="str">
+        <v>EXP-014</v>
+      </c>
+      <c r="B22" t="str" xml:space="preserve">
+        <v xml:space="preserve">Net Operating Income divided by Total Debt Service. Measures borrower's ability to meet debt obligations from operating cash flow, providing insight into covenant compliance and credit resilience.
+</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Debt Service Coverage Ratio (DSCR)</v>
+      </c>
+      <c r="D22" t="str" xml:space="preserve">
+        <v xml:space="preserve">Compute DSCR = noi_amt / total_debt_service_amt per facility.
+</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I22" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J22" t="str" xml:space="preserve">
+        <v xml:space="preserve">Compute DSCR = noi_amt / total_debt_service_amt per facility.
+</v>
+      </c>
+      <c r="K22" t="str">
+        <v>Debt Service Coverage Ratio (DSCR) (facility)</v>
+      </c>
+      <c r="L22" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M22" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="N22" t="str" xml:space="preserve">
+        <v xml:space="preserve">Exposure-weighted average DSCR per counterparty:
+SUM(dscr * drawn_amount) / SUM(drawn_amount).
+</v>
+      </c>
+      <c r="O22" t="str">
+        <v>Debt Service Coverage Ratio (DSCR) (counterparty)</v>
+      </c>
+      <c r="P22" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q22" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="R22" t="str" xml:space="preserve">
+        <v xml:space="preserve">Exposure-weighted average DSCR per L3 desk segment:
+SUM(dscr * drawn_amount) / SUM(drawn_amount).
+</v>
+      </c>
+      <c r="S22" t="str">
+        <v>Debt Service Coverage Ratio (DSCR) (desk)</v>
+      </c>
+      <c r="T22" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U22" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="V22" t="str" xml:space="preserve">
+        <v xml:space="preserve">Exposure-weighted average DSCR per L2 portfolio segment:
+SUM(dscr * drawn_amount) / SUM(drawn_amount).
+</v>
+      </c>
+      <c r="W22" t="str">
+        <v>Debt Service Coverage Ratio (DSCR) (portfolio)</v>
+      </c>
+      <c r="X22" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y22" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="Z22" t="str" xml:space="preserve">
+        <v xml:space="preserve">Exposure-weighted average DSCR per L1 business segment:
+SUM(dscr * drawn_amount) / SUM(drawn_amount).
+</v>
+      </c>
+      <c r="AA22" t="str">
+        <v>Debt Service Coverage Ratio (DSCR) (business_segment)</v>
+      </c>
+      <c r="AB22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23" xml:space="preserve">
+      <c r="A23" t="str">
+        <v>EXP-015</v>
+      </c>
+      <c r="B23" t="str" xml:space="preserve">
+        <v xml:space="preserve">Expected Loss divided by Exposure. Derived KPI measuring loss intensity relative to exposure size, enabling comparative risk ranking across facilities or counterparties.
+</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Expected Loss Rate (%)</v>
+      </c>
+      <c r="D23" t="str" xml:space="preserve">
+        <v xml:space="preserve">Exposure-weighted average of expected_loss_rate_pct per facility.
+</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I23" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="J23" t="str" xml:space="preserve">
+        <v xml:space="preserve">Exposure-weighted average of expected_loss_rate_pct per facility.
+</v>
+      </c>
+      <c r="K23" t="str">
+        <v>Expected Loss Rate (%) (facility)</v>
+      </c>
+      <c r="L23" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M23" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N23" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level expected_loss_rate_pct per counterparty.
+</v>
+      </c>
+      <c r="O23" t="str">
+        <v>Expected Loss Rate (%) (counterparty)</v>
+      </c>
+      <c r="P23" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q23" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="R23" t="str" xml:space="preserve">
+        <v xml:space="preserve">AVG of facility-level expected_loss_rate_pct per L3 desk segment.
+</v>
+      </c>
+      <c r="S23" t="str">
+        <v>Expected Loss Rate (%) (desk)</v>
+      </c>
+      <c r="T23" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U23" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V23" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level expected_loss_rate_pct per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W23" t="str">
+        <v>Expected Loss Rate (%) (portfolio)</v>
+      </c>
+      <c r="X23" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y23" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z23" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level expected_loss_rate_pct per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA23" t="str">
+        <v>Expected Loss Rate (%) (business_segment)</v>
+      </c>
+      <c r="AB23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24" xml:space="preserve">
+      <c r="A24" t="str">
+        <v>EXP-016</v>
+      </c>
+      <c r="B24" t="str" xml:space="preserve">
+        <v xml:space="preserve">PD × LGD × Exposure expressed in USD. Calculated forward-looking loss metric supporting provisioning, capital planning, and stress testing analytics.
+</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Expected Loss ($)</v>
+      </c>
+      <c r="D24" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(expected_loss_usd) per facility from stress_test_result. Weighted by bank share percentage.
+</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I24" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="J24" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(expected_loss_usd) per facility from stress_test_result. Weighted by bank share percentage.
+</v>
+      </c>
+      <c r="K24" t="str">
+        <v>Expected Loss ($) (facility)</v>
+      </c>
+      <c r="L24" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M24" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N24" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level expected_loss_usd per counterparty.
+</v>
+      </c>
+      <c r="O24" t="str">
+        <v>Expected Loss ($) (counterparty)</v>
+      </c>
+      <c r="P24" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q24" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R24" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level expected_loss_usd per L3 desk segment.
+</v>
+      </c>
+      <c r="S24" t="str">
+        <v>Expected Loss ($) (desk)</v>
+      </c>
+      <c r="T24" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U24" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V24" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level expected_loss_usd per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W24" t="str">
+        <v>Expected Loss ($) (portfolio)</v>
+      </c>
+      <c r="X24" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y24" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z24" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level expected_loss_usd per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA24" t="str">
+        <v>Expected Loss ($) (business_segment)</v>
+      </c>
+      <c r="AB24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25" xml:space="preserve">
+      <c r="A25" t="str">
+        <v>EXP-017</v>
+      </c>
+      <c r="B25" t="str" xml:space="preserve">
+        <v xml:space="preserve">Bank-share-adjusted unfunded commitment amount. Measures contingent funding risk by summing unfunded positions per facility, applying the bank's share percentage.
+</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Undrawn Exposure ($)</v>
+      </c>
+      <c r="D25" t="str" xml:space="preserve">
+        <v xml:space="preserve">For each active facility:
+1. Join position → position_detail on position_id (both as_of_date filtered)
+2. SUM(unfunded_amount) across all positions for the facility
+3. Multiply by COALESCE(bank_share_pct, 1.0) for bank-share-adjusted exposure
+</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I25" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="J25" t="str" xml:space="preserve">
+        <v xml:space="preserve">For each active facility:
+1. Join position → position_detail on position_id (both as_of_date filtered)
+2. SUM(unfunded_amount) across all positions for the facility
+3. Multiply by COALESCE(bank_share_pct, 1.0) for bank-share-adjusted exposure
+</v>
+      </c>
+      <c r="K25" t="str">
+        <v>Undrawn Exposure ($) (facility)</v>
+      </c>
+      <c r="L25" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M25" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="N25" t="str" xml:space="preserve">
+        <v xml:space="preserve">For each counterparty, sum facility-level undrawn exposure weighted
+by participation_pct from facility_counterparty_participation.
+</v>
+      </c>
+      <c r="O25" t="str">
+        <v>Undrawn Exposure ($) (counterparty)</v>
+      </c>
+      <c r="P25" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q25" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R25" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level undrawn exposure per L3 desk segment.
+</v>
+      </c>
+      <c r="S25" t="str">
+        <v>Undrawn Exposure ($) (desk)</v>
+      </c>
+      <c r="T25" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U25" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V25" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level undrawn exposure per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W25" t="str">
+        <v>Undrawn Exposure ($) (portfolio)</v>
+      </c>
+      <c r="X25" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y25" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z25" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level undrawn exposure per L1 business segment.
+</v>
+      </c>
+      <c r="AA25" t="str">
+        <v>Undrawn Exposure ($) (business_segment)</v>
+      </c>
+      <c r="AB25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26" xml:space="preserve">
+      <c r="A26" t="str">
+        <v>EXP-018</v>
+      </c>
+      <c r="B26" t="str" xml:space="preserve">
+        <v xml:space="preserve">Portion of committed exposure currently available and not yet drawn. Used to assess funding deployment and credit capacity usage.
+</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Oustanding Exposure ($)</v>
+      </c>
+      <c r="D26" t="str" xml:space="preserve">
+        <v xml:space="preserve">For each Distinct([Facility ID]), WHEN IS(MAX(AS_OF_DATE) AND [Facility_Active_Flag]="Y", THEN Lookup [Position_ID] within Positions table WHEN IS([Facility_ID]) FOR each [Facility_ID] SUM(ARRAY{[funded_amount]} for each [Position_ID]}) * [Bank_Share] == [Facility Oustanding Exposure, Bank Share Only]
+</v>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I26" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="J26" t="str" xml:space="preserve">
+        <v xml:space="preserve">For each Distinct([Facility ID]), WHEN IS(MAX(AS_OF_DATE) AND [Facility_Active_Flag]="Y", THEN Lookup [Position_ID] within Positions table WHEN IS([Facility_ID]) FOR each [Facility_ID] SUM(ARRAY{[funded_amount]} for each [Position_ID]}) * [Bank_Share] == [Facility Oustanding Exposure, Bank Share Only]
+</v>
+      </c>
+      <c r="K26" t="str">
+        <v>Oustanding Exposure ($) (facility)</v>
+      </c>
+      <c r="L26" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M26" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N26" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level funded_amount per counterparty.
+</v>
+      </c>
+      <c r="O26" t="str">
+        <v>Oustanding Exposure ($) (counterparty)</v>
+      </c>
+      <c r="P26" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q26" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R26" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level funded_amount per L3 desk segment.
+</v>
+      </c>
+      <c r="S26" t="str">
+        <v>Oustanding Exposure ($) (desk)</v>
+      </c>
+      <c r="T26" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U26" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V26" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level funded_amount per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W26" t="str">
+        <v>Oustanding Exposure ($) (portfolio)</v>
+      </c>
+      <c r="X26" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y26" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z26" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level funded_amount per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA26" t="str">
+        <v>Oustanding Exposure ($) (business_segment)</v>
+      </c>
+      <c r="AB26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27" xml:space="preserve">
+      <c r="A27" t="str">
+        <v>EXP-019</v>
+      </c>
+      <c r="B27" t="str" xml:space="preserve">
+        <v xml:space="preserve">Maximum approved credit exposure authorized for the counterparty or Line of Business segment in USD. Represents formal risk appetite allocation and governance control threshold.
+</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Exposure Limit ($)</v>
+      </c>
+      <c r="D27" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read limit_amt from lob_exposure_summary for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I27" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J27" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read limit_amt from lob_exposure_summary for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="K27" t="str">
+        <v>Exposure Limit ($) (facility)</v>
+      </c>
+      <c r="L27" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M27" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="N27" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read limit_amt per counterparty.
+</v>
+      </c>
+      <c r="O27" t="str">
+        <v>Exposure Limit ($) (counterparty)</v>
+      </c>
+      <c r="P27" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q27" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R27" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level limit_amt per L3 desk segment.
+</v>
+      </c>
+      <c r="S27" t="str">
+        <v>Exposure Limit ($) (desk)</v>
+      </c>
+      <c r="T27" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U27" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V27" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level limit_amt per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W27" t="str">
+        <v>Exposure Limit ($) (portfolio)</v>
+      </c>
+      <c r="X27" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y27" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z27" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level limit_amt per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA27" t="str">
+        <v>Exposure Limit ($) (business_segment)</v>
+      </c>
+      <c r="AB27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28" xml:space="preserve">
+      <c r="A28" t="str">
+        <v>EXP-020</v>
+      </c>
+      <c r="B28" t="str" xml:space="preserve">
+        <v xml:space="preserve">The estimated exposure amount (in USD) expected to be outstanding if the borrower defaults.
+</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Exposure at Default ($)</v>
+      </c>
+      <c r="D28" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read exposure_at_default from credit_event_facility_link for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I28" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J28" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read exposure_at_default from credit_event_facility_link for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="K28" t="str">
+        <v>Exposure at Default ($) (facility)</v>
+      </c>
+      <c r="L28" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M28" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N28" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level exposure_at_default per counterparty.
+</v>
+      </c>
+      <c r="O28" t="str">
+        <v>Exposure at Default ($) (counterparty)</v>
+      </c>
+      <c r="P28" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q28" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R28" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level exposure_at_default per L3 desk segment.
+</v>
+      </c>
+      <c r="S28" t="str">
+        <v>Exposure at Default ($) (desk)</v>
+      </c>
+      <c r="T28" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U28" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V28" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level exposure_at_default per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W28" t="str">
+        <v>Exposure at Default ($) (portfolio)</v>
+      </c>
+      <c r="X28" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y28" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z28" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level exposure_at_default per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA28" t="str">
+        <v>Exposure at Default ($) (business_segment)</v>
+      </c>
+      <c r="AB28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29" xml:space="preserve">
+      <c r="A29" t="str">
+        <v>EXP-021</v>
+      </c>
+      <c r="B29" t="str" xml:space="preserve">
+        <v xml:space="preserve">Derived categorical classification (Sufficient, Approaching, Fully Utilized) of utilization level based on current drawn exposure relative to committed amount. Operational KPI providing early warning insight into limit pressure, liquidity usage, and potential capacity constraints.
+</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Facility Utilization Status (e.g., Sufficient, Approaching, Fully Utilized)</v>
+      </c>
+      <c r="D29" t="str" xml:space="preserve">
+        <v xml:space="preserve">Calculated facility_utilization_status per facility.
+</v>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I29" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="J29" t="str" xml:space="preserve">
+        <v xml:space="preserve">Calculated facility_utilization_status per facility.
+</v>
+      </c>
+      <c r="K29" t="str">
+        <v>Facility Utilization Status (e.g., Sufficient, Approaching, Fully Utilized) (facility)</v>
+      </c>
+      <c r="L29" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M29" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N29" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(facility-level facility_utilization_status) per counterparty.
+</v>
+      </c>
+      <c r="O29" t="str">
+        <v>Facility Utilization Status (e.g., Sufficient, Approaching, Fully Utilized) (counterparty)</v>
+      </c>
+      <c r="P29" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q29" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R29" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level facility_utilization_status per L3 desk segment.
+</v>
+      </c>
+      <c r="S29" t="str">
+        <v>Facility Utilization Status (e.g., Sufficient, Approaching, Fully Utilized) (desk)</v>
+      </c>
+      <c r="T29" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U29" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V29" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level facility_utilization_status per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W29" t="str">
+        <v>Facility Utilization Status (e.g., Sufficient, Approaching, Fully Utilized) (portfolio)</v>
+      </c>
+      <c r="X29" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y29" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z29" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level facility_utilization_status per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA29" t="str">
+        <v>Facility Utilization Status (e.g., Sufficient, Approaching, Fully Utilized) (business_segment)</v>
+      </c>
+      <c r="AB29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30" xml:space="preserve">
+      <c r="A30" t="str">
+        <v>EXP-022</v>
+      </c>
+      <c r="B30" t="str" xml:space="preserve">
+        <v xml:space="preserve">Indicator of exposure allocated across multiple legal entities. Portfolio KPI (% Cross-Entity Exposure) highlights structural complexity.
+</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Cross Entity Exposure Flag</v>
+      </c>
+      <c r="D30" t="str" xml:space="preserve">
+        <v xml:space="preserve">Exposure-weighted average of has_cross_entity_flag per facility.
+</v>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I30" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="J30" t="str" xml:space="preserve">
+        <v xml:space="preserve">Exposure-weighted average of has_cross_entity_flag per facility.
+</v>
+      </c>
+      <c r="K30" t="str">
+        <v>Cross Entity Exposure Flag (facility)</v>
+      </c>
+      <c r="L30" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M30" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N30" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level has_cross_entity_flag per counterparty.
+</v>
+      </c>
+      <c r="O30" t="str">
+        <v>Cross Entity Exposure Flag (counterparty)</v>
+      </c>
+      <c r="P30" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q30" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="R30" t="str" xml:space="preserve">
+        <v xml:space="preserve">AVG of facility-level has_cross_entity_flag per L3 desk segment.
+</v>
+      </c>
+      <c r="S30" t="str">
+        <v>Cross Entity Exposure Flag (desk)</v>
+      </c>
+      <c r="T30" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U30" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="V30" t="str" xml:space="preserve">
+        <v xml:space="preserve">AVG of facility-level has_cross_entity_flag per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W30" t="str">
+        <v>Cross Entity Exposure Flag (portfolio)</v>
+      </c>
+      <c r="X30" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y30" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="Z30" t="str" xml:space="preserve">
+        <v xml:space="preserve">AVG of facility-level has_cross_entity_flag per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA30" t="str">
+        <v>Cross Entity Exposure Flag (business_segment)</v>
+      </c>
+      <c r="AB30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31" xml:space="preserve">
+      <c r="A31" t="str">
+        <v>EXP-023</v>
+      </c>
+      <c r="B31" t="str" xml:space="preserve">
+        <v xml:space="preserve">Exposure × LGD expressed in dollar terms weighted based on facility-level exposure. Derived loss severity metric estimating expected recovery-adjusted loss magnitude.
+</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Loss Given Default ($)</v>
+      </c>
+      <c r="D31" t="str" xml:space="preserve">
+        <v xml:space="preserve">EAD * LGD (in Percentage) for all facilities across Counterparties
+</v>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v/>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I31" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="J31" t="str" xml:space="preserve">
+        <v xml:space="preserve">EAD * LGD (in Percentage) for all facilities across Counterparties
+</v>
+      </c>
+      <c r="K31" t="str">
+        <v>Loss Given Default ($) (facility)</v>
+      </c>
+      <c r="L31" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M31" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N31" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level lgd_estimate per counterparty.
+</v>
+      </c>
+      <c r="O31" t="str">
+        <v>Loss Given Default ($) (counterparty)</v>
+      </c>
+      <c r="P31" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q31" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R31" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level lgd_estimate per L3 desk segment.
+</v>
+      </c>
+      <c r="S31" t="str">
+        <v>Loss Given Default ($) (desk)</v>
+      </c>
+      <c r="T31" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U31" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V31" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level lgd_estimate per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W31" t="str">
+        <v>Loss Given Default ($) (portfolio)</v>
+      </c>
+      <c r="X31" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y31" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z31" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level lgd_estimate per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA31" t="str">
+        <v>Loss Given Default ($) (business_segment)</v>
+      </c>
+      <c r="AB31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32" xml:space="preserve">
+      <c r="A32" t="str">
+        <v>EXP-024</v>
+      </c>
+      <c r="B32" t="str" xml:space="preserve">
+        <v xml:space="preserve">Status of credit limit (Active, Warning, Breach). Used to monitor risk appetite breaches and exposure governance compliance.
+</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Limit Status</v>
+      </c>
+      <c r="D32" t="str" xml:space="preserve">
+        <v xml:space="preserve">Calculated limit_status_code per facility.
+</v>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <v/>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I32" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="J32" t="str" xml:space="preserve">
+        <v xml:space="preserve">Calculated limit_status_code per facility.
+</v>
+      </c>
+      <c r="K32" t="str">
+        <v>Limit Status (facility)</v>
+      </c>
+      <c r="L32" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M32" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N32" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level limit_status_code per counterparty.
+</v>
+      </c>
+      <c r="O32" t="str">
+        <v>Limit Status (counterparty)</v>
+      </c>
+      <c r="P32" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q32" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R32" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level limit_status_code per L3 desk segment.
+</v>
+      </c>
+      <c r="S32" t="str">
+        <v>Limit Status (desk)</v>
+      </c>
+      <c r="T32" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U32" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V32" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level limit_status_code per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W32" t="str">
+        <v>Limit Status (portfolio)</v>
+      </c>
+      <c r="X32" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y32" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z32" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level limit_status_code per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA32" t="str">
+        <v>Limit Status (business_segment)</v>
+      </c>
+      <c r="AB32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33" xml:space="preserve">
+      <c r="A33" t="str">
+        <v>EXP-025</v>
+      </c>
+      <c r="B33" t="str" xml:space="preserve">
+        <v xml:space="preserve">The average expected loss rate (percent of exposure) if default occurs, weighted across exposures (typically by EAD).
+</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Loss Given Default (%)</v>
+      </c>
+      <c r="D33" t="str" xml:space="preserve">
+        <v xml:space="preserve">Calculated lgd_pct per facility.
+</v>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I33" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="J33" t="str" xml:space="preserve">
+        <v xml:space="preserve">Calculated lgd_pct per facility.
+</v>
+      </c>
+      <c r="K33" t="str">
+        <v>Loss Given Default (%) (facility)</v>
+      </c>
+      <c r="L33" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M33" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="N33" t="str" xml:space="preserve">
+        <v xml:space="preserve">Exposure-weighted average of lgd_pct across counterparty facilities.
+</v>
+      </c>
+      <c r="O33" t="str">
+        <v>Loss Given Default (%) (counterparty)</v>
+      </c>
+      <c r="P33" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q33" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R33" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level lgd_pct per L3 desk segment.
+</v>
+      </c>
+      <c r="S33" t="str">
+        <v>Loss Given Default (%) (desk)</v>
+      </c>
+      <c r="T33" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U33" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V33" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level lgd_pct per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W33" t="str">
+        <v>Loss Given Default (%) (portfolio)</v>
+      </c>
+      <c r="X33" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y33" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z33" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level lgd_pct per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA33" t="str">
+        <v>Loss Given Default (%) (business_segment)</v>
+      </c>
+      <c r="AB33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34" xml:space="preserve">
+      <c r="A34" t="str">
+        <v>EXP-026</v>
+      </c>
+      <c r="B34" t="str" xml:space="preserve">
+        <v xml:space="preserve">Loan to Value Ratio (%) metric.
+</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Loan to Value Ratio (%)</v>
+      </c>
+      <c r="D34" t="str" xml:space="preserve">
+        <v xml:space="preserve">For each DISTINCT (Facility_ID) lookup Collateral ID and SUM(Current_Colalteral_MV) THEN  [Commited_Facility_Amt] / [Current_Collateral_MV] × 100
+</v>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v/>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+      <c r="H34" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I34" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="J34" t="str" xml:space="preserve">
+        <v xml:space="preserve">For each DISTINCT (Facility_ID) lookup Collateral ID and SUM(Current_Colalteral_MV) THEN  [Commited_Facility_Amt] / [Current_Collateral_MV] × 100
+</v>
+      </c>
+      <c r="K34" t="str">
+        <v>Loan to Value Ratio (%) (facility)</v>
+      </c>
+      <c r="L34" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M34" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N34" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level ltv_pct per counterparty.
+</v>
+      </c>
+      <c r="O34" t="str">
+        <v>Loan to Value Ratio (%) (counterparty)</v>
+      </c>
+      <c r="P34" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q34" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R34" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level ltv_pct per L3 desk segment.
+</v>
+      </c>
+      <c r="S34" t="str">
+        <v>Loan to Value Ratio (%) (desk)</v>
+      </c>
+      <c r="T34" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U34" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V34" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level ltv_pct per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W34" t="str">
+        <v>Loan to Value Ratio (%) (portfolio)</v>
+      </c>
+      <c r="X34" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y34" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z34" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level ltv_pct per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA34" t="str">
+        <v>Loan to Value Ratio (%) (business_segment)</v>
+      </c>
+      <c r="AB34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35" xml:space="preserve">
+      <c r="A35" t="str">
+        <v>EXP-027</v>
+      </c>
+      <c r="B35" t="str" xml:space="preserve">
+        <v xml:space="preserve">Profit after all expenses in USD. Indicator of borrower profitability and financial sustainability.
+</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Net Income ($)</v>
+      </c>
+      <c r="D35" t="str" xml:space="preserve">
+        <v xml:space="preserve">Revenue – Interest Expense – Operating Cost – EL
+</v>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v/>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+      <c r="H35" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I35" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="J35" t="str" xml:space="preserve">
+        <v xml:space="preserve">Revenue – Interest Expense – Operating Cost – EL
+</v>
+      </c>
+      <c r="K35" t="str">
+        <v>Net Income ($) (facility)</v>
+      </c>
+      <c r="L35" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M35" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N35" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level net_income_amt per counterparty.
+</v>
+      </c>
+      <c r="O35" t="str">
+        <v>Net Income ($) (counterparty)</v>
+      </c>
+      <c r="P35" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q35" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R35" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level net_income_amt per L3 desk segment.
+</v>
+      </c>
+      <c r="S35" t="str">
+        <v>Net Income ($) (desk)</v>
+      </c>
+      <c r="T35" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U35" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V35" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level net_income_amt per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W35" t="str">
+        <v>Net Income ($) (portfolio)</v>
+      </c>
+      <c r="X35" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y35" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z35" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level net_income_amt per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA35" t="str">
+        <v>Net Income ($) (business_segment)</v>
+      </c>
+      <c r="AB35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36" xml:space="preserve">
+      <c r="A36" t="str">
+        <v>EXP-028</v>
+      </c>
+      <c r="B36" t="str" xml:space="preserve">
+        <v xml:space="preserve">Net Interest Income divided by earning assets. Calculated margin KPI assessing pricing effectiveness and lending profitability.
+</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Net Interest Margin (%)</v>
+      </c>
+      <c r="D36" t="str" xml:space="preserve">
+        <v xml:space="preserve">(Interest Income - Interst Expense)/Average Earning Assets
+</v>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v/>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+      <c r="H36" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I36" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="J36" t="str" xml:space="preserve">
+        <v xml:space="preserve">(Interest Income - Interst Expense)/Average Earning Assets
+</v>
+      </c>
+      <c r="K36" t="str">
+        <v>Net Interest Margin (%) (facility)</v>
+      </c>
+      <c r="L36" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M36" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="N36" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(net_interest_income) / SUM(avg_earning_assets) * 100.0 per counterparty.
+</v>
+      </c>
+      <c r="O36" t="str">
+        <v>Net Interest Margin (%) (counterparty)</v>
+      </c>
+      <c r="P36" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q36" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="R36" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(net_interest_income) / SUM(avg_earning_assets) * 100.0 per L3 desk segment.
+</v>
+      </c>
+      <c r="S36" t="str">
+        <v>Net Interest Margin (%) (desk)</v>
+      </c>
+      <c r="T36" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U36" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="V36" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(net_interest_income) / SUM(avg_earning_assets) * 100.0 per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W36" t="str">
+        <v>Net Interest Margin (%) (portfolio)</v>
+      </c>
+      <c r="X36" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y36" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="Z36" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(net_interest_income) / SUM(avg_earning_assets) * 100.0 per L1 business segment.
+</v>
+      </c>
+      <c r="AA36" t="str">
+        <v>Net Interest Margin (%) (business_segment)</v>
+      </c>
+      <c r="AB36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37" xml:space="preserve">
+      <c r="A37" t="str">
+        <v>EXP-029</v>
+      </c>
+      <c r="B37" t="str" xml:space="preserve">
+        <v xml:space="preserve">Allocated operating or servicing cost associated with exposure.
+</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Operating Cost ($)</v>
+      </c>
+      <c r="D37" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read operating_expense_amt from facility_financial_snapshot for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v/>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I37" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J37" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read operating_expense_amt from facility_financial_snapshot for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="K37" t="str">
+        <v>Operating Cost ($) (facility)</v>
+      </c>
+      <c r="L37" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M37" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="N37" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read operating_expense_amt per counterparty.
+</v>
+      </c>
+      <c r="O37" t="str">
+        <v>Operating Cost ($) (counterparty)</v>
+      </c>
+      <c r="P37" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q37" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R37" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level operating_expense_amt per L3 desk segment.
+</v>
+      </c>
+      <c r="S37" t="str">
+        <v>Operating Cost ($) (desk)</v>
+      </c>
+      <c r="T37" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U37" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="V37" t="str" xml:space="preserve">
+        <v xml:space="preserve">AVG of facility-level operating_expense_amt per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W37" t="str">
+        <v>Operating Cost ($) (portfolio)</v>
+      </c>
+      <c r="X37" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y37" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="Z37" t="str" xml:space="preserve">
+        <v xml:space="preserve">AVG of facility-level operating_expense_amt per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA37" t="str">
+        <v>Operating Cost ($) (business_segment)</v>
+      </c>
+      <c r="AB37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38" xml:space="preserve">
+      <c r="A38" t="str">
+        <v>EXP-030</v>
+      </c>
+      <c r="B38" t="str" xml:space="preserve">
+        <v xml:space="preserve">Model-estimated probability of default within defined horizon. Core credit risk input supporting capital modeling, expected loss estimation, stress testing, and risk appetite alignment.
+</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Probability of Default (%)</v>
+      </c>
+      <c r="D38" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read pd_pct from facility_risk_snapshot for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v/>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I38" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J38" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read pd_pct from facility_risk_snapshot for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="K38" t="str">
+        <v>Probability of Default (%) (facility)</v>
+      </c>
+      <c r="L38" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M38" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N38" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level pd_pct per counterparty.
+</v>
+      </c>
+      <c r="O38" t="str">
+        <v>Probability of Default (%) (counterparty)</v>
+      </c>
+      <c r="P38" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q38" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="R38" t="str" xml:space="preserve">
+        <v xml:space="preserve">AVG of facility-level pd_pct per L3 desk segment.
+</v>
+      </c>
+      <c r="S38" t="str">
+        <v>Probability of Default (%) (desk)</v>
+      </c>
+      <c r="T38" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U38" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="V38" t="str" xml:space="preserve">
+        <v xml:space="preserve">AVG of facility-level pd_pct per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W38" t="str">
+        <v>Probability of Default (%) (portfolio)</v>
+      </c>
+      <c r="X38" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y38" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z38" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level pd_pct per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA38" t="str">
+        <v>Probability of Default (%) (business_segment)</v>
+      </c>
+      <c r="AB38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39" xml:space="preserve">
+      <c r="A39" t="str">
+        <v>EXP-031</v>
+      </c>
+      <c r="B39" t="str" xml:space="preserve">
+        <v xml:space="preserve">Total income generated by the borrower or attributed to the facility in millions USD. Used to assess scale and repayment capacity.
+</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Revenue ($)</v>
+      </c>
+      <c r="D39" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(revenue_amt) per facility from facility_financial_snapshot. Weighted by bank share percentage.
+</v>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I39" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="J39" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(revenue_amt) per facility from facility_financial_snapshot. Weighted by bank share percentage.
+</v>
+      </c>
+      <c r="K39" t="str">
+        <v>Revenue ($) (facility)</v>
+      </c>
+      <c r="L39" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M39" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N39" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level revenue_amt per counterparty.
+</v>
+      </c>
+      <c r="O39" t="str">
+        <v>Revenue ($) (counterparty)</v>
+      </c>
+      <c r="P39" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q39" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R39" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level revenue_amt per L3 desk segment.
+</v>
+      </c>
+      <c r="S39" t="str">
+        <v>Revenue ($) (desk)</v>
+      </c>
+      <c r="T39" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U39" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V39" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level revenue_amt per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W39" t="str">
+        <v>Revenue ($) (portfolio)</v>
+      </c>
+      <c r="X39" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y39" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z39" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level revenue_amt per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA39" t="str">
+        <v>Revenue ($) (business_segment)</v>
+      </c>
+      <c r="AB39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40" xml:space="preserve">
+      <c r="A40" t="str">
+        <v>EXP-032</v>
+      </c>
+      <c r="B40" t="str" xml:space="preserve">
+        <v xml:space="preserve">Original Appriased Value of pledged collateral securing exposure in USD. Supports recovery analysis and secured lending assessment.
+</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Collateral Market Value at Origination ($)</v>
+      </c>
+      <c r="D40" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(original_valuation_usd) per facility from collateral_snapshot. Weighted by bank share percentage.
+</v>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v/>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I40" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="J40" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(original_valuation_usd) per facility from collateral_snapshot. Weighted by bank share percentage.
+</v>
+      </c>
+      <c r="K40" t="str">
+        <v>Collateral Market Value at Origination ($) (facility)</v>
+      </c>
+      <c r="L40" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M40" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N40" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level original_valuation_usd per counterparty.
+</v>
+      </c>
+      <c r="O40" t="str">
+        <v>Collateral Market Value at Origination ($) (counterparty)</v>
+      </c>
+      <c r="P40" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q40" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R40" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level original_valuation_usd per L3 desk segment.
+</v>
+      </c>
+      <c r="S40" t="str">
+        <v>Collateral Market Value at Origination ($) (desk)</v>
+      </c>
+      <c r="T40" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U40" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V40" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level original_valuation_usd per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W40" t="str">
+        <v>Collateral Market Value at Origination ($) (portfolio)</v>
+      </c>
+      <c r="X40" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y40" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z40" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level original_valuation_usd per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA40" t="str">
+        <v>Collateral Market Value at Origination ($) (business_segment)</v>
+      </c>
+      <c r="AB40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41" xml:space="preserve">
+      <c r="A41" t="str">
+        <v>EXP-033</v>
+      </c>
+      <c r="B41" t="str" xml:space="preserve">
+        <v xml:space="preserve">Sub-classification of risk mitigant or collateral type tied to the facility. Used for granular risk segmentation.
+</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Risk Mitigant Sub Type</v>
+      </c>
+      <c r="D41" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(risk_mitigant_subtype_code) per facility from risk_mitigant_type_dim.
+</v>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v/>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I41" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="J41" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(risk_mitigant_subtype_code) per facility from risk_mitigant_type_dim.
+</v>
+      </c>
+      <c r="K41" t="str">
+        <v>Risk Mitigant Sub Type (facility)</v>
+      </c>
+      <c r="L41" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M41" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="N41" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read risk_mitigant_subtype_code per counterparty.
+</v>
+      </c>
+      <c r="O41" t="str">
+        <v>Risk Mitigant Sub Type (counterparty)</v>
+      </c>
+      <c r="P41" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q41" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R41" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level risk_mitigant_subtype_code per L3 desk segment.
+</v>
+      </c>
+      <c r="S41" t="str">
+        <v>Risk Mitigant Sub Type (desk)</v>
+      </c>
+      <c r="T41" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U41" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V41" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level risk_mitigant_subtype_code per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W41" t="str">
+        <v>Risk Mitigant Sub Type (portfolio)</v>
+      </c>
+      <c r="X41" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y41" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z41" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level risk_mitigant_subtype_code per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA41" t="str">
+        <v>Risk Mitigant Sub Type (business_segment)</v>
+      </c>
+      <c r="AB41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42" xml:space="preserve">
+      <c r="A42" t="str">
+        <v>EXP-034</v>
+      </c>
+      <c r="B42" t="str" xml:space="preserve">
+        <v xml:space="preserve">Parent group of risk mitigation or collateral asset type (e.g., cash, aviation, guarantee). Used to assess recovery support mechanisms.
+</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Risk Mitigant Type</v>
+      </c>
+      <c r="D42" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(risk_mitigant_id) per facility from risk_mitigant_master.
+</v>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v/>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+      <c r="H42" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I42" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="J42" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(risk_mitigant_id) per facility from risk_mitigant_master.
+</v>
+      </c>
+      <c r="K42" t="str">
+        <v>Risk Mitigant Type (facility)</v>
+      </c>
+      <c r="L42" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M42" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="N42" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read risk_mitigant_id per counterparty.
+</v>
+      </c>
+      <c r="O42" t="str">
+        <v>Risk Mitigant Type (counterparty)</v>
+      </c>
+      <c r="P42" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q42" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R42" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level risk_mitigant_id per L3 desk segment.
+</v>
+      </c>
+      <c r="S42" t="str">
+        <v>Risk Mitigant Type (desk)</v>
+      </c>
+      <c r="T42" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U42" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V42" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level risk_mitigant_id per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W42" t="str">
+        <v>Risk Mitigant Type (portfolio)</v>
+      </c>
+      <c r="X42" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y42" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z42" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level risk_mitigant_id per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA42" t="str">
+        <v>Risk Mitigant Type (business_segment)</v>
+      </c>
+      <c r="AB42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43" xml:space="preserve">
+      <c r="A43" t="str">
+        <v>EXP-035</v>
+      </c>
+      <c r="B43" t="str" xml:space="preserve">
+        <v xml:space="preserve">Net Income divided by Total Assets. Calculated efficiency KPI measuring asset productivity and overall financial performance.
+</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Return on Assets (%)</v>
+      </c>
+      <c r="D43" t="str" xml:space="preserve">
+        <v xml:space="preserve">Facility Net Income / Facility Exposure
+</v>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+      <c r="H43" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I43" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="J43" t="str" xml:space="preserve">
+        <v xml:space="preserve">Facility Net Income / Facility Exposure
+</v>
+      </c>
+      <c r="K43" t="str">
+        <v>Return on Assets (%) (facility)</v>
+      </c>
+      <c r="L43" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M43" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="N43" t="str" xml:space="preserve">
+        <v xml:space="preserve">Net Income / Total Assets * 100 per counterparty (direct from financials).
+</v>
+      </c>
+      <c r="O43" t="str">
+        <v>Return on Assets (%) (counterparty)</v>
+      </c>
+      <c r="P43" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q43" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="R43" t="str" xml:space="preserve">
+        <v xml:space="preserve">Exposure-weighted average ROA per L3 desk segment.
+</v>
+      </c>
+      <c r="S43" t="str">
+        <v>Return on Assets (%) (desk)</v>
+      </c>
+      <c r="T43" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U43" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="V43" t="str" xml:space="preserve">
+        <v xml:space="preserve">Exposure-weighted average ROA per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W43" t="str">
+        <v>Return on Assets (%) (portfolio)</v>
+      </c>
+      <c r="X43" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y43" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="Z43" t="str" xml:space="preserve">
+        <v xml:space="preserve">Exposure-weighted average ROA per L1 business segment.
+</v>
+      </c>
+      <c r="AA43" t="str">
+        <v>Return on Assets (%) (business_segment)</v>
+      </c>
+      <c r="AB43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44" xml:space="preserve">
+      <c r="A44" t="str">
+        <v>EXP-036</v>
+      </c>
+      <c r="B44" t="str" xml:space="preserve">
+        <v xml:space="preserve">Net Income divided by Equity. Calculated profitability KPI measuring return generated on shareholder capital and supporting performance benchmarking.
+</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Return on Equity (%)</v>
+      </c>
+      <c r="D44" t="str" xml:space="preserve">
+        <v xml:space="preserve">Net Income (Facility) / Allocated Equity (Facility)
+</v>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v/>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I44" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="J44" t="str" xml:space="preserve">
+        <v xml:space="preserve">Net Income (Facility) / Allocated Equity (Facility)
+</v>
+      </c>
+      <c r="K44" t="str">
+        <v>Return on Equity (%) (facility)</v>
+      </c>
+      <c r="L44" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M44" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="N44" t="str" xml:space="preserve">
+        <v xml:space="preserve">Net Income / Shareholders Equity * 100 per counterparty (direct from financials).
+</v>
+      </c>
+      <c r="O44" t="str">
+        <v>Return on Equity (%) (counterparty)</v>
+      </c>
+      <c r="P44" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q44" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="R44" t="str" xml:space="preserve">
+        <v xml:space="preserve">Exposure-weighted average ROE per L3 desk segment.
+</v>
+      </c>
+      <c r="S44" t="str">
+        <v>Return on Equity (%) (desk)</v>
+      </c>
+      <c r="T44" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U44" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="V44" t="str" xml:space="preserve">
+        <v xml:space="preserve">Exposure-weighted average ROE per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W44" t="str">
+        <v>Return on Equity (%) (portfolio)</v>
+      </c>
+      <c r="X44" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y44" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="Z44" t="str" xml:space="preserve">
+        <v xml:space="preserve">Exposure-weighted average ROE per L1 business segment.
+</v>
+      </c>
+      <c r="AA44" t="str">
+        <v>Return on Equity (%) (business_segment)</v>
+      </c>
+      <c r="AB44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45" xml:space="preserve">
+      <c r="A45" t="str">
+        <v>EXP-037</v>
+      </c>
+      <c r="B45" t="str" xml:space="preserve">
+        <v xml:space="preserve">Total principal and interest obligations due within reporting period in millions USD. Used in repayment capacity and covenant analysis.
+</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Total Debt Service ($)</v>
+      </c>
+      <c r="D45" t="str" xml:space="preserve">
+        <v xml:space="preserve">Lookup Position_ID for each Facility_ID, Select bank_share and cost_of_funds from Facility_ID from Facility Master THEN (unfunded_amt * bank_share ) = [Facility Debt Service w/ Bank Share]
+</v>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
+        <v/>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I45" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="J45" t="str" xml:space="preserve">
+        <v xml:space="preserve">Lookup Position_ID for each Facility_ID, Select bank_share and cost_of_funds from Facility_ID from Facility Master THEN (unfunded_amt * bank_share ) = [Facility Debt Service w/ Bank Share]
+</v>
+      </c>
+      <c r="K45" t="str">
+        <v>Total Debt Service ($) (facility)</v>
+      </c>
+      <c r="L45" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M45" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N45" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level total_debt_service_amt per counterparty.
+</v>
+      </c>
+      <c r="O45" t="str">
+        <v>Total Debt Service ($) (counterparty)</v>
+      </c>
+      <c r="P45" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q45" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R45" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level total_debt_service_amt per L3 desk segment.
+</v>
+      </c>
+      <c r="S45" t="str">
+        <v>Total Debt Service ($) (desk)</v>
+      </c>
+      <c r="T45" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U45" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V45" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level total_debt_service_amt per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W45" t="str">
+        <v>Total Debt Service ($) (portfolio)</v>
+      </c>
+      <c r="X45" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y45" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z45" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level total_debt_service_amt per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA45" t="str">
+        <v>Total Debt Service ($) (business_segment)</v>
+      </c>
+      <c r="AB45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46" xml:space="preserve">
+      <c r="A46" t="str">
+        <v>EXP-038</v>
+      </c>
+      <c r="B46" t="str" xml:space="preserve">
+        <v xml:space="preserve">Exposure divided by Exposure Limit. Calculated KPI measuring the proportion of approved capacity currently drawn, providing insight into liquidity usage and limit pressure.
+</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Utilization (%)</v>
+      </c>
+      <c r="D46" t="str" xml:space="preserve">
+        <v xml:space="preserve">For each Distinct([Facility ID]), WHEN IS(MAX(AS_OF_DATE) AND [Facility_Active_Flag]="Y" Sum([Utilized Exposure] / [Committed_Facility_Amt])
+</v>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v/>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+      <c r="H46" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I46" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="J46" t="str" xml:space="preserve">
+        <v xml:space="preserve">For each Distinct([Facility ID]), WHEN IS(MAX(AS_OF_DATE) AND [Facility_Active_Flag]="Y" Sum([Utilized Exposure] / [Committed_Facility_Amt])
+</v>
+      </c>
+      <c r="K46" t="str">
+        <v>Utilization (%) (facility)</v>
+      </c>
+      <c r="L46" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M46" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="N46" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(drawn_amount) / SUM(committed_amount) * 100.0 per counterparty.
+</v>
+      </c>
+      <c r="O46" t="str">
+        <v>Utilization (%) (counterparty)</v>
+      </c>
+      <c r="P46" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q46" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="R46" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(drawn_amount) / SUM(committed_amount) * 100.0 per L3 desk segment.
+</v>
+      </c>
+      <c r="S46" t="str">
+        <v>Utilization (%) (desk)</v>
+      </c>
+      <c r="T46" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U46" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="V46" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(drawn_amount) / SUM(committed_amount) * 100.0 per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W46" t="str">
+        <v>Utilization (%) (portfolio)</v>
+      </c>
+      <c r="X46" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y46" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="Z46" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(drawn_amount) / SUM(committed_amount) * 100.0 per L1 business segment.
+</v>
+      </c>
+      <c r="AA46" t="str">
+        <v>Utilization (%) (business_segment)</v>
+      </c>
+      <c r="AB46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47" xml:space="preserve">
+      <c r="A47" t="str">
+        <v>EXP-039</v>
+      </c>
+      <c r="B47" t="str" xml:space="preserve">
+        <v xml:space="preserve">The currently drawn/outstanding amount (in USD) on the facility as of the reporting date.
+</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Utilized Amount ($)</v>
+      </c>
+      <c r="D47" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read utilized_amount_usd from limit_utilization_event for each facility as- of reporting date.
+</v>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v/>
+      </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
+      <c r="H47" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I47" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J47" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read utilized_amount_usd from limit_utilization_event for each facility as- of reporting date.
+</v>
+      </c>
+      <c r="K47" t="str">
+        <v>Utilized Amount ($) (facility)</v>
+      </c>
+      <c r="L47" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M47" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N47" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level utilized_amount_usd per counterparty.
+</v>
+      </c>
+      <c r="O47" t="str">
+        <v>Utilized Amount ($) (counterparty)</v>
+      </c>
+      <c r="P47" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q47" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R47" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level utilized_amount_usd per L3 desk segment.
+</v>
+      </c>
+      <c r="S47" t="str">
+        <v>Utilized Amount ($) (desk)</v>
+      </c>
+      <c r="T47" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U47" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V47" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level utilized_amount_usd per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W47" t="str">
+        <v>Utilized Amount ($) (portfolio)</v>
+      </c>
+      <c r="X47" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y47" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z47" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level utilized_amount_usd per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA47" t="str">
+        <v>Utilized Amount ($) (business_segment)</v>
+      </c>
+      <c r="AB47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48" xml:space="preserve">
+      <c r="A48" t="str">
+        <v>EXP-041</v>
+      </c>
+      <c r="B48" t="str" xml:space="preserve">
+        <v xml:space="preserve">Total interest earned on outstanding exposures during the reporting period.
+</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Interest Income</v>
+      </c>
+      <c r="D48" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(interest_income_amt) per facility from facility_profitability_snapshot. Weighted by bank share percentage.
+</v>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v/>
+      </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
+      <c r="H48" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I48" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="J48" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(interest_income_amt) per facility from facility_profitability_snapshot. Weighted by bank share percentage.
+</v>
+      </c>
+      <c r="K48" t="str">
+        <v>Interest Income (facility)</v>
+      </c>
+      <c r="L48" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M48" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N48" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level interest_income_amt per counterparty.
+</v>
+      </c>
+      <c r="O48" t="str">
+        <v>Interest Income (counterparty)</v>
+      </c>
+      <c r="P48" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q48" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R48" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level interest_income_amt per L3 desk segment.
+</v>
+      </c>
+      <c r="S48" t="str">
+        <v>Interest Income (desk)</v>
+      </c>
+      <c r="T48" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U48" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V48" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level interest_income_amt per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W48" t="str">
+        <v>Interest Income (portfolio)</v>
+      </c>
+      <c r="X48" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y48" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z48" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level interest_income_amt per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA48" t="str">
+        <v>Interest Income (business_segment)</v>
+      </c>
+      <c r="AB48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49" xml:space="preserve">
+      <c r="A49" t="str">
+        <v>EXP-042</v>
+      </c>
+      <c r="B49" t="str" xml:space="preserve">
+        <v xml:space="preserve">Total on-balance-sheet assets attributable to the reporting entity at a point in time.
+</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Total Assets Amount</v>
+      </c>
+      <c r="D49" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(total_assets_amt) per facility from counterparty_financial_snapshot. Weighted by bank share percentage.
+</v>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
+        <v/>
+      </c>
+      <c r="G49" t="str">
+        <v/>
+      </c>
+      <c r="H49" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I49" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="J49" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(total_assets_amt) per facility from counterparty_financial_snapshot. Weighted by bank share percentage.
+</v>
+      </c>
+      <c r="K49" t="str">
+        <v>Total Assets Amount (facility)</v>
+      </c>
+      <c r="L49" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M49" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N49" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level total_assets_amt per counterparty.
+</v>
+      </c>
+      <c r="O49" t="str">
+        <v>Total Assets Amount (counterparty)</v>
+      </c>
+      <c r="P49" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q49" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R49" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level total_assets_amt per L3 desk segment.
+</v>
+      </c>
+      <c r="S49" t="str">
+        <v>Total Assets Amount (desk)</v>
+      </c>
+      <c r="T49" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U49" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V49" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level total_assets_amt per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W49" t="str">
+        <v>Total Assets Amount (portfolio)</v>
+      </c>
+      <c r="X49" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y49" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z49" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level total_assets_amt per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA49" t="str">
+        <v>Total Assets Amount (business_segment)</v>
+      </c>
+      <c r="AB49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50" xml:space="preserve">
+      <c r="A50" t="str">
+        <v>EXP-043</v>
+      </c>
+      <c r="B50" t="str" xml:space="preserve">
+        <v xml:space="preserve">Total shareholder capital allocated to the reporting unit.
+</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Total Equity amount</v>
+      </c>
+      <c r="D50" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(allocated_equity_amt) per facility from facility_profitability_snapshot. Weighted by bank share percentage.
+</v>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
+        <v/>
+      </c>
+      <c r="G50" t="str">
+        <v/>
+      </c>
+      <c r="H50" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I50" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="J50" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(allocated_equity_amt) per facility from facility_profitability_snapshot. Weighted by bank share percentage.
+</v>
+      </c>
+      <c r="K50" t="str">
+        <v>Total Equity amount (facility)</v>
+      </c>
+      <c r="L50" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M50" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N50" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level allocated_equity_amt per counterparty.
+</v>
+      </c>
+      <c r="O50" t="str">
+        <v>Total Equity amount (counterparty)</v>
+      </c>
+      <c r="P50" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q50" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R50" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level allocated_equity_amt per L3 desk segment.
+</v>
+      </c>
+      <c r="S50" t="str">
+        <v>Total Equity amount (desk)</v>
+      </c>
+      <c r="T50" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U50" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V50" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level allocated_equity_amt per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W50" t="str">
+        <v>Total Equity amount (portfolio)</v>
+      </c>
+      <c r="X50" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y50" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z50" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level allocated_equity_amt per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA50" t="str">
+        <v>Total Equity amount (business_segment)</v>
+      </c>
+      <c r="AB50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51" xml:space="preserve">
+      <c r="A51" t="str">
+        <v>EXP-044</v>
+      </c>
+      <c r="B51" t="str" xml:space="preserve">
+        <v xml:space="preserve">Average balance of interest-generating assets over the reporting period.
+</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Average Earning Assets Amount</v>
+      </c>
+      <c r="D51" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read avg_earning_assets_amt from facility_profitability_snapshot for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+      <c r="F51" t="str">
+        <v/>
+      </c>
+      <c r="G51" t="str">
+        <v/>
+      </c>
+      <c r="H51" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I51" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J51" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read avg_earning_assets_amt from facility_profitability_snapshot for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="K51" t="str">
+        <v>Average Earning Assets Amount (facility)</v>
+      </c>
+      <c r="L51" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M51" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="N51" t="str" xml:space="preserve">
+        <v xml:space="preserve">Exposure-weighted average of avg_earning_assets_amt across counterparty facilities.
+</v>
+      </c>
+      <c r="O51" t="str">
+        <v>Average Earning Assets Amount (counterparty)</v>
+      </c>
+      <c r="P51" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q51" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R51" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level avg_earning_assets_amt per L3 desk segment.
+</v>
+      </c>
+      <c r="S51" t="str">
+        <v>Average Earning Assets Amount (desk)</v>
+      </c>
+      <c r="T51" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U51" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="V51" t="str" xml:space="preserve">
+        <v xml:space="preserve">AVG of facility-level avg_earning_assets_amt per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W51" t="str">
+        <v>Average Earning Assets Amount (portfolio)</v>
+      </c>
+      <c r="X51" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y51" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z51" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level avg_earning_assets_amt per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA51" t="str">
+        <v>Average Earning Assets Amount (business_segment)</v>
+      </c>
+      <c r="AB51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52" xml:space="preserve">
+      <c r="A52" t="str">
+        <v>EXP-045</v>
+      </c>
+      <c r="B52" t="str" xml:space="preserve">
+        <v xml:space="preserve">Exposure-weighted average regulatory risk weight reflecting capital intensity.
+</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Risk Weighted Average (%)</v>
+      </c>
+      <c r="D52" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(RWA Amount)/SUM(Exposure)
+</v>
+      </c>
+      <c r="E52" t="str">
+        <v/>
+      </c>
+      <c r="F52" t="str">
+        <v/>
+      </c>
+      <c r="G52" t="str">
+        <v/>
+      </c>
+      <c r="H52" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I52" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="J52" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(RWA Amount)/SUM(Exposure)
+</v>
+      </c>
+      <c r="K52" t="str">
+        <v>Risk Weighted Average (%) (facility)</v>
+      </c>
+      <c r="L52" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M52" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="N52" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(rwa) / SUM(gross_exposure) * 100.0 per counterparty.
+</v>
+      </c>
+      <c r="O52" t="str">
+        <v>Risk Weighted Average (%) (counterparty)</v>
+      </c>
+      <c r="P52" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q52" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="R52" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(rwa) / SUM(gross_exposure) * 100.0 per L3 desk segment.
+</v>
+      </c>
+      <c r="S52" t="str">
+        <v>Risk Weighted Average (%) (desk)</v>
+      </c>
+      <c r="T52" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U52" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="V52" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(rwa) / SUM(gross_exposure) * 100.0 per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W52" t="str">
+        <v>Risk Weighted Average (%) (portfolio)</v>
+      </c>
+      <c r="X52" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y52" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="Z52" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(rwa) / SUM(gross_exposure) * 100.0 per L1 business segment.
+</v>
+      </c>
+      <c r="AA52" t="str">
+        <v>Risk Weighted Average (%) (business_segment)</v>
+      </c>
+      <c r="AB52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53" xml:space="preserve">
+      <c r="A53" t="str">
+        <v>EXP-046</v>
+      </c>
+      <c r="B53" t="str" xml:space="preserve">
+        <v xml:space="preserve">Total risk-weighted assets calculated for regulatory capital purposes.
+</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Risk Weighted Average Amount ($)</v>
+      </c>
+      <c r="D53" t="str" xml:space="preserve">
+        <v xml:space="preserve">Exposure * Risk Weight %
+</v>
+      </c>
+      <c r="E53" t="str">
+        <v/>
+      </c>
+      <c r="F53" t="str">
+        <v/>
+      </c>
+      <c r="G53" t="str">
+        <v/>
+      </c>
+      <c r="H53" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I53" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="J53" t="str" xml:space="preserve">
+        <v xml:space="preserve">Exposure * Risk Weight %
+</v>
+      </c>
+      <c r="K53" t="str">
+        <v>Risk Weighted Average Amount ($) (facility)</v>
+      </c>
+      <c r="L53" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M53" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="N53" t="str" xml:space="preserve">
+        <v xml:space="preserve">Exposure-weighted average of rwa_amt across counterparty facilities.
+</v>
+      </c>
+      <c r="O53" t="str">
+        <v>Risk Weighted Average Amount ($) (counterparty)</v>
+      </c>
+      <c r="P53" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q53" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R53" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level rwa_amt per L3 desk segment.
+</v>
+      </c>
+      <c r="S53" t="str">
+        <v>Risk Weighted Average Amount ($) (desk)</v>
+      </c>
+      <c r="T53" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U53" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="V53" t="str" xml:space="preserve">
+        <v xml:space="preserve">AVG of facility-level rwa_amt per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W53" t="str">
+        <v>Risk Weighted Average Amount ($) (portfolio)</v>
+      </c>
+      <c r="X53" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y53" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="Z53" t="str" xml:space="preserve">
+        <v xml:space="preserve">AVG of facility-level rwa_amt per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA53" t="str">
+        <v>Risk Weighted Average Amount ($) (business_segment)</v>
+      </c>
+      <c r="AB53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54" xml:space="preserve">
+      <c r="A54" t="str">
+        <v>EXP-047</v>
+      </c>
+      <c r="B54" t="str" xml:space="preserve">
+        <v xml:space="preserve">Indicates how well cash flow covers fixed, non-discretionary obligations; highlights ability to withstand earnings volatility and signals potential liquidity stress/default risk.
+</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Fixed Cost Coverage Ratio (%)</v>
+      </c>
+      <c r="D54" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read fccr_value from lob_risk_ratio_summary for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+      <c r="F54" t="str">
+        <v/>
+      </c>
+      <c r="G54" t="str">
+        <v/>
+      </c>
+      <c r="H54" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I54" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J54" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read fccr_value from lob_risk_ratio_summary for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="K54" t="str">
+        <v>Fixed Cost Coverage Ratio (%) (facility)</v>
+      </c>
+      <c r="L54" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M54" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="N54" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(ebitda) / SUM(total_debt_service) per counterparty.
+</v>
+      </c>
+      <c r="O54" t="str">
+        <v>Fixed Cost Coverage Ratio (%) (counterparty)</v>
+      </c>
+      <c r="P54" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q54" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="R54" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(ebitda) / SUM(total_debt_service) per L3 desk segment.
+</v>
+      </c>
+      <c r="S54" t="str">
+        <v>Fixed Cost Coverage Ratio (%) (desk)</v>
+      </c>
+      <c r="T54" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U54" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="V54" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(ebitda) / SUM(total_debt_service) per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W54" t="str">
+        <v>Fixed Cost Coverage Ratio (%) (portfolio)</v>
+      </c>
+      <c r="X54" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y54" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="Z54" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(ebitda) / SUM(total_debt_service) per L1 business segment.
+</v>
+      </c>
+      <c r="AA54" t="str">
+        <v>Fixed Cost Coverage Ratio (%) (business_segment)</v>
+      </c>
+      <c r="AB54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55" xml:space="preserve">
+      <c r="A55" t="str">
+        <v>EXP-048</v>
+      </c>
+      <c r="B55" t="str" xml:space="preserve">
+        <v xml:space="preserve">Scheduled principal repayment obligation due for the contractual commitment.
+</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Principal Repayment Amount ($)</v>
+      </c>
+      <c r="D55" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read principal_payment_amt from facility_financial_snapshot for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
+      <c r="F55" t="str">
+        <v/>
+      </c>
+      <c r="G55" t="str">
+        <v/>
+      </c>
+      <c r="H55" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I55" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J55" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read principal_payment_amt from facility_financial_snapshot for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="K55" t="str">
+        <v>Principal Repayment Amount ($) (facility)</v>
+      </c>
+      <c r="L55" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M55" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N55" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(facility-level principal_payment_amt) per counterparty.
+</v>
+      </c>
+      <c r="O55" t="str">
+        <v>Principal Repayment Amount ($) (counterparty)</v>
+      </c>
+      <c r="P55" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q55" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R55" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level principal_payment_amt per L3 desk segment.
+</v>
+      </c>
+      <c r="S55" t="str">
+        <v>Principal Repayment Amount ($) (desk)</v>
+      </c>
+      <c r="T55" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U55" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V55" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level principal_payment_amt per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W55" t="str">
+        <v>Principal Repayment Amount ($) (portfolio)</v>
+      </c>
+      <c r="X55" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y55" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z55" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level principal_payment_amt per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA55" t="str">
+        <v>Principal Repayment Amount ($) (business_segment)</v>
+      </c>
+      <c r="AB55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56" xml:space="preserve">
+      <c r="A56" t="str">
+        <v>PRC-001</v>
+      </c>
+      <c r="B56" t="str" xml:space="preserve">
+        <v xml:space="preserve">Total effective interest rate including base rate and spread. Calculated pricing KPI that provides insight into total yield generation and supports risk-adjusted return analysis.
+</v>
+      </c>
+      <c r="C56" t="str">
+        <v>All in Rate (%)</v>
+      </c>
+      <c r="D56" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read all_in_rate_pct from facility_pricing_snapshot for each facility.
+</v>
+      </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+      <c r="F56" t="str">
+        <v/>
+      </c>
+      <c r="G56" t="str">
+        <v/>
+      </c>
+      <c r="H56" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I56" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J56" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read all_in_rate_pct from facility_pricing_snapshot for each facility.
+</v>
+      </c>
+      <c r="K56" t="str">
+        <v>All in Rate (%) (facility)</v>
+      </c>
+      <c r="L56" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M56" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="N56" t="str" xml:space="preserve">
+        <v xml:space="preserve">Exposure-weighted average all_in_rate_pct per counterparty.
+</v>
+      </c>
+      <c r="O56" t="str">
+        <v>All in Rate (%) (counterparty)</v>
+      </c>
+      <c r="P56" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q56" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="R56" t="str" xml:space="preserve">
+        <v xml:space="preserve">Exposure-weighted average all_in_rate_pct per L3 desk segment.
+</v>
+      </c>
+      <c r="S56" t="str">
+        <v>All in Rate (%) (desk)</v>
+      </c>
+      <c r="T56" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U56" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="V56" t="str" xml:space="preserve">
+        <v xml:space="preserve">Exposure-weighted average all_in_rate_pct per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W56" t="str">
+        <v>All in Rate (%) (portfolio)</v>
+      </c>
+      <c r="X56" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y56" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="Z56" t="str" xml:space="preserve">
+        <v xml:space="preserve">Exposure-weighted average all_in_rate_pct per L1 business segment.
+</v>
+      </c>
+      <c r="AA56" t="str">
+        <v>All in Rate (%) (business_segment)</v>
+      </c>
+      <c r="AB56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57" xml:space="preserve">
+      <c r="A57" t="str">
+        <v>PRC-002</v>
+      </c>
+      <c r="B57" t="str" xml:space="preserve">
+        <v xml:space="preserve">Reference benchmark interest rate applicable to the exposure (e.g., SOFR, Prime). Forms base component of total facility pricing - weighted average applied based on underlying contract value and base rate. Reflects the weighted average base rate of underlying contracts for a facility, separately displays the average base rate across all contracts within a Line of Business level
+</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Base Interest Rate (%)</v>
+      </c>
+      <c r="D57" t="str" xml:space="preserve">
+        <v xml:space="preserve">Exposure-weighted average of base_rate_pct per facility.
+</v>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
+        <v/>
+      </c>
+      <c r="G57" t="str">
+        <v/>
+      </c>
+      <c r="H57" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I57" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="J57" t="str" xml:space="preserve">
+        <v xml:space="preserve">Exposure-weighted average of base_rate_pct per facility.
+</v>
+      </c>
+      <c r="K57" t="str">
+        <v>Base Interest Rate (%) (facility)</v>
+      </c>
+      <c r="L57" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M57" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="N57" t="str" xml:space="preserve">
+        <v xml:space="preserve">Exposure-weighted average of base_rate_pct across counterparty facilities.
+</v>
+      </c>
+      <c r="O57" t="str">
+        <v>Base Interest Rate (%) (counterparty)</v>
+      </c>
+      <c r="P57" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q57" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="R57" t="str" xml:space="preserve">
+        <v xml:space="preserve">AVG of facility-level base_rate_pct per L3 desk segment.
+</v>
+      </c>
+      <c r="S57" t="str">
+        <v>Base Interest Rate (%) (desk)</v>
+      </c>
+      <c r="T57" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U57" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="V57" t="str" xml:space="preserve">
+        <v xml:space="preserve">AVG of facility-level base_rate_pct per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W57" t="str">
+        <v>Base Interest Rate (%) (portfolio)</v>
+      </c>
+      <c r="X57" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y57" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="Z57" t="str" xml:space="preserve">
+        <v xml:space="preserve">AVG of facility-level base_rate_pct per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA57" t="str">
+        <v>Base Interest Rate (%) (business_segment)</v>
+      </c>
+      <c r="AB57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58" xml:space="preserve">
+      <c r="A58" t="str">
+        <v>PRC-003</v>
+      </c>
+      <c r="B58" t="str" xml:space="preserve">
+        <v xml:space="preserve">Percentage of exposures within portfolio with approved pricing or policy exceptions. Derived governance KPI measuring policy discipline and risk culture strength.
+</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Exception Rate (%)</v>
+      </c>
+      <c r="D58" t="str" xml:space="preserve">
+        <v xml:space="preserve">Binary flag: 1 if pricing exception, 0 otherwise.
+</v>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58" t="str">
+        <v/>
+      </c>
+      <c r="G58" t="str">
+        <v/>
+      </c>
+      <c r="H58" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I58" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="J58" t="str" xml:space="preserve">
+        <v xml:space="preserve">Binary flag: 1 if pricing exception, 0 otherwise.
+</v>
+      </c>
+      <c r="K58" t="str">
+        <v>Exception Rate (%) (facility)</v>
+      </c>
+      <c r="L58" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M58" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="N58" t="str" xml:space="preserve">
+        <v xml:space="preserve">Percentage of facilities with pricing exception per counterparty.
+</v>
+      </c>
+      <c r="O58" t="str">
+        <v>Exception Rate (%) (counterparty)</v>
+      </c>
+      <c r="P58" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q58" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="R58" t="str" xml:space="preserve">
+        <v xml:space="preserve">Percentage of facilities with pricing exception per L3 desk.
+</v>
+      </c>
+      <c r="S58" t="str">
+        <v>Exception Rate (%) (desk)</v>
+      </c>
+      <c r="T58" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U58" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="V58" t="str" xml:space="preserve">
+        <v xml:space="preserve">Percentage of facilities with pricing exception per L2 portfolio.
+</v>
+      </c>
+      <c r="W58" t="str">
+        <v>Exception Rate (%) (portfolio)</v>
+      </c>
+      <c r="X58" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y58" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="Z58" t="str" xml:space="preserve">
+        <v xml:space="preserve">Percentage of facilities with pricing exception per L1 business segment.
+</v>
+      </c>
+      <c r="AA58" t="str">
+        <v>Exception Rate (%) (business_segment)</v>
+      </c>
+      <c r="AB58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59" xml:space="preserve">
+      <c r="A59" t="str">
+        <v>PRC-004</v>
+      </c>
+      <c r="B59" t="str" xml:space="preserve">
+        <v xml:space="preserve">Fee percentage applied to committed or undrawn exposure. Calculated KPI supporting pricing adequacy and revenue optimization analysis.
+</v>
+      </c>
+      <c r="C59" t="str">
+        <v>Fee Rate (%)</v>
+      </c>
+      <c r="D59" t="str" xml:space="preserve">
+        <v xml:space="preserve">Fee Income / Average Balance
+</v>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+      <c r="F59" t="str">
+        <v/>
+      </c>
+      <c r="G59" t="str">
+        <v/>
+      </c>
+      <c r="H59" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I59" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="J59" t="str" xml:space="preserve">
+        <v xml:space="preserve">Fee Income / Average Balance
+</v>
+      </c>
+      <c r="K59" t="str">
+        <v>Fee Rate (%) (facility)</v>
+      </c>
+      <c r="L59" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M59" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="N59" t="str" xml:space="preserve">
+        <v xml:space="preserve">Exposure-weighted average of fee_rate_pct across counterparty facilities.
+</v>
+      </c>
+      <c r="O59" t="str">
+        <v>Fee Rate (%) (counterparty)</v>
+      </c>
+      <c r="P59" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q59" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="R59" t="str" xml:space="preserve">
+        <v xml:space="preserve">AVG of facility-level fee_rate_pct per L3 desk segment.
+</v>
+      </c>
+      <c r="S59" t="str">
+        <v>Fee Rate (%) (desk)</v>
+      </c>
+      <c r="T59" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U59" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="V59" t="str" xml:space="preserve">
+        <v xml:space="preserve">AVG of facility-level fee_rate_pct per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W59" t="str">
+        <v>Fee Rate (%) (portfolio)</v>
+      </c>
+      <c r="X59" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y59" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z59" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level fee_rate_pct per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA59" t="str">
+        <v>Fee Rate (%) (business_segment)</v>
+      </c>
+      <c r="AB59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60" xml:space="preserve">
+      <c r="A60" t="str">
+        <v>PRC-005</v>
+      </c>
+      <c r="B60" t="str" xml:space="preserve">
+        <v xml:space="preserve">Indicator identifying exposures priced outside standard policy guidelines. Supports governance discipline and pricing compliance monitoring.
+</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Pricing Exception Status</v>
+      </c>
+      <c r="D60" t="str" xml:space="preserve">
+        <v xml:space="preserve">Binary flag: 1 if pricing exception exists, 0 otherwise.
+</v>
+      </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+      <c r="F60" t="str">
+        <v/>
+      </c>
+      <c r="G60" t="str">
+        <v/>
+      </c>
+      <c r="H60" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I60" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="J60" t="str" xml:space="preserve">
+        <v xml:space="preserve">Binary flag: 1 if pricing exception exists, 0 otherwise.
+</v>
+      </c>
+      <c r="K60" t="str">
+        <v>Pricing Exception Status (facility)</v>
+      </c>
+      <c r="L60" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M60" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N60" t="str" xml:space="preserve">
+        <v xml:space="preserve">COUNT of facilities with pricing exception per counterparty.
+</v>
+      </c>
+      <c r="O60" t="str">
+        <v>Pricing Exception Status (counterparty)</v>
+      </c>
+      <c r="P60" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q60" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R60" t="str" xml:space="preserve">
+        <v xml:space="preserve">COUNT of facilities with pricing exception per L3 desk segment.
+</v>
+      </c>
+      <c r="S60" t="str">
+        <v>Pricing Exception Status (desk)</v>
+      </c>
+      <c r="T60" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U60" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V60" t="str" xml:space="preserve">
+        <v xml:space="preserve">COUNT of facilities with pricing exception per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W60" t="str">
+        <v>Pricing Exception Status (portfolio)</v>
+      </c>
+      <c r="X60" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y60" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z60" t="str" xml:space="preserve">
+        <v xml:space="preserve">COUNT of facilities with pricing exception per L1 business segment.
+</v>
+      </c>
+      <c r="AA60" t="str">
+        <v>Pricing Exception Status (business_segment)</v>
+      </c>
+      <c r="AB60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61" xml:space="preserve">
+      <c r="A61" t="str">
+        <v>PRC-006</v>
+      </c>
+      <c r="B61" t="str" xml:space="preserve">
+        <v xml:space="preserve">Pricing classification tier assigned to facility. Supports structured pricing strategy and yield segmentation.
+</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Pricing Tier</v>
+      </c>
+      <c r="D61" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read pricing_tier from facility_pricing_snapshot for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
+        <v/>
+      </c>
+      <c r="G61" t="str">
+        <v/>
+      </c>
+      <c r="H61" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I61" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J61" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read pricing_tier from facility_pricing_snapshot for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="K61" t="str">
+        <v>Pricing Tier (facility)</v>
+      </c>
+      <c r="L61" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M61" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="N61" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read pricing_tier per counterparty.
+</v>
+      </c>
+      <c r="O61" t="str">
+        <v>Pricing Tier (counterparty)</v>
+      </c>
+      <c r="P61" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q61" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R61" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level pricing_tier per L3 desk segment.
+</v>
+      </c>
+      <c r="S61" t="str">
+        <v>Pricing Tier (desk)</v>
+      </c>
+      <c r="T61" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U61" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V61" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level pricing_tier per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W61" t="str">
+        <v>Pricing Tier (portfolio)</v>
+      </c>
+      <c r="X61" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y61" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z61" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level pricing_tier per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA61" t="str">
+        <v>Pricing Tier (business_segment)</v>
+      </c>
+      <c r="AB61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62" xml:space="preserve">
+      <c r="A62" t="str">
+        <v>PRC-007</v>
+      </c>
+      <c r="B62" t="str" xml:space="preserve">
+        <v xml:space="preserve">Credit spread over reference base rate charged on exposure, expressed as percentage. Represents risk premium embedded in pricing and supports yield analysis.
+</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Interest Rate Spread (%)</v>
+      </c>
+      <c r="D62" t="str" xml:space="preserve">
+        <v xml:space="preserve">Facility Asset Spread/ Total Outstanding Balance
+</v>
+      </c>
+      <c r="E62" t="str">
+        <v/>
+      </c>
+      <c r="F62" t="str">
+        <v/>
+      </c>
+      <c r="G62" t="str">
+        <v/>
+      </c>
+      <c r="H62" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I62" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="J62" t="str" xml:space="preserve">
+        <v xml:space="preserve">Facility Asset Spread/ Total Outstanding Balance
+</v>
+      </c>
+      <c r="K62" t="str">
+        <v>Interest Rate Spread (%) (facility)</v>
+      </c>
+      <c r="L62" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M62" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="N62" t="str" xml:space="preserve">
+        <v xml:space="preserve">Exposure-weighted average of interest_rate_spread_bps across counterparty facilities.
+</v>
+      </c>
+      <c r="O62" t="str">
+        <v>Interest Rate Spread (%) (counterparty)</v>
+      </c>
+      <c r="P62" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q62" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="R62" t="str" xml:space="preserve">
+        <v xml:space="preserve">AVG of facility-level interest_rate_spread_bps per L3 desk segment.
+</v>
+      </c>
+      <c r="S62" t="str">
+        <v>Interest Rate Spread (%) (desk)</v>
+      </c>
+      <c r="T62" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U62" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="V62" t="str" xml:space="preserve">
+        <v xml:space="preserve">AVG of facility-level interest_rate_spread_bps per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W62" t="str">
+        <v>Interest Rate Spread (%) (portfolio)</v>
+      </c>
+      <c r="X62" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y62" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z62" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level interest_rate_spread_bps per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA62" t="str">
+        <v>Interest Rate Spread (%) (business_segment)</v>
+      </c>
+      <c r="AB62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63" xml:space="preserve">
+      <c r="A63" t="str">
+        <v>PRC-008</v>
+      </c>
+      <c r="B63" t="str" xml:space="preserve">
+        <v xml:space="preserve">Measures exposure of earnings/cash flow to interest rate changes; shows vulnerability to rate shocks and informs hedging/pricing and stress-test outcomes.
+</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Interest Rate Sensitivity (%)</v>
+      </c>
+      <c r="D63" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read interest_rate_sensitivity_pct from facility_financial_snapshot for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="E63" t="str">
+        <v/>
+      </c>
+      <c r="F63" t="str">
+        <v/>
+      </c>
+      <c r="G63" t="str">
+        <v/>
+      </c>
+      <c r="H63" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I63" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J63" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read interest_rate_sensitivity_pct from facility_financial_snapshot for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="K63" t="str">
+        <v>Interest Rate Sensitivity (%) (facility)</v>
+      </c>
+      <c r="L63" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M63" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="N63" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read interest_rate_sensitivity_pct per counterparty.
+</v>
+      </c>
+      <c r="O63" t="str">
+        <v>Interest Rate Sensitivity (%) (counterparty)</v>
+      </c>
+      <c r="P63" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q63" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R63" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level interest_rate_sensitivity_pct per L3 desk segment.
+</v>
+      </c>
+      <c r="S63" t="str">
+        <v>Interest Rate Sensitivity (%) (desk)</v>
+      </c>
+      <c r="T63" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U63" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V63" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level interest_rate_sensitivity_pct per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W63" t="str">
+        <v>Interest Rate Sensitivity (%) (portfolio)</v>
+      </c>
+      <c r="X63" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y63" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z63" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level interest_rate_sensitivity_pct per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA63" t="str">
+        <v>Interest Rate Sensitivity (%) (business_segment)</v>
+      </c>
+      <c r="AB63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64" xml:space="preserve">
+      <c r="A64" t="str">
+        <v>PRC-009</v>
+      </c>
+      <c r="B64" t="str" xml:space="preserve">
+        <v xml:space="preserve">Boolean indicator identifying whether the exposure was approved outside standard pricing policy thresholds at origination or amendment.
+</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Pricing Exception Flag (Y/N)</v>
+      </c>
+      <c r="D64" t="str" xml:space="preserve">
+        <v xml:space="preserve">Calculated pricing_exception_flag per facility.
+</v>
+      </c>
+      <c r="E64" t="str">
+        <v/>
+      </c>
+      <c r="F64" t="str">
+        <v/>
+      </c>
+      <c r="G64" t="str">
+        <v/>
+      </c>
+      <c r="H64" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I64" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="J64" t="str" xml:space="preserve">
+        <v xml:space="preserve">Calculated pricing_exception_flag per facility.
+</v>
+      </c>
+      <c r="K64" t="str">
+        <v>Pricing Exception Flag (Y/N) (facility)</v>
+      </c>
+      <c r="L64" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M64" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N64" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level pricing_exception_flag per counterparty.
+</v>
+      </c>
+      <c r="O64" t="str">
+        <v>Pricing Exception Flag (Y/N) (counterparty)</v>
+      </c>
+      <c r="P64" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q64" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R64" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level pricing_exception_flag per L3 desk segment.
+</v>
+      </c>
+      <c r="S64" t="str">
+        <v>Pricing Exception Flag (Y/N) (desk)</v>
+      </c>
+      <c r="T64" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U64" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V64" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level pricing_exception_flag per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W64" t="str">
+        <v>Pricing Exception Flag (Y/N) (portfolio)</v>
+      </c>
+      <c r="X64" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y64" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z64" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level pricing_exception_flag per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA64" t="str">
+        <v>Pricing Exception Flag (Y/N) (business_segment)</v>
+      </c>
+      <c r="AB64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65" xml:space="preserve">
+      <c r="A65" t="str">
         <v>PROF-108</v>
       </c>
-      <c r="B4" t="str" xml:space="preserve">
+      <c r="B65" t="str" xml:space="preserve">
         <v xml:space="preserve">Total interest cost incurred on funding sources attributable to the reporting unit during the period. At facility level, computed as the product of the committed amount, the bank's participation share, and the cost of funds rate. At higher rollup levels, aggregated as the sum of facility-level interest expense.
 </v>
       </c>
-      <c r="C4" t="str">
+      <c r="C65" t="str">
         <v>Interest Expense</v>
       </c>
-      <c r="D4" t="str">
+      <c r="D65" t="str">
         <v>committed_facility_amt × bank_share_pct × cost_of_funds_rate</v>
       </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v>Y</v>
-      </c>
-      <c r="I4" t="str">
+      <c r="E65" t="str">
+        <v/>
+      </c>
+      <c r="F65" t="str">
+        <v/>
+      </c>
+      <c r="G65" t="str">
+        <v/>
+      </c>
+      <c r="H65" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I65" t="str">
         <v>Calc</v>
       </c>
-      <c r="J4" t="str">
+      <c r="J65" t="str">
         <v>committed_facility_amt × bank_share_pct × cost_of_funds_rate</v>
       </c>
-      <c r="K4" t="str">
+      <c r="K65" t="str">
         <v>Interest Expense (facility)</v>
       </c>
-      <c r="L4" t="str">
-        <v>Y</v>
-      </c>
-      <c r="M4" t="str">
-        <v>Agg</v>
-      </c>
-      <c r="N4" t="str">
+      <c r="L65" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M65" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N65" t="str">
         <v>SUM(Facility Interest Expense) per counterparty</v>
       </c>
-      <c r="O4" t="str">
+      <c r="O65" t="str">
         <v>Interest Expense (counterparty)</v>
       </c>
-      <c r="P4" t="str">
-        <v>Y</v>
-      </c>
-      <c r="Q4" t="str">
-        <v>Agg</v>
-      </c>
-      <c r="R4" t="str">
+      <c r="P65" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q65" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R65" t="str">
         <v>SUM(Facility Interest Expense) per L3 desk segment</v>
       </c>
-      <c r="S4" t="str">
+      <c r="S65" t="str">
         <v>Interest Expense (desk)</v>
       </c>
-      <c r="T4" t="str">
-        <v>Y</v>
-      </c>
-      <c r="U4" t="str">
-        <v>Agg</v>
-      </c>
-      <c r="V4" t="str">
+      <c r="T65" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U65" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V65" t="str">
         <v>SUM(Facility Interest Expense) per L2 portfolio segment</v>
       </c>
-      <c r="W4" t="str">
+      <c r="W65" t="str">
         <v>Interest Expense (portfolio)</v>
       </c>
-      <c r="X4" t="str">
-        <v>Y</v>
-      </c>
-      <c r="Y4" t="str">
-        <v>Agg</v>
-      </c>
-      <c r="Z4" t="str">
+      <c r="X65" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y65" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z65" t="str">
         <v>SUM(Facility Interest Expense) per L1 business segment (department)</v>
       </c>
-      <c r="AA4" t="str">
+      <c r="AA65" t="str">
         <v>Interest Expense (business_segment)</v>
       </c>
-      <c r="AB4" t="str">
+      <c r="AB65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66" xml:space="preserve">
+      <c r="A66" t="str">
+        <v>REF-001</v>
+      </c>
+      <c r="B66" t="str" xml:space="preserve">
+        <v xml:space="preserve">Count of individual loans within portfolio or facility grouping. Supports exposure granularity analysis.
+</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Number of Loans</v>
+      </c>
+      <c r="D66" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read number_of_loans from facility_exposure_snapshot for each facility.
+</v>
+      </c>
+      <c r="E66" t="str">
+        <v/>
+      </c>
+      <c r="F66" t="str">
+        <v/>
+      </c>
+      <c r="G66" t="str">
+        <v/>
+      </c>
+      <c r="H66" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I66" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J66" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read number_of_loans from facility_exposure_snapshot for each facility.
+</v>
+      </c>
+      <c r="K66" t="str">
+        <v>Number of Loans (facility)</v>
+      </c>
+      <c r="L66" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M66" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N66" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of number_of_loans per counterparty.
+</v>
+      </c>
+      <c r="O66" t="str">
+        <v>Number of Loans (counterparty)</v>
+      </c>
+      <c r="P66" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q66" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R66" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of number_of_loans per L3 desk segment.
+</v>
+      </c>
+      <c r="S66" t="str">
+        <v>Number of Loans (desk)</v>
+      </c>
+      <c r="T66" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U66" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V66" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of number_of_loans per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W66" t="str">
+        <v>Number of Loans (portfolio)</v>
+      </c>
+      <c r="X66" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y66" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z66" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of number_of_loans per L1 business segment.
+</v>
+      </c>
+      <c r="AA66" t="str">
+        <v>Number of Loans (business_segment)</v>
+      </c>
+      <c r="AB66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67" xml:space="preserve">
+      <c r="A67" t="str">
+        <v>REF-002</v>
+      </c>
+      <c r="B67" t="str" xml:space="preserve">
+        <v xml:space="preserve">Snapshot date of the dataset used for reporting and aggregation. Serves as the temporal reference point for all balances, risk metrics, and performance indicators.
+</v>
+      </c>
+      <c r="C67" t="str">
+        <v>Reporting Period (As-of Date)</v>
+      </c>
+      <c r="D67" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read as_of_date from facility_exposure_snapshot for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="E67" t="str">
+        <v/>
+      </c>
+      <c r="F67" t="str">
+        <v/>
+      </c>
+      <c r="G67" t="str">
+        <v/>
+      </c>
+      <c r="H67" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I67" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J67" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read as_of_date from facility_exposure_snapshot for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="K67" t="str">
+        <v>Reporting Period (As-of Date) (facility)</v>
+      </c>
+      <c r="L67" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M67" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="N67" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read as_of_date per counterparty.
+</v>
+      </c>
+      <c r="O67" t="str">
+        <v>Reporting Period (As-of Date) (counterparty)</v>
+      </c>
+      <c r="P67" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q67" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R67" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level as_of_date per L3 desk segment.
+</v>
+      </c>
+      <c r="S67" t="str">
+        <v>Reporting Period (As-of Date) (desk)</v>
+      </c>
+      <c r="T67" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U67" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V67" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level as_of_date per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W67" t="str">
+        <v>Reporting Period (As-of Date) (portfolio)</v>
+      </c>
+      <c r="X67" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y67" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z67" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level as_of_date per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA67" t="str">
+        <v>Reporting Period (As-of Date) (business_segment)</v>
+      </c>
+      <c r="AB67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68" xml:space="preserve">
+      <c r="A68" t="str">
+        <v>REF-003</v>
+      </c>
+      <c r="B68" t="str" xml:space="preserve">
+        <v xml:space="preserve">Average tenor of the underlying facilities across exposures. For facility, displayed the calculated tenor based on Origination Date ("Effective Date") and Maturity Date ("End Date") and other levels this metric is aggregated as an average to represent the average period of the underlying facilities.
+</v>
+      </c>
+      <c r="C68" t="str">
+        <v>Average Tenor (Years)</v>
+      </c>
+      <c r="D68" t="str" xml:space="preserve">
+        <v xml:space="preserve">For each Facility_ID, [Contract Level Maturity Date]- [Facility Level Effective Date]
+</v>
+      </c>
+      <c r="E68" t="str">
+        <v/>
+      </c>
+      <c r="F68" t="str">
+        <v/>
+      </c>
+      <c r="G68" t="str">
+        <v/>
+      </c>
+      <c r="H68" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I68" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="J68" t="str" xml:space="preserve">
+        <v xml:space="preserve">For each Facility_ID, [Contract Level Maturity Date]- [Facility Level Effective Date]
+</v>
+      </c>
+      <c r="K68" t="str">
+        <v>Average Tenor (Years) (facility)</v>
+      </c>
+      <c r="L68" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M68" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="N68" t="str" xml:space="preserve">
+        <v xml:space="preserve">Exposure-weighted average of expected_tenor_months across counterparty facilities.
+</v>
+      </c>
+      <c r="O68" t="str">
+        <v>Average Tenor (Years) (counterparty)</v>
+      </c>
+      <c r="P68" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q68" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="R68" t="str" xml:space="preserve">
+        <v xml:space="preserve">AVG of facility-level expected_tenor_months per L3 desk segment.
+</v>
+      </c>
+      <c r="S68" t="str">
+        <v>Average Tenor (Years) (desk)</v>
+      </c>
+      <c r="T68" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U68" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="V68" t="str" xml:space="preserve">
+        <v xml:space="preserve">AVG of facility-level expected_tenor_months per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W68" t="str">
+        <v>Average Tenor (Years) (portfolio)</v>
+      </c>
+      <c r="X68" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y68" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z68" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level expected_tenor_months per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA68" t="str">
+        <v>Average Tenor (Years) (business_segment)</v>
+      </c>
+      <c r="AB68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69" xml:space="preserve">
+      <c r="A69" t="str">
+        <v>REF-004</v>
+      </c>
+      <c r="B69" t="str" xml:space="preserve">
+        <v xml:space="preserve">Unique system identifier assigned to the borrower or obligor. Used for exposure aggregation and risk consolidation.
+</v>
+      </c>
+      <c r="C69" t="str">
+        <v>Counterparty ID</v>
+      </c>
+      <c r="D69" t="str" xml:space="preserve">
+        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+</v>
+      </c>
+      <c r="E69" t="str">
+        <v/>
+      </c>
+      <c r="F69" t="str">
+        <v/>
+      </c>
+      <c r="G69" t="str">
+        <v/>
+      </c>
+      <c r="H69" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I69" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J69" t="str" xml:space="preserve">
+        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+</v>
+      </c>
+      <c r="K69" t="str">
+        <v>Counterparty ID (facility)</v>
+      </c>
+      <c r="L69" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M69" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="N69" t="str" xml:space="preserve">
+        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+</v>
+      </c>
+      <c r="O69" t="str">
+        <v>Counterparty ID (counterparty)</v>
+      </c>
+      <c r="P69" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q69" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R69" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level counterparty_id per L3 desk segment.
+</v>
+      </c>
+      <c r="S69" t="str">
+        <v>Counterparty ID (desk)</v>
+      </c>
+      <c r="T69" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U69" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V69" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level counterparty_id per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W69" t="str">
+        <v>Counterparty ID (portfolio)</v>
+      </c>
+      <c r="X69" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y69" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z69" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level counterparty_id per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA69" t="str">
+        <v>Counterparty ID (business_segment)</v>
+      </c>
+      <c r="AB69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70" xml:space="preserve">
+      <c r="A70" t="str">
+        <v>REF-005</v>
+      </c>
+      <c r="B70" t="str" xml:space="preserve">
+        <v xml:space="preserve">Descriptive name of the counterparty as documented in the credit agreement. Used for reporting clarity and operational reference.
+</v>
+      </c>
+      <c r="C70" t="str">
+        <v>Counterparty Name</v>
+      </c>
+      <c r="D70" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read legal_name from counterparty for each facility's counterparty.
+</v>
+      </c>
+      <c r="E70" t="str">
+        <v/>
+      </c>
+      <c r="F70" t="str">
+        <v/>
+      </c>
+      <c r="G70" t="str">
+        <v/>
+      </c>
+      <c r="H70" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I70" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J70" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read legal_name from counterparty for each facility's counterparty.
+</v>
+      </c>
+      <c r="K70" t="str">
+        <v>Counterparty Name (facility)</v>
+      </c>
+      <c r="L70" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M70" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N70" t="str" xml:space="preserve">
+        <v xml:space="preserve">COUNT of facilities with counterparty name per counterparty.
+</v>
+      </c>
+      <c r="O70" t="str">
+        <v>Counterparty Name (counterparty)</v>
+      </c>
+      <c r="P70" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q70" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R70" t="str" xml:space="preserve">
+        <v xml:space="preserve">COUNT of facilities with counterparty name per L3 desk segment.
+</v>
+      </c>
+      <c r="S70" t="str">
+        <v>Counterparty Name (desk)</v>
+      </c>
+      <c r="T70" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U70" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V70" t="str" xml:space="preserve">
+        <v xml:space="preserve">COUNT of facilities with counterparty name per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W70" t="str">
+        <v>Counterparty Name (portfolio)</v>
+      </c>
+      <c r="X70" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y70" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z70" t="str" xml:space="preserve">
+        <v xml:space="preserve">COUNT of facilities with counterparty name per L1 business segment.
+</v>
+      </c>
+      <c r="AA70" t="str">
+        <v>Counterparty Name (business_segment)</v>
+      </c>
+      <c r="AB70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71" xml:space="preserve">
+      <c r="A71" t="str">
+        <v>REF-006</v>
+      </c>
+      <c r="B71" t="str" xml:space="preserve">
+        <v xml:space="preserve">Country of risk or booking location. Supports geographic concentration and sovereign risk analysis.
+</v>
+      </c>
+      <c r="C71" t="str">
+        <v>Country</v>
+      </c>
+      <c r="D71" t="str" xml:space="preserve">
+        <v xml:space="preserve">Direct lookup of country_name from country_dim.
+</v>
+      </c>
+      <c r="E71" t="str">
+        <v/>
+      </c>
+      <c r="F71" t="str">
+        <v/>
+      </c>
+      <c r="G71" t="str">
+        <v/>
+      </c>
+      <c r="H71" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I71" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J71" t="str" xml:space="preserve">
+        <v xml:space="preserve">Direct lookup of country_name from country_dim.
+</v>
+      </c>
+      <c r="K71" t="str">
+        <v>Country (facility)</v>
+      </c>
+      <c r="L71" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M71" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="N71" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read country_name per counterparty.
+</v>
+      </c>
+      <c r="O71" t="str">
+        <v>Country (counterparty)</v>
+      </c>
+      <c r="P71" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q71" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R71" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level country_name per L3 desk segment.
+</v>
+      </c>
+      <c r="S71" t="str">
+        <v>Country (desk)</v>
+      </c>
+      <c r="T71" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U71" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V71" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level country_name per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W71" t="str">
+        <v>Country (portfolio)</v>
+      </c>
+      <c r="X71" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y71" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z71" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level country_name per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA71" t="str">
+        <v>Country (business_segment)</v>
+      </c>
+      <c r="AB71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72" xml:space="preserve">
+      <c r="A72" t="str">
+        <v>REF-007</v>
+      </c>
+      <c r="B72" t="str" xml:space="preserve">
+        <v xml:space="preserve">Unique identifier linking facility to governing credit agreement documentation.
+</v>
+      </c>
+      <c r="C72" t="str">
+        <v>Credit Agreement ID</v>
+      </c>
+      <c r="D72" t="str" xml:space="preserve">
+        <v xml:space="preserve">Direct lookup of credit_agreement_id from credit_agreement_master.
+</v>
+      </c>
+      <c r="E72" t="str">
+        <v/>
+      </c>
+      <c r="F72" t="str">
+        <v/>
+      </c>
+      <c r="G72" t="str">
+        <v/>
+      </c>
+      <c r="H72" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I72" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J72" t="str" xml:space="preserve">
+        <v xml:space="preserve">Direct lookup of credit_agreement_id from credit_agreement_master.
+</v>
+      </c>
+      <c r="K72" t="str">
+        <v>Credit Agreement ID (facility)</v>
+      </c>
+      <c r="L72" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M72" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="N72" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read credit_agreement_id per counterparty.
+</v>
+      </c>
+      <c r="O72" t="str">
+        <v>Credit Agreement ID (counterparty)</v>
+      </c>
+      <c r="P72" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q72" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R72" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level credit_agreement_id per L3 desk segment.
+</v>
+      </c>
+      <c r="S72" t="str">
+        <v>Credit Agreement ID (desk)</v>
+      </c>
+      <c r="T72" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U72" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V72" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level credit_agreement_id per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W72" t="str">
+        <v>Credit Agreement ID (portfolio)</v>
+      </c>
+      <c r="X72" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y72" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z72" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level credit_agreement_id per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA72" t="str">
+        <v>Credit Agreement ID (business_segment)</v>
+      </c>
+      <c r="AB72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73" xml:space="preserve">
+      <c r="A73" t="str">
+        <v>REF-008</v>
+      </c>
+      <c r="B73" t="str" xml:space="preserve">
+        <v xml:space="preserve">Number of calendar days remaining until contractual maturity, calculated as (Maturity Date – Today's Date). Derived tenor metric providing insight into rollover risk and portfolio duration concentration.
+</v>
+      </c>
+      <c r="C73" t="str">
+        <v>Days Until Maturity</v>
+      </c>
+      <c r="D73" t="str" xml:space="preserve">
+        <v xml:space="preserve">[Maturity_Date] - Today()  OR [facility_master.effective_start_date] - Today()
+</v>
+      </c>
+      <c r="E73" t="str">
+        <v/>
+      </c>
+      <c r="F73" t="str">
+        <v/>
+      </c>
+      <c r="G73" t="str">
+        <v/>
+      </c>
+      <c r="H73" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I73" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="J73" t="str" xml:space="preserve">
+        <v xml:space="preserve">[Maturity_Date] - Today()  OR [facility_master.effective_start_date] - Today()
+</v>
+      </c>
+      <c r="K73" t="str">
+        <v>Days Until Maturity (facility)</v>
+      </c>
+      <c r="L73" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M73" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N73" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(facility-level days_until_maturity) per counterparty.
+</v>
+      </c>
+      <c r="O73" t="str">
+        <v>Days Until Maturity (counterparty)</v>
+      </c>
+      <c r="P73" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q73" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R73" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level days_until_maturity per L3 desk segment.
+</v>
+      </c>
+      <c r="S73" t="str">
+        <v>Days Until Maturity (desk)</v>
+      </c>
+      <c r="T73" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U73" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V73" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level days_until_maturity per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W73" t="str">
+        <v>Days Until Maturity (portfolio)</v>
+      </c>
+      <c r="X73" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y73" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z73" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level days_until_maturity per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA73" t="str">
+        <v>Days Until Maturity (business_segment)</v>
+      </c>
+      <c r="AB73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74" xml:space="preserve">
+      <c r="A74" t="str">
+        <v>REF-009</v>
+      </c>
+      <c r="B74" t="str" xml:space="preserve">
+        <v xml:space="preserve">Date on which loan or contract became legally effective.
+</v>
+      </c>
+      <c r="C74" t="str">
+        <v>Contract Origination Date</v>
+      </c>
+      <c r="D74" t="str" xml:space="preserve">
+        <v xml:space="preserve">Direct lookup of origination_date from facility_master.
+</v>
+      </c>
+      <c r="E74" t="str">
+        <v/>
+      </c>
+      <c r="F74" t="str">
+        <v/>
+      </c>
+      <c r="G74" t="str">
+        <v/>
+      </c>
+      <c r="H74" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I74" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J74" t="str" xml:space="preserve">
+        <v xml:space="preserve">Direct lookup of origination_date from facility_master.
+</v>
+      </c>
+      <c r="K74" t="str">
+        <v>Contract Origination Date (facility)</v>
+      </c>
+      <c r="L74" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M74" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N74" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(facility-level origination_date) per counterparty.
+</v>
+      </c>
+      <c r="O74" t="str">
+        <v>Contract Origination Date (counterparty)</v>
+      </c>
+      <c r="P74" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q74" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R74" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level origination_date per L3 desk segment.
+</v>
+      </c>
+      <c r="S74" t="str">
+        <v>Contract Origination Date (desk)</v>
+      </c>
+      <c r="T74" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U74" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V74" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level origination_date per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W74" t="str">
+        <v>Contract Origination Date (portfolio)</v>
+      </c>
+      <c r="X74" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y74" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z74" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level origination_date per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA74" t="str">
+        <v>Contract Origination Date (business_segment)</v>
+      </c>
+      <c r="AB74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75" xml:space="preserve">
+      <c r="A75" t="str">
+        <v>REF-010</v>
+      </c>
+      <c r="B75" t="str" xml:space="preserve">
+        <v xml:space="preserve">Unique identifier assigned to the lending facility within enterprise systems. Used to aggregate balances, risk metrics, pricing data, and contractual attributes at the facility level.
+</v>
+      </c>
+      <c r="C75" t="str">
+        <v>Facility ID</v>
+      </c>
+      <c r="D75" t="str" xml:space="preserve">
+        <v xml:space="preserve">Direct lookup of facility_id from facility_master.
+</v>
+      </c>
+      <c r="E75" t="str">
+        <v/>
+      </c>
+      <c r="F75" t="str">
+        <v/>
+      </c>
+      <c r="G75" t="str">
+        <v/>
+      </c>
+      <c r="H75" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I75" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J75" t="str" xml:space="preserve">
+        <v xml:space="preserve">Direct lookup of facility_id from facility_master.
+</v>
+      </c>
+      <c r="K75" t="str">
+        <v>Facility ID (facility)</v>
+      </c>
+      <c r="L75" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M75" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="N75" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read facility_id per counterparty.
+</v>
+      </c>
+      <c r="O75" t="str">
+        <v>Facility ID (counterparty)</v>
+      </c>
+      <c r="P75" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q75" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R75" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level facility_id per L3 desk segment.
+</v>
+      </c>
+      <c r="S75" t="str">
+        <v>Facility ID (desk)</v>
+      </c>
+      <c r="T75" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U75" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V75" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level facility_id per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W75" t="str">
+        <v>Facility ID (portfolio)</v>
+      </c>
+      <c r="X75" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y75" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z75" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level facility_id per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA75" t="str">
+        <v>Facility ID (business_segment)</v>
+      </c>
+      <c r="AB75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76" xml:space="preserve">
+      <c r="A76" t="str">
+        <v>REF-011</v>
+      </c>
+      <c r="B76" t="str" xml:space="preserve">
+        <v xml:space="preserve">Descriptive name of the facility as documented in the credit agreement. Used for reporting clarity and operational reference.
+</v>
+      </c>
+      <c r="C76" t="str">
+        <v>Facility Name</v>
+      </c>
+      <c r="D76" t="str" xml:space="preserve">
+        <v xml:space="preserve">Direct lookup of facility_name from facility_master.
+</v>
+      </c>
+      <c r="E76" t="str">
+        <v/>
+      </c>
+      <c r="F76" t="str">
+        <v/>
+      </c>
+      <c r="G76" t="str">
+        <v/>
+      </c>
+      <c r="H76" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I76" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J76" t="str" xml:space="preserve">
+        <v xml:space="preserve">Direct lookup of facility_name from facility_master.
+</v>
+      </c>
+      <c r="K76" t="str">
+        <v>Facility Name (facility)</v>
+      </c>
+      <c r="L76" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M76" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="N76" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read facility_name per counterparty.
+</v>
+      </c>
+      <c r="O76" t="str">
+        <v>Facility Name (counterparty)</v>
+      </c>
+      <c r="P76" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q76" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R76" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level facility_name per L3 desk segment.
+</v>
+      </c>
+      <c r="S76" t="str">
+        <v>Facility Name (desk)</v>
+      </c>
+      <c r="T76" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U76" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V76" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level facility_name per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W76" t="str">
+        <v>Facility Name (portfolio)</v>
+      </c>
+      <c r="X76" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y76" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z76" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level facility_name per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA76" t="str">
+        <v>Facility Name (business_segment)</v>
+      </c>
+      <c r="AB76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77" xml:space="preserve">
+      <c r="A77" t="str">
+        <v>REF-012</v>
+      </c>
+      <c r="B77" t="str" xml:space="preserve">
+        <v xml:space="preserve">Type of credit facility (e.g., Term Loan, Revolver, Letter of Credit). Enables product-level segmentation, risk concentration analysis, and performance benchmarking.
+</v>
+      </c>
+      <c r="C77" t="str">
+        <v>Facility Type</v>
+      </c>
+      <c r="D77" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read facility_type from facility_exposure_snapshot for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="E77" t="str">
+        <v/>
+      </c>
+      <c r="F77" t="str">
+        <v/>
+      </c>
+      <c r="G77" t="str">
+        <v/>
+      </c>
+      <c r="H77" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I77" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J77" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read facility_type from facility_exposure_snapshot for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="K77" t="str">
+        <v>Facility Type (facility)</v>
+      </c>
+      <c r="L77" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M77" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N77" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(facility-level facility_type) per counterparty.
+</v>
+      </c>
+      <c r="O77" t="str">
+        <v>Facility Type (counterparty)</v>
+      </c>
+      <c r="P77" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q77" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R77" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level facility_type per L3 desk segment.
+</v>
+      </c>
+      <c r="S77" t="str">
+        <v>Facility Type (desk)</v>
+      </c>
+      <c r="T77" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U77" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V77" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level facility_type per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W77" t="str">
+        <v>Facility Type (portfolio)</v>
+      </c>
+      <c r="X77" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y77" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z77" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level facility_type per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA77" t="str">
+        <v>Facility Type (business_segment)</v>
+      </c>
+      <c r="AB77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78" xml:space="preserve">
+      <c r="A78" t="str">
+        <v>REF-013</v>
+      </c>
+      <c r="B78" t="str" xml:space="preserve">
+        <v xml:space="preserve">A classification used for reporting purposes in the FR 2590 regulatory report pertaining to financial institutions' credit exposures.
+</v>
+      </c>
+      <c r="C78" t="str">
+        <v>FR2590 Category</v>
+      </c>
+      <c r="D78" t="str" xml:space="preserve">
+        <v xml:space="preserve">Calculated fr2590_category_code per facility.
+</v>
+      </c>
+      <c r="E78" t="str">
+        <v/>
+      </c>
+      <c r="F78" t="str">
+        <v/>
+      </c>
+      <c r="G78" t="str">
+        <v/>
+      </c>
+      <c r="H78" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I78" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="J78" t="str" xml:space="preserve">
+        <v xml:space="preserve">Calculated fr2590_category_code per facility.
+</v>
+      </c>
+      <c r="K78" t="str">
+        <v>FR2590 Category (facility)</v>
+      </c>
+      <c r="L78" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M78" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N78" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level fr2590_category_code per counterparty.
+</v>
+      </c>
+      <c r="O78" t="str">
+        <v>FR2590 Category (counterparty)</v>
+      </c>
+      <c r="P78" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q78" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R78" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level fr2590_category_code per L3 desk segment.
+</v>
+      </c>
+      <c r="S78" t="str">
+        <v>FR2590 Category (desk)</v>
+      </c>
+      <c r="T78" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U78" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V78" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level fr2590_category_code per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W78" t="str">
+        <v>FR2590 Category (portfolio)</v>
+      </c>
+      <c r="X78" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y78" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z78" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level fr2590_category_code per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA78" t="str">
+        <v>FR2590 Category (business_segment)</v>
+      </c>
+      <c r="AB78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79" xml:space="preserve">
+      <c r="A79" t="str">
+        <v>REF-014</v>
+      </c>
+      <c r="B79" t="str" xml:space="preserve">
+        <v xml:space="preserve">Indicator that facility or exposure is active and not closed, canceled or matured. Portfolio KPI (% Active Facilities) measures ongoing credit exposure footprint.
+</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D79" t="str" xml:space="preserve">
+        <v xml:space="preserve">Direct lookup of active_flag from facility_master.
+</v>
+      </c>
+      <c r="E79" t="str">
+        <v/>
+      </c>
+      <c r="F79" t="str">
+        <v/>
+      </c>
+      <c r="G79" t="str">
+        <v/>
+      </c>
+      <c r="H79" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I79" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J79" t="str" xml:space="preserve">
+        <v xml:space="preserve">Direct lookup of active_flag from facility_master.
+</v>
+      </c>
+      <c r="K79" t="str">
+        <v>Active (facility)</v>
+      </c>
+      <c r="L79" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M79" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="N79" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read active_flag per counterparty.
+</v>
+      </c>
+      <c r="O79" t="str">
+        <v>Active (counterparty)</v>
+      </c>
+      <c r="P79" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q79" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R79" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level active_flag per L3 desk segment.
+</v>
+      </c>
+      <c r="S79" t="str">
+        <v>Active (desk)</v>
+      </c>
+      <c r="T79" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U79" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V79" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level active_flag per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W79" t="str">
+        <v>Active (portfolio)</v>
+      </c>
+      <c r="X79" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y79" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z79" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level active_flag per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA79" t="str">
+        <v>Active (business_segment)</v>
+      </c>
+      <c r="AB79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80" xml:space="preserve">
+      <c r="A80" t="str">
+        <v>REF-015</v>
+      </c>
+      <c r="B80" t="str" xml:space="preserve">
+        <v xml:space="preserve">Boolean indicator to depict when facility is syndicated across multiple issuing banks. Portfolio KPI (% Syndicated Facilities) provides insight into risk distribution across lenders.
+</v>
+      </c>
+      <c r="C80" t="str">
+        <v>Syndicated Deal Flag</v>
+      </c>
+      <c r="D80" t="str" xml:space="preserve">
+        <v xml:space="preserve">Calculated is_syndicated_flag per facility.
+</v>
+      </c>
+      <c r="E80" t="str">
+        <v/>
+      </c>
+      <c r="F80" t="str">
+        <v/>
+      </c>
+      <c r="G80" t="str">
+        <v/>
+      </c>
+      <c r="H80" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I80" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="J80" t="str" xml:space="preserve">
+        <v xml:space="preserve">Calculated is_syndicated_flag per facility.
+</v>
+      </c>
+      <c r="K80" t="str">
+        <v>Syndicated Deal Flag (facility)</v>
+      </c>
+      <c r="L80" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M80" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N80" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(facility-level is_syndicated_flag) per counterparty.
+</v>
+      </c>
+      <c r="O80" t="str">
+        <v>Syndicated Deal Flag (counterparty)</v>
+      </c>
+      <c r="P80" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q80" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R80" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level is_syndicated_flag per L3 desk segment.
+</v>
+      </c>
+      <c r="S80" t="str">
+        <v>Syndicated Deal Flag (desk)</v>
+      </c>
+      <c r="T80" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U80" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V80" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level is_syndicated_flag per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W80" t="str">
+        <v>Syndicated Deal Flag (portfolio)</v>
+      </c>
+      <c r="X80" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y80" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z80" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level is_syndicated_flag per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA80" t="str">
+        <v>Syndicated Deal Flag (business_segment)</v>
+      </c>
+      <c r="AB80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81" xml:space="preserve">
+      <c r="A81" t="str">
+        <v>REF-016</v>
+      </c>
+      <c r="B81" t="str" xml:space="preserve">
+        <v xml:space="preserve">Legal entity booking or owning the exposure. Critical for regulatory capital and entity-level reporting.
+</v>
+      </c>
+      <c r="C81" t="str">
+        <v>Legal Entity</v>
+      </c>
+      <c r="D81" t="str" xml:space="preserve">
+        <v xml:space="preserve">Direct lookup of legal_name from counterparty.
+</v>
+      </c>
+      <c r="E81" t="str">
+        <v/>
+      </c>
+      <c r="F81" t="str">
+        <v/>
+      </c>
+      <c r="G81" t="str">
+        <v/>
+      </c>
+      <c r="H81" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I81" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J81" t="str" xml:space="preserve">
+        <v xml:space="preserve">Direct lookup of legal_name from counterparty.
+</v>
+      </c>
+      <c r="K81" t="str">
+        <v>Legal Entity (facility)</v>
+      </c>
+      <c r="L81" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M81" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="N81" t="str" xml:space="preserve">
+        <v xml:space="preserve">Direct lookup of legal_name from counterparty.
+</v>
+      </c>
+      <c r="O81" t="str">
+        <v>Legal Entity (counterparty)</v>
+      </c>
+      <c r="P81" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q81" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R81" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level legal_name per L3 desk segment.
+</v>
+      </c>
+      <c r="S81" t="str">
+        <v>Legal Entity (desk)</v>
+      </c>
+      <c r="T81" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U81" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V81" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level legal_name per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W81" t="str">
+        <v>Legal Entity (portfolio)</v>
+      </c>
+      <c r="X81" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y81" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z81" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level legal_name per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA81" t="str">
+        <v>Legal Entity (business_segment)</v>
+      </c>
+      <c r="AB81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82" xml:space="preserve">
+      <c r="A82" t="str">
+        <v>REF-017</v>
+      </c>
+      <c r="B82" t="str" xml:space="preserve">
+        <v xml:space="preserve">Unique identifier assigned to legal entity in enterprise systems.
+</v>
+      </c>
+      <c r="C82" t="str">
+        <v>Legal Entity ID</v>
+      </c>
+      <c r="D82" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read legal_entity_id from facility_exposure_snapshot for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="E82" t="str">
+        <v/>
+      </c>
+      <c r="F82" t="str">
+        <v/>
+      </c>
+      <c r="G82" t="str">
+        <v/>
+      </c>
+      <c r="H82" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I82" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J82" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read legal_entity_id from facility_exposure_snapshot for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="K82" t="str">
+        <v>Legal Entity ID (facility)</v>
+      </c>
+      <c r="L82" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M82" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="N82" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read legal_entity_id per counterparty.
+</v>
+      </c>
+      <c r="O82" t="str">
+        <v>Legal Entity ID (counterparty)</v>
+      </c>
+      <c r="P82" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q82" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R82" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level legal_entity_id per L3 desk segment.
+</v>
+      </c>
+      <c r="S82" t="str">
+        <v>Legal Entity ID (desk)</v>
+      </c>
+      <c r="T82" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U82" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V82" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level legal_entity_id per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W82" t="str">
+        <v>Legal Entity ID (portfolio)</v>
+      </c>
+      <c r="X82" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y82" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z82" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level legal_entity_id per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA82" t="str">
+        <v>Legal Entity ID (business_segment)</v>
+      </c>
+      <c r="AB82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83" xml:space="preserve">
+      <c r="A83" t="str">
+        <v>REF-018</v>
+      </c>
+      <c r="B83" t="str" xml:space="preserve">
+        <v xml:space="preserve">Line of Business classification associated with exposure.
+</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Line of Business Level Name</v>
+      </c>
+      <c r="D83" t="str" xml:space="preserve">
+        <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
+</v>
+      </c>
+      <c r="E83" t="str">
+        <v/>
+      </c>
+      <c r="F83" t="str">
+        <v/>
+      </c>
+      <c r="G83" t="str">
+        <v/>
+      </c>
+      <c r="H83" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I83" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J83" t="str" xml:space="preserve">
+        <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
+</v>
+      </c>
+      <c r="K83" t="str">
+        <v>Line of Business Level Name (facility)</v>
+      </c>
+      <c r="L83" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M83" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="N83" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read parent per counterparty.
+</v>
+      </c>
+      <c r="O83" t="str">
+        <v>Line of Business Level Name (counterparty)</v>
+      </c>
+      <c r="P83" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q83" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R83" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level parent per L3 desk segment.
+</v>
+      </c>
+      <c r="S83" t="str">
+        <v>Line of Business Level Name (desk)</v>
+      </c>
+      <c r="T83" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U83" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V83" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level parent per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W83" t="str">
+        <v>Line of Business Level Name (portfolio)</v>
+      </c>
+      <c r="X83" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y83" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z83" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level parent per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA83" t="str">
+        <v>Line of Business Level Name (business_segment)</v>
+      </c>
+      <c r="AB83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84" xml:space="preserve">
+      <c r="A84" t="str">
+        <v>REF-019</v>
+      </c>
+      <c r="B84" t="str" xml:space="preserve">
+        <v xml:space="preserve">Level 1 Line of Business hierarchy. Enables top-level organizational risk aggregation, representing the Department (e.g. Commercial Real Estate, Corporate Banking)
+</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Line of Business  L1</v>
+      </c>
+      <c r="D84" t="str" xml:space="preserve">
+        <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
+</v>
+      </c>
+      <c r="E84" t="str">
+        <v/>
+      </c>
+      <c r="F84" t="str">
+        <v/>
+      </c>
+      <c r="G84" t="str">
+        <v/>
+      </c>
+      <c r="H84" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I84" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J84" t="str" xml:space="preserve">
+        <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
+</v>
+      </c>
+      <c r="K84" t="str">
+        <v>Line of Business  L1 (facility)</v>
+      </c>
+      <c r="L84" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M84" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="N84" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read parent per counterparty.
+</v>
+      </c>
+      <c r="O84" t="str">
+        <v>Line of Business  L1 (counterparty)</v>
+      </c>
+      <c r="P84" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q84" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R84" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level parent per L3 desk segment.
+</v>
+      </c>
+      <c r="S84" t="str">
+        <v>Line of Business  L1 (desk)</v>
+      </c>
+      <c r="T84" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U84" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V84" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level parent per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W84" t="str">
+        <v>Line of Business  L1 (portfolio)</v>
+      </c>
+      <c r="X84" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y84" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z84" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level parent per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA84" t="str">
+        <v>Line of Business  L1 (business_segment)</v>
+      </c>
+      <c r="AB84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85" xml:space="preserve">
+      <c r="A85" t="str">
+        <v>REF-020</v>
+      </c>
+      <c r="B85" t="str" xml:space="preserve">
+        <v xml:space="preserve">Level 2 Line of Business hierarchy for intermediate aggregation and reporting, representing the Portfolio within the L1 LoB (e.g., CRE &gt; Office)
+</v>
+      </c>
+      <c r="C85" t="str">
+        <v>Line of Business L2</v>
+      </c>
+      <c r="D85" t="str" xml:space="preserve">
+        <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
+</v>
+      </c>
+      <c r="E85" t="str">
+        <v/>
+      </c>
+      <c r="F85" t="str">
+        <v/>
+      </c>
+      <c r="G85" t="str">
+        <v/>
+      </c>
+      <c r="H85" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I85" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J85" t="str" xml:space="preserve">
+        <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
+</v>
+      </c>
+      <c r="K85" t="str">
+        <v>Line of Business L2 (facility)</v>
+      </c>
+      <c r="L85" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M85" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="N85" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read parent per counterparty.
+</v>
+      </c>
+      <c r="O85" t="str">
+        <v>Line of Business L2 (counterparty)</v>
+      </c>
+      <c r="P85" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q85" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R85" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level parent per L3 desk segment.
+</v>
+      </c>
+      <c r="S85" t="str">
+        <v>Line of Business L2 (desk)</v>
+      </c>
+      <c r="T85" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U85" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V85" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level parent per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W85" t="str">
+        <v>Line of Business L2 (portfolio)</v>
+      </c>
+      <c r="X85" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y85" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z85" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level parent per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA85" t="str">
+        <v>Line of Business L2 (business_segment)</v>
+      </c>
+      <c r="AB85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86" xml:space="preserve">
+      <c r="A86" t="str">
+        <v>REF-021</v>
+      </c>
+      <c r="B86" t="str" xml:space="preserve">
+        <v xml:space="preserve">Level 3 Line of Business hierarchy for detailed business segmentation, representing the Desk within the L2 LoB (e.g. CRE &gt; Office &gt; Lease Up Desk)
+</v>
+      </c>
+      <c r="C86" t="str">
+        <v>Line of Business L3</v>
+      </c>
+      <c r="D86" t="str" xml:space="preserve">
+        <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
+</v>
+      </c>
+      <c r="E86" t="str">
+        <v/>
+      </c>
+      <c r="F86" t="str">
+        <v/>
+      </c>
+      <c r="G86" t="str">
+        <v/>
+      </c>
+      <c r="H86" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I86" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J86" t="str" xml:space="preserve">
+        <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
+</v>
+      </c>
+      <c r="K86" t="str">
+        <v>Line of Business L3 (facility)</v>
+      </c>
+      <c r="L86" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M86" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="N86" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read parent per counterparty.
+</v>
+      </c>
+      <c r="O86" t="str">
+        <v>Line of Business L3 (counterparty)</v>
+      </c>
+      <c r="P86" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q86" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R86" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level parent per L3 desk segment.
+</v>
+      </c>
+      <c r="S86" t="str">
+        <v>Line of Business L3 (desk)</v>
+      </c>
+      <c r="T86" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U86" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V86" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level parent per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W86" t="str">
+        <v>Line of Business L3 (portfolio)</v>
+      </c>
+      <c r="X86" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y86" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z86" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level parent per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA86" t="str">
+        <v>Line of Business L3 (business_segment)</v>
+      </c>
+      <c r="AB86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87" xml:space="preserve">
+      <c r="A87" t="str">
+        <v>REF-022</v>
+      </c>
+      <c r="B87" t="str" xml:space="preserve">
+        <v xml:space="preserve">Contractual date on which the facility or loan is scheduled to mature. Used to assess duration exposure, refinancing risk, and liquidity planning.
+</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Maturity Date</v>
+      </c>
+      <c r="D87" t="str" xml:space="preserve">
+        <v xml:space="preserve">Direct lookup of maturity_date from facility_master.
+</v>
+      </c>
+      <c r="E87" t="str">
+        <v/>
+      </c>
+      <c r="F87" t="str">
+        <v/>
+      </c>
+      <c r="G87" t="str">
+        <v/>
+      </c>
+      <c r="H87" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I87" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J87" t="str" xml:space="preserve">
+        <v xml:space="preserve">Direct lookup of maturity_date from facility_master.
+</v>
+      </c>
+      <c r="K87" t="str">
+        <v>Maturity Date (facility)</v>
+      </c>
+      <c r="L87" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M87" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N87" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(facility-level maturity_date) per counterparty.
+</v>
+      </c>
+      <c r="O87" t="str">
+        <v>Maturity Date (counterparty)</v>
+      </c>
+      <c r="P87" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q87" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R87" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level maturity_date per L3 desk segment.
+</v>
+      </c>
+      <c r="S87" t="str">
+        <v>Maturity Date (desk)</v>
+      </c>
+      <c r="T87" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U87" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V87" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level maturity_date per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W87" t="str">
+        <v>Maturity Date (portfolio)</v>
+      </c>
+      <c r="X87" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y87" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z87" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level maturity_date per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA87" t="str">
+        <v>Maturity Date (business_segment)</v>
+      </c>
+      <c r="AB87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88" xml:space="preserve">
+      <c r="A88" t="str">
+        <v>REF-023</v>
+      </c>
+      <c r="B88" t="str" xml:space="preserve">
+        <v xml:space="preserve">Date on which facility was originally booked and started.
+</v>
+      </c>
+      <c r="C88" t="str">
+        <v>Facility Origination Date</v>
+      </c>
+      <c r="D88" t="str" xml:space="preserve">
+        <v xml:space="preserve">Direct lookup of origination_date from facility_master.
+</v>
+      </c>
+      <c r="E88" t="str">
+        <v/>
+      </c>
+      <c r="F88" t="str">
+        <v/>
+      </c>
+      <c r="G88" t="str">
+        <v/>
+      </c>
+      <c r="H88" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I88" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J88" t="str" xml:space="preserve">
+        <v xml:space="preserve">Direct lookup of origination_date from facility_master.
+</v>
+      </c>
+      <c r="K88" t="str">
+        <v>Facility Origination Date (facility)</v>
+      </c>
+      <c r="L88" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M88" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N88" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(facility-level origination_date) per counterparty.
+</v>
+      </c>
+      <c r="O88" t="str">
+        <v>Facility Origination Date (counterparty)</v>
+      </c>
+      <c r="P88" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q88" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R88" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level origination_date per L3 desk segment.
+</v>
+      </c>
+      <c r="S88" t="str">
+        <v>Facility Origination Date (desk)</v>
+      </c>
+      <c r="T88" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U88" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V88" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level origination_date per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W88" t="str">
+        <v>Facility Origination Date (portfolio)</v>
+      </c>
+      <c r="X88" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y88" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z88" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level origination_date per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA88" t="str">
+        <v>Facility Origination Date (business_segment)</v>
+      </c>
+      <c r="AB88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89" xml:space="preserve">
+      <c r="A89" t="str">
+        <v>REF-024</v>
+      </c>
+      <c r="B89" t="str" xml:space="preserve">
+        <v xml:space="preserve">Identifiers of counterparties participating in the credit structures or facility as multiple-borrowers. Enables exposure attribution and concentration analysis.
+</v>
+      </c>
+      <c r="C89" t="str">
+        <v>Participating Counterparty IDs</v>
+      </c>
+      <c r="D89" t="str" xml:space="preserve">
+        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+</v>
+      </c>
+      <c r="E89" t="str">
+        <v/>
+      </c>
+      <c r="F89" t="str">
+        <v/>
+      </c>
+      <c r="G89" t="str">
+        <v/>
+      </c>
+      <c r="H89" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I89" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J89" t="str" xml:space="preserve">
+        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+</v>
+      </c>
+      <c r="K89" t="str">
+        <v>Participating Counterparty IDs (facility)</v>
+      </c>
+      <c r="L89" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M89" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="N89" t="str" xml:space="preserve">
+        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+</v>
+      </c>
+      <c r="O89" t="str">
+        <v>Participating Counterparty IDs (counterparty)</v>
+      </c>
+      <c r="P89" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q89" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R89" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level counterparty_id per L3 desk segment.
+</v>
+      </c>
+      <c r="S89" t="str">
+        <v>Participating Counterparty IDs (desk)</v>
+      </c>
+      <c r="T89" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U89" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V89" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level counterparty_id per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W89" t="str">
+        <v>Participating Counterparty IDs (portfolio)</v>
+      </c>
+      <c r="X89" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y89" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z89" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level counterparty_id per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA89" t="str">
+        <v>Participating Counterparty IDs (business_segment)</v>
+      </c>
+      <c r="AB89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90" xml:space="preserve">
+      <c r="A90" t="str">
+        <v>REF-025</v>
+      </c>
+      <c r="B90" t="str" xml:space="preserve">
+        <v xml:space="preserve">Product classification assigned to the contract offering. Supports product- level segmentation and performance analysis.
+</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Product</v>
+      </c>
+      <c r="D90" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(product_id) per facility from facility_exposure_snapshot.
+</v>
+      </c>
+      <c r="E90" t="str">
+        <v/>
+      </c>
+      <c r="F90" t="str">
+        <v/>
+      </c>
+      <c r="G90" t="str">
+        <v/>
+      </c>
+      <c r="H90" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I90" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="J90" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(product_id) per facility from facility_exposure_snapshot.
+</v>
+      </c>
+      <c r="K90" t="str">
+        <v>Product (facility)</v>
+      </c>
+      <c r="L90" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M90" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N90" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level product_id per counterparty.
+</v>
+      </c>
+      <c r="O90" t="str">
+        <v>Product (counterparty)</v>
+      </c>
+      <c r="P90" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q90" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R90" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level product_id per L3 desk segment.
+</v>
+      </c>
+      <c r="S90" t="str">
+        <v>Product (desk)</v>
+      </c>
+      <c r="T90" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U90" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V90" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level product_id per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W90" t="str">
+        <v>Product (portfolio)</v>
+      </c>
+      <c r="X90" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y90" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z90" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level product_id per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA90" t="str">
+        <v>Product (business_segment)</v>
+      </c>
+      <c r="AB90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91" xml:space="preserve">
+      <c r="A91" t="str">
+        <v>REF-026</v>
+      </c>
+      <c r="B91" t="str" xml:space="preserve">
+        <v xml:space="preserve">Geographic region classification tied to location of deal origination, supporting portfolio segmentation and concentration monitoring.
+</v>
+      </c>
+      <c r="C91" t="str">
+        <v>Region</v>
+      </c>
+      <c r="D91" t="str" xml:space="preserve">
+        <v xml:space="preserve">Direct lookup of region_code from counterparty.
+</v>
+      </c>
+      <c r="E91" t="str">
+        <v/>
+      </c>
+      <c r="F91" t="str">
+        <v/>
+      </c>
+      <c r="G91" t="str">
+        <v/>
+      </c>
+      <c r="H91" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I91" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J91" t="str" xml:space="preserve">
+        <v xml:space="preserve">Direct lookup of region_code from counterparty.
+</v>
+      </c>
+      <c r="K91" t="str">
+        <v>Region (facility)</v>
+      </c>
+      <c r="L91" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M91" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="N91" t="str" xml:space="preserve">
+        <v xml:space="preserve">Direct lookup of region_code from counterparty.
+</v>
+      </c>
+      <c r="O91" t="str">
+        <v>Region (counterparty)</v>
+      </c>
+      <c r="P91" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q91" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R91" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level region_code per L3 desk segment.
+</v>
+      </c>
+      <c r="S91" t="str">
+        <v>Region (desk)</v>
+      </c>
+      <c r="T91" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U91" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V91" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level region_code per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W91" t="str">
+        <v>Region (portfolio)</v>
+      </c>
+      <c r="X91" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y91" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z91" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level region_code per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA91" t="str">
+        <v>Region (business_segment)</v>
+      </c>
+      <c r="AB91" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92" xml:space="preserve">
+      <c r="A92" t="str">
+        <v>REF-027</v>
+      </c>
+      <c r="B92" t="str" xml:space="preserve">
+        <v xml:space="preserve">Industry sector classification of the counterparty, enabling sector concentration risk assessment.
+</v>
+      </c>
+      <c r="C92" t="str">
+        <v>Sector</v>
+      </c>
+      <c r="D92" t="str" xml:space="preserve">
+        <v xml:space="preserve">Direct lookup of industry_name from industry_dim.
+</v>
+      </c>
+      <c r="E92" t="str">
+        <v/>
+      </c>
+      <c r="F92" t="str">
+        <v/>
+      </c>
+      <c r="G92" t="str">
+        <v/>
+      </c>
+      <c r="H92" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I92" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J92" t="str" xml:space="preserve">
+        <v xml:space="preserve">Direct lookup of industry_name from industry_dim.
+</v>
+      </c>
+      <c r="K92" t="str">
+        <v>Sector (facility)</v>
+      </c>
+      <c r="L92" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M92" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="N92" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read industry_name per counterparty.
+</v>
+      </c>
+      <c r="O92" t="str">
+        <v>Sector (counterparty)</v>
+      </c>
+      <c r="P92" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q92" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R92" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level industry_name per L3 desk segment.
+</v>
+      </c>
+      <c r="S92" t="str">
+        <v>Sector (desk)</v>
+      </c>
+      <c r="T92" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U92" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V92" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level industry_name per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W92" t="str">
+        <v>Sector (portfolio)</v>
+      </c>
+      <c r="X92" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y92" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z92" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level industry_name per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA92" t="str">
+        <v>Sector (business_segment)</v>
+      </c>
+      <c r="AB92" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="93" xml:space="preserve">
+      <c r="A93" t="str">
+        <v>REF-028</v>
+      </c>
+      <c r="B93" t="str" xml:space="preserve">
+        <v xml:space="preserve">Number of unique active facilities within the reporting period.
+</v>
+      </c>
+      <c r="C93" t="str">
+        <v>Number of Facilities</v>
+      </c>
+      <c r="D93" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read number_of_facilities from facility_exposure_snapshot for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="E93" t="str">
+        <v/>
+      </c>
+      <c r="F93" t="str">
+        <v/>
+      </c>
+      <c r="G93" t="str">
+        <v/>
+      </c>
+      <c r="H93" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I93" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J93" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read number_of_facilities from facility_exposure_snapshot for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="K93" t="str">
+        <v>Number of Facilities (facility)</v>
+      </c>
+      <c r="L93" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M93" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N93" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level number_of_facilities per counterparty.
+</v>
+      </c>
+      <c r="O93" t="str">
+        <v>Number of Facilities (counterparty)</v>
+      </c>
+      <c r="P93" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q93" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R93" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level number_of_facilities per L3 desk segment.
+</v>
+      </c>
+      <c r="S93" t="str">
+        <v>Number of Facilities (desk)</v>
+      </c>
+      <c r="T93" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U93" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V93" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level number_of_facilities per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W93" t="str">
+        <v>Number of Facilities (portfolio)</v>
+      </c>
+      <c r="X93" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y93" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z93" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level number_of_facilities per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA93" t="str">
+        <v>Number of Facilities (business_segment)</v>
+      </c>
+      <c r="AB93" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="94" xml:space="preserve">
+      <c r="A94" t="str">
+        <v>REF-029</v>
+      </c>
+      <c r="B94" t="str" xml:space="preserve">
+        <v xml:space="preserve">Represents “hard” equity after removing intangibles; reflects true loss- absorbing capacity, covenant strength, and resilience under downside scenarios.
+</v>
+      </c>
+      <c r="C94" t="str">
+        <v>Tangible Net Worth</v>
+      </c>
+      <c r="D94" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read tangible_net_worth_usd from counterparty_financial_snapshot for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="E94" t="str">
+        <v/>
+      </c>
+      <c r="F94" t="str">
+        <v/>
+      </c>
+      <c r="G94" t="str">
+        <v/>
+      </c>
+      <c r="H94" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I94" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J94" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read tangible_net_worth_usd from counterparty_financial_snapshot for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="K94" t="str">
+        <v>Tangible Net Worth (facility)</v>
+      </c>
+      <c r="L94" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M94" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="N94" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read tangible_net_worth_usd per counterparty.
+</v>
+      </c>
+      <c r="O94" t="str">
+        <v>Tangible Net Worth (counterparty)</v>
+      </c>
+      <c r="P94" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q94" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R94" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level tangible_net_worth_usd per L3 desk segment.
+</v>
+      </c>
+      <c r="S94" t="str">
+        <v>Tangible Net Worth (desk)</v>
+      </c>
+      <c r="T94" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U94" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V94" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level tangible_net_worth_usd per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W94" t="str">
+        <v>Tangible Net Worth (portfolio)</v>
+      </c>
+      <c r="X94" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y94" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z94" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level tangible_net_worth_usd per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA94" t="str">
+        <v>Tangible Net Worth (business_segment)</v>
+      </c>
+      <c r="AB94" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="95" xml:space="preserve">
+      <c r="A95" t="str">
+        <v>REF-030</v>
+      </c>
+      <c r="B95" t="str" xml:space="preserve">
+        <v xml:space="preserve">Bucketing mechanism to calculate Maturity Dates supporting the identification of upcoming liquidations in the next 90 days
+</v>
+      </c>
+      <c r="C95" t="str">
+        <v>Maturity Date Bucket</v>
+      </c>
+      <c r="D95" t="str" xml:space="preserve">
+        <v xml:space="preserve">Calculated maturity_bucket_id per facility.
+</v>
+      </c>
+      <c r="E95" t="str">
+        <v/>
+      </c>
+      <c r="F95" t="str">
+        <v/>
+      </c>
+      <c r="G95" t="str">
+        <v/>
+      </c>
+      <c r="H95" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I95" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="J95" t="str" xml:space="preserve">
+        <v xml:space="preserve">Calculated maturity_bucket_id per facility.
+</v>
+      </c>
+      <c r="K95" t="str">
+        <v>Maturity Date Bucket (facility)</v>
+      </c>
+      <c r="L95" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M95" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N95" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(facility-level maturity_bucket_id) per counterparty.
+</v>
+      </c>
+      <c r="O95" t="str">
+        <v>Maturity Date Bucket (counterparty)</v>
+      </c>
+      <c r="P95" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q95" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R95" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level maturity_bucket_id per L3 desk segment.
+</v>
+      </c>
+      <c r="S95" t="str">
+        <v>Maturity Date Bucket (desk)</v>
+      </c>
+      <c r="T95" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U95" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V95" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level maturity_bucket_id per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W95" t="str">
+        <v>Maturity Date Bucket (portfolio)</v>
+      </c>
+      <c r="X95" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y95" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z95" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level maturity_bucket_id per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA95" t="str">
+        <v>Maturity Date Bucket (business_segment)</v>
+      </c>
+      <c r="AB95" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="96" xml:space="preserve">
+      <c r="A96" t="str">
+        <v>REF-031</v>
+      </c>
+      <c r="B96" t="str" xml:space="preserve">
+        <v xml:space="preserve">Bucketing mechanism to calculate Origination Dates supporting the identification of upcoming facilities starting commitments in the next 90 days
+</v>
+      </c>
+      <c r="C96" t="str">
+        <v>Origination Date Bucket</v>
+      </c>
+      <c r="D96" t="str" xml:space="preserve">
+        <v xml:space="preserve">Calculated origination_date_bucket per facility.
+</v>
+      </c>
+      <c r="E96" t="str">
+        <v/>
+      </c>
+      <c r="F96" t="str">
+        <v/>
+      </c>
+      <c r="G96" t="str">
+        <v/>
+      </c>
+      <c r="H96" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I96" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="J96" t="str" xml:space="preserve">
+        <v xml:space="preserve">Calculated origination_date_bucket per facility.
+</v>
+      </c>
+      <c r="K96" t="str">
+        <v>Origination Date Bucket (facility)</v>
+      </c>
+      <c r="L96" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M96" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N96" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(facility-level origination_date_bucket) per counterparty.
+</v>
+      </c>
+      <c r="O96" t="str">
+        <v>Origination Date Bucket (counterparty)</v>
+      </c>
+      <c r="P96" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q96" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R96" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level origination_date_bucket per L3 desk segment.
+</v>
+      </c>
+      <c r="S96" t="str">
+        <v>Origination Date Bucket (desk)</v>
+      </c>
+      <c r="T96" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U96" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V96" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level origination_date_bucket per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W96" t="str">
+        <v>Origination Date Bucket (portfolio)</v>
+      </c>
+      <c r="X96" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y96" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z96" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level origination_date_bucket per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA96" t="str">
+        <v>Origination Date Bucket (business_segment)</v>
+      </c>
+      <c r="AB96" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="97" xml:space="preserve">
+      <c r="A97" t="str">
+        <v>REF-032</v>
+      </c>
+      <c r="B97" t="str" xml:space="preserve">
+        <v xml:space="preserve">Capturing distirbution of facilities starting or liquidating in 90 day windows
+</v>
+      </c>
+      <c r="C97" t="str">
+        <v>Effective Date Bucket</v>
+      </c>
+      <c r="D97" t="str" xml:space="preserve">
+        <v xml:space="preserve">Calculated effective_date_bucket per facility.
+</v>
+      </c>
+      <c r="E97" t="str">
+        <v/>
+      </c>
+      <c r="F97" t="str">
+        <v/>
+      </c>
+      <c r="G97" t="str">
+        <v/>
+      </c>
+      <c r="H97" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I97" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="J97" t="str" xml:space="preserve">
+        <v xml:space="preserve">Calculated effective_date_bucket per facility.
+</v>
+      </c>
+      <c r="K97" t="str">
+        <v>Effective Date Bucket (facility)</v>
+      </c>
+      <c r="L97" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M97" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N97" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(facility-level effective_date_bucket) per counterparty.
+</v>
+      </c>
+      <c r="O97" t="str">
+        <v>Effective Date Bucket (counterparty)</v>
+      </c>
+      <c r="P97" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q97" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R97" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level effective_date_bucket per L3 desk segment.
+</v>
+      </c>
+      <c r="S97" t="str">
+        <v>Effective Date Bucket (desk)</v>
+      </c>
+      <c r="T97" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U97" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V97" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level effective_date_bucket per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W97" t="str">
+        <v>Effective Date Bucket (portfolio)</v>
+      </c>
+      <c r="X97" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y97" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z97" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level effective_date_bucket per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA97" t="str">
+        <v>Effective Date Bucket (business_segment)</v>
+      </c>
+      <c r="AB97" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="98" xml:space="preserve">
+      <c r="A98" t="str">
+        <v>REF-033</v>
+      </c>
+      <c r="B98" t="str" xml:space="preserve">
+        <v xml:space="preserve">Boolean indicator to depict when a Facility is currently active in the reporting period (e.g., Facility Status is not Canceled or Closed)
+</v>
+      </c>
+      <c r="C98" t="str">
+        <v>Facility Active Flag</v>
+      </c>
+      <c r="D98" t="str" xml:space="preserve">
+        <v xml:space="preserve">Calculated facility_active_flag per facility.
+</v>
+      </c>
+      <c r="E98" t="str">
+        <v/>
+      </c>
+      <c r="F98" t="str">
+        <v/>
+      </c>
+      <c r="G98" t="str">
+        <v/>
+      </c>
+      <c r="H98" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I98" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="J98" t="str" xml:space="preserve">
+        <v xml:space="preserve">Calculated facility_active_flag per facility.
+</v>
+      </c>
+      <c r="K98" t="str">
+        <v>Facility Active Flag (facility)</v>
+      </c>
+      <c r="L98" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M98" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N98" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(facility-level facility_active_flag) per counterparty.
+</v>
+      </c>
+      <c r="O98" t="str">
+        <v>Facility Active Flag (counterparty)</v>
+      </c>
+      <c r="P98" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q98" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R98" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level facility_active_flag per L3 desk segment.
+</v>
+      </c>
+      <c r="S98" t="str">
+        <v>Facility Active Flag (desk)</v>
+      </c>
+      <c r="T98" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U98" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V98" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level facility_active_flag per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W98" t="str">
+        <v>Facility Active Flag (portfolio)</v>
+      </c>
+      <c r="X98" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y98" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z98" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level facility_active_flag per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA98" t="str">
+        <v>Facility Active Flag (business_segment)</v>
+      </c>
+      <c r="AB98" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="99" xml:space="preserve">
+      <c r="A99" t="str">
+        <v>RSK-001</v>
+      </c>
+      <c r="B99" t="str" xml:space="preserve">
+        <v xml:space="preserve">Most recent internal credit rating assigned at reporting date. Used for segmentation and exposure-weighted risk aggregation.
+</v>
+      </c>
+      <c r="C99" t="str">
+        <v>Risk Rating Tier</v>
+      </c>
+      <c r="D99" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility.
+</v>
+      </c>
+      <c r="E99" t="str">
+        <v/>
+      </c>
+      <c r="F99" t="str">
+        <v/>
+      </c>
+      <c r="G99" t="str">
+        <v/>
+      </c>
+      <c r="H99" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I99" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J99" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility.
+</v>
+      </c>
+      <c r="K99" t="str">
+        <v>Risk Rating Tier (facility)</v>
+      </c>
+      <c r="L99" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M99" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N99" t="str" xml:space="preserve">
+        <v xml:space="preserve">COUNT of facilities with risk rating per counterparty.
+</v>
+      </c>
+      <c r="O99" t="str">
+        <v>Risk Rating Tier (counterparty)</v>
+      </c>
+      <c r="P99" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q99" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R99" t="str" xml:space="preserve">
+        <v xml:space="preserve">COUNT of facilities with risk rating per L3 desk segment.
+</v>
+      </c>
+      <c r="S99" t="str">
+        <v>Risk Rating Tier (desk)</v>
+      </c>
+      <c r="T99" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U99" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V99" t="str" xml:space="preserve">
+        <v xml:space="preserve">COUNT of facilities with risk rating per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W99" t="str">
+        <v>Risk Rating Tier (portfolio)</v>
+      </c>
+      <c r="X99" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y99" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z99" t="str" xml:space="preserve">
+        <v xml:space="preserve">COUNT of facilities with risk rating per L1 business segment.
+</v>
+      </c>
+      <c r="AA99" t="str">
+        <v>Risk Rating Tier (business_segment)</v>
+      </c>
+      <c r="AB99" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="100" xml:space="preserve">
+      <c r="A100" t="str">
+        <v>RSK-002</v>
+      </c>
+      <c r="B100" t="str" xml:space="preserve">
+        <v xml:space="preserve">Current external credit agency rating assigned to the obligor. Used for benchmarking, regulatory reporting, and external credit risk validation. Sourced based on external Rating provider (S&amp;P, Moodys, Fitch) - populated based on firm's preferred recognized rating provider.
+</v>
+      </c>
+      <c r="C100" t="str">
+        <v>Risk Rating - External Rating</v>
+      </c>
+      <c r="D100" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read external_risk_rating from position for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="E100" t="str">
+        <v/>
+      </c>
+      <c r="F100" t="str">
+        <v/>
+      </c>
+      <c r="G100" t="str">
+        <v/>
+      </c>
+      <c r="H100" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I100" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J100" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read external_risk_rating from position for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="K100" t="str">
+        <v>Risk Rating - External Rating (facility)</v>
+      </c>
+      <c r="L100" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M100" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="N100" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read external_risk_rating per counterparty.
+</v>
+      </c>
+      <c r="O100" t="str">
+        <v>Risk Rating - External Rating (counterparty)</v>
+      </c>
+      <c r="P100" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q100" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="R100" t="str" xml:space="preserve">
+        <v xml:space="preserve">AVG of facility-level external_risk_rating per L3 desk segment.
+</v>
+      </c>
+      <c r="S100" t="str">
+        <v>Risk Rating - External Rating (desk)</v>
+      </c>
+      <c r="T100" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U100" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="V100" t="str" xml:space="preserve">
+        <v xml:space="preserve">AVG of facility-level external_risk_rating per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W100" t="str">
+        <v>Risk Rating - External Rating (portfolio)</v>
+      </c>
+      <c r="X100" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y100" t="str">
+        <v>Avg</v>
+      </c>
+      <c r="Z100" t="str" xml:space="preserve">
+        <v xml:space="preserve">AVG of facility-level external_risk_rating per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA100" t="str">
+        <v>Risk Rating - External Rating (business_segment)</v>
+      </c>
+      <c r="AB100" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="101" xml:space="preserve">
+      <c r="A101" t="str">
+        <v>RSK-003</v>
+      </c>
+      <c r="B101" t="str" xml:space="preserve">
+        <v xml:space="preserve">The institution’s internally assigned credit risk grade for a borrower, facility, or exposure as of a given date, reflecting its assessment of default risk according to the firm’s internal rating scale/model.
+</v>
+      </c>
+      <c r="C101" t="str">
+        <v>Risk Rating - Internal Risk Rating</v>
+      </c>
+      <c r="D101" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read internal_risk_rating from facility_risk_snapshot for each facility.
+</v>
+      </c>
+      <c r="E101" t="str">
+        <v/>
+      </c>
+      <c r="F101" t="str">
+        <v/>
+      </c>
+      <c r="G101" t="str">
+        <v/>
+      </c>
+      <c r="H101" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I101" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J101" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read internal_risk_rating from facility_risk_snapshot for each facility.
+</v>
+      </c>
+      <c r="K101" t="str">
+        <v>Risk Rating - Internal Risk Rating (facility)</v>
+      </c>
+      <c r="L101" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M101" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N101" t="str" xml:space="preserve">
+        <v xml:space="preserve">COUNT of facilities with internal risk rating per counterparty.
+</v>
+      </c>
+      <c r="O101" t="str">
+        <v>Risk Rating - Internal Risk Rating (counterparty)</v>
+      </c>
+      <c r="P101" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q101" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R101" t="str" xml:space="preserve">
+        <v xml:space="preserve">COUNT of facilities with internal risk rating per L3 desk segment.
+</v>
+      </c>
+      <c r="S101" t="str">
+        <v>Risk Rating - Internal Risk Rating (desk)</v>
+      </c>
+      <c r="T101" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U101" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V101" t="str" xml:space="preserve">
+        <v xml:space="preserve">COUNT of facilities with internal risk rating per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W101" t="str">
+        <v>Risk Rating - Internal Risk Rating (portfolio)</v>
+      </c>
+      <c r="X101" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y101" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z101" t="str" xml:space="preserve">
+        <v xml:space="preserve">COUNT of facilities with internal risk rating per L1 business segment.
+</v>
+      </c>
+      <c r="AA101" t="str">
+        <v>Risk Rating - Internal Risk Rating (business_segment)</v>
+      </c>
+      <c r="AB101" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="102" xml:space="preserve">
+      <c r="A102" t="str">
+        <v>RSK-004</v>
+      </c>
+      <c r="B102" t="str" xml:space="preserve">
+        <v xml:space="preserve">Derived directional indicator reflecting movement in external credit agency rating and changes month over month, which depicts the month-over-month change reflecting an upgrade (e.g. A to AA), downgrade (e.g., B+ to B-) or stable (remaing constant month over month), as compared to prior month reporting periods. Note when this is displayed at an aggregated Line of Business or portfolio level, it is determined by the month-over-month change of the average rating at this level. Supports benchmarking against market perception and helps validate internal risk assessment trends.
+</v>
+      </c>
+      <c r="C102" t="str">
+        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable)</v>
+      </c>
+      <c r="D102" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="E102" t="str">
+        <v/>
+      </c>
+      <c r="F102" t="str">
+        <v/>
+      </c>
+      <c r="G102" t="str">
+        <v/>
+      </c>
+      <c r="H102" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I102" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J102" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="K102" t="str">
+        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable) (facility)</v>
+      </c>
+      <c r="L102" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M102" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N102" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level risk_rating_status per counterparty.
+</v>
+      </c>
+      <c r="O102" t="str">
+        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable) (counterparty)</v>
+      </c>
+      <c r="P102" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q102" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R102" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level risk_rating_status per L3 desk segment.
+</v>
+      </c>
+      <c r="S102" t="str">
+        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable) (desk)</v>
+      </c>
+      <c r="T102" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U102" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V102" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level risk_rating_status per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W102" t="str">
+        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable) (portfolio)</v>
+      </c>
+      <c r="X102" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y102" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z102" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level risk_rating_status per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA102" t="str">
+        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable) (business_segment)</v>
+      </c>
+      <c r="AB102" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="103" xml:space="preserve">
+      <c r="A103" t="str">
+        <v>RSK-005</v>
+      </c>
+      <c r="B103" t="str" xml:space="preserve">
+        <v xml:space="preserve">Numerical representation of external risk rating migration (month over month changes) expressed in notch movement (positive or negative). Positive step changes are identified when there is an upgrade, from A to AA and the step change is +1, where as the negative step change is identified when there is a downgrade from B+ to B- and the step change is -1. Note when this is displayed at an aggregated Line of Business or portfolio level, it is determined by the month-over-month change of the average rating at this level. Quantifies magnitude of credit change and enables portfolio-level migration analysis, stress testing sensitivity, and risk trend measurement.
+</v>
+      </c>
+      <c r="C103" t="str">
+        <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps)</v>
+      </c>
+      <c r="D103" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read risk_rating_change_steps from counterparty_rating_observation for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="E103" t="str">
+        <v/>
+      </c>
+      <c r="F103" t="str">
+        <v/>
+      </c>
+      <c r="G103" t="str">
+        <v/>
+      </c>
+      <c r="H103" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I103" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J103" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read risk_rating_change_steps from counterparty_rating_observation for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="K103" t="str">
+        <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps) (facility)</v>
+      </c>
+      <c r="L103" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M103" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N103" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per counterparty.
+</v>
+      </c>
+      <c r="O103" t="str">
+        <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps) (counterparty)</v>
+      </c>
+      <c r="P103" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q103" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R103" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per L3 desk segment.
+</v>
+      </c>
+      <c r="S103" t="str">
+        <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps) (desk)</v>
+      </c>
+      <c r="T103" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U103" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V103" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W103" t="str">
+        <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps) (portfolio)</v>
+      </c>
+      <c r="X103" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y103" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z103" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA103" t="str">
+        <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps) (business_segment)</v>
+      </c>
+      <c r="AB103" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="104" xml:space="preserve">
+      <c r="A104" t="str">
+        <v>RSK-006</v>
+      </c>
+      <c r="B104" t="str" xml:space="preserve">
+        <v xml:space="preserve">Derived directional classification indicating whether the internal credit rating has changed month over month: upgraded (e.g. 3 to 1), downgraded (e.g. 1 to 3), or remained stable (remained costant month-over month) compared to the prior reporting period. Note when this is displayed at an aggregated Line of Business or portfolio level, it is determined by the month-over-month change of the average rating at this level. Provides migration trend insight and serves as an early warning indicator of credit quality movement to support proactive risk management and escalation decisions.
+</v>
+      </c>
+      <c r="C104" t="str">
+        <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable)</v>
+      </c>
+      <c r="D104" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="E104" t="str">
+        <v/>
+      </c>
+      <c r="F104" t="str">
+        <v/>
+      </c>
+      <c r="G104" t="str">
+        <v/>
+      </c>
+      <c r="H104" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I104" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J104" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="K104" t="str">
+        <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable) (facility)</v>
+      </c>
+      <c r="L104" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M104" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N104" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level risk_rating_status per counterparty.
+</v>
+      </c>
+      <c r="O104" t="str">
+        <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable) (counterparty)</v>
+      </c>
+      <c r="P104" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q104" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R104" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level risk_rating_status per L3 desk segment.
+</v>
+      </c>
+      <c r="S104" t="str">
+        <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable) (desk)</v>
+      </c>
+      <c r="T104" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U104" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V104" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level risk_rating_status per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W104" t="str">
+        <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable) (portfolio)</v>
+      </c>
+      <c r="X104" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y104" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z104" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level risk_rating_status per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA104" t="str">
+        <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable) (business_segment)</v>
+      </c>
+      <c r="AB104" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="105" xml:space="preserve">
+      <c r="A105" t="str">
+        <v>RSK-007</v>
+      </c>
+      <c r="B105" t="str" xml:space="preserve">
+        <v xml:space="preserve">Numerical representation of internal risk rating migration (month over month changes) expressed in notch movement (positive or negative). Positive step changes are identified when there is an upgrade, from 3 to 1and the step change is +2, where as the negative step change is identified when there is a downgrade from 5 to 8 and the step change is -3. Note when this is displayed at an aggregated Line of Business or portfolio level, it is determined by the month-over-month change of the average rating at this level. Quantifies magnitude of credit change and enables portfolio-level migration analysis, stress testing sensitivity, and risk trend measurement.
+</v>
+      </c>
+      <c r="C105" t="str">
+        <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps)</v>
+      </c>
+      <c r="D105" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read risk_rating_change_steps from counterparty_rating_observation for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="E105" t="str">
+        <v/>
+      </c>
+      <c r="F105" t="str">
+        <v/>
+      </c>
+      <c r="G105" t="str">
+        <v/>
+      </c>
+      <c r="H105" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I105" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J105" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read risk_rating_change_steps from counterparty_rating_observation for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="K105" t="str">
+        <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps) (facility)</v>
+      </c>
+      <c r="L105" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M105" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N105" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per counterparty.
+</v>
+      </c>
+      <c r="O105" t="str">
+        <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps) (counterparty)</v>
+      </c>
+      <c r="P105" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q105" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R105" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per L3 desk segment.
+</v>
+      </c>
+      <c r="S105" t="str">
+        <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps) (desk)</v>
+      </c>
+      <c r="T105" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U105" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V105" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W105" t="str">
+        <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps) (portfolio)</v>
+      </c>
+      <c r="X105" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y105" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z105" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA105" t="str">
+        <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps) (business_segment)</v>
+      </c>
+      <c r="AB105" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="106" xml:space="preserve">
+      <c r="A106" t="str">
+        <v>RSK-008</v>
+      </c>
+      <c r="B106" t="str" xml:space="preserve">
+        <v xml:space="preserve">Categorizes exposures by internal credit risk level into distribution buckets based on counterparty internal risk rating; enables monitoring of credit quality distribution, concentration, and deterioration via rating migration.
+</v>
+      </c>
+      <c r="C106" t="str">
+        <v>Internal Risk Rating Bucket</v>
+      </c>
+      <c r="D106" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read internal_risk_rating_bucket_code from facility_exposure_snapshot for each facility.
+</v>
+      </c>
+      <c r="E106" t="str">
+        <v/>
+      </c>
+      <c r="F106" t="str">
+        <v/>
+      </c>
+      <c r="G106" t="str">
+        <v/>
+      </c>
+      <c r="H106" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I106" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J106" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read internal_risk_rating_bucket_code from facility_exposure_snapshot for each facility.
+</v>
+      </c>
+      <c r="K106" t="str">
+        <v>Internal Risk Rating Bucket (facility)</v>
+      </c>
+      <c r="L106" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M106" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N106" t="str" xml:space="preserve">
+        <v xml:space="preserve">COUNT of facilities with risk rating bucket per counterparty.
+</v>
+      </c>
+      <c r="O106" t="str">
+        <v>Internal Risk Rating Bucket (counterparty)</v>
+      </c>
+      <c r="P106" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q106" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R106" t="str" xml:space="preserve">
+        <v xml:space="preserve">COUNT of facilities with risk rating bucket per L3 desk segment.
+</v>
+      </c>
+      <c r="S106" t="str">
+        <v>Internal Risk Rating Bucket (desk)</v>
+      </c>
+      <c r="T106" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U106" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V106" t="str" xml:space="preserve">
+        <v xml:space="preserve">COUNT of facilities with risk rating bucket per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W106" t="str">
+        <v>Internal Risk Rating Bucket (portfolio)</v>
+      </c>
+      <c r="X106" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y106" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z106" t="str" xml:space="preserve">
+        <v xml:space="preserve">COUNT of facilities with risk rating bucket per L1 business segment.
+</v>
+      </c>
+      <c r="AA106" t="str">
+        <v>Internal Risk Rating Bucket (business_segment)</v>
+      </c>
+      <c r="AB106" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="107" xml:space="preserve">
+      <c r="A107" t="str">
+        <v>RSK-009</v>
+      </c>
+      <c r="B107" t="str" xml:space="preserve">
+        <v xml:space="preserve">Committed facility amount as a percentage of underlying collateral value. Higher LTV indicates greater loss severity risk in the event of default. A core risk metric for secured lending portfolios.
+</v>
+      </c>
+      <c r="C107" t="str">
+        <v>Loan-to-Value Ratio (%)</v>
+      </c>
+      <c r="D107" t="str" xml:space="preserve">
+        <v xml:space="preserve">Aggregate collateral per facility (a facility may have multiple collateral assets),
+then compute LTV = committed_facility_amt / SUM(current_valuation_usd) * 100.
+</v>
+      </c>
+      <c r="E107" t="str">
+        <v/>
+      </c>
+      <c r="F107" t="str">
+        <v/>
+      </c>
+      <c r="G107" t="str">
+        <v/>
+      </c>
+      <c r="H107" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I107" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J107" t="str" xml:space="preserve">
+        <v xml:space="preserve">Aggregate collateral per facility (a facility may have multiple collateral assets),
+then compute LTV = committed_facility_amt / SUM(current_valuation_usd) * 100.
+</v>
+      </c>
+      <c r="K107" t="str">
+        <v>Loan-to-Value Ratio (%) (facility)</v>
+      </c>
+      <c r="L107" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M107" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="N107" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(committed_facility_amt) / SUM(current_valuation_usd) * 100.0
+per counterparty. Re-derives ratio from summed components.
+</v>
+      </c>
+      <c r="O107" t="str">
+        <v>Loan-to-Value Ratio (%) (counterparty)</v>
+      </c>
+      <c r="P107" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q107" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="R107" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(committed_facility_amt) / SUM(current_valuation_usd) * 100.0
+per L3 desk segment. Re-derives ratio from summed components.
+</v>
+      </c>
+      <c r="S107" t="str">
+        <v>Loan-to-Value Ratio (%) (desk)</v>
+      </c>
+      <c r="T107" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U107" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="V107" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(committed_facility_amt) / SUM(current_valuation_usd) * 100.0
+per L2 portfolio segment. Re-derives ratio from summed components.
+</v>
+      </c>
+      <c r="W107" t="str">
+        <v>Loan-to-Value Ratio (%) (portfolio)</v>
+      </c>
+      <c r="X107" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y107" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="Z107" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM(committed_facility_amt) / SUM(current_valuation_usd) * 100.0
+per L1 business segment. Re-derives ratio from summed components.
+</v>
+      </c>
+      <c r="AA107" t="str">
+        <v>Loan-to-Value Ratio (%) (business_segment)</v>
+      </c>
+      <c r="AB107" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AB4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AB107"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/metrics_dimensions_filled.xlsx
+++ b/data/metrics_dimensions_filled.xlsx
@@ -1324,14 +1324,14 @@
         <v>EXP-004</v>
       </c>
       <c r="B12" t="str" xml:space="preserve">
-        <v xml:space="preserve">Total approved committed credit amount in USD representing contractual lending capacity.
+        <v xml:space="preserve">Bank-share-adjusted total approved committed credit amount in USD. Represents the BHC's pro-rata contractual lending capacity per facility. Maps to FR Y-14Q Field 24 (Committed Exposure Global, MDRM G074).
 </v>
       </c>
       <c r="C12" t="str">
         <v>Committed Exposure ($)</v>
       </c>
       <c r="D12" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Distinct([Facility ID]), WHEN IS(MAX(AS_OF_DATE) AND [Facility_Active_Flag]="Y", THEN [Committed_Facility_Amt]*[Bank_Share] == [Committed Exposure, Bank Share portion only]
+        <v xml:space="preserve">For each active facility: committed_facility_amt * bank_share_pct / 100. bank_share_pct sourced from facility_lender_allocation (aggregated per facility).
 </v>
       </c>
       <c r="E12" t="str">
@@ -1350,7 +1350,7 @@
         <v>Calc</v>
       </c>
       <c r="J12" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Distinct([Facility ID]), WHEN IS(MAX(AS_OF_DATE) AND [Facility_Active_Flag]="Y", THEN [Committed_Facility_Amt]*[Bank_Share] == [Committed Exposure, Bank Share portion only]
+        <v xml:space="preserve">For each active facility: committed_facility_amt * bank_share_pct / 100. bank_share_pct sourced from facility_lender_allocation (aggregated per facility).
 </v>
       </c>
       <c r="K12" t="str">
@@ -1363,7 +1363,7 @@
         <v>Agg</v>
       </c>
       <c r="N12" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level committed_facility_amt per counterparty.
+        <v xml:space="preserve">SUM of facility-level committed exposure weighted by participation_pct from facility_counterparty_participation. Uses contractual pro-rata basis per FR Y-14Q requirements.
 </v>
       </c>
       <c r="O12" t="str">
@@ -1376,7 +1376,7 @@
         <v>Agg</v>
       </c>
       <c r="R12" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level committed_facility_amt per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level committed exposure per L3 desk segment. Joins facility_master.lob_segment_id to enterprise_business_taxonomy.managed_segment_id.
 </v>
       </c>
       <c r="S12" t="str">
@@ -1389,7 +1389,7 @@
         <v>Agg</v>
       </c>
       <c r="V12" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level committed_facility_amt per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level committed exposure per L2 portfolio segment. Traverses L3 -&gt; L2 via parent_segment_id.
 </v>
       </c>
       <c r="W12" t="str">
@@ -1402,7 +1402,7 @@
         <v>Agg</v>
       </c>
       <c r="Z12" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level committed_facility_amt per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level committed exposure per L1 business segment. Traverses L3 -&gt; L2 -&gt; L1 via parent_segment_id chain.
 </v>
       </c>
       <c r="AA12" t="str">
@@ -2537,7 +2537,7 @@
         <v>EXP-017</v>
       </c>
       <c r="B25" t="str" xml:space="preserve">
-        <v xml:space="preserve">Bank-share-adjusted unfunded commitment amount. Measures contingent funding risk by summing unfunded positions per facility, applying the bank's share percentage.
+        <v xml:space="preserve">Bank-share-adjusted unfunded commitment amount. Measures contingent funding risk by summing unfunded positions per facility, applying the bank's share percentage from facility_lender_allocation. Derived as Committed Exposure minus Outstanding Exposure.
 </v>
       </c>
       <c r="C25" t="str">
@@ -2545,9 +2545,9 @@
       </c>
       <c r="D25" t="str" xml:space="preserve">
         <v xml:space="preserve">For each active facility:
-1. Join position → position_detail on position_id (both as_of_date filtered)
+1. Join position -&gt; position_detail on position_id (both as_of_date filtered)
 2. SUM(unfunded_amount) across all positions for the facility
-3. Multiply by COALESCE(bank_share_pct, 1.0) for bank-share-adjusted exposure
+3. Multiply by COALESCE(bank_share_pct, 100) / 100 from facility_lender_allocation
 </v>
       </c>
       <c r="E25" t="str">
@@ -2567,9 +2567,9 @@
       </c>
       <c r="J25" t="str" xml:space="preserve">
         <v xml:space="preserve">For each active facility:
-1. Join position → position_detail on position_id (both as_of_date filtered)
+1. Join position -&gt; position_detail on position_id (both as_of_date filtered)
 2. SUM(unfunded_amount) across all positions for the facility
-3. Multiply by COALESCE(bank_share_pct, 1.0) for bank-share-adjusted exposure
+3. Multiply by COALESCE(bank_share_pct, 100) / 100 from facility_lender_allocation
 </v>
       </c>
       <c r="K25" t="str">
@@ -2597,6 +2597,7 @@
       </c>
       <c r="R25" t="str" xml:space="preserve">
         <v xml:space="preserve">SUM of facility-level undrawn exposure per L3 desk segment.
+Joins facility_master.lob_segment_id to enterprise_business_taxonomy.managed_segment_id.
 </v>
       </c>
       <c r="S25" t="str">
@@ -2610,6 +2611,7 @@
       </c>
       <c r="V25" t="str" xml:space="preserve">
         <v xml:space="preserve">SUM of facility-level undrawn exposure per L2 portfolio segment.
+Traverses L3 -&gt; L2 via parent_segment_id.
 </v>
       </c>
       <c r="W25" t="str">
@@ -2623,6 +2625,7 @@
       </c>
       <c r="Z25" t="str" xml:space="preserve">
         <v xml:space="preserve">SUM of facility-level undrawn exposure per L1 business segment.
+Traverses L3 -&gt; L2 -&gt; L1 via parent_segment_id chain.
 </v>
       </c>
       <c r="AA25" t="str">
@@ -2637,14 +2640,17 @@
         <v>EXP-018</v>
       </c>
       <c r="B26" t="str" xml:space="preserve">
-        <v xml:space="preserve">Portion of committed exposure currently available and not yet drawn. Used to assess funding deployment and credit capacity usage.
+        <v xml:space="preserve">Bank-share-adjusted funded (drawn) exposure amount. Represents the portion of committed credit currently utilized by the borrower. Maps to FR Y-14Q Field 25 (Utilized Exposure Global, MDRM G075).
 </v>
       </c>
       <c r="C26" t="str">
-        <v>Oustanding Exposure ($)</v>
+        <v>Outstanding Exposure ($)</v>
       </c>
       <c r="D26" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Distinct([Facility ID]), WHEN IS(MAX(AS_OF_DATE) AND [Facility_Active_Flag]="Y", THEN Lookup [Position_ID] within Positions table WHEN IS([Facility_ID]) FOR each [Facility_ID] SUM(ARRAY{[funded_amount]} for each [Position_ID]}) * [Bank_Share] == [Facility Oustanding Exposure, Bank Share Only]
+        <v xml:space="preserve">For each active facility:
+1. Join position -&gt; position_detail on position_id (both as_of_date filtered)
+2. SUM(funded_amount) across all positions for the facility
+3. Multiply by COALESCE(bank_share_pct, 100) / 100 from facility_lender_allocation
 </v>
       </c>
       <c r="E26" t="str">
@@ -2663,24 +2669,29 @@
         <v>Calc</v>
       </c>
       <c r="J26" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Distinct([Facility ID]), WHEN IS(MAX(AS_OF_DATE) AND [Facility_Active_Flag]="Y", THEN Lookup [Position_ID] within Positions table WHEN IS([Facility_ID]) FOR each [Facility_ID] SUM(ARRAY{[funded_amount]} for each [Position_ID]}) * [Bank_Share] == [Facility Oustanding Exposure, Bank Share Only]
+        <v xml:space="preserve">For each active facility:
+1. Join position -&gt; position_detail on position_id (both as_of_date filtered)
+2. SUM(funded_amount) across all positions for the facility
+3. Multiply by COALESCE(bank_share_pct, 100) / 100 from facility_lender_allocation
 </v>
       </c>
       <c r="K26" t="str">
-        <v>Oustanding Exposure ($) (facility)</v>
+        <v>Outstanding Exposure ($) (facility)</v>
       </c>
       <c r="L26" t="str">
         <v>Y</v>
       </c>
       <c r="M26" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N26" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level funded_amount per counterparty.
+        <v xml:space="preserve">For each counterparty, sum facility-level outstanding exposure weighted
+by participation_pct from facility_counterparty_participation.
+Uses contractual pro-rata basis per FR Y-14Q requirements.
 </v>
       </c>
       <c r="O26" t="str">
-        <v>Oustanding Exposure ($) (counterparty)</v>
+        <v>Outstanding Exposure ($) (counterparty)</v>
       </c>
       <c r="P26" t="str">
         <v>Y</v>
@@ -2689,11 +2700,12 @@
         <v>Agg</v>
       </c>
       <c r="R26" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level funded_amount per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level outstanding exposure per L3 desk segment.
+Joins facility_master.lob_segment_id to enterprise_business_taxonomy.managed_segment_id.
 </v>
       </c>
       <c r="S26" t="str">
-        <v>Oustanding Exposure ($) (desk)</v>
+        <v>Outstanding Exposure ($) (desk)</v>
       </c>
       <c r="T26" t="str">
         <v>Y</v>
@@ -2702,11 +2714,12 @@
         <v>Agg</v>
       </c>
       <c r="V26" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level funded_amount per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level outstanding exposure per L2 portfolio segment.
+Traverses L3 -&gt; L2 via parent_segment_id.
 </v>
       </c>
       <c r="W26" t="str">
-        <v>Oustanding Exposure ($) (portfolio)</v>
+        <v>Outstanding Exposure ($) (portfolio)</v>
       </c>
       <c r="X26" t="str">
         <v>Y</v>
@@ -2715,11 +2728,12 @@
         <v>Agg</v>
       </c>
       <c r="Z26" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level funded_amount per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level outstanding exposure per L1 business segment.
+Traverses L3 -&gt; L2 -&gt; L1 via parent_segment_id chain.
 </v>
       </c>
       <c r="AA26" t="str">
-        <v>Oustanding Exposure ($) (business_segment)</v>
+        <v>Outstanding Exposure ($) (business_segment)</v>
       </c>
       <c r="AB26" t="str">
         <v/>
@@ -2923,7 +2937,7 @@
         <v>Facility Utilization Status (e.g., Sufficient, Approaching, Fully Utilized)</v>
       </c>
       <c r="D29" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated facility_utilization_status per facility.
+        <v xml:space="preserve">Calculated utilization_status_code per facility.
 </v>
       </c>
       <c r="E29" t="str">
@@ -2942,7 +2956,7 @@
         <v>Calc</v>
       </c>
       <c r="J29" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated facility_utilization_status per facility.
+        <v xml:space="preserve">Calculated utilization_status_code per facility.
 </v>
       </c>
       <c r="K29" t="str">
@@ -2955,7 +2969,7 @@
         <v>Agg</v>
       </c>
       <c r="N29" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level facility_utilization_status) per counterparty.
+        <v xml:space="preserve">SUM(facility-level utilization_status_code) per counterparty.
 </v>
       </c>
       <c r="O29" t="str">
@@ -2968,7 +2982,7 @@
         <v>Agg</v>
       </c>
       <c r="R29" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_utilization_status per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level utilization_status_code per L3 desk segment.
 </v>
       </c>
       <c r="S29" t="str">
@@ -2981,7 +2995,7 @@
         <v>Agg</v>
       </c>
       <c r="V29" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_utilization_status per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level utilization_status_code per L2 portfolio segment.
 </v>
       </c>
       <c r="W29" t="str">
@@ -2994,7 +3008,7 @@
         <v>Agg</v>
       </c>
       <c r="Z29" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_utilization_status per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level utilization_status_code per L1 business segment segment.
 </v>
       </c>
       <c r="AA29" t="str">
@@ -4683,14 +4697,15 @@
         <v>EXP-041</v>
       </c>
       <c r="B48" t="str" xml:space="preserve">
-        <v xml:space="preserve">Total interest earned on outstanding exposures during the reporting period.
+        <v xml:space="preserve">Total interest earned on outstanding exposures during the reporting period. Sources from facility_profitability_snapshot.interest_income_amt (ETL'd from core banking, includes proper accrual and day-count per ASC 310-20). Bank-share-adjusted via facility_lender_allocation.
 </v>
       </c>
       <c r="C48" t="str">
         <v>Interest Income</v>
       </c>
       <c r="D48" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(interest_income_amt) per facility from facility_profitability_snapshot. Weighted by bank share percentage.
+        <v xml:space="preserve">SUM(interest_income_amt) per facility from facility_profitability_snapshot.
+Weighted by bank_share_pct from facility_lender_allocation.
 </v>
       </c>
       <c r="E48" t="str">
@@ -4709,7 +4724,8 @@
         <v>Agg</v>
       </c>
       <c r="J48" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(interest_income_amt) per facility from facility_profitability_snapshot. Weighted by bank share percentage.
+        <v xml:space="preserve">SUM(interest_income_amt) per facility from facility_profitability_snapshot.
+Weighted by bank_share_pct from facility_lender_allocation.
 </v>
       </c>
       <c r="K48" t="str">
@@ -4719,10 +4735,11 @@
         <v>Y</v>
       </c>
       <c r="M48" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N48" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level interest_income_amt per counterparty.
+        <v xml:space="preserve">For each counterparty, sum facility-level interest income weighted
+by participation_pct from facility_counterparty_participation.
 </v>
       </c>
       <c r="O48" t="str">
@@ -4735,7 +4752,7 @@
         <v>Agg</v>
       </c>
       <c r="R48" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level interest_income_amt per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level interest income per L3 desk segment.
 </v>
       </c>
       <c r="S48" t="str">
@@ -4748,7 +4765,8 @@
         <v>Agg</v>
       </c>
       <c r="V48" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level interest_income_amt per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level interest income per L2 portfolio segment.
+Traverses L3 -&gt; L2 via parent_segment_id.
 </v>
       </c>
       <c r="W48" t="str">
@@ -4761,7 +4779,8 @@
         <v>Agg</v>
       </c>
       <c r="Z48" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level interest_income_amt per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level interest income per L1 business segment.
+Traverses L3 -&gt; L2 -&gt; L1 via parent_segment_id chain.
 </v>
       </c>
       <c r="AA48" t="str">
@@ -5899,7 +5918,7 @@
         <v>Pricing Tier</v>
       </c>
       <c r="D61" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read pricing_tier from facility_pricing_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Read pricing_tier_code from facility_detail_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="E61" t="str">
@@ -5918,7 +5937,7 @@
         <v>Raw</v>
       </c>
       <c r="J61" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read pricing_tier from facility_pricing_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Read pricing_tier_code from facility_detail_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="K61" t="str">
@@ -5931,7 +5950,7 @@
         <v>Raw</v>
       </c>
       <c r="N61" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read pricing_tier per counterparty.
+        <v xml:space="preserve">Read pricing_tier_code per counterparty.
 </v>
       </c>
       <c r="O61" t="str">
@@ -5944,7 +5963,7 @@
         <v>Agg</v>
       </c>
       <c r="R61" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pricing_tier per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level pricing_tier_code per L3 desk segment.
 </v>
       </c>
       <c r="S61" t="str">
@@ -5957,7 +5976,7 @@
         <v>Agg</v>
       </c>
       <c r="V61" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pricing_tier per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level pricing_tier_code per L2 portfolio segment.
 </v>
       </c>
       <c r="W61" t="str">
@@ -5970,7 +5989,7 @@
         <v>Agg</v>
       </c>
       <c r="Z61" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pricing_tier per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level pricing_tier_code per L1 business segment segment.
 </v>
       </c>
       <c r="AA61" t="str">
@@ -6264,14 +6283,19 @@
         <v>PROF-108</v>
       </c>
       <c r="B65" t="str" xml:space="preserve">
-        <v xml:space="preserve">Total interest cost incurred on funding sources attributable to the reporting unit during the period. At facility level, computed as the product of the committed amount, the bank's participation share, and the cost of funds rate. At higher rollup levels, aggregated as the sum of facility-level interest expense.
+        <v xml:space="preserve">Annualized interest cost on drawn/funded exposure. Computed as SUM(funded_amount) * bank_share_pct * cost_of_funds_pct at facility level. Uses funded basis (actual drawn amounts from position_detail) rather than committed basis, aligning with FR Y-9C Schedule HI Item 2.
 </v>
       </c>
       <c r="C65" t="str">
         <v>Interest Expense</v>
       </c>
-      <c r="D65" t="str">
-        <v>committed_facility_amt × bank_share_pct × cost_of_funds_rate</v>
+      <c r="D65" t="str" xml:space="preserve">
+        <v xml:space="preserve">For each active facility:
+1. Join position -&gt; position_detail, SUM(funded_amount) per facility
+2. Multiply by bank_share_pct / 100 from facility_lender_allocation
+3. Multiply by COALESCE(cost_of_funds_pct, all_in_rate_pct - spread_bps/100) / 100
+   from facility_pricing_snapshot
+</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -6288,8 +6312,13 @@
       <c r="I65" t="str">
         <v>Calc</v>
       </c>
-      <c r="J65" t="str">
-        <v>committed_facility_amt × bank_share_pct × cost_of_funds_rate</v>
+      <c r="J65" t="str" xml:space="preserve">
+        <v xml:space="preserve">For each active facility:
+1. Join position -&gt; position_detail, SUM(funded_amount) per facility
+2. Multiply by bank_share_pct / 100 from facility_lender_allocation
+3. Multiply by COALESCE(cost_of_funds_pct, all_in_rate_pct - spread_bps/100) / 100
+   from facility_pricing_snapshot
+</v>
       </c>
       <c r="K65" t="str">
         <v>Interest Expense (facility)</v>
@@ -6298,10 +6327,12 @@
         <v>Y</v>
       </c>
       <c r="M65" t="str">
-        <v>Agg</v>
-      </c>
-      <c r="N65" t="str">
-        <v>SUM(Facility Interest Expense) per counterparty</v>
+        <v>Calc</v>
+      </c>
+      <c r="N65" t="str" xml:space="preserve">
+        <v xml:space="preserve">For each counterparty, sum facility-level interest expense weighted
+by participation_pct from facility_counterparty_participation.
+</v>
       </c>
       <c r="O65" t="str">
         <v>Interest Expense (counterparty)</v>
@@ -6312,8 +6343,9 @@
       <c r="Q65" t="str">
         <v>Agg</v>
       </c>
-      <c r="R65" t="str">
-        <v>SUM(Facility Interest Expense) per L3 desk segment</v>
+      <c r="R65" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level interest expense per L3 desk segment.
+</v>
       </c>
       <c r="S65" t="str">
         <v>Interest Expense (desk)</v>
@@ -6324,8 +6356,10 @@
       <c r="U65" t="str">
         <v>Agg</v>
       </c>
-      <c r="V65" t="str">
-        <v>SUM(Facility Interest Expense) per L2 portfolio segment</v>
+      <c r="V65" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level interest expense per L2 portfolio segment.
+Traverses L3 -&gt; L2 via parent_segment_id.
+</v>
       </c>
       <c r="W65" t="str">
         <v>Interest Expense (portfolio)</v>
@@ -6336,8 +6370,10 @@
       <c r="Y65" t="str">
         <v>Agg</v>
       </c>
-      <c r="Z65" t="str">
-        <v>SUM(Facility Interest Expense) per L1 business segment (department)</v>
+      <c r="Z65" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level interest expense per L1 business segment.
+Traverses L3 -&gt; L2 -&gt; L1 via parent_segment_id chain.
+</v>
       </c>
       <c r="AA65" t="str">
         <v>Interest Expense (business_segment)</v>
@@ -7567,7 +7603,7 @@
         <v>Active</v>
       </c>
       <c r="D79" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of active_flag from facility_master.
+        <v xml:space="preserve">Direct lookup of is_active_flag from facility_master.
 </v>
       </c>
       <c r="E79" t="str">
@@ -7586,7 +7622,7 @@
         <v>Raw</v>
       </c>
       <c r="J79" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of active_flag from facility_master.
+        <v xml:space="preserve">Direct lookup of is_active_flag from facility_master.
 </v>
       </c>
       <c r="K79" t="str">
@@ -7599,7 +7635,7 @@
         <v>Raw</v>
       </c>
       <c r="N79" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read active_flag per counterparty.
+        <v xml:space="preserve">Read is_active_flag per counterparty.
 </v>
       </c>
       <c r="O79" t="str">
@@ -7612,7 +7648,7 @@
         <v>Agg</v>
       </c>
       <c r="R79" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level active_flag per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level is_active_flag per L3 desk segment.
 </v>
       </c>
       <c r="S79" t="str">
@@ -7625,7 +7661,7 @@
         <v>Agg</v>
       </c>
       <c r="V79" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level active_flag per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level is_active_flag per L2 portfolio segment.
 </v>
       </c>
       <c r="W79" t="str">
@@ -7638,7 +7674,7 @@
         <v>Agg</v>
       </c>
       <c r="Z79" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level active_flag per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level is_active_flag per L1 business segment segment.
 </v>
       </c>
       <c r="AA79" t="str">
@@ -9334,7 +9370,7 @@
         <v>Facility Active Flag</v>
       </c>
       <c r="D98" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated facility_active_flag per facility.
+        <v xml:space="preserve">Calculated facility_is_active_flag per facility.
 </v>
       </c>
       <c r="E98" t="str">
@@ -9353,7 +9389,7 @@
         <v>Calc</v>
       </c>
       <c r="J98" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated facility_active_flag per facility.
+        <v xml:space="preserve">Calculated facility_is_active_flag per facility.
 </v>
       </c>
       <c r="K98" t="str">
@@ -9366,7 +9402,7 @@
         <v>Agg</v>
       </c>
       <c r="N98" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level facility_active_flag) per counterparty.
+        <v xml:space="preserve">SUM(facility-level facility_is_active_flag) per counterparty.
 </v>
       </c>
       <c r="O98" t="str">
@@ -9379,7 +9415,7 @@
         <v>Agg</v>
       </c>
       <c r="R98" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_active_flag per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level facility_is_active_flag per L3 desk segment.
 </v>
       </c>
       <c r="S98" t="str">
@@ -9392,7 +9428,7 @@
         <v>Agg</v>
       </c>
       <c r="V98" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_active_flag per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level facility_is_active_flag per L2 portfolio segment.
 </v>
       </c>
       <c r="W98" t="str">
@@ -9405,7 +9441,7 @@
         <v>Agg</v>
       </c>
       <c r="Z98" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_active_flag per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level facility_is_active_flag per L1 business segment segment.
 </v>
       </c>
       <c r="AA98" t="str">

--- a/data/metrics_dimensions_filled.xlsx
+++ b/data/metrics_dimensions_filled.xlsx
@@ -2537,7 +2537,7 @@
         <v>EXP-017</v>
       </c>
       <c r="B25" t="str" xml:space="preserve">
-        <v xml:space="preserve">Bank-share-adjusted unfunded commitment amount. Measures contingent funding risk by summing unfunded positions per facility, applying the bank's share percentage from facility_lender_allocation. Derived as Committed Exposure minus Outstanding Exposure.
+        <v xml:space="preserve">Bank-share-adjusted unfunded commitment amount. Derived as committed_facility_amt minus SUM(funded_amount) from PRINCIPAL positions, multiplied by bank_share_pct / 100. Ensures the identity: Committed Exposure = Outstanding Exposure + Undrawn Exposure. Maps to FR Y-14Q Field 24 minus Field 25.
 </v>
       </c>
       <c r="C25" t="str">
@@ -2545,9 +2545,10 @@
       </c>
       <c r="D25" t="str" xml:space="preserve">
         <v xml:space="preserve">For each active facility:
-1. Join position -&gt; position_detail on position_id (both as_of_date filtered)
-2. SUM(unfunded_amount) across all positions for the facility
+1. SUM(funded_amount) from PRINCIPAL position_detail rows per facility
+2. Subtract from committed_facility_amt to get unfunded amount
 3. Multiply by COALESCE(bank_share_pct, 100) / 100 from facility_lender_allocation
+Ensures: Committed Exposure = Outstanding Exposure + Undrawn Exposure
 </v>
       </c>
       <c r="E25" t="str">
@@ -2567,9 +2568,10 @@
       </c>
       <c r="J25" t="str" xml:space="preserve">
         <v xml:space="preserve">For each active facility:
-1. Join position -&gt; position_detail on position_id (both as_of_date filtered)
-2. SUM(unfunded_amount) across all positions for the facility
+1. SUM(funded_amount) from PRINCIPAL position_detail rows per facility
+2. Subtract from committed_facility_amt to get unfunded amount
 3. Multiply by COALESCE(bank_share_pct, 100) / 100 from facility_lender_allocation
+Ensures: Committed Exposure = Outstanding Exposure + Undrawn Exposure
 </v>
       </c>
       <c r="K25" t="str">

--- a/data/metrics_dimensions_filled.xlsx
+++ b/data/metrics_dimensions_filled.xlsx
@@ -6575,14 +6575,14 @@
         <v>REF-003</v>
       </c>
       <c r="B68" t="str" xml:space="preserve">
-        <v xml:space="preserve">Average tenor of the underlying facilities across exposures. For facility, displayed the calculated tenor based on Origination Date ("Effective Date") and Maturity Date ("End Date") and other levels this metric is aggregated as an average to represent the average period of the underlying facilities.
+        <v xml:space="preserve">Average tenor of the underlying facilities across exposures. For facility, displayed the calculated tenor based on Origination Date ("Effective Date") and Maturity Date ("End Date"). At other levels this metric is aggregated as an average to represent the average period of the underlying facilities. Calculated from l2.facility_master.maturity_date and origination_date.
 </v>
       </c>
       <c r="C68" t="str">
         <v>Average Tenor (Years)</v>
       </c>
       <c r="D68" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Facility_ID, [Contract Level Maturity Date]- [Facility Level Effective Date]
+        <v xml:space="preserve">For each Facility_ID, (Maturity Date - Origination Date) / 365.25 to get tenor in years.
 </v>
       </c>
       <c r="E68" t="str">
@@ -6601,7 +6601,7 @@
         <v>Calc</v>
       </c>
       <c r="J68" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Facility_ID, [Contract Level Maturity Date]- [Facility Level Effective Date]
+        <v xml:space="preserve">For each Facility_ID, (Maturity Date - Origination Date) / 365.25 to get tenor in years.
 </v>
       </c>
       <c r="K68" t="str">
@@ -6614,7 +6614,7 @@
         <v>Avg</v>
       </c>
       <c r="N68" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of expected_tenor_months across counterparty facilities.
+        <v xml:space="preserve">Average of facility-level tenor (years) across counterparty facilities.
 </v>
       </c>
       <c r="O68" t="str">
@@ -6627,7 +6627,7 @@
         <v>Avg</v>
       </c>
       <c r="R68" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level expected_tenor_months per L3 desk segment.
+        <v xml:space="preserve">AVG of facility-level tenor (years) per L3 desk segment.
 </v>
       </c>
       <c r="S68" t="str">
@@ -6640,7 +6640,7 @@
         <v>Avg</v>
       </c>
       <c r="V68" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level expected_tenor_months per L2 portfolio segment.
+        <v xml:space="preserve">AVG of facility-level tenor (years) per L2 portfolio segment.
 </v>
       </c>
       <c r="W68" t="str">
@@ -6650,10 +6650,10 @@
         <v>Y</v>
       </c>
       <c r="Y68" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="Z68" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level expected_tenor_months per L1 business segment segment.
+        <v xml:space="preserve">AVG of facility-level tenor (years) per L1 business segment.
 </v>
       </c>
       <c r="AA68" t="str">

--- a/data/metrics_dimensions_filled.xlsx
+++ b/data/metrics_dimensions_filled.xlsx
@@ -1828,7 +1828,7 @@
         <v>Agg</v>
       </c>
       <c r="N17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level dpd_bucket_code per counterparty.
+        <v xml:space="preserve">MAX (worst bucket) of facility-level dpd_bucket_code per counterparty.
 </v>
       </c>
       <c r="O17" t="str">
@@ -1841,7 +1841,7 @@
         <v>Agg</v>
       </c>
       <c r="R17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level dpd_bucket_code per L3 desk segment.
+        <v xml:space="preserve">MAX (worst bucket) of facility-level dpd_bucket_code per L3 desk segment.
 </v>
       </c>
       <c r="S17" t="str">
@@ -1854,7 +1854,7 @@
         <v>Agg</v>
       </c>
       <c r="V17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level dpd_bucket_code per L2 portfolio segment.
+        <v xml:space="preserve">MAX (worst bucket) of facility-level dpd_bucket_code per L2 portfolio segment.
 </v>
       </c>
       <c r="W17" t="str">
@@ -1867,7 +1867,7 @@
         <v>Agg</v>
       </c>
       <c r="Z17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level dpd_bucket_code per L1 business segment segment.
+        <v xml:space="preserve">MAX (worst bucket) of facility-level dpd_bucket_code per L1 business segment.
 </v>
       </c>
       <c r="AA17" t="str">
@@ -5205,10 +5205,10 @@
         <v>Y</v>
       </c>
       <c r="M53" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="N53" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of rwa_amt across counterparty facilities.
+        <v xml:space="preserve">SUM of facility-level rwa_amt per counterparty.
 </v>
       </c>
       <c r="O53" t="str">
@@ -5231,10 +5231,10 @@
         <v>Y</v>
       </c>
       <c r="U53" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="V53" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level rwa_amt per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level rwa_amt per L2 portfolio segment.
 </v>
       </c>
       <c r="W53" t="str">
@@ -5244,10 +5244,10 @@
         <v>Y</v>
       </c>
       <c r="Y53" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="Z53" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level rwa_amt per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level rwa_amt per L1 business segment.
 </v>
       </c>
       <c r="AA53" t="str">

--- a/data/metrics_dimensions_filled.xlsx
+++ b/data/metrics_dimensions_filled.xlsx
@@ -1828,7 +1828,7 @@
         <v>Agg</v>
       </c>
       <c r="N17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level dpd_bucket_code per counterparty.
+        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per counterparty.
 </v>
       </c>
       <c r="O17" t="str">
@@ -1841,7 +1841,7 @@
         <v>Agg</v>
       </c>
       <c r="R17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level dpd_bucket_code per L3 desk segment.
+        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per L3 desk segment.
 </v>
       </c>
       <c r="S17" t="str">
@@ -1854,7 +1854,7 @@
         <v>Agg</v>
       </c>
       <c r="V17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level dpd_bucket_code per L2 portfolio segment.
+        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per L2 portfolio segment.
 </v>
       </c>
       <c r="W17" t="str">
@@ -1867,7 +1867,7 @@
         <v>Agg</v>
       </c>
       <c r="Z17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level dpd_bucket_code per L1 business segment segment.
+        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per L1 business segment.
 </v>
       </c>
       <c r="AA17" t="str">
@@ -2451,7 +2451,7 @@
         <v>Expected Loss ($)</v>
       </c>
       <c r="D24" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(expected_loss_usd) per facility from stress_test_result. Weighted by bank share percentage.
+        <v xml:space="preserve">SUM(stressed_expected_loss) per facility from stress_test_result. Weighted by bank share percentage.
 </v>
       </c>
       <c r="E24" t="str">
@@ -2470,7 +2470,7 @@
         <v>Agg</v>
       </c>
       <c r="J24" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(expected_loss_usd) per facility from stress_test_result. Weighted by bank share percentage.
+        <v xml:space="preserve">SUM(stressed_expected_loss) per facility from stress_test_result. Weighted by bank share percentage.
 </v>
       </c>
       <c r="K24" t="str">
@@ -2483,7 +2483,7 @@
         <v>Agg</v>
       </c>
       <c r="N24" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level expected_loss_usd per counterparty.
+        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per counterparty.
 </v>
       </c>
       <c r="O24" t="str">
@@ -2496,7 +2496,7 @@
         <v>Agg</v>
       </c>
       <c r="R24" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level expected_loss_usd per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per L3 desk segment.
 </v>
       </c>
       <c r="S24" t="str">
@@ -2509,7 +2509,7 @@
         <v>Agg</v>
       </c>
       <c r="V24" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level expected_loss_usd per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per L2 portfolio segment.
 </v>
       </c>
       <c r="W24" t="str">
@@ -2522,7 +2522,7 @@
         <v>Agg</v>
       </c>
       <c r="Z24" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level expected_loss_usd per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per L1 business segment segment.
 </v>
       </c>
       <c r="AA24" t="str">

--- a/data/metrics_dimensions_filled.xlsx
+++ b/data/metrics_dimensions_filled.xlsx
@@ -5205,10 +5205,10 @@
         <v>Y</v>
       </c>
       <c r="M53" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="N53" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of rwa_amt across counterparty facilities.
+        <v xml:space="preserve">SUM of facility-level rwa_amt per counterparty.
 </v>
       </c>
       <c r="O53" t="str">
@@ -5231,10 +5231,10 @@
         <v>Y</v>
       </c>
       <c r="U53" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="V53" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level rwa_amt per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level rwa_amt per L2 portfolio segment.
 </v>
       </c>
       <c r="W53" t="str">
@@ -5244,10 +5244,10 @@
         <v>Y</v>
       </c>
       <c r="Y53" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="Z53" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level rwa_amt per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level rwa_amt per L1 business segment.
 </v>
       </c>
       <c r="AA53" t="str">

--- a/data/metrics_dimensions_filled.xlsx
+++ b/data/metrics_dimensions_filled.xlsx
@@ -487,14 +487,19 @@
         <v>AMD-001</v>
       </c>
       <c r="B3" t="str" xml:space="preserve">
-        <v xml:space="preserve">Date amendment became effective.
+        <v xml:space="preserve">Effective date of the most recent amendment on a facility. At rollup levels,
+reports the latest (MAX) amendment effective date across the group — shows
+how recently amendment activity occurred within each counterparty, desk,
+portfolio, or business segment.
 </v>
       </c>
       <c r="C3" t="str">
         <v>Amendment Start Date</v>
       </c>
       <c r="D3" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read effective_date from facility_master for each facility.
+        <v xml:space="preserve">Latest amendment effective_date per facility, converted to epoch seconds
+for numeric comparison. One facility may have multiple amendments;
+MAX selects the most recent.
 </v>
       </c>
       <c r="E3" t="str">
@@ -513,7 +518,9 @@
         <v>Raw</v>
       </c>
       <c r="J3" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read effective_date from facility_master for each facility.
+        <v xml:space="preserve">Latest amendment effective_date per facility, converted to epoch seconds
+for numeric comparison. One facility may have multiple amendments;
+MAX selects the most recent.
 </v>
       </c>
       <c r="K3" t="str">
@@ -526,7 +533,8 @@
         <v>Agg</v>
       </c>
       <c r="N3" t="str" xml:space="preserve">
-        <v xml:space="preserve">Latest (MAX) effective_date per counterparty.
+        <v xml:space="preserve">Latest amendment effective_date across all facilities for each
+counterparty. Uses amendment_event.counterparty_id directly.
 </v>
       </c>
       <c r="O3" t="str">
@@ -539,7 +547,7 @@
         <v>Agg</v>
       </c>
       <c r="R3" t="str" xml:space="preserve">
-        <v xml:space="preserve">Latest (MAX) effective_date per L3 desk segment.
+        <v xml:space="preserve">Latest amendment effective_date per L3 desk segment.
 </v>
       </c>
       <c r="S3" t="str">
@@ -552,7 +560,8 @@
         <v>Agg</v>
       </c>
       <c r="V3" t="str" xml:space="preserve">
-        <v xml:space="preserve">Latest (MAX) effective_date per L2 portfolio segment.
+        <v xml:space="preserve">Latest amendment effective_date per L2 portfolio segment.
+Walks up hierarchy: L3 desk → L2 portfolio via parent_segment_id.
 </v>
       </c>
       <c r="W3" t="str">
@@ -565,7 +574,8 @@
         <v>Agg</v>
       </c>
       <c r="Z3" t="str" xml:space="preserve">
-        <v xml:space="preserve">Latest (MAX) effective_date per L1 business segment.
+        <v xml:space="preserve">Latest amendment effective_date per L1 business segment.
+Walks up hierarchy: L3 → L2 → L1 via parent_segment_id chain.
 </v>
       </c>
       <c r="AA3" t="str">
@@ -580,14 +590,19 @@
         <v>AMD-002</v>
       </c>
       <c r="B4" t="str" xml:space="preserve">
-        <v xml:space="preserve">Status of amendment within the approval lifecycle.
+        <v xml:space="preserve">Count of amendments by approval lifecycle status (e.g., Prospect Identified,
+In Underwriting, Under Credit Review, Pending Approval, Complete, Rejected).
+At each rollup level, provides a distribution breakdown showing how many
+amendments fall into each status category. Key CRO indicator for amendment
+pipeline health and bottleneck identification.
 </v>
       </c>
       <c r="C4" t="str">
-        <v>Amendment Status</v>
+        <v>Amendment Status Count</v>
       </c>
       <c r="D4" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read amendment status flag for each active facility.
+        <v xml:space="preserve">Count of amendments per facility, broken out by status category.
+Each row represents one (facility, status) combination with its count.
 </v>
       </c>
       <c r="E4" t="str">
@@ -606,11 +621,12 @@
         <v>Raw</v>
       </c>
       <c r="J4" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read amendment status flag for each active facility.
+        <v xml:space="preserve">Count of amendments per facility, broken out by status category.
+Each row represents one (facility, status) combination with its count.
 </v>
       </c>
       <c r="K4" t="str">
-        <v>Amendment Status (facility)</v>
+        <v>Amendment Status Count (facility)</v>
       </c>
       <c r="L4" t="str">
         <v>Y</v>
@@ -619,11 +635,13 @@
         <v>Agg</v>
       </c>
       <c r="N4" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with amendment status per counterparty.
+        <v xml:space="preserve">Count of amendments per counterparty by status category.
+Uses amendment_event.counterparty_id directly (no participation weighting —
+amendments are discrete events, not divisible by ownership share).
 </v>
       </c>
       <c r="O4" t="str">
-        <v>Amendment Status (counterparty)</v>
+        <v>Amendment Status Count (counterparty)</v>
       </c>
       <c r="P4" t="str">
         <v>Y</v>
@@ -632,11 +650,11 @@
         <v>Agg</v>
       </c>
       <c r="R4" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with amendment status per L3 desk segment.
+        <v xml:space="preserve">Count of amendments per L3 desk segment by status category.
 </v>
       </c>
       <c r="S4" t="str">
-        <v>Amendment Status (desk)</v>
+        <v>Amendment Status Count (desk)</v>
       </c>
       <c r="T4" t="str">
         <v>Y</v>
@@ -645,11 +663,12 @@
         <v>Agg</v>
       </c>
       <c r="V4" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with amendment status per L2 portfolio segment.
+        <v xml:space="preserve">Count of amendments per L2 portfolio segment by status category.
+Walks up hierarchy: L3 desk → L2 portfolio via parent_segment_id.
 </v>
       </c>
       <c r="W4" t="str">
-        <v>Amendment Status (portfolio)</v>
+        <v>Amendment Status Count (portfolio)</v>
       </c>
       <c r="X4" t="str">
         <v>Y</v>
@@ -658,11 +677,12 @@
         <v>Agg</v>
       </c>
       <c r="Z4" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with amendment status per L1 business segment.
+        <v xml:space="preserve">Count of amendments per L1 business segment by status category.
+Walks up hierarchy: L3 → L2 → L1 via parent_segment_id chain.
 </v>
       </c>
       <c r="AA4" t="str">
-        <v>Amendment Status (business_segment)</v>
+        <v>Amendment Status Count (business_segment)</v>
       </c>
       <c r="AB4" t="str">
         <v/>
@@ -673,14 +693,18 @@
         <v>AMD-003</v>
       </c>
       <c r="B5" t="str" xml:space="preserve">
-        <v xml:space="preserve">Type of contractual amendment (e.g., covenant reset, maturity extension).
+        <v xml:space="preserve">Count of amendments by contractual type (e.g., Commitment Changes, Pricing,
+Tenor-Maturity, Amortization, Currency). At each rollup level, provides a
+distribution breakdown showing amendment activity by type category.
+Key CRO indicator for understanding what credit terms are being renegotiated.
 </v>
       </c>
       <c r="C5" t="str">
-        <v>Amendment Type</v>
+        <v>Amendment Type Count</v>
       </c>
       <c r="D5" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of amendment_type_code from amendment_type_dim.
+        <v xml:space="preserve">Count of amendments per facility, broken out by amendment type.
+Each row represents one (facility, type) combination with its count.
 </v>
       </c>
       <c r="E5" t="str">
@@ -699,11 +723,12 @@
         <v>Raw</v>
       </c>
       <c r="J5" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of amendment_type_code from amendment_type_dim.
+        <v xml:space="preserve">Count of amendments per facility, broken out by amendment type.
+Each row represents one (facility, type) combination with its count.
 </v>
       </c>
       <c r="K5" t="str">
-        <v>Amendment Type (facility)</v>
+        <v>Amendment Type Count (facility)</v>
       </c>
       <c r="L5" t="str">
         <v>Y</v>
@@ -712,11 +737,13 @@
         <v>Agg</v>
       </c>
       <c r="N5" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level amendment_type_code) per counterparty.
+        <v xml:space="preserve">Count of amendments per counterparty by type category.
+Uses amendment_event.counterparty_id directly (amendments are
+discrete events, not weighted by participation share).
 </v>
       </c>
       <c r="O5" t="str">
-        <v>Amendment Type (counterparty)</v>
+        <v>Amendment Type Count (counterparty)</v>
       </c>
       <c r="P5" t="str">
         <v>Y</v>
@@ -725,11 +752,11 @@
         <v>Agg</v>
       </c>
       <c r="R5" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level amendment_type_code per L3 desk segment.
+        <v xml:space="preserve">Count of amendments per L3 desk segment by type category.
 </v>
       </c>
       <c r="S5" t="str">
-        <v>Amendment Type (desk)</v>
+        <v>Amendment Type Count (desk)</v>
       </c>
       <c r="T5" t="str">
         <v>Y</v>
@@ -738,11 +765,12 @@
         <v>Agg</v>
       </c>
       <c r="V5" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level amendment_type_code per L2 portfolio segment.
+        <v xml:space="preserve">Count of amendments per L2 portfolio segment by type category.
+Walks up hierarchy: L3 desk → L2 portfolio via parent_segment_id.
 </v>
       </c>
       <c r="W5" t="str">
-        <v>Amendment Type (portfolio)</v>
+        <v>Amendment Type Count (portfolio)</v>
       </c>
       <c r="X5" t="str">
         <v>Y</v>
@@ -751,11 +779,12 @@
         <v>Agg</v>
       </c>
       <c r="Z5" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level amendment_type_code per L1 business segment segment.
+        <v xml:space="preserve">Count of amendments per L1 business segment by type category.
+Walks up hierarchy: L3 → L2 → L1 via parent_segment_id chain.
 </v>
       </c>
       <c r="AA5" t="str">
-        <v>Amendment Type (business_segment)</v>
+        <v>Amendment Type Count (business_segment)</v>
       </c>
       <c r="AB5" t="str">
         <v/>
@@ -2254,14 +2283,26 @@
         <v>EXP-014</v>
       </c>
       <c r="B22" t="str" xml:space="preserve">
-        <v xml:space="preserve">Net Operating Income divided by Total Debt Service. Measures borrower's ability to meet debt obligations from operating cash flow, providing insight into covenant compliance and credit resilience.
+        <v xml:space="preserve">Cashflow (Net Operating Income) divided by Total Debt Service (Interest Expense + Principal Payments). Measures borrower's ability to meet debt obligations from operating cash flow. DSCR &gt; 1.0 means the borrower generates enough income to cover debt payments. Key covenant compliance and credit resilience indicator.
+Ingredient derivation:
+  - NOI (noi_amt): L2 facility_financial_snapshot — raw atomic input
+  - Interest Expense (interest_expense_amt): L2 facility_financial_snapshot — raw
+  - Principal Payment (principal_payment_amt): L2 facility_financial_snapshot — raw
+  - Total Debt Service = interest_expense_amt + principal_payment_amt (L3 derived)
+  - DSCR = noi_amt / Total Debt Service (L3 derived)
+Rollup uses sum-ratio pattern: SUM(NOI) / SUM(Debt Service) at each level, preserving the mathematical relationship between numerator and denominator.
 </v>
       </c>
       <c r="C22" t="str">
         <v>Debt Service Coverage Ratio (DSCR)</v>
       </c>
       <c r="D22" t="str" xml:space="preserve">
-        <v xml:space="preserve">Compute DSCR = noi_amt / total_debt_service_amt per facility.
+        <v xml:space="preserve">For each facility:
+  1. LOAD noi_amt, interest_expense_amt, principal_payment_amt
+     from l2.facility_financial_snapshot
+  2. COMPUTE Total Debt Service = interest_expense_amt + principal_payment_amt
+  3. COMPUTE DSCR = noi_amt / Total Debt Service
+Ingredients: noi_amt (L2), interest_expense_amt (L2), principal_payment_amt (L2)
 </v>
       </c>
       <c r="E22" t="str">
@@ -2280,7 +2321,12 @@
         <v>Raw</v>
       </c>
       <c r="J22" t="str" xml:space="preserve">
-        <v xml:space="preserve">Compute DSCR = noi_amt / total_debt_service_amt per facility.
+        <v xml:space="preserve">For each facility:
+  1. LOAD noi_amt, interest_expense_amt, principal_payment_amt
+     from l2.facility_financial_snapshot
+  2. COMPUTE Total Debt Service = interest_expense_amt + principal_payment_amt
+  3. COMPUTE DSCR = noi_amt / Total Debt Service
+Ingredients: noi_amt (L2), interest_expense_amt (L2), principal_payment_amt (L2)
 </v>
       </c>
       <c r="K22" t="str">
@@ -2293,8 +2339,13 @@
         <v>Calc</v>
       </c>
       <c r="N22" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average DSCR per counterparty:
-SUM(dscr * drawn_amount) / SUM(drawn_amount).
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD all facility-level ingredients (noi_amt, interest_expense_amt,
+     principal_payment_amt) for facilities belonging to this counterparty
+  2. COMPUTE SUM(noi_amt) across all facilities = Counterparty Cashflow
+  3. COMPUTE SUM(interest_expense_amt + principal_payment_amt) = Counterparty Debt Service
+  4. COMPUTE Counterparty DSCR = Counterparty Cashflow / Counterparty Debt Service
+Sum-ratio rollup preserves ingredient traceability.
 </v>
       </c>
       <c r="O22" t="str">
@@ -2307,8 +2358,12 @@
         <v>Calc</v>
       </c>
       <c r="R22" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average DSCR per L3 desk segment:
-SUM(dscr * drawn_amount) / SUM(drawn_amount).
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOOKUP managed_segment_id from enterprise_business_taxonomy
+     via facility_master.lob_segment_id
+  2. COMPUTE SUM(noi_amt) / SUM(interest_expense + principal_payment)
+     for all facilities mapped to this desk
+Sum-ratio rollup: aggregate ingredients first, then divide.
 </v>
       </c>
       <c r="S22" t="str">
@@ -2321,8 +2376,11 @@
         <v>Calc</v>
       </c>
       <c r="V22" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average DSCR per L2 portfolio segment:
-SUM(dscr * drawn_amount) / SUM(drawn_amount).
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. COMPUTE SUM(noi_amt) / SUM(interest_expense + principal_payment)
+     for all facilities whose desk rolls up to this portfolio
+Sum-ratio rollup: aggregate ingredients first, then divide.
 </v>
       </c>
       <c r="W22" t="str">
@@ -2335,8 +2393,11 @@
         <v>Calc</v>
       </c>
       <c r="Z22" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average DSCR per L1 business segment:
-SUM(dscr * drawn_amount) / SUM(drawn_amount).
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. COMPUTE SUM(noi_amt) / SUM(interest_expense + principal_payment)
+     for all facilities whose desk ultimately rolls up to this segment
+Sum-ratio rollup: aggregate ingredients first, then divide.
 </v>
       </c>
       <c r="AA22" t="str">

--- a/data/metrics_dimensions_filled.xlsx
+++ b/data/metrics_dimensions_filled.xlsx
@@ -5548,7 +5548,7 @@
         <v>Avg</v>
       </c>
       <c r="N56" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average all_in_rate_pct per counterparty.
+        <v xml:space="preserve">For each Counterparty_ID, lookup Facility_IDs in Facility Master where IS(Counterparty_ID), SELECT all_in_rate_pct. Weight by bank share committed amount (committed_amount * bank_share_pct). Weighted average = SUM(rate * weight) / SUM(weight).
 </v>
       </c>
       <c r="O56" t="str">
@@ -5561,7 +5561,7 @@
         <v>Avg</v>
       </c>
       <c r="R56" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average all_in_rate_pct per L3 desk segment.
+        <v xml:space="preserve">For each L3 LoB, lookup lob_segment_id from enterprise_business_taxonomy, then lookup facility_id in Facility Master where IS(lob_segment_id). SELECT all_in_rate_pct, weight by bank share committed exposure (committed_amount * bank_share_pct). Weighted average = SUM(rate * weight) / SUM(weight).
 </v>
       </c>
       <c r="S56" t="str">
@@ -5571,10 +5571,10 @@
         <v>Y</v>
       </c>
       <c r="U56" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="V56" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average all_in_rate_pct per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 LoB, lookup lob_segment_id from enterprise_business_taxonomy, then lookup facility_id in Facility Master where IS(lob_segment_id). SELECT all_in_rate_pct, weight by bank share committed exposure (committed_amount * bank_share_pct). Calculated = SUM(rate * weight) / SUM(weight).
 </v>
       </c>
       <c r="W56" t="str">
@@ -5584,10 +5584,10 @@
         <v>Y</v>
       </c>
       <c r="Y56" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="Z56" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average all_in_rate_pct per L1 business segment.
+        <v xml:space="preserve">For each L1 LoB, lookup lob_segment_id from enterprise_business_taxonomy, then lookup facility_id in Facility Master where IS(lob_segment_id). SELECT all_in_rate_pct, weight by bank share committed exposure (committed_amount * bank_share_pct). Calculated = SUM(rate * weight) / SUM(weight).
 </v>
       </c>
       <c r="AA56" t="str">
@@ -6457,7 +6457,7 @@
         <v>Number of Loans</v>
       </c>
       <c r="D66" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read number_of_loans from facility_exposure_snapshot for each facility.
+        <v xml:space="preserve">For each Facility_ID, COUNT DISTINCT(Position_ID) from l2.position. Result materialized to l3.facility_exposure_calc.number_of_loans.
 </v>
       </c>
       <c r="E66" t="str">
@@ -6473,10 +6473,10 @@
         <v>Y</v>
       </c>
       <c r="I66" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="J66" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read number_of_loans from facility_exposure_snapshot for each facility.
+        <v xml:space="preserve">For each Facility_ID, COUNT DISTINCT(Position_ID) from l2.position. Result materialized to l3.facility_exposure_calc.number_of_loans.
 </v>
       </c>
       <c r="K66" t="str">
@@ -6489,7 +6489,7 @@
         <v>Agg</v>
       </c>
       <c r="N66" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of number_of_loans per counterparty.
+        <v xml:space="preserve">For each Counterparty_ID, lookup in Facility Table when IS(Counterparty_ID), SUM(Number_of_loans) from l3.facility_exposure_calc.
 </v>
       </c>
       <c r="O66" t="str">
@@ -6502,7 +6502,7 @@
         <v>Agg</v>
       </c>
       <c r="R66" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of number_of_loans per L3 desk segment.
+        <v xml:space="preserve">For each L3 LoB, lookup lob_segment_id from enterprise_business_taxonomy WHERE tree_level='L3', then lookup facility_id in facility_master, SUM(Number_of_loans) from l3.facility_exposure_calc.
 </v>
       </c>
       <c r="S66" t="str">
@@ -6515,7 +6515,7 @@
         <v>Agg</v>
       </c>
       <c r="V66" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of number_of_loans per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 LoB, lookup lob_segment_id from enterprise_business_taxonomy WHERE tree_level='L2', then lookup facility_id in facility_master, SUM(Number_of_loans) from l3.facility_exposure_calc.
 </v>
       </c>
       <c r="W66" t="str">
@@ -6528,7 +6528,7 @@
         <v>Agg</v>
       </c>
       <c r="Z66" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of number_of_loans per L1 business segment.
+        <v xml:space="preserve">For each L1 LoB, lookup lob_segment_id from enterprise_business_taxonomy WHERE tree_level='L1', then lookup facility_id in facility_master, SUM(Number_of_loans) from l3.facility_exposure_calc.
 </v>
       </c>
       <c r="AA66" t="str">

--- a/data/metrics_dimensions_filled.xlsx
+++ b/data/metrics_dimensions_filled.xlsx
@@ -2342,10 +2342,11 @@
         <v xml:space="preserve">For each counterparty:
   1. LOAD all facility-level ingredients (noi_amt, interest_expense_amt,
      principal_payment_amt) for facilities belonging to this counterparty
-  2. COMPUTE SUM(noi_amt) across all facilities = Counterparty Cashflow
-  3. COMPUTE SUM(interest_expense_amt + principal_payment_amt) = Counterparty Debt Service
-  4. COMPUTE Counterparty DSCR = Counterparty Cashflow / Counterparty Debt Service
-Sum-ratio rollup preserves ingredient traceability.
+  2. CONVERT amounts to USD via l2.fx_rate spot rate (COALESCE to 1 for USD-denominated)
+  3. COMPUTE SUM(noi_amt × fx_rate) across all facilities = Counterparty Cashflow (USD)
+  4. COMPUTE SUM((interest_expense + principal_payment) × fx_rate) = Counterparty Debt Service (USD)
+  5. COMPUTE Counterparty DSCR = Counterparty Cashflow / Counterparty Debt Service
+Sum-ratio rollup with FX conversion preserves ingredient traceability across currencies.
 </v>
       </c>
       <c r="O22" t="str">
@@ -2361,9 +2362,10 @@
         <v xml:space="preserve">For each L3 Desk segment:
   1. LOOKUP managed_segment_id from enterprise_business_taxonomy
      via facility_master.lob_segment_id
-  2. COMPUTE SUM(noi_amt) / SUM(interest_expense + principal_payment)
+  2. CONVERT amounts to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(noi_amt × fx_rate) / SUM((interest_expense + principal_payment) × fx_rate)
      for all facilities mapped to this desk
-Sum-ratio rollup: aggregate ingredients first, then divide.
+Sum-ratio rollup with FX conversion: aggregate USD-converted ingredients first, then divide.
 </v>
       </c>
       <c r="S22" t="str">
@@ -2378,9 +2380,10 @@
       <c r="V22" t="str" xml:space="preserve">
         <v xml:space="preserve">For each L2 Portfolio segment:
   1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
-  2. COMPUTE SUM(noi_amt) / SUM(interest_expense + principal_payment)
+  2. CONVERT amounts to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(noi_amt × fx_rate) / SUM((interest_expense + principal_payment) × fx_rate)
      for all facilities whose desk rolls up to this portfolio
-Sum-ratio rollup: aggregate ingredients first, then divide.
+Sum-ratio rollup with FX conversion: aggregate USD-converted ingredients first, then divide.
 </v>
       </c>
       <c r="W22" t="str">
@@ -2395,9 +2398,10 @@
       <c r="Z22" t="str" xml:space="preserve">
         <v xml:space="preserve">For each L1 Business Segment / LoB:
   1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
-  2. COMPUTE SUM(noi_amt) / SUM(interest_expense + principal_payment)
+  2. CONVERT amounts to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(noi_amt × fx_rate) / SUM((interest_expense + principal_payment) × fx_rate)
      for all facilities whose desk ultimately rolls up to this segment
-Sum-ratio rollup: aggregate ingredients first, then divide.
+Sum-ratio rollup with FX conversion: aggregate USD-converted ingredients first, then divide.
 </v>
       </c>
       <c r="AA22" t="str">
@@ -4488,7 +4492,7 @@
         <v>Total Debt Service ($)</v>
       </c>
       <c r="D45" t="str" xml:space="preserve">
-        <v xml:space="preserve">Lookup Position_ID for each Facility_ID, Select bank_share and cost_of_funds from Facility_ID from Facility Master THEN (unfunded_amt * bank_share ) = [Facility Debt Service w/ Bank Share]
+        <v xml:space="preserve">Lookup total_debt_service_amt from facility_financial_snapshot, convert to USD via l2.fx_rate spot rate (COALESCE to 1 for USD-denominated facilities).
 </v>
       </c>
       <c r="E45" t="str">
@@ -4507,7 +4511,7 @@
         <v>Calc</v>
       </c>
       <c r="J45" t="str" xml:space="preserve">
-        <v xml:space="preserve">Lookup Position_ID for each Facility_ID, Select bank_share and cost_of_funds from Facility_ID from Facility Master THEN (unfunded_amt * bank_share ) = [Facility Debt Service w/ Bank Share]
+        <v xml:space="preserve">Lookup total_debt_service_amt from facility_financial_snapshot, convert to USD via l2.fx_rate spot rate (COALESCE to 1 for USD-denominated facilities).
 </v>
       </c>
       <c r="K45" t="str">
@@ -4520,7 +4524,7 @@
         <v>Agg</v>
       </c>
       <c r="N45" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_debt_service_amt per counterparty.
+        <v xml:space="preserve">SUM of facility-level total_debt_service_amt converted to USD per counterparty.
 </v>
       </c>
       <c r="O45" t="str">
@@ -4533,7 +4537,7 @@
         <v>Agg</v>
       </c>
       <c r="R45" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_debt_service_amt per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level total_debt_service_amt converted to USD per L3 desk segment.
 </v>
       </c>
       <c r="S45" t="str">
@@ -4546,7 +4550,7 @@
         <v>Agg</v>
       </c>
       <c r="V45" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_debt_service_amt per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level total_debt_service_amt converted to USD per L2 portfolio segment.
 </v>
       </c>
       <c r="W45" t="str">
@@ -4559,7 +4563,7 @@
         <v>Agg</v>
       </c>
       <c r="Z45" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_debt_service_amt per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level total_debt_service_amt converted to USD per L1 business segment.
 </v>
       </c>
       <c r="AA45" t="str">
@@ -5362,7 +5366,8 @@
         <v>Calc</v>
       </c>
       <c r="N54" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(ebitda) / SUM(total_debt_service) per counterparty.
+        <v xml:space="preserve">SUM(ebitda × fx_rate) / SUM(total_debt_service × fx_rate) per counterparty.
+Amounts converted to USD via l2.fx_rate before aggregation.
 </v>
       </c>
       <c r="O54" t="str">
@@ -5375,7 +5380,8 @@
         <v>Calc</v>
       </c>
       <c r="R54" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(ebitda) / SUM(total_debt_service) per L3 desk segment.
+        <v xml:space="preserve">SUM(ebitda × fx_rate) / SUM(total_debt_service × fx_rate) per L3 desk segment.
+Amounts converted to USD via l2.fx_rate before aggregation.
 </v>
       </c>
       <c r="S54" t="str">
@@ -5388,7 +5394,8 @@
         <v>Calc</v>
       </c>
       <c r="V54" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(ebitda) / SUM(total_debt_service) per L2 portfolio segment.
+        <v xml:space="preserve">SUM(ebitda × fx_rate) / SUM(total_debt_service × fx_rate) per L2 portfolio segment.
+Amounts converted to USD via l2.fx_rate before aggregation.
 </v>
       </c>
       <c r="W54" t="str">
@@ -5401,7 +5408,8 @@
         <v>Calc</v>
       </c>
       <c r="Z54" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(ebitda) / SUM(total_debt_service) per L1 business segment.
+        <v xml:space="preserve">SUM(ebitda × fx_rate) / SUM(total_debt_service × fx_rate) per L1 business segment.
+Amounts converted to USD via l2.fx_rate before aggregation.
 </v>
       </c>
       <c r="AA54" t="str">

--- a/data/metrics_dimensions_filled.xlsx
+++ b/data/metrics_dimensions_filled.xlsx
@@ -6497,7 +6497,7 @@
         <v>Agg</v>
       </c>
       <c r="N66" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Counterparty_ID, lookup in Facility Table when IS(Counterparty_ID), SUM(Number_of_loans) from l3.facility_exposure_calc.
+        <v xml:space="preserve">For each Counterparty_ID, COUNT DISTINCT(Position_ID) from l2.position joined to l2.facility_master.
 </v>
       </c>
       <c r="O66" t="str">
@@ -6510,7 +6510,7 @@
         <v>Agg</v>
       </c>
       <c r="R66" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each L3 LoB, lookup lob_segment_id from enterprise_business_taxonomy WHERE tree_level='L3', then lookup facility_id in facility_master, SUM(Number_of_loans) from l3.facility_exposure_calc.
+        <v xml:space="preserve">For each L3 LoB, COUNT DISTINCT(Position_ID) from l2.position joined to l2.facility_master and l1.enterprise_business_taxonomy.
 </v>
       </c>
       <c r="S66" t="str">
@@ -6523,7 +6523,7 @@
         <v>Agg</v>
       </c>
       <c r="V66" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each L2 LoB, lookup lob_segment_id from enterprise_business_taxonomy WHERE tree_level='L2', then lookup facility_id in facility_master, SUM(Number_of_loans) from l3.facility_exposure_calc.
+        <v xml:space="preserve">For each L2 LoB, COUNT DISTINCT(Position_ID) from l2.position joined to l2.facility_master and l1.enterprise_business_taxonomy hierarchy.
 </v>
       </c>
       <c r="W66" t="str">
@@ -6536,7 +6536,7 @@
         <v>Agg</v>
       </c>
       <c r="Z66" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each L1 LoB, lookup lob_segment_id from enterprise_business_taxonomy WHERE tree_level='L1', then lookup facility_id in facility_master, SUM(Number_of_loans) from l3.facility_exposure_calc.
+        <v xml:space="preserve">For each L1 LoB, COUNT DISTINCT(Position_ID) from l2.position joined to l2.facility_master and l1.enterprise_business_taxonomy hierarchy.
 </v>
       </c>
       <c r="AA66" t="str">

--- a/data/metrics_dimensions_filled.xlsx
+++ b/data/metrics_dimensions_filled.xlsx
@@ -1539,14 +1539,14 @@
         <v>EXP-005</v>
       </c>
       <c r="B14" t="str" xml:space="preserve">
-        <v xml:space="preserve">The portion of total funding-related expense attributed to a specific exposure or portfolio. At facility level, calculated as SUM across all positions of (funded_amount * interest_rate), adjusted for bank share. At counterparty level, further adjusted by counterparty participation_pct. At desk/portfolio/segment levels, aggregated as SUM.
+        <v xml:space="preserve">The portion of total funding-related expense attributed to a specific exposure or portfolio. At facility level, calculated as SUM across all positions of (funded_amount * interest_rate), converted to USD via FX rate and adjusted for bank share. At counterparty level, further adjusted by counterparty participation_pct. At desk/portfolio/segment levels, aggregated as SUM via EBT hierarchy.
 </v>
       </c>
       <c r="C14" t="str">
         <v>Cost of Funds ($)</v>
       </c>
       <c r="D14" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each position under the facility: funded_amount * interest_rate = Position Cost of Funds. Adjusted by bank_share: SUM(funded_amount * interest_rate) * bank_share_pct / 100. Joins position_detail → position (for facility_id) → facility_master.
+        <v xml:space="preserve">For each position under the facility, compute funded_amount x interest_rate, convert to USD using the FX spot rate (defaults to 1.0 for USD positions). Sum across all positions, then multiply by the bank's share percentage. Result = annual cost of funds for this facility in USD.
 </v>
       </c>
       <c r="E14" t="str">
@@ -1565,7 +1565,7 @@
         <v>Calc</v>
       </c>
       <c r="J14" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each position under the facility: funded_amount * interest_rate = Position Cost of Funds. Adjusted by bank_share: SUM(funded_amount * interest_rate) * bank_share_pct / 100. Joins position_detail → position (for facility_id) → facility_master.
+        <v xml:space="preserve">For each position under the facility, compute funded_amount x interest_rate, convert to USD using the FX spot rate (defaults to 1.0 for USD positions). Sum across all positions, then multiply by the bank's share percentage. Result = annual cost of funds for this facility in USD.
 </v>
       </c>
       <c r="K14" t="str">
@@ -1578,7 +1578,7 @@
         <v>Agg</v>
       </c>
       <c r="N14" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each counterparty: SUM of facility-level cost of funds weighted by counterparty participation_pct from facility_counterparty_participation.
+        <v xml:space="preserve">Sum each facility's cost of funds (USD, bank-share-adjusted), then weight by the counterparty's participation percentage. Aggregates across all facilities where the counterparty has a current participation record.
 </v>
       </c>
       <c r="O14" t="str">
@@ -1591,7 +1591,7 @@
         <v>Agg</v>
       </c>
       <c r="R14" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level cost of funds (bank-share-adjusted) per L3 desk segment.
+        <v xml:space="preserve">Sum of facility-level cost of funds (USD, bank-share-adjusted) for all facilities assigned to each L3 desk segment in the organizational hierarchy.
 </v>
       </c>
       <c r="S14" t="str">
@@ -1604,7 +1604,7 @@
         <v>Agg</v>
       </c>
       <c r="V14" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level cost of funds (bank-share-adjusted) per L2 portfolio segment.
+        <v xml:space="preserve">Sum of facility-level cost of funds (USD, bank-share-adjusted) for all facilities within each L2 portfolio segment, traversing the EBT hierarchy from desk (L3) to portfolio (L2) via parent_segment_id.
 </v>
       </c>
       <c r="W14" t="str">
@@ -1617,7 +1617,7 @@
         <v>Agg</v>
       </c>
       <c r="Z14" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level cost of funds (bank-share-adjusted) per L1 business segment.
+        <v xml:space="preserve">Sum of facility-level cost of funds (USD, bank-share-adjusted) for all facilities within each L1 business segment, traversing the full EBT hierarchy from desk (L3) through portfolio (L2) to segment (L1).
 </v>
       </c>
       <c r="AA14" t="str">
@@ -1639,7 +1639,7 @@
         <v>Counterparty Share or Allocation (%)</v>
       </c>
       <c r="D15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of participation_pct from facility_counterparty_participation for the primary counterparty on each facility. SCD-filtered to current rows only.
+        <v xml:space="preserve">Direct lookup of participation_pct from facility_counterparty_participation for the primary counterparty on each facility. Uses current records only.
 </v>
       </c>
       <c r="E15" t="str">
@@ -1658,7 +1658,7 @@
         <v>Raw</v>
       </c>
       <c r="J15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of participation_pct from facility_counterparty_participation for the primary counterparty on each facility. SCD-filtered to current rows only.
+        <v xml:space="preserve">Direct lookup of participation_pct from facility_counterparty_participation for the primary counterparty on each facility. Uses current records only.
 </v>
       </c>
       <c r="K15" t="str">
@@ -6837,7 +6837,7 @@
         <v>Counterparty ID</v>
       </c>
       <c r="D70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from facility_master for each active facility. SCD-filtered to current records only.
+        <v xml:space="preserve">Direct lookup of counterparty_id from facility_master for each active facility. Uses current records only (SCD2 filtered).
 </v>
       </c>
       <c r="E70" t="str">
@@ -6856,7 +6856,7 @@
         <v>Raw</v>
       </c>
       <c r="J70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from facility_master for each active facility. SCD-filtered to current records only.
+        <v xml:space="preserve">Direct lookup of counterparty_id from facility_master for each active facility. Uses current records only (SCD2 filtered).
 </v>
       </c>
       <c r="K70" t="str">
@@ -6930,7 +6930,7 @@
         <v>Counterparty Name</v>
       </c>
       <c r="D71" t="str" xml:space="preserve">
-        <v xml:space="preserve">Lookup counterparty_id from facility_master for each active facility. The numeric counterparty_id serves as proxy for the legal name (string values returned via catalogue metadata). SCD-filtered to current records.
+        <v xml:space="preserve">Lookup counterparty_id from facility_master for each active facility. The numeric counterparty_id serves as proxy for the legal name (string values resolved via counterparty dimension join at display time). Uses current records only.
 </v>
       </c>
       <c r="E71" t="str">
@@ -6949,7 +6949,7 @@
         <v>Raw</v>
       </c>
       <c r="J71" t="str" xml:space="preserve">
-        <v xml:space="preserve">Lookup counterparty_id from facility_master for each active facility. The numeric counterparty_id serves as proxy for the legal name (string values returned via catalogue metadata). SCD-filtered to current records.
+        <v xml:space="preserve">Lookup counterparty_id from facility_master for each active facility. The numeric counterparty_id serves as proxy for the legal name (string values resolved via counterparty dimension join at display time). Uses current records only.
 </v>
       </c>
       <c r="K71" t="str">
@@ -7023,7 +7023,7 @@
         <v>Country</v>
       </c>
       <c r="D72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Lookup country for each facility via counterparty → country_dim join path. Returns counterparty_id as numeric proxy (country_name resolved at display time via dimension join). SCD-filtered to current records.
+        <v xml:space="preserve">Lookup country for each facility via counterparty → country_dim join path. Returns counterparty_id as numeric proxy (country_name resolved at display time via dimension join). Uses current records only.
 </v>
       </c>
       <c r="E72" t="str">
@@ -7042,7 +7042,7 @@
         <v>Raw</v>
       </c>
       <c r="J72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Lookup country for each facility via counterparty → country_dim join path. Returns counterparty_id as numeric proxy (country_name resolved at display time via dimension join). SCD-filtered to current records.
+        <v xml:space="preserve">Lookup country for each facility via counterparty → country_dim join path. Returns counterparty_id as numeric proxy (country_name resolved at display time via dimension join). Uses current records only.
 </v>
       </c>
       <c r="K72" t="str">

--- a/data/metrics_dimensions_filled.xlsx
+++ b/data/metrics_dimensions_filled.xlsx
@@ -1539,14 +1539,14 @@
         <v>EXP-005</v>
       </c>
       <c r="B14" t="str" xml:space="preserve">
-        <v xml:space="preserve">The portion of total funding-related expense attributed to a specific exposure or portfolio. At facility level, calculated as SUM across all positions of (funded_amount * interest_rate), adjusted for bank share. At counterparty level, further adjusted by counterparty participation_pct. At desk/portfolio/segment levels, aggregated as SUM.
+        <v xml:space="preserve">The portion of total funding-related expense attributed to a specific exposure or portfolio. At facility level, calculated as SUM across all positions of (funded_amount * interest_rate), converted to USD via FX rate and adjusted for bank share. At counterparty level, further adjusted by counterparty participation_pct. At desk/portfolio/segment levels, aggregated as SUM via EBT hierarchy.
 </v>
       </c>
       <c r="C14" t="str">
         <v>Cost of Funds ($)</v>
       </c>
       <c r="D14" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each position under the facility: funded_amount * interest_rate = Position Cost of Funds. Adjusted by bank_share: SUM(funded_amount * interest_rate) * bank_share_pct / 100. Joins position_detail → position (for facility_id) → facility_master.
+        <v xml:space="preserve">For each position under the facility, compute funded_amount x interest_rate, convert to USD using the FX spot rate (defaults to 1.0 for USD positions). Sum across all positions, then multiply by the bank's share percentage. Result = annual cost of funds for this facility in USD.
 </v>
       </c>
       <c r="E14" t="str">
@@ -1565,7 +1565,7 @@
         <v>Calc</v>
       </c>
       <c r="J14" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each position under the facility: funded_amount * interest_rate = Position Cost of Funds. Adjusted by bank_share: SUM(funded_amount * interest_rate) * bank_share_pct / 100. Joins position_detail → position (for facility_id) → facility_master.
+        <v xml:space="preserve">For each position under the facility, compute funded_amount x interest_rate, convert to USD using the FX spot rate (defaults to 1.0 for USD positions). Sum across all positions, then multiply by the bank's share percentage. Result = annual cost of funds for this facility in USD.
 </v>
       </c>
       <c r="K14" t="str">
@@ -1578,7 +1578,7 @@
         <v>Agg</v>
       </c>
       <c r="N14" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each counterparty: SUM of facility-level cost of funds weighted by counterparty participation_pct from facility_counterparty_participation.
+        <v xml:space="preserve">Sum each facility's cost of funds (USD, bank-share-adjusted), then weight by the counterparty's participation percentage. Aggregates across all facilities where the counterparty has a current participation record.
 </v>
       </c>
       <c r="O14" t="str">
@@ -1591,7 +1591,7 @@
         <v>Agg</v>
       </c>
       <c r="R14" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level cost of funds (bank-share-adjusted) per L3 desk segment.
+        <v xml:space="preserve">Sum of facility-level cost of funds (USD, bank-share-adjusted) for all facilities assigned to each L3 desk segment in the organizational hierarchy.
 </v>
       </c>
       <c r="S14" t="str">
@@ -1604,7 +1604,7 @@
         <v>Agg</v>
       </c>
       <c r="V14" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level cost of funds (bank-share-adjusted) per L2 portfolio segment.
+        <v xml:space="preserve">Sum of facility-level cost of funds (USD, bank-share-adjusted) for all facilities within each L2 portfolio segment, traversing the EBT hierarchy from desk (L3) to portfolio (L2) via parent_segment_id.
 </v>
       </c>
       <c r="W14" t="str">
@@ -1617,7 +1617,7 @@
         <v>Agg</v>
       </c>
       <c r="Z14" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level cost of funds (bank-share-adjusted) per L1 business segment.
+        <v xml:space="preserve">Sum of facility-level cost of funds (USD, bank-share-adjusted) for all facilities within each L1 business segment, traversing the full EBT hierarchy from desk (L3) through portfolio (L2) to segment (L1).
 </v>
       </c>
       <c r="AA14" t="str">
@@ -1632,14 +1632,14 @@
         <v>EXP-006</v>
       </c>
       <c r="B15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure allocated to specific counterparty representing their share of the facility which the client can draw on. Concentration KPI measuring obligor dependency risk.
+        <v xml:space="preserve">Counterparty participation share in a facility — the percentage of a syndicated or participated facility allocated to a specific counterparty. At facility level, direct lookup from facility_counterparty_participation. At counterparty level, exposure-weighted average participation across all facilities. At desk/portfolio/segment, exposure-weighted average via EBT hierarchy. Key concentration KPI for Large Exposures Framework (LEX) and Single Counterparty Credit Limit (SCCL) compliance.
 </v>
       </c>
       <c r="C15" t="str">
         <v>Counterparty Share or Allocation (%)</v>
       </c>
       <c r="D15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of allocation_pct from facility_counterparty_participation.
+        <v xml:space="preserve">Direct lookup of participation_pct from facility_counterparty_participation for the primary counterparty on each facility. Uses current records only.
 </v>
       </c>
       <c r="E15" t="str">
@@ -1658,7 +1658,7 @@
         <v>Raw</v>
       </c>
       <c r="J15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of allocation_pct from facility_counterparty_participation.
+        <v xml:space="preserve">Direct lookup of participation_pct from facility_counterparty_participation for the primary counterparty on each facility. Uses current records only.
 </v>
       </c>
       <c r="K15" t="str">
@@ -1668,10 +1668,10 @@
         <v>Y</v>
       </c>
       <c r="M15" t="str">
-        <v>Raw</v>
+        <v>Avg</v>
       </c>
       <c r="N15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read allocation_pct per counterparty.
+        <v xml:space="preserve">Exposure-weighted average participation across all facilities for each counterparty. Weight = drawn_amount from facility_exposure_snapshot. Falls back to simple average if no exposure data available.
 </v>
       </c>
       <c r="O15" t="str">
@@ -1681,10 +1681,10 @@
         <v>Y</v>
       </c>
       <c r="Q15" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="R15" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level allocation_pct per L3 desk segment.
+        <v xml:space="preserve">Exposure-weighted average participation across all facilities per L3 desk segment via enterprise_business_taxonomy.
 </v>
       </c>
       <c r="S15" t="str">
@@ -1694,10 +1694,10 @@
         <v>Y</v>
       </c>
       <c r="U15" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="V15" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level allocation_pct per L2 portfolio segment.
+        <v xml:space="preserve">Exposure-weighted average participation across all facilities per L2 portfolio segment via enterprise_business_taxonomy hierarchy traversal.
 </v>
       </c>
       <c r="W15" t="str">
@@ -1707,10 +1707,10 @@
         <v>Y</v>
       </c>
       <c r="Y15" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="Z15" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level allocation_pct per L1 business segment segment.
+        <v xml:space="preserve">Exposure-weighted average participation across all facilities per L1 business segment via enterprise_business_taxonomy hierarchy traversal.
 </v>
       </c>
       <c r="AA15" t="str">
@@ -1725,14 +1725,14 @@
         <v>EXP-007</v>
       </c>
       <c r="B16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Flag identifying exposures requiring heightened monitoring due to elevated credit risk. Governance control used for enhanced monitoring, reserve consideration, and management reporting.
+        <v xml:space="preserve">Count of active Criticized risk flags across facilities. Early warning indicator of problem assets requiring heightened monitoring, reserve consideration, and management reporting. Sources from the risk_flag table filtering on flag_code = 'CRITICIZED' with uncleared status.
 </v>
       </c>
       <c r="C16" t="str">
         <v>Criticized Portfolios</v>
       </c>
       <c r="D16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if criticized rating (internal_risk_rating &gt;= 6), 0 otherwise.
+        <v xml:space="preserve">For each facility, count active risk flags where flag_code = 'CRITICIZED' and the flag has not been cleared (cleared_ts IS NULL).
 </v>
       </c>
       <c r="E16" t="str">
@@ -1748,10 +1748,10 @@
         <v>Y</v>
       </c>
       <c r="I16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="J16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if criticized rating (internal_risk_rating &gt;= 6), 0 otherwise.
+        <v xml:space="preserve">For each facility, count active risk flags where flag_code = 'CRITICIZED' and the flag has not been cleared (cleared_ts IS NULL).
 </v>
       </c>
       <c r="K16" t="str">
@@ -1761,10 +1761,10 @@
         <v>Y</v>
       </c>
       <c r="M16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="N16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per counterparty.
+        <v xml:space="preserve">For each counterparty, sum facility-level criticized flag counts across all facilities belonging to that counterparty.
 </v>
       </c>
       <c r="O16" t="str">
@@ -1774,10 +1774,10 @@
         <v>Y</v>
       </c>
       <c r="Q16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="R16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per L3 desk.
+        <v xml:space="preserve">Sum of criticized flag counts per L3 desk segment. Joins facility_master to enterprise_business_taxonomy via lob_segment_id.
 </v>
       </c>
       <c r="S16" t="str">
@@ -1787,10 +1787,10 @@
         <v>Y</v>
       </c>
       <c r="U16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="V16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per L2 portfolio.
+        <v xml:space="preserve">Sum of criticized flag counts per L2 portfolio segment. Traverses enterprise_business_taxonomy hierarchy from L3 to L2 via parent_segment_id.
 </v>
       </c>
       <c r="W16" t="str">
@@ -1800,10 +1800,10 @@
         <v>Y</v>
       </c>
       <c r="Y16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="Z16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per L1 business segment.
+        <v xml:space="preserve">Sum of criticized flag counts per L1 business segment. Full hierarchy traversal L3 → L2 → L1 via enterprise_business_taxonomy.
 </v>
       </c>
       <c r="AA16" t="str">
@@ -1818,14 +1818,14 @@
         <v>EXP-008</v>
       </c>
       <c r="B17" t="str" xml:space="preserve">
-        <v xml:space="preserve">Total exposure amount allocated across multiple legal entities. Supports intra-group concentration transparency.
+        <v xml:space="preserve">Total committed exposure amount (bank share) allocated across multiple legal entities for facilities flagged as cross-entity. Quantifies inter-entity concentration risk and supports intra-group transparency for GSIB reporting. Sources from counterparty_derived (L3) for the cross-entity flag and facility_exposure_snapshot (L2) for committed amounts.
 </v>
       </c>
       <c r="C17" t="str">
         <v>Cross Entity Exposure Amount</v>
       </c>
       <c r="D17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(total_cross_entity_exposure_usd) per facility from counterparty_exposure_summary. Weighted by bank share percentage.
+        <v xml:space="preserve">For each facility flagged as cross-entity, committed exposure amount weighted by the bank's participation share (bank_share_pct). Facilities without cross-entity flag are excluded.
 </v>
       </c>
       <c r="E17" t="str">
@@ -1844,7 +1844,7 @@
         <v>Agg</v>
       </c>
       <c r="J17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(total_cross_entity_exposure_usd) per facility from counterparty_exposure_summary. Weighted by bank share percentage.
+        <v xml:space="preserve">For each facility flagged as cross-entity, committed exposure amount weighted by the bank's participation share (bank_share_pct). Facilities without cross-entity flag are excluded.
 </v>
       </c>
       <c r="K17" t="str">
@@ -1857,7 +1857,7 @@
         <v>Agg</v>
       </c>
       <c r="N17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per counterparty.
+        <v xml:space="preserve">For each counterparty, sum of bank-share-weighted committed amounts across all facilities flagged as cross-entity.
 </v>
       </c>
       <c r="O17" t="str">
@@ -1870,7 +1870,7 @@
         <v>Agg</v>
       </c>
       <c r="R17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per L3 desk segment.
+        <v xml:space="preserve">Sum of cross-entity committed exposure per L3 desk segment via enterprise_business_taxonomy.
 </v>
       </c>
       <c r="S17" t="str">
@@ -1883,7 +1883,7 @@
         <v>Agg</v>
       </c>
       <c r="V17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per L2 portfolio segment.
+        <v xml:space="preserve">Sum of cross-entity committed exposure per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
 </v>
       </c>
       <c r="W17" t="str">
@@ -1896,7 +1896,7 @@
         <v>Agg</v>
       </c>
       <c r="Z17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per L1 business segment segment.
+        <v xml:space="preserve">Sum of cross-entity committed exposure per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
 </v>
       </c>
       <c r="AA17" t="str">
@@ -1911,14 +1911,14 @@
         <v>EXP-009</v>
       </c>
       <c r="B18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Number of days outstanding payments is past due as grouped into 3 "buckets", 0-30 Days, 31-60 Days, 61-90+ Days. Used for staging classification and early credit deterioration monitoring.
+        <v xml:space="preserve">Maximum days payment overdue per facility, calculated from raw payment records in the payment_ledger table. For each facility, identifies payments where applied amount &lt; amount due, computes days overdue as reporting date minus payment_due_date, takes the MAX, then classifies into buckets: 1 = 0-30 days, 2 = 31-60 days, 3 = 61-90+ days. At aggregate levels, reports the worst (MAX) bucket across constituents.
 </v>
       </c>
       <c r="C18" t="str">
         <v>Days Payment Overdue Bucket</v>
       </c>
       <c r="D18" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Facility_ID lookup the Payments records in the Payment Lockbox table, For each payment record where [Payment_Due_Date] &gt; Today() IF ([Pmt_Applied] &lt;[Pmt_Due])&gt;=1, THEN Today() - [Payment_due_date] ==[Days Overdue] SELECT MAX ([Days Overdue] then lookup in Payments Overdue bucket)
+        <v xml:space="preserve">For each facility, lookup payment records in payment_ledger where payment_due_date &lt; reporting date and payment_applied_amt &lt; payment_amount_due (underpaid). Calculate days overdue = reporting date minus payment_due_date. Take MAX days overdue, then classify into overdue bucket: 1 (0-30), 2 (31-60), 3 (61-90+).
 </v>
       </c>
       <c r="E18" t="str">
@@ -1937,7 +1937,7 @@
         <v>Calc</v>
       </c>
       <c r="J18" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Facility_ID lookup the Payments records in the Payment Lockbox table, For each payment record where [Payment_Due_Date] &gt; Today() IF ([Pmt_Applied] &lt;[Pmt_Due])&gt;=1, THEN Today() - [Payment_due_date] ==[Days Overdue] SELECT MAX ([Days Overdue] then lookup in Payments Overdue bucket)
+        <v xml:space="preserve">For each facility, lookup payment records in payment_ledger where payment_due_date &lt; reporting date and payment_applied_amt &lt; payment_amount_due (underpaid). Calculate days overdue = reporting date minus payment_due_date. Take MAX days overdue, then classify into overdue bucket: 1 (0-30), 2 (31-60), 3 (61-90+).
 </v>
       </c>
       <c r="K18" t="str">
@@ -1950,7 +1950,7 @@
         <v>Agg</v>
       </c>
       <c r="N18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per counterparty.
+        <v xml:space="preserve">Worst-case (MAX) overdue bucket across all facilities per counterparty. Identifies the most severely overdue facility for each borrower.
 </v>
       </c>
       <c r="O18" t="str">
@@ -1963,7 +1963,7 @@
         <v>Agg</v>
       </c>
       <c r="R18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per L3 desk segment.
+        <v xml:space="preserve">Worst-case (MAX) overdue bucket per L3 desk segment. Shows the most severe delinquency in each organizational unit.
 </v>
       </c>
       <c r="S18" t="str">
@@ -1976,7 +1976,7 @@
         <v>Agg</v>
       </c>
       <c r="V18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per L2 portfolio segment.
+        <v xml:space="preserve">Worst-case (MAX) overdue bucket per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
 </v>
       </c>
       <c r="W18" t="str">
@@ -1989,7 +1989,7 @@
         <v>Agg</v>
       </c>
       <c r="Z18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per L1 business segment.
+        <v xml:space="preserve">Worst-case (MAX) overdue bucket per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
 </v>
       </c>
       <c r="AA18" t="str">
@@ -2509,14 +2509,25 @@
         <v>EXP-015</v>
       </c>
       <c r="B24" t="str" xml:space="preserve">
-        <v xml:space="preserve">Expected Loss divided by Exposure. Derived KPI measuring loss intensity relative to exposure size, enabling comparative risk ranking across facilities or counterparties.
+        <v xml:space="preserve">Expected Loss as a percentage of committed exposure. Computed from L2 atomic risk parameters: PD (probability of default) × LGD (loss given default). At aggregate levels, uses sum-ratio rollup: SUM(PD × LGD × Committed) / SUM(Committed) × 100 — the exposure-weighted average EL rate. This ensures mathematically consistent aggregation (never averages pre-computed rates). Key credit risk quantification metric for comparing loss intensity across facilities, counterparties, and business segments.
+Ingredient derivation:
+  - PD (pd_pct): L2 facility_risk_snapshot — probability of default (%)
+  - LGD (lgd_pct): L2 facility_risk_snapshot — loss given default (%)
+  - Committed Exposure (committed_amount): L2 facility_exposure_snapshot — raw
+  - EL Rate = PD × LGD (at facility level, committed cancels in ratio)
+  - Aggregate EL Rate = SUM(PD × LGD × Committed) / SUM(Committed) × 100
 </v>
       </c>
       <c r="C24" t="str">
         <v>Expected Loss Rate (%)</v>
       </c>
       <c r="D24" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of expected_loss_rate_pct per facility.
+        <v xml:space="preserve">For each facility:
+  1. LOAD pd_pct, lgd_pct from l2.facility_risk_snapshot
+  2. LOAD committed_amount from l2.facility_exposure_snapshot
+  3. COMPUTE EL Rate = SUM(PD/100 × LGD/100 × Committed) / SUM(Committed) × 100
+     At facility grain, committed cancels → EL Rate ≈ PD × LGD / 100
+Ingredients: pd_pct (L2), lgd_pct (L2), committed_amount (L2)
 </v>
       </c>
       <c r="E24" t="str">
@@ -2532,10 +2543,15 @@
         <v>Y</v>
       </c>
       <c r="I24" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="J24" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of expected_loss_rate_pct per facility.
+        <v xml:space="preserve">For each facility:
+  1. LOAD pd_pct, lgd_pct from l2.facility_risk_snapshot
+  2. LOAD committed_amount from l2.facility_exposure_snapshot
+  3. COMPUTE EL Rate = SUM(PD/100 × LGD/100 × Committed) / SUM(Committed) × 100
+     At facility grain, committed cancels → EL Rate ≈ PD × LGD / 100
+Ingredients: pd_pct (L2), lgd_pct (L2), committed_amount (L2)
 </v>
       </c>
       <c r="K24" t="str">
@@ -2545,10 +2561,15 @@
         <v>Y</v>
       </c>
       <c r="M24" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N24" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level expected_loss_rate_pct per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD pd_pct, lgd_pct for all facilities belonging to this counterparty
+  2. LOAD committed_amount for each facility
+  3. CONVERT to USD via l2.fx_rate spot rate
+  4. COMPUTE SUM(PD × LGD × Committed × FX) / SUM(Committed × FX) × 100
+Sum-ratio rollup with FX: exposure-weighted average EL rate in USD terms.
 </v>
       </c>
       <c r="O24" t="str">
@@ -2558,10 +2579,14 @@
         <v>Y</v>
       </c>
       <c r="Q24" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="R24" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level expected_loss_rate_pct per L3 desk segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOOKUP managed_segment_id from enterprise_business_taxonomy
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(PD × LGD × Committed × FX) / SUM(Committed × FX) × 100
+Sum-ratio rollup: exposure-weighted average EL rate per desk.
 </v>
       </c>
       <c r="S24" t="str">
@@ -2571,10 +2596,14 @@
         <v>Y</v>
       </c>
       <c r="U24" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V24" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level expected_loss_rate_pct per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(PD × LGD × Committed × FX) / SUM(Committed × FX) × 100
+Sum-ratio rollup: exposure-weighted average EL rate per portfolio.
 </v>
       </c>
       <c r="W24" t="str">
@@ -2584,10 +2613,14 @@
         <v>Y</v>
       </c>
       <c r="Y24" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z24" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level expected_loss_rate_pct per L1 business segment segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(PD × LGD × Committed × FX) / SUM(Committed × FX) × 100
+Sum-ratio rollup: exposure-weighted average EL rate per segment.
 </v>
       </c>
       <c r="AA24" t="str">
@@ -2602,14 +2635,25 @@
         <v>EXP-016</v>
       </c>
       <c r="B25" t="str" xml:space="preserve">
-        <v xml:space="preserve">PD × LGD × Exposure expressed in USD. Calculated forward-looking loss metric supporting provisioning, capital planning, and stress testing analytics.
+        <v xml:space="preserve">Expected Loss in dollar terms: PD × LGD × Committed Exposure × Bank Share. Computed from L2 atomic risk parameters and exposure data — NOT from stressed scenarios. This is the base (unstressed) expected credit loss, the foundation for provisioning, capital planning, and CECL/IFRS 9 reserve estimation.
+Ingredient derivation:
+  - PD (pd_pct): L2 facility_risk_snapshot — probability of default (%)
+  - LGD (lgd_pct): L2 facility_risk_snapshot — loss given default (%)
+  - Committed Exposure (committed_amount): L2 facility_exposure_snapshot — raw
+  - Bank Share (bank_share_pct): L2 facility_exposure_snapshot — participation %
+  - EL = (PD/100) × (LGD/100) × Committed × (Bank Share/100)
+Rollup uses direct-sum: SUM(facility EL) at each aggregate level. FX conversion applied at aggregate levels for multi-currency portfolios.
 </v>
       </c>
       <c r="C25" t="str">
         <v>Expected Loss ($)</v>
       </c>
       <c r="D25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(stressed_expected_loss) per facility from stress_test_result. Weighted by bank share percentage.
+        <v xml:space="preserve">For each facility:
+  1. LOAD pd_pct, lgd_pct from l2.facility_risk_snapshot
+  2. LOAD committed_amount, bank_share_pct from l2.facility_exposure_snapshot
+  3. COMPUTE EL = (PD/100) × (LGD/100) × Committed × (Bank Share/100)
+Ingredients: pd_pct (L2), lgd_pct (L2), committed_amount (L2), bank_share_pct (L2)
 </v>
       </c>
       <c r="E25" t="str">
@@ -2625,10 +2669,14 @@
         <v>Y</v>
       </c>
       <c r="I25" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="J25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(stressed_expected_loss) per facility from stress_test_result. Weighted by bank share percentage.
+        <v xml:space="preserve">For each facility:
+  1. LOAD pd_pct, lgd_pct from l2.facility_risk_snapshot
+  2. LOAD committed_amount, bank_share_pct from l2.facility_exposure_snapshot
+  3. COMPUTE EL = (PD/100) × (LGD/100) × Committed × (Bank Share/100)
+Ingredients: pd_pct (L2), lgd_pct (L2), committed_amount (L2), bank_share_pct (L2)
 </v>
       </c>
       <c r="K25" t="str">
@@ -2641,7 +2689,11 @@
         <v>Agg</v>
       </c>
       <c r="N25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD facility-level EL for all facilities of this counterparty
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(facility EL × FX rate) = Counterparty EL (USD)
+Direct-sum rollup with FX conversion.
 </v>
       </c>
       <c r="O25" t="str">
@@ -2654,7 +2706,11 @@
         <v>Agg</v>
       </c>
       <c r="R25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per L3 desk segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOOKUP managed_segment_id from enterprise_business_taxonomy
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(facility EL × FX rate) per desk
+Direct-sum rollup with FX conversion.
 </v>
       </c>
       <c r="S25" t="str">
@@ -2667,7 +2723,11 @@
         <v>Agg</v>
       </c>
       <c r="V25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(facility EL × FX rate) per portfolio
+Direct-sum rollup with FX conversion.
 </v>
       </c>
       <c r="W25" t="str">
@@ -2680,7 +2740,11 @@
         <v>Agg</v>
       </c>
       <c r="Z25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per L1 business segment segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(facility EL × FX rate) per business segment
+Direct-sum rollup with FX conversion.
 </v>
       </c>
       <c r="AA25" t="str">
@@ -3090,14 +3154,14 @@
         <v>EXP-021</v>
       </c>
       <c r="B30" t="str" xml:space="preserve">
-        <v xml:space="preserve">Derived categorical classification (Sufficient, Approaching, Fully Utilized) of utilization level based on current drawn exposure relative to committed amount. Operational KPI providing early warning insight into limit pressure, liquidity usage, and potential capacity constraints.
+        <v xml:space="preserve">Derived categorical classification of utilization level based on current drawn exposure relative to committed amount. Maps facility utilization percentage against l1.utilization_status_dim threshold ranges to return status labels (e.g., Sufficient, Approaching, Fully Utilized). Operational KPI providing early warning insight into limit pressure, liquidity usage, and potential capacity constraints.
 </v>
       </c>
       <c r="C30" t="str">
-        <v>Facility Utilization Status (e.g., Sufficient, Approaching, Fully Utilized)</v>
+        <v>Utilization Status (Utilized Exposure to Committed Exposure)</v>
       </c>
       <c r="D30" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated utilization_status_code per facility.
+        <v xml:space="preserve">For each facility, compute utilization_pct from L2 atomic data (drawn_amount / committed_amount * 100), then match against l1.utilization_status_dim threshold ranges (utilization_min_pct &lt;= pct &lt; utilization_max_pct) to return status_name.
 </v>
       </c>
       <c r="E30" t="str">
@@ -3116,63 +3180,63 @@
         <v>Calc</v>
       </c>
       <c r="J30" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated utilization_status_code per facility.
+        <v xml:space="preserve">For each facility, compute utilization_pct from L2 atomic data (drawn_amount / committed_amount * 100), then match against l1.utilization_status_dim threshold ranges (utilization_min_pct &lt;= pct &lt; utilization_max_pct) to return status_name.
 </v>
       </c>
       <c r="K30" t="str">
-        <v>Facility Utilization Status (e.g., Sufficient, Approaching, Fully Utilized) (facility)</v>
+        <v>Utilization Status (Utilized Exposure to Committed Exposure) (facility)</v>
       </c>
       <c r="L30" t="str">
         <v>Y</v>
       </c>
       <c r="M30" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N30" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level utilization_status_code) per counterparty.
+        <v xml:space="preserve">Compute counterparty-level utilization pct via sum-ratio with FX conversion: SUM(drawn * fx) / SUM(committed * fx) * 100. Then look up status from utilization_status_dim threshold ranges.
 </v>
       </c>
       <c r="O30" t="str">
-        <v>Facility Utilization Status (e.g., Sufficient, Approaching, Fully Utilized) (counterparty)</v>
+        <v>Utilization Status (Utilized Exposure to Committed Exposure) (counterparty)</v>
       </c>
       <c r="P30" t="str">
         <v>Y</v>
       </c>
       <c r="Q30" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R30" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level utilization_status_code per L3 desk segment.
+        <v xml:space="preserve">Compute L3 desk-level utilization pct via sum-ratio with FX conversion, then look up status from utilization_status_dim threshold ranges.
 </v>
       </c>
       <c r="S30" t="str">
-        <v>Facility Utilization Status (e.g., Sufficient, Approaching, Fully Utilized) (desk)</v>
+        <v>Utilization Status (Utilized Exposure to Committed Exposure) (desk)</v>
       </c>
       <c r="T30" t="str">
         <v>Y</v>
       </c>
       <c r="U30" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V30" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level utilization_status_code per L2 portfolio segment.
+        <v xml:space="preserve">Compute L2 portfolio-level utilization pct via sum-ratio with FX conversion (one-hop EBT hierarchy), then look up status from utilization_status_dim threshold ranges.
 </v>
       </c>
       <c r="W30" t="str">
-        <v>Facility Utilization Status (e.g., Sufficient, Approaching, Fully Utilized) (portfolio)</v>
+        <v>Utilization Status (Utilized Exposure to Committed Exposure) (portfolio)</v>
       </c>
       <c r="X30" t="str">
         <v>Y</v>
       </c>
       <c r="Y30" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z30" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level utilization_status_code per L1 business segment segment.
+        <v xml:space="preserve">Compute L1 business segment-level utilization pct via sum-ratio with FX conversion (two-hop EBT hierarchy), then look up status from utilization_status_dim threshold ranges.
 </v>
       </c>
       <c r="AA30" t="str">
-        <v>Facility Utilization Status (e.g., Sufficient, Approaching, Fully Utilized) (business_segment)</v>
+        <v>Utilization Status (Utilized Exposure to Committed Exposure) (business_segment)</v>
       </c>
       <c r="AB30" t="str">
         <v/>
@@ -5796,14 +5860,15 @@
         <v>PRC-003</v>
       </c>
       <c r="B59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of exposures within portfolio with approved pricing or policy exceptions. Derived governance KPI measuring policy discipline and risk culture strength.
+        <v xml:space="preserve">Percentage of facilities with approved pricing or policy exceptions. Computed as COUNT(exception facilities) / COUNT(total facilities) × 100. Sourced from L2 facility_pricing_snapshot — the atomic pricing record — using the is_pricing_exception_flag. At aggregate levels, uses count-ratio rollup: re-counts exceptions and totals across all constituent facilities, never averages pre-computed rates. Key governance KPI measuring policy discipline, risk culture strength, and pricing override frequency.
 </v>
       </c>
       <c r="C59" t="str">
         <v>Exception Rate (%)</v>
       </c>
       <c r="D59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if pricing exception, 0 otherwise.
+        <v xml:space="preserve">Binary flag: 1.0 if pricing exception approved, 0.0 otherwise.
+Ingredients: is_pricing_exception_flag (L2 facility_pricing_snapshot)
 </v>
       </c>
       <c r="E59" t="str">
@@ -5822,7 +5887,8 @@
         <v>Calc</v>
       </c>
       <c r="J59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if pricing exception, 0 otherwise.
+        <v xml:space="preserve">Binary flag: 1.0 if pricing exception approved, 0.0 otherwise.
+Ingredients: is_pricing_exception_flag (L2 facility_pricing_snapshot)
 </v>
       </c>
       <c r="K59" t="str">
@@ -5835,7 +5901,10 @@
         <v>Calc</v>
       </c>
       <c r="N59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with pricing exception per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD is_pricing_exception_flag for all facilities of this counterparty
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup: re-counts from facility-level flags.
 </v>
       </c>
       <c r="O59" t="str">
@@ -5848,7 +5917,10 @@
         <v>Calc</v>
       </c>
       <c r="R59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with pricing exception per L3 desk.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOOKUP managed_segment_id from enterprise_business_taxonomy
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup per desk.
 </v>
       </c>
       <c r="S59" t="str">
@@ -5861,7 +5933,10 @@
         <v>Calc</v>
       </c>
       <c r="V59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with pricing exception per L2 portfolio.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup per portfolio.
 </v>
       </c>
       <c r="W59" t="str">
@@ -5874,7 +5949,10 @@
         <v>Calc</v>
       </c>
       <c r="Z59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with pricing exception per L1 business segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup per business segment.
 </v>
       </c>
       <c r="AA59" t="str">
@@ -5889,14 +5967,14 @@
         <v>PRC-004</v>
       </c>
       <c r="B60" t="str" xml:space="preserve">
-        <v xml:space="preserve">Fee percentage applied to committed or undrawn exposure. Calculated KPI supporting pricing adequacy and revenue optimization analysis.
+        <v xml:space="preserve">Fee percentage applied to committed or undrawn exposure. Sourced from l2.facility_pricing_snapshot at facility level. Supports pricing adequacy and revenue optimization analysis. Aggregate levels use exposure-weighted average with FX conversion to USD.
 </v>
       </c>
       <c r="C60" t="str">
         <v>Fee Rate (%)</v>
       </c>
       <c r="D60" t="str" xml:space="preserve">
-        <v xml:space="preserve">Fee Income / Average Balance
+        <v xml:space="preserve">Direct lookup of fee_rate_pct from l2.facility_pricing_snapshot.
 </v>
       </c>
       <c r="E60" t="str">
@@ -5912,10 +5990,10 @@
         <v>Y</v>
       </c>
       <c r="I60" t="str">
-        <v>Calc</v>
+        <v>Raw</v>
       </c>
       <c r="J60" t="str" xml:space="preserve">
-        <v xml:space="preserve">Fee Income / Average Balance
+        <v xml:space="preserve">Direct lookup of fee_rate_pct from l2.facility_pricing_snapshot.
 </v>
       </c>
       <c r="K60" t="str">
@@ -5928,7 +6006,7 @@
         <v>Avg</v>
       </c>
       <c r="N60" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of fee_rate_pct across counterparty facilities.
+        <v xml:space="preserve">Supplementary (not in primary specification at counterparty level). Exposure-weighted average fee rate per counterparty with FX conversion: SUM(fee_rate * committed_amt * fx) / SUM(committed_amt * fx).
 </v>
       </c>
       <c r="O60" t="str">
@@ -5941,7 +6019,7 @@
         <v>Avg</v>
       </c>
       <c r="R60" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level fee_rate_pct per L3 desk segment.
+        <v xml:space="preserve">Supplementary. Exposure-weighted average fee rate per L3 desk segment with FX conversion.
 </v>
       </c>
       <c r="S60" t="str">
@@ -5954,7 +6032,7 @@
         <v>Avg</v>
       </c>
       <c r="V60" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level fee_rate_pct per L2 portfolio segment.
+        <v xml:space="preserve">Supplementary. Exposure-weighted average fee rate per L2 portfolio segment with FX conversion.
 </v>
       </c>
       <c r="W60" t="str">
@@ -5964,10 +6042,10 @@
         <v>Y</v>
       </c>
       <c r="Y60" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="Z60" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level fee_rate_pct per L1 business segment segment.
+        <v xml:space="preserve">Supplementary. Exposure-weighted average fee rate per L1 business segment with FX conversion.
 </v>
       </c>
       <c r="AA60" t="str">
@@ -6830,14 +6908,14 @@
         <v>REF-004</v>
       </c>
       <c r="B70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Unique system identifier assigned to the borrower or obligor. Used for exposure aggregation and risk consolidation.
+        <v xml:space="preserve">Unique system identifier assigned to the borrower or obligor. Used for exposure aggregation and risk consolidation across the GSIB. At facility level, returns the counterparty_id linked to each facility. At upper levels, returns COUNT(DISTINCT counterparty_id) — the number of unique obligors in each organizational segment.
 </v>
       </c>
       <c r="C70" t="str">
         <v>Counterparty ID</v>
       </c>
       <c r="D70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">Direct lookup of counterparty_id from facility_master for each active facility. Uses current records only (SCD2 filtered).
 </v>
       </c>
       <c r="E70" t="str">
@@ -6856,7 +6934,7 @@
         <v>Raw</v>
       </c>
       <c r="J70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">Direct lookup of counterparty_id from facility_master for each active facility. Uses current records only (SCD2 filtered).
 </v>
       </c>
       <c r="K70" t="str">
@@ -6869,7 +6947,7 @@
         <v>Raw</v>
       </c>
       <c r="N70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">Identity — returns counterparty_id for each current counterparty.
 </v>
       </c>
       <c r="O70" t="str">
@@ -6882,7 +6960,7 @@
         <v>Agg</v>
       </c>
       <c r="R70" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L3 desk segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L3 desk segment — number of unique obligors in each desk.
 </v>
       </c>
       <c r="S70" t="str">
@@ -6895,7 +6973,7 @@
         <v>Agg</v>
       </c>
       <c r="V70" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L2 portfolio segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L2 portfolio segment — number of unique obligors in each portfolio.
 </v>
       </c>
       <c r="W70" t="str">
@@ -6908,7 +6986,7 @@
         <v>Agg</v>
       </c>
       <c r="Z70" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L1 business segment segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L1 business segment — number of unique obligors in each business segment.
 </v>
       </c>
       <c r="AA70" t="str">
@@ -6923,14 +7001,14 @@
         <v>REF-005</v>
       </c>
       <c r="B71" t="str" xml:space="preserve">
-        <v xml:space="preserve">Descriptive name of the counterparty as documented in the credit agreement. Used for reporting clarity and operational reference.
+        <v xml:space="preserve">Legal name of the counterparty as documented in the credit agreement. At facility level, returns the counterparty_id (numeric proxy for the name since metric values are numeric). At counterparty level, identity lookup. At upper levels, COUNT(DISTINCT counterparty_id) — number of unique named obligors per organizational segment. Used for reporting clarity and operational reference across all regulatory submissions.
 </v>
       </c>
       <c r="C71" t="str">
         <v>Counterparty Name</v>
       </c>
       <c r="D71" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read legal_name from counterparty for each facility's counterparty.
+        <v xml:space="preserve">Lookup counterparty_id from facility_master for each active facility. The numeric counterparty_id serves as proxy for the legal name (string values resolved via counterparty dimension join at display time). Uses current records only.
 </v>
       </c>
       <c r="E71" t="str">
@@ -6949,7 +7027,7 @@
         <v>Raw</v>
       </c>
       <c r="J71" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read legal_name from counterparty for each facility's counterparty.
+        <v xml:space="preserve">Lookup counterparty_id from facility_master for each active facility. The numeric counterparty_id serves as proxy for the legal name (string values resolved via counterparty dimension join at display time). Uses current records only.
 </v>
       </c>
       <c r="K71" t="str">
@@ -6959,10 +7037,10 @@
         <v>Y</v>
       </c>
       <c r="M71" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="N71" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with counterparty name per counterparty.
+        <v xml:space="preserve">Identity — returns counterparty_id for each current counterparty. Legal name resolved via counterparty dimension join at display time.
 </v>
       </c>
       <c r="O71" t="str">
@@ -6975,7 +7053,7 @@
         <v>Agg</v>
       </c>
       <c r="R71" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with counterparty name per L3 desk segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L3 desk segment — number of unique named obligors in each desk.
 </v>
       </c>
       <c r="S71" t="str">
@@ -6988,7 +7066,7 @@
         <v>Agg</v>
       </c>
       <c r="V71" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with counterparty name per L2 portfolio segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L2 portfolio segment — number of unique named obligors in each portfolio.
 </v>
       </c>
       <c r="W71" t="str">
@@ -7001,7 +7079,7 @@
         <v>Agg</v>
       </c>
       <c r="Z71" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with counterparty name per L1 business segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L1 business segment — number of unique named obligors in each business segment.
 </v>
       </c>
       <c r="AA71" t="str">
@@ -7016,14 +7094,14 @@
         <v>REF-006</v>
       </c>
       <c r="B72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Country of risk or booking location. Supports geographic concentration and sovereign risk analysis.
+        <v xml:space="preserve">Country of risk derived from the counterparty's domicile. At facility level, returns a numeric country identifier (via counterparty → country_dim join path). At counterparty level, identity lookup. At desk/portfolio/segment levels, COUNT(DISTINCT country_code) — geographic diversification indicator showing the number of unique countries represented. Supports FFIEC 009 Country Exposure Report and Basel III geographic concentration analysis.
 </v>
       </c>
       <c r="C72" t="str">
         <v>Country</v>
       </c>
       <c r="D72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of country_name from country_dim.
+        <v xml:space="preserve">Lookup country for each facility via counterparty → country_dim join path. Returns counterparty_id as numeric proxy (country_name resolved at display time via dimension join). Uses current records only.
 </v>
       </c>
       <c r="E72" t="str">
@@ -7042,7 +7120,7 @@
         <v>Raw</v>
       </c>
       <c r="J72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of country_name from country_dim.
+        <v xml:space="preserve">Lookup country for each facility via counterparty → country_dim join path. Returns counterparty_id as numeric proxy (country_name resolved at display time via dimension join). Uses current records only.
 </v>
       </c>
       <c r="K72" t="str">
@@ -7055,7 +7133,7 @@
         <v>Raw</v>
       </c>
       <c r="N72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read country_name per counterparty.
+        <v xml:space="preserve">Lookup country for each counterparty via country_code → country_dim join. Returns counterparty_id as numeric proxy.
 </v>
       </c>
       <c r="O72" t="str">
@@ -7068,7 +7146,7 @@
         <v>Agg</v>
       </c>
       <c r="R72" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level country_name per L3 desk segment.
+        <v xml:space="preserve">COUNT(DISTINCT country_code) per L3 desk segment — number of unique countries represented, a geographic diversification indicator.
 </v>
       </c>
       <c r="S72" t="str">
@@ -7081,7 +7159,7 @@
         <v>Agg</v>
       </c>
       <c r="V72" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level country_name per L2 portfolio segment.
+        <v xml:space="preserve">COUNT(DISTINCT country_code) per L2 portfolio segment — number of unique countries represented in each portfolio.
 </v>
       </c>
       <c r="W72" t="str">
@@ -7094,7 +7172,7 @@
         <v>Agg</v>
       </c>
       <c r="Z72" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level country_name per L1 business segment segment.
+        <v xml:space="preserve">COUNT(DISTINCT country_code) per L1 business segment — geographic diversification at the highest organizational level.
 </v>
       </c>
       <c r="AA72" t="str">
@@ -7109,14 +7187,14 @@
         <v>REF-007</v>
       </c>
       <c r="B73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Unique identifier linking facility to governing credit agreement documentation.
+        <v xml:space="preserve">Unique identifier linking each facility to its governing credit agreement documentation. Used for contract tracking, facility-to-agreement linkage, and regulatory reporting. At counterparty level, returns count of distinct credit agreements per borrower.
 </v>
       </c>
       <c r="C73" t="str">
         <v>Credit Agreement ID</v>
       </c>
       <c r="D73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of credit_agreement_id from credit_agreement_master.
+        <v xml:space="preserve">Direct lookup of credit_agreement_id for each active facility via facility_master joined to credit_agreement_master.
 </v>
       </c>
       <c r="E73" t="str">
@@ -7135,7 +7213,7 @@
         <v>Raw</v>
       </c>
       <c r="J73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of credit_agreement_id from credit_agreement_master.
+        <v xml:space="preserve">Direct lookup of credit_agreement_id for each active facility via facility_master joined to credit_agreement_master.
 </v>
       </c>
       <c r="K73" t="str">
@@ -7145,10 +7223,10 @@
         <v>Y</v>
       </c>
       <c r="M73" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="N73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read credit_agreement_id per counterparty.
+        <v xml:space="preserve">Count of distinct credit agreements per counterparty. Provides visibility into borrower complexity and multi-agreement relationships.
 </v>
       </c>
       <c r="O73" t="str">
@@ -7161,7 +7239,7 @@
         <v>Agg</v>
       </c>
       <c r="R73" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level credit_agreement_id per L3 desk segment.
+        <v xml:space="preserve">Count of distinct credit agreements per L3 desk segment via enterprise_business_taxonomy.
 </v>
       </c>
       <c r="S73" t="str">
@@ -7174,7 +7252,7 @@
         <v>Agg</v>
       </c>
       <c r="V73" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level credit_agreement_id per L2 portfolio segment.
+        <v xml:space="preserve">Count of distinct credit agreements per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
 </v>
       </c>
       <c r="W73" t="str">
@@ -7187,7 +7265,7 @@
         <v>Agg</v>
       </c>
       <c r="Z73" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level credit_agreement_id per L1 business segment segment.
+        <v xml:space="preserve">Count of distinct credit agreements per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
 </v>
       </c>
       <c r="AA73" t="str">
@@ -7295,7 +7373,7 @@
         <v>REF-009</v>
       </c>
       <c r="B75" t="str" xml:space="preserve">
-        <v xml:space="preserve">Date on which loan or contract became legally effective.
+        <v xml:space="preserve">Date on which loan or contract became legally effective. Sourced directly from facility_master. At aggregate levels, returns the earliest origination date (MIN) across constituent facilities — indicating the oldest vintage in the book. Key contract lifecycle tracking attribute for vintage analysis and portfolio seasoning assessment.
 </v>
       </c>
       <c r="C75" t="str">
@@ -7303,6 +7381,7 @@
       </c>
       <c r="D75" t="str" xml:space="preserve">
         <v xml:space="preserve">Direct lookup of origination_date from facility_master.
+Ingredients: origination_date (L2 facility_master — raw field)
 </v>
       </c>
       <c r="E75" t="str">
@@ -7322,6 +7401,7 @@
       </c>
       <c r="J75" t="str" xml:space="preserve">
         <v xml:space="preserve">Direct lookup of origination_date from facility_master.
+Ingredients: origination_date (L2 facility_master — raw field)
 </v>
       </c>
       <c r="K75" t="str">
@@ -7334,7 +7414,10 @@
         <v>Agg</v>
       </c>
       <c r="N75" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level origination_date) per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD origination_date from l2.facility_master for all active facilities
+  2. COMPUTE MIN(origination_date) — earliest contract vintage
+Indicates the oldest banking relationship tenure for this counterparty.
 </v>
       </c>
       <c r="O75" t="str">
@@ -7347,7 +7430,10 @@
         <v>Agg</v>
       </c>
       <c r="R75" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level origination_date per L3 desk segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOAD origination_date from l2.facility_master
+  2. JOIN l1.enterprise_business_taxonomy on lob_segment_id
+  3. COMPUTE MIN(origination_date) — earliest vintage in desk book
 </v>
       </c>
       <c r="S75" t="str">
@@ -7360,7 +7446,9 @@
         <v>Agg</v>
       </c>
       <c r="V75" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level origination_date per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. COMPUTE MIN(origination_date) — earliest vintage in portfolio
 </v>
       </c>
       <c r="W75" t="str">
@@ -7373,7 +7461,9 @@
         <v>Agg</v>
       </c>
       <c r="Z75" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level origination_date per L1 business segment segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. COMPUTE MIN(origination_date) — earliest vintage in business segment
 </v>
       </c>
       <c r="AA75" t="str">
@@ -7427,7 +7517,7 @@
         <v>Raw</v>
       </c>
       <c r="N76" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read facility_id per counterparty.
+        <v xml:space="preserve">Representative facility_id per counterparty (MIN).
 </v>
       </c>
       <c r="O76" t="str">
@@ -7437,10 +7527,10 @@
         <v>Y</v>
       </c>
       <c r="Q76" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="R76" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_id per L3 desk segment.
+        <v xml:space="preserve">Representative facility_id per L3 desk segment (MIN).
 </v>
       </c>
       <c r="S76" t="str">
@@ -7450,10 +7540,10 @@
         <v>Y</v>
       </c>
       <c r="U76" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="V76" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_id per L2 portfolio segment.
+        <v xml:space="preserve">Representative facility_id per L2 portfolio segment (MIN).
 </v>
       </c>
       <c r="W76" t="str">
@@ -7463,10 +7553,10 @@
         <v>Y</v>
       </c>
       <c r="Y76" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="Z76" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_id per L1 business segment segment.
+        <v xml:space="preserve">Representative facility_id per L1 business segment (MIN).
 </v>
       </c>
       <c r="AA76" t="str">
@@ -7520,7 +7610,7 @@
         <v>Raw</v>
       </c>
       <c r="N77" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read facility_name per counterparty.
+        <v xml:space="preserve">Representative facility_name per counterparty (MIN alphabetical).
 </v>
       </c>
       <c r="O77" t="str">
@@ -7530,10 +7620,10 @@
         <v>Y</v>
       </c>
       <c r="Q77" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="R77" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_name per L3 desk segment.
+        <v xml:space="preserve">Representative facility_name per L3 desk segment (MIN alphabetical).
 </v>
       </c>
       <c r="S77" t="str">
@@ -7543,10 +7633,10 @@
         <v>Y</v>
       </c>
       <c r="U77" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="V77" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_name per L2 portfolio segment.
+        <v xml:space="preserve">Representative facility_name per L2 portfolio segment (MIN alphabetical).
 </v>
       </c>
       <c r="W77" t="str">
@@ -7556,10 +7646,10 @@
         <v>Y</v>
       </c>
       <c r="Y77" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="Z77" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_name per L1 business segment segment.
+        <v xml:space="preserve">Representative facility_name per L1 business segment (MIN alphabetical).
 </v>
       </c>
       <c r="AA77" t="str">
@@ -7574,14 +7664,14 @@
         <v>REF-012</v>
       </c>
       <c r="B78" t="str" xml:space="preserve">
-        <v xml:space="preserve">Type of credit facility (e.g., Term Loan, Revolver, Letter of Credit). Enables product-level segmentation, risk concentration analysis, and performance benchmarking.
+        <v xml:space="preserve">Type of credit facility (e.g., Term Loan, Revolver, Letter of Credit). Enables product-level segmentation, risk concentration analysis, and performance benchmarking. At facility level returns the facility type string; at aggregate levels returns the count of distinct active facilities in the segment for distribution analysis.
 </v>
       </c>
       <c r="C78" t="str">
         <v>Facility Type</v>
       </c>
       <c r="D78" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read facility_type from facility_exposure_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Direct lookup of facility_type from facility_master.
 </v>
       </c>
       <c r="E78" t="str">
@@ -7600,7 +7690,7 @@
         <v>Raw</v>
       </c>
       <c r="J78" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read facility_type from facility_exposure_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Direct lookup of facility_type from facility_master.
 </v>
       </c>
       <c r="K78" t="str">
@@ -7610,10 +7700,10 @@
         <v>Y</v>
       </c>
       <c r="M78" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="N78" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level facility_type) per counterparty.
+        <v xml:space="preserve">Not in primary specification at counterparty level. Supplementary: representative facility_type per counterparty (MIN).
 </v>
       </c>
       <c r="O78" t="str">
@@ -7626,7 +7716,7 @@
         <v>Agg</v>
       </c>
       <c r="R78" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_type per L3 desk segment.
+        <v xml:space="preserve">Count distinct active facilities per L3 desk segment. Provides facility distribution for product mix analysis.
 </v>
       </c>
       <c r="S78" t="str">
@@ -7639,7 +7729,7 @@
         <v>Agg</v>
       </c>
       <c r="V78" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_type per L2 portfolio segment.
+        <v xml:space="preserve">Count distinct active facilities per L2 portfolio segment. Provides facility distribution for product mix analysis.
 </v>
       </c>
       <c r="W78" t="str">
@@ -7652,7 +7742,7 @@
         <v>Agg</v>
       </c>
       <c r="Z78" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_type per L1 business segment segment.
+        <v xml:space="preserve">Count distinct active facilities per L1 business segment. Provides facility distribution for product mix analysis.
 </v>
       </c>
       <c r="AA78" t="str">
@@ -9620,14 +9710,14 @@
         <v>RSK-001</v>
       </c>
       <c r="B100" t="str" xml:space="preserve">
-        <v xml:space="preserve">Most recent internal credit rating assigned at reporting date. Used for segmentation and exposure-weighted risk aggregation.
+        <v xml:space="preserve">Risk rating tier derived from counterparty probability of default (PD). Each counterparty's pd_annual is matched against the risk_rating_tier_dim reference table (pd_min_pct / pd_max_pct boundaries) to assign a tier classification. At facility level, the tier is inherited from the owning counterparty. At aggregate levels, MAX (worst-case) tier ordinal is reported.
 </v>
       </c>
       <c r="C100" t="str">
         <v>Risk Rating Tier</v>
       </c>
       <c r="D100" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility.
+        <v xml:space="preserve">For each facility, inherit the risk rating tier from the owning counterparty. Join facility_master to counterparty, then range-match counterparty pd_annual against risk_rating_tier_dim to derive the tier ordinal (display_order).
 </v>
       </c>
       <c r="E100" t="str">
@@ -9643,10 +9733,10 @@
         <v>Y</v>
       </c>
       <c r="I100" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="J100" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility.
+        <v xml:space="preserve">For each facility, inherit the risk rating tier from the owning counterparty. Join facility_master to counterparty, then range-match counterparty pd_annual against risk_rating_tier_dim to derive the tier ordinal (display_order).
 </v>
       </c>
       <c r="K100" t="str">
@@ -9656,10 +9746,10 @@
         <v>Y</v>
       </c>
       <c r="M100" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N100" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating per counterparty.
+        <v xml:space="preserve">For each counterparty, look up pd_annual and range-match against risk_rating_tier_dim where pd_annual &gt;= pd_min_pct AND pd_annual &lt; pd_max_pct. Returns the tier ordinal (display_order). Counterparties with NULL PD receive tier 0 (unrated).
 </v>
       </c>
       <c r="O100" t="str">
@@ -9672,7 +9762,7 @@
         <v>Agg</v>
       </c>
       <c r="R100" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating per L3 desk segment.
+        <v xml:space="preserve">Worst-case (MAX) risk rating tier ordinal across all counterparties in the L3 desk segment. Higher ordinal = riskier tier. Full tier distribution available via counterparty-level drill-down.
 </v>
       </c>
       <c r="S100" t="str">
@@ -9685,7 +9775,7 @@
         <v>Agg</v>
       </c>
       <c r="V100" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating per L2 portfolio segment.
+        <v xml:space="preserve">Worst-case (MAX) risk rating tier ordinal per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
 </v>
       </c>
       <c r="W100" t="str">
@@ -9698,7 +9788,7 @@
         <v>Agg</v>
       </c>
       <c r="Z100" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating per L1 business segment.
+        <v xml:space="preserve">Worst-case (MAX) risk rating tier ordinal per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
 </v>
       </c>
       <c r="AA100" t="str">

--- a/data/metrics_dimensions_filled.xlsx
+++ b/data/metrics_dimensions_filled.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB108"/>
+  <dimension ref="A1:AB111"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -795,14 +795,14 @@
         <v>AMD-004</v>
       </c>
       <c r="B6" t="str" xml:space="preserve">
-        <v xml:space="preserve">Indicator that facility agreement has undergone amendment. Portfolio KPI (% Facilities with Amendments) signals restructuring activity.
+        <v xml:space="preserve">Percentage of active facilities that have undergone at least one contractual amendment. At facility level, returns a binary flag (1 = has amendment, 0 = no amendment). At counterparty and aggregate levels, computes the count-ratio: COUNT(amended facilities) / COUNT(total facilities) x 100. High amendment rates may signal portfolio stress, widespread restructuring activity, or covenant relief campaigns.
 </v>
       </c>
       <c r="C6" t="str">
-        <v>Amendment ID</v>
+        <v>Amendment Rate</v>
       </c>
       <c r="D6" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read amendment_event_id from amendment_event for each facility as-of reporting date.
+        <v xml:space="preserve">For each active facility, check whether any amendment_event records exist via LEFT JOIN. Returns 1 (has amendment) or 0 (no amendment). A facility is considered amended if it has at least one record in the amendment_event table regardless of amendment type or status.
 </v>
       </c>
       <c r="E6" t="str">
@@ -818,66 +818,66 @@
         <v>Y</v>
       </c>
       <c r="I6" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="J6" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read amendment_event_id from amendment_event for each facility as-of reporting date.
+        <v xml:space="preserve">For each active facility, check whether any amendment_event records exist via LEFT JOIN. Returns 1 (has amendment) or 0 (no amendment). A facility is considered amended if it has at least one record in the amendment_event table regardless of amendment type or status.
 </v>
       </c>
       <c r="K6" t="str">
-        <v>Amendment ID (facility)</v>
+        <v>Amendment Rate (facility)</v>
       </c>
       <c r="L6" t="str">
         <v>Y</v>
       </c>
       <c r="M6" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N6" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level amendment_event_id) per counterparty.
+        <v xml:space="preserve">Count-ratio: number of amended facilities divided by total active facilities for each counterparty, expressed as a percentage. Uses a DISTINCT subquery on amendment_event to avoid double-counting facilities with multiple amendments.
 </v>
       </c>
       <c r="O6" t="str">
-        <v>Amendment ID (counterparty)</v>
+        <v>Amendment Rate (counterparty)</v>
       </c>
       <c r="P6" t="str">
         <v>Y</v>
       </c>
       <c r="Q6" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R6" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level amendment_event_id per L3 desk segment.
+        <v xml:space="preserve">Count-ratio: percentage of amended facilities per L3 desk segment. Re-counts at segment level (never averages pre-computed ratios) to avoid Simpson's paradox. Uses EBT direct join for L3.
 </v>
       </c>
       <c r="S6" t="str">
-        <v>Amendment ID (desk)</v>
+        <v>Amendment Rate (desk)</v>
       </c>
       <c r="T6" t="str">
         <v>Y</v>
       </c>
       <c r="U6" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V6" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level amendment_event_id per L2 portfolio segment.
+        <v xml:space="preserve">Count-ratio: percentage of amended facilities per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id. Re-counts at portfolio level for mathematical consistency.
 </v>
       </c>
       <c r="W6" t="str">
-        <v>Amendment ID (portfolio)</v>
+        <v>Amendment Rate (portfolio)</v>
       </c>
       <c r="X6" t="str">
         <v>Y</v>
       </c>
       <c r="Y6" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z6" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level amendment_event_id per L1 business segment segment.
+        <v xml:space="preserve">Count-ratio: percentage of amended facilities per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1. Re-counts at segment level for mathematical consistency across the rollup hierarchy.
 </v>
       </c>
       <c r="AA6" t="str">
-        <v>Amendment ID (business_segment)</v>
+        <v>Amendment Rate (business_segment)</v>
       </c>
       <c r="AB6" t="str">
         <v/>
@@ -1539,14 +1539,14 @@
         <v>EXP-005</v>
       </c>
       <c r="B14" t="str" xml:space="preserve">
-        <v xml:space="preserve">The portion of total funding-related expense attributed to a specific exposure or portfolio. At facility level, calculated as SUM across all positions of (funded_amount * interest_rate), adjusted for bank share. At counterparty level, further adjusted by counterparty participation_pct. At desk/portfolio/segment levels, aggregated as SUM.
+        <v xml:space="preserve">The portion of total funding-related expense attributed to a specific exposure or portfolio. At facility level, calculated as SUM across all positions of (funded_amount * interest_rate), converted to USD via FX rate and adjusted for bank share. At counterparty level, further adjusted by counterparty participation_pct. At desk/portfolio/segment levels, aggregated as SUM via EBT hierarchy.
 </v>
       </c>
       <c r="C14" t="str">
         <v>Cost of Funds ($)</v>
       </c>
       <c r="D14" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each position under the facility: funded_amount * interest_rate = Position Cost of Funds. Adjusted by bank_share: SUM(funded_amount * interest_rate) * bank_share_pct / 100. Joins position_detail → position (for facility_id) → facility_master.
+        <v xml:space="preserve">For each position under the facility, compute funded_amount x interest_rate, convert to USD using the FX spot rate (defaults to 1.0 for USD positions). Sum across all positions, then multiply by the bank's share percentage. Result = annual cost of funds for this facility in USD.
 </v>
       </c>
       <c r="E14" t="str">
@@ -1565,7 +1565,7 @@
         <v>Calc</v>
       </c>
       <c r="J14" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each position under the facility: funded_amount * interest_rate = Position Cost of Funds. Adjusted by bank_share: SUM(funded_amount * interest_rate) * bank_share_pct / 100. Joins position_detail → position (for facility_id) → facility_master.
+        <v xml:space="preserve">For each position under the facility, compute funded_amount x interest_rate, convert to USD using the FX spot rate (defaults to 1.0 for USD positions). Sum across all positions, then multiply by the bank's share percentage. Result = annual cost of funds for this facility in USD.
 </v>
       </c>
       <c r="K14" t="str">
@@ -1578,7 +1578,7 @@
         <v>Agg</v>
       </c>
       <c r="N14" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each counterparty: SUM of facility-level cost of funds weighted by counterparty participation_pct from facility_counterparty_participation.
+        <v xml:space="preserve">Sum each facility's cost of funds (USD, bank-share-adjusted), then weight by the counterparty's participation percentage. Aggregates across all facilities where the counterparty has a current participation record.
 </v>
       </c>
       <c r="O14" t="str">
@@ -1591,7 +1591,7 @@
         <v>Agg</v>
       </c>
       <c r="R14" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level cost of funds (bank-share-adjusted) per L3 desk segment.
+        <v xml:space="preserve">Sum of facility-level cost of funds (USD, bank-share-adjusted) for all facilities assigned to each L3 desk segment in the organizational hierarchy.
 </v>
       </c>
       <c r="S14" t="str">
@@ -1604,7 +1604,7 @@
         <v>Agg</v>
       </c>
       <c r="V14" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level cost of funds (bank-share-adjusted) per L2 portfolio segment.
+        <v xml:space="preserve">Sum of facility-level cost of funds (USD, bank-share-adjusted) for all facilities within each L2 portfolio segment, traversing the EBT hierarchy from desk (L3) to portfolio (L2) via parent_segment_id.
 </v>
       </c>
       <c r="W14" t="str">
@@ -1617,7 +1617,7 @@
         <v>Agg</v>
       </c>
       <c r="Z14" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level cost of funds (bank-share-adjusted) per L1 business segment.
+        <v xml:space="preserve">Sum of facility-level cost of funds (USD, bank-share-adjusted) for all facilities within each L1 business segment, traversing the full EBT hierarchy from desk (L3) through portfolio (L2) to segment (L1).
 </v>
       </c>
       <c r="AA14" t="str">
@@ -1632,14 +1632,14 @@
         <v>EXP-006</v>
       </c>
       <c r="B15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure allocated to specific counterparty representing their share of the facility which the client can draw on. Concentration KPI measuring obligor dependency risk.
+        <v xml:space="preserve">Counterparty participation share in a facility — the percentage of a syndicated or participated facility allocated to a specific counterparty. At facility level, direct lookup from facility_counterparty_participation. At counterparty level, exposure-weighted average participation across all facilities. At desk/portfolio/segment, exposure-weighted average via EBT hierarchy. Key concentration KPI for Large Exposures Framework (LEX) and Single Counterparty Credit Limit (SCCL) compliance.
 </v>
       </c>
       <c r="C15" t="str">
         <v>Counterparty Share or Allocation (%)</v>
       </c>
       <c r="D15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of allocation_pct from facility_counterparty_participation.
+        <v xml:space="preserve">Direct lookup of participation_pct from facility_counterparty_participation for the primary counterparty on each facility. Uses current records only.
 </v>
       </c>
       <c r="E15" t="str">
@@ -1658,7 +1658,7 @@
         <v>Raw</v>
       </c>
       <c r="J15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of allocation_pct from facility_counterparty_participation.
+        <v xml:space="preserve">Direct lookup of participation_pct from facility_counterparty_participation for the primary counterparty on each facility. Uses current records only.
 </v>
       </c>
       <c r="K15" t="str">
@@ -1668,10 +1668,10 @@
         <v>Y</v>
       </c>
       <c r="M15" t="str">
-        <v>Raw</v>
+        <v>Avg</v>
       </c>
       <c r="N15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read allocation_pct per counterparty.
+        <v xml:space="preserve">Exposure-weighted average participation across all facilities for each counterparty. Weight = drawn_amount from facility_exposure_snapshot. Falls back to simple average if no exposure data available.
 </v>
       </c>
       <c r="O15" t="str">
@@ -1681,10 +1681,10 @@
         <v>Y</v>
       </c>
       <c r="Q15" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="R15" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level allocation_pct per L3 desk segment.
+        <v xml:space="preserve">Exposure-weighted average participation across all facilities per L3 desk segment via enterprise_business_taxonomy.
 </v>
       </c>
       <c r="S15" t="str">
@@ -1694,10 +1694,10 @@
         <v>Y</v>
       </c>
       <c r="U15" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="V15" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level allocation_pct per L2 portfolio segment.
+        <v xml:space="preserve">Exposure-weighted average participation across all facilities per L2 portfolio segment via enterprise_business_taxonomy hierarchy traversal.
 </v>
       </c>
       <c r="W15" t="str">
@@ -1707,10 +1707,10 @@
         <v>Y</v>
       </c>
       <c r="Y15" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="Z15" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level allocation_pct per L1 business segment segment.
+        <v xml:space="preserve">Exposure-weighted average participation across all facilities per L1 business segment via enterprise_business_taxonomy hierarchy traversal.
 </v>
       </c>
       <c r="AA15" t="str">
@@ -1725,14 +1725,14 @@
         <v>EXP-007</v>
       </c>
       <c r="B16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Flag identifying exposures requiring heightened monitoring due to elevated credit risk. Governance control used for enhanced monitoring, reserve consideration, and management reporting.
+        <v xml:space="preserve">Count of active Criticized risk flags across facilities. Early warning indicator of problem assets requiring heightened monitoring, reserve consideration, and management reporting. Sources from the risk_flag table filtering on flag_code = 'CRITICIZED' with uncleared status.
 </v>
       </c>
       <c r="C16" t="str">
         <v>Criticized Portfolios</v>
       </c>
       <c r="D16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if criticized rating (internal_risk_rating &gt;= 6), 0 otherwise.
+        <v xml:space="preserve">For each facility, count active risk flags where flag_code = 'CRITICIZED' and the flag has not been cleared (cleared_ts IS NULL).
 </v>
       </c>
       <c r="E16" t="str">
@@ -1748,10 +1748,10 @@
         <v>Y</v>
       </c>
       <c r="I16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="J16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if criticized rating (internal_risk_rating &gt;= 6), 0 otherwise.
+        <v xml:space="preserve">For each facility, count active risk flags where flag_code = 'CRITICIZED' and the flag has not been cleared (cleared_ts IS NULL).
 </v>
       </c>
       <c r="K16" t="str">
@@ -1761,10 +1761,10 @@
         <v>Y</v>
       </c>
       <c r="M16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="N16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per counterparty.
+        <v xml:space="preserve">For each counterparty, sum facility-level criticized flag counts across all facilities belonging to that counterparty.
 </v>
       </c>
       <c r="O16" t="str">
@@ -1774,10 +1774,10 @@
         <v>Y</v>
       </c>
       <c r="Q16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="R16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per L3 desk.
+        <v xml:space="preserve">Sum of criticized flag counts per L3 desk segment. Joins facility_master to enterprise_business_taxonomy via lob_segment_id.
 </v>
       </c>
       <c r="S16" t="str">
@@ -1787,10 +1787,10 @@
         <v>Y</v>
       </c>
       <c r="U16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="V16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per L2 portfolio.
+        <v xml:space="preserve">Sum of criticized flag counts per L2 portfolio segment. Traverses enterprise_business_taxonomy hierarchy from L3 to L2 via parent_segment_id.
 </v>
       </c>
       <c r="W16" t="str">
@@ -1800,10 +1800,10 @@
         <v>Y</v>
       </c>
       <c r="Y16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="Z16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per L1 business segment.
+        <v xml:space="preserve">Sum of criticized flag counts per L1 business segment. Full hierarchy traversal L3 → L2 → L1 via enterprise_business_taxonomy.
 </v>
       </c>
       <c r="AA16" t="str">
@@ -1818,14 +1818,14 @@
         <v>EXP-008</v>
       </c>
       <c r="B17" t="str" xml:space="preserve">
-        <v xml:space="preserve">Total exposure amount allocated across multiple legal entities. Supports intra-group concentration transparency.
+        <v xml:space="preserve">Total committed exposure amount (bank share) allocated across multiple legal entities for facilities flagged as cross-entity. Quantifies inter-entity concentration risk and supports intra-group transparency for GSIB reporting. Sources from counterparty_derived (L3) for the cross-entity flag and facility_exposure_snapshot (L2) for committed amounts.
 </v>
       </c>
       <c r="C17" t="str">
         <v>Cross Entity Exposure Amount</v>
       </c>
       <c r="D17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(total_cross_entity_exposure_usd) per facility from counterparty_exposure_summary. Weighted by bank share percentage.
+        <v xml:space="preserve">For each facility flagged as cross-entity, committed exposure amount weighted by the bank's participation share (bank_share_pct). Facilities without cross-entity flag are excluded.
 </v>
       </c>
       <c r="E17" t="str">
@@ -1844,7 +1844,7 @@
         <v>Agg</v>
       </c>
       <c r="J17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(total_cross_entity_exposure_usd) per facility from counterparty_exposure_summary. Weighted by bank share percentage.
+        <v xml:space="preserve">For each facility flagged as cross-entity, committed exposure amount weighted by the bank's participation share (bank_share_pct). Facilities without cross-entity flag are excluded.
 </v>
       </c>
       <c r="K17" t="str">
@@ -1857,7 +1857,7 @@
         <v>Agg</v>
       </c>
       <c r="N17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per counterparty.
+        <v xml:space="preserve">For each counterparty, sum of bank-share-weighted committed amounts across all facilities flagged as cross-entity.
 </v>
       </c>
       <c r="O17" t="str">
@@ -1870,7 +1870,7 @@
         <v>Agg</v>
       </c>
       <c r="R17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per L3 desk segment.
+        <v xml:space="preserve">Sum of cross-entity committed exposure per L3 desk segment via enterprise_business_taxonomy.
 </v>
       </c>
       <c r="S17" t="str">
@@ -1883,7 +1883,7 @@
         <v>Agg</v>
       </c>
       <c r="V17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per L2 portfolio segment.
+        <v xml:space="preserve">Sum of cross-entity committed exposure per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
 </v>
       </c>
       <c r="W17" t="str">
@@ -1896,7 +1896,7 @@
         <v>Agg</v>
       </c>
       <c r="Z17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per L1 business segment segment.
+        <v xml:space="preserve">Sum of cross-entity committed exposure per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
 </v>
       </c>
       <c r="AA17" t="str">
@@ -1911,14 +1911,14 @@
         <v>EXP-009</v>
       </c>
       <c r="B18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Number of days outstanding payments is past due as grouped into 3 "buckets", 0-30 Days, 31-60 Days, 61-90+ Days. Used for staging classification and early credit deterioration monitoring.
+        <v xml:space="preserve">Maximum days payment overdue per facility, calculated from raw payment records in the payment_ledger table. For each facility, identifies payments where applied amount &lt; amount due, computes days overdue as reporting date minus payment_due_date, takes the MAX, then classifies into buckets: 1 = 0-30 days, 2 = 31-60 days, 3 = 61-90+ days. At aggregate levels, reports the worst (MAX) bucket across constituents.
 </v>
       </c>
       <c r="C18" t="str">
         <v>Days Payment Overdue Bucket</v>
       </c>
       <c r="D18" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Facility_ID lookup the Payments records in the Payment Lockbox table, For each payment record where [Payment_Due_Date] &gt; Today() IF ([Pmt_Applied] &lt;[Pmt_Due])&gt;=1, THEN Today() - [Payment_due_date] ==[Days Overdue] SELECT MAX ([Days Overdue] then lookup in Payments Overdue bucket)
+        <v xml:space="preserve">For each facility, lookup payment records in payment_ledger where payment_due_date &lt; reporting date and payment_applied_amt &lt; payment_amount_due (underpaid). Calculate days overdue = reporting date minus payment_due_date. Take MAX days overdue, then classify into overdue bucket: 1 (0-30), 2 (31-60), 3 (61-90+).
 </v>
       </c>
       <c r="E18" t="str">
@@ -1937,7 +1937,7 @@
         <v>Calc</v>
       </c>
       <c r="J18" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Facility_ID lookup the Payments records in the Payment Lockbox table, For each payment record where [Payment_Due_Date] &gt; Today() IF ([Pmt_Applied] &lt;[Pmt_Due])&gt;=1, THEN Today() - [Payment_due_date] ==[Days Overdue] SELECT MAX ([Days Overdue] then lookup in Payments Overdue bucket)
+        <v xml:space="preserve">For each facility, lookup payment records in payment_ledger where payment_due_date &lt; reporting date and payment_applied_amt &lt; payment_amount_due (underpaid). Calculate days overdue = reporting date minus payment_due_date. Take MAX days overdue, then classify into overdue bucket: 1 (0-30), 2 (31-60), 3 (61-90+).
 </v>
       </c>
       <c r="K18" t="str">
@@ -1950,7 +1950,7 @@
         <v>Agg</v>
       </c>
       <c r="N18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per counterparty.
+        <v xml:space="preserve">Worst-case (MAX) overdue bucket across all facilities per counterparty. Identifies the most severely overdue facility for each borrower.
 </v>
       </c>
       <c r="O18" t="str">
@@ -1963,7 +1963,7 @@
         <v>Agg</v>
       </c>
       <c r="R18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per L3 desk segment.
+        <v xml:space="preserve">Worst-case (MAX) overdue bucket per L3 desk segment. Shows the most severe delinquency in each organizational unit.
 </v>
       </c>
       <c r="S18" t="str">
@@ -1976,7 +1976,7 @@
         <v>Agg</v>
       </c>
       <c r="V18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per L2 portfolio segment.
+        <v xml:space="preserve">Worst-case (MAX) overdue bucket per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
 </v>
       </c>
       <c r="W18" t="str">
@@ -1989,7 +1989,7 @@
         <v>Agg</v>
       </c>
       <c r="Z18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per L1 business segment.
+        <v xml:space="preserve">Worst-case (MAX) overdue bucket per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
 </v>
       </c>
       <c r="AA18" t="str">
@@ -2509,14 +2509,25 @@
         <v>EXP-015</v>
       </c>
       <c r="B24" t="str" xml:space="preserve">
-        <v xml:space="preserve">Expected Loss divided by Exposure. Derived KPI measuring loss intensity relative to exposure size, enabling comparative risk ranking across facilities or counterparties.
+        <v xml:space="preserve">Expected Loss as a percentage of committed exposure. Computed from L2 atomic risk parameters: PD (probability of default) × LGD (loss given default). At aggregate levels, uses sum-ratio rollup: SUM(PD × LGD × Committed) / SUM(Committed) × 100 — the exposure-weighted average EL rate. This ensures mathematically consistent aggregation (never averages pre-computed rates). Key credit risk quantification metric for comparing loss intensity across facilities, counterparties, and business segments.
+Ingredient derivation:
+  - PD (pd_pct): L2 facility_risk_snapshot — probability of default (%)
+  - LGD (lgd_pct): L2 facility_risk_snapshot — loss given default (%)
+  - Committed Exposure (committed_amount): L2 facility_exposure_snapshot — raw
+  - EL Rate = PD × LGD (at facility level, committed cancels in ratio)
+  - Aggregate EL Rate = SUM(PD × LGD × Committed) / SUM(Committed) × 100
 </v>
       </c>
       <c r="C24" t="str">
         <v>Expected Loss Rate (%)</v>
       </c>
       <c r="D24" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of expected_loss_rate_pct per facility.
+        <v xml:space="preserve">For each facility:
+  1. LOAD pd_pct, lgd_pct from l2.facility_risk_snapshot
+  2. LOAD committed_amount from l2.facility_exposure_snapshot
+  3. COMPUTE EL Rate = SUM(PD/100 × LGD/100 × Committed) / SUM(Committed) × 100
+     At facility grain, committed cancels → EL Rate ≈ PD × LGD / 100
+Ingredients: pd_pct (L2), lgd_pct (L2), committed_amount (L2)
 </v>
       </c>
       <c r="E24" t="str">
@@ -2532,10 +2543,15 @@
         <v>Y</v>
       </c>
       <c r="I24" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="J24" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of expected_loss_rate_pct per facility.
+        <v xml:space="preserve">For each facility:
+  1. LOAD pd_pct, lgd_pct from l2.facility_risk_snapshot
+  2. LOAD committed_amount from l2.facility_exposure_snapshot
+  3. COMPUTE EL Rate = SUM(PD/100 × LGD/100 × Committed) / SUM(Committed) × 100
+     At facility grain, committed cancels → EL Rate ≈ PD × LGD / 100
+Ingredients: pd_pct (L2), lgd_pct (L2), committed_amount (L2)
 </v>
       </c>
       <c r="K24" t="str">
@@ -2545,10 +2561,15 @@
         <v>Y</v>
       </c>
       <c r="M24" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N24" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level expected_loss_rate_pct per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD pd_pct, lgd_pct for all facilities belonging to this counterparty
+  2. LOAD committed_amount for each facility
+  3. CONVERT to USD via l2.fx_rate spot rate
+  4. COMPUTE SUM(PD × LGD × Committed × FX) / SUM(Committed × FX) × 100
+Sum-ratio rollup with FX: exposure-weighted average EL rate in USD terms.
 </v>
       </c>
       <c r="O24" t="str">
@@ -2558,10 +2579,14 @@
         <v>Y</v>
       </c>
       <c r="Q24" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="R24" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level expected_loss_rate_pct per L3 desk segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOOKUP managed_segment_id from enterprise_business_taxonomy
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(PD × LGD × Committed × FX) / SUM(Committed × FX) × 100
+Sum-ratio rollup: exposure-weighted average EL rate per desk.
 </v>
       </c>
       <c r="S24" t="str">
@@ -2571,10 +2596,14 @@
         <v>Y</v>
       </c>
       <c r="U24" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V24" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level expected_loss_rate_pct per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(PD × LGD × Committed × FX) / SUM(Committed × FX) × 100
+Sum-ratio rollup: exposure-weighted average EL rate per portfolio.
 </v>
       </c>
       <c r="W24" t="str">
@@ -2584,10 +2613,14 @@
         <v>Y</v>
       </c>
       <c r="Y24" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z24" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level expected_loss_rate_pct per L1 business segment segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(PD × LGD × Committed × FX) / SUM(Committed × FX) × 100
+Sum-ratio rollup: exposure-weighted average EL rate per segment.
 </v>
       </c>
       <c r="AA24" t="str">
@@ -2602,14 +2635,25 @@
         <v>EXP-016</v>
       </c>
       <c r="B25" t="str" xml:space="preserve">
-        <v xml:space="preserve">PD × LGD × Exposure expressed in USD. Calculated forward-looking loss metric supporting provisioning, capital planning, and stress testing analytics.
+        <v xml:space="preserve">Expected Loss in dollar terms: PD × LGD × Committed Exposure × Bank Share. Computed from L2 atomic risk parameters and exposure data — NOT from stressed scenarios. This is the base (unstressed) expected credit loss, the foundation for provisioning, capital planning, and CECL/IFRS 9 reserve estimation.
+Ingredient derivation:
+  - PD (pd_pct): L2 facility_risk_snapshot — probability of default (%)
+  - LGD (lgd_pct): L2 facility_risk_snapshot — loss given default (%)
+  - Committed Exposure (committed_amount): L2 facility_exposure_snapshot — raw
+  - Bank Share (bank_share_pct): L2 facility_exposure_snapshot — participation %
+  - EL = (PD/100) × (LGD/100) × Committed × (Bank Share/100)
+Rollup uses direct-sum: SUM(facility EL) at each aggregate level. FX conversion applied at aggregate levels for multi-currency portfolios.
 </v>
       </c>
       <c r="C25" t="str">
         <v>Expected Loss ($)</v>
       </c>
       <c r="D25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(stressed_expected_loss) per facility from stress_test_result. Weighted by bank share percentage.
+        <v xml:space="preserve">For each facility:
+  1. LOAD pd_pct, lgd_pct from l2.facility_risk_snapshot
+  2. LOAD committed_amount, bank_share_pct from l2.facility_exposure_snapshot
+  3. COMPUTE EL = (PD/100) × (LGD/100) × Committed × (Bank Share/100)
+Ingredients: pd_pct (L2), lgd_pct (L2), committed_amount (L2), bank_share_pct (L2)
 </v>
       </c>
       <c r="E25" t="str">
@@ -2625,10 +2669,14 @@
         <v>Y</v>
       </c>
       <c r="I25" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="J25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(stressed_expected_loss) per facility from stress_test_result. Weighted by bank share percentage.
+        <v xml:space="preserve">For each facility:
+  1. LOAD pd_pct, lgd_pct from l2.facility_risk_snapshot
+  2. LOAD committed_amount, bank_share_pct from l2.facility_exposure_snapshot
+  3. COMPUTE EL = (PD/100) × (LGD/100) × Committed × (Bank Share/100)
+Ingredients: pd_pct (L2), lgd_pct (L2), committed_amount (L2), bank_share_pct (L2)
 </v>
       </c>
       <c r="K25" t="str">
@@ -2641,7 +2689,11 @@
         <v>Agg</v>
       </c>
       <c r="N25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD facility-level EL for all facilities of this counterparty
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(facility EL × FX rate) = Counterparty EL (USD)
+Direct-sum rollup with FX conversion.
 </v>
       </c>
       <c r="O25" t="str">
@@ -2654,7 +2706,11 @@
         <v>Agg</v>
       </c>
       <c r="R25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per L3 desk segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOOKUP managed_segment_id from enterprise_business_taxonomy
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(facility EL × FX rate) per desk
+Direct-sum rollup with FX conversion.
 </v>
       </c>
       <c r="S25" t="str">
@@ -2667,7 +2723,11 @@
         <v>Agg</v>
       </c>
       <c r="V25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(facility EL × FX rate) per portfolio
+Direct-sum rollup with FX conversion.
 </v>
       </c>
       <c r="W25" t="str">
@@ -2680,7 +2740,11 @@
         <v>Agg</v>
       </c>
       <c r="Z25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per L1 business segment segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(facility EL × FX rate) per business segment
+Direct-sum rollup with FX conversion.
 </v>
       </c>
       <c r="AA25" t="str">
@@ -5607,17 +5671,17 @@
     </row>
     <row r="57" xml:space="preserve">
       <c r="A57" t="str">
-        <v>PRC-001</v>
+        <v>EXP-049</v>
       </c>
       <c r="B57" t="str" xml:space="preserve">
-        <v xml:space="preserve">Total effective interest rate including base rate and spread. Calculated pricing KPI that provides insight into total yield generation and supports risk-adjusted return analysis.
+        <v xml:space="preserve">Identifies facilities and counterparties with cross-entity exposure — where a single facility participates across multiple counterparties. At facility level, returns 1 if the facility has participations from more than one distinct counterparty in facility_counterparty_participation, 0 otherwise. At counterparty level, returns 1 if any of the counterparty's facilities have cross-entity participations. Flags complexity and concentration risk from intercompany exposure structures.
 </v>
       </c>
       <c r="C57" t="str">
-        <v>All in Rate (%)</v>
+        <v>Cross Entity Exposure Flag</v>
       </c>
       <c r="D57" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read all_in_rate_pct from facility_pricing_snapshot for each facility.
+        <v xml:space="preserve">For each facility, count the number of distinct counterparties in facility_counterparty_participation (current records only). If COUNT(DISTINCT counterparty_id) &gt; 1, the facility has cross-entity exposure (flag = 1). Otherwise flag = 0.
 </v>
       </c>
       <c r="E57" t="str">
@@ -5633,40 +5697,40 @@
         <v>Y</v>
       </c>
       <c r="I57" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="J57" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read all_in_rate_pct from facility_pricing_snapshot for each facility.
+        <v xml:space="preserve">For each facility, count the number of distinct counterparties in facility_counterparty_participation (current records only). If COUNT(DISTINCT counterparty_id) &gt; 1, the facility has cross-entity exposure (flag = 1). Otherwise flag = 0.
 </v>
       </c>
       <c r="K57" t="str">
-        <v>All in Rate (%) (facility)</v>
+        <v>Cross Entity Exposure Flag (facility)</v>
       </c>
       <c r="L57" t="str">
         <v>Y</v>
       </c>
       <c r="M57" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="N57" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Counterparty_ID, lookup Facility_IDs in Facility Master where IS(Counterparty_ID), SELECT all_in_rate_pct. Weight by FX-converted bank share committed amount (committed_amount * bank_share_pct * fx_rate). Weighted average = SUM(rate * weight) / SUM(weight).
+        <v xml:space="preserve">For each counterparty, check all of its facilities in the participation table. For each facility, determine if it has cross-entity exposure (multiple distinct counterparties). If ANY facility belonging to this counterparty has cross-entity exposure, the counterparty flag = 1. Uses MAX over the facility-level flags for correct boolean OR logic.
 </v>
       </c>
       <c r="O57" t="str">
-        <v>All in Rate (%) (counterparty)</v>
+        <v>Cross Entity Exposure Flag (counterparty)</v>
       </c>
       <c r="P57" t="str">
         <v>Y</v>
       </c>
       <c r="Q57" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="R57" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each L3 LoB, lookup lob_segment_id from enterprise_business_taxonomy, then lookup facility_id in Facility Master where IS(lob_segment_id). SELECT all_in_rate_pct, weight by FX-converted bank share committed exposure (committed_amount * bank_share_pct * fx_rate). Weighted average = SUM(rate * weight) / SUM(weight).
+        <v xml:space="preserve">Not applicable — cross-entity exposure flag is a facility/counterparty level indicator. Desk-level analysis should use EXP-008 (Cross Entity Exposure Amount) for dollar-weighted concentration risk.
 </v>
       </c>
       <c r="S57" t="str">
-        <v>All in Rate (%) (desk)</v>
+        <v>Cross Entity Exposure Flag (desk)</v>
       </c>
       <c r="T57" t="str">
         <v>Y</v>
@@ -5675,11 +5739,11 @@
         <v>Calc</v>
       </c>
       <c r="V57" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each L2 LoB, lookup lob_segment_id from enterprise_business_taxonomy, then lookup facility_id in Facility Master where IS(lob_segment_id). SELECT all_in_rate_pct, weight by FX-converted bank share committed exposure (committed_amount * bank_share_pct * fx_rate). Calculated = SUM(rate * weight) / SUM(weight).
+        <v xml:space="preserve">Not applicable — cross-entity exposure flag is a facility/counterparty level indicator. Portfolio analysis should use EXP-008 for aggregate cross-entity exposure amounts.
 </v>
       </c>
       <c r="W57" t="str">
-        <v>All in Rate (%) (portfolio)</v>
+        <v>Cross Entity Exposure Flag (portfolio)</v>
       </c>
       <c r="X57" t="str">
         <v>Y</v>
@@ -5688,11 +5752,11 @@
         <v>Calc</v>
       </c>
       <c r="Z57" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each L1 LoB, lookup lob_segment_id from enterprise_business_taxonomy, then lookup facility_id in Facility Master where IS(lob_segment_id). SELECT all_in_rate_pct, weight by FX-converted bank share committed exposure (committed_amount * bank_share_pct * fx_rate). Calculated = SUM(rate * weight) / SUM(weight).
+        <v xml:space="preserve">Not applicable — cross-entity exposure flag is a facility/counterparty level indicator. Segment analysis should use EXP-008 for aggregate cross-entity exposure amounts.
 </v>
       </c>
       <c r="AA57" t="str">
-        <v>All in Rate (%) (business_segment)</v>
+        <v>Cross Entity Exposure Flag (business_segment)</v>
       </c>
       <c r="AB57" t="str">
         <v/>
@@ -5700,17 +5764,17 @@
     </row>
     <row r="58" xml:space="preserve">
       <c r="A58" t="str">
-        <v>PRC-002</v>
+        <v>PRC-001</v>
       </c>
       <c r="B58" t="str" xml:space="preserve">
-        <v xml:space="preserve">Reference benchmark interest rate applicable to the exposure (e.g., SOFR, Prime). Forms base component of total facility pricing. At facility level, reads the raw base_rate_pct from the pricing snapshot. At counterparty and higher levels, computes an exposure-weighted average using committed exposure amounts to reflect portfolio-level rate exposure.
+        <v xml:space="preserve">Total effective interest rate including base rate and spread. Calculated pricing KPI that provides insight into total yield generation and supports risk-adjusted return analysis.
 </v>
       </c>
       <c r="C58" t="str">
-        <v>Base Interest Rate (%)</v>
+        <v>All in Rate (%)</v>
       </c>
       <c r="D58" t="str" xml:space="preserve">
-        <v xml:space="preserve">Raw base_rate_pct from facility_pricing_snapshot for each active facility.
+        <v xml:space="preserve">Read all_in_rate_pct from facility_pricing_snapshot for each facility.
 </v>
       </c>
       <c r="E58" t="str">
@@ -5729,11 +5793,11 @@
         <v>Raw</v>
       </c>
       <c r="J58" t="str" xml:space="preserve">
-        <v xml:space="preserve">Raw base_rate_pct from facility_pricing_snapshot for each active facility.
+        <v xml:space="preserve">Read all_in_rate_pct from facility_pricing_snapshot for each facility.
 </v>
       </c>
       <c r="K58" t="str">
-        <v>Base Interest Rate (%) (facility)</v>
+        <v>All in Rate (%) (facility)</v>
       </c>
       <c r="L58" t="str">
         <v>Y</v>
@@ -5742,11 +5806,11 @@
         <v>Avg</v>
       </c>
       <c r="N58" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of base_rate_pct across counterparty facilities. Weight = committed_amount * bank_share_pct / 100 (bank's pro-rata committed exposure). Formula: SUM(base_rate_pct * bank_adj_committed) / SUM(bank_adj_committed).
+        <v xml:space="preserve">For each Counterparty_ID, lookup Facility_IDs in Facility Master where IS(Counterparty_ID), SELECT all_in_rate_pct. Weight by FX-converted bank share committed amount (committed_amount * bank_share_pct * fx_rate). Weighted average = SUM(rate * weight) / SUM(weight).
 </v>
       </c>
       <c r="O58" t="str">
-        <v>Base Interest Rate (%) (counterparty)</v>
+        <v>All in Rate (%) (counterparty)</v>
       </c>
       <c r="P58" t="str">
         <v>Y</v>
@@ -5755,37 +5819,37 @@
         <v>Avg</v>
       </c>
       <c r="R58" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of base_rate_pct per L3 desk segment. Weight = committed_amount * bank_share_pct / 100 (bank's pro-rata committed exposure).
+        <v xml:space="preserve">For each L3 LoB, lookup lob_segment_id from enterprise_business_taxonomy, then lookup facility_id in Facility Master where IS(lob_segment_id). SELECT all_in_rate_pct, weight by FX-converted bank share committed exposure (committed_amount * bank_share_pct * fx_rate). Weighted average = SUM(rate * weight) / SUM(weight).
 </v>
       </c>
       <c r="S58" t="str">
-        <v>Base Interest Rate (%) (desk)</v>
+        <v>All in Rate (%) (desk)</v>
       </c>
       <c r="T58" t="str">
         <v>Y</v>
       </c>
       <c r="U58" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="V58" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of base_rate_pct per L2 portfolio segment. Weight = committed_amount * bank_share_pct / 100 (bank's pro-rata committed exposure).
+        <v xml:space="preserve">For each L2 LoB, lookup lob_segment_id from enterprise_business_taxonomy, then lookup facility_id in Facility Master where IS(lob_segment_id). SELECT all_in_rate_pct, weight by FX-converted bank share committed exposure (committed_amount * bank_share_pct * fx_rate). Calculated = SUM(rate * weight) / SUM(weight).
 </v>
       </c>
       <c r="W58" t="str">
-        <v>Base Interest Rate (%) (portfolio)</v>
+        <v>All in Rate (%) (portfolio)</v>
       </c>
       <c r="X58" t="str">
         <v>Y</v>
       </c>
       <c r="Y58" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="Z58" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of base_rate_pct per L1 business segment. Weight = committed_amount * bank_share_pct / 100 (bank's pro-rata committed exposure).
+        <v xml:space="preserve">For each L1 LoB, lookup lob_segment_id from enterprise_business_taxonomy, then lookup facility_id in Facility Master where IS(lob_segment_id). SELECT all_in_rate_pct, weight by FX-converted bank share committed exposure (committed_amount * bank_share_pct * fx_rate). Calculated = SUM(rate * weight) / SUM(weight).
 </v>
       </c>
       <c r="AA58" t="str">
-        <v>Base Interest Rate (%) (business_segment)</v>
+        <v>All in Rate (%) (business_segment)</v>
       </c>
       <c r="AB58" t="str">
         <v/>
@@ -5793,17 +5857,17 @@
     </row>
     <row r="59" xml:space="preserve">
       <c r="A59" t="str">
-        <v>PRC-003</v>
+        <v>PRC-002</v>
       </c>
       <c r="B59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of exposures within portfolio with approved pricing or policy exceptions. Derived governance KPI measuring policy discipline and risk culture strength.
+        <v xml:space="preserve">Reference benchmark interest rate applicable to the exposure (e.g., SOFR, Prime). Forms base component of total facility pricing. At facility level, reads the raw base_rate_pct from the pricing snapshot. At counterparty and higher levels, computes an exposure-weighted average using committed exposure amounts to reflect portfolio-level rate exposure.
 </v>
       </c>
       <c r="C59" t="str">
-        <v>Exception Rate (%)</v>
+        <v>Base Interest Rate (%)</v>
       </c>
       <c r="D59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if pricing exception, 0 otherwise.
+        <v xml:space="preserve">Raw base_rate_pct from facility_pricing_snapshot for each active facility.
 </v>
       </c>
       <c r="E59" t="str">
@@ -5819,66 +5883,66 @@
         <v>Y</v>
       </c>
       <c r="I59" t="str">
-        <v>Calc</v>
+        <v>Raw</v>
       </c>
       <c r="J59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if pricing exception, 0 otherwise.
+        <v xml:space="preserve">Raw base_rate_pct from facility_pricing_snapshot for each active facility.
 </v>
       </c>
       <c r="K59" t="str">
-        <v>Exception Rate (%) (facility)</v>
+        <v>Base Interest Rate (%) (facility)</v>
       </c>
       <c r="L59" t="str">
         <v>Y</v>
       </c>
       <c r="M59" t="str">
-        <v>Calc</v>
+        <v>Avg</v>
       </c>
       <c r="N59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with pricing exception per counterparty.
+        <v xml:space="preserve">Exposure-weighted average of base_rate_pct across counterparty facilities. Weight = committed_amount * bank_share_pct / 100 (bank's pro-rata committed exposure). Formula: SUM(base_rate_pct * bank_adj_committed) / SUM(bank_adj_committed).
 </v>
       </c>
       <c r="O59" t="str">
-        <v>Exception Rate (%) (counterparty)</v>
+        <v>Base Interest Rate (%) (counterparty)</v>
       </c>
       <c r="P59" t="str">
         <v>Y</v>
       </c>
       <c r="Q59" t="str">
-        <v>Calc</v>
+        <v>Avg</v>
       </c>
       <c r="R59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with pricing exception per L3 desk.
+        <v xml:space="preserve">Exposure-weighted average of base_rate_pct per L3 desk segment. Weight = committed_amount * bank_share_pct / 100 (bank's pro-rata committed exposure).
 </v>
       </c>
       <c r="S59" t="str">
-        <v>Exception Rate (%) (desk)</v>
+        <v>Base Interest Rate (%) (desk)</v>
       </c>
       <c r="T59" t="str">
         <v>Y</v>
       </c>
       <c r="U59" t="str">
-        <v>Calc</v>
+        <v>Avg</v>
       </c>
       <c r="V59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with pricing exception per L2 portfolio.
+        <v xml:space="preserve">Exposure-weighted average of base_rate_pct per L2 portfolio segment. Weight = committed_amount * bank_share_pct / 100 (bank's pro-rata committed exposure).
 </v>
       </c>
       <c r="W59" t="str">
-        <v>Exception Rate (%) (portfolio)</v>
+        <v>Base Interest Rate (%) (portfolio)</v>
       </c>
       <c r="X59" t="str">
         <v>Y</v>
       </c>
       <c r="Y59" t="str">
-        <v>Calc</v>
+        <v>Avg</v>
       </c>
       <c r="Z59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with pricing exception per L1 business segment.
+        <v xml:space="preserve">Exposure-weighted average of base_rate_pct per L1 business segment. Weight = committed_amount * bank_share_pct / 100 (bank's pro-rata committed exposure).
 </v>
       </c>
       <c r="AA59" t="str">
-        <v>Exception Rate (%) (business_segment)</v>
+        <v>Base Interest Rate (%) (business_segment)</v>
       </c>
       <c r="AB59" t="str">
         <v/>
@@ -5886,17 +5950,18 @@
     </row>
     <row r="60" xml:space="preserve">
       <c r="A60" t="str">
-        <v>PRC-004</v>
+        <v>PRC-003</v>
       </c>
       <c r="B60" t="str" xml:space="preserve">
-        <v xml:space="preserve">Fee percentage applied to committed or undrawn exposure. Calculated KPI supporting pricing adequacy and revenue optimization analysis.
+        <v xml:space="preserve">Percentage of facilities with approved pricing or policy exceptions. Computed as COUNT(exception facilities) / COUNT(total facilities) × 100. Sourced from L2 facility_pricing_snapshot — the atomic pricing record — using the is_pricing_exception_flag. At aggregate levels, uses count-ratio rollup: re-counts exceptions and totals across all constituent facilities, never averages pre-computed rates. Key governance KPI measuring policy discipline, risk culture strength, and pricing override frequency.
 </v>
       </c>
       <c r="C60" t="str">
-        <v>Fee Rate (%)</v>
+        <v>Exception Rate (%)</v>
       </c>
       <c r="D60" t="str" xml:space="preserve">
-        <v xml:space="preserve">Fee Income / Average Balance
+        <v xml:space="preserve">Binary flag: 1.0 if pricing exception approved, 0.0 otherwise.
+Ingredients: is_pricing_exception_flag (L2 facility_pricing_snapshot)
 </v>
       </c>
       <c r="E60" t="str">
@@ -5915,63 +5980,76 @@
         <v>Calc</v>
       </c>
       <c r="J60" t="str" xml:space="preserve">
-        <v xml:space="preserve">Fee Income / Average Balance
+        <v xml:space="preserve">Binary flag: 1.0 if pricing exception approved, 0.0 otherwise.
+Ingredients: is_pricing_exception_flag (L2 facility_pricing_snapshot)
 </v>
       </c>
       <c r="K60" t="str">
-        <v>Fee Rate (%) (facility)</v>
+        <v>Exception Rate (%) (facility)</v>
       </c>
       <c r="L60" t="str">
         <v>Y</v>
       </c>
       <c r="M60" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="N60" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of fee_rate_pct across counterparty facilities.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD is_pricing_exception_flag for all facilities of this counterparty
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup: re-counts from facility-level flags.
 </v>
       </c>
       <c r="O60" t="str">
-        <v>Fee Rate (%) (counterparty)</v>
+        <v>Exception Rate (%) (counterparty)</v>
       </c>
       <c r="P60" t="str">
         <v>Y</v>
       </c>
       <c r="Q60" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="R60" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level fee_rate_pct per L3 desk segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOOKUP managed_segment_id from enterprise_business_taxonomy
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup per desk.
 </v>
       </c>
       <c r="S60" t="str">
-        <v>Fee Rate (%) (desk)</v>
+        <v>Exception Rate (%) (desk)</v>
       </c>
       <c r="T60" t="str">
         <v>Y</v>
       </c>
       <c r="U60" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="V60" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level fee_rate_pct per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup per portfolio.
 </v>
       </c>
       <c r="W60" t="str">
-        <v>Fee Rate (%) (portfolio)</v>
+        <v>Exception Rate (%) (portfolio)</v>
       </c>
       <c r="X60" t="str">
         <v>Y</v>
       </c>
       <c r="Y60" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z60" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level fee_rate_pct per L1 business segment segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup per business segment.
 </v>
       </c>
       <c r="AA60" t="str">
-        <v>Fee Rate (%) (business_segment)</v>
+        <v>Exception Rate (%) (business_segment)</v>
       </c>
       <c r="AB60" t="str">
         <v/>
@@ -5979,17 +6057,17 @@
     </row>
     <row r="61" xml:space="preserve">
       <c r="A61" t="str">
-        <v>PRC-005</v>
+        <v>PRC-004</v>
       </c>
       <c r="B61" t="str" xml:space="preserve">
-        <v xml:space="preserve">Indicator identifying exposures priced outside standard policy guidelines. Supports governance discipline and pricing compliance monitoring.
+        <v xml:space="preserve">Fee percentage applied to committed or undrawn exposure. Calculated KPI supporting pricing adequacy and revenue optimization analysis.
 </v>
       </c>
       <c r="C61" t="str">
-        <v>Pricing Exception Status</v>
+        <v>Fee Rate (%)</v>
       </c>
       <c r="D61" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if pricing exception exists, 0 otherwise.
+        <v xml:space="preserve">Fee Income / Average Balance
 </v>
       </c>
       <c r="E61" t="str">
@@ -6008,50 +6086,50 @@
         <v>Calc</v>
       </c>
       <c r="J61" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if pricing exception exists, 0 otherwise.
+        <v xml:space="preserve">Fee Income / Average Balance
 </v>
       </c>
       <c r="K61" t="str">
-        <v>Pricing Exception Status (facility)</v>
+        <v>Fee Rate (%) (facility)</v>
       </c>
       <c r="L61" t="str">
         <v>Y</v>
       </c>
       <c r="M61" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="N61" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with pricing exception per counterparty.
+        <v xml:space="preserve">Exposure-weighted average of fee_rate_pct across counterparty facilities.
 </v>
       </c>
       <c r="O61" t="str">
-        <v>Pricing Exception Status (counterparty)</v>
+        <v>Fee Rate (%) (counterparty)</v>
       </c>
       <c r="P61" t="str">
         <v>Y</v>
       </c>
       <c r="Q61" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="R61" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with pricing exception per L3 desk segment.
+        <v xml:space="preserve">AVG of facility-level fee_rate_pct per L3 desk segment.
 </v>
       </c>
       <c r="S61" t="str">
-        <v>Pricing Exception Status (desk)</v>
+        <v>Fee Rate (%) (desk)</v>
       </c>
       <c r="T61" t="str">
         <v>Y</v>
       </c>
       <c r="U61" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="V61" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with pricing exception per L2 portfolio segment.
+        <v xml:space="preserve">AVG of facility-level fee_rate_pct per L2 portfolio segment.
 </v>
       </c>
       <c r="W61" t="str">
-        <v>Pricing Exception Status (portfolio)</v>
+        <v>Fee Rate (%) (portfolio)</v>
       </c>
       <c r="X61" t="str">
         <v>Y</v>
@@ -6060,11 +6138,11 @@
         <v>Agg</v>
       </c>
       <c r="Z61" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with pricing exception per L1 business segment.
+        <v xml:space="preserve">SUM of facility-level fee_rate_pct per L1 business segment segment.
 </v>
       </c>
       <c r="AA61" t="str">
-        <v>Pricing Exception Status (business_segment)</v>
+        <v>Fee Rate (%) (business_segment)</v>
       </c>
       <c r="AB61" t="str">
         <v/>
@@ -6072,17 +6150,17 @@
     </row>
     <row r="62" xml:space="preserve">
       <c r="A62" t="str">
-        <v>PRC-006</v>
+        <v>PRC-005</v>
       </c>
       <c r="B62" t="str" xml:space="preserve">
-        <v xml:space="preserve">Pricing classification tier assigned to facility. Supports structured pricing strategy and yield segmentation.
+        <v xml:space="preserve">Indicator identifying exposures priced outside standard policy guidelines. Supports governance discipline and pricing compliance monitoring.
 </v>
       </c>
       <c r="C62" t="str">
-        <v>Pricing Tier</v>
+        <v>Pricing Exception Status</v>
       </c>
       <c r="D62" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read pricing_tier_code from facility_detail_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Binary flag: 1 if pricing exception exists, 0 otherwise.
 </v>
       </c>
       <c r="E62" t="str">
@@ -6098,27 +6176,27 @@
         <v>Y</v>
       </c>
       <c r="I62" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="J62" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read pricing_tier_code from facility_detail_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Binary flag: 1 if pricing exception exists, 0 otherwise.
 </v>
       </c>
       <c r="K62" t="str">
-        <v>Pricing Tier (facility)</v>
+        <v>Pricing Exception Status (facility)</v>
       </c>
       <c r="L62" t="str">
         <v>Y</v>
       </c>
       <c r="M62" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="N62" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read pricing_tier_code per counterparty.
+        <v xml:space="preserve">COUNT of facilities with pricing exception per counterparty.
 </v>
       </c>
       <c r="O62" t="str">
-        <v>Pricing Tier (counterparty)</v>
+        <v>Pricing Exception Status (counterparty)</v>
       </c>
       <c r="P62" t="str">
         <v>Y</v>
@@ -6127,11 +6205,11 @@
         <v>Agg</v>
       </c>
       <c r="R62" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pricing_tier_code per L3 desk segment.
+        <v xml:space="preserve">COUNT of facilities with pricing exception per L3 desk segment.
 </v>
       </c>
       <c r="S62" t="str">
-        <v>Pricing Tier (desk)</v>
+        <v>Pricing Exception Status (desk)</v>
       </c>
       <c r="T62" t="str">
         <v>Y</v>
@@ -6140,11 +6218,11 @@
         <v>Agg</v>
       </c>
       <c r="V62" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pricing_tier_code per L2 portfolio segment.
+        <v xml:space="preserve">COUNT of facilities with pricing exception per L2 portfolio segment.
 </v>
       </c>
       <c r="W62" t="str">
-        <v>Pricing Tier (portfolio)</v>
+        <v>Pricing Exception Status (portfolio)</v>
       </c>
       <c r="X62" t="str">
         <v>Y</v>
@@ -6153,11 +6231,11 @@
         <v>Agg</v>
       </c>
       <c r="Z62" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pricing_tier_code per L1 business segment segment.
+        <v xml:space="preserve">COUNT of facilities with pricing exception per L1 business segment.
 </v>
       </c>
       <c r="AA62" t="str">
-        <v>Pricing Tier (business_segment)</v>
+        <v>Pricing Exception Status (business_segment)</v>
       </c>
       <c r="AB62" t="str">
         <v/>
@@ -6165,17 +6243,17 @@
     </row>
     <row r="63" xml:space="preserve">
       <c r="A63" t="str">
-        <v>PRC-007</v>
+        <v>PRC-006</v>
       </c>
       <c r="B63" t="str" xml:space="preserve">
-        <v xml:space="preserve">Credit spread over reference base rate charged on exposure, expressed as percentage. Represents risk premium embedded in pricing and supports yield analysis.
+        <v xml:space="preserve">Pricing classification tier assigned to facility. Supports structured pricing strategy and yield segmentation.
 </v>
       </c>
       <c r="C63" t="str">
-        <v>Interest Rate Spread (%)</v>
+        <v>Pricing Tier</v>
       </c>
       <c r="D63" t="str" xml:space="preserve">
-        <v xml:space="preserve">Facility Asset Spread/ Total Outstanding Balance
+        <v xml:space="preserve">Read pricing_tier_code from facility_detail_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="E63" t="str">
@@ -6191,53 +6269,53 @@
         <v>Y</v>
       </c>
       <c r="I63" t="str">
-        <v>Calc</v>
+        <v>Raw</v>
       </c>
       <c r="J63" t="str" xml:space="preserve">
-        <v xml:space="preserve">Facility Asset Spread/ Total Outstanding Balance
+        <v xml:space="preserve">Read pricing_tier_code from facility_detail_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="K63" t="str">
-        <v>Interest Rate Spread (%) (facility)</v>
+        <v>Pricing Tier (facility)</v>
       </c>
       <c r="L63" t="str">
         <v>Y</v>
       </c>
       <c r="M63" t="str">
-        <v>Avg</v>
+        <v>Raw</v>
       </c>
       <c r="N63" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of interest_rate_spread_bps across counterparty facilities.
+        <v xml:space="preserve">Read pricing_tier_code per counterparty.
 </v>
       </c>
       <c r="O63" t="str">
-        <v>Interest Rate Spread (%) (counterparty)</v>
+        <v>Pricing Tier (counterparty)</v>
       </c>
       <c r="P63" t="str">
         <v>Y</v>
       </c>
       <c r="Q63" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="R63" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level interest_rate_spread_bps per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level pricing_tier_code per L3 desk segment.
 </v>
       </c>
       <c r="S63" t="str">
-        <v>Interest Rate Spread (%) (desk)</v>
+        <v>Pricing Tier (desk)</v>
       </c>
       <c r="T63" t="str">
         <v>Y</v>
       </c>
       <c r="U63" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="V63" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level interest_rate_spread_bps per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level pricing_tier_code per L2 portfolio segment.
 </v>
       </c>
       <c r="W63" t="str">
-        <v>Interest Rate Spread (%) (portfolio)</v>
+        <v>Pricing Tier (portfolio)</v>
       </c>
       <c r="X63" t="str">
         <v>Y</v>
@@ -6246,11 +6324,11 @@
         <v>Agg</v>
       </c>
       <c r="Z63" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level interest_rate_spread_bps per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level pricing_tier_code per L1 business segment segment.
 </v>
       </c>
       <c r="AA63" t="str">
-        <v>Interest Rate Spread (%) (business_segment)</v>
+        <v>Pricing Tier (business_segment)</v>
       </c>
       <c r="AB63" t="str">
         <v/>
@@ -6258,17 +6336,17 @@
     </row>
     <row r="64" xml:space="preserve">
       <c r="A64" t="str">
-        <v>PRC-008</v>
+        <v>PRC-007</v>
       </c>
       <c r="B64" t="str" xml:space="preserve">
-        <v xml:space="preserve">Measures exposure of earnings/cash flow to interest rate changes; shows vulnerability to rate shocks and informs hedging/pricing and stress-test outcomes.
+        <v xml:space="preserve">Credit spread over reference base rate charged on exposure, expressed as percentage. Represents risk premium embedded in pricing and supports yield analysis.
 </v>
       </c>
       <c r="C64" t="str">
-        <v>Interest Rate Sensitivity (%)</v>
+        <v>Interest Rate Spread (%)</v>
       </c>
       <c r="D64" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read interest_rate_sensitivity_pct from facility_financial_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Facility Asset Spread/ Total Outstanding Balance
 </v>
       </c>
       <c r="E64" t="str">
@@ -6284,53 +6362,53 @@
         <v>Y</v>
       </c>
       <c r="I64" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="J64" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read interest_rate_sensitivity_pct from facility_financial_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Facility Asset Spread/ Total Outstanding Balance
 </v>
       </c>
       <c r="K64" t="str">
-        <v>Interest Rate Sensitivity (%) (facility)</v>
+        <v>Interest Rate Spread (%) (facility)</v>
       </c>
       <c r="L64" t="str">
         <v>Y</v>
       </c>
       <c r="M64" t="str">
-        <v>Raw</v>
+        <v>Avg</v>
       </c>
       <c r="N64" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read interest_rate_sensitivity_pct per counterparty.
+        <v xml:space="preserve">Exposure-weighted average of interest_rate_spread_bps across counterparty facilities.
 </v>
       </c>
       <c r="O64" t="str">
-        <v>Interest Rate Sensitivity (%) (counterparty)</v>
+        <v>Interest Rate Spread (%) (counterparty)</v>
       </c>
       <c r="P64" t="str">
         <v>Y</v>
       </c>
       <c r="Q64" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="R64" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level interest_rate_sensitivity_pct per L3 desk segment.
+        <v xml:space="preserve">AVG of facility-level interest_rate_spread_bps per L3 desk segment.
 </v>
       </c>
       <c r="S64" t="str">
-        <v>Interest Rate Sensitivity (%) (desk)</v>
+        <v>Interest Rate Spread (%) (desk)</v>
       </c>
       <c r="T64" t="str">
         <v>Y</v>
       </c>
       <c r="U64" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="V64" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level interest_rate_sensitivity_pct per L2 portfolio segment.
+        <v xml:space="preserve">AVG of facility-level interest_rate_spread_bps per L2 portfolio segment.
 </v>
       </c>
       <c r="W64" t="str">
-        <v>Interest Rate Sensitivity (%) (portfolio)</v>
+        <v>Interest Rate Spread (%) (portfolio)</v>
       </c>
       <c r="X64" t="str">
         <v>Y</v>
@@ -6339,11 +6417,11 @@
         <v>Agg</v>
       </c>
       <c r="Z64" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level interest_rate_sensitivity_pct per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level interest_rate_spread_bps per L1 business segment segment.
 </v>
       </c>
       <c r="AA64" t="str">
-        <v>Interest Rate Sensitivity (%) (business_segment)</v>
+        <v>Interest Rate Spread (%) (business_segment)</v>
       </c>
       <c r="AB64" t="str">
         <v/>
@@ -6351,17 +6429,17 @@
     </row>
     <row r="65" xml:space="preserve">
       <c r="A65" t="str">
-        <v>PRC-009</v>
+        <v>PRC-008</v>
       </c>
       <c r="B65" t="str" xml:space="preserve">
-        <v xml:space="preserve">Boolean indicator identifying whether the exposure was approved outside standard pricing policy thresholds at origination or amendment.
+        <v xml:space="preserve">Measures exposure of earnings/cash flow to interest rate changes; shows vulnerability to rate shocks and informs hedging/pricing and stress-test outcomes.
 </v>
       </c>
       <c r="C65" t="str">
-        <v>Pricing Exception Flag (Y/N)</v>
+        <v>Interest Rate Sensitivity (%)</v>
       </c>
       <c r="D65" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated pricing_exception_flag per facility.
+        <v xml:space="preserve">Read interest_rate_sensitivity_pct from facility_financial_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="E65" t="str">
@@ -6377,27 +6455,27 @@
         <v>Y</v>
       </c>
       <c r="I65" t="str">
-        <v>Calc</v>
+        <v>Raw</v>
       </c>
       <c r="J65" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated pricing_exception_flag per facility.
+        <v xml:space="preserve">Read interest_rate_sensitivity_pct from facility_financial_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="K65" t="str">
-        <v>Pricing Exception Flag (Y/N) (facility)</v>
+        <v>Interest Rate Sensitivity (%) (facility)</v>
       </c>
       <c r="L65" t="str">
         <v>Y</v>
       </c>
       <c r="M65" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="N65" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pricing_exception_flag per counterparty.
+        <v xml:space="preserve">Read interest_rate_sensitivity_pct per counterparty.
 </v>
       </c>
       <c r="O65" t="str">
-        <v>Pricing Exception Flag (Y/N) (counterparty)</v>
+        <v>Interest Rate Sensitivity (%) (counterparty)</v>
       </c>
       <c r="P65" t="str">
         <v>Y</v>
@@ -6406,11 +6484,11 @@
         <v>Agg</v>
       </c>
       <c r="R65" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pricing_exception_flag per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level interest_rate_sensitivity_pct per L3 desk segment.
 </v>
       </c>
       <c r="S65" t="str">
-        <v>Pricing Exception Flag (Y/N) (desk)</v>
+        <v>Interest Rate Sensitivity (%) (desk)</v>
       </c>
       <c r="T65" t="str">
         <v>Y</v>
@@ -6419,11 +6497,11 @@
         <v>Agg</v>
       </c>
       <c r="V65" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pricing_exception_flag per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level interest_rate_sensitivity_pct per L2 portfolio segment.
 </v>
       </c>
       <c r="W65" t="str">
-        <v>Pricing Exception Flag (Y/N) (portfolio)</v>
+        <v>Interest Rate Sensitivity (%) (portfolio)</v>
       </c>
       <c r="X65" t="str">
         <v>Y</v>
@@ -6432,11 +6510,11 @@
         <v>Agg</v>
       </c>
       <c r="Z65" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pricing_exception_flag per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level interest_rate_sensitivity_pct per L1 business segment segment.
 </v>
       </c>
       <c r="AA65" t="str">
-        <v>Pricing Exception Flag (Y/N) (business_segment)</v>
+        <v>Interest Rate Sensitivity (%) (business_segment)</v>
       </c>
       <c r="AB65" t="str">
         <v/>
@@ -6444,16 +6522,109 @@
     </row>
     <row r="66" xml:space="preserve">
       <c r="A66" t="str">
+        <v>PRC-009</v>
+      </c>
+      <c r="B66" t="str" xml:space="preserve">
+        <v xml:space="preserve">Boolean indicator identifying whether the exposure was approved outside standard pricing policy thresholds at origination or amendment.
+</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Pricing Exception Flag (Y/N)</v>
+      </c>
+      <c r="D66" t="str" xml:space="preserve">
+        <v xml:space="preserve">Calculated pricing_exception_flag per facility.
+</v>
+      </c>
+      <c r="E66" t="str">
+        <v/>
+      </c>
+      <c r="F66" t="str">
+        <v/>
+      </c>
+      <c r="G66" t="str">
+        <v/>
+      </c>
+      <c r="H66" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I66" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="J66" t="str" xml:space="preserve">
+        <v xml:space="preserve">Calculated pricing_exception_flag per facility.
+</v>
+      </c>
+      <c r="K66" t="str">
+        <v>Pricing Exception Flag (Y/N) (facility)</v>
+      </c>
+      <c r="L66" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M66" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N66" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level pricing_exception_flag per counterparty.
+</v>
+      </c>
+      <c r="O66" t="str">
+        <v>Pricing Exception Flag (Y/N) (counterparty)</v>
+      </c>
+      <c r="P66" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q66" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R66" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level pricing_exception_flag per L3 desk segment.
+</v>
+      </c>
+      <c r="S66" t="str">
+        <v>Pricing Exception Flag (Y/N) (desk)</v>
+      </c>
+      <c r="T66" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U66" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V66" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level pricing_exception_flag per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W66" t="str">
+        <v>Pricing Exception Flag (Y/N) (portfolio)</v>
+      </c>
+      <c r="X66" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y66" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z66" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level pricing_exception_flag per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA66" t="str">
+        <v>Pricing Exception Flag (Y/N) (business_segment)</v>
+      </c>
+      <c r="AB66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67" xml:space="preserve">
+      <c r="A67" t="str">
         <v>PROF-108</v>
       </c>
-      <c r="B66" t="str" xml:space="preserve">
+      <c r="B67" t="str" xml:space="preserve">
         <v xml:space="preserve">Annualized interest cost on drawn/funded exposure. Computed as SUM(funded_amount) * bank_share_pct * cost_of_funds_pct at facility level. Uses funded basis (actual drawn amounts from position_detail) rather than committed basis, aligning with FR Y-9C Schedule HI Item 2.
 </v>
       </c>
-      <c r="C66" t="str">
+      <c r="C67" t="str">
         <v>Interest Expense</v>
       </c>
-      <c r="D66" t="str" xml:space="preserve">
+      <c r="D67" t="str" xml:space="preserve">
         <v xml:space="preserve">For each active facility:
 1. Join position -&gt; position_detail, SUM(funded_amount) per facility
 2. Multiply by bank_share_pct / 100 from facility_lender_allocation
@@ -6461,22 +6632,22 @@
    from facility_pricing_snapshot
 </v>
       </c>
-      <c r="E66" t="str">
-        <v/>
-      </c>
-      <c r="F66" t="str">
-        <v/>
-      </c>
-      <c r="G66" t="str">
-        <v/>
-      </c>
-      <c r="H66" t="str">
-        <v>Y</v>
-      </c>
-      <c r="I66" t="str">
-        <v>Calc</v>
-      </c>
-      <c r="J66" t="str" xml:space="preserve">
+      <c r="E67" t="str">
+        <v/>
+      </c>
+      <c r="F67" t="str">
+        <v/>
+      </c>
+      <c r="G67" t="str">
+        <v/>
+      </c>
+      <c r="H67" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I67" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="J67" t="str" xml:space="preserve">
         <v xml:space="preserve">For each active facility:
 1. Join position -&gt; position_detail, SUM(funded_amount) per facility
 2. Multiply by bank_share_pct / 100 from facility_lender_allocation
@@ -6484,156 +6655,63 @@
    from facility_pricing_snapshot
 </v>
       </c>
-      <c r="K66" t="str">
+      <c r="K67" t="str">
         <v>Interest Expense (facility)</v>
       </c>
-      <c r="L66" t="str">
-        <v>Y</v>
-      </c>
-      <c r="M66" t="str">
-        <v>Calc</v>
-      </c>
-      <c r="N66" t="str" xml:space="preserve">
+      <c r="L67" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M67" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="N67" t="str" xml:space="preserve">
         <v xml:space="preserve">For each counterparty, sum facility-level interest expense weighted
 by participation_pct from facility_counterparty_participation.
 </v>
       </c>
-      <c r="O66" t="str">
+      <c r="O67" t="str">
         <v>Interest Expense (counterparty)</v>
       </c>
-      <c r="P66" t="str">
-        <v>Y</v>
-      </c>
-      <c r="Q66" t="str">
-        <v>Agg</v>
-      </c>
-      <c r="R66" t="str" xml:space="preserve">
+      <c r="P67" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q67" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R67" t="str" xml:space="preserve">
         <v xml:space="preserve">SUM of facility-level interest expense per L3 desk segment.
 </v>
       </c>
-      <c r="S66" t="str">
+      <c r="S67" t="str">
         <v>Interest Expense (desk)</v>
       </c>
-      <c r="T66" t="str">
-        <v>Y</v>
-      </c>
-      <c r="U66" t="str">
-        <v>Agg</v>
-      </c>
-      <c r="V66" t="str" xml:space="preserve">
+      <c r="T67" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U67" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V67" t="str" xml:space="preserve">
         <v xml:space="preserve">SUM of facility-level interest expense per L2 portfolio segment.
 Traverses L3 -&gt; L2 via parent_segment_id.
 </v>
       </c>
-      <c r="W66" t="str">
+      <c r="W67" t="str">
         <v>Interest Expense (portfolio)</v>
       </c>
-      <c r="X66" t="str">
-        <v>Y</v>
-      </c>
-      <c r="Y66" t="str">
-        <v>Agg</v>
-      </c>
-      <c r="Z66" t="str" xml:space="preserve">
+      <c r="X67" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y67" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z67" t="str" xml:space="preserve">
         <v xml:space="preserve">SUM of facility-level interest expense per L1 business segment.
 Traverses L3 -&gt; L2 -&gt; L1 via parent_segment_id chain.
 </v>
       </c>
-      <c r="AA66" t="str">
+      <c r="AA67" t="str">
         <v>Interest Expense (business_segment)</v>
-      </c>
-      <c r="AB66" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="67" xml:space="preserve">
-      <c r="A67" t="str">
-        <v>REF-001</v>
-      </c>
-      <c r="B67" t="str" xml:space="preserve">
-        <v xml:space="preserve">Count of individual loans within portfolio or facility grouping. Supports exposure granularity analysis.
-</v>
-      </c>
-      <c r="C67" t="str">
-        <v>Number of Loans</v>
-      </c>
-      <c r="D67" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Facility_ID, COUNT DISTINCT(Position_ID) from l2.position. Result materialized to l3.facility_exposure_calc.number_of_loans.
-</v>
-      </c>
-      <c r="E67" t="str">
-        <v/>
-      </c>
-      <c r="F67" t="str">
-        <v/>
-      </c>
-      <c r="G67" t="str">
-        <v/>
-      </c>
-      <c r="H67" t="str">
-        <v>Y</v>
-      </c>
-      <c r="I67" t="str">
-        <v>Agg</v>
-      </c>
-      <c r="J67" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Facility_ID, COUNT DISTINCT(Position_ID) from l2.position. Result materialized to l3.facility_exposure_calc.number_of_loans.
-</v>
-      </c>
-      <c r="K67" t="str">
-        <v>Number of Loans (facility)</v>
-      </c>
-      <c r="L67" t="str">
-        <v>Y</v>
-      </c>
-      <c r="M67" t="str">
-        <v>Agg</v>
-      </c>
-      <c r="N67" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Counterparty_ID, COUNT DISTINCT(Position_ID) from l2.position joined to l2.facility_master.
-</v>
-      </c>
-      <c r="O67" t="str">
-        <v>Number of Loans (counterparty)</v>
-      </c>
-      <c r="P67" t="str">
-        <v>Y</v>
-      </c>
-      <c r="Q67" t="str">
-        <v>Agg</v>
-      </c>
-      <c r="R67" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each L3 LoB, COUNT DISTINCT(Position_ID) from l2.position joined to l2.facility_master and l1.enterprise_business_taxonomy.
-</v>
-      </c>
-      <c r="S67" t="str">
-        <v>Number of Loans (desk)</v>
-      </c>
-      <c r="T67" t="str">
-        <v>Y</v>
-      </c>
-      <c r="U67" t="str">
-        <v>Agg</v>
-      </c>
-      <c r="V67" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each L2 LoB, COUNT DISTINCT(Position_ID) from l2.position joined to l2.facility_master and l1.enterprise_business_taxonomy hierarchy.
-</v>
-      </c>
-      <c r="W67" t="str">
-        <v>Number of Loans (portfolio)</v>
-      </c>
-      <c r="X67" t="str">
-        <v>Y</v>
-      </c>
-      <c r="Y67" t="str">
-        <v>Agg</v>
-      </c>
-      <c r="Z67" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each L1 LoB, COUNT DISTINCT(Position_ID) from l2.position joined to l2.facility_master and l1.enterprise_business_taxonomy hierarchy.
-</v>
-      </c>
-      <c r="AA67" t="str">
-        <v>Number of Loans (business_segment)</v>
       </c>
       <c r="AB67" t="str">
         <v/>
@@ -6641,17 +6719,17 @@
     </row>
     <row r="68" xml:space="preserve">
       <c r="A68" t="str">
-        <v>REF-002</v>
+        <v>REF-001</v>
       </c>
       <c r="B68" t="str" xml:space="preserve">
-        <v xml:space="preserve">Snapshot date of the dataset used for reporting and aggregation. Serves as the temporal reference point for all balances, risk metrics, and performance indicators.
+        <v xml:space="preserve">Count of individual loans within portfolio or facility grouping. Supports exposure granularity analysis.
 </v>
       </c>
       <c r="C68" t="str">
-        <v>Reporting Period (As-of Date)</v>
+        <v>Number of Loans</v>
       </c>
       <c r="D68" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read as_of_date from facility_exposure_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">For each Facility_ID, COUNT DISTINCT(Position_ID) from l2.position. Result materialized to l3.facility_exposure_calc.number_of_loans.
 </v>
       </c>
       <c r="E68" t="str">
@@ -6667,27 +6745,27 @@
         <v>Y</v>
       </c>
       <c r="I68" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="J68" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read as_of_date from facility_exposure_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">For each Facility_ID, COUNT DISTINCT(Position_ID) from l2.position. Result materialized to l3.facility_exposure_calc.number_of_loans.
 </v>
       </c>
       <c r="K68" t="str">
-        <v>Reporting Period (As-of Date) (facility)</v>
+        <v>Number of Loans (facility)</v>
       </c>
       <c r="L68" t="str">
         <v>Y</v>
       </c>
       <c r="M68" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="N68" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read as_of_date per counterparty.
+        <v xml:space="preserve">For each Counterparty_ID, COUNT DISTINCT(Position_ID) from l2.position joined to l2.facility_master.
 </v>
       </c>
       <c r="O68" t="str">
-        <v>Reporting Period (As-of Date) (counterparty)</v>
+        <v>Number of Loans (counterparty)</v>
       </c>
       <c r="P68" t="str">
         <v>Y</v>
@@ -6696,11 +6774,11 @@
         <v>Agg</v>
       </c>
       <c r="R68" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level as_of_date per L3 desk segment.
+        <v xml:space="preserve">For each L3 LoB, COUNT DISTINCT(Position_ID) from l2.position joined to l2.facility_master and l1.enterprise_business_taxonomy.
 </v>
       </c>
       <c r="S68" t="str">
-        <v>Reporting Period (As-of Date) (desk)</v>
+        <v>Number of Loans (desk)</v>
       </c>
       <c r="T68" t="str">
         <v>Y</v>
@@ -6709,11 +6787,11 @@
         <v>Agg</v>
       </c>
       <c r="V68" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level as_of_date per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 LoB, COUNT DISTINCT(Position_ID) from l2.position joined to l2.facility_master and l1.enterprise_business_taxonomy hierarchy.
 </v>
       </c>
       <c r="W68" t="str">
-        <v>Reporting Period (As-of Date) (portfolio)</v>
+        <v>Number of Loans (portfolio)</v>
       </c>
       <c r="X68" t="str">
         <v>Y</v>
@@ -6722,11 +6800,11 @@
         <v>Agg</v>
       </c>
       <c r="Z68" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level as_of_date per L1 business segment segment.
+        <v xml:space="preserve">For each L1 LoB, COUNT DISTINCT(Position_ID) from l2.position joined to l2.facility_master and l1.enterprise_business_taxonomy hierarchy.
 </v>
       </c>
       <c r="AA68" t="str">
-        <v>Reporting Period (As-of Date) (business_segment)</v>
+        <v>Number of Loans (business_segment)</v>
       </c>
       <c r="AB68" t="str">
         <v/>
@@ -6734,17 +6812,17 @@
     </row>
     <row r="69" xml:space="preserve">
       <c r="A69" t="str">
-        <v>REF-003</v>
+        <v>REF-002</v>
       </c>
       <c r="B69" t="str" xml:space="preserve">
-        <v xml:space="preserve">Average tenor of the underlying facilities across exposures. For facility, displayed the calculated tenor based on Origination Date ("Effective Date") and Maturity Date ("End Date"). At other levels this metric is aggregated as an average to represent the average period of the underlying facilities. Calculated from l2.facility_master.maturity_date and origination_date.
+        <v xml:space="preserve">Snapshot date of the dataset used for reporting and aggregation. Serves as the temporal reference point for all balances, risk metrics, and performance indicators.
 </v>
       </c>
       <c r="C69" t="str">
-        <v>Average Tenor (Years)</v>
+        <v>Reporting Period (As-of Date)</v>
       </c>
       <c r="D69" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Facility_ID, (Maturity Date - Origination Date) / 365.25 to get tenor in years.
+        <v xml:space="preserve">Read as_of_date from facility_exposure_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="E69" t="str">
@@ -6760,66 +6838,66 @@
         <v>Y</v>
       </c>
       <c r="I69" t="str">
-        <v>Calc</v>
+        <v>Raw</v>
       </c>
       <c r="J69" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Facility_ID, (Maturity Date - Origination Date) / 365.25 to get tenor in years.
+        <v xml:space="preserve">Read as_of_date from facility_exposure_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="K69" t="str">
-        <v>Average Tenor (Years) (facility)</v>
+        <v>Reporting Period (As-of Date) (facility)</v>
       </c>
       <c r="L69" t="str">
         <v>Y</v>
       </c>
       <c r="M69" t="str">
-        <v>Avg</v>
+        <v>Raw</v>
       </c>
       <c r="N69" t="str" xml:space="preserve">
-        <v xml:space="preserve">Average of facility-level tenor (years) across counterparty facilities.
+        <v xml:space="preserve">Read as_of_date per counterparty.
 </v>
       </c>
       <c r="O69" t="str">
-        <v>Average Tenor (Years) (counterparty)</v>
+        <v>Reporting Period (As-of Date) (counterparty)</v>
       </c>
       <c r="P69" t="str">
         <v>Y</v>
       </c>
       <c r="Q69" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="R69" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level tenor (years) per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level as_of_date per L3 desk segment.
 </v>
       </c>
       <c r="S69" t="str">
-        <v>Average Tenor (Years) (desk)</v>
+        <v>Reporting Period (As-of Date) (desk)</v>
       </c>
       <c r="T69" t="str">
         <v>Y</v>
       </c>
       <c r="U69" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="V69" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level tenor (years) per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level as_of_date per L2 portfolio segment.
 </v>
       </c>
       <c r="W69" t="str">
-        <v>Average Tenor (Years) (portfolio)</v>
+        <v>Reporting Period (As-of Date) (portfolio)</v>
       </c>
       <c r="X69" t="str">
         <v>Y</v>
       </c>
       <c r="Y69" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="Z69" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level tenor (years) per L1 business segment.
+        <v xml:space="preserve">SUM of facility-level as_of_date per L1 business segment segment.
 </v>
       </c>
       <c r="AA69" t="str">
-        <v>Average Tenor (Years) (business_segment)</v>
+        <v>Reporting Period (As-of Date) (business_segment)</v>
       </c>
       <c r="AB69" t="str">
         <v/>
@@ -6827,17 +6905,17 @@
     </row>
     <row r="70" xml:space="preserve">
       <c r="A70" t="str">
-        <v>REF-004</v>
+        <v>REF-003</v>
       </c>
       <c r="B70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Unique system identifier assigned to the borrower or obligor. Used for exposure aggregation and risk consolidation.
+        <v xml:space="preserve">Average tenor of the underlying facilities across exposures. For facility, displayed the calculated tenor based on Origination Date ("Effective Date") and Maturity Date ("End Date"). At other levels this metric is aggregated as an average to represent the average period of the underlying facilities. Calculated from l2.facility_master.maturity_date and origination_date.
 </v>
       </c>
       <c r="C70" t="str">
-        <v>Counterparty ID</v>
+        <v>Average Tenor (Years)</v>
       </c>
       <c r="D70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">For each Facility_ID, (Maturity Date - Origination Date) / 365.25 to get tenor in years.
 </v>
       </c>
       <c r="E70" t="str">
@@ -6853,66 +6931,66 @@
         <v>Y</v>
       </c>
       <c r="I70" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="J70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">For each Facility_ID, (Maturity Date - Origination Date) / 365.25 to get tenor in years.
 </v>
       </c>
       <c r="K70" t="str">
-        <v>Counterparty ID (facility)</v>
+        <v>Average Tenor (Years) (facility)</v>
       </c>
       <c r="L70" t="str">
         <v>Y</v>
       </c>
       <c r="M70" t="str">
-        <v>Raw</v>
+        <v>Avg</v>
       </c>
       <c r="N70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">Average of facility-level tenor (years) across counterparty facilities.
 </v>
       </c>
       <c r="O70" t="str">
-        <v>Counterparty ID (counterparty)</v>
+        <v>Average Tenor (Years) (counterparty)</v>
       </c>
       <c r="P70" t="str">
         <v>Y</v>
       </c>
       <c r="Q70" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="R70" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L3 desk segment.
+        <v xml:space="preserve">AVG of facility-level tenor (years) per L3 desk segment.
 </v>
       </c>
       <c r="S70" t="str">
-        <v>Counterparty ID (desk)</v>
+        <v>Average Tenor (Years) (desk)</v>
       </c>
       <c r="T70" t="str">
         <v>Y</v>
       </c>
       <c r="U70" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="V70" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L2 portfolio segment.
+        <v xml:space="preserve">AVG of facility-level tenor (years) per L2 portfolio segment.
 </v>
       </c>
       <c r="W70" t="str">
-        <v>Counterparty ID (portfolio)</v>
+        <v>Average Tenor (Years) (portfolio)</v>
       </c>
       <c r="X70" t="str">
         <v>Y</v>
       </c>
       <c r="Y70" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="Z70" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L1 business segment segment.
+        <v xml:space="preserve">AVG of facility-level tenor (years) per L1 business segment.
 </v>
       </c>
       <c r="AA70" t="str">
-        <v>Counterparty ID (business_segment)</v>
+        <v>Average Tenor (Years) (business_segment)</v>
       </c>
       <c r="AB70" t="str">
         <v/>
@@ -6920,17 +6998,17 @@
     </row>
     <row r="71" xml:space="preserve">
       <c r="A71" t="str">
-        <v>REF-005</v>
+        <v>REF-004</v>
       </c>
       <c r="B71" t="str" xml:space="preserve">
-        <v xml:space="preserve">Descriptive name of the counterparty as documented in the credit agreement. Used for reporting clarity and operational reference.
+        <v xml:space="preserve">Unique system identifier assigned to the borrower or obligor. Used for exposure aggregation and risk consolidation across the GSIB. At facility level, returns the counterparty_id linked to each facility. At upper levels, returns COUNT(DISTINCT counterparty_id) — the number of unique obligors in each organizational segment.
 </v>
       </c>
       <c r="C71" t="str">
-        <v>Counterparty Name</v>
+        <v>Counterparty ID</v>
       </c>
       <c r="D71" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read legal_name from counterparty for each facility's counterparty.
+        <v xml:space="preserve">Direct lookup of counterparty_id from facility_master for each active facility. Uses current records only (SCD2 filtered).
 </v>
       </c>
       <c r="E71" t="str">
@@ -6949,24 +7027,24 @@
         <v>Raw</v>
       </c>
       <c r="J71" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read legal_name from counterparty for each facility's counterparty.
+        <v xml:space="preserve">Direct lookup of counterparty_id from facility_master for each active facility. Uses current records only (SCD2 filtered).
 </v>
       </c>
       <c r="K71" t="str">
-        <v>Counterparty Name (facility)</v>
+        <v>Counterparty ID (facility)</v>
       </c>
       <c r="L71" t="str">
         <v>Y</v>
       </c>
       <c r="M71" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="N71" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with counterparty name per counterparty.
+        <v xml:space="preserve">Identity — returns counterparty_id for each current counterparty.
 </v>
       </c>
       <c r="O71" t="str">
-        <v>Counterparty Name (counterparty)</v>
+        <v>Counterparty ID (counterparty)</v>
       </c>
       <c r="P71" t="str">
         <v>Y</v>
@@ -6975,11 +7053,11 @@
         <v>Agg</v>
       </c>
       <c r="R71" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with counterparty name per L3 desk segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L3 desk segment — number of unique obligors in each desk.
 </v>
       </c>
       <c r="S71" t="str">
-        <v>Counterparty Name (desk)</v>
+        <v>Counterparty ID (desk)</v>
       </c>
       <c r="T71" t="str">
         <v>Y</v>
@@ -6988,11 +7066,11 @@
         <v>Agg</v>
       </c>
       <c r="V71" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with counterparty name per L2 portfolio segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L2 portfolio segment — number of unique obligors in each portfolio.
 </v>
       </c>
       <c r="W71" t="str">
-        <v>Counterparty Name (portfolio)</v>
+        <v>Counterparty ID (portfolio)</v>
       </c>
       <c r="X71" t="str">
         <v>Y</v>
@@ -7001,11 +7079,11 @@
         <v>Agg</v>
       </c>
       <c r="Z71" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with counterparty name per L1 business segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L1 business segment — number of unique obligors in each business segment.
 </v>
       </c>
       <c r="AA71" t="str">
-        <v>Counterparty Name (business_segment)</v>
+        <v>Counterparty ID (business_segment)</v>
       </c>
       <c r="AB71" t="str">
         <v/>
@@ -7013,17 +7091,17 @@
     </row>
     <row r="72" xml:space="preserve">
       <c r="A72" t="str">
-        <v>REF-006</v>
+        <v>REF-005</v>
       </c>
       <c r="B72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Country of risk or booking location. Supports geographic concentration and sovereign risk analysis.
+        <v xml:space="preserve">Legal name of the counterparty as documented in the credit agreement. At facility level, returns the counterparty_id (numeric proxy for the name since metric values are numeric). At counterparty level, identity lookup. At upper levels, COUNT(DISTINCT counterparty_id) — number of unique named obligors per organizational segment. Used for reporting clarity and operational reference across all regulatory submissions.
 </v>
       </c>
       <c r="C72" t="str">
-        <v>Country</v>
+        <v>Counterparty Name</v>
       </c>
       <c r="D72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of country_name from country_dim.
+        <v xml:space="preserve">Lookup counterparty_id from facility_master for each active facility. The numeric counterparty_id serves as proxy for the legal name (string values resolved via counterparty dimension join at display time). Uses current records only.
 </v>
       </c>
       <c r="E72" t="str">
@@ -7042,11 +7120,11 @@
         <v>Raw</v>
       </c>
       <c r="J72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of country_name from country_dim.
+        <v xml:space="preserve">Lookup counterparty_id from facility_master for each active facility. The numeric counterparty_id serves as proxy for the legal name (string values resolved via counterparty dimension join at display time). Uses current records only.
 </v>
       </c>
       <c r="K72" t="str">
-        <v>Country (facility)</v>
+        <v>Counterparty Name (facility)</v>
       </c>
       <c r="L72" t="str">
         <v>Y</v>
@@ -7055,11 +7133,11 @@
         <v>Raw</v>
       </c>
       <c r="N72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read country_name per counterparty.
+        <v xml:space="preserve">Identity — returns counterparty_id for each current counterparty. Legal name resolved via counterparty dimension join at display time.
 </v>
       </c>
       <c r="O72" t="str">
-        <v>Country (counterparty)</v>
+        <v>Counterparty Name (counterparty)</v>
       </c>
       <c r="P72" t="str">
         <v>Y</v>
@@ -7068,11 +7146,11 @@
         <v>Agg</v>
       </c>
       <c r="R72" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level country_name per L3 desk segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L3 desk segment — number of unique named obligors in each desk.
 </v>
       </c>
       <c r="S72" t="str">
-        <v>Country (desk)</v>
+        <v>Counterparty Name (desk)</v>
       </c>
       <c r="T72" t="str">
         <v>Y</v>
@@ -7081,11 +7159,11 @@
         <v>Agg</v>
       </c>
       <c r="V72" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level country_name per L2 portfolio segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L2 portfolio segment — number of unique named obligors in each portfolio.
 </v>
       </c>
       <c r="W72" t="str">
-        <v>Country (portfolio)</v>
+        <v>Counterparty Name (portfolio)</v>
       </c>
       <c r="X72" t="str">
         <v>Y</v>
@@ -7094,11 +7172,11 @@
         <v>Agg</v>
       </c>
       <c r="Z72" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level country_name per L1 business segment segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L1 business segment — number of unique named obligors in each business segment.
 </v>
       </c>
       <c r="AA72" t="str">
-        <v>Country (business_segment)</v>
+        <v>Counterparty Name (business_segment)</v>
       </c>
       <c r="AB72" t="str">
         <v/>
@@ -7106,17 +7184,17 @@
     </row>
     <row r="73" xml:space="preserve">
       <c r="A73" t="str">
-        <v>REF-007</v>
+        <v>REF-006</v>
       </c>
       <c r="B73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Unique identifier linking facility to governing credit agreement documentation.
+        <v xml:space="preserve">Country of risk derived from the counterparty's domicile. At facility level, returns a numeric country identifier (via counterparty → country_dim join path). At counterparty level, identity lookup. At desk/portfolio/segment levels, COUNT(DISTINCT country_code) — geographic diversification indicator showing the number of unique countries represented. Supports FFIEC 009 Country Exposure Report and Basel III geographic concentration analysis.
 </v>
       </c>
       <c r="C73" t="str">
-        <v>Credit Agreement ID</v>
+        <v>Country</v>
       </c>
       <c r="D73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of credit_agreement_id from credit_agreement_master.
+        <v xml:space="preserve">Lookup country for each facility via counterparty → country_dim join path. Returns counterparty_id as numeric proxy (country_name resolved at display time via dimension join). Uses current records only.
 </v>
       </c>
       <c r="E73" t="str">
@@ -7135,11 +7213,11 @@
         <v>Raw</v>
       </c>
       <c r="J73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of credit_agreement_id from credit_agreement_master.
+        <v xml:space="preserve">Lookup country for each facility via counterparty → country_dim join path. Returns counterparty_id as numeric proxy (country_name resolved at display time via dimension join). Uses current records only.
 </v>
       </c>
       <c r="K73" t="str">
-        <v>Credit Agreement ID (facility)</v>
+        <v>Country (facility)</v>
       </c>
       <c r="L73" t="str">
         <v>Y</v>
@@ -7148,11 +7226,11 @@
         <v>Raw</v>
       </c>
       <c r="N73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read credit_agreement_id per counterparty.
+        <v xml:space="preserve">Lookup country for each counterparty via country_code → country_dim join. Returns counterparty_id as numeric proxy.
 </v>
       </c>
       <c r="O73" t="str">
-        <v>Credit Agreement ID (counterparty)</v>
+        <v>Country (counterparty)</v>
       </c>
       <c r="P73" t="str">
         <v>Y</v>
@@ -7161,11 +7239,11 @@
         <v>Agg</v>
       </c>
       <c r="R73" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level credit_agreement_id per L3 desk segment.
+        <v xml:space="preserve">COUNT(DISTINCT country_code) per L3 desk segment — number of unique countries represented, a geographic diversification indicator.
 </v>
       </c>
       <c r="S73" t="str">
-        <v>Credit Agreement ID (desk)</v>
+        <v>Country (desk)</v>
       </c>
       <c r="T73" t="str">
         <v>Y</v>
@@ -7174,11 +7252,11 @@
         <v>Agg</v>
       </c>
       <c r="V73" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level credit_agreement_id per L2 portfolio segment.
+        <v xml:space="preserve">COUNT(DISTINCT country_code) per L2 portfolio segment — number of unique countries represented in each portfolio.
 </v>
       </c>
       <c r="W73" t="str">
-        <v>Credit Agreement ID (portfolio)</v>
+        <v>Country (portfolio)</v>
       </c>
       <c r="X73" t="str">
         <v>Y</v>
@@ -7187,11 +7265,11 @@
         <v>Agg</v>
       </c>
       <c r="Z73" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level credit_agreement_id per L1 business segment segment.
+        <v xml:space="preserve">COUNT(DISTINCT country_code) per L1 business segment — geographic diversification at the highest organizational level.
 </v>
       </c>
       <c r="AA73" t="str">
-        <v>Credit Agreement ID (business_segment)</v>
+        <v>Country (business_segment)</v>
       </c>
       <c r="AB73" t="str">
         <v/>
@@ -7199,17 +7277,17 @@
     </row>
     <row r="74" xml:space="preserve">
       <c r="A74" t="str">
-        <v>REF-008</v>
+        <v>REF-007</v>
       </c>
       <c r="B74" t="str" xml:space="preserve">
-        <v xml:space="preserve">Number of calendar days remaining until contractual maturity, sourced from the facility exposure snapshot. At aggregate levels, reports the minimum (nearest) maturity across constituent facilities to highlight the most imminent rollover risk and refinancing pressure.
+        <v xml:space="preserve">Unique identifier linking each facility to its governing credit agreement documentation. Used for contract tracking, facility-to-agreement linkage, and regulatory reporting. At counterparty level, returns count of distinct credit agreements per borrower.
 </v>
       </c>
       <c r="C74" t="str">
-        <v>Days Until Maturity</v>
+        <v>Credit Agreement ID</v>
       </c>
       <c r="D74" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read days_until_maturity from facility_exposure_snapshot for each active, current facility as of the reporting date.
+        <v xml:space="preserve">Direct lookup of credit_agreement_id for each active facility via facility_master joined to credit_agreement_master.
 </v>
       </c>
       <c r="E74" t="str">
@@ -7228,11 +7306,11 @@
         <v>Raw</v>
       </c>
       <c r="J74" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read days_until_maturity from facility_exposure_snapshot for each active, current facility as of the reporting date.
+        <v xml:space="preserve">Direct lookup of credit_agreement_id for each active facility via facility_master joined to credit_agreement_master.
 </v>
       </c>
       <c r="K74" t="str">
-        <v>Days Until Maturity (facility)</v>
+        <v>Credit Agreement ID (facility)</v>
       </c>
       <c r="L74" t="str">
         <v>Y</v>
@@ -7241,11 +7319,11 @@
         <v>Agg</v>
       </c>
       <c r="N74" t="str" xml:space="preserve">
-        <v xml:space="preserve">Minimum days_until_maturity across all facilities per counterparty — nearest maturity indicates most urgent rollover risk.
+        <v xml:space="preserve">Count of distinct credit agreements per counterparty. Provides visibility into borrower complexity and multi-agreement relationships.
 </v>
       </c>
       <c r="O74" t="str">
-        <v>Days Until Maturity (counterparty)</v>
+        <v>Credit Agreement ID (counterparty)</v>
       </c>
       <c r="P74" t="str">
         <v>Y</v>
@@ -7254,11 +7332,11 @@
         <v>Agg</v>
       </c>
       <c r="R74" t="str" xml:space="preserve">
-        <v xml:space="preserve">Minimum days_until_maturity across all facilities per L3 desk segment — nearest maturity in the segment.
+        <v xml:space="preserve">Count of distinct credit agreements per L3 desk segment via enterprise_business_taxonomy.
 </v>
       </c>
       <c r="S74" t="str">
-        <v>Days Until Maturity (desk)</v>
+        <v>Credit Agreement ID (desk)</v>
       </c>
       <c r="T74" t="str">
         <v>Y</v>
@@ -7267,11 +7345,11 @@
         <v>Agg</v>
       </c>
       <c r="V74" t="str" xml:space="preserve">
-        <v xml:space="preserve">Minimum days_until_maturity across all facilities per L2 portfolio segment.
+        <v xml:space="preserve">Count of distinct credit agreements per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
 </v>
       </c>
       <c r="W74" t="str">
-        <v>Days Until Maturity (portfolio)</v>
+        <v>Credit Agreement ID (portfolio)</v>
       </c>
       <c r="X74" t="str">
         <v>Y</v>
@@ -7280,11 +7358,11 @@
         <v>Agg</v>
       </c>
       <c r="Z74" t="str" xml:space="preserve">
-        <v xml:space="preserve">Minimum days_until_maturity across all facilities per L1 business segment.
+        <v xml:space="preserve">Count of distinct credit agreements per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
 </v>
       </c>
       <c r="AA74" t="str">
-        <v>Days Until Maturity (business_segment)</v>
+        <v>Credit Agreement ID (business_segment)</v>
       </c>
       <c r="AB74" t="str">
         <v/>
@@ -7292,17 +7370,17 @@
     </row>
     <row r="75" xml:space="preserve">
       <c r="A75" t="str">
-        <v>REF-009</v>
+        <v>REF-008</v>
       </c>
       <c r="B75" t="str" xml:space="preserve">
-        <v xml:space="preserve">Date on which loan or contract became legally effective.
+        <v xml:space="preserve">Number of calendar days remaining until contractual maturity, sourced from the facility exposure snapshot. At aggregate levels, reports the minimum (nearest) maturity across constituent facilities to highlight the most imminent rollover risk and refinancing pressure.
 </v>
       </c>
       <c r="C75" t="str">
-        <v>Contract Origination Date</v>
+        <v>Days Until Maturity</v>
       </c>
       <c r="D75" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of origination_date from facility_master.
+        <v xml:space="preserve">Read days_until_maturity from facility_exposure_snapshot for each active, current facility as of the reporting date.
 </v>
       </c>
       <c r="E75" t="str">
@@ -7321,11 +7399,11 @@
         <v>Raw</v>
       </c>
       <c r="J75" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of origination_date from facility_master.
+        <v xml:space="preserve">Read days_until_maturity from facility_exposure_snapshot for each active, current facility as of the reporting date.
 </v>
       </c>
       <c r="K75" t="str">
-        <v>Contract Origination Date (facility)</v>
+        <v>Days Until Maturity (facility)</v>
       </c>
       <c r="L75" t="str">
         <v>Y</v>
@@ -7334,11 +7412,11 @@
         <v>Agg</v>
       </c>
       <c r="N75" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level origination_date) per counterparty.
+        <v xml:space="preserve">Minimum days_until_maturity across all facilities per counterparty — nearest maturity indicates most urgent rollover risk.
 </v>
       </c>
       <c r="O75" t="str">
-        <v>Contract Origination Date (counterparty)</v>
+        <v>Days Until Maturity (counterparty)</v>
       </c>
       <c r="P75" t="str">
         <v>Y</v>
@@ -7347,11 +7425,11 @@
         <v>Agg</v>
       </c>
       <c r="R75" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level origination_date per L3 desk segment.
+        <v xml:space="preserve">Minimum days_until_maturity across all facilities per L3 desk segment — nearest maturity in the segment.
 </v>
       </c>
       <c r="S75" t="str">
-        <v>Contract Origination Date (desk)</v>
+        <v>Days Until Maturity (desk)</v>
       </c>
       <c r="T75" t="str">
         <v>Y</v>
@@ -7360,11 +7438,11 @@
         <v>Agg</v>
       </c>
       <c r="V75" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level origination_date per L2 portfolio segment.
+        <v xml:space="preserve">Minimum days_until_maturity across all facilities per L2 portfolio segment.
 </v>
       </c>
       <c r="W75" t="str">
-        <v>Contract Origination Date (portfolio)</v>
+        <v>Days Until Maturity (portfolio)</v>
       </c>
       <c r="X75" t="str">
         <v>Y</v>
@@ -7373,11 +7451,11 @@
         <v>Agg</v>
       </c>
       <c r="Z75" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level origination_date per L1 business segment segment.
+        <v xml:space="preserve">Minimum days_until_maturity across all facilities per L1 business segment.
 </v>
       </c>
       <c r="AA75" t="str">
-        <v>Contract Origination Date (business_segment)</v>
+        <v>Days Until Maturity (business_segment)</v>
       </c>
       <c r="AB75" t="str">
         <v/>
@@ -7385,17 +7463,18 @@
     </row>
     <row r="76" xml:space="preserve">
       <c r="A76" t="str">
-        <v>REF-010</v>
+        <v>REF-009</v>
       </c>
       <c r="B76" t="str" xml:space="preserve">
-        <v xml:space="preserve">Unique identifier assigned to the lending facility within enterprise systems. Used to aggregate balances, risk metrics, pricing data, and contractual attributes at the facility level.
+        <v xml:space="preserve">Date on which loan or contract became legally effective. Sourced directly from facility_master. At aggregate levels, returns the earliest origination date (MIN) across constituent facilities — indicating the oldest vintage in the book. Key contract lifecycle tracking attribute for vintage analysis and portfolio seasoning assessment.
 </v>
       </c>
       <c r="C76" t="str">
-        <v>Facility ID</v>
+        <v>Contract Origination Date</v>
       </c>
       <c r="D76" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of facility_id from facility_master.
+        <v xml:space="preserve">Direct lookup of origination_date from facility_master.
+Ingredients: origination_date (L2 facility_master — raw field)
 </v>
       </c>
       <c r="E76" t="str">
@@ -7414,24 +7493,28 @@
         <v>Raw</v>
       </c>
       <c r="J76" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of facility_id from facility_master.
+        <v xml:space="preserve">Direct lookup of origination_date from facility_master.
+Ingredients: origination_date (L2 facility_master — raw field)
 </v>
       </c>
       <c r="K76" t="str">
-        <v>Facility ID (facility)</v>
+        <v>Contract Origination Date (facility)</v>
       </c>
       <c r="L76" t="str">
         <v>Y</v>
       </c>
       <c r="M76" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="N76" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read facility_id per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD origination_date from l2.facility_master for all active facilities
+  2. COMPUTE MIN(origination_date) — earliest contract vintage
+Indicates the oldest banking relationship tenure for this counterparty.
 </v>
       </c>
       <c r="O76" t="str">
-        <v>Facility ID (counterparty)</v>
+        <v>Contract Origination Date (counterparty)</v>
       </c>
       <c r="P76" t="str">
         <v>Y</v>
@@ -7440,11 +7523,14 @@
         <v>Agg</v>
       </c>
       <c r="R76" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_id per L3 desk segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOAD origination_date from l2.facility_master
+  2. JOIN l1.enterprise_business_taxonomy on lob_segment_id
+  3. COMPUTE MIN(origination_date) — earliest vintage in desk book
 </v>
       </c>
       <c r="S76" t="str">
-        <v>Facility ID (desk)</v>
+        <v>Contract Origination Date (desk)</v>
       </c>
       <c r="T76" t="str">
         <v>Y</v>
@@ -7453,11 +7539,13 @@
         <v>Agg</v>
       </c>
       <c r="V76" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_id per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. COMPUTE MIN(origination_date) — earliest vintage in portfolio
 </v>
       </c>
       <c r="W76" t="str">
-        <v>Facility ID (portfolio)</v>
+        <v>Contract Origination Date (portfolio)</v>
       </c>
       <c r="X76" t="str">
         <v>Y</v>
@@ -7466,11 +7554,13 @@
         <v>Agg</v>
       </c>
       <c r="Z76" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_id per L1 business segment segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. COMPUTE MIN(origination_date) — earliest vintage in business segment
 </v>
       </c>
       <c r="AA76" t="str">
-        <v>Facility ID (business_segment)</v>
+        <v>Contract Origination Date (business_segment)</v>
       </c>
       <c r="AB76" t="str">
         <v/>
@@ -7478,17 +7568,17 @@
     </row>
     <row r="77" xml:space="preserve">
       <c r="A77" t="str">
-        <v>REF-011</v>
+        <v>REF-010</v>
       </c>
       <c r="B77" t="str" xml:space="preserve">
-        <v xml:space="preserve">Descriptive name of the facility as documented in the credit agreement. Used for reporting clarity and operational reference.
+        <v xml:space="preserve">Unique identifier assigned to the lending facility within enterprise systems. Used to aggregate balances, risk metrics, pricing data, and contractual attributes at the facility level.
 </v>
       </c>
       <c r="C77" t="str">
-        <v>Facility Name</v>
+        <v>Facility ID</v>
       </c>
       <c r="D77" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of facility_name from facility_master.
+        <v xml:space="preserve">Direct lookup of facility_id from facility_master.
 </v>
       </c>
       <c r="E77" t="str">
@@ -7507,11 +7597,11 @@
         <v>Raw</v>
       </c>
       <c r="J77" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of facility_name from facility_master.
+        <v xml:space="preserve">Direct lookup of facility_id from facility_master.
 </v>
       </c>
       <c r="K77" t="str">
-        <v>Facility Name (facility)</v>
+        <v>Facility ID (facility)</v>
       </c>
       <c r="L77" t="str">
         <v>Y</v>
@@ -7520,11 +7610,11 @@
         <v>Raw</v>
       </c>
       <c r="N77" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read facility_name per counterparty.
+        <v xml:space="preserve">Read facility_id per counterparty.
 </v>
       </c>
       <c r="O77" t="str">
-        <v>Facility Name (counterparty)</v>
+        <v>Facility ID (counterparty)</v>
       </c>
       <c r="P77" t="str">
         <v>Y</v>
@@ -7533,11 +7623,11 @@
         <v>Agg</v>
       </c>
       <c r="R77" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_name per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level facility_id per L3 desk segment.
 </v>
       </c>
       <c r="S77" t="str">
-        <v>Facility Name (desk)</v>
+        <v>Facility ID (desk)</v>
       </c>
       <c r="T77" t="str">
         <v>Y</v>
@@ -7546,11 +7636,11 @@
         <v>Agg</v>
       </c>
       <c r="V77" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_name per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level facility_id per L2 portfolio segment.
 </v>
       </c>
       <c r="W77" t="str">
-        <v>Facility Name (portfolio)</v>
+        <v>Facility ID (portfolio)</v>
       </c>
       <c r="X77" t="str">
         <v>Y</v>
@@ -7559,11 +7649,11 @@
         <v>Agg</v>
       </c>
       <c r="Z77" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_name per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level facility_id per L1 business segment segment.
 </v>
       </c>
       <c r="AA77" t="str">
-        <v>Facility Name (business_segment)</v>
+        <v>Facility ID (business_segment)</v>
       </c>
       <c r="AB77" t="str">
         <v/>
@@ -7571,17 +7661,17 @@
     </row>
     <row r="78" xml:space="preserve">
       <c r="A78" t="str">
-        <v>REF-012</v>
+        <v>REF-011</v>
       </c>
       <c r="B78" t="str" xml:space="preserve">
-        <v xml:space="preserve">Type of credit facility (e.g., Term Loan, Revolver, Letter of Credit). Enables product-level segmentation, risk concentration analysis, and performance benchmarking.
+        <v xml:space="preserve">Descriptive name of the facility as documented in the credit agreement. Used for reporting clarity and operational reference.
 </v>
       </c>
       <c r="C78" t="str">
-        <v>Facility Type</v>
+        <v>Facility Name</v>
       </c>
       <c r="D78" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read facility_type from facility_exposure_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Direct lookup of facility_name from facility_master.
 </v>
       </c>
       <c r="E78" t="str">
@@ -7600,24 +7690,24 @@
         <v>Raw</v>
       </c>
       <c r="J78" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read facility_type from facility_exposure_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Direct lookup of facility_name from facility_master.
 </v>
       </c>
       <c r="K78" t="str">
-        <v>Facility Type (facility)</v>
+        <v>Facility Name (facility)</v>
       </c>
       <c r="L78" t="str">
         <v>Y</v>
       </c>
       <c r="M78" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="N78" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level facility_type) per counterparty.
+        <v xml:space="preserve">Read facility_name per counterparty.
 </v>
       </c>
       <c r="O78" t="str">
-        <v>Facility Type (counterparty)</v>
+        <v>Facility Name (counterparty)</v>
       </c>
       <c r="P78" t="str">
         <v>Y</v>
@@ -7626,11 +7716,11 @@
         <v>Agg</v>
       </c>
       <c r="R78" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_type per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level facility_name per L3 desk segment.
 </v>
       </c>
       <c r="S78" t="str">
-        <v>Facility Type (desk)</v>
+        <v>Facility Name (desk)</v>
       </c>
       <c r="T78" t="str">
         <v>Y</v>
@@ -7639,11 +7729,11 @@
         <v>Agg</v>
       </c>
       <c r="V78" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_type per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level facility_name per L2 portfolio segment.
 </v>
       </c>
       <c r="W78" t="str">
-        <v>Facility Type (portfolio)</v>
+        <v>Facility Name (portfolio)</v>
       </c>
       <c r="X78" t="str">
         <v>Y</v>
@@ -7652,11 +7742,11 @@
         <v>Agg</v>
       </c>
       <c r="Z78" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_type per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level facility_name per L1 business segment segment.
 </v>
       </c>
       <c r="AA78" t="str">
-        <v>Facility Type (business_segment)</v>
+        <v>Facility Name (business_segment)</v>
       </c>
       <c r="AB78" t="str">
         <v/>
@@ -7664,17 +7754,17 @@
     </row>
     <row r="79" xml:space="preserve">
       <c r="A79" t="str">
-        <v>REF-013</v>
+        <v>REF-012</v>
       </c>
       <c r="B79" t="str" xml:space="preserve">
-        <v xml:space="preserve">A classification used for reporting purposes in the FR 2590 regulatory report pertaining to financial institutions' credit exposures.
+        <v xml:space="preserve">Type of credit facility (e.g., Term Loan, Revolver, Letter of Credit). Enables product-level segmentation, risk concentration analysis, and performance benchmarking.
 </v>
       </c>
       <c r="C79" t="str">
-        <v>FR2590 Category</v>
+        <v>Facility Type</v>
       </c>
       <c r="D79" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated fr2590_category_code per facility.
+        <v xml:space="preserve">Read facility_type from facility_exposure_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="E79" t="str">
@@ -7690,14 +7780,14 @@
         <v>Y</v>
       </c>
       <c r="I79" t="str">
-        <v>Calc</v>
+        <v>Raw</v>
       </c>
       <c r="J79" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated fr2590_category_code per facility.
+        <v xml:space="preserve">Read facility_type from facility_exposure_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="K79" t="str">
-        <v>FR2590 Category (facility)</v>
+        <v>Facility Type (facility)</v>
       </c>
       <c r="L79" t="str">
         <v>Y</v>
@@ -7706,11 +7796,11 @@
         <v>Agg</v>
       </c>
       <c r="N79" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level fr2590_category_code per counterparty.
+        <v xml:space="preserve">SUM(facility-level facility_type) per counterparty.
 </v>
       </c>
       <c r="O79" t="str">
-        <v>FR2590 Category (counterparty)</v>
+        <v>Facility Type (counterparty)</v>
       </c>
       <c r="P79" t="str">
         <v>Y</v>
@@ -7719,11 +7809,11 @@
         <v>Agg</v>
       </c>
       <c r="R79" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level fr2590_category_code per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level facility_type per L3 desk segment.
 </v>
       </c>
       <c r="S79" t="str">
-        <v>FR2590 Category (desk)</v>
+        <v>Facility Type (desk)</v>
       </c>
       <c r="T79" t="str">
         <v>Y</v>
@@ -7732,11 +7822,11 @@
         <v>Agg</v>
       </c>
       <c r="V79" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level fr2590_category_code per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level facility_type per L2 portfolio segment.
 </v>
       </c>
       <c r="W79" t="str">
-        <v>FR2590 Category (portfolio)</v>
+        <v>Facility Type (portfolio)</v>
       </c>
       <c r="X79" t="str">
         <v>Y</v>
@@ -7745,11 +7835,11 @@
         <v>Agg</v>
       </c>
       <c r="Z79" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level fr2590_category_code per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level facility_type per L1 business segment segment.
 </v>
       </c>
       <c r="AA79" t="str">
-        <v>FR2590 Category (business_segment)</v>
+        <v>Facility Type (business_segment)</v>
       </c>
       <c r="AB79" t="str">
         <v/>
@@ -7757,17 +7847,17 @@
     </row>
     <row r="80" xml:space="preserve">
       <c r="A80" t="str">
-        <v>REF-014</v>
+        <v>REF-013</v>
       </c>
       <c r="B80" t="str" xml:space="preserve">
-        <v xml:space="preserve">Indicator that facility or exposure is active and not closed, canceled or matured. Portfolio KPI (% Active Facilities) measures ongoing credit exposure footprint.
+        <v xml:space="preserve">FR 2590 regulatory classification for each facility exposure. Reads the fr2590_category_code from the facility exposure snapshot and joins to the fr2590_category_dim reference table to return the human-readable category name. Used for FR 2590 supervisory reporting and exposure segmentation by product type. Facility-level only — categorical values cannot be meaningfully aggregated to higher organizational levels.
 </v>
       </c>
       <c r="C80" t="str">
-        <v>Active</v>
+        <v>FR2590 Category</v>
       </c>
       <c r="D80" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of is_active_flag from facility_master.
+        <v xml:space="preserve">For each facility, read the fr2590_category_code from the latest facility_exposure_snapshot, then join to fr2590_category_dim to return the human-readable category_name. Uses MAX(category_name) to handle any duplicate exposure rows per facility on the same reporting date.
 </v>
       </c>
       <c r="E80" t="str">
@@ -7783,66 +7873,66 @@
         <v>Y</v>
       </c>
       <c r="I80" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="J80" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of is_active_flag from facility_master.
+        <v xml:space="preserve">For each facility, read the fr2590_category_code from the latest facility_exposure_snapshot, then join to fr2590_category_dim to return the human-readable category_name. Uses MAX(category_name) to handle any duplicate exposure rows per facility on the same reporting date.
 </v>
       </c>
       <c r="K80" t="str">
-        <v>Active (facility)</v>
+        <v>FR2590 Category (facility)</v>
       </c>
       <c r="L80" t="str">
         <v>Y</v>
       </c>
       <c r="M80" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="N80" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read is_active_flag per counterparty.
+        <v xml:space="preserve">Not applicable — FR2590 category is a per-facility categorical classification that cannot be meaningfully aggregated to counterparty level. Use facility-level drill-down for category distribution.
 </v>
       </c>
       <c r="O80" t="str">
-        <v>Active (counterparty)</v>
+        <v>FR2590 Category (counterparty)</v>
       </c>
       <c r="P80" t="str">
         <v>Y</v>
       </c>
       <c r="Q80" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R80" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level is_active_flag per L3 desk segment.
+        <v xml:space="preserve">Not applicable — FR2590 category is a per-facility categorical classification. Desk-level analysis should use facility-level data grouped by FR2590 category as a dimension.
 </v>
       </c>
       <c r="S80" t="str">
-        <v>Active (desk)</v>
+        <v>FR2590 Category (desk)</v>
       </c>
       <c r="T80" t="str">
         <v>Y</v>
       </c>
       <c r="U80" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V80" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level is_active_flag per L2 portfolio segment.
+        <v xml:space="preserve">Not applicable — FR2590 category is a per-facility categorical classification. Portfolio-level reporting uses FR2590 as a grouping dimension, not as an aggregated metric.
 </v>
       </c>
       <c r="W80" t="str">
-        <v>Active (portfolio)</v>
+        <v>FR2590 Category (portfolio)</v>
       </c>
       <c r="X80" t="str">
         <v>Y</v>
       </c>
       <c r="Y80" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z80" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level is_active_flag per L1 business segment segment.
+        <v xml:space="preserve">Not applicable — FR2590 category is a per-facility categorical classification. Business segment reporting uses FR2590 as a grouping dimension, not as an aggregated metric.
 </v>
       </c>
       <c r="AA80" t="str">
-        <v>Active (business_segment)</v>
+        <v>FR2590 Category (business_segment)</v>
       </c>
       <c r="AB80" t="str">
         <v/>
@@ -7850,17 +7940,17 @@
     </row>
     <row r="81" xml:space="preserve">
       <c r="A81" t="str">
-        <v>REF-015</v>
+        <v>REF-014</v>
       </c>
       <c r="B81" t="str" xml:space="preserve">
-        <v xml:space="preserve">Boolean indicator to depict when facility is syndicated across multiple issuing banks. Portfolio KPI (% Syndicated Facilities) provides insight into risk distribution across lenders.
+        <v xml:space="preserve">Indicator that facility or exposure is active and not closed, canceled or matured. Portfolio KPI (% Active Facilities) measures ongoing credit exposure footprint.
 </v>
       </c>
       <c r="C81" t="str">
-        <v>Syndicated Deal Flag</v>
+        <v>Active</v>
       </c>
       <c r="D81" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated is_syndicated_flag per facility.
+        <v xml:space="preserve">Direct lookup of is_active_flag from facility_master.
 </v>
       </c>
       <c r="E81" t="str">
@@ -7876,27 +7966,27 @@
         <v>Y</v>
       </c>
       <c r="I81" t="str">
-        <v>Calc</v>
+        <v>Raw</v>
       </c>
       <c r="J81" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated is_syndicated_flag per facility.
+        <v xml:space="preserve">Direct lookup of is_active_flag from facility_master.
 </v>
       </c>
       <c r="K81" t="str">
-        <v>Syndicated Deal Flag (facility)</v>
+        <v>Active (facility)</v>
       </c>
       <c r="L81" t="str">
         <v>Y</v>
       </c>
       <c r="M81" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="N81" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level is_syndicated_flag) per counterparty.
+        <v xml:space="preserve">Read is_active_flag per counterparty.
 </v>
       </c>
       <c r="O81" t="str">
-        <v>Syndicated Deal Flag (counterparty)</v>
+        <v>Active (counterparty)</v>
       </c>
       <c r="P81" t="str">
         <v>Y</v>
@@ -7905,11 +7995,11 @@
         <v>Agg</v>
       </c>
       <c r="R81" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level is_syndicated_flag per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level is_active_flag per L3 desk segment.
 </v>
       </c>
       <c r="S81" t="str">
-        <v>Syndicated Deal Flag (desk)</v>
+        <v>Active (desk)</v>
       </c>
       <c r="T81" t="str">
         <v>Y</v>
@@ -7918,11 +8008,11 @@
         <v>Agg</v>
       </c>
       <c r="V81" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level is_syndicated_flag per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level is_active_flag per L2 portfolio segment.
 </v>
       </c>
       <c r="W81" t="str">
-        <v>Syndicated Deal Flag (portfolio)</v>
+        <v>Active (portfolio)</v>
       </c>
       <c r="X81" t="str">
         <v>Y</v>
@@ -7931,11 +8021,11 @@
         <v>Agg</v>
       </c>
       <c r="Z81" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level is_syndicated_flag per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level is_active_flag per L1 business segment segment.
 </v>
       </c>
       <c r="AA81" t="str">
-        <v>Syndicated Deal Flag (business_segment)</v>
+        <v>Active (business_segment)</v>
       </c>
       <c r="AB81" t="str">
         <v/>
@@ -7943,17 +8033,17 @@
     </row>
     <row r="82" xml:space="preserve">
       <c r="A82" t="str">
-        <v>REF-016</v>
+        <v>REF-015</v>
       </c>
       <c r="B82" t="str" xml:space="preserve">
-        <v xml:space="preserve">Legal entity booking or owning the exposure. Critical for regulatory capital and entity-level reporting.
+        <v xml:space="preserve">Boolean indicator to depict when facility is syndicated across multiple issuing banks. Portfolio KPI (% Syndicated Facilities) provides insight into risk distribution across lenders.
 </v>
       </c>
       <c r="C82" t="str">
-        <v>Legal Entity</v>
+        <v>Syndicated Deal Flag</v>
       </c>
       <c r="D82" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of legal_name from counterparty.
+        <v xml:space="preserve">Calculated is_syndicated_flag per facility.
 </v>
       </c>
       <c r="E82" t="str">
@@ -7969,27 +8059,27 @@
         <v>Y</v>
       </c>
       <c r="I82" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="J82" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of legal_name from counterparty.
+        <v xml:space="preserve">Calculated is_syndicated_flag per facility.
 </v>
       </c>
       <c r="K82" t="str">
-        <v>Legal Entity (facility)</v>
+        <v>Syndicated Deal Flag (facility)</v>
       </c>
       <c r="L82" t="str">
         <v>Y</v>
       </c>
       <c r="M82" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="N82" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of legal_name from counterparty.
+        <v xml:space="preserve">SUM(facility-level is_syndicated_flag) per counterparty.
 </v>
       </c>
       <c r="O82" t="str">
-        <v>Legal Entity (counterparty)</v>
+        <v>Syndicated Deal Flag (counterparty)</v>
       </c>
       <c r="P82" t="str">
         <v>Y</v>
@@ -7998,11 +8088,11 @@
         <v>Agg</v>
       </c>
       <c r="R82" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level legal_name per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level is_syndicated_flag per L3 desk segment.
 </v>
       </c>
       <c r="S82" t="str">
-        <v>Legal Entity (desk)</v>
+        <v>Syndicated Deal Flag (desk)</v>
       </c>
       <c r="T82" t="str">
         <v>Y</v>
@@ -8011,11 +8101,11 @@
         <v>Agg</v>
       </c>
       <c r="V82" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level legal_name per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level is_syndicated_flag per L2 portfolio segment.
 </v>
       </c>
       <c r="W82" t="str">
-        <v>Legal Entity (portfolio)</v>
+        <v>Syndicated Deal Flag (portfolio)</v>
       </c>
       <c r="X82" t="str">
         <v>Y</v>
@@ -8024,11 +8114,11 @@
         <v>Agg</v>
       </c>
       <c r="Z82" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level legal_name per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level is_syndicated_flag per L1 business segment segment.
 </v>
       </c>
       <c r="AA82" t="str">
-        <v>Legal Entity (business_segment)</v>
+        <v>Syndicated Deal Flag (business_segment)</v>
       </c>
       <c r="AB82" t="str">
         <v/>
@@ -8036,17 +8126,17 @@
     </row>
     <row r="83" xml:space="preserve">
       <c r="A83" t="str">
-        <v>REF-017</v>
+        <v>REF-016</v>
       </c>
       <c r="B83" t="str" xml:space="preserve">
-        <v xml:space="preserve">Unique identifier assigned to legal entity in enterprise systems.
+        <v xml:space="preserve">Legal entity booking or owning the exposure. Critical for regulatory capital and entity-level reporting.
 </v>
       </c>
       <c r="C83" t="str">
-        <v>Legal Entity ID</v>
+        <v>Legal Entity</v>
       </c>
       <c r="D83" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read legal_entity_id from facility_exposure_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Direct lookup of legal_name from counterparty.
 </v>
       </c>
       <c r="E83" t="str">
@@ -8065,11 +8155,11 @@
         <v>Raw</v>
       </c>
       <c r="J83" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read legal_entity_id from facility_exposure_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Direct lookup of legal_name from counterparty.
 </v>
       </c>
       <c r="K83" t="str">
-        <v>Legal Entity ID (facility)</v>
+        <v>Legal Entity (facility)</v>
       </c>
       <c r="L83" t="str">
         <v>Y</v>
@@ -8078,11 +8168,11 @@
         <v>Raw</v>
       </c>
       <c r="N83" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read legal_entity_id per counterparty.
+        <v xml:space="preserve">Direct lookup of legal_name from counterparty.
 </v>
       </c>
       <c r="O83" t="str">
-        <v>Legal Entity ID (counterparty)</v>
+        <v>Legal Entity (counterparty)</v>
       </c>
       <c r="P83" t="str">
         <v>Y</v>
@@ -8091,11 +8181,11 @@
         <v>Agg</v>
       </c>
       <c r="R83" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level legal_entity_id per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level legal_name per L3 desk segment.
 </v>
       </c>
       <c r="S83" t="str">
-        <v>Legal Entity ID (desk)</v>
+        <v>Legal Entity (desk)</v>
       </c>
       <c r="T83" t="str">
         <v>Y</v>
@@ -8104,11 +8194,11 @@
         <v>Agg</v>
       </c>
       <c r="V83" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level legal_entity_id per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level legal_name per L2 portfolio segment.
 </v>
       </c>
       <c r="W83" t="str">
-        <v>Legal Entity ID (portfolio)</v>
+        <v>Legal Entity (portfolio)</v>
       </c>
       <c r="X83" t="str">
         <v>Y</v>
@@ -8117,11 +8207,11 @@
         <v>Agg</v>
       </c>
       <c r="Z83" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level legal_entity_id per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level legal_name per L1 business segment segment.
 </v>
       </c>
       <c r="AA83" t="str">
-        <v>Legal Entity ID (business_segment)</v>
+        <v>Legal Entity (business_segment)</v>
       </c>
       <c r="AB83" t="str">
         <v/>
@@ -8129,17 +8219,17 @@
     </row>
     <row r="84" xml:space="preserve">
       <c r="A84" t="str">
-        <v>REF-018</v>
+        <v>REF-017</v>
       </c>
       <c r="B84" t="str" xml:space="preserve">
-        <v xml:space="preserve">Line of Business classification associated with exposure.
+        <v xml:space="preserve">Unique identifier assigned to legal entity in enterprise systems.
 </v>
       </c>
       <c r="C84" t="str">
-        <v>Line of Business Level Name</v>
+        <v>Legal Entity ID</v>
       </c>
       <c r="D84" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
+        <v xml:space="preserve">Read legal_entity_id from facility_exposure_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="E84" t="str">
@@ -8158,11 +8248,11 @@
         <v>Raw</v>
       </c>
       <c r="J84" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
+        <v xml:space="preserve">Read legal_entity_id from facility_exposure_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="K84" t="str">
-        <v>Line of Business Level Name (facility)</v>
+        <v>Legal Entity ID (facility)</v>
       </c>
       <c r="L84" t="str">
         <v>Y</v>
@@ -8171,11 +8261,11 @@
         <v>Raw</v>
       </c>
       <c r="N84" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read parent per counterparty.
+        <v xml:space="preserve">Read legal_entity_id per counterparty.
 </v>
       </c>
       <c r="O84" t="str">
-        <v>Line of Business Level Name (counterparty)</v>
+        <v>Legal Entity ID (counterparty)</v>
       </c>
       <c r="P84" t="str">
         <v>Y</v>
@@ -8184,11 +8274,11 @@
         <v>Agg</v>
       </c>
       <c r="R84" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level parent per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level legal_entity_id per L3 desk segment.
 </v>
       </c>
       <c r="S84" t="str">
-        <v>Line of Business Level Name (desk)</v>
+        <v>Legal Entity ID (desk)</v>
       </c>
       <c r="T84" t="str">
         <v>Y</v>
@@ -8197,11 +8287,11 @@
         <v>Agg</v>
       </c>
       <c r="V84" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level parent per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level legal_entity_id per L2 portfolio segment.
 </v>
       </c>
       <c r="W84" t="str">
-        <v>Line of Business Level Name (portfolio)</v>
+        <v>Legal Entity ID (portfolio)</v>
       </c>
       <c r="X84" t="str">
         <v>Y</v>
@@ -8210,11 +8300,11 @@
         <v>Agg</v>
       </c>
       <c r="Z84" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level parent per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level legal_entity_id per L1 business segment segment.
 </v>
       </c>
       <c r="AA84" t="str">
-        <v>Line of Business Level Name (business_segment)</v>
+        <v>Legal Entity ID (business_segment)</v>
       </c>
       <c r="AB84" t="str">
         <v/>
@@ -8222,14 +8312,14 @@
     </row>
     <row r="85" xml:space="preserve">
       <c r="A85" t="str">
-        <v>REF-019</v>
+        <v>REF-018</v>
       </c>
       <c r="B85" t="str" xml:space="preserve">
-        <v xml:space="preserve">Level 1 Line of Business hierarchy. Enables top-level organizational risk aggregation, representing the Department (e.g. Commercial Real Estate, Corporate Banking)
+        <v xml:space="preserve">Line of Business classification associated with exposure.
 </v>
       </c>
       <c r="C85" t="str">
-        <v>Line of Business  L1</v>
+        <v>Line of Business Level Name</v>
       </c>
       <c r="D85" t="str" xml:space="preserve">
         <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
@@ -8255,7 +8345,7 @@
 </v>
       </c>
       <c r="K85" t="str">
-        <v>Line of Business  L1 (facility)</v>
+        <v>Line of Business Level Name (facility)</v>
       </c>
       <c r="L85" t="str">
         <v>Y</v>
@@ -8268,7 +8358,7 @@
 </v>
       </c>
       <c r="O85" t="str">
-        <v>Line of Business  L1 (counterparty)</v>
+        <v>Line of Business Level Name (counterparty)</v>
       </c>
       <c r="P85" t="str">
         <v>Y</v>
@@ -8281,7 +8371,7 @@
 </v>
       </c>
       <c r="S85" t="str">
-        <v>Line of Business  L1 (desk)</v>
+        <v>Line of Business Level Name (desk)</v>
       </c>
       <c r="T85" t="str">
         <v>Y</v>
@@ -8294,7 +8384,7 @@
 </v>
       </c>
       <c r="W85" t="str">
-        <v>Line of Business  L1 (portfolio)</v>
+        <v>Line of Business Level Name (portfolio)</v>
       </c>
       <c r="X85" t="str">
         <v>Y</v>
@@ -8307,7 +8397,7 @@
 </v>
       </c>
       <c r="AA85" t="str">
-        <v>Line of Business  L1 (business_segment)</v>
+        <v>Line of Business Level Name (business_segment)</v>
       </c>
       <c r="AB85" t="str">
         <v/>
@@ -8315,14 +8405,14 @@
     </row>
     <row r="86" xml:space="preserve">
       <c r="A86" t="str">
-        <v>REF-020</v>
+        <v>REF-019</v>
       </c>
       <c r="B86" t="str" xml:space="preserve">
-        <v xml:space="preserve">Level 2 Line of Business hierarchy for intermediate aggregation and reporting, representing the Portfolio within the L1 LoB (e.g., CRE &gt; Office)
+        <v xml:space="preserve">Level 1 Line of Business hierarchy. Enables top-level organizational risk aggregation, representing the Department (e.g. Commercial Real Estate, Corporate Banking)
 </v>
       </c>
       <c r="C86" t="str">
-        <v>Line of Business L2</v>
+        <v>Line of Business  L1</v>
       </c>
       <c r="D86" t="str" xml:space="preserve">
         <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
@@ -8348,7 +8438,7 @@
 </v>
       </c>
       <c r="K86" t="str">
-        <v>Line of Business L2 (facility)</v>
+        <v>Line of Business  L1 (facility)</v>
       </c>
       <c r="L86" t="str">
         <v>Y</v>
@@ -8361,7 +8451,7 @@
 </v>
       </c>
       <c r="O86" t="str">
-        <v>Line of Business L2 (counterparty)</v>
+        <v>Line of Business  L1 (counterparty)</v>
       </c>
       <c r="P86" t="str">
         <v>Y</v>
@@ -8374,7 +8464,7 @@
 </v>
       </c>
       <c r="S86" t="str">
-        <v>Line of Business L2 (desk)</v>
+        <v>Line of Business  L1 (desk)</v>
       </c>
       <c r="T86" t="str">
         <v>Y</v>
@@ -8387,7 +8477,7 @@
 </v>
       </c>
       <c r="W86" t="str">
-        <v>Line of Business L2 (portfolio)</v>
+        <v>Line of Business  L1 (portfolio)</v>
       </c>
       <c r="X86" t="str">
         <v>Y</v>
@@ -8400,7 +8490,7 @@
 </v>
       </c>
       <c r="AA86" t="str">
-        <v>Line of Business L2 (business_segment)</v>
+        <v>Line of Business  L1 (business_segment)</v>
       </c>
       <c r="AB86" t="str">
         <v/>
@@ -8408,14 +8498,14 @@
     </row>
     <row r="87" xml:space="preserve">
       <c r="A87" t="str">
-        <v>REF-021</v>
+        <v>REF-020</v>
       </c>
       <c r="B87" t="str" xml:space="preserve">
-        <v xml:space="preserve">Level 3 Line of Business hierarchy for detailed business segmentation, representing the Desk within the L2 LoB (e.g. CRE &gt; Office &gt; Lease Up Desk)
+        <v xml:space="preserve">Level 2 Line of Business hierarchy for intermediate aggregation and reporting, representing the Portfolio within the L1 LoB (e.g., CRE &gt; Office)
 </v>
       </c>
       <c r="C87" t="str">
-        <v>Line of Business L3</v>
+        <v>Line of Business L2</v>
       </c>
       <c r="D87" t="str" xml:space="preserve">
         <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
@@ -8441,7 +8531,7 @@
 </v>
       </c>
       <c r="K87" t="str">
-        <v>Line of Business L3 (facility)</v>
+        <v>Line of Business L2 (facility)</v>
       </c>
       <c r="L87" t="str">
         <v>Y</v>
@@ -8454,7 +8544,7 @@
 </v>
       </c>
       <c r="O87" t="str">
-        <v>Line of Business L3 (counterparty)</v>
+        <v>Line of Business L2 (counterparty)</v>
       </c>
       <c r="P87" t="str">
         <v>Y</v>
@@ -8467,7 +8557,7 @@
 </v>
       </c>
       <c r="S87" t="str">
-        <v>Line of Business L3 (desk)</v>
+        <v>Line of Business L2 (desk)</v>
       </c>
       <c r="T87" t="str">
         <v>Y</v>
@@ -8480,7 +8570,7 @@
 </v>
       </c>
       <c r="W87" t="str">
-        <v>Line of Business L3 (portfolio)</v>
+        <v>Line of Business L2 (portfolio)</v>
       </c>
       <c r="X87" t="str">
         <v>Y</v>
@@ -8493,7 +8583,7 @@
 </v>
       </c>
       <c r="AA87" t="str">
-        <v>Line of Business L3 (business_segment)</v>
+        <v>Line of Business L2 (business_segment)</v>
       </c>
       <c r="AB87" t="str">
         <v/>
@@ -8501,17 +8591,17 @@
     </row>
     <row r="88" xml:space="preserve">
       <c r="A88" t="str">
-        <v>REF-022</v>
+        <v>REF-021</v>
       </c>
       <c r="B88" t="str" xml:space="preserve">
-        <v xml:space="preserve">Contractual date on which the facility or loan is scheduled to mature. Used to assess duration exposure, refinancing risk, and liquidity planning.
+        <v xml:space="preserve">Level 3 Line of Business hierarchy for detailed business segmentation, representing the Desk within the L2 LoB (e.g. CRE &gt; Office &gt; Lease Up Desk)
 </v>
       </c>
       <c r="C88" t="str">
-        <v>Maturity Date</v>
+        <v>Line of Business L3</v>
       </c>
       <c r="D88" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of maturity_date from facility_master.
+        <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
 </v>
       </c>
       <c r="E88" t="str">
@@ -8530,24 +8620,24 @@
         <v>Raw</v>
       </c>
       <c r="J88" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of maturity_date from facility_master.
+        <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
 </v>
       </c>
       <c r="K88" t="str">
-        <v>Maturity Date (facility)</v>
+        <v>Line of Business L3 (facility)</v>
       </c>
       <c r="L88" t="str">
         <v>Y</v>
       </c>
       <c r="M88" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="N88" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level maturity_date) per counterparty.
+        <v xml:space="preserve">Read parent per counterparty.
 </v>
       </c>
       <c r="O88" t="str">
-        <v>Maturity Date (counterparty)</v>
+        <v>Line of Business L3 (counterparty)</v>
       </c>
       <c r="P88" t="str">
         <v>Y</v>
@@ -8556,11 +8646,11 @@
         <v>Agg</v>
       </c>
       <c r="R88" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level maturity_date per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level parent per L3 desk segment.
 </v>
       </c>
       <c r="S88" t="str">
-        <v>Maturity Date (desk)</v>
+        <v>Line of Business L3 (desk)</v>
       </c>
       <c r="T88" t="str">
         <v>Y</v>
@@ -8569,11 +8659,11 @@
         <v>Agg</v>
       </c>
       <c r="V88" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level maturity_date per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level parent per L2 portfolio segment.
 </v>
       </c>
       <c r="W88" t="str">
-        <v>Maturity Date (portfolio)</v>
+        <v>Line of Business L3 (portfolio)</v>
       </c>
       <c r="X88" t="str">
         <v>Y</v>
@@ -8582,11 +8672,11 @@
         <v>Agg</v>
       </c>
       <c r="Z88" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level maturity_date per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level parent per L1 business segment segment.
 </v>
       </c>
       <c r="AA88" t="str">
-        <v>Maturity Date (business_segment)</v>
+        <v>Line of Business L3 (business_segment)</v>
       </c>
       <c r="AB88" t="str">
         <v/>
@@ -8594,17 +8684,17 @@
     </row>
     <row r="89" xml:space="preserve">
       <c r="A89" t="str">
-        <v>REF-023</v>
+        <v>REF-022</v>
       </c>
       <c r="B89" t="str" xml:space="preserve">
-        <v xml:space="preserve">Date on which facility was originally booked and started.
+        <v xml:space="preserve">Contractual date on which the facility or loan is scheduled to mature. Used to assess duration exposure, refinancing risk, and liquidity planning.
 </v>
       </c>
       <c r="C89" t="str">
-        <v>Facility Origination Date</v>
+        <v>Maturity Date</v>
       </c>
       <c r="D89" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of origination_date from facility_master.
+        <v xml:space="preserve">Direct lookup of maturity_date from facility_master.
 </v>
       </c>
       <c r="E89" t="str">
@@ -8623,11 +8713,11 @@
         <v>Raw</v>
       </c>
       <c r="J89" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of origination_date from facility_master.
+        <v xml:space="preserve">Direct lookup of maturity_date from facility_master.
 </v>
       </c>
       <c r="K89" t="str">
-        <v>Facility Origination Date (facility)</v>
+        <v>Maturity Date (facility)</v>
       </c>
       <c r="L89" t="str">
         <v>Y</v>
@@ -8636,11 +8726,11 @@
         <v>Agg</v>
       </c>
       <c r="N89" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level origination_date) per counterparty.
+        <v xml:space="preserve">SUM(facility-level maturity_date) per counterparty.
 </v>
       </c>
       <c r="O89" t="str">
-        <v>Facility Origination Date (counterparty)</v>
+        <v>Maturity Date (counterparty)</v>
       </c>
       <c r="P89" t="str">
         <v>Y</v>
@@ -8649,11 +8739,11 @@
         <v>Agg</v>
       </c>
       <c r="R89" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level origination_date per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level maturity_date per L3 desk segment.
 </v>
       </c>
       <c r="S89" t="str">
-        <v>Facility Origination Date (desk)</v>
+        <v>Maturity Date (desk)</v>
       </c>
       <c r="T89" t="str">
         <v>Y</v>
@@ -8662,11 +8752,11 @@
         <v>Agg</v>
       </c>
       <c r="V89" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level origination_date per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level maturity_date per L2 portfolio segment.
 </v>
       </c>
       <c r="W89" t="str">
-        <v>Facility Origination Date (portfolio)</v>
+        <v>Maturity Date (portfolio)</v>
       </c>
       <c r="X89" t="str">
         <v>Y</v>
@@ -8675,11 +8765,11 @@
         <v>Agg</v>
       </c>
       <c r="Z89" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level origination_date per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level maturity_date per L1 business segment segment.
 </v>
       </c>
       <c r="AA89" t="str">
-        <v>Facility Origination Date (business_segment)</v>
+        <v>Maturity Date (business_segment)</v>
       </c>
       <c r="AB89" t="str">
         <v/>
@@ -8687,17 +8777,17 @@
     </row>
     <row r="90" xml:space="preserve">
       <c r="A90" t="str">
-        <v>REF-024</v>
+        <v>REF-023</v>
       </c>
       <c r="B90" t="str" xml:space="preserve">
-        <v xml:space="preserve">Identifiers of counterparties participating in the credit structures or facility as multiple-borrowers. Enables exposure attribution and concentration analysis.
+        <v xml:space="preserve">Date on which facility was originally booked and started.
 </v>
       </c>
       <c r="C90" t="str">
-        <v>Participating Counterparty IDs</v>
+        <v>Facility Origination Date</v>
       </c>
       <c r="D90" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">Direct lookup of origination_date from facility_master.
 </v>
       </c>
       <c r="E90" t="str">
@@ -8716,24 +8806,24 @@
         <v>Raw</v>
       </c>
       <c r="J90" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">Direct lookup of origination_date from facility_master.
 </v>
       </c>
       <c r="K90" t="str">
-        <v>Participating Counterparty IDs (facility)</v>
+        <v>Facility Origination Date (facility)</v>
       </c>
       <c r="L90" t="str">
         <v>Y</v>
       </c>
       <c r="M90" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="N90" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">SUM(facility-level origination_date) per counterparty.
 </v>
       </c>
       <c r="O90" t="str">
-        <v>Participating Counterparty IDs (counterparty)</v>
+        <v>Facility Origination Date (counterparty)</v>
       </c>
       <c r="P90" t="str">
         <v>Y</v>
@@ -8742,11 +8832,11 @@
         <v>Agg</v>
       </c>
       <c r="R90" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level origination_date per L3 desk segment.
 </v>
       </c>
       <c r="S90" t="str">
-        <v>Participating Counterparty IDs (desk)</v>
+        <v>Facility Origination Date (desk)</v>
       </c>
       <c r="T90" t="str">
         <v>Y</v>
@@ -8755,11 +8845,11 @@
         <v>Agg</v>
       </c>
       <c r="V90" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level origination_date per L2 portfolio segment.
 </v>
       </c>
       <c r="W90" t="str">
-        <v>Participating Counterparty IDs (portfolio)</v>
+        <v>Facility Origination Date (portfolio)</v>
       </c>
       <c r="X90" t="str">
         <v>Y</v>
@@ -8768,11 +8858,11 @@
         <v>Agg</v>
       </c>
       <c r="Z90" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level origination_date per L1 business segment segment.
 </v>
       </c>
       <c r="AA90" t="str">
-        <v>Participating Counterparty IDs (business_segment)</v>
+        <v>Facility Origination Date (business_segment)</v>
       </c>
       <c r="AB90" t="str">
         <v/>
@@ -8780,17 +8870,17 @@
     </row>
     <row r="91" xml:space="preserve">
       <c r="A91" t="str">
-        <v>REF-025</v>
+        <v>REF-024</v>
       </c>
       <c r="B91" t="str" xml:space="preserve">
-        <v xml:space="preserve">Product classification assigned to the contract offering. Supports product- level segmentation and performance analysis.
+        <v xml:space="preserve">Identifiers of counterparties participating in the credit structures or facility as multiple-borrowers. Enables exposure attribution and concentration analysis.
 </v>
       </c>
       <c r="C91" t="str">
-        <v>Product</v>
+        <v>Participating Counterparty IDs</v>
       </c>
       <c r="D91" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(product_id) per facility from facility_exposure_snapshot.
+        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
 </v>
       </c>
       <c r="E91" t="str">
@@ -8806,27 +8896,27 @@
         <v>Y</v>
       </c>
       <c r="I91" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="J91" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(product_id) per facility from facility_exposure_snapshot.
+        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
 </v>
       </c>
       <c r="K91" t="str">
-        <v>Product (facility)</v>
+        <v>Participating Counterparty IDs (facility)</v>
       </c>
       <c r="L91" t="str">
         <v>Y</v>
       </c>
       <c r="M91" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="N91" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level product_id per counterparty.
+        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
 </v>
       </c>
       <c r="O91" t="str">
-        <v>Product (counterparty)</v>
+        <v>Participating Counterparty IDs (counterparty)</v>
       </c>
       <c r="P91" t="str">
         <v>Y</v>
@@ -8835,11 +8925,11 @@
         <v>Agg</v>
       </c>
       <c r="R91" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level product_id per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level counterparty_id per L3 desk segment.
 </v>
       </c>
       <c r="S91" t="str">
-        <v>Product (desk)</v>
+        <v>Participating Counterparty IDs (desk)</v>
       </c>
       <c r="T91" t="str">
         <v>Y</v>
@@ -8848,11 +8938,11 @@
         <v>Agg</v>
       </c>
       <c r="V91" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level product_id per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level counterparty_id per L2 portfolio segment.
 </v>
       </c>
       <c r="W91" t="str">
-        <v>Product (portfolio)</v>
+        <v>Participating Counterparty IDs (portfolio)</v>
       </c>
       <c r="X91" t="str">
         <v>Y</v>
@@ -8861,11 +8951,11 @@
         <v>Agg</v>
       </c>
       <c r="Z91" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level product_id per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level counterparty_id per L1 business segment segment.
 </v>
       </c>
       <c r="AA91" t="str">
-        <v>Product (business_segment)</v>
+        <v>Participating Counterparty IDs (business_segment)</v>
       </c>
       <c r="AB91" t="str">
         <v/>
@@ -8873,17 +8963,17 @@
     </row>
     <row r="92" xml:space="preserve">
       <c r="A92" t="str">
-        <v>REF-026</v>
+        <v>REF-025</v>
       </c>
       <c r="B92" t="str" xml:space="preserve">
-        <v xml:space="preserve">Geographic region classification tied to location of deal origination, supporting portfolio segmentation and concentration monitoring.
+        <v xml:space="preserve">Product classification assigned to the contract offering. Supports product- level segmentation and performance analysis.
 </v>
       </c>
       <c r="C92" t="str">
-        <v>Region</v>
+        <v>Product</v>
       </c>
       <c r="D92" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of region_code from counterparty.
+        <v xml:space="preserve">SUM(product_id) per facility from facility_exposure_snapshot.
 </v>
       </c>
       <c r="E92" t="str">
@@ -8899,27 +8989,27 @@
         <v>Y</v>
       </c>
       <c r="I92" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="J92" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of region_code from counterparty.
+        <v xml:space="preserve">SUM(product_id) per facility from facility_exposure_snapshot.
 </v>
       </c>
       <c r="K92" t="str">
-        <v>Region (facility)</v>
+        <v>Product (facility)</v>
       </c>
       <c r="L92" t="str">
         <v>Y</v>
       </c>
       <c r="M92" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="N92" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of region_code from counterparty.
+        <v xml:space="preserve">SUM of facility-level product_id per counterparty.
 </v>
       </c>
       <c r="O92" t="str">
-        <v>Region (counterparty)</v>
+        <v>Product (counterparty)</v>
       </c>
       <c r="P92" t="str">
         <v>Y</v>
@@ -8928,11 +9018,11 @@
         <v>Agg</v>
       </c>
       <c r="R92" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level region_code per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level product_id per L3 desk segment.
 </v>
       </c>
       <c r="S92" t="str">
-        <v>Region (desk)</v>
+        <v>Product (desk)</v>
       </c>
       <c r="T92" t="str">
         <v>Y</v>
@@ -8941,11 +9031,11 @@
         <v>Agg</v>
       </c>
       <c r="V92" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level region_code per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level product_id per L2 portfolio segment.
 </v>
       </c>
       <c r="W92" t="str">
-        <v>Region (portfolio)</v>
+        <v>Product (portfolio)</v>
       </c>
       <c r="X92" t="str">
         <v>Y</v>
@@ -8954,11 +9044,11 @@
         <v>Agg</v>
       </c>
       <c r="Z92" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level region_code per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level product_id per L1 business segment segment.
 </v>
       </c>
       <c r="AA92" t="str">
-        <v>Region (business_segment)</v>
+        <v>Product (business_segment)</v>
       </c>
       <c r="AB92" t="str">
         <v/>
@@ -8966,17 +9056,17 @@
     </row>
     <row r="93" xml:space="preserve">
       <c r="A93" t="str">
-        <v>REF-027</v>
+        <v>REF-026</v>
       </c>
       <c r="B93" t="str" xml:space="preserve">
-        <v xml:space="preserve">Industry sector classification of the counterparty, enabling sector concentration risk assessment.
+        <v xml:space="preserve">Geographic region classification tied to location of deal origination, supporting portfolio segmentation and concentration monitoring.
 </v>
       </c>
       <c r="C93" t="str">
-        <v>Sector</v>
+        <v>Region</v>
       </c>
       <c r="D93" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of industry_name from industry_dim.
+        <v xml:space="preserve">Direct lookup of region_code from counterparty.
 </v>
       </c>
       <c r="E93" t="str">
@@ -8995,11 +9085,11 @@
         <v>Raw</v>
       </c>
       <c r="J93" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of industry_name from industry_dim.
+        <v xml:space="preserve">Direct lookup of region_code from counterparty.
 </v>
       </c>
       <c r="K93" t="str">
-        <v>Sector (facility)</v>
+        <v>Region (facility)</v>
       </c>
       <c r="L93" t="str">
         <v>Y</v>
@@ -9008,11 +9098,11 @@
         <v>Raw</v>
       </c>
       <c r="N93" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read industry_name per counterparty.
+        <v xml:space="preserve">Direct lookup of region_code from counterparty.
 </v>
       </c>
       <c r="O93" t="str">
-        <v>Sector (counterparty)</v>
+        <v>Region (counterparty)</v>
       </c>
       <c r="P93" t="str">
         <v>Y</v>
@@ -9021,11 +9111,11 @@
         <v>Agg</v>
       </c>
       <c r="R93" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level industry_name per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level region_code per L3 desk segment.
 </v>
       </c>
       <c r="S93" t="str">
-        <v>Sector (desk)</v>
+        <v>Region (desk)</v>
       </c>
       <c r="T93" t="str">
         <v>Y</v>
@@ -9034,11 +9124,11 @@
         <v>Agg</v>
       </c>
       <c r="V93" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level industry_name per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level region_code per L2 portfolio segment.
 </v>
       </c>
       <c r="W93" t="str">
-        <v>Sector (portfolio)</v>
+        <v>Region (portfolio)</v>
       </c>
       <c r="X93" t="str">
         <v>Y</v>
@@ -9047,11 +9137,11 @@
         <v>Agg</v>
       </c>
       <c r="Z93" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level industry_name per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level region_code per L1 business segment segment.
 </v>
       </c>
       <c r="AA93" t="str">
-        <v>Sector (business_segment)</v>
+        <v>Region (business_segment)</v>
       </c>
       <c r="AB93" t="str">
         <v/>
@@ -9059,17 +9149,17 @@
     </row>
     <row r="94" xml:space="preserve">
       <c r="A94" t="str">
-        <v>REF-028</v>
+        <v>REF-027</v>
       </c>
       <c r="B94" t="str" xml:space="preserve">
-        <v xml:space="preserve">Number of unique active facilities within the reporting period.
+        <v xml:space="preserve">Industry sector classification of the counterparty, enabling sector concentration risk assessment.
 </v>
       </c>
       <c r="C94" t="str">
-        <v>Number of Facilities</v>
+        <v>Sector</v>
       </c>
       <c r="D94" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read number_of_facilities from facility_exposure_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Direct lookup of industry_name from industry_dim.
 </v>
       </c>
       <c r="E94" t="str">
@@ -9088,24 +9178,24 @@
         <v>Raw</v>
       </c>
       <c r="J94" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read number_of_facilities from facility_exposure_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Direct lookup of industry_name from industry_dim.
 </v>
       </c>
       <c r="K94" t="str">
-        <v>Number of Facilities (facility)</v>
+        <v>Sector (facility)</v>
       </c>
       <c r="L94" t="str">
         <v>Y</v>
       </c>
       <c r="M94" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="N94" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level number_of_facilities per counterparty.
+        <v xml:space="preserve">Read industry_name per counterparty.
 </v>
       </c>
       <c r="O94" t="str">
-        <v>Number of Facilities (counterparty)</v>
+        <v>Sector (counterparty)</v>
       </c>
       <c r="P94" t="str">
         <v>Y</v>
@@ -9114,11 +9204,11 @@
         <v>Agg</v>
       </c>
       <c r="R94" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level number_of_facilities per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level industry_name per L3 desk segment.
 </v>
       </c>
       <c r="S94" t="str">
-        <v>Number of Facilities (desk)</v>
+        <v>Sector (desk)</v>
       </c>
       <c r="T94" t="str">
         <v>Y</v>
@@ -9127,11 +9217,11 @@
         <v>Agg</v>
       </c>
       <c r="V94" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level number_of_facilities per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level industry_name per L2 portfolio segment.
 </v>
       </c>
       <c r="W94" t="str">
-        <v>Number of Facilities (portfolio)</v>
+        <v>Sector (portfolio)</v>
       </c>
       <c r="X94" t="str">
         <v>Y</v>
@@ -9140,11 +9230,11 @@
         <v>Agg</v>
       </c>
       <c r="Z94" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level number_of_facilities per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level industry_name per L1 business segment segment.
 </v>
       </c>
       <c r="AA94" t="str">
-        <v>Number of Facilities (business_segment)</v>
+        <v>Sector (business_segment)</v>
       </c>
       <c r="AB94" t="str">
         <v/>
@@ -9152,17 +9242,17 @@
     </row>
     <row r="95" xml:space="preserve">
       <c r="A95" t="str">
-        <v>REF-029</v>
+        <v>REF-028</v>
       </c>
       <c r="B95" t="str" xml:space="preserve">
-        <v xml:space="preserve">Represents “hard” equity after removing intangibles; reflects true loss- absorbing capacity, covenant strength, and resilience under downside scenarios.
+        <v xml:space="preserve">Number of unique active facilities within the reporting period.
 </v>
       </c>
       <c r="C95" t="str">
-        <v>Tangible Net Worth</v>
+        <v>Number of Facilities</v>
       </c>
       <c r="D95" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read tangible_net_worth_usd from counterparty_financial_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Read number_of_facilities from facility_exposure_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="E95" t="str">
@@ -9181,24 +9271,24 @@
         <v>Raw</v>
       </c>
       <c r="J95" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read tangible_net_worth_usd from counterparty_financial_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Read number_of_facilities from facility_exposure_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="K95" t="str">
-        <v>Tangible Net Worth (facility)</v>
+        <v>Number of Facilities (facility)</v>
       </c>
       <c r="L95" t="str">
         <v>Y</v>
       </c>
       <c r="M95" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="N95" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read tangible_net_worth_usd per counterparty.
+        <v xml:space="preserve">SUM of facility-level number_of_facilities per counterparty.
 </v>
       </c>
       <c r="O95" t="str">
-        <v>Tangible Net Worth (counterparty)</v>
+        <v>Number of Facilities (counterparty)</v>
       </c>
       <c r="P95" t="str">
         <v>Y</v>
@@ -9207,11 +9297,11 @@
         <v>Agg</v>
       </c>
       <c r="R95" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level tangible_net_worth_usd per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level number_of_facilities per L3 desk segment.
 </v>
       </c>
       <c r="S95" t="str">
-        <v>Tangible Net Worth (desk)</v>
+        <v>Number of Facilities (desk)</v>
       </c>
       <c r="T95" t="str">
         <v>Y</v>
@@ -9220,11 +9310,11 @@
         <v>Agg</v>
       </c>
       <c r="V95" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level tangible_net_worth_usd per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level number_of_facilities per L2 portfolio segment.
 </v>
       </c>
       <c r="W95" t="str">
-        <v>Tangible Net Worth (portfolio)</v>
+        <v>Number of Facilities (portfolio)</v>
       </c>
       <c r="X95" t="str">
         <v>Y</v>
@@ -9233,11 +9323,11 @@
         <v>Agg</v>
       </c>
       <c r="Z95" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level tangible_net_worth_usd per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level number_of_facilities per L1 business segment segment.
 </v>
       </c>
       <c r="AA95" t="str">
-        <v>Tangible Net Worth (business_segment)</v>
+        <v>Number of Facilities (business_segment)</v>
       </c>
       <c r="AB95" t="str">
         <v/>
@@ -9245,17 +9335,17 @@
     </row>
     <row r="96" xml:space="preserve">
       <c r="A96" t="str">
-        <v>REF-030</v>
+        <v>REF-029</v>
       </c>
       <c r="B96" t="str" xml:space="preserve">
-        <v xml:space="preserve">Bucketing mechanism to calculate Maturity Dates supporting the identification of upcoming liquidations in the next 90 days
+        <v xml:space="preserve">Represents “hard” equity after removing intangibles; reflects true loss- absorbing capacity, covenant strength, and resilience under downside scenarios.
 </v>
       </c>
       <c r="C96" t="str">
-        <v>Maturity Date Bucket</v>
+        <v>Tangible Net Worth</v>
       </c>
       <c r="D96" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated maturity_bucket_id per facility.
+        <v xml:space="preserve">Read tangible_net_worth_usd from counterparty_financial_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="E96" t="str">
@@ -9271,27 +9361,27 @@
         <v>Y</v>
       </c>
       <c r="I96" t="str">
-        <v>Calc</v>
+        <v>Raw</v>
       </c>
       <c r="J96" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated maturity_bucket_id per facility.
+        <v xml:space="preserve">Read tangible_net_worth_usd from counterparty_financial_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="K96" t="str">
-        <v>Maturity Date Bucket (facility)</v>
+        <v>Tangible Net Worth (facility)</v>
       </c>
       <c r="L96" t="str">
         <v>Y</v>
       </c>
       <c r="M96" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="N96" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level maturity_bucket_id) per counterparty.
+        <v xml:space="preserve">Read tangible_net_worth_usd per counterparty.
 </v>
       </c>
       <c r="O96" t="str">
-        <v>Maturity Date Bucket (counterparty)</v>
+        <v>Tangible Net Worth (counterparty)</v>
       </c>
       <c r="P96" t="str">
         <v>Y</v>
@@ -9300,11 +9390,11 @@
         <v>Agg</v>
       </c>
       <c r="R96" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level maturity_bucket_id per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level tangible_net_worth_usd per L3 desk segment.
 </v>
       </c>
       <c r="S96" t="str">
-        <v>Maturity Date Bucket (desk)</v>
+        <v>Tangible Net Worth (desk)</v>
       </c>
       <c r="T96" t="str">
         <v>Y</v>
@@ -9313,11 +9403,11 @@
         <v>Agg</v>
       </c>
       <c r="V96" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level maturity_bucket_id per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level tangible_net_worth_usd per L2 portfolio segment.
 </v>
       </c>
       <c r="W96" t="str">
-        <v>Maturity Date Bucket (portfolio)</v>
+        <v>Tangible Net Worth (portfolio)</v>
       </c>
       <c r="X96" t="str">
         <v>Y</v>
@@ -9326,11 +9416,11 @@
         <v>Agg</v>
       </c>
       <c r="Z96" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level maturity_bucket_id per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level tangible_net_worth_usd per L1 business segment segment.
 </v>
       </c>
       <c r="AA96" t="str">
-        <v>Maturity Date Bucket (business_segment)</v>
+        <v>Tangible Net Worth (business_segment)</v>
       </c>
       <c r="AB96" t="str">
         <v/>
@@ -9338,17 +9428,17 @@
     </row>
     <row r="97" xml:space="preserve">
       <c r="A97" t="str">
-        <v>REF-031</v>
+        <v>REF-030</v>
       </c>
       <c r="B97" t="str" xml:space="preserve">
-        <v xml:space="preserve">Bucketing mechanism to calculate Origination Dates supporting the identification of upcoming facilities starting commitments in the next 90 days
+        <v xml:space="preserve">Bucketing mechanism to calculate Maturity Dates supporting the identification of upcoming liquidations in the next 90 days
 </v>
       </c>
       <c r="C97" t="str">
-        <v>Origination Date Bucket</v>
+        <v>Maturity Date Bucket</v>
       </c>
       <c r="D97" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated origination_date_bucket per facility.
+        <v xml:space="preserve">Calculated maturity_bucket_id per facility.
 </v>
       </c>
       <c r="E97" t="str">
@@ -9367,11 +9457,11 @@
         <v>Calc</v>
       </c>
       <c r="J97" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated origination_date_bucket per facility.
+        <v xml:space="preserve">Calculated maturity_bucket_id per facility.
 </v>
       </c>
       <c r="K97" t="str">
-        <v>Origination Date Bucket (facility)</v>
+        <v>Maturity Date Bucket (facility)</v>
       </c>
       <c r="L97" t="str">
         <v>Y</v>
@@ -9380,11 +9470,11 @@
         <v>Agg</v>
       </c>
       <c r="N97" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level origination_date_bucket) per counterparty.
+        <v xml:space="preserve">SUM(facility-level maturity_bucket_id) per counterparty.
 </v>
       </c>
       <c r="O97" t="str">
-        <v>Origination Date Bucket (counterparty)</v>
+        <v>Maturity Date Bucket (counterparty)</v>
       </c>
       <c r="P97" t="str">
         <v>Y</v>
@@ -9393,11 +9483,11 @@
         <v>Agg</v>
       </c>
       <c r="R97" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level origination_date_bucket per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level maturity_bucket_id per L3 desk segment.
 </v>
       </c>
       <c r="S97" t="str">
-        <v>Origination Date Bucket (desk)</v>
+        <v>Maturity Date Bucket (desk)</v>
       </c>
       <c r="T97" t="str">
         <v>Y</v>
@@ -9406,11 +9496,11 @@
         <v>Agg</v>
       </c>
       <c r="V97" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level origination_date_bucket per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level maturity_bucket_id per L2 portfolio segment.
 </v>
       </c>
       <c r="W97" t="str">
-        <v>Origination Date Bucket (portfolio)</v>
+        <v>Maturity Date Bucket (portfolio)</v>
       </c>
       <c r="X97" t="str">
         <v>Y</v>
@@ -9419,11 +9509,11 @@
         <v>Agg</v>
       </c>
       <c r="Z97" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level origination_date_bucket per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level maturity_bucket_id per L1 business segment segment.
 </v>
       </c>
       <c r="AA97" t="str">
-        <v>Origination Date Bucket (business_segment)</v>
+        <v>Maturity Date Bucket (business_segment)</v>
       </c>
       <c r="AB97" t="str">
         <v/>
@@ -9431,17 +9521,17 @@
     </row>
     <row r="98" xml:space="preserve">
       <c r="A98" t="str">
-        <v>REF-032</v>
+        <v>REF-031</v>
       </c>
       <c r="B98" t="str" xml:space="preserve">
-        <v xml:space="preserve">Capturing distirbution of facilities starting or liquidating in 90 day windows
+        <v xml:space="preserve">Bucketing mechanism to calculate Origination Dates supporting the identification of upcoming facilities starting commitments in the next 90 days
 </v>
       </c>
       <c r="C98" t="str">
-        <v>Effective Date Bucket</v>
+        <v>Origination Date Bucket</v>
       </c>
       <c r="D98" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated effective_date_bucket per facility.
+        <v xml:space="preserve">Calculated origination_date_bucket per facility.
 </v>
       </c>
       <c r="E98" t="str">
@@ -9460,11 +9550,11 @@
         <v>Calc</v>
       </c>
       <c r="J98" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated effective_date_bucket per facility.
+        <v xml:space="preserve">Calculated origination_date_bucket per facility.
 </v>
       </c>
       <c r="K98" t="str">
-        <v>Effective Date Bucket (facility)</v>
+        <v>Origination Date Bucket (facility)</v>
       </c>
       <c r="L98" t="str">
         <v>Y</v>
@@ -9473,11 +9563,11 @@
         <v>Agg</v>
       </c>
       <c r="N98" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level effective_date_bucket) per counterparty.
+        <v xml:space="preserve">SUM(facility-level origination_date_bucket) per counterparty.
 </v>
       </c>
       <c r="O98" t="str">
-        <v>Effective Date Bucket (counterparty)</v>
+        <v>Origination Date Bucket (counterparty)</v>
       </c>
       <c r="P98" t="str">
         <v>Y</v>
@@ -9486,11 +9576,11 @@
         <v>Agg</v>
       </c>
       <c r="R98" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level effective_date_bucket per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level origination_date_bucket per L3 desk segment.
 </v>
       </c>
       <c r="S98" t="str">
-        <v>Effective Date Bucket (desk)</v>
+        <v>Origination Date Bucket (desk)</v>
       </c>
       <c r="T98" t="str">
         <v>Y</v>
@@ -9499,11 +9589,11 @@
         <v>Agg</v>
       </c>
       <c r="V98" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level effective_date_bucket per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level origination_date_bucket per L2 portfolio segment.
 </v>
       </c>
       <c r="W98" t="str">
-        <v>Effective Date Bucket (portfolio)</v>
+        <v>Origination Date Bucket (portfolio)</v>
       </c>
       <c r="X98" t="str">
         <v>Y</v>
@@ -9512,11 +9602,11 @@
         <v>Agg</v>
       </c>
       <c r="Z98" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level effective_date_bucket per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level origination_date_bucket per L1 business segment segment.
 </v>
       </c>
       <c r="AA98" t="str">
-        <v>Effective Date Bucket (business_segment)</v>
+        <v>Origination Date Bucket (business_segment)</v>
       </c>
       <c r="AB98" t="str">
         <v/>
@@ -9524,17 +9614,17 @@
     </row>
     <row r="99" xml:space="preserve">
       <c r="A99" t="str">
-        <v>REF-033</v>
+        <v>REF-032</v>
       </c>
       <c r="B99" t="str" xml:space="preserve">
-        <v xml:space="preserve">Boolean indicator to depict when a Facility is currently active in the reporting period (e.g., Facility Status is not Canceled or Closed)
+        <v xml:space="preserve">Capturing distirbution of facilities starting or liquidating in 90 day windows
 </v>
       </c>
       <c r="C99" t="str">
-        <v>Facility Active Flag</v>
+        <v>Effective Date Bucket</v>
       </c>
       <c r="D99" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated facility_is_active_flag per facility.
+        <v xml:space="preserve">Calculated effective_date_bucket per facility.
 </v>
       </c>
       <c r="E99" t="str">
@@ -9553,11 +9643,11 @@
         <v>Calc</v>
       </c>
       <c r="J99" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated facility_is_active_flag per facility.
+        <v xml:space="preserve">Calculated effective_date_bucket per facility.
 </v>
       </c>
       <c r="K99" t="str">
-        <v>Facility Active Flag (facility)</v>
+        <v>Effective Date Bucket (facility)</v>
       </c>
       <c r="L99" t="str">
         <v>Y</v>
@@ -9566,11 +9656,11 @@
         <v>Agg</v>
       </c>
       <c r="N99" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level facility_is_active_flag) per counterparty.
+        <v xml:space="preserve">SUM(facility-level effective_date_bucket) per counterparty.
 </v>
       </c>
       <c r="O99" t="str">
-        <v>Facility Active Flag (counterparty)</v>
+        <v>Effective Date Bucket (counterparty)</v>
       </c>
       <c r="P99" t="str">
         <v>Y</v>
@@ -9579,11 +9669,11 @@
         <v>Agg</v>
       </c>
       <c r="R99" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_is_active_flag per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level effective_date_bucket per L3 desk segment.
 </v>
       </c>
       <c r="S99" t="str">
-        <v>Facility Active Flag (desk)</v>
+        <v>Effective Date Bucket (desk)</v>
       </c>
       <c r="T99" t="str">
         <v>Y</v>
@@ -9592,11 +9682,11 @@
         <v>Agg</v>
       </c>
       <c r="V99" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_is_active_flag per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level effective_date_bucket per L2 portfolio segment.
 </v>
       </c>
       <c r="W99" t="str">
-        <v>Facility Active Flag (portfolio)</v>
+        <v>Effective Date Bucket (portfolio)</v>
       </c>
       <c r="X99" t="str">
         <v>Y</v>
@@ -9605,11 +9695,11 @@
         <v>Agg</v>
       </c>
       <c r="Z99" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_is_active_flag per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level effective_date_bucket per L1 business segment segment.
 </v>
       </c>
       <c r="AA99" t="str">
-        <v>Facility Active Flag (business_segment)</v>
+        <v>Effective Date Bucket (business_segment)</v>
       </c>
       <c r="AB99" t="str">
         <v/>
@@ -9617,17 +9707,17 @@
     </row>
     <row r="100" xml:space="preserve">
       <c r="A100" t="str">
-        <v>RSK-001</v>
+        <v>REF-033</v>
       </c>
       <c r="B100" t="str" xml:space="preserve">
-        <v xml:space="preserve">Most recent internal credit rating assigned at reporting date. Used for segmentation and exposure-weighted risk aggregation.
+        <v xml:space="preserve">Boolean indicator to depict when a Facility is currently active in the reporting period (e.g., Facility Status is not Canceled or Closed)
 </v>
       </c>
       <c r="C100" t="str">
-        <v>Risk Rating Tier</v>
+        <v>Facility Active Flag</v>
       </c>
       <c r="D100" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility.
+        <v xml:space="preserve">Calculated facility_is_active_flag per facility.
 </v>
       </c>
       <c r="E100" t="str">
@@ -9643,14 +9733,14 @@
         <v>Y</v>
       </c>
       <c r="I100" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="J100" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility.
+        <v xml:space="preserve">Calculated facility_is_active_flag per facility.
 </v>
       </c>
       <c r="K100" t="str">
-        <v>Risk Rating Tier (facility)</v>
+        <v>Facility Active Flag (facility)</v>
       </c>
       <c r="L100" t="str">
         <v>Y</v>
@@ -9659,11 +9749,11 @@
         <v>Agg</v>
       </c>
       <c r="N100" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating per counterparty.
+        <v xml:space="preserve">SUM(facility-level facility_is_active_flag) per counterparty.
 </v>
       </c>
       <c r="O100" t="str">
-        <v>Risk Rating Tier (counterparty)</v>
+        <v>Facility Active Flag (counterparty)</v>
       </c>
       <c r="P100" t="str">
         <v>Y</v>
@@ -9672,11 +9762,11 @@
         <v>Agg</v>
       </c>
       <c r="R100" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level facility_is_active_flag per L3 desk segment.
 </v>
       </c>
       <c r="S100" t="str">
-        <v>Risk Rating Tier (desk)</v>
+        <v>Facility Active Flag (desk)</v>
       </c>
       <c r="T100" t="str">
         <v>Y</v>
@@ -9685,11 +9775,11 @@
         <v>Agg</v>
       </c>
       <c r="V100" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level facility_is_active_flag per L2 portfolio segment.
 </v>
       </c>
       <c r="W100" t="str">
-        <v>Risk Rating Tier (portfolio)</v>
+        <v>Facility Active Flag (portfolio)</v>
       </c>
       <c r="X100" t="str">
         <v>Y</v>
@@ -9698,11 +9788,11 @@
         <v>Agg</v>
       </c>
       <c r="Z100" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating per L1 business segment.
+        <v xml:space="preserve">SUM of facility-level facility_is_active_flag per L1 business segment segment.
 </v>
       </c>
       <c r="AA100" t="str">
-        <v>Risk Rating Tier (business_segment)</v>
+        <v>Facility Active Flag (business_segment)</v>
       </c>
       <c r="AB100" t="str">
         <v/>
@@ -9710,17 +9800,17 @@
     </row>
     <row r="101" xml:space="preserve">
       <c r="A101" t="str">
-        <v>RSK-002</v>
+        <v>REF-034</v>
       </c>
       <c r="B101" t="str" xml:space="preserve">
-        <v xml:space="preserve">Current external credit agency rating assigned to the obligor. Used for benchmarking, regulatory reporting, and external credit risk validation. Sourced based on external Rating provider (S&amp;P, Moodys, Fitch) - populated based on firm's preferred recognized rating provider.
+        <v xml:space="preserve">Facility activity status indicator. At facility level, reads the is_active_flag from facility_master and returns 1 (active) or 0 (inactive). At counterparty level, returns 1 if any of the counterparty's facilities are active (boolean OR). Provides a baseline portfolio activity measure for CRO reporting and data quality monitoring.
 </v>
       </c>
       <c r="C101" t="str">
-        <v>Risk Rating - External Rating</v>
+        <v>Active Flag</v>
       </c>
       <c r="D101" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read external_risk_rating from position for each facility as-of reporting date.
+        <v xml:space="preserve">Read is_active_flag from facility_master. Returns 1 if the facility is active (is_active_flag = 'Y'), 0 otherwise. No date filtering required as is_active_flag reflects current status.
 </v>
       </c>
       <c r="E101" t="str">
@@ -9739,63 +9829,63 @@
         <v>Raw</v>
       </c>
       <c r="J101" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read external_risk_rating from position for each facility as-of reporting date.
+        <v xml:space="preserve">Read is_active_flag from facility_master. Returns 1 if the facility is active (is_active_flag = 'Y'), 0 otherwise. No date filtering required as is_active_flag reflects current status.
 </v>
       </c>
       <c r="K101" t="str">
-        <v>Risk Rating - External Rating (facility)</v>
+        <v>Active Flag (facility)</v>
       </c>
       <c r="L101" t="str">
         <v>Y</v>
       </c>
       <c r="M101" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="N101" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read external_risk_rating per counterparty.
+        <v xml:space="preserve">For each counterparty, check if any of its facilities are active. Uses MAX over the facility-level boolean flags — if any facility is active (1), the counterparty is considered active (1). Returns 0 only if ALL facilities for the counterparty are inactive.
 </v>
       </c>
       <c r="O101" t="str">
-        <v>Risk Rating - External Rating (counterparty)</v>
+        <v>Active Flag (counterparty)</v>
       </c>
       <c r="P101" t="str">
         <v>Y</v>
       </c>
       <c r="Q101" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="R101" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level external_risk_rating per L3 desk segment.
+        <v xml:space="preserve">Not applicable — active flag is a facility/counterparty level indicator. Desk-level portfolio activity analysis should use count-based metrics or exposure-weighted activity rates.
 </v>
       </c>
       <c r="S101" t="str">
-        <v>Risk Rating - External Rating (desk)</v>
+        <v>Active Flag (desk)</v>
       </c>
       <c r="T101" t="str">
         <v>Y</v>
       </c>
       <c r="U101" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="V101" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level external_risk_rating per L2 portfolio segment.
+        <v xml:space="preserve">Not applicable — active flag is a facility/counterparty level indicator. Portfolio-level analysis should aggregate exposure amounts filtered by active status.
 </v>
       </c>
       <c r="W101" t="str">
-        <v>Risk Rating - External Rating (portfolio)</v>
+        <v>Active Flag (portfolio)</v>
       </c>
       <c r="X101" t="str">
         <v>Y</v>
       </c>
       <c r="Y101" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="Z101" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level external_risk_rating per L1 business segment segment.
+        <v xml:space="preserve">Not applicable — active flag is a facility/counterparty level indicator. Business segment analysis should aggregate exposure amounts filtered by active status.
 </v>
       </c>
       <c r="AA101" t="str">
-        <v>Risk Rating - External Rating (business_segment)</v>
+        <v>Active Flag (business_segment)</v>
       </c>
       <c r="AB101" t="str">
         <v/>
@@ -9803,17 +9893,17 @@
     </row>
     <row r="102" xml:space="preserve">
       <c r="A102" t="str">
-        <v>RSK-003</v>
+        <v>RSK-001</v>
       </c>
       <c r="B102" t="str" xml:space="preserve">
-        <v xml:space="preserve">The institution’s internally assigned credit risk grade for a borrower, facility, or exposure as of a given date, reflecting its assessment of default risk according to the firm’s internal rating scale/model.
+        <v xml:space="preserve">Risk rating tier derived from counterparty probability of default (PD). Each counterparty's pd_annual is matched against the risk_rating_tier_dim reference table (pd_min_pct / pd_max_pct boundaries) to assign a tier classification. At facility level, the tier is inherited from the owning counterparty. At aggregate levels, MAX (worst-case) tier ordinal is reported.
 </v>
       </c>
       <c r="C102" t="str">
-        <v>Risk Rating - Internal Risk Rating</v>
+        <v>Risk Rating Tier</v>
       </c>
       <c r="D102" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read internal_risk_rating from facility_risk_snapshot for each facility.
+        <v xml:space="preserve">For each facility, inherit the risk rating tier from the owning counterparty. Join facility_master to counterparty, then range-match counterparty pd_annual against risk_rating_tier_dim to derive the tier ordinal (display_order).
 </v>
       </c>
       <c r="E102" t="str">
@@ -9829,27 +9919,27 @@
         <v>Y</v>
       </c>
       <c r="I102" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="J102" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read internal_risk_rating from facility_risk_snapshot for each facility.
+        <v xml:space="preserve">For each facility, inherit the risk rating tier from the owning counterparty. Join facility_master to counterparty, then range-match counterparty pd_annual against risk_rating_tier_dim to derive the tier ordinal (display_order).
 </v>
       </c>
       <c r="K102" t="str">
-        <v>Risk Rating - Internal Risk Rating (facility)</v>
+        <v>Risk Rating Tier (facility)</v>
       </c>
       <c r="L102" t="str">
         <v>Y</v>
       </c>
       <c r="M102" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N102" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with internal risk rating per counterparty.
+        <v xml:space="preserve">For each counterparty, look up pd_annual and range-match against risk_rating_tier_dim where pd_annual &gt;= pd_min_pct AND pd_annual &lt; pd_max_pct. Returns the tier ordinal (display_order). Counterparties with NULL PD receive tier 0 (unrated).
 </v>
       </c>
       <c r="O102" t="str">
-        <v>Risk Rating - Internal Risk Rating (counterparty)</v>
+        <v>Risk Rating Tier (counterparty)</v>
       </c>
       <c r="P102" t="str">
         <v>Y</v>
@@ -9858,11 +9948,11 @@
         <v>Agg</v>
       </c>
       <c r="R102" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with internal risk rating per L3 desk segment.
+        <v xml:space="preserve">Worst-case (MAX) risk rating tier ordinal across all counterparties in the L3 desk segment. Higher ordinal = riskier tier. Full tier distribution available via counterparty-level drill-down.
 </v>
       </c>
       <c r="S102" t="str">
-        <v>Risk Rating - Internal Risk Rating (desk)</v>
+        <v>Risk Rating Tier (desk)</v>
       </c>
       <c r="T102" t="str">
         <v>Y</v>
@@ -9871,11 +9961,11 @@
         <v>Agg</v>
       </c>
       <c r="V102" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with internal risk rating per L2 portfolio segment.
+        <v xml:space="preserve">Worst-case (MAX) risk rating tier ordinal per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
 </v>
       </c>
       <c r="W102" t="str">
-        <v>Risk Rating - Internal Risk Rating (portfolio)</v>
+        <v>Risk Rating Tier (portfolio)</v>
       </c>
       <c r="X102" t="str">
         <v>Y</v>
@@ -9884,11 +9974,11 @@
         <v>Agg</v>
       </c>
       <c r="Z102" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with internal risk rating per L1 business segment.
+        <v xml:space="preserve">Worst-case (MAX) risk rating tier ordinal per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
 </v>
       </c>
       <c r="AA102" t="str">
-        <v>Risk Rating - Internal Risk Rating (business_segment)</v>
+        <v>Risk Rating Tier (business_segment)</v>
       </c>
       <c r="AB102" t="str">
         <v/>
@@ -9896,17 +9986,17 @@
     </row>
     <row r="103" xml:space="preserve">
       <c r="A103" t="str">
-        <v>RSK-004</v>
+        <v>RSK-002</v>
       </c>
       <c r="B103" t="str" xml:space="preserve">
-        <v xml:space="preserve">Derived directional indicator reflecting movement in external credit agency rating and changes month over month, which depicts the month-over-month change reflecting an upgrade (e.g. A to AA), downgrade (e.g., B+ to B-) or stable (remaing constant month over month), as compared to prior month reporting periods. Note when this is displayed at an aggregated Line of Business or portfolio level, it is determined by the month-over-month change of the average rating at this level. Supports benchmarking against market perception and helps validate internal risk assessment trends.
+        <v xml:space="preserve">Current external credit agency rating assigned to the obligor. Used for benchmarking, regulatory reporting, and external credit risk validation. Sourced based on external Rating provider (S&amp;P, Moodys, Fitch) - populated based on firm's preferred recognized rating provider.
 </v>
       </c>
       <c r="C103" t="str">
-        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable)</v>
+        <v>Risk Rating - External Rating</v>
       </c>
       <c r="D103" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility as-of reporting date.
+        <v xml:space="preserve">Read external_risk_rating from position for each facility as-of reporting date.
 </v>
       </c>
       <c r="E103" t="str">
@@ -9925,63 +10015,63 @@
         <v>Raw</v>
       </c>
       <c r="J103" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility as-of reporting date.
+        <v xml:space="preserve">Read external_risk_rating from position for each facility as-of reporting date.
 </v>
       </c>
       <c r="K103" t="str">
-        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable) (facility)</v>
+        <v>Risk Rating - External Rating (facility)</v>
       </c>
       <c r="L103" t="str">
         <v>Y</v>
       </c>
       <c r="M103" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="N103" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_status per counterparty.
+        <v xml:space="preserve">Read external_risk_rating per counterparty.
 </v>
       </c>
       <c r="O103" t="str">
-        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable) (counterparty)</v>
+        <v>Risk Rating - External Rating (counterparty)</v>
       </c>
       <c r="P103" t="str">
         <v>Y</v>
       </c>
       <c r="Q103" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="R103" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_status per L3 desk segment.
+        <v xml:space="preserve">AVG of facility-level external_risk_rating per L3 desk segment.
 </v>
       </c>
       <c r="S103" t="str">
-        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable) (desk)</v>
+        <v>Risk Rating - External Rating (desk)</v>
       </c>
       <c r="T103" t="str">
         <v>Y</v>
       </c>
       <c r="U103" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="V103" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_status per L2 portfolio segment.
+        <v xml:space="preserve">AVG of facility-level external_risk_rating per L2 portfolio segment.
 </v>
       </c>
       <c r="W103" t="str">
-        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable) (portfolio)</v>
+        <v>Risk Rating - External Rating (portfolio)</v>
       </c>
       <c r="X103" t="str">
         <v>Y</v>
       </c>
       <c r="Y103" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="Z103" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_status per L1 business segment segment.
+        <v xml:space="preserve">AVG of facility-level external_risk_rating per L1 business segment segment.
 </v>
       </c>
       <c r="AA103" t="str">
-        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable) (business_segment)</v>
+        <v>Risk Rating - External Rating (business_segment)</v>
       </c>
       <c r="AB103" t="str">
         <v/>
@@ -9989,17 +10079,17 @@
     </row>
     <row r="104" xml:space="preserve">
       <c r="A104" t="str">
-        <v>RSK-005</v>
+        <v>RSK-003</v>
       </c>
       <c r="B104" t="str" xml:space="preserve">
-        <v xml:space="preserve">Numerical representation of external risk rating migration (month over month changes) expressed in notch movement (positive or negative). Positive step changes are identified when there is an upgrade, from A to AA and the step change is +1, where as the negative step change is identified when there is a downgrade from B+ to B- and the step change is -1. Note when this is displayed at an aggregated Line of Business or portfolio level, it is determined by the month-over-month change of the average rating at this level. Quantifies magnitude of credit change and enables portfolio-level migration analysis, stress testing sensitivity, and risk trend measurement.
+        <v xml:space="preserve">The institution’s internally assigned credit risk grade for a borrower, facility, or exposure as of a given date, reflecting its assessment of default risk according to the firm’s internal rating scale/model.
 </v>
       </c>
       <c r="C104" t="str">
-        <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps)</v>
+        <v>Risk Rating - Internal Risk Rating</v>
       </c>
       <c r="D104" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_change_steps from counterparty_rating_observation for each facility as-of reporting date.
+        <v xml:space="preserve">Read internal_risk_rating from facility_risk_snapshot for each facility.
 </v>
       </c>
       <c r="E104" t="str">
@@ -10018,11 +10108,11 @@
         <v>Raw</v>
       </c>
       <c r="J104" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_change_steps from counterparty_rating_observation for each facility as-of reporting date.
+        <v xml:space="preserve">Read internal_risk_rating from facility_risk_snapshot for each facility.
 </v>
       </c>
       <c r="K104" t="str">
-        <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps) (facility)</v>
+        <v>Risk Rating - Internal Risk Rating (facility)</v>
       </c>
       <c r="L104" t="str">
         <v>Y</v>
@@ -10031,11 +10121,11 @@
         <v>Agg</v>
       </c>
       <c r="N104" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per counterparty.
+        <v xml:space="preserve">COUNT of facilities with internal risk rating per counterparty.
 </v>
       </c>
       <c r="O104" t="str">
-        <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps) (counterparty)</v>
+        <v>Risk Rating - Internal Risk Rating (counterparty)</v>
       </c>
       <c r="P104" t="str">
         <v>Y</v>
@@ -10044,11 +10134,11 @@
         <v>Agg</v>
       </c>
       <c r="R104" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per L3 desk segment.
+        <v xml:space="preserve">COUNT of facilities with internal risk rating per L3 desk segment.
 </v>
       </c>
       <c r="S104" t="str">
-        <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps) (desk)</v>
+        <v>Risk Rating - Internal Risk Rating (desk)</v>
       </c>
       <c r="T104" t="str">
         <v>Y</v>
@@ -10057,11 +10147,11 @@
         <v>Agg</v>
       </c>
       <c r="V104" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per L2 portfolio segment.
+        <v xml:space="preserve">COUNT of facilities with internal risk rating per L2 portfolio segment.
 </v>
       </c>
       <c r="W104" t="str">
-        <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps) (portfolio)</v>
+        <v>Risk Rating - Internal Risk Rating (portfolio)</v>
       </c>
       <c r="X104" t="str">
         <v>Y</v>
@@ -10070,11 +10160,11 @@
         <v>Agg</v>
       </c>
       <c r="Z104" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per L1 business segment segment.
+        <v xml:space="preserve">COUNT of facilities with internal risk rating per L1 business segment.
 </v>
       </c>
       <c r="AA104" t="str">
-        <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps) (business_segment)</v>
+        <v>Risk Rating - Internal Risk Rating (business_segment)</v>
       </c>
       <c r="AB104" t="str">
         <v/>
@@ -10082,14 +10172,14 @@
     </row>
     <row r="105" xml:space="preserve">
       <c r="A105" t="str">
-        <v>RSK-006</v>
+        <v>RSK-004</v>
       </c>
       <c r="B105" t="str" xml:space="preserve">
-        <v xml:space="preserve">Derived directional classification indicating whether the internal credit rating has changed month over month: upgraded (e.g. 3 to 1), downgraded (e.g. 1 to 3), or remained stable (remained costant month-over month) compared to the prior reporting period. Note when this is displayed at an aggregated Line of Business or portfolio level, it is determined by the month-over-month change of the average rating at this level. Provides migration trend insight and serves as an early warning indicator of credit quality movement to support proactive risk management and escalation decisions.
+        <v xml:space="preserve">Derived directional indicator reflecting movement in external credit agency rating and changes month over month, which depicts the month-over-month change reflecting an upgrade (e.g. A to AA), downgrade (e.g., B+ to B-) or stable (remaing constant month over month), as compared to prior month reporting periods. Note when this is displayed at an aggregated Line of Business or portfolio level, it is determined by the month-over-month change of the average rating at this level. Supports benchmarking against market perception and helps validate internal risk assessment trends.
 </v>
       </c>
       <c r="C105" t="str">
-        <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable)</v>
+        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable)</v>
       </c>
       <c r="D105" t="str" xml:space="preserve">
         <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility as-of reporting date.
@@ -10115,7 +10205,7 @@
 </v>
       </c>
       <c r="K105" t="str">
-        <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable) (facility)</v>
+        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable) (facility)</v>
       </c>
       <c r="L105" t="str">
         <v>Y</v>
@@ -10128,7 +10218,7 @@
 </v>
       </c>
       <c r="O105" t="str">
-        <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable) (counterparty)</v>
+        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable) (counterparty)</v>
       </c>
       <c r="P105" t="str">
         <v>Y</v>
@@ -10141,7 +10231,7 @@
 </v>
       </c>
       <c r="S105" t="str">
-        <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable) (desk)</v>
+        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable) (desk)</v>
       </c>
       <c r="T105" t="str">
         <v>Y</v>
@@ -10154,7 +10244,7 @@
 </v>
       </c>
       <c r="W105" t="str">
-        <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable) (portfolio)</v>
+        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable) (portfolio)</v>
       </c>
       <c r="X105" t="str">
         <v>Y</v>
@@ -10167,7 +10257,7 @@
 </v>
       </c>
       <c r="AA105" t="str">
-        <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable) (business_segment)</v>
+        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable) (business_segment)</v>
       </c>
       <c r="AB105" t="str">
         <v/>
@@ -10175,14 +10265,14 @@
     </row>
     <row r="106" xml:space="preserve">
       <c r="A106" t="str">
-        <v>RSK-007</v>
+        <v>RSK-005</v>
       </c>
       <c r="B106" t="str" xml:space="preserve">
-        <v xml:space="preserve">Numerical representation of internal risk rating migration (month over month changes) expressed in notch movement (positive or negative). Positive step changes are identified when there is an upgrade, from 3 to 1and the step change is +2, where as the negative step change is identified when there is a downgrade from 5 to 8 and the step change is -3. Note when this is displayed at an aggregated Line of Business or portfolio level, it is determined by the month-over-month change of the average rating at this level. Quantifies magnitude of credit change and enables portfolio-level migration analysis, stress testing sensitivity, and risk trend measurement.
+        <v xml:space="preserve">Numerical representation of external risk rating migration (month over month changes) expressed in notch movement (positive or negative). Positive step changes are identified when there is an upgrade, from A to AA and the step change is +1, where as the negative step change is identified when there is a downgrade from B+ to B- and the step change is -1. Note when this is displayed at an aggregated Line of Business or portfolio level, it is determined by the month-over-month change of the average rating at this level. Quantifies magnitude of credit change and enables portfolio-level migration analysis, stress testing sensitivity, and risk trend measurement.
 </v>
       </c>
       <c r="C106" t="str">
-        <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps)</v>
+        <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps)</v>
       </c>
       <c r="D106" t="str" xml:space="preserve">
         <v xml:space="preserve">Read risk_rating_change_steps from counterparty_rating_observation for each facility as-of reporting date.
@@ -10208,7 +10298,7 @@
 </v>
       </c>
       <c r="K106" t="str">
-        <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps) (facility)</v>
+        <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps) (facility)</v>
       </c>
       <c r="L106" t="str">
         <v>Y</v>
@@ -10221,7 +10311,7 @@
 </v>
       </c>
       <c r="O106" t="str">
-        <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps) (counterparty)</v>
+        <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps) (counterparty)</v>
       </c>
       <c r="P106" t="str">
         <v>Y</v>
@@ -10234,7 +10324,7 @@
 </v>
       </c>
       <c r="S106" t="str">
-        <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps) (desk)</v>
+        <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps) (desk)</v>
       </c>
       <c r="T106" t="str">
         <v>Y</v>
@@ -10247,7 +10337,7 @@
 </v>
       </c>
       <c r="W106" t="str">
-        <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps) (portfolio)</v>
+        <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps) (portfolio)</v>
       </c>
       <c r="X106" t="str">
         <v>Y</v>
@@ -10260,7 +10350,7 @@
 </v>
       </c>
       <c r="AA106" t="str">
-        <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps) (business_segment)</v>
+        <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps) (business_segment)</v>
       </c>
       <c r="AB106" t="str">
         <v/>
@@ -10268,17 +10358,17 @@
     </row>
     <row r="107" xml:space="preserve">
       <c r="A107" t="str">
-        <v>RSK-008</v>
+        <v>RSK-006</v>
       </c>
       <c r="B107" t="str" xml:space="preserve">
-        <v xml:space="preserve">Categorizes exposures by internal credit risk level into distribution buckets based on counterparty internal risk rating; enables monitoring of credit quality distribution, concentration, and deterioration via rating migration.
+        <v xml:space="preserve">Derived directional classification indicating whether the internal credit rating has changed month over month: upgraded (e.g. 3 to 1), downgraded (e.g. 1 to 3), or remained stable (remained costant month-over month) compared to the prior reporting period. Note when this is displayed at an aggregated Line of Business or portfolio level, it is determined by the month-over-month change of the average rating at this level. Provides migration trend insight and serves as an early warning indicator of credit quality movement to support proactive risk management and escalation decisions.
 </v>
       </c>
       <c r="C107" t="str">
-        <v>Internal Risk Rating Bucket</v>
+        <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable)</v>
       </c>
       <c r="D107" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read internal_risk_rating_bucket_code from facility_exposure_snapshot for each facility.
+        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility as-of reporting date.
 </v>
       </c>
       <c r="E107" t="str">
@@ -10297,11 +10387,11 @@
         <v>Raw</v>
       </c>
       <c r="J107" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read internal_risk_rating_bucket_code from facility_exposure_snapshot for each facility.
+        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility as-of reporting date.
 </v>
       </c>
       <c r="K107" t="str">
-        <v>Internal Risk Rating Bucket (facility)</v>
+        <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable) (facility)</v>
       </c>
       <c r="L107" t="str">
         <v>Y</v>
@@ -10310,11 +10400,11 @@
         <v>Agg</v>
       </c>
       <c r="N107" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating bucket per counterparty.
+        <v xml:space="preserve">SUM of facility-level risk_rating_status per counterparty.
 </v>
       </c>
       <c r="O107" t="str">
-        <v>Internal Risk Rating Bucket (counterparty)</v>
+        <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable) (counterparty)</v>
       </c>
       <c r="P107" t="str">
         <v>Y</v>
@@ -10323,11 +10413,11 @@
         <v>Agg</v>
       </c>
       <c r="R107" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating bucket per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level risk_rating_status per L3 desk segment.
 </v>
       </c>
       <c r="S107" t="str">
-        <v>Internal Risk Rating Bucket (desk)</v>
+        <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable) (desk)</v>
       </c>
       <c r="T107" t="str">
         <v>Y</v>
@@ -10336,11 +10426,11 @@
         <v>Agg</v>
       </c>
       <c r="V107" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating bucket per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level risk_rating_status per L2 portfolio segment.
 </v>
       </c>
       <c r="W107" t="str">
-        <v>Internal Risk Rating Bucket (portfolio)</v>
+        <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable) (portfolio)</v>
       </c>
       <c r="X107" t="str">
         <v>Y</v>
@@ -10349,11 +10439,11 @@
         <v>Agg</v>
       </c>
       <c r="Z107" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating bucket per L1 business segment.
+        <v xml:space="preserve">SUM of facility-level risk_rating_status per L1 business segment segment.
 </v>
       </c>
       <c r="AA107" t="str">
-        <v>Internal Risk Rating Bucket (business_segment)</v>
+        <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable) (business_segment)</v>
       </c>
       <c r="AB107" t="str">
         <v/>
@@ -10361,106 +10451,385 @@
     </row>
     <row r="108" xml:space="preserve">
       <c r="A108" t="str">
+        <v>RSK-007</v>
+      </c>
+      <c r="B108" t="str" xml:space="preserve">
+        <v xml:space="preserve">Numerical representation of internal risk rating migration (month over month changes) expressed in notch movement (positive or negative). Positive step changes are identified when there is an upgrade, from 3 to 1and the step change is +2, where as the negative step change is identified when there is a downgrade from 5 to 8 and the step change is -3. Note when this is displayed at an aggregated Line of Business or portfolio level, it is determined by the month-over-month change of the average rating at this level. Quantifies magnitude of credit change and enables portfolio-level migration analysis, stress testing sensitivity, and risk trend measurement.
+</v>
+      </c>
+      <c r="C108" t="str">
+        <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps)</v>
+      </c>
+      <c r="D108" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read risk_rating_change_steps from counterparty_rating_observation for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="E108" t="str">
+        <v/>
+      </c>
+      <c r="F108" t="str">
+        <v/>
+      </c>
+      <c r="G108" t="str">
+        <v/>
+      </c>
+      <c r="H108" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I108" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J108" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read risk_rating_change_steps from counterparty_rating_observation for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="K108" t="str">
+        <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps) (facility)</v>
+      </c>
+      <c r="L108" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M108" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N108" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per counterparty.
+</v>
+      </c>
+      <c r="O108" t="str">
+        <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps) (counterparty)</v>
+      </c>
+      <c r="P108" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q108" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R108" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per L3 desk segment.
+</v>
+      </c>
+      <c r="S108" t="str">
+        <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps) (desk)</v>
+      </c>
+      <c r="T108" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U108" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V108" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W108" t="str">
+        <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps) (portfolio)</v>
+      </c>
+      <c r="X108" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y108" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z108" t="str" xml:space="preserve">
+        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per L1 business segment segment.
+</v>
+      </c>
+      <c r="AA108" t="str">
+        <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps) (business_segment)</v>
+      </c>
+      <c r="AB108" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="109" xml:space="preserve">
+      <c r="A109" t="str">
+        <v>RSK-008</v>
+      </c>
+      <c r="B109" t="str" xml:space="preserve">
+        <v xml:space="preserve">Categorizes exposures by internal credit risk level into distribution buckets based on counterparty internal risk rating; enables monitoring of credit quality distribution, concentration, and deterioration via rating migration.
+</v>
+      </c>
+      <c r="C109" t="str">
+        <v>Internal Risk Rating Bucket</v>
+      </c>
+      <c r="D109" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read internal_risk_rating_bucket_code from facility_exposure_snapshot for each facility.
+</v>
+      </c>
+      <c r="E109" t="str">
+        <v/>
+      </c>
+      <c r="F109" t="str">
+        <v/>
+      </c>
+      <c r="G109" t="str">
+        <v/>
+      </c>
+      <c r="H109" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I109" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J109" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read internal_risk_rating_bucket_code from facility_exposure_snapshot for each facility.
+</v>
+      </c>
+      <c r="K109" t="str">
+        <v>Internal Risk Rating Bucket (facility)</v>
+      </c>
+      <c r="L109" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M109" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N109" t="str" xml:space="preserve">
+        <v xml:space="preserve">COUNT of facilities with risk rating bucket per counterparty.
+</v>
+      </c>
+      <c r="O109" t="str">
+        <v>Internal Risk Rating Bucket (counterparty)</v>
+      </c>
+      <c r="P109" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q109" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R109" t="str" xml:space="preserve">
+        <v xml:space="preserve">COUNT of facilities with risk rating bucket per L3 desk segment.
+</v>
+      </c>
+      <c r="S109" t="str">
+        <v>Internal Risk Rating Bucket (desk)</v>
+      </c>
+      <c r="T109" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U109" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V109" t="str" xml:space="preserve">
+        <v xml:space="preserve">COUNT of facilities with risk rating bucket per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W109" t="str">
+        <v>Internal Risk Rating Bucket (portfolio)</v>
+      </c>
+      <c r="X109" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y109" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z109" t="str" xml:space="preserve">
+        <v xml:space="preserve">COUNT of facilities with risk rating bucket per L1 business segment.
+</v>
+      </c>
+      <c r="AA109" t="str">
+        <v>Internal Risk Rating Bucket (business_segment)</v>
+      </c>
+      <c r="AB109" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="110" xml:space="preserve">
+      <c r="A110" t="str">
         <v>RSK-009</v>
       </c>
-      <c r="B108" t="str" xml:space="preserve">
+      <c r="B110" t="str" xml:space="preserve">
         <v xml:space="preserve">Committed facility amount as a percentage of underlying collateral value. Higher LTV indicates greater loss severity risk in the event of default. A core risk metric for secured lending portfolios.
 </v>
       </c>
-      <c r="C108" t="str">
+      <c r="C110" t="str">
         <v>Loan-to-Value Ratio (%)</v>
       </c>
-      <c r="D108" t="str" xml:space="preserve">
+      <c r="D110" t="str" xml:space="preserve">
         <v xml:space="preserve">Aggregate collateral per facility (a facility may have multiple collateral assets),
 then compute LTV = committed_facility_amt / SUM(current_valuation_usd) * 100.
 </v>
       </c>
-      <c r="E108" t="str">
-        <v/>
-      </c>
-      <c r="F108" t="str">
-        <v/>
-      </c>
-      <c r="G108" t="str">
-        <v/>
-      </c>
-      <c r="H108" t="str">
-        <v>Y</v>
-      </c>
-      <c r="I108" t="str">
+      <c r="E110" t="str">
+        <v/>
+      </c>
+      <c r="F110" t="str">
+        <v/>
+      </c>
+      <c r="G110" t="str">
+        <v/>
+      </c>
+      <c r="H110" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I110" t="str">
         <v>Raw</v>
       </c>
-      <c r="J108" t="str" xml:space="preserve">
+      <c r="J110" t="str" xml:space="preserve">
         <v xml:space="preserve">Aggregate collateral per facility (a facility may have multiple collateral assets),
 then compute LTV = committed_facility_amt / SUM(current_valuation_usd) * 100.
 </v>
       </c>
-      <c r="K108" t="str">
+      <c r="K110" t="str">
         <v>Loan-to-Value Ratio (%) (facility)</v>
       </c>
-      <c r="L108" t="str">
-        <v>Y</v>
-      </c>
-      <c r="M108" t="str">
-        <v>Calc</v>
-      </c>
-      <c r="N108" t="str" xml:space="preserve">
+      <c r="L110" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M110" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="N110" t="str" xml:space="preserve">
         <v xml:space="preserve">SUM(committed_facility_amt) / SUM(current_valuation_usd) * 100.0
 per counterparty. Re-derives ratio from summed components.
 </v>
       </c>
-      <c r="O108" t="str">
+      <c r="O110" t="str">
         <v>Loan-to-Value Ratio (%) (counterparty)</v>
       </c>
-      <c r="P108" t="str">
-        <v>Y</v>
-      </c>
-      <c r="Q108" t="str">
-        <v>Calc</v>
-      </c>
-      <c r="R108" t="str" xml:space="preserve">
+      <c r="P110" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q110" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="R110" t="str" xml:space="preserve">
         <v xml:space="preserve">SUM(committed_facility_amt) / SUM(current_valuation_usd) * 100.0
 per L3 desk segment. Re-derives ratio from summed components.
 </v>
       </c>
-      <c r="S108" t="str">
+      <c r="S110" t="str">
         <v>Loan-to-Value Ratio (%) (desk)</v>
       </c>
-      <c r="T108" t="str">
-        <v>Y</v>
-      </c>
-      <c r="U108" t="str">
-        <v>Calc</v>
-      </c>
-      <c r="V108" t="str" xml:space="preserve">
+      <c r="T110" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U110" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="V110" t="str" xml:space="preserve">
         <v xml:space="preserve">SUM(committed_facility_amt) / SUM(current_valuation_usd) * 100.0
 per L2 portfolio segment. Re-derives ratio from summed components.
 </v>
       </c>
-      <c r="W108" t="str">
+      <c r="W110" t="str">
         <v>Loan-to-Value Ratio (%) (portfolio)</v>
       </c>
-      <c r="X108" t="str">
-        <v>Y</v>
-      </c>
-      <c r="Y108" t="str">
-        <v>Calc</v>
-      </c>
-      <c r="Z108" t="str" xml:space="preserve">
+      <c r="X110" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y110" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="Z110" t="str" xml:space="preserve">
         <v xml:space="preserve">SUM(committed_facility_amt) / SUM(current_valuation_usd) * 100.0
 per L1 business segment. Re-derives ratio from summed components.
 </v>
       </c>
-      <c r="AA108" t="str">
+      <c r="AA110" t="str">
         <v>Loan-to-Value Ratio (%) (business_segment)</v>
       </c>
-      <c r="AB108" t="str">
+      <c r="AB110" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="111" xml:space="preserve">
+      <c r="A111" t="str">
+        <v>RSK-010</v>
+      </c>
+      <c r="B111" t="str" xml:space="preserve">
+        <v xml:space="preserve">Internal risk rating expressed as a numeric notch value. At facility level, reads the internal_risk_rating from the latest facility risk snapshot and maps it to a numeric rating_value via the rating_scale_dim reference table. At counterparty level, maps the counterparty's internal_risk_rating to a numeric notch. At desk, portfolio, and business segment levels, computes the average rating notch across distinct counterparties in the segment, then rounds to the nearest integer for a representative rating grade. Lower values indicate better credit quality.
+</v>
+      </c>
+      <c r="C111" t="str">
+        <v>Internal Risk Rating</v>
+      </c>
+      <c r="D111" t="str" xml:space="preserve">
+        <v xml:space="preserve">For each facility, read the internal_risk_rating from the latest facility_risk_snapshot (MAX as_of_date), then join to rating_scale_dim to convert the rating string to a numeric rating_value (notch ordinal). Uses MIN(rating_value) to handle potential duplicate dim matches.
+</v>
+      </c>
+      <c r="E111" t="str">
+        <v/>
+      </c>
+      <c r="F111" t="str">
+        <v/>
+      </c>
+      <c r="G111" t="str">
+        <v/>
+      </c>
+      <c r="H111" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I111" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J111" t="str" xml:space="preserve">
+        <v xml:space="preserve">For each facility, read the internal_risk_rating from the latest facility_risk_snapshot (MAX as_of_date), then join to rating_scale_dim to convert the rating string to a numeric rating_value (notch ordinal). Uses MIN(rating_value) to handle potential duplicate dim matches.
+</v>
+      </c>
+      <c r="K111" t="str">
+        <v>Internal Risk Rating (facility)</v>
+      </c>
+      <c r="L111" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M111" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="N111" t="str" xml:space="preserve">
+        <v xml:space="preserve">For each counterparty, read the internal_risk_rating from the counterparty table, then join to rating_scale_dim to convert to a numeric rating_value. Uses MIN(rating_value) for deduplication.
+</v>
+      </c>
+      <c r="O111" t="str">
+        <v>Internal Risk Rating (counterparty)</v>
+      </c>
+      <c r="P111" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q111" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="R111" t="str" xml:space="preserve">
+        <v xml:space="preserve">Average internal risk rating notch across distinct counterparties in each L3 desk segment. Inner query ensures each counterparty is counted once per segment (avoids weighting by facility count). Result is rounded to nearest integer for a representative rating grade. Uses EBT direct join for L3 desk lookup.
+</v>
+      </c>
+      <c r="S111" t="str">
+        <v>Internal Risk Rating (desk)</v>
+      </c>
+      <c r="T111" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U111" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="V111" t="str" xml:space="preserve">
+        <v xml:space="preserve">Average internal risk rating notch across distinct counterparties per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id. Each counterparty counted once per portfolio for a true counterparty-level average, then rounded.
+</v>
+      </c>
+      <c r="W111" t="str">
+        <v>Internal Risk Rating (portfolio)</v>
+      </c>
+      <c r="X111" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y111" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="Z111" t="str" xml:space="preserve">
+        <v xml:space="preserve">Average internal risk rating notch across distinct counterparties per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1. Each counterparty counted once per business segment, averaged, and rounded to nearest integer for a representative segment rating grade.
+</v>
+      </c>
+      <c r="AA111" t="str">
+        <v>Internal Risk Rating (business_segment)</v>
+      </c>
+      <c r="AB111" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AB108"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AB111"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/metrics_dimensions_filled.xlsx
+++ b/data/metrics_dimensions_filled.xlsx
@@ -1539,14 +1539,14 @@
         <v>EXP-005</v>
       </c>
       <c r="B14" t="str" xml:space="preserve">
-        <v xml:space="preserve">The portion of total funding-related expense attributed to a specific exposure or portfolio. At facility level, calculated as SUM across all positions of (funded_amount * interest_rate), adjusted for bank share. At counterparty level, further adjusted by counterparty participation_pct. At desk/portfolio/segment levels, aggregated as SUM.
+        <v xml:space="preserve">The portion of total funding-related expense attributed to a specific exposure or portfolio. At facility level, calculated as SUM across all positions of (funded_amount * interest_rate), converted to USD via FX rate and adjusted for bank share. At counterparty level, further adjusted by counterparty participation_pct. At desk/portfolio/segment levels, aggregated as SUM via EBT hierarchy.
 </v>
       </c>
       <c r="C14" t="str">
         <v>Cost of Funds ($)</v>
       </c>
       <c r="D14" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each position under the facility: funded_amount * interest_rate = Position Cost of Funds. Adjusted by bank_share: SUM(funded_amount * interest_rate) * bank_share_pct / 100. Joins position_detail → position (for facility_id) → facility_master.
+        <v xml:space="preserve">For each position under the facility, compute funded_amount x interest_rate, convert to USD using the FX spot rate (defaults to 1.0 for USD positions). Sum across all positions, then multiply by the bank's share percentage. Result = annual cost of funds for this facility in USD.
 </v>
       </c>
       <c r="E14" t="str">
@@ -1565,7 +1565,7 @@
         <v>Calc</v>
       </c>
       <c r="J14" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each position under the facility: funded_amount * interest_rate = Position Cost of Funds. Adjusted by bank_share: SUM(funded_amount * interest_rate) * bank_share_pct / 100. Joins position_detail → position (for facility_id) → facility_master.
+        <v xml:space="preserve">For each position under the facility, compute funded_amount x interest_rate, convert to USD using the FX spot rate (defaults to 1.0 for USD positions). Sum across all positions, then multiply by the bank's share percentage. Result = annual cost of funds for this facility in USD.
 </v>
       </c>
       <c r="K14" t="str">
@@ -1578,7 +1578,7 @@
         <v>Agg</v>
       </c>
       <c r="N14" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each counterparty: SUM of facility-level cost of funds weighted by counterparty participation_pct from facility_counterparty_participation.
+        <v xml:space="preserve">Sum each facility's cost of funds (USD, bank-share-adjusted), then weight by the counterparty's participation percentage. Aggregates across all facilities where the counterparty has a current participation record.
 </v>
       </c>
       <c r="O14" t="str">
@@ -1591,7 +1591,7 @@
         <v>Agg</v>
       </c>
       <c r="R14" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level cost of funds (bank-share-adjusted) per L3 desk segment.
+        <v xml:space="preserve">Sum of facility-level cost of funds (USD, bank-share-adjusted) for all facilities assigned to each L3 desk segment in the organizational hierarchy.
 </v>
       </c>
       <c r="S14" t="str">
@@ -1604,7 +1604,7 @@
         <v>Agg</v>
       </c>
       <c r="V14" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level cost of funds (bank-share-adjusted) per L2 portfolio segment.
+        <v xml:space="preserve">Sum of facility-level cost of funds (USD, bank-share-adjusted) for all facilities within each L2 portfolio segment, traversing the EBT hierarchy from desk (L3) to portfolio (L2) via parent_segment_id.
 </v>
       </c>
       <c r="W14" t="str">
@@ -1617,7 +1617,7 @@
         <v>Agg</v>
       </c>
       <c r="Z14" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level cost of funds (bank-share-adjusted) per L1 business segment.
+        <v xml:space="preserve">Sum of facility-level cost of funds (USD, bank-share-adjusted) for all facilities within each L1 business segment, traversing the full EBT hierarchy from desk (L3) through portfolio (L2) to segment (L1).
 </v>
       </c>
       <c r="AA14" t="str">
@@ -1632,14 +1632,14 @@
         <v>EXP-006</v>
       </c>
       <c r="B15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure allocated to specific counterparty representing their share of the facility which the client can draw on. Concentration KPI measuring obligor dependency risk.
+        <v xml:space="preserve">Counterparty participation share in a facility — the percentage of a syndicated or participated facility allocated to a specific counterparty. At facility level, direct lookup from facility_counterparty_participation. At counterparty level, exposure-weighted average participation across all facilities. At desk/portfolio/segment, exposure-weighted average via EBT hierarchy. Key concentration KPI for Large Exposures Framework (LEX) and Single Counterparty Credit Limit (SCCL) compliance.
 </v>
       </c>
       <c r="C15" t="str">
         <v>Counterparty Share or Allocation (%)</v>
       </c>
       <c r="D15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of allocation_pct from facility_counterparty_participation.
+        <v xml:space="preserve">Direct lookup of participation_pct from facility_counterparty_participation for the primary counterparty on each facility. Uses current records only.
 </v>
       </c>
       <c r="E15" t="str">
@@ -1658,7 +1658,7 @@
         <v>Raw</v>
       </c>
       <c r="J15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of allocation_pct from facility_counterparty_participation.
+        <v xml:space="preserve">Direct lookup of participation_pct from facility_counterparty_participation for the primary counterparty on each facility. Uses current records only.
 </v>
       </c>
       <c r="K15" t="str">
@@ -1668,10 +1668,10 @@
         <v>Y</v>
       </c>
       <c r="M15" t="str">
-        <v>Raw</v>
+        <v>Avg</v>
       </c>
       <c r="N15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read allocation_pct per counterparty.
+        <v xml:space="preserve">Exposure-weighted average participation across all facilities for each counterparty. Weight = drawn_amount from facility_exposure_snapshot. Falls back to simple average if no exposure data available.
 </v>
       </c>
       <c r="O15" t="str">
@@ -1681,10 +1681,10 @@
         <v>Y</v>
       </c>
       <c r="Q15" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="R15" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level allocation_pct per L3 desk segment.
+        <v xml:space="preserve">Exposure-weighted average participation across all facilities per L3 desk segment via enterprise_business_taxonomy.
 </v>
       </c>
       <c r="S15" t="str">
@@ -1694,10 +1694,10 @@
         <v>Y</v>
       </c>
       <c r="U15" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="V15" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level allocation_pct per L2 portfolio segment.
+        <v xml:space="preserve">Exposure-weighted average participation across all facilities per L2 portfolio segment via enterprise_business_taxonomy hierarchy traversal.
 </v>
       </c>
       <c r="W15" t="str">
@@ -1707,10 +1707,10 @@
         <v>Y</v>
       </c>
       <c r="Y15" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="Z15" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level allocation_pct per L1 business segment segment.
+        <v xml:space="preserve">Exposure-weighted average participation across all facilities per L1 business segment via enterprise_business_taxonomy hierarchy traversal.
 </v>
       </c>
       <c r="AA15" t="str">
@@ -1725,14 +1725,14 @@
         <v>EXP-007</v>
       </c>
       <c r="B16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Flag identifying exposures requiring heightened monitoring due to elevated credit risk. Governance control used for enhanced monitoring, reserve consideration, and management reporting.
+        <v xml:space="preserve">Count of active Criticized risk flags across facilities. Early warning indicator of problem assets requiring heightened monitoring, reserve consideration, and management reporting. Sources from the risk_flag table filtering on flag_code = 'CRITICIZED' with uncleared status.
 </v>
       </c>
       <c r="C16" t="str">
         <v>Criticized Portfolios</v>
       </c>
       <c r="D16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if criticized rating (internal_risk_rating &gt;= 6), 0 otherwise.
+        <v xml:space="preserve">For each facility, count active risk flags where flag_code = 'CRITICIZED' and the flag has not been cleared (cleared_ts IS NULL).
 </v>
       </c>
       <c r="E16" t="str">
@@ -1748,10 +1748,10 @@
         <v>Y</v>
       </c>
       <c r="I16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="J16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if criticized rating (internal_risk_rating &gt;= 6), 0 otherwise.
+        <v xml:space="preserve">For each facility, count active risk flags where flag_code = 'CRITICIZED' and the flag has not been cleared (cleared_ts IS NULL).
 </v>
       </c>
       <c r="K16" t="str">
@@ -1761,10 +1761,10 @@
         <v>Y</v>
       </c>
       <c r="M16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="N16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per counterparty.
+        <v xml:space="preserve">For each counterparty, sum facility-level criticized flag counts across all facilities belonging to that counterparty.
 </v>
       </c>
       <c r="O16" t="str">
@@ -1774,10 +1774,10 @@
         <v>Y</v>
       </c>
       <c r="Q16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="R16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per L3 desk.
+        <v xml:space="preserve">Sum of criticized flag counts per L3 desk segment. Joins facility_master to enterprise_business_taxonomy via lob_segment_id.
 </v>
       </c>
       <c r="S16" t="str">
@@ -1787,10 +1787,10 @@
         <v>Y</v>
       </c>
       <c r="U16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="V16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per L2 portfolio.
+        <v xml:space="preserve">Sum of criticized flag counts per L2 portfolio segment. Traverses enterprise_business_taxonomy hierarchy from L3 to L2 via parent_segment_id.
 </v>
       </c>
       <c r="W16" t="str">
@@ -1800,10 +1800,10 @@
         <v>Y</v>
       </c>
       <c r="Y16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="Z16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per L1 business segment.
+        <v xml:space="preserve">Sum of criticized flag counts per L1 business segment. Full hierarchy traversal L3 → L2 → L1 via enterprise_business_taxonomy.
 </v>
       </c>
       <c r="AA16" t="str">
@@ -1818,14 +1818,14 @@
         <v>EXP-008</v>
       </c>
       <c r="B17" t="str" xml:space="preserve">
-        <v xml:space="preserve">Total exposure amount allocated across multiple legal entities. Supports intra-group concentration transparency.
+        <v xml:space="preserve">Total committed exposure amount (bank share) allocated across multiple legal entities for facilities flagged as cross-entity. Quantifies inter-entity concentration risk and supports intra-group transparency for GSIB reporting. Sources from counterparty_derived (L3) for the cross-entity flag and facility_exposure_snapshot (L2) for committed amounts.
 </v>
       </c>
       <c r="C17" t="str">
         <v>Cross Entity Exposure Amount</v>
       </c>
       <c r="D17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(total_cross_entity_exposure_usd) per facility from counterparty_exposure_summary. Weighted by bank share percentage.
+        <v xml:space="preserve">For each facility flagged as cross-entity, committed exposure amount weighted by the bank's participation share (bank_share_pct). Facilities without cross-entity flag are excluded.
 </v>
       </c>
       <c r="E17" t="str">
@@ -1844,7 +1844,7 @@
         <v>Agg</v>
       </c>
       <c r="J17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(total_cross_entity_exposure_usd) per facility from counterparty_exposure_summary. Weighted by bank share percentage.
+        <v xml:space="preserve">For each facility flagged as cross-entity, committed exposure amount weighted by the bank's participation share (bank_share_pct). Facilities without cross-entity flag are excluded.
 </v>
       </c>
       <c r="K17" t="str">
@@ -1857,7 +1857,7 @@
         <v>Agg</v>
       </c>
       <c r="N17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per counterparty.
+        <v xml:space="preserve">For each counterparty, sum of bank-share-weighted committed amounts across all facilities flagged as cross-entity.
 </v>
       </c>
       <c r="O17" t="str">
@@ -1870,7 +1870,7 @@
         <v>Agg</v>
       </c>
       <c r="R17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per L3 desk segment.
+        <v xml:space="preserve">Sum of cross-entity committed exposure per L3 desk segment via enterprise_business_taxonomy.
 </v>
       </c>
       <c r="S17" t="str">
@@ -1883,7 +1883,7 @@
         <v>Agg</v>
       </c>
       <c r="V17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per L2 portfolio segment.
+        <v xml:space="preserve">Sum of cross-entity committed exposure per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
 </v>
       </c>
       <c r="W17" t="str">
@@ -1896,7 +1896,7 @@
         <v>Agg</v>
       </c>
       <c r="Z17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per L1 business segment segment.
+        <v xml:space="preserve">Sum of cross-entity committed exposure per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
 </v>
       </c>
       <c r="AA17" t="str">
@@ -1911,14 +1911,14 @@
         <v>EXP-009</v>
       </c>
       <c r="B18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Number of days outstanding payments is past due as grouped into 3 "buckets", 0-30 Days, 31-60 Days, 61-90+ Days. Used for staging classification and early credit deterioration monitoring.
+        <v xml:space="preserve">Maximum days payment overdue per facility, calculated from raw payment records in the payment_ledger table. For each facility, identifies payments where applied amount &lt; amount due, computes days overdue as reporting date minus payment_due_date, takes the MAX, then classifies into buckets: 1 = 0-30 days, 2 = 31-60 days, 3 = 61-90+ days. At aggregate levels, reports the worst (MAX) bucket across constituents.
 </v>
       </c>
       <c r="C18" t="str">
         <v>Days Payment Overdue Bucket</v>
       </c>
       <c r="D18" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Facility_ID lookup the Payments records in the Payment Lockbox table, For each payment record where [Payment_Due_Date] &gt; Today() IF ([Pmt_Applied] &lt;[Pmt_Due])&gt;=1, THEN Today() - [Payment_due_date] ==[Days Overdue] SELECT MAX ([Days Overdue] then lookup in Payments Overdue bucket)
+        <v xml:space="preserve">For each facility, lookup payment records in payment_ledger where payment_due_date &lt; reporting date and payment_applied_amt &lt; payment_amount_due (underpaid). Calculate days overdue = reporting date minus payment_due_date. Take MAX days overdue, then classify into overdue bucket: 1 (0-30), 2 (31-60), 3 (61-90+).
 </v>
       </c>
       <c r="E18" t="str">
@@ -1937,7 +1937,7 @@
         <v>Calc</v>
       </c>
       <c r="J18" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Facility_ID lookup the Payments records in the Payment Lockbox table, For each payment record where [Payment_Due_Date] &gt; Today() IF ([Pmt_Applied] &lt;[Pmt_Due])&gt;=1, THEN Today() - [Payment_due_date] ==[Days Overdue] SELECT MAX ([Days Overdue] then lookup in Payments Overdue bucket)
+        <v xml:space="preserve">For each facility, lookup payment records in payment_ledger where payment_due_date &lt; reporting date and payment_applied_amt &lt; payment_amount_due (underpaid). Calculate days overdue = reporting date minus payment_due_date. Take MAX days overdue, then classify into overdue bucket: 1 (0-30), 2 (31-60), 3 (61-90+).
 </v>
       </c>
       <c r="K18" t="str">
@@ -1950,7 +1950,7 @@
         <v>Agg</v>
       </c>
       <c r="N18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per counterparty.
+        <v xml:space="preserve">Worst-case (MAX) overdue bucket across all facilities per counterparty. Identifies the most severely overdue facility for each borrower.
 </v>
       </c>
       <c r="O18" t="str">
@@ -1963,7 +1963,7 @@
         <v>Agg</v>
       </c>
       <c r="R18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per L3 desk segment.
+        <v xml:space="preserve">Worst-case (MAX) overdue bucket per L3 desk segment. Shows the most severe delinquency in each organizational unit.
 </v>
       </c>
       <c r="S18" t="str">
@@ -1976,7 +1976,7 @@
         <v>Agg</v>
       </c>
       <c r="V18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per L2 portfolio segment.
+        <v xml:space="preserve">Worst-case (MAX) overdue bucket per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
 </v>
       </c>
       <c r="W18" t="str">
@@ -1989,7 +1989,7 @@
         <v>Agg</v>
       </c>
       <c r="Z18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per L1 business segment.
+        <v xml:space="preserve">Worst-case (MAX) overdue bucket per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
 </v>
       </c>
       <c r="AA18" t="str">
@@ -2509,14 +2509,25 @@
         <v>EXP-015</v>
       </c>
       <c r="B24" t="str" xml:space="preserve">
-        <v xml:space="preserve">Expected Loss divided by Exposure. Derived KPI measuring loss intensity relative to exposure size, enabling comparative risk ranking across facilities or counterparties.
+        <v xml:space="preserve">Expected Loss as a percentage of committed exposure. Computed from L2 atomic risk parameters: PD (probability of default) × LGD (loss given default). At aggregate levels, uses sum-ratio rollup: SUM(PD × LGD × Committed) / SUM(Committed) × 100 — the exposure-weighted average EL rate. This ensures mathematically consistent aggregation (never averages pre-computed rates). Key credit risk quantification metric for comparing loss intensity across facilities, counterparties, and business segments.
+Ingredient derivation:
+  - PD (pd_pct): L2 facility_risk_snapshot — probability of default (%)
+  - LGD (lgd_pct): L2 facility_risk_snapshot — loss given default (%)
+  - Committed Exposure (committed_amount): L2 facility_exposure_snapshot — raw
+  - EL Rate = PD × LGD (at facility level, committed cancels in ratio)
+  - Aggregate EL Rate = SUM(PD × LGD × Committed) / SUM(Committed) × 100
 </v>
       </c>
       <c r="C24" t="str">
         <v>Expected Loss Rate (%)</v>
       </c>
       <c r="D24" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of expected_loss_rate_pct per facility.
+        <v xml:space="preserve">For each facility:
+  1. LOAD pd_pct, lgd_pct from l2.facility_risk_snapshot
+  2. LOAD committed_amount from l2.facility_exposure_snapshot
+  3. COMPUTE EL Rate = SUM(PD/100 × LGD/100 × Committed) / SUM(Committed) × 100
+     At facility grain, committed cancels → EL Rate ≈ PD × LGD / 100
+Ingredients: pd_pct (L2), lgd_pct (L2), committed_amount (L2)
 </v>
       </c>
       <c r="E24" t="str">
@@ -2532,10 +2543,15 @@
         <v>Y</v>
       </c>
       <c r="I24" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="J24" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of expected_loss_rate_pct per facility.
+        <v xml:space="preserve">For each facility:
+  1. LOAD pd_pct, lgd_pct from l2.facility_risk_snapshot
+  2. LOAD committed_amount from l2.facility_exposure_snapshot
+  3. COMPUTE EL Rate = SUM(PD/100 × LGD/100 × Committed) / SUM(Committed) × 100
+     At facility grain, committed cancels → EL Rate ≈ PD × LGD / 100
+Ingredients: pd_pct (L2), lgd_pct (L2), committed_amount (L2)
 </v>
       </c>
       <c r="K24" t="str">
@@ -2545,10 +2561,15 @@
         <v>Y</v>
       </c>
       <c r="M24" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N24" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level expected_loss_rate_pct per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD pd_pct, lgd_pct for all facilities belonging to this counterparty
+  2. LOAD committed_amount for each facility
+  3. CONVERT to USD via l2.fx_rate spot rate
+  4. COMPUTE SUM(PD × LGD × Committed × FX) / SUM(Committed × FX) × 100
+Sum-ratio rollup with FX: exposure-weighted average EL rate in USD terms.
 </v>
       </c>
       <c r="O24" t="str">
@@ -2558,10 +2579,14 @@
         <v>Y</v>
       </c>
       <c r="Q24" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="R24" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level expected_loss_rate_pct per L3 desk segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOOKUP managed_segment_id from enterprise_business_taxonomy
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(PD × LGD × Committed × FX) / SUM(Committed × FX) × 100
+Sum-ratio rollup: exposure-weighted average EL rate per desk.
 </v>
       </c>
       <c r="S24" t="str">
@@ -2571,10 +2596,14 @@
         <v>Y</v>
       </c>
       <c r="U24" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V24" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level expected_loss_rate_pct per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(PD × LGD × Committed × FX) / SUM(Committed × FX) × 100
+Sum-ratio rollup: exposure-weighted average EL rate per portfolio.
 </v>
       </c>
       <c r="W24" t="str">
@@ -2584,10 +2613,14 @@
         <v>Y</v>
       </c>
       <c r="Y24" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z24" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level expected_loss_rate_pct per L1 business segment segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(PD × LGD × Committed × FX) / SUM(Committed × FX) × 100
+Sum-ratio rollup: exposure-weighted average EL rate per segment.
 </v>
       </c>
       <c r="AA24" t="str">
@@ -2602,14 +2635,25 @@
         <v>EXP-016</v>
       </c>
       <c r="B25" t="str" xml:space="preserve">
-        <v xml:space="preserve">PD × LGD × Exposure expressed in USD. Calculated forward-looking loss metric supporting provisioning, capital planning, and stress testing analytics.
+        <v xml:space="preserve">Expected Loss in dollar terms: PD × LGD × Committed Exposure × Bank Share. Computed from L2 atomic risk parameters and exposure data — NOT from stressed scenarios. This is the base (unstressed) expected credit loss, the foundation for provisioning, capital planning, and CECL/IFRS 9 reserve estimation.
+Ingredient derivation:
+  - PD (pd_pct): L2 facility_risk_snapshot — probability of default (%)
+  - LGD (lgd_pct): L2 facility_risk_snapshot — loss given default (%)
+  - Committed Exposure (committed_amount): L2 facility_exposure_snapshot — raw
+  - Bank Share (bank_share_pct): L2 facility_exposure_snapshot — participation %
+  - EL = (PD/100) × (LGD/100) × Committed × (Bank Share/100)
+Rollup uses direct-sum: SUM(facility EL) at each aggregate level. FX conversion applied at aggregate levels for multi-currency portfolios.
 </v>
       </c>
       <c r="C25" t="str">
         <v>Expected Loss ($)</v>
       </c>
       <c r="D25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(stressed_expected_loss) per facility from stress_test_result. Weighted by bank share percentage.
+        <v xml:space="preserve">For each facility:
+  1. LOAD pd_pct, lgd_pct from l2.facility_risk_snapshot
+  2. LOAD committed_amount, bank_share_pct from l2.facility_exposure_snapshot
+  3. COMPUTE EL = (PD/100) × (LGD/100) × Committed × (Bank Share/100)
+Ingredients: pd_pct (L2), lgd_pct (L2), committed_amount (L2), bank_share_pct (L2)
 </v>
       </c>
       <c r="E25" t="str">
@@ -2625,10 +2669,14 @@
         <v>Y</v>
       </c>
       <c r="I25" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="J25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(stressed_expected_loss) per facility from stress_test_result. Weighted by bank share percentage.
+        <v xml:space="preserve">For each facility:
+  1. LOAD pd_pct, lgd_pct from l2.facility_risk_snapshot
+  2. LOAD committed_amount, bank_share_pct from l2.facility_exposure_snapshot
+  3. COMPUTE EL = (PD/100) × (LGD/100) × Committed × (Bank Share/100)
+Ingredients: pd_pct (L2), lgd_pct (L2), committed_amount (L2), bank_share_pct (L2)
 </v>
       </c>
       <c r="K25" t="str">
@@ -2641,7 +2689,11 @@
         <v>Agg</v>
       </c>
       <c r="N25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD facility-level EL for all facilities of this counterparty
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(facility EL × FX rate) = Counterparty EL (USD)
+Direct-sum rollup with FX conversion.
 </v>
       </c>
       <c r="O25" t="str">
@@ -2654,7 +2706,11 @@
         <v>Agg</v>
       </c>
       <c r="R25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per L3 desk segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOOKUP managed_segment_id from enterprise_business_taxonomy
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(facility EL × FX rate) per desk
+Direct-sum rollup with FX conversion.
 </v>
       </c>
       <c r="S25" t="str">
@@ -2667,7 +2723,11 @@
         <v>Agg</v>
       </c>
       <c r="V25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(facility EL × FX rate) per portfolio
+Direct-sum rollup with FX conversion.
 </v>
       </c>
       <c r="W25" t="str">
@@ -2680,7 +2740,11 @@
         <v>Agg</v>
       </c>
       <c r="Z25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per L1 business segment segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(facility EL × FX rate) per business segment
+Direct-sum rollup with FX conversion.
 </v>
       </c>
       <c r="AA25" t="str">
@@ -2702,11 +2766,21 @@
         <v>Undrawn Exposure ($)</v>
       </c>
       <c r="D26" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each active facility:
-1. SUM(funded_amount) from PRINCIPAL position_detail rows per facility
-2. Subtract from committed_facility_amt to get unfunded amount
-3. Multiply by COALESCE(bank_share_pct, 100) / 100 from facility_lender_allocation
-Ensures: Committed Exposure = Outstanding Exposure + Undrawn Exposure
+        <v xml:space="preserve">1. LOAD  l2.position  (pos)
+   WHERE pos.as_of_date = :as_of_date
+2. JOIN  l2.position_detail  (pdtl)
+   ON    pdtl.position_id = pos.position_id
+   AND   pdtl.detail_type = 'PRINCIPAL'
+3. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = pos.facility_id
+   WHERE fm.is_active_flag = 'Y'
+4. LEFT JOIN  l2.facility_lender_allocation  (fla)
+   ON    fla.facility_id = fm.facility_id
+   AND   fla.is_current_flag = 'Y'
+5. GROUP BY fm.facility_id
+6. COMPUTE
+   metric_value = (committed_facility_amt - SUM(funded_amount))
+                  * COALESCE(bank_share_pct, 100) / 100
 </v>
       </c>
       <c r="E26" t="str">
@@ -2725,11 +2799,21 @@
         <v>Calc</v>
       </c>
       <c r="J26" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each active facility:
-1. SUM(funded_amount) from PRINCIPAL position_detail rows per facility
-2. Subtract from committed_facility_amt to get unfunded amount
-3. Multiply by COALESCE(bank_share_pct, 100) / 100 from facility_lender_allocation
-Ensures: Committed Exposure = Outstanding Exposure + Undrawn Exposure
+        <v xml:space="preserve">1. LOAD  l2.position  (pos)
+   WHERE pos.as_of_date = :as_of_date
+2. JOIN  l2.position_detail  (pdtl)
+   ON    pdtl.position_id = pos.position_id
+   AND   pdtl.detail_type = 'PRINCIPAL'
+3. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = pos.facility_id
+   WHERE fm.is_active_flag = 'Y'
+4. LEFT JOIN  l2.facility_lender_allocation  (fla)
+   ON    fla.facility_id = fm.facility_id
+   AND   fla.is_current_flag = 'Y'
+5. GROUP BY fm.facility_id
+6. COMPUTE
+   metric_value = (committed_facility_amt - SUM(funded_amount))
+                  * COALESCE(bank_share_pct, 100) / 100
 </v>
       </c>
       <c r="K26" t="str">
@@ -2742,8 +2826,13 @@
         <v>Calc</v>
       </c>
       <c r="N26" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each counterparty, sum facility-level undrawn exposure weighted
-by participation_pct from facility_counterparty_participation.
+        <v xml:space="preserve">1. LOAD  facility-level undrawn exposure (subquery)
+2. JOIN  l2.facility_counterparty_participation  (fcp)
+   ON    fcp.facility_id = fac.facility_id
+   AND   fcp.is_current_flag = 'Y'
+3. GROUP BY fcp.counterparty_id
+4. COMPUTE
+   metric_value = SUM(facility_undrawn * participation_pct)
 </v>
       </c>
       <c r="O26" t="str">
@@ -2756,8 +2845,15 @@
         <v>Agg</v>
       </c>
       <c r="R26" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level undrawn exposure per L3 desk segment.
-Joins facility_master.lob_segment_id to enterprise_business_taxonomy.managed_segment_id.
+        <v xml:space="preserve">1. LOAD  facility-level undrawn exposure (subquery)
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = fac.facility_id
+3. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt)
+   ON    ebt.managed_segment_id = fm.lob_segment_id
+   AND   ebt.is_current_flag = 'Y'
+4. GROUP BY ebt.managed_segment_id
+5. COMPUTE
+   metric_value = SUM(facility_undrawn)
 </v>
       </c>
       <c r="S26" t="str">
@@ -2770,8 +2866,16 @@
         <v>Agg</v>
       </c>
       <c r="V26" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level undrawn exposure per L2 portfolio segment.
-Traverses L3 -&gt; L2 via parent_segment_id.
+        <v xml:space="preserve">1. LOAD  facility-level undrawn exposure (subquery)
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = fac.facility_id
+3. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l3)
+   ON    ebt_l3.managed_segment_id = fm.lob_segment_id
+4. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l2)
+   ON    ebt_l2.managed_segment_id = ebt_l3.parent_segment_id
+5. GROUP BY ebt_l2.managed_segment_id
+6. COMPUTE
+   metric_value = SUM(facility_undrawn)
 </v>
       </c>
       <c r="W26" t="str">
@@ -2784,8 +2888,18 @@
         <v>Agg</v>
       </c>
       <c r="Z26" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level undrawn exposure per L1 business segment.
-Traverses L3 -&gt; L2 -&gt; L1 via parent_segment_id chain.
+        <v xml:space="preserve">1. LOAD  facility-level undrawn exposure (subquery)
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = fac.facility_id
+3. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l3)
+   ON    ebt_l3.managed_segment_id = fm.lob_segment_id
+4. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l2)
+   ON    ebt_l2.managed_segment_id = ebt_l3.parent_segment_id
+5. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l1)
+   ON    ebt_l1.managed_segment_id = ebt_l2.parent_segment_id
+6. GROUP BY ebt_l1.managed_segment_id
+7. COMPUTE
+   metric_value = SUM(facility_undrawn)
 </v>
       </c>
       <c r="AA26" t="str">
@@ -2800,17 +2914,28 @@
         <v>EXP-018</v>
       </c>
       <c r="B27" t="str" xml:space="preserve">
-        <v xml:space="preserve">Bank-share-adjusted funded (drawn) exposure amount. Represents the portion of committed credit currently utilized by the borrower. Maps to FR Y-14Q Field 25 (Utilized Exposure Global, MDRM G075).
+        <v xml:space="preserve">Bank-share-adjusted funded (drawn) exposure amount. Represents the portion of committed credit currently utilized by the borrower. Maps to FR Y-14Q Field 25 (Utilized Exposure Global, MDRM G075). Counterparty level uses exposure_counterparty_attribution for risk-shifted attribution weighting per Basel III requirements.
 </v>
       </c>
       <c r="C27" t="str">
         <v>Outstanding Exposure ($)</v>
       </c>
       <c r="D27" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each active facility:
-1. Join position -&gt; position_detail on position_id (both as_of_date filtered)
-2. SUM(funded_amount) across all positions for the facility
-3. Multiply by COALESCE(bank_share_pct, 100) / 100 from facility_lender_allocation
+        <v xml:space="preserve">1. LOAD  l2.position  (pos)
+   WHERE pos.as_of_date = :as_of_date
+2. JOIN  l2.position_detail  (pdtl)
+   ON    pdtl.position_id = pos.position_id
+   AND   pdtl.detail_type = 'PRINCIPAL'
+3. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = pos.facility_id
+   WHERE fm.is_active_flag = 'Y'
+4. LEFT JOIN  l2.facility_lender_allocation  (fla)
+   ON    fla.facility_id = fm.facility_id
+   AND   fla.is_current_flag = 'Y'
+5. GROUP BY pos.facility_id
+6. COMPUTE
+   metric_value = SUM(funded_amount)
+                  * COALESCE(bank_share_pct, 100) / 100
 </v>
       </c>
       <c r="E27" t="str">
@@ -2829,10 +2954,21 @@
         <v>Calc</v>
       </c>
       <c r="J27" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each active facility:
-1. Join position -&gt; position_detail on position_id (both as_of_date filtered)
-2. SUM(funded_amount) across all positions for the facility
-3. Multiply by COALESCE(bank_share_pct, 100) / 100 from facility_lender_allocation
+        <v xml:space="preserve">1. LOAD  l2.position  (pos)
+   WHERE pos.as_of_date = :as_of_date
+2. JOIN  l2.position_detail  (pdtl)
+   ON    pdtl.position_id = pos.position_id
+   AND   pdtl.detail_type = 'PRINCIPAL'
+3. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = pos.facility_id
+   WHERE fm.is_active_flag = 'Y'
+4. LEFT JOIN  l2.facility_lender_allocation  (fla)
+   ON    fla.facility_id = fm.facility_id
+   AND   fla.is_current_flag = 'Y'
+5. GROUP BY pos.facility_id
+6. COMPUTE
+   metric_value = SUM(funded_amount)
+                  * COALESCE(bank_share_pct, 100) / 100
 </v>
       </c>
       <c r="K27" t="str">
@@ -2845,9 +2981,13 @@
         <v>Calc</v>
       </c>
       <c r="N27" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each counterparty, sum facility-level outstanding exposure weighted
-by participation_pct from facility_counterparty_participation.
-Uses contractual pro-rata basis per FR Y-14Q requirements.
+        <v xml:space="preserve">1. LOAD  facility-level outstanding exposure (subquery)
+2. JOIN  l2.exposure_counterparty_attribution  (eca)
+   ON    eca.facility_id = fac.facility_id
+   AND   eca.as_of_date = :as_of_date
+3. GROUP BY eca.counterparty_id
+4. COMPUTE
+   metric_value = SUM(facility_outstanding * attribution_pct)
 </v>
       </c>
       <c r="O27" t="str">
@@ -2860,8 +3000,15 @@
         <v>Agg</v>
       </c>
       <c r="R27" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level outstanding exposure per L3 desk segment.
-Joins facility_master.lob_segment_id to enterprise_business_taxonomy.managed_segment_id.
+        <v xml:space="preserve">1. LOAD  facility-level outstanding exposure (subquery)
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = fac.facility_id
+3. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt)
+   ON    ebt.managed_segment_id = fm.lob_segment_id
+   AND   ebt.is_current_flag = 'Y'
+4. GROUP BY ebt.managed_segment_id
+5. COMPUTE
+   metric_value = SUM(facility_outstanding)
 </v>
       </c>
       <c r="S27" t="str">
@@ -2874,8 +3021,16 @@
         <v>Agg</v>
       </c>
       <c r="V27" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level outstanding exposure per L2 portfolio segment.
-Traverses L3 -&gt; L2 via parent_segment_id.
+        <v xml:space="preserve">1. LOAD  facility-level outstanding exposure (subquery)
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = fac.facility_id
+3. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l3)
+   ON    ebt_l3.managed_segment_id = fm.lob_segment_id
+4. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l2)
+   ON    ebt_l2.managed_segment_id = ebt_l3.parent_segment_id
+5. GROUP BY ebt_l2.managed_segment_id
+6. COMPUTE
+   metric_value = SUM(facility_outstanding)
 </v>
       </c>
       <c r="W27" t="str">
@@ -2888,8 +3043,14 @@
         <v>Agg</v>
       </c>
       <c r="Z27" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level outstanding exposure per L1 business segment.
-Traverses L3 -&gt; L2 -&gt; L1 via parent_segment_id chain.
+        <v xml:space="preserve">1. LOAD  facility-level outstanding exposure (subquery)
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = fac.facility_id
+3. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l3, ebt_l2, ebt_l1)
+   Traverse L3 -&gt; L2 -&gt; L1 via parent_segment_id chain
+4. GROUP BY ebt_l1.managed_segment_id
+5. COMPUTE
+   metric_value = SUM(facility_outstanding)
 </v>
       </c>
       <c r="AA27" t="str">
@@ -2904,14 +3065,15 @@
         <v>EXP-019</v>
       </c>
       <c r="B28" t="str" xml:space="preserve">
-        <v xml:space="preserve">Maximum approved credit exposure authorized for the counterparty or Line of Business segment in USD. Represents formal risk appetite allocation and governance control threshold.
+        <v xml:space="preserve">Maximum approved credit exposure authorized for the counterparty or Line of Business segment in USD. Sourced directly from the limit_rule reference table. Represents formal risk appetite allocation and governance control threshold set by the Credit Risk Committee. Not applicable at individual facility level — limits are set at counterparty and organizational hierarchy levels.
 </v>
       </c>
       <c r="C28" t="str">
         <v>Exposure Limit ($)</v>
       </c>
       <c r="D28" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read limit_amt from lob_exposure_summary for each facility as-of reporting date.
+        <v xml:space="preserve">Not applicable — exposure limits are set at counterparty and
+organizational levels, not per individual facility. Returns NULL.
 </v>
       </c>
       <c r="E28" t="str">
@@ -2930,7 +3092,8 @@
         <v>Raw</v>
       </c>
       <c r="J28" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read limit_amt from lob_exposure_summary for each facility as-of reporting date.
+        <v xml:space="preserve">Not applicable — exposure limits are set at counterparty and
+organizational levels, not per individual facility. Returns NULL.
 </v>
       </c>
       <c r="K28" t="str">
@@ -2943,7 +3106,12 @@
         <v>Raw</v>
       </c>
       <c r="N28" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read limit_amt per counterparty.
+        <v xml:space="preserve">1. LOAD  l1.limit_rule  (lr)
+   WHERE lr.is_current_flag = 'Y'
+   AND   lr.counterparty_id IS NOT NULL
+2. GROUP BY lr.counterparty_id
+3. COMPUTE
+   metric_value = SUM(limit_amount_usd)
 </v>
       </c>
       <c r="O28" t="str">
@@ -2953,10 +3121,18 @@
         <v>Y</v>
       </c>
       <c r="Q28" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="R28" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level limit_amt per L3 desk segment.
+        <v xml:space="preserve">1. LOAD  l1.limit_rule  (lr)
+   WHERE lr.is_current_flag = 'Y'
+   AND   lr.lob_segment_id IS NOT NULL
+2. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt)
+   ON    ebt.managed_segment_id = lr.lob_segment_id
+   AND   ebt.is_current_flag = 'Y'
+3. GROUP BY lr.lob_segment_id
+4. COMPUTE
+   metric_value = SUM(limit_amount_usd)
 </v>
       </c>
       <c r="S28" t="str">
@@ -2966,10 +3142,18 @@
         <v>Y</v>
       </c>
       <c r="U28" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="V28" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level limit_amt per L2 portfolio segment.
+        <v xml:space="preserve">1. LOAD  l1.limit_rule  (lr)
+   WHERE lr.is_current_flag = 'Y'
+   AND   lr.lob_segment_id IS NOT NULL
+2. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt)
+   ON    ebt.managed_segment_id = lr.lob_segment_id
+   AND   ebt.is_current_flag = 'Y'
+3. GROUP BY lr.lob_segment_id
+4. COMPUTE
+   metric_value = SUM(limit_amount_usd)
 </v>
       </c>
       <c r="W28" t="str">
@@ -2979,10 +3163,18 @@
         <v>Y</v>
       </c>
       <c r="Y28" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="Z28" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level limit_amt per L1 business segment segment.
+        <v xml:space="preserve">1. LOAD  l1.limit_rule  (lr)
+   WHERE lr.is_current_flag = 'Y'
+   AND   lr.lob_segment_id IS NOT NULL
+2. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt)
+   ON    ebt.managed_segment_id = lr.lob_segment_id
+   AND   ebt.is_current_flag = 'Y'
+3. GROUP BY lr.lob_segment_id
+4. COMPUTE
+   metric_value = SUM(limit_amount_usd)
 </v>
       </c>
       <c r="AA28" t="str">
@@ -2997,14 +3189,25 @@
         <v>EXP-020</v>
       </c>
       <c r="B29" t="str" xml:space="preserve">
-        <v xml:space="preserve">The estimated exposure amount (in USD) expected to be outstanding if the borrower defaults.
+        <v xml:space="preserve">Estimated exposure amount outstanding if the borrower defaults, computed from L2 atomic inputs per Basel III: EAD = OB + CCF × Undrawn, where OB = drawn/funded amount, CCF = credit conversion factor from facility_risk_snapshot, and Undrawn = committed minus drawn from facility_exposure_snapshot. Bank-share adjusted via facility_exposure_snapshot. At counterparty level, weighted by participation_pct from facility_counterparty_participation per FR Y-14Q requirements.
 </v>
       </c>
       <c r="C29" t="str">
         <v>Exposure at Default ($)</v>
       </c>
       <c r="D29" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read exposure_at_default from credit_event_facility_link for each facility as-of reporting date.
+        <v xml:space="preserve">1. LOAD  l2.facility_exposure_snapshot  (fes)
+   WHERE fes.as_of_date = :as_of_date
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = fes.facility_id
+   WHERE fm.is_active_flag = 'Y'
+3. LEFT JOIN  l2.facility_risk_snapshot  (frs)
+   ON    frs.facility_id = fes.facility_id
+   AND   frs.as_of_date = fes.as_of_date
+4. GROUP BY fes.facility_id
+5. COMPUTE
+   metric_value = (drawn_amount + CCF * undrawn_amount)
+                  * bank_share_pct / 100
 </v>
       </c>
       <c r="E29" t="str">
@@ -3020,10 +3223,21 @@
         <v>Y</v>
       </c>
       <c r="I29" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="J29" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read exposure_at_default from credit_event_facility_link for each facility as-of reporting date.
+        <v xml:space="preserve">1. LOAD  l2.facility_exposure_snapshot  (fes)
+   WHERE fes.as_of_date = :as_of_date
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = fes.facility_id
+   WHERE fm.is_active_flag = 'Y'
+3. LEFT JOIN  l2.facility_risk_snapshot  (frs)
+   ON    frs.facility_id = fes.facility_id
+   AND   frs.as_of_date = fes.as_of_date
+4. GROUP BY fes.facility_id
+5. COMPUTE
+   metric_value = (drawn_amount + CCF * undrawn_amount)
+                  * bank_share_pct / 100
 </v>
       </c>
       <c r="K29" t="str">
@@ -3033,10 +3247,22 @@
         <v>Y</v>
       </c>
       <c r="M29" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N29" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level exposure_at_default per counterparty.
+        <v xml:space="preserve">1. LOAD  l2.facility_exposure_snapshot  (fes)
+   WHERE fes.as_of_date = :as_of_date
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = fes.facility_id
+3. LEFT JOIN  l2.facility_risk_snapshot  (frs)
+   ON    frs.facility_id = fes.facility_id
+4. JOIN  l2.facility_counterparty_participation  (fcp)
+   ON    fcp.facility_id = fes.facility_id
+   AND   fcp.is_current_flag = 'Y'
+5. GROUP BY fcp.counterparty_id
+6. COMPUTE
+   metric_value = SUM((drawn + CCF * undrawn) * bank_share / 100
+                  * participation_pct)
 </v>
       </c>
       <c r="O29" t="str">
@@ -3049,7 +3275,15 @@
         <v>Agg</v>
       </c>
       <c r="R29" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level exposure_at_default per L3 desk segment.
+        <v xml:space="preserve">1. LOAD  facility-level EAD (subquery)
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = fac.facility_id
+3. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt)
+   ON    ebt.managed_segment_id = fm.lob_segment_id
+   AND   ebt.is_current_flag = 'Y'
+4. GROUP BY ebt.managed_segment_id
+5. COMPUTE
+   metric_value = SUM(facility_ead)
 </v>
       </c>
       <c r="S29" t="str">
@@ -3062,7 +3296,13 @@
         <v>Agg</v>
       </c>
       <c r="V29" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level exposure_at_default per L2 portfolio segment.
+        <v xml:space="preserve">1. LOAD  facility-level EAD (subquery)
+2. JOIN  l2.facility_master  (fm)
+3. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l3, ebt_l2)
+   Traverse L3 -&gt; L2 via parent_segment_id
+4. GROUP BY ebt_l2.managed_segment_id
+5. COMPUTE
+   metric_value = SUM(facility_ead)
 </v>
       </c>
       <c r="W29" t="str">
@@ -3075,7 +3315,13 @@
         <v>Agg</v>
       </c>
       <c r="Z29" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level exposure_at_default per L1 business segment segment.
+        <v xml:space="preserve">1. LOAD  facility-level EAD (subquery)
+2. JOIN  l2.facility_master  (fm)
+3. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l3, ebt_l2, ebt_l1)
+   Traverse L3 -&gt; L2 -&gt; L1 via parent_segment_id chain
+4. GROUP BY ebt_l1.managed_segment_id
+5. COMPUTE
+   metric_value = SUM(facility_ead)
 </v>
       </c>
       <c r="AA29" t="str">
@@ -5796,14 +6042,15 @@
         <v>PRC-003</v>
       </c>
       <c r="B59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of exposures within portfolio with approved pricing or policy exceptions. Derived governance KPI measuring policy discipline and risk culture strength.
+        <v xml:space="preserve">Percentage of facilities with approved pricing or policy exceptions. Computed as COUNT(exception facilities) / COUNT(total facilities) × 100. Sourced from L2 facility_pricing_snapshot — the atomic pricing record — using the is_pricing_exception_flag. At aggregate levels, uses count-ratio rollup: re-counts exceptions and totals across all constituent facilities, never averages pre-computed rates. Key governance KPI measuring policy discipline, risk culture strength, and pricing override frequency.
 </v>
       </c>
       <c r="C59" t="str">
         <v>Exception Rate (%)</v>
       </c>
       <c r="D59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if pricing exception, 0 otherwise.
+        <v xml:space="preserve">Binary flag: 1.0 if pricing exception approved, 0.0 otherwise.
+Ingredients: is_pricing_exception_flag (L2 facility_pricing_snapshot)
 </v>
       </c>
       <c r="E59" t="str">
@@ -5822,7 +6069,8 @@
         <v>Calc</v>
       </c>
       <c r="J59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if pricing exception, 0 otherwise.
+        <v xml:space="preserve">Binary flag: 1.0 if pricing exception approved, 0.0 otherwise.
+Ingredients: is_pricing_exception_flag (L2 facility_pricing_snapshot)
 </v>
       </c>
       <c r="K59" t="str">
@@ -5835,7 +6083,10 @@
         <v>Calc</v>
       </c>
       <c r="N59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with pricing exception per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD is_pricing_exception_flag for all facilities of this counterparty
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup: re-counts from facility-level flags.
 </v>
       </c>
       <c r="O59" t="str">
@@ -5848,7 +6099,10 @@
         <v>Calc</v>
       </c>
       <c r="R59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with pricing exception per L3 desk.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOOKUP managed_segment_id from enterprise_business_taxonomy
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup per desk.
 </v>
       </c>
       <c r="S59" t="str">
@@ -5861,7 +6115,10 @@
         <v>Calc</v>
       </c>
       <c r="V59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with pricing exception per L2 portfolio.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup per portfolio.
 </v>
       </c>
       <c r="W59" t="str">
@@ -5874,7 +6131,10 @@
         <v>Calc</v>
       </c>
       <c r="Z59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with pricing exception per L1 business segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup per business segment.
 </v>
       </c>
       <c r="AA59" t="str">
@@ -6830,14 +7090,14 @@
         <v>REF-004</v>
       </c>
       <c r="B70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Unique system identifier assigned to the borrower or obligor. Used for exposure aggregation and risk consolidation.
+        <v xml:space="preserve">Unique system identifier assigned to the borrower or obligor. Used for exposure aggregation and risk consolidation across the GSIB. At facility level, returns the counterparty_id linked to each facility. At upper levels, returns COUNT(DISTINCT counterparty_id) — the number of unique obligors in each organizational segment.
 </v>
       </c>
       <c r="C70" t="str">
         <v>Counterparty ID</v>
       </c>
       <c r="D70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">Direct lookup of counterparty_id from facility_master for each active facility. Uses current records only (SCD2 filtered).
 </v>
       </c>
       <c r="E70" t="str">
@@ -6856,7 +7116,7 @@
         <v>Raw</v>
       </c>
       <c r="J70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">Direct lookup of counterparty_id from facility_master for each active facility. Uses current records only (SCD2 filtered).
 </v>
       </c>
       <c r="K70" t="str">
@@ -6869,7 +7129,7 @@
         <v>Raw</v>
       </c>
       <c r="N70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">Identity — returns counterparty_id for each current counterparty.
 </v>
       </c>
       <c r="O70" t="str">
@@ -6882,7 +7142,7 @@
         <v>Agg</v>
       </c>
       <c r="R70" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L3 desk segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L3 desk segment — number of unique obligors in each desk.
 </v>
       </c>
       <c r="S70" t="str">
@@ -6895,7 +7155,7 @@
         <v>Agg</v>
       </c>
       <c r="V70" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L2 portfolio segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L2 portfolio segment — number of unique obligors in each portfolio.
 </v>
       </c>
       <c r="W70" t="str">
@@ -6908,7 +7168,7 @@
         <v>Agg</v>
       </c>
       <c r="Z70" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L1 business segment segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L1 business segment — number of unique obligors in each business segment.
 </v>
       </c>
       <c r="AA70" t="str">
@@ -6923,14 +7183,14 @@
         <v>REF-005</v>
       </c>
       <c r="B71" t="str" xml:space="preserve">
-        <v xml:space="preserve">Descriptive name of the counterparty as documented in the credit agreement. Used for reporting clarity and operational reference.
+        <v xml:space="preserve">Legal name of the counterparty as documented in the credit agreement. At facility level, returns the counterparty_id (numeric proxy for the name since metric values are numeric). At counterparty level, identity lookup. At upper levels, COUNT(DISTINCT counterparty_id) — number of unique named obligors per organizational segment. Used for reporting clarity and operational reference across all regulatory submissions.
 </v>
       </c>
       <c r="C71" t="str">
         <v>Counterparty Name</v>
       </c>
       <c r="D71" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read legal_name from counterparty for each facility's counterparty.
+        <v xml:space="preserve">Lookup counterparty_id from facility_master for each active facility. The numeric counterparty_id serves as proxy for the legal name (string values resolved via counterparty dimension join at display time). Uses current records only.
 </v>
       </c>
       <c r="E71" t="str">
@@ -6949,7 +7209,7 @@
         <v>Raw</v>
       </c>
       <c r="J71" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read legal_name from counterparty for each facility's counterparty.
+        <v xml:space="preserve">Lookup counterparty_id from facility_master for each active facility. The numeric counterparty_id serves as proxy for the legal name (string values resolved via counterparty dimension join at display time). Uses current records only.
 </v>
       </c>
       <c r="K71" t="str">
@@ -6959,10 +7219,10 @@
         <v>Y</v>
       </c>
       <c r="M71" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="N71" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with counterparty name per counterparty.
+        <v xml:space="preserve">Identity — returns counterparty_id for each current counterparty. Legal name resolved via counterparty dimension join at display time.
 </v>
       </c>
       <c r="O71" t="str">
@@ -6975,7 +7235,7 @@
         <v>Agg</v>
       </c>
       <c r="R71" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with counterparty name per L3 desk segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L3 desk segment — number of unique named obligors in each desk.
 </v>
       </c>
       <c r="S71" t="str">
@@ -6988,7 +7248,7 @@
         <v>Agg</v>
       </c>
       <c r="V71" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with counterparty name per L2 portfolio segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L2 portfolio segment — number of unique named obligors in each portfolio.
 </v>
       </c>
       <c r="W71" t="str">
@@ -7001,7 +7261,7 @@
         <v>Agg</v>
       </c>
       <c r="Z71" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with counterparty name per L1 business segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L1 business segment — number of unique named obligors in each business segment.
 </v>
       </c>
       <c r="AA71" t="str">
@@ -7016,14 +7276,14 @@
         <v>REF-006</v>
       </c>
       <c r="B72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Country of risk or booking location. Supports geographic concentration and sovereign risk analysis.
+        <v xml:space="preserve">Country of risk derived from the counterparty's domicile. At facility level, returns a numeric country identifier (via counterparty → country_dim join path). At counterparty level, identity lookup. At desk/portfolio/segment levels, COUNT(DISTINCT country_code) — geographic diversification indicator showing the number of unique countries represented. Supports FFIEC 009 Country Exposure Report and Basel III geographic concentration analysis.
 </v>
       </c>
       <c r="C72" t="str">
         <v>Country</v>
       </c>
       <c r="D72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of country_name from country_dim.
+        <v xml:space="preserve">Lookup country for each facility via counterparty → country_dim join path. Returns counterparty_id as numeric proxy (country_name resolved at display time via dimension join). Uses current records only.
 </v>
       </c>
       <c r="E72" t="str">
@@ -7042,7 +7302,7 @@
         <v>Raw</v>
       </c>
       <c r="J72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of country_name from country_dim.
+        <v xml:space="preserve">Lookup country for each facility via counterparty → country_dim join path. Returns counterparty_id as numeric proxy (country_name resolved at display time via dimension join). Uses current records only.
 </v>
       </c>
       <c r="K72" t="str">
@@ -7055,7 +7315,7 @@
         <v>Raw</v>
       </c>
       <c r="N72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read country_name per counterparty.
+        <v xml:space="preserve">Lookup country for each counterparty via country_code → country_dim join. Returns counterparty_id as numeric proxy.
 </v>
       </c>
       <c r="O72" t="str">
@@ -7068,7 +7328,7 @@
         <v>Agg</v>
       </c>
       <c r="R72" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level country_name per L3 desk segment.
+        <v xml:space="preserve">COUNT(DISTINCT country_code) per L3 desk segment — number of unique countries represented, a geographic diversification indicator.
 </v>
       </c>
       <c r="S72" t="str">
@@ -7081,7 +7341,7 @@
         <v>Agg</v>
       </c>
       <c r="V72" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level country_name per L2 portfolio segment.
+        <v xml:space="preserve">COUNT(DISTINCT country_code) per L2 portfolio segment — number of unique countries represented in each portfolio.
 </v>
       </c>
       <c r="W72" t="str">
@@ -7094,7 +7354,7 @@
         <v>Agg</v>
       </c>
       <c r="Z72" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level country_name per L1 business segment segment.
+        <v xml:space="preserve">COUNT(DISTINCT country_code) per L1 business segment — geographic diversification at the highest organizational level.
 </v>
       </c>
       <c r="AA72" t="str">
@@ -7109,14 +7369,14 @@
         <v>REF-007</v>
       </c>
       <c r="B73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Unique identifier linking facility to governing credit agreement documentation.
+        <v xml:space="preserve">Unique identifier linking each facility to its governing credit agreement documentation. Used for contract tracking, facility-to-agreement linkage, and regulatory reporting. At counterparty level, returns count of distinct credit agreements per borrower.
 </v>
       </c>
       <c r="C73" t="str">
         <v>Credit Agreement ID</v>
       </c>
       <c r="D73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of credit_agreement_id from credit_agreement_master.
+        <v xml:space="preserve">Direct lookup of credit_agreement_id for each active facility via facility_master joined to credit_agreement_master.
 </v>
       </c>
       <c r="E73" t="str">
@@ -7135,7 +7395,7 @@
         <v>Raw</v>
       </c>
       <c r="J73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of credit_agreement_id from credit_agreement_master.
+        <v xml:space="preserve">Direct lookup of credit_agreement_id for each active facility via facility_master joined to credit_agreement_master.
 </v>
       </c>
       <c r="K73" t="str">
@@ -7145,10 +7405,10 @@
         <v>Y</v>
       </c>
       <c r="M73" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="N73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read credit_agreement_id per counterparty.
+        <v xml:space="preserve">Count of distinct credit agreements per counterparty. Provides visibility into borrower complexity and multi-agreement relationships.
 </v>
       </c>
       <c r="O73" t="str">
@@ -7161,7 +7421,7 @@
         <v>Agg</v>
       </c>
       <c r="R73" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level credit_agreement_id per L3 desk segment.
+        <v xml:space="preserve">Count of distinct credit agreements per L3 desk segment via enterprise_business_taxonomy.
 </v>
       </c>
       <c r="S73" t="str">
@@ -7174,7 +7434,7 @@
         <v>Agg</v>
       </c>
       <c r="V73" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level credit_agreement_id per L2 portfolio segment.
+        <v xml:space="preserve">Count of distinct credit agreements per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
 </v>
       </c>
       <c r="W73" t="str">
@@ -7187,7 +7447,7 @@
         <v>Agg</v>
       </c>
       <c r="Z73" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level credit_agreement_id per L1 business segment segment.
+        <v xml:space="preserve">Count of distinct credit agreements per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
 </v>
       </c>
       <c r="AA73" t="str">
@@ -7295,7 +7555,7 @@
         <v>REF-009</v>
       </c>
       <c r="B75" t="str" xml:space="preserve">
-        <v xml:space="preserve">Date on which loan or contract became legally effective.
+        <v xml:space="preserve">Date on which loan or contract became legally effective. Sourced directly from facility_master. At aggregate levels, returns the earliest origination date (MIN) across constituent facilities — indicating the oldest vintage in the book. Key contract lifecycle tracking attribute for vintage analysis and portfolio seasoning assessment.
 </v>
       </c>
       <c r="C75" t="str">
@@ -7303,6 +7563,7 @@
       </c>
       <c r="D75" t="str" xml:space="preserve">
         <v xml:space="preserve">Direct lookup of origination_date from facility_master.
+Ingredients: origination_date (L2 facility_master — raw field)
 </v>
       </c>
       <c r="E75" t="str">
@@ -7322,6 +7583,7 @@
       </c>
       <c r="J75" t="str" xml:space="preserve">
         <v xml:space="preserve">Direct lookup of origination_date from facility_master.
+Ingredients: origination_date (L2 facility_master — raw field)
 </v>
       </c>
       <c r="K75" t="str">
@@ -7334,7 +7596,10 @@
         <v>Agg</v>
       </c>
       <c r="N75" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level origination_date) per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD origination_date from l2.facility_master for all active facilities
+  2. COMPUTE MIN(origination_date) — earliest contract vintage
+Indicates the oldest banking relationship tenure for this counterparty.
 </v>
       </c>
       <c r="O75" t="str">
@@ -7347,7 +7612,10 @@
         <v>Agg</v>
       </c>
       <c r="R75" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level origination_date per L3 desk segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOAD origination_date from l2.facility_master
+  2. JOIN l1.enterprise_business_taxonomy on lob_segment_id
+  3. COMPUTE MIN(origination_date) — earliest vintage in desk book
 </v>
       </c>
       <c r="S75" t="str">
@@ -7360,7 +7628,9 @@
         <v>Agg</v>
       </c>
       <c r="V75" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level origination_date per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. COMPUTE MIN(origination_date) — earliest vintage in portfolio
 </v>
       </c>
       <c r="W75" t="str">
@@ -7373,7 +7643,9 @@
         <v>Agg</v>
       </c>
       <c r="Z75" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level origination_date per L1 business segment segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. COMPUTE MIN(origination_date) — earliest vintage in business segment
 </v>
       </c>
       <c r="AA75" t="str">
@@ -9620,14 +9892,14 @@
         <v>RSK-001</v>
       </c>
       <c r="B100" t="str" xml:space="preserve">
-        <v xml:space="preserve">Most recent internal credit rating assigned at reporting date. Used for segmentation and exposure-weighted risk aggregation.
+        <v xml:space="preserve">Risk rating tier derived from counterparty probability of default (PD). Each counterparty's pd_annual is matched against the risk_rating_tier_dim reference table (pd_min_pct / pd_max_pct boundaries) to assign a tier classification. At facility level, the tier is inherited from the owning counterparty. At aggregate levels, MAX (worst-case) tier ordinal is reported.
 </v>
       </c>
       <c r="C100" t="str">
         <v>Risk Rating Tier</v>
       </c>
       <c r="D100" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility.
+        <v xml:space="preserve">For each facility, inherit the risk rating tier from the owning counterparty. Join facility_master to counterparty, then range-match counterparty pd_annual against risk_rating_tier_dim to derive the tier ordinal (display_order).
 </v>
       </c>
       <c r="E100" t="str">
@@ -9643,10 +9915,10 @@
         <v>Y</v>
       </c>
       <c r="I100" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="J100" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility.
+        <v xml:space="preserve">For each facility, inherit the risk rating tier from the owning counterparty. Join facility_master to counterparty, then range-match counterparty pd_annual against risk_rating_tier_dim to derive the tier ordinal (display_order).
 </v>
       </c>
       <c r="K100" t="str">
@@ -9656,10 +9928,10 @@
         <v>Y</v>
       </c>
       <c r="M100" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N100" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating per counterparty.
+        <v xml:space="preserve">For each counterparty, look up pd_annual and range-match against risk_rating_tier_dim where pd_annual &gt;= pd_min_pct AND pd_annual &lt; pd_max_pct. Returns the tier ordinal (display_order). Counterparties with NULL PD receive tier 0 (unrated).
 </v>
       </c>
       <c r="O100" t="str">
@@ -9672,7 +9944,7 @@
         <v>Agg</v>
       </c>
       <c r="R100" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating per L3 desk segment.
+        <v xml:space="preserve">Worst-case (MAX) risk rating tier ordinal across all counterparties in the L3 desk segment. Higher ordinal = riskier tier. Full tier distribution available via counterparty-level drill-down.
 </v>
       </c>
       <c r="S100" t="str">
@@ -9685,7 +9957,7 @@
         <v>Agg</v>
       </c>
       <c r="V100" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating per L2 portfolio segment.
+        <v xml:space="preserve">Worst-case (MAX) risk rating tier ordinal per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
 </v>
       </c>
       <c r="W100" t="str">
@@ -9698,7 +9970,7 @@
         <v>Agg</v>
       </c>
       <c r="Z100" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating per L1 business segment.
+        <v xml:space="preserve">Worst-case (MAX) risk rating tier ordinal per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
 </v>
       </c>
       <c r="AA100" t="str">
@@ -9713,14 +9985,23 @@
         <v>RSK-002</v>
       </c>
       <c r="B101" t="str" xml:space="preserve">
-        <v xml:space="preserve">Current external credit agency rating assigned to the obligor. Used for benchmarking, regulatory reporting, and external credit risk validation. Sourced based on external Rating provider (S&amp;P, Moodys, Fitch) - populated based on firm's preferred recognized rating provider.
+        <v xml:space="preserve">External credit agency rating expressed as a numeric notch value from the rating_scale_dim. At facility/counterparty levels, returns the raw notch of the external rating. At aggregate levels (desk, portfolio, segment), computes the exposure-weighted average notch across all positions, rounded to the nearest whole notch. Lower notch = better rating (e.g., 1=AAA, 21=D). Sourced from position.external_risk_rating, mapped to rating_scale_dim.rating_value.
 </v>
       </c>
       <c r="C101" t="str">
         <v>Risk Rating - External Rating</v>
       </c>
       <c r="D101" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read external_risk_rating from position for each facility as-of reporting date.
+        <v xml:space="preserve">1. LOAD  l2.position  (pos)
+   WHERE pos.as_of_date = :as_of_date
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = pos.facility_id
+   WHERE fm.is_active_flag = 'Y'
+3. LEFT JOIN  l1.rating_scale_dim  (rs)
+   ON    rs.rating_notch = pos.external_risk_rating
+   AND   rs.is_current_flag = 'Y'
+4. COMPUTE
+   metric_value = rs.rating_value
 </v>
       </c>
       <c r="E101" t="str">
@@ -9739,7 +10020,16 @@
         <v>Raw</v>
       </c>
       <c r="J101" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read external_risk_rating from position for each facility as-of reporting date.
+        <v xml:space="preserve">1. LOAD  l2.position  (pos)
+   WHERE pos.as_of_date = :as_of_date
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = pos.facility_id
+   WHERE fm.is_active_flag = 'Y'
+3. LEFT JOIN  l1.rating_scale_dim  (rs)
+   ON    rs.rating_notch = pos.external_risk_rating
+   AND   rs.is_current_flag = 'Y'
+4. COMPUTE
+   metric_value = rs.rating_value
 </v>
       </c>
       <c r="K101" t="str">
@@ -9752,7 +10042,15 @@
         <v>Raw</v>
       </c>
       <c r="N101" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read external_risk_rating per counterparty.
+        <v xml:space="preserve">1. LOAD  l2.position  (pos)
+   WHERE pos.as_of_date = :as_of_date
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = pos.facility_id
+3. LEFT JOIN  l1.rating_scale_dim  (rs)
+   ON    rs.rating_notch = pos.external_risk_rating
+4. GROUP BY fm.counterparty_id
+5. COMPUTE
+   metric_value = ROUND(AVG(rating_value))
 </v>
       </c>
       <c r="O101" t="str">
@@ -9762,10 +10060,20 @@
         <v>Y</v>
       </c>
       <c r="Q101" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="R101" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level external_risk_rating per L3 desk segment.
+        <v xml:space="preserve">1. LOAD  l2.position  (pos)
+   WHERE pos.as_of_date = :as_of_date
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = pos.facility_id
+3. LEFT JOIN  l1.rating_scale_dim  (rs)
+   ON    rs.rating_notch = pos.external_risk_rating
+4. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt)
+   ON    ebt.managed_segment_id = fm.lob_segment_id
+5. GROUP BY ebt.managed_segment_id
+6. COMPUTE
+   metric_value = ROUND(AVG(rating_value))
 </v>
       </c>
       <c r="S101" t="str">
@@ -9775,10 +10083,19 @@
         <v>Y</v>
       </c>
       <c r="U101" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="V101" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level external_risk_rating per L2 portfolio segment.
+        <v xml:space="preserve">1. LOAD  l2.position  (pos)
+   WHERE pos.as_of_date = :as_of_date
+2. JOIN  l2.facility_master  (fm)
+3. LEFT JOIN  l1.rating_scale_dim  (rs)
+   ON    rs.rating_notch = pos.external_risk_rating
+4. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l3, ebt_l2)
+   Traverse L3 -&gt; L2 via parent_segment_id
+5. GROUP BY ebt_l2.managed_segment_id
+6. COMPUTE
+   metric_value = ROUND(AVG(rating_value))
 </v>
       </c>
       <c r="W101" t="str">
@@ -9788,10 +10105,19 @@
         <v>Y</v>
       </c>
       <c r="Y101" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="Z101" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level external_risk_rating per L1 business segment segment.
+        <v xml:space="preserve">1. LOAD  l2.position  (pos)
+   WHERE pos.as_of_date = :as_of_date
+2. JOIN  l2.facility_master  (fm)
+3. LEFT JOIN  l1.rating_scale_dim  (rs)
+   ON    rs.rating_notch = pos.external_risk_rating
+4. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l3, ebt_l2, ebt_l1)
+   Traverse L3 -&gt; L2 -&gt; L1 via parent_segment_id chain
+5. GROUP BY ebt_l1.managed_segment_id
+6. COMPUTE
+   metric_value = ROUND(AVG(rating_value))
 </v>
       </c>
       <c r="AA101" t="str">

--- a/data/metrics_dimensions_filled.xlsx
+++ b/data/metrics_dimensions_filled.xlsx
@@ -1539,14 +1539,14 @@
         <v>EXP-005</v>
       </c>
       <c r="B14" t="str" xml:space="preserve">
-        <v xml:space="preserve">The portion of total funding-related expense attributed to a specific exposure or portfolio. At facility level, calculated as SUM across all positions of (funded_amount * interest_rate), adjusted for bank share. At counterparty level, further adjusted by counterparty participation_pct. At desk/portfolio/segment levels, aggregated as SUM.
+        <v xml:space="preserve">The portion of total funding-related expense attributed to a specific exposure or portfolio. At facility level, calculated as SUM across all positions of (funded_amount * interest_rate), converted to USD via FX rate and adjusted for bank share. At counterparty level, further adjusted by counterparty participation_pct. At desk/portfolio/segment levels, aggregated as SUM via EBT hierarchy.
 </v>
       </c>
       <c r="C14" t="str">
         <v>Cost of Funds ($)</v>
       </c>
       <c r="D14" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each position under the facility: funded_amount * interest_rate = Position Cost of Funds. Adjusted by bank_share: SUM(funded_amount * interest_rate) * bank_share_pct / 100. Joins position_detail → position (for facility_id) → facility_master.
+        <v xml:space="preserve">For each position under the facility, compute funded_amount x interest_rate, convert to USD using the FX spot rate (defaults to 1.0 for USD positions). Sum across all positions, then multiply by the bank's share percentage. Result = annual cost of funds for this facility in USD.
 </v>
       </c>
       <c r="E14" t="str">
@@ -1565,7 +1565,7 @@
         <v>Calc</v>
       </c>
       <c r="J14" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each position under the facility: funded_amount * interest_rate = Position Cost of Funds. Adjusted by bank_share: SUM(funded_amount * interest_rate) * bank_share_pct / 100. Joins position_detail → position (for facility_id) → facility_master.
+        <v xml:space="preserve">For each position under the facility, compute funded_amount x interest_rate, convert to USD using the FX spot rate (defaults to 1.0 for USD positions). Sum across all positions, then multiply by the bank's share percentage. Result = annual cost of funds for this facility in USD.
 </v>
       </c>
       <c r="K14" t="str">
@@ -1578,7 +1578,7 @@
         <v>Agg</v>
       </c>
       <c r="N14" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each counterparty: SUM of facility-level cost of funds weighted by counterparty participation_pct from facility_counterparty_participation.
+        <v xml:space="preserve">Sum each facility's cost of funds (USD, bank-share-adjusted), then weight by the counterparty's participation percentage. Aggregates across all facilities where the counterparty has a current participation record.
 </v>
       </c>
       <c r="O14" t="str">
@@ -1591,7 +1591,7 @@
         <v>Agg</v>
       </c>
       <c r="R14" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level cost of funds (bank-share-adjusted) per L3 desk segment.
+        <v xml:space="preserve">Sum of facility-level cost of funds (USD, bank-share-adjusted) for all facilities assigned to each L3 desk segment in the organizational hierarchy.
 </v>
       </c>
       <c r="S14" t="str">
@@ -1604,7 +1604,7 @@
         <v>Agg</v>
       </c>
       <c r="V14" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level cost of funds (bank-share-adjusted) per L2 portfolio segment.
+        <v xml:space="preserve">Sum of facility-level cost of funds (USD, bank-share-adjusted) for all facilities within each L2 portfolio segment, traversing the EBT hierarchy from desk (L3) to portfolio (L2) via parent_segment_id.
 </v>
       </c>
       <c r="W14" t="str">
@@ -1617,7 +1617,7 @@
         <v>Agg</v>
       </c>
       <c r="Z14" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level cost of funds (bank-share-adjusted) per L1 business segment.
+        <v xml:space="preserve">Sum of facility-level cost of funds (USD, bank-share-adjusted) for all facilities within each L1 business segment, traversing the full EBT hierarchy from desk (L3) through portfolio (L2) to segment (L1).
 </v>
       </c>
       <c r="AA14" t="str">
@@ -1632,14 +1632,14 @@
         <v>EXP-006</v>
       </c>
       <c r="B15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure allocated to specific counterparty representing their share of the facility which the client can draw on. Concentration KPI measuring obligor dependency risk.
+        <v xml:space="preserve">Counterparty participation share in a facility — the percentage of a syndicated or participated facility allocated to a specific counterparty. At facility level, direct lookup from facility_counterparty_participation. At counterparty level, exposure-weighted average participation across all facilities. At desk/portfolio/segment, exposure-weighted average via EBT hierarchy. Key concentration KPI for Large Exposures Framework (LEX) and Single Counterparty Credit Limit (SCCL) compliance.
 </v>
       </c>
       <c r="C15" t="str">
         <v>Counterparty Share or Allocation (%)</v>
       </c>
       <c r="D15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of allocation_pct from facility_counterparty_participation.
+        <v xml:space="preserve">Direct lookup of participation_pct from facility_counterparty_participation for the primary counterparty on each facility. Uses current records only.
 </v>
       </c>
       <c r="E15" t="str">
@@ -1658,7 +1658,7 @@
         <v>Raw</v>
       </c>
       <c r="J15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of allocation_pct from facility_counterparty_participation.
+        <v xml:space="preserve">Direct lookup of participation_pct from facility_counterparty_participation for the primary counterparty on each facility. Uses current records only.
 </v>
       </c>
       <c r="K15" t="str">
@@ -1668,10 +1668,10 @@
         <v>Y</v>
       </c>
       <c r="M15" t="str">
-        <v>Raw</v>
+        <v>Avg</v>
       </c>
       <c r="N15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read allocation_pct per counterparty.
+        <v xml:space="preserve">Exposure-weighted average participation across all facilities for each counterparty. Weight = drawn_amount from facility_exposure_snapshot. Falls back to simple average if no exposure data available.
 </v>
       </c>
       <c r="O15" t="str">
@@ -1681,10 +1681,10 @@
         <v>Y</v>
       </c>
       <c r="Q15" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="R15" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level allocation_pct per L3 desk segment.
+        <v xml:space="preserve">Exposure-weighted average participation across all facilities per L3 desk segment via enterprise_business_taxonomy.
 </v>
       </c>
       <c r="S15" t="str">
@@ -1694,10 +1694,10 @@
         <v>Y</v>
       </c>
       <c r="U15" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="V15" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level allocation_pct per L2 portfolio segment.
+        <v xml:space="preserve">Exposure-weighted average participation across all facilities per L2 portfolio segment via enterprise_business_taxonomy hierarchy traversal.
 </v>
       </c>
       <c r="W15" t="str">
@@ -1707,10 +1707,10 @@
         <v>Y</v>
       </c>
       <c r="Y15" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="Z15" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level allocation_pct per L1 business segment segment.
+        <v xml:space="preserve">Exposure-weighted average participation across all facilities per L1 business segment via enterprise_business_taxonomy hierarchy traversal.
 </v>
       </c>
       <c r="AA15" t="str">
@@ -1725,14 +1725,14 @@
         <v>EXP-007</v>
       </c>
       <c r="B16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Flag identifying exposures requiring heightened monitoring due to elevated credit risk. Governance control used for enhanced monitoring, reserve consideration, and management reporting.
+        <v xml:space="preserve">Count of active Criticized risk flags across facilities. Early warning indicator of problem assets requiring heightened monitoring, reserve consideration, and management reporting. Sources from the risk_flag table filtering on flag_code = 'CRITICIZED' with uncleared status.
 </v>
       </c>
       <c r="C16" t="str">
         <v>Criticized Portfolios</v>
       </c>
       <c r="D16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if criticized rating (internal_risk_rating &gt;= 6), 0 otherwise.
+        <v xml:space="preserve">For each facility, count active risk flags where flag_code = 'CRITICIZED' and the flag has not been cleared (cleared_ts IS NULL).
 </v>
       </c>
       <c r="E16" t="str">
@@ -1748,10 +1748,10 @@
         <v>Y</v>
       </c>
       <c r="I16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="J16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if criticized rating (internal_risk_rating &gt;= 6), 0 otherwise.
+        <v xml:space="preserve">For each facility, count active risk flags where flag_code = 'CRITICIZED' and the flag has not been cleared (cleared_ts IS NULL).
 </v>
       </c>
       <c r="K16" t="str">
@@ -1761,10 +1761,10 @@
         <v>Y</v>
       </c>
       <c r="M16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="N16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per counterparty.
+        <v xml:space="preserve">For each counterparty, sum facility-level criticized flag counts across all facilities belonging to that counterparty.
 </v>
       </c>
       <c r="O16" t="str">
@@ -1774,10 +1774,10 @@
         <v>Y</v>
       </c>
       <c r="Q16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="R16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per L3 desk.
+        <v xml:space="preserve">Sum of criticized flag counts per L3 desk segment. Joins facility_master to enterprise_business_taxonomy via lob_segment_id.
 </v>
       </c>
       <c r="S16" t="str">
@@ -1787,10 +1787,10 @@
         <v>Y</v>
       </c>
       <c r="U16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="V16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per L2 portfolio.
+        <v xml:space="preserve">Sum of criticized flag counts per L2 portfolio segment. Traverses enterprise_business_taxonomy hierarchy from L3 to L2 via parent_segment_id.
 </v>
       </c>
       <c r="W16" t="str">
@@ -1800,10 +1800,10 @@
         <v>Y</v>
       </c>
       <c r="Y16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="Z16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per L1 business segment.
+        <v xml:space="preserve">Sum of criticized flag counts per L1 business segment. Full hierarchy traversal L3 → L2 → L1 via enterprise_business_taxonomy.
 </v>
       </c>
       <c r="AA16" t="str">
@@ -1818,14 +1818,14 @@
         <v>EXP-008</v>
       </c>
       <c r="B17" t="str" xml:space="preserve">
-        <v xml:space="preserve">Total exposure amount allocated across multiple legal entities. Supports intra-group concentration transparency.
+        <v xml:space="preserve">Total committed exposure amount (bank share) allocated across multiple legal entities for facilities flagged as cross-entity. Quantifies inter-entity concentration risk and supports intra-group transparency for GSIB reporting. Sources from counterparty_derived (L3) for the cross-entity flag and facility_exposure_snapshot (L2) for committed amounts.
 </v>
       </c>
       <c r="C17" t="str">
         <v>Cross Entity Exposure Amount</v>
       </c>
       <c r="D17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(total_cross_entity_exposure_usd) per facility from counterparty_exposure_summary. Weighted by bank share percentage.
+        <v xml:space="preserve">For each facility flagged as cross-entity, committed exposure amount weighted by the bank's participation share (bank_share_pct). Facilities without cross-entity flag are excluded.
 </v>
       </c>
       <c r="E17" t="str">
@@ -1844,7 +1844,7 @@
         <v>Agg</v>
       </c>
       <c r="J17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(total_cross_entity_exposure_usd) per facility from counterparty_exposure_summary. Weighted by bank share percentage.
+        <v xml:space="preserve">For each facility flagged as cross-entity, committed exposure amount weighted by the bank's participation share (bank_share_pct). Facilities without cross-entity flag are excluded.
 </v>
       </c>
       <c r="K17" t="str">
@@ -1857,7 +1857,7 @@
         <v>Agg</v>
       </c>
       <c r="N17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per counterparty.
+        <v xml:space="preserve">For each counterparty, sum of bank-share-weighted committed amounts across all facilities flagged as cross-entity.
 </v>
       </c>
       <c r="O17" t="str">
@@ -1870,7 +1870,7 @@
         <v>Agg</v>
       </c>
       <c r="R17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per L3 desk segment.
+        <v xml:space="preserve">Sum of cross-entity committed exposure per L3 desk segment via enterprise_business_taxonomy.
 </v>
       </c>
       <c r="S17" t="str">
@@ -1883,7 +1883,7 @@
         <v>Agg</v>
       </c>
       <c r="V17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per L2 portfolio segment.
+        <v xml:space="preserve">Sum of cross-entity committed exposure per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
 </v>
       </c>
       <c r="W17" t="str">
@@ -1896,7 +1896,7 @@
         <v>Agg</v>
       </c>
       <c r="Z17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per L1 business segment segment.
+        <v xml:space="preserve">Sum of cross-entity committed exposure per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
 </v>
       </c>
       <c r="AA17" t="str">
@@ -1911,14 +1911,14 @@
         <v>EXP-009</v>
       </c>
       <c r="B18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Number of days outstanding payments is past due as grouped into 3 "buckets", 0-30 Days, 31-60 Days, 61-90+ Days. Used for staging classification and early credit deterioration monitoring.
+        <v xml:space="preserve">Maximum days payment overdue per facility, calculated from raw payment records in the payment_ledger table. For each facility, identifies payments where applied amount &lt; amount due, computes days overdue as reporting date minus payment_due_date, takes the MAX, then classifies into buckets: 1 = 0-30 days, 2 = 31-60 days, 3 = 61-90+ days. At aggregate levels, reports the worst (MAX) bucket across constituents.
 </v>
       </c>
       <c r="C18" t="str">
         <v>Days Payment Overdue Bucket</v>
       </c>
       <c r="D18" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Facility_ID lookup the Payments records in the Payment Lockbox table, For each payment record where [Payment_Due_Date] &gt; Today() IF ([Pmt_Applied] &lt;[Pmt_Due])&gt;=1, THEN Today() - [Payment_due_date] ==[Days Overdue] SELECT MAX ([Days Overdue] then lookup in Payments Overdue bucket)
+        <v xml:space="preserve">For each facility, lookup payment records in payment_ledger where payment_due_date &lt; reporting date and payment_applied_amt &lt; payment_amount_due (underpaid). Calculate days overdue = reporting date minus payment_due_date. Take MAX days overdue, then classify into overdue bucket: 1 (0-30), 2 (31-60), 3 (61-90+).
 </v>
       </c>
       <c r="E18" t="str">
@@ -1937,7 +1937,7 @@
         <v>Calc</v>
       </c>
       <c r="J18" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Facility_ID lookup the Payments records in the Payment Lockbox table, For each payment record where [Payment_Due_Date] &gt; Today() IF ([Pmt_Applied] &lt;[Pmt_Due])&gt;=1, THEN Today() - [Payment_due_date] ==[Days Overdue] SELECT MAX ([Days Overdue] then lookup in Payments Overdue bucket)
+        <v xml:space="preserve">For each facility, lookup payment records in payment_ledger where payment_due_date &lt; reporting date and payment_applied_amt &lt; payment_amount_due (underpaid). Calculate days overdue = reporting date minus payment_due_date. Take MAX days overdue, then classify into overdue bucket: 1 (0-30), 2 (31-60), 3 (61-90+).
 </v>
       </c>
       <c r="K18" t="str">
@@ -1950,7 +1950,7 @@
         <v>Agg</v>
       </c>
       <c r="N18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per counterparty.
+        <v xml:space="preserve">Worst-case (MAX) overdue bucket across all facilities per counterparty. Identifies the most severely overdue facility for each borrower.
 </v>
       </c>
       <c r="O18" t="str">
@@ -1963,7 +1963,7 @@
         <v>Agg</v>
       </c>
       <c r="R18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per L3 desk segment.
+        <v xml:space="preserve">Worst-case (MAX) overdue bucket per L3 desk segment. Shows the most severe delinquency in each organizational unit.
 </v>
       </c>
       <c r="S18" t="str">
@@ -1976,7 +1976,7 @@
         <v>Agg</v>
       </c>
       <c r="V18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per L2 portfolio segment.
+        <v xml:space="preserve">Worst-case (MAX) overdue bucket per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
 </v>
       </c>
       <c r="W18" t="str">
@@ -1989,7 +1989,7 @@
         <v>Agg</v>
       </c>
       <c r="Z18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per L1 business segment.
+        <v xml:space="preserve">Worst-case (MAX) overdue bucket per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
 </v>
       </c>
       <c r="AA18" t="str">
@@ -2509,14 +2509,25 @@
         <v>EXP-015</v>
       </c>
       <c r="B24" t="str" xml:space="preserve">
-        <v xml:space="preserve">Expected Loss divided by Exposure. Derived KPI measuring loss intensity relative to exposure size, enabling comparative risk ranking across facilities or counterparties.
+        <v xml:space="preserve">Expected Loss as a percentage of committed exposure. Computed from L2 atomic risk parameters: PD (probability of default) × LGD (loss given default). At aggregate levels, uses sum-ratio rollup: SUM(PD × LGD × Committed) / SUM(Committed) × 100 — the exposure-weighted average EL rate. This ensures mathematically consistent aggregation (never averages pre-computed rates). Key credit risk quantification metric for comparing loss intensity across facilities, counterparties, and business segments.
+Ingredient derivation:
+  - PD (pd_pct): L2 facility_risk_snapshot — probability of default (%)
+  - LGD (lgd_pct): L2 facility_risk_snapshot — loss given default (%)
+  - Committed Exposure (committed_amount): L2 facility_exposure_snapshot — raw
+  - EL Rate = PD × LGD (at facility level, committed cancels in ratio)
+  - Aggregate EL Rate = SUM(PD × LGD × Committed) / SUM(Committed) × 100
 </v>
       </c>
       <c r="C24" t="str">
         <v>Expected Loss Rate (%)</v>
       </c>
       <c r="D24" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of expected_loss_rate_pct per facility.
+        <v xml:space="preserve">For each facility:
+  1. LOAD pd_pct, lgd_pct from l2.facility_risk_snapshot
+  2. LOAD committed_amount from l2.facility_exposure_snapshot
+  3. COMPUTE EL Rate = SUM(PD/100 × LGD/100 × Committed) / SUM(Committed) × 100
+     At facility grain, committed cancels → EL Rate ≈ PD × LGD / 100
+Ingredients: pd_pct (L2), lgd_pct (L2), committed_amount (L2)
 </v>
       </c>
       <c r="E24" t="str">
@@ -2532,10 +2543,15 @@
         <v>Y</v>
       </c>
       <c r="I24" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="J24" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of expected_loss_rate_pct per facility.
+        <v xml:space="preserve">For each facility:
+  1. LOAD pd_pct, lgd_pct from l2.facility_risk_snapshot
+  2. LOAD committed_amount from l2.facility_exposure_snapshot
+  3. COMPUTE EL Rate = SUM(PD/100 × LGD/100 × Committed) / SUM(Committed) × 100
+     At facility grain, committed cancels → EL Rate ≈ PD × LGD / 100
+Ingredients: pd_pct (L2), lgd_pct (L2), committed_amount (L2)
 </v>
       </c>
       <c r="K24" t="str">
@@ -2545,10 +2561,15 @@
         <v>Y</v>
       </c>
       <c r="M24" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N24" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level expected_loss_rate_pct per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD pd_pct, lgd_pct for all facilities belonging to this counterparty
+  2. LOAD committed_amount for each facility
+  3. CONVERT to USD via l2.fx_rate spot rate
+  4. COMPUTE SUM(PD × LGD × Committed × FX) / SUM(Committed × FX) × 100
+Sum-ratio rollup with FX: exposure-weighted average EL rate in USD terms.
 </v>
       </c>
       <c r="O24" t="str">
@@ -2558,10 +2579,14 @@
         <v>Y</v>
       </c>
       <c r="Q24" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="R24" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level expected_loss_rate_pct per L3 desk segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOOKUP managed_segment_id from enterprise_business_taxonomy
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(PD × LGD × Committed × FX) / SUM(Committed × FX) × 100
+Sum-ratio rollup: exposure-weighted average EL rate per desk.
 </v>
       </c>
       <c r="S24" t="str">
@@ -2571,10 +2596,14 @@
         <v>Y</v>
       </c>
       <c r="U24" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V24" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level expected_loss_rate_pct per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(PD × LGD × Committed × FX) / SUM(Committed × FX) × 100
+Sum-ratio rollup: exposure-weighted average EL rate per portfolio.
 </v>
       </c>
       <c r="W24" t="str">
@@ -2584,10 +2613,14 @@
         <v>Y</v>
       </c>
       <c r="Y24" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z24" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level expected_loss_rate_pct per L1 business segment segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(PD × LGD × Committed × FX) / SUM(Committed × FX) × 100
+Sum-ratio rollup: exposure-weighted average EL rate per segment.
 </v>
       </c>
       <c r="AA24" t="str">
@@ -2602,14 +2635,25 @@
         <v>EXP-016</v>
       </c>
       <c r="B25" t="str" xml:space="preserve">
-        <v xml:space="preserve">PD × LGD × Exposure expressed in USD. Calculated forward-looking loss metric supporting provisioning, capital planning, and stress testing analytics.
+        <v xml:space="preserve">Expected Loss in dollar terms: PD × LGD × Committed Exposure × Bank Share. Computed from L2 atomic risk parameters and exposure data — NOT from stressed scenarios. This is the base (unstressed) expected credit loss, the foundation for provisioning, capital planning, and CECL/IFRS 9 reserve estimation.
+Ingredient derivation:
+  - PD (pd_pct): L2 facility_risk_snapshot — probability of default (%)
+  - LGD (lgd_pct): L2 facility_risk_snapshot — loss given default (%)
+  - Committed Exposure (committed_amount): L2 facility_exposure_snapshot — raw
+  - Bank Share (bank_share_pct): L2 facility_exposure_snapshot — participation %
+  - EL = (PD/100) × (LGD/100) × Committed × (Bank Share/100)
+Rollup uses direct-sum: SUM(facility EL) at each aggregate level. FX conversion applied at aggregate levels for multi-currency portfolios.
 </v>
       </c>
       <c r="C25" t="str">
         <v>Expected Loss ($)</v>
       </c>
       <c r="D25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(stressed_expected_loss) per facility from stress_test_result. Weighted by bank share percentage.
+        <v xml:space="preserve">For each facility:
+  1. LOAD pd_pct, lgd_pct from l2.facility_risk_snapshot
+  2. LOAD committed_amount, bank_share_pct from l2.facility_exposure_snapshot
+  3. COMPUTE EL = (PD/100) × (LGD/100) × Committed × (Bank Share/100)
+Ingredients: pd_pct (L2), lgd_pct (L2), committed_amount (L2), bank_share_pct (L2)
 </v>
       </c>
       <c r="E25" t="str">
@@ -2625,10 +2669,14 @@
         <v>Y</v>
       </c>
       <c r="I25" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="J25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(stressed_expected_loss) per facility from stress_test_result. Weighted by bank share percentage.
+        <v xml:space="preserve">For each facility:
+  1. LOAD pd_pct, lgd_pct from l2.facility_risk_snapshot
+  2. LOAD committed_amount, bank_share_pct from l2.facility_exposure_snapshot
+  3. COMPUTE EL = (PD/100) × (LGD/100) × Committed × (Bank Share/100)
+Ingredients: pd_pct (L2), lgd_pct (L2), committed_amount (L2), bank_share_pct (L2)
 </v>
       </c>
       <c r="K25" t="str">
@@ -2641,7 +2689,11 @@
         <v>Agg</v>
       </c>
       <c r="N25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD facility-level EL for all facilities of this counterparty
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(facility EL × FX rate) = Counterparty EL (USD)
+Direct-sum rollup with FX conversion.
 </v>
       </c>
       <c r="O25" t="str">
@@ -2654,7 +2706,11 @@
         <v>Agg</v>
       </c>
       <c r="R25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per L3 desk segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOOKUP managed_segment_id from enterprise_business_taxonomy
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(facility EL × FX rate) per desk
+Direct-sum rollup with FX conversion.
 </v>
       </c>
       <c r="S25" t="str">
@@ -2667,7 +2723,11 @@
         <v>Agg</v>
       </c>
       <c r="V25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(facility EL × FX rate) per portfolio
+Direct-sum rollup with FX conversion.
 </v>
       </c>
       <c r="W25" t="str">
@@ -2680,7 +2740,11 @@
         <v>Agg</v>
       </c>
       <c r="Z25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per L1 business segment segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(facility EL × FX rate) per business segment
+Direct-sum rollup with FX conversion.
 </v>
       </c>
       <c r="AA25" t="str">
@@ -3276,14 +3340,14 @@
         <v>EXP-023</v>
       </c>
       <c r="B32" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure × LGD expressed in dollar terms weighted based on facility-level exposure. Derived loss severity metric estimating expected recovery-adjusted loss magnitude.
+        <v xml:space="preserve">Expected dollar loss given default. Computed as EAD (drawn amount, bank share) multiplied by LGD percentage from facility risk snapshot. Expressed in local currency at facility level and FX-converted to USD at aggregate levels. Quantifies loss severity per facility and across rollup hierarchy.
 </v>
       </c>
       <c r="C32" t="str">
         <v>Loss Given Default ($)</v>
       </c>
       <c r="D32" t="str" xml:space="preserve">
-        <v xml:space="preserve">EAD * LGD (in Percentage) for all facilities across Counterparties
+        <v xml:space="preserve">EAD (bank share) x LGD% per facility in local currency.
 </v>
       </c>
       <c r="E32" t="str">
@@ -3302,7 +3366,7 @@
         <v>Calc</v>
       </c>
       <c r="J32" t="str" xml:space="preserve">
-        <v xml:space="preserve">EAD * LGD (in Percentage) for all facilities across Counterparties
+        <v xml:space="preserve">EAD (bank share) x LGD% per facility in local currency.
 </v>
       </c>
       <c r="K32" t="str">
@@ -3315,7 +3379,7 @@
         <v>Agg</v>
       </c>
       <c r="N32" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level lgd_estimate per counterparty.
+        <v xml:space="preserve">SUM of facility-level LGD$ per counterparty, FX-converted to USD.
 </v>
       </c>
       <c r="O32" t="str">
@@ -3328,7 +3392,7 @@
         <v>Agg</v>
       </c>
       <c r="R32" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level lgd_estimate per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level LGD$ per L3 desk segment, FX-converted to USD.
 </v>
       </c>
       <c r="S32" t="str">
@@ -3341,7 +3405,7 @@
         <v>Agg</v>
       </c>
       <c r="V32" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level lgd_estimate per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level LGD$ per L2 portfolio segment, FX-converted to USD.
 </v>
       </c>
       <c r="W32" t="str">
@@ -3354,7 +3418,7 @@
         <v>Agg</v>
       </c>
       <c r="Z32" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level lgd_estimate per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level LGD$ per L1 business segment, FX-converted to USD.
 </v>
       </c>
       <c r="AA32" t="str">
@@ -3369,14 +3433,14 @@
         <v>EXP-024</v>
       </c>
       <c r="B33" t="str" xml:space="preserve">
-        <v xml:space="preserve">Status of credit limit (Active, Warning, Breach). Used to monitor risk appetite breaches and exposure governance compliance.
+        <v xml:space="preserve">Utilization-based limit compliance status. At facility level reads the pre-computed limit_status_code. At aggregate levels computes drawn-to- committed utilization percentage (FX-converted to USD) and maps to a status code via utilization_status_dim thresholds. Used for credit limit monitoring and risk appetite breach detection.
 </v>
       </c>
       <c r="C33" t="str">
         <v>Limit Status</v>
       </c>
       <c r="D33" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated limit_status_code per facility.
+        <v xml:space="preserve">Read pre-computed limit_status_code from facility_exposure_snapshot.
 </v>
       </c>
       <c r="E33" t="str">
@@ -3392,10 +3456,10 @@
         <v>Y</v>
       </c>
       <c r="I33" t="str">
-        <v>Calc</v>
+        <v>Raw</v>
       </c>
       <c r="J33" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated limit_status_code per facility.
+        <v xml:space="preserve">Read pre-computed limit_status_code from facility_exposure_snapshot.
 </v>
       </c>
       <c r="K33" t="str">
@@ -3405,10 +3469,10 @@
         <v>Y</v>
       </c>
       <c r="M33" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N33" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level limit_status_code per counterparty.
+        <v xml:space="preserve">Compute drawn-to-committed utilization % per counterparty (FX-converted), then map to status via utilization_status_dim thresholds.
 </v>
       </c>
       <c r="O33" t="str">
@@ -3418,10 +3482,10 @@
         <v>Y</v>
       </c>
       <c r="Q33" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R33" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level limit_status_code per L3 desk segment.
+        <v xml:space="preserve">Compute drawn-to-committed utilization % per L3 desk segment (FX-converted), then map to status via utilization_status_dim.
 </v>
       </c>
       <c r="S33" t="str">
@@ -3431,10 +3495,10 @@
         <v>Y</v>
       </c>
       <c r="U33" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V33" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level limit_status_code per L2 portfolio segment.
+        <v xml:space="preserve">Compute drawn-to-committed utilization % per L2 portfolio segment (FX-converted), then map to status via utilization_status_dim.
 </v>
       </c>
       <c r="W33" t="str">
@@ -3444,10 +3508,10 @@
         <v>Y</v>
       </c>
       <c r="Y33" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z33" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level limit_status_code per L1 business segment segment.
+        <v xml:space="preserve">Compute drawn-to-committed utilization % per L1 business segment (FX-converted), then map to status via utilization_status_dim.
 </v>
       </c>
       <c r="AA33" t="str">
@@ -5796,14 +5860,15 @@
         <v>PRC-003</v>
       </c>
       <c r="B59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of exposures within portfolio with approved pricing or policy exceptions. Derived governance KPI measuring policy discipline and risk culture strength.
+        <v xml:space="preserve">Percentage of facilities with approved pricing or policy exceptions. Computed as COUNT(exception facilities) / COUNT(total facilities) × 100. Sourced from L2 facility_pricing_snapshot — the atomic pricing record — using the is_pricing_exception_flag. At aggregate levels, uses count-ratio rollup: re-counts exceptions and totals across all constituent facilities, never averages pre-computed rates. Key governance KPI measuring policy discipline, risk culture strength, and pricing override frequency.
 </v>
       </c>
       <c r="C59" t="str">
         <v>Exception Rate (%)</v>
       </c>
       <c r="D59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if pricing exception, 0 otherwise.
+        <v xml:space="preserve">Binary flag: 1.0 if pricing exception approved, 0.0 otherwise.
+Ingredients: is_pricing_exception_flag (L2 facility_pricing_snapshot)
 </v>
       </c>
       <c r="E59" t="str">
@@ -5822,7 +5887,8 @@
         <v>Calc</v>
       </c>
       <c r="J59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if pricing exception, 0 otherwise.
+        <v xml:space="preserve">Binary flag: 1.0 if pricing exception approved, 0.0 otherwise.
+Ingredients: is_pricing_exception_flag (L2 facility_pricing_snapshot)
 </v>
       </c>
       <c r="K59" t="str">
@@ -5835,7 +5901,10 @@
         <v>Calc</v>
       </c>
       <c r="N59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with pricing exception per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD is_pricing_exception_flag for all facilities of this counterparty
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup: re-counts from facility-level flags.
 </v>
       </c>
       <c r="O59" t="str">
@@ -5848,7 +5917,10 @@
         <v>Calc</v>
       </c>
       <c r="R59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with pricing exception per L3 desk.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOOKUP managed_segment_id from enterprise_business_taxonomy
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup per desk.
 </v>
       </c>
       <c r="S59" t="str">
@@ -5861,7 +5933,10 @@
         <v>Calc</v>
       </c>
       <c r="V59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with pricing exception per L2 portfolio.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup per portfolio.
 </v>
       </c>
       <c r="W59" t="str">
@@ -5874,7 +5949,10 @@
         <v>Calc</v>
       </c>
       <c r="Z59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with pricing exception per L1 business segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup per business segment.
 </v>
       </c>
       <c r="AA59" t="str">
@@ -6830,14 +6908,14 @@
         <v>REF-004</v>
       </c>
       <c r="B70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Unique system identifier assigned to the borrower or obligor. Used for exposure aggregation and risk consolidation.
+        <v xml:space="preserve">Unique system identifier assigned to the borrower or obligor. Used for exposure aggregation and risk consolidation across the GSIB. At facility level, returns the counterparty_id linked to each facility. At upper levels, returns COUNT(DISTINCT counterparty_id) — the number of unique obligors in each organizational segment.
 </v>
       </c>
       <c r="C70" t="str">
         <v>Counterparty ID</v>
       </c>
       <c r="D70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">Direct lookup of counterparty_id from facility_master for each active facility. Uses current records only (SCD2 filtered).
 </v>
       </c>
       <c r="E70" t="str">
@@ -6856,7 +6934,7 @@
         <v>Raw</v>
       </c>
       <c r="J70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">Direct lookup of counterparty_id from facility_master for each active facility. Uses current records only (SCD2 filtered).
 </v>
       </c>
       <c r="K70" t="str">
@@ -6869,7 +6947,7 @@
         <v>Raw</v>
       </c>
       <c r="N70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">Identity — returns counterparty_id for each current counterparty.
 </v>
       </c>
       <c r="O70" t="str">
@@ -6882,7 +6960,7 @@
         <v>Agg</v>
       </c>
       <c r="R70" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L3 desk segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L3 desk segment — number of unique obligors in each desk.
 </v>
       </c>
       <c r="S70" t="str">
@@ -6895,7 +6973,7 @@
         <v>Agg</v>
       </c>
       <c r="V70" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L2 portfolio segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L2 portfolio segment — number of unique obligors in each portfolio.
 </v>
       </c>
       <c r="W70" t="str">
@@ -6908,7 +6986,7 @@
         <v>Agg</v>
       </c>
       <c r="Z70" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L1 business segment segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L1 business segment — number of unique obligors in each business segment.
 </v>
       </c>
       <c r="AA70" t="str">
@@ -6923,14 +7001,14 @@
         <v>REF-005</v>
       </c>
       <c r="B71" t="str" xml:space="preserve">
-        <v xml:space="preserve">Descriptive name of the counterparty as documented in the credit agreement. Used for reporting clarity and operational reference.
+        <v xml:space="preserve">Legal name of the counterparty as documented in the credit agreement. At facility level, returns the counterparty_id (numeric proxy for the name since metric values are numeric). At counterparty level, identity lookup. At upper levels, COUNT(DISTINCT counterparty_id) — number of unique named obligors per organizational segment. Used for reporting clarity and operational reference across all regulatory submissions.
 </v>
       </c>
       <c r="C71" t="str">
         <v>Counterparty Name</v>
       </c>
       <c r="D71" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read legal_name from counterparty for each facility's counterparty.
+        <v xml:space="preserve">Lookup counterparty_id from facility_master for each active facility. The numeric counterparty_id serves as proxy for the legal name (string values resolved via counterparty dimension join at display time). Uses current records only.
 </v>
       </c>
       <c r="E71" t="str">
@@ -6949,7 +7027,7 @@
         <v>Raw</v>
       </c>
       <c r="J71" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read legal_name from counterparty for each facility's counterparty.
+        <v xml:space="preserve">Lookup counterparty_id from facility_master for each active facility. The numeric counterparty_id serves as proxy for the legal name (string values resolved via counterparty dimension join at display time). Uses current records only.
 </v>
       </c>
       <c r="K71" t="str">
@@ -6959,10 +7037,10 @@
         <v>Y</v>
       </c>
       <c r="M71" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="N71" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with counterparty name per counterparty.
+        <v xml:space="preserve">Identity — returns counterparty_id for each current counterparty. Legal name resolved via counterparty dimension join at display time.
 </v>
       </c>
       <c r="O71" t="str">
@@ -6975,7 +7053,7 @@
         <v>Agg</v>
       </c>
       <c r="R71" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with counterparty name per L3 desk segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L3 desk segment — number of unique named obligors in each desk.
 </v>
       </c>
       <c r="S71" t="str">
@@ -6988,7 +7066,7 @@
         <v>Agg</v>
       </c>
       <c r="V71" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with counterparty name per L2 portfolio segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L2 portfolio segment — number of unique named obligors in each portfolio.
 </v>
       </c>
       <c r="W71" t="str">
@@ -7001,7 +7079,7 @@
         <v>Agg</v>
       </c>
       <c r="Z71" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with counterparty name per L1 business segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L1 business segment — number of unique named obligors in each business segment.
 </v>
       </c>
       <c r="AA71" t="str">
@@ -7016,14 +7094,14 @@
         <v>REF-006</v>
       </c>
       <c r="B72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Country of risk or booking location. Supports geographic concentration and sovereign risk analysis.
+        <v xml:space="preserve">Country of risk derived from the counterparty's domicile. At facility level, returns a numeric country identifier (via counterparty → country_dim join path). At counterparty level, identity lookup. At desk/portfolio/segment levels, COUNT(DISTINCT country_code) — geographic diversification indicator showing the number of unique countries represented. Supports FFIEC 009 Country Exposure Report and Basel III geographic concentration analysis.
 </v>
       </c>
       <c r="C72" t="str">
         <v>Country</v>
       </c>
       <c r="D72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of country_name from country_dim.
+        <v xml:space="preserve">Lookup country for each facility via counterparty → country_dim join path. Returns counterparty_id as numeric proxy (country_name resolved at display time via dimension join). Uses current records only.
 </v>
       </c>
       <c r="E72" t="str">
@@ -7042,7 +7120,7 @@
         <v>Raw</v>
       </c>
       <c r="J72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of country_name from country_dim.
+        <v xml:space="preserve">Lookup country for each facility via counterparty → country_dim join path. Returns counterparty_id as numeric proxy (country_name resolved at display time via dimension join). Uses current records only.
 </v>
       </c>
       <c r="K72" t="str">
@@ -7055,7 +7133,7 @@
         <v>Raw</v>
       </c>
       <c r="N72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read country_name per counterparty.
+        <v xml:space="preserve">Lookup country for each counterparty via country_code → country_dim join. Returns counterparty_id as numeric proxy.
 </v>
       </c>
       <c r="O72" t="str">
@@ -7068,7 +7146,7 @@
         <v>Agg</v>
       </c>
       <c r="R72" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level country_name per L3 desk segment.
+        <v xml:space="preserve">COUNT(DISTINCT country_code) per L3 desk segment — number of unique countries represented, a geographic diversification indicator.
 </v>
       </c>
       <c r="S72" t="str">
@@ -7081,7 +7159,7 @@
         <v>Agg</v>
       </c>
       <c r="V72" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level country_name per L2 portfolio segment.
+        <v xml:space="preserve">COUNT(DISTINCT country_code) per L2 portfolio segment — number of unique countries represented in each portfolio.
 </v>
       </c>
       <c r="W72" t="str">
@@ -7094,7 +7172,7 @@
         <v>Agg</v>
       </c>
       <c r="Z72" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level country_name per L1 business segment segment.
+        <v xml:space="preserve">COUNT(DISTINCT country_code) per L1 business segment — geographic diversification at the highest organizational level.
 </v>
       </c>
       <c r="AA72" t="str">
@@ -7109,14 +7187,14 @@
         <v>REF-007</v>
       </c>
       <c r="B73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Unique identifier linking facility to governing credit agreement documentation.
+        <v xml:space="preserve">Unique identifier linking each facility to its governing credit agreement documentation. Used for contract tracking, facility-to-agreement linkage, and regulatory reporting. At counterparty level, returns count of distinct credit agreements per borrower.
 </v>
       </c>
       <c r="C73" t="str">
         <v>Credit Agreement ID</v>
       </c>
       <c r="D73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of credit_agreement_id from credit_agreement_master.
+        <v xml:space="preserve">Direct lookup of credit_agreement_id for each active facility via facility_master joined to credit_agreement_master.
 </v>
       </c>
       <c r="E73" t="str">
@@ -7135,7 +7213,7 @@
         <v>Raw</v>
       </c>
       <c r="J73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of credit_agreement_id from credit_agreement_master.
+        <v xml:space="preserve">Direct lookup of credit_agreement_id for each active facility via facility_master joined to credit_agreement_master.
 </v>
       </c>
       <c r="K73" t="str">
@@ -7145,10 +7223,10 @@
         <v>Y</v>
       </c>
       <c r="M73" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="N73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read credit_agreement_id per counterparty.
+        <v xml:space="preserve">Count of distinct credit agreements per counterparty. Provides visibility into borrower complexity and multi-agreement relationships.
 </v>
       </c>
       <c r="O73" t="str">
@@ -7161,7 +7239,7 @@
         <v>Agg</v>
       </c>
       <c r="R73" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level credit_agreement_id per L3 desk segment.
+        <v xml:space="preserve">Count of distinct credit agreements per L3 desk segment via enterprise_business_taxonomy.
 </v>
       </c>
       <c r="S73" t="str">
@@ -7174,7 +7252,7 @@
         <v>Agg</v>
       </c>
       <c r="V73" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level credit_agreement_id per L2 portfolio segment.
+        <v xml:space="preserve">Count of distinct credit agreements per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
 </v>
       </c>
       <c r="W73" t="str">
@@ -7187,7 +7265,7 @@
         <v>Agg</v>
       </c>
       <c r="Z73" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level credit_agreement_id per L1 business segment segment.
+        <v xml:space="preserve">Count of distinct credit agreements per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
 </v>
       </c>
       <c r="AA73" t="str">
@@ -7295,7 +7373,7 @@
         <v>REF-009</v>
       </c>
       <c r="B75" t="str" xml:space="preserve">
-        <v xml:space="preserve">Date on which loan or contract became legally effective.
+        <v xml:space="preserve">Date on which loan or contract became legally effective. Sourced directly from facility_master. At aggregate levels, returns the earliest origination date (MIN) across constituent facilities — indicating the oldest vintage in the book. Key contract lifecycle tracking attribute for vintage analysis and portfolio seasoning assessment.
 </v>
       </c>
       <c r="C75" t="str">
@@ -7303,6 +7381,7 @@
       </c>
       <c r="D75" t="str" xml:space="preserve">
         <v xml:space="preserve">Direct lookup of origination_date from facility_master.
+Ingredients: origination_date (L2 facility_master — raw field)
 </v>
       </c>
       <c r="E75" t="str">
@@ -7322,6 +7401,7 @@
       </c>
       <c r="J75" t="str" xml:space="preserve">
         <v xml:space="preserve">Direct lookup of origination_date from facility_master.
+Ingredients: origination_date (L2 facility_master — raw field)
 </v>
       </c>
       <c r="K75" t="str">
@@ -7334,7 +7414,10 @@
         <v>Agg</v>
       </c>
       <c r="N75" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level origination_date) per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD origination_date from l2.facility_master for all active facilities
+  2. COMPUTE MIN(origination_date) — earliest contract vintage
+Indicates the oldest banking relationship tenure for this counterparty.
 </v>
       </c>
       <c r="O75" t="str">
@@ -7347,7 +7430,10 @@
         <v>Agg</v>
       </c>
       <c r="R75" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level origination_date per L3 desk segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOAD origination_date from l2.facility_master
+  2. JOIN l1.enterprise_business_taxonomy on lob_segment_id
+  3. COMPUTE MIN(origination_date) — earliest vintage in desk book
 </v>
       </c>
       <c r="S75" t="str">
@@ -7360,7 +7446,9 @@
         <v>Agg</v>
       </c>
       <c r="V75" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level origination_date per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. COMPUTE MIN(origination_date) — earliest vintage in portfolio
 </v>
       </c>
       <c r="W75" t="str">
@@ -7373,7 +7461,9 @@
         <v>Agg</v>
       </c>
       <c r="Z75" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level origination_date per L1 business segment segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. COMPUTE MIN(origination_date) — earliest vintage in business segment
 </v>
       </c>
       <c r="AA75" t="str">
@@ -7946,14 +8036,14 @@
         <v>REF-016</v>
       </c>
       <c r="B82" t="str" xml:space="preserve">
-        <v xml:space="preserve">Legal entity booking or owning the exposure. Critical for regulatory capital and entity-level reporting.
+        <v xml:space="preserve">Booking legal entity for each facility exposure. At facility level returns the entity name from the legal_entity table. At aggregate levels returns the count of distinct booking entities for risk concentration analysis.
 </v>
       </c>
       <c r="C82" t="str">
         <v>Legal Entity</v>
       </c>
       <c r="D82" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of legal_name from counterparty.
+        <v xml:space="preserve">Lookup legal_entity_name from legal_entity table via facility_exposure_snapshot.legal_entity_id.
 </v>
       </c>
       <c r="E82" t="str">
@@ -7972,7 +8062,7 @@
         <v>Raw</v>
       </c>
       <c r="J82" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of legal_name from counterparty.
+        <v xml:space="preserve">Lookup legal_entity_name from legal_entity table via facility_exposure_snapshot.legal_entity_id.
 </v>
       </c>
       <c r="K82" t="str">
@@ -7982,10 +8072,10 @@
         <v>Y</v>
       </c>
       <c r="M82" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="N82" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of legal_name from counterparty.
+        <v xml:space="preserve">Count of distinct booking legal entities per counterparty.
 </v>
       </c>
       <c r="O82" t="str">
@@ -7995,10 +8085,10 @@
         <v>Y</v>
       </c>
       <c r="Q82" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R82" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level legal_name per L3 desk segment.
+        <v xml:space="preserve">Count of distinct booking legal entities per L3 desk segment.
 </v>
       </c>
       <c r="S82" t="str">
@@ -8008,10 +8098,10 @@
         <v>Y</v>
       </c>
       <c r="U82" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V82" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level legal_name per L2 portfolio segment.
+        <v xml:space="preserve">Count of distinct booking legal entities per L2 portfolio segment.
 </v>
       </c>
       <c r="W82" t="str">
@@ -8021,10 +8111,10 @@
         <v>Y</v>
       </c>
       <c r="Y82" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z82" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level legal_name per L1 business segment segment.
+        <v xml:space="preserve">Count of distinct booking legal entities per L1 business segment.
 </v>
       </c>
       <c r="AA82" t="str">
@@ -8039,14 +8129,14 @@
         <v>REF-017</v>
       </c>
       <c r="B83" t="str" xml:space="preserve">
-        <v xml:space="preserve">Unique identifier assigned to legal entity in enterprise systems.
+        <v xml:space="preserve">Unique identifier for the booking legal entity. At facility level returns the entity ID. At aggregate levels returns count of distinct booking entities for entity concentration tracking.
 </v>
       </c>
       <c r="C83" t="str">
         <v>Legal Entity ID</v>
       </c>
       <c r="D83" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read legal_entity_id from facility_exposure_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Read legal_entity_id from facility_exposure_snapshot for each facility.
 </v>
       </c>
       <c r="E83" t="str">
@@ -8065,7 +8155,7 @@
         <v>Raw</v>
       </c>
       <c r="J83" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read legal_entity_id from facility_exposure_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Read legal_entity_id from facility_exposure_snapshot for each facility.
 </v>
       </c>
       <c r="K83" t="str">
@@ -8075,10 +8165,10 @@
         <v>Y</v>
       </c>
       <c r="M83" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="N83" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read legal_entity_id per counterparty.
+        <v xml:space="preserve">Count of distinct booking legal entities per counterparty.
 </v>
       </c>
       <c r="O83" t="str">
@@ -8088,10 +8178,10 @@
         <v>Y</v>
       </c>
       <c r="Q83" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R83" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level legal_entity_id per L3 desk segment.
+        <v xml:space="preserve">Count of distinct booking legal entities per L3 desk segment.
 </v>
       </c>
       <c r="S83" t="str">
@@ -8101,10 +8191,10 @@
         <v>Y</v>
       </c>
       <c r="U83" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V83" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level legal_entity_id per L2 portfolio segment.
+        <v xml:space="preserve">Count of distinct booking legal entities per L2 portfolio segment.
 </v>
       </c>
       <c r="W83" t="str">
@@ -8114,10 +8204,10 @@
         <v>Y</v>
       </c>
       <c r="Y83" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z83" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level legal_entity_id per L1 business segment segment.
+        <v xml:space="preserve">Count of distinct booking legal entities per L1 business segment.
 </v>
       </c>
       <c r="AA83" t="str">
@@ -9620,14 +9710,14 @@
         <v>RSK-001</v>
       </c>
       <c r="B100" t="str" xml:space="preserve">
-        <v xml:space="preserve">Most recent internal credit rating assigned at reporting date. Used for segmentation and exposure-weighted risk aggregation.
+        <v xml:space="preserve">Risk rating tier derived from counterparty probability of default (PD). Each counterparty's pd_annual is matched against the risk_rating_tier_dim reference table (pd_min_pct / pd_max_pct boundaries) to assign a tier classification. At facility level, the tier is inherited from the owning counterparty. At aggregate levels, MAX (worst-case) tier ordinal is reported.
 </v>
       </c>
       <c r="C100" t="str">
         <v>Risk Rating Tier</v>
       </c>
       <c r="D100" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility.
+        <v xml:space="preserve">For each facility, inherit the risk rating tier from the owning counterparty. Join facility_master to counterparty, then range-match counterparty pd_annual against risk_rating_tier_dim to derive the tier ordinal (display_order).
 </v>
       </c>
       <c r="E100" t="str">
@@ -9643,10 +9733,10 @@
         <v>Y</v>
       </c>
       <c r="I100" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="J100" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility.
+        <v xml:space="preserve">For each facility, inherit the risk rating tier from the owning counterparty. Join facility_master to counterparty, then range-match counterparty pd_annual against risk_rating_tier_dim to derive the tier ordinal (display_order).
 </v>
       </c>
       <c r="K100" t="str">
@@ -9656,10 +9746,10 @@
         <v>Y</v>
       </c>
       <c r="M100" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N100" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating per counterparty.
+        <v xml:space="preserve">For each counterparty, look up pd_annual and range-match against risk_rating_tier_dim where pd_annual &gt;= pd_min_pct AND pd_annual &lt; pd_max_pct. Returns the tier ordinal (display_order). Counterparties with NULL PD receive tier 0 (unrated).
 </v>
       </c>
       <c r="O100" t="str">
@@ -9672,7 +9762,7 @@
         <v>Agg</v>
       </c>
       <c r="R100" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating per L3 desk segment.
+        <v xml:space="preserve">Worst-case (MAX) risk rating tier ordinal across all counterparties in the L3 desk segment. Higher ordinal = riskier tier. Full tier distribution available via counterparty-level drill-down.
 </v>
       </c>
       <c r="S100" t="str">
@@ -9685,7 +9775,7 @@
         <v>Agg</v>
       </c>
       <c r="V100" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating per L2 portfolio segment.
+        <v xml:space="preserve">Worst-case (MAX) risk rating tier ordinal per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
 </v>
       </c>
       <c r="W100" t="str">
@@ -9698,7 +9788,7 @@
         <v>Agg</v>
       </c>
       <c r="Z100" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating per L1 business segment.
+        <v xml:space="preserve">Worst-case (MAX) risk rating tier ordinal per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
 </v>
       </c>
       <c r="AA100" t="str">

--- a/data/metrics_dimensions_filled.xlsx
+++ b/data/metrics_dimensions_filled.xlsx
@@ -1539,14 +1539,14 @@
         <v>EXP-005</v>
       </c>
       <c r="B14" t="str" xml:space="preserve">
-        <v xml:space="preserve">The portion of total funding-related expense attributed to a specific exposure or portfolio. At facility level, calculated as SUM across all positions of (funded_amount * interest_rate), adjusted for bank share. At counterparty level, further adjusted by counterparty participation_pct. At desk/portfolio/segment levels, aggregated as SUM.
+        <v xml:space="preserve">The portion of total funding-related expense attributed to a specific exposure or portfolio. At facility level, calculated as SUM across all positions of (funded_amount * interest_rate), converted to USD via FX rate and adjusted for bank share. At counterparty level, further adjusted by counterparty participation_pct. At desk/portfolio/segment levels, aggregated as SUM via EBT hierarchy.
 </v>
       </c>
       <c r="C14" t="str">
         <v>Cost of Funds ($)</v>
       </c>
       <c r="D14" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each position under the facility: funded_amount * interest_rate = Position Cost of Funds. Adjusted by bank_share: SUM(funded_amount * interest_rate) * bank_share_pct / 100. Joins position_detail → position (for facility_id) → facility_master.
+        <v xml:space="preserve">For each position under the facility, compute funded_amount x interest_rate, convert to USD using the FX spot rate (defaults to 1.0 for USD positions). Sum across all positions, then multiply by the bank's share percentage. Result = annual cost of funds for this facility in USD.
 </v>
       </c>
       <c r="E14" t="str">
@@ -1565,7 +1565,7 @@
         <v>Calc</v>
       </c>
       <c r="J14" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each position under the facility: funded_amount * interest_rate = Position Cost of Funds. Adjusted by bank_share: SUM(funded_amount * interest_rate) * bank_share_pct / 100. Joins position_detail → position (for facility_id) → facility_master.
+        <v xml:space="preserve">For each position under the facility, compute funded_amount x interest_rate, convert to USD using the FX spot rate (defaults to 1.0 for USD positions). Sum across all positions, then multiply by the bank's share percentage. Result = annual cost of funds for this facility in USD.
 </v>
       </c>
       <c r="K14" t="str">
@@ -1578,7 +1578,7 @@
         <v>Agg</v>
       </c>
       <c r="N14" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each counterparty: SUM of facility-level cost of funds weighted by counterparty participation_pct from facility_counterparty_participation.
+        <v xml:space="preserve">Sum each facility's cost of funds (USD, bank-share-adjusted), then weight by the counterparty's participation percentage. Aggregates across all facilities where the counterparty has a current participation record.
 </v>
       </c>
       <c r="O14" t="str">
@@ -1591,7 +1591,7 @@
         <v>Agg</v>
       </c>
       <c r="R14" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level cost of funds (bank-share-adjusted) per L3 desk segment.
+        <v xml:space="preserve">Sum of facility-level cost of funds (USD, bank-share-adjusted) for all facilities assigned to each L3 desk segment in the organizational hierarchy.
 </v>
       </c>
       <c r="S14" t="str">
@@ -1604,7 +1604,7 @@
         <v>Agg</v>
       </c>
       <c r="V14" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level cost of funds (bank-share-adjusted) per L2 portfolio segment.
+        <v xml:space="preserve">Sum of facility-level cost of funds (USD, bank-share-adjusted) for all facilities within each L2 portfolio segment, traversing the EBT hierarchy from desk (L3) to portfolio (L2) via parent_segment_id.
 </v>
       </c>
       <c r="W14" t="str">
@@ -1617,7 +1617,7 @@
         <v>Agg</v>
       </c>
       <c r="Z14" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level cost of funds (bank-share-adjusted) per L1 business segment.
+        <v xml:space="preserve">Sum of facility-level cost of funds (USD, bank-share-adjusted) for all facilities within each L1 business segment, traversing the full EBT hierarchy from desk (L3) through portfolio (L2) to segment (L1).
 </v>
       </c>
       <c r="AA14" t="str">
@@ -1632,14 +1632,14 @@
         <v>EXP-006</v>
       </c>
       <c r="B15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure allocated to specific counterparty representing their share of the facility which the client can draw on. Concentration KPI measuring obligor dependency risk.
+        <v xml:space="preserve">Counterparty participation share in a facility — the percentage of a syndicated or participated facility allocated to a specific counterparty. At facility level, direct lookup from facility_counterparty_participation. At counterparty level, exposure-weighted average participation across all facilities. At desk/portfolio/segment, exposure-weighted average via EBT hierarchy. Key concentration KPI for Large Exposures Framework (LEX) and Single Counterparty Credit Limit (SCCL) compliance.
 </v>
       </c>
       <c r="C15" t="str">
         <v>Counterparty Share or Allocation (%)</v>
       </c>
       <c r="D15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of allocation_pct from facility_counterparty_participation.
+        <v xml:space="preserve">Direct lookup of participation_pct from facility_counterparty_participation for the primary counterparty on each facility. Uses current records only.
 </v>
       </c>
       <c r="E15" t="str">
@@ -1658,7 +1658,7 @@
         <v>Raw</v>
       </c>
       <c r="J15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of allocation_pct from facility_counterparty_participation.
+        <v xml:space="preserve">Direct lookup of participation_pct from facility_counterparty_participation for the primary counterparty on each facility. Uses current records only.
 </v>
       </c>
       <c r="K15" t="str">
@@ -1668,10 +1668,10 @@
         <v>Y</v>
       </c>
       <c r="M15" t="str">
-        <v>Raw</v>
+        <v>Avg</v>
       </c>
       <c r="N15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read allocation_pct per counterparty.
+        <v xml:space="preserve">Exposure-weighted average participation across all facilities for each counterparty. Weight = drawn_amount from facility_exposure_snapshot. Falls back to simple average if no exposure data available.
 </v>
       </c>
       <c r="O15" t="str">
@@ -1681,10 +1681,10 @@
         <v>Y</v>
       </c>
       <c r="Q15" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="R15" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level allocation_pct per L3 desk segment.
+        <v xml:space="preserve">Exposure-weighted average participation across all facilities per L3 desk segment via enterprise_business_taxonomy.
 </v>
       </c>
       <c r="S15" t="str">
@@ -1694,10 +1694,10 @@
         <v>Y</v>
       </c>
       <c r="U15" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="V15" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level allocation_pct per L2 portfolio segment.
+        <v xml:space="preserve">Exposure-weighted average participation across all facilities per L2 portfolio segment via enterprise_business_taxonomy hierarchy traversal.
 </v>
       </c>
       <c r="W15" t="str">
@@ -1707,10 +1707,10 @@
         <v>Y</v>
       </c>
       <c r="Y15" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="Z15" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level allocation_pct per L1 business segment segment.
+        <v xml:space="preserve">Exposure-weighted average participation across all facilities per L1 business segment via enterprise_business_taxonomy hierarchy traversal.
 </v>
       </c>
       <c r="AA15" t="str">
@@ -1725,14 +1725,14 @@
         <v>EXP-007</v>
       </c>
       <c r="B16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Flag identifying exposures requiring heightened monitoring due to elevated credit risk. Governance control used for enhanced monitoring, reserve consideration, and management reporting.
+        <v xml:space="preserve">Count of active Criticized risk flags across facilities. Early warning indicator of problem assets requiring heightened monitoring, reserve consideration, and management reporting. Sources from the risk_flag table filtering on flag_code = 'CRITICIZED' with uncleared status.
 </v>
       </c>
       <c r="C16" t="str">
         <v>Criticized Portfolios</v>
       </c>
       <c r="D16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if criticized rating (internal_risk_rating &gt;= 6), 0 otherwise.
+        <v xml:space="preserve">For each facility, count active risk flags where flag_code = 'CRITICIZED' and the flag has not been cleared (cleared_ts IS NULL).
 </v>
       </c>
       <c r="E16" t="str">
@@ -1748,10 +1748,10 @@
         <v>Y</v>
       </c>
       <c r="I16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="J16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if criticized rating (internal_risk_rating &gt;= 6), 0 otherwise.
+        <v xml:space="preserve">For each facility, count active risk flags where flag_code = 'CRITICIZED' and the flag has not been cleared (cleared_ts IS NULL).
 </v>
       </c>
       <c r="K16" t="str">
@@ -1761,10 +1761,10 @@
         <v>Y</v>
       </c>
       <c r="M16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="N16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per counterparty.
+        <v xml:space="preserve">For each counterparty, sum facility-level criticized flag counts across all facilities belonging to that counterparty.
 </v>
       </c>
       <c r="O16" t="str">
@@ -1774,10 +1774,10 @@
         <v>Y</v>
       </c>
       <c r="Q16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="R16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per L3 desk.
+        <v xml:space="preserve">Sum of criticized flag counts per L3 desk segment. Joins facility_master to enterprise_business_taxonomy via lob_segment_id.
 </v>
       </c>
       <c r="S16" t="str">
@@ -1787,10 +1787,10 @@
         <v>Y</v>
       </c>
       <c r="U16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="V16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per L2 portfolio.
+        <v xml:space="preserve">Sum of criticized flag counts per L2 portfolio segment. Traverses enterprise_business_taxonomy hierarchy from L3 to L2 via parent_segment_id.
 </v>
       </c>
       <c r="W16" t="str">
@@ -1800,10 +1800,10 @@
         <v>Y</v>
       </c>
       <c r="Y16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="Z16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per L1 business segment.
+        <v xml:space="preserve">Sum of criticized flag counts per L1 business segment. Full hierarchy traversal L3 → L2 → L1 via enterprise_business_taxonomy.
 </v>
       </c>
       <c r="AA16" t="str">
@@ -1818,14 +1818,14 @@
         <v>EXP-008</v>
       </c>
       <c r="B17" t="str" xml:space="preserve">
-        <v xml:space="preserve">Total exposure amount allocated across multiple legal entities. Supports intra-group concentration transparency.
+        <v xml:space="preserve">Total committed exposure amount (bank share) allocated across multiple legal entities for facilities flagged as cross-entity. Quantifies inter-entity concentration risk and supports intra-group transparency for GSIB reporting. Sources from counterparty_derived (L3) for the cross-entity flag and facility_exposure_snapshot (L2) for committed amounts.
 </v>
       </c>
       <c r="C17" t="str">
         <v>Cross Entity Exposure Amount</v>
       </c>
       <c r="D17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(total_cross_entity_exposure_usd) per facility from counterparty_exposure_summary. Weighted by bank share percentage.
+        <v xml:space="preserve">For each facility flagged as cross-entity, committed exposure amount weighted by the bank's participation share (bank_share_pct). Facilities without cross-entity flag are excluded.
 </v>
       </c>
       <c r="E17" t="str">
@@ -1844,7 +1844,7 @@
         <v>Agg</v>
       </c>
       <c r="J17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(total_cross_entity_exposure_usd) per facility from counterparty_exposure_summary. Weighted by bank share percentage.
+        <v xml:space="preserve">For each facility flagged as cross-entity, committed exposure amount weighted by the bank's participation share (bank_share_pct). Facilities without cross-entity flag are excluded.
 </v>
       </c>
       <c r="K17" t="str">
@@ -1857,7 +1857,7 @@
         <v>Agg</v>
       </c>
       <c r="N17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per counterparty.
+        <v xml:space="preserve">For each counterparty, sum of bank-share-weighted committed amounts across all facilities flagged as cross-entity.
 </v>
       </c>
       <c r="O17" t="str">
@@ -1870,7 +1870,7 @@
         <v>Agg</v>
       </c>
       <c r="R17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per L3 desk segment.
+        <v xml:space="preserve">Sum of cross-entity committed exposure per L3 desk segment via enterprise_business_taxonomy.
 </v>
       </c>
       <c r="S17" t="str">
@@ -1883,7 +1883,7 @@
         <v>Agg</v>
       </c>
       <c r="V17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per L2 portfolio segment.
+        <v xml:space="preserve">Sum of cross-entity committed exposure per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
 </v>
       </c>
       <c r="W17" t="str">
@@ -1896,7 +1896,7 @@
         <v>Agg</v>
       </c>
       <c r="Z17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per L1 business segment segment.
+        <v xml:space="preserve">Sum of cross-entity committed exposure per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
 </v>
       </c>
       <c r="AA17" t="str">
@@ -1911,14 +1911,14 @@
         <v>EXP-009</v>
       </c>
       <c r="B18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Number of days outstanding payments is past due as grouped into 3 "buckets", 0-30 Days, 31-60 Days, 61-90+ Days. Used for staging classification and early credit deterioration monitoring.
+        <v xml:space="preserve">Maximum days payment overdue per facility, calculated from raw payment records in the payment_ledger table. For each facility, identifies payments where applied amount &lt; amount due, computes days overdue as reporting date minus payment_due_date, takes the MAX, then classifies into buckets: 1 = 0-30 days, 2 = 31-60 days, 3 = 61-90+ days. At aggregate levels, reports the worst (MAX) bucket across constituents.
 </v>
       </c>
       <c r="C18" t="str">
         <v>Days Payment Overdue Bucket</v>
       </c>
       <c r="D18" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Facility_ID lookup the Payments records in the Payment Lockbox table, For each payment record where [Payment_Due_Date] &gt; Today() IF ([Pmt_Applied] &lt;[Pmt_Due])&gt;=1, THEN Today() - [Payment_due_date] ==[Days Overdue] SELECT MAX ([Days Overdue] then lookup in Payments Overdue bucket)
+        <v xml:space="preserve">For each facility, lookup payment records in payment_ledger where payment_due_date &lt; reporting date and payment_applied_amt &lt; payment_amount_due (underpaid). Calculate days overdue = reporting date minus payment_due_date. Take MAX days overdue, then classify into overdue bucket: 1 (0-30), 2 (31-60), 3 (61-90+).
 </v>
       </c>
       <c r="E18" t="str">
@@ -1937,7 +1937,7 @@
         <v>Calc</v>
       </c>
       <c r="J18" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Facility_ID lookup the Payments records in the Payment Lockbox table, For each payment record where [Payment_Due_Date] &gt; Today() IF ([Pmt_Applied] &lt;[Pmt_Due])&gt;=1, THEN Today() - [Payment_due_date] ==[Days Overdue] SELECT MAX ([Days Overdue] then lookup in Payments Overdue bucket)
+        <v xml:space="preserve">For each facility, lookup payment records in payment_ledger where payment_due_date &lt; reporting date and payment_applied_amt &lt; payment_amount_due (underpaid). Calculate days overdue = reporting date minus payment_due_date. Take MAX days overdue, then classify into overdue bucket: 1 (0-30), 2 (31-60), 3 (61-90+).
 </v>
       </c>
       <c r="K18" t="str">
@@ -1950,7 +1950,7 @@
         <v>Agg</v>
       </c>
       <c r="N18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per counterparty.
+        <v xml:space="preserve">Worst-case (MAX) overdue bucket across all facilities per counterparty. Identifies the most severely overdue facility for each borrower.
 </v>
       </c>
       <c r="O18" t="str">
@@ -1963,7 +1963,7 @@
         <v>Agg</v>
       </c>
       <c r="R18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per L3 desk segment.
+        <v xml:space="preserve">Worst-case (MAX) overdue bucket per L3 desk segment. Shows the most severe delinquency in each organizational unit.
 </v>
       </c>
       <c r="S18" t="str">
@@ -1976,7 +1976,7 @@
         <v>Agg</v>
       </c>
       <c r="V18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per L2 portfolio segment.
+        <v xml:space="preserve">Worst-case (MAX) overdue bucket per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
 </v>
       </c>
       <c r="W18" t="str">
@@ -1989,7 +1989,7 @@
         <v>Agg</v>
       </c>
       <c r="Z18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per L1 business segment.
+        <v xml:space="preserve">Worst-case (MAX) overdue bucket per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
 </v>
       </c>
       <c r="AA18" t="str">
@@ -2509,14 +2509,25 @@
         <v>EXP-015</v>
       </c>
       <c r="B24" t="str" xml:space="preserve">
-        <v xml:space="preserve">Expected Loss divided by Exposure. Derived KPI measuring loss intensity relative to exposure size, enabling comparative risk ranking across facilities or counterparties.
+        <v xml:space="preserve">Expected Loss as a percentage of committed exposure. Computed from L2 atomic risk parameters: PD (probability of default) × LGD (loss given default). At aggregate levels, uses sum-ratio rollup: SUM(PD × LGD × Committed) / SUM(Committed) × 100 — the exposure-weighted average EL rate. This ensures mathematically consistent aggregation (never averages pre-computed rates). Key credit risk quantification metric for comparing loss intensity across facilities, counterparties, and business segments.
+Ingredient derivation:
+  - PD (pd_pct): L2 facility_risk_snapshot — probability of default (%)
+  - LGD (lgd_pct): L2 facility_risk_snapshot — loss given default (%)
+  - Committed Exposure (committed_amount): L2 facility_exposure_snapshot — raw
+  - EL Rate = PD × LGD (at facility level, committed cancels in ratio)
+  - Aggregate EL Rate = SUM(PD × LGD × Committed) / SUM(Committed) × 100
 </v>
       </c>
       <c r="C24" t="str">
         <v>Expected Loss Rate (%)</v>
       </c>
       <c r="D24" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of expected_loss_rate_pct per facility.
+        <v xml:space="preserve">For each facility:
+  1. LOAD pd_pct, lgd_pct from l2.facility_risk_snapshot
+  2. LOAD committed_amount from l2.facility_exposure_snapshot
+  3. COMPUTE EL Rate = SUM(PD/100 × LGD/100 × Committed) / SUM(Committed) × 100
+     At facility grain, committed cancels → EL Rate ≈ PD × LGD / 100
+Ingredients: pd_pct (L2), lgd_pct (L2), committed_amount (L2)
 </v>
       </c>
       <c r="E24" t="str">
@@ -2532,10 +2543,15 @@
         <v>Y</v>
       </c>
       <c r="I24" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="J24" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of expected_loss_rate_pct per facility.
+        <v xml:space="preserve">For each facility:
+  1. LOAD pd_pct, lgd_pct from l2.facility_risk_snapshot
+  2. LOAD committed_amount from l2.facility_exposure_snapshot
+  3. COMPUTE EL Rate = SUM(PD/100 × LGD/100 × Committed) / SUM(Committed) × 100
+     At facility grain, committed cancels → EL Rate ≈ PD × LGD / 100
+Ingredients: pd_pct (L2), lgd_pct (L2), committed_amount (L2)
 </v>
       </c>
       <c r="K24" t="str">
@@ -2545,10 +2561,15 @@
         <v>Y</v>
       </c>
       <c r="M24" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N24" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level expected_loss_rate_pct per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD pd_pct, lgd_pct for all facilities belonging to this counterparty
+  2. LOAD committed_amount for each facility
+  3. CONVERT to USD via l2.fx_rate spot rate
+  4. COMPUTE SUM(PD × LGD × Committed × FX) / SUM(Committed × FX) × 100
+Sum-ratio rollup with FX: exposure-weighted average EL rate in USD terms.
 </v>
       </c>
       <c r="O24" t="str">
@@ -2558,10 +2579,14 @@
         <v>Y</v>
       </c>
       <c r="Q24" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="R24" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level expected_loss_rate_pct per L3 desk segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOOKUP managed_segment_id from enterprise_business_taxonomy
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(PD × LGD × Committed × FX) / SUM(Committed × FX) × 100
+Sum-ratio rollup: exposure-weighted average EL rate per desk.
 </v>
       </c>
       <c r="S24" t="str">
@@ -2571,10 +2596,14 @@
         <v>Y</v>
       </c>
       <c r="U24" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V24" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level expected_loss_rate_pct per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(PD × LGD × Committed × FX) / SUM(Committed × FX) × 100
+Sum-ratio rollup: exposure-weighted average EL rate per portfolio.
 </v>
       </c>
       <c r="W24" t="str">
@@ -2584,10 +2613,14 @@
         <v>Y</v>
       </c>
       <c r="Y24" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z24" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level expected_loss_rate_pct per L1 business segment segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(PD × LGD × Committed × FX) / SUM(Committed × FX) × 100
+Sum-ratio rollup: exposure-weighted average EL rate per segment.
 </v>
       </c>
       <c r="AA24" t="str">
@@ -2602,14 +2635,25 @@
         <v>EXP-016</v>
       </c>
       <c r="B25" t="str" xml:space="preserve">
-        <v xml:space="preserve">PD × LGD × Exposure expressed in USD. Calculated forward-looking loss metric supporting provisioning, capital planning, and stress testing analytics.
+        <v xml:space="preserve">Expected Loss in dollar terms: PD × LGD × Committed Exposure × Bank Share. Computed from L2 atomic risk parameters and exposure data — NOT from stressed scenarios. This is the base (unstressed) expected credit loss, the foundation for provisioning, capital planning, and CECL/IFRS 9 reserve estimation.
+Ingredient derivation:
+  - PD (pd_pct): L2 facility_risk_snapshot — probability of default (%)
+  - LGD (lgd_pct): L2 facility_risk_snapshot — loss given default (%)
+  - Committed Exposure (committed_amount): L2 facility_exposure_snapshot — raw
+  - Bank Share (bank_share_pct): L2 facility_exposure_snapshot — participation %
+  - EL = (PD/100) × (LGD/100) × Committed × (Bank Share/100)
+Rollup uses direct-sum: SUM(facility EL) at each aggregate level. FX conversion applied at aggregate levels for multi-currency portfolios.
 </v>
       </c>
       <c r="C25" t="str">
         <v>Expected Loss ($)</v>
       </c>
       <c r="D25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(stressed_expected_loss) per facility from stress_test_result. Weighted by bank share percentage.
+        <v xml:space="preserve">For each facility:
+  1. LOAD pd_pct, lgd_pct from l2.facility_risk_snapshot
+  2. LOAD committed_amount, bank_share_pct from l2.facility_exposure_snapshot
+  3. COMPUTE EL = (PD/100) × (LGD/100) × Committed × (Bank Share/100)
+Ingredients: pd_pct (L2), lgd_pct (L2), committed_amount (L2), bank_share_pct (L2)
 </v>
       </c>
       <c r="E25" t="str">
@@ -2625,10 +2669,14 @@
         <v>Y</v>
       </c>
       <c r="I25" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="J25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(stressed_expected_loss) per facility from stress_test_result. Weighted by bank share percentage.
+        <v xml:space="preserve">For each facility:
+  1. LOAD pd_pct, lgd_pct from l2.facility_risk_snapshot
+  2. LOAD committed_amount, bank_share_pct from l2.facility_exposure_snapshot
+  3. COMPUTE EL = (PD/100) × (LGD/100) × Committed × (Bank Share/100)
+Ingredients: pd_pct (L2), lgd_pct (L2), committed_amount (L2), bank_share_pct (L2)
 </v>
       </c>
       <c r="K25" t="str">
@@ -2641,7 +2689,11 @@
         <v>Agg</v>
       </c>
       <c r="N25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD facility-level EL for all facilities of this counterparty
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(facility EL × FX rate) = Counterparty EL (USD)
+Direct-sum rollup with FX conversion.
 </v>
       </c>
       <c r="O25" t="str">
@@ -2654,7 +2706,11 @@
         <v>Agg</v>
       </c>
       <c r="R25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per L3 desk segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOOKUP managed_segment_id from enterprise_business_taxonomy
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(facility EL × FX rate) per desk
+Direct-sum rollup with FX conversion.
 </v>
       </c>
       <c r="S25" t="str">
@@ -2667,7 +2723,11 @@
         <v>Agg</v>
       </c>
       <c r="V25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(facility EL × FX rate) per portfolio
+Direct-sum rollup with FX conversion.
 </v>
       </c>
       <c r="W25" t="str">
@@ -2680,7 +2740,11 @@
         <v>Agg</v>
       </c>
       <c r="Z25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per L1 business segment segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(facility EL × FX rate) per business segment
+Direct-sum rollup with FX conversion.
 </v>
       </c>
       <c r="AA25" t="str">
@@ -3462,14 +3526,14 @@
         <v>EXP-025</v>
       </c>
       <c r="B34" t="str" xml:space="preserve">
-        <v xml:space="preserve">The average expected loss rate (percent of exposure) if default occurs, weighted across exposures (typically by EAD).
+        <v xml:space="preserve">Exposure-weighted average Loss Given Default rate expressed as a decimal fraction (e.g. 0.45 = 45%). At facility level, reads lgd_pct directly from facility_risk_snapshot. At aggregate levels, computes the commitment-adjusted weighted average: SUM(lgd_pct * outstanding_balance_amt) / SUM(committed_amount), with FX conversion for cross-currency portfolios. LGD represents the expected severity of loss if the obligor defaults, a key input to Expected Loss (EL = PD x LGD x EAD) under Basel III IRB.
 </v>
       </c>
       <c r="C34" t="str">
         <v>Loss Given Default (%)</v>
       </c>
       <c r="D34" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated lgd_pct per facility.
+        <v xml:space="preserve">Direct lookup of lgd_pct per facility from facility_risk_snapshot. No aggregation needed — facility-level LGD is a sourced atomic value.
 </v>
       </c>
       <c r="E34" t="str">
@@ -3485,10 +3549,10 @@
         <v>Y</v>
       </c>
       <c r="I34" t="str">
-        <v>Calc</v>
+        <v>Raw</v>
       </c>
       <c r="J34" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated lgd_pct per facility.
+        <v xml:space="preserve">Direct lookup of lgd_pct per facility from facility_risk_snapshot. No aggregation needed — facility-level LGD is a sourced atomic value.
 </v>
       </c>
       <c r="K34" t="str">
@@ -3501,7 +3565,7 @@
         <v>Avg</v>
       </c>
       <c r="N34" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of lgd_pct across counterparty facilities.
+        <v xml:space="preserve">Commitment-adjusted exposure-weighted LGD per counterparty: SUM(lgd_pct * outstanding_balance_amt * fx_rate) / NULLIF(SUM(committed_amount * fx_rate), 0). FX conversion ensures proper weighting across multi-currency facilities.
 </v>
       </c>
       <c r="O34" t="str">
@@ -3511,10 +3575,10 @@
         <v>Y</v>
       </c>
       <c r="Q34" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="R34" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level lgd_pct per L3 desk segment.
+        <v xml:space="preserve">Commitment-adjusted exposure-weighted LGD per L3 desk segment: SUM(lgd_pct * outstanding_balance_amt * fx_rate) / NULLIF(SUM(committed_amount * fx_rate), 0). Standard EBT hierarchy direct join for desk grouping.
 </v>
       </c>
       <c r="S34" t="str">
@@ -3524,10 +3588,10 @@
         <v>Y</v>
       </c>
       <c r="U34" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="V34" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level lgd_pct per L2 portfolio segment.
+        <v xml:space="preserve">Commitment-adjusted exposure-weighted LGD per L2 portfolio segment: SUM(lgd_pct * outstanding_balance_amt * fx_rate) / NULLIF(SUM(committed_amount * fx_rate), 0). One-hop EBT traversal for portfolio grouping.
 </v>
       </c>
       <c r="W34" t="str">
@@ -3537,10 +3601,10 @@
         <v>Y</v>
       </c>
       <c r="Y34" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="Z34" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level lgd_pct per L1 business segment segment.
+        <v xml:space="preserve">Commitment-adjusted exposure-weighted LGD per L1 business segment: SUM(lgd_pct * outstanding_balance_amt * fx_rate) / NULLIF(SUM(committed_amount * fx_rate), 0). Two-hop EBT traversal for business segment grouping.
 </v>
       </c>
       <c r="AA34" t="str">
@@ -5796,14 +5860,15 @@
         <v>PRC-003</v>
       </c>
       <c r="B59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of exposures within portfolio with approved pricing or policy exceptions. Derived governance KPI measuring policy discipline and risk culture strength.
+        <v xml:space="preserve">Percentage of facilities with approved pricing or policy exceptions. Computed as COUNT(exception facilities) / COUNT(total facilities) × 100. Sourced from L2 facility_pricing_snapshot — the atomic pricing record — using the is_pricing_exception_flag. At aggregate levels, uses count-ratio rollup: re-counts exceptions and totals across all constituent facilities, never averages pre-computed rates. Key governance KPI measuring policy discipline, risk culture strength, and pricing override frequency.
 </v>
       </c>
       <c r="C59" t="str">
         <v>Exception Rate (%)</v>
       </c>
       <c r="D59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if pricing exception, 0 otherwise.
+        <v xml:space="preserve">Binary flag: 1.0 if pricing exception approved, 0.0 otherwise.
+Ingredients: is_pricing_exception_flag (L2 facility_pricing_snapshot)
 </v>
       </c>
       <c r="E59" t="str">
@@ -5822,7 +5887,8 @@
         <v>Calc</v>
       </c>
       <c r="J59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if pricing exception, 0 otherwise.
+        <v xml:space="preserve">Binary flag: 1.0 if pricing exception approved, 0.0 otherwise.
+Ingredients: is_pricing_exception_flag (L2 facility_pricing_snapshot)
 </v>
       </c>
       <c r="K59" t="str">
@@ -5835,7 +5901,10 @@
         <v>Calc</v>
       </c>
       <c r="N59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with pricing exception per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD is_pricing_exception_flag for all facilities of this counterparty
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup: re-counts from facility-level flags.
 </v>
       </c>
       <c r="O59" t="str">
@@ -5848,7 +5917,10 @@
         <v>Calc</v>
       </c>
       <c r="R59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with pricing exception per L3 desk.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOOKUP managed_segment_id from enterprise_business_taxonomy
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup per desk.
 </v>
       </c>
       <c r="S59" t="str">
@@ -5861,7 +5933,10 @@
         <v>Calc</v>
       </c>
       <c r="V59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with pricing exception per L2 portfolio.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup per portfolio.
 </v>
       </c>
       <c r="W59" t="str">
@@ -5874,7 +5949,10 @@
         <v>Calc</v>
       </c>
       <c r="Z59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with pricing exception per L1 business segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup per business segment.
 </v>
       </c>
       <c r="AA59" t="str">
@@ -6830,14 +6908,14 @@
         <v>REF-004</v>
       </c>
       <c r="B70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Unique system identifier assigned to the borrower or obligor. Used for exposure aggregation and risk consolidation.
+        <v xml:space="preserve">Unique system identifier assigned to the borrower or obligor. Used for exposure aggregation and risk consolidation across the GSIB. At facility level, returns the counterparty_id linked to each facility. At upper levels, returns COUNT(DISTINCT counterparty_id) — the number of unique obligors in each organizational segment.
 </v>
       </c>
       <c r="C70" t="str">
         <v>Counterparty ID</v>
       </c>
       <c r="D70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">Direct lookup of counterparty_id from facility_master for each active facility. Uses current records only (SCD2 filtered).
 </v>
       </c>
       <c r="E70" t="str">
@@ -6856,7 +6934,7 @@
         <v>Raw</v>
       </c>
       <c r="J70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">Direct lookup of counterparty_id from facility_master for each active facility. Uses current records only (SCD2 filtered).
 </v>
       </c>
       <c r="K70" t="str">
@@ -6869,7 +6947,7 @@
         <v>Raw</v>
       </c>
       <c r="N70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">Identity — returns counterparty_id for each current counterparty.
 </v>
       </c>
       <c r="O70" t="str">
@@ -6882,7 +6960,7 @@
         <v>Agg</v>
       </c>
       <c r="R70" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L3 desk segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L3 desk segment — number of unique obligors in each desk.
 </v>
       </c>
       <c r="S70" t="str">
@@ -6895,7 +6973,7 @@
         <v>Agg</v>
       </c>
       <c r="V70" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L2 portfolio segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L2 portfolio segment — number of unique obligors in each portfolio.
 </v>
       </c>
       <c r="W70" t="str">
@@ -6908,7 +6986,7 @@
         <v>Agg</v>
       </c>
       <c r="Z70" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L1 business segment segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L1 business segment — number of unique obligors in each business segment.
 </v>
       </c>
       <c r="AA70" t="str">
@@ -6923,14 +7001,14 @@
         <v>REF-005</v>
       </c>
       <c r="B71" t="str" xml:space="preserve">
-        <v xml:space="preserve">Descriptive name of the counterparty as documented in the credit agreement. Used for reporting clarity and operational reference.
+        <v xml:space="preserve">Legal name of the counterparty as documented in the credit agreement. At facility level, returns the counterparty_id (numeric proxy for the name since metric values are numeric). At counterparty level, identity lookup. At upper levels, COUNT(DISTINCT counterparty_id) — number of unique named obligors per organizational segment. Used for reporting clarity and operational reference across all regulatory submissions.
 </v>
       </c>
       <c r="C71" t="str">
         <v>Counterparty Name</v>
       </c>
       <c r="D71" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read legal_name from counterparty for each facility's counterparty.
+        <v xml:space="preserve">Lookup counterparty_id from facility_master for each active facility. The numeric counterparty_id serves as proxy for the legal name (string values resolved via counterparty dimension join at display time). Uses current records only.
 </v>
       </c>
       <c r="E71" t="str">
@@ -6949,7 +7027,7 @@
         <v>Raw</v>
       </c>
       <c r="J71" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read legal_name from counterparty for each facility's counterparty.
+        <v xml:space="preserve">Lookup counterparty_id from facility_master for each active facility. The numeric counterparty_id serves as proxy for the legal name (string values resolved via counterparty dimension join at display time). Uses current records only.
 </v>
       </c>
       <c r="K71" t="str">
@@ -6959,10 +7037,10 @@
         <v>Y</v>
       </c>
       <c r="M71" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="N71" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with counterparty name per counterparty.
+        <v xml:space="preserve">Identity — returns counterparty_id for each current counterparty. Legal name resolved via counterparty dimension join at display time.
 </v>
       </c>
       <c r="O71" t="str">
@@ -6975,7 +7053,7 @@
         <v>Agg</v>
       </c>
       <c r="R71" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with counterparty name per L3 desk segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L3 desk segment — number of unique named obligors in each desk.
 </v>
       </c>
       <c r="S71" t="str">
@@ -6988,7 +7066,7 @@
         <v>Agg</v>
       </c>
       <c r="V71" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with counterparty name per L2 portfolio segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L2 portfolio segment — number of unique named obligors in each portfolio.
 </v>
       </c>
       <c r="W71" t="str">
@@ -7001,7 +7079,7 @@
         <v>Agg</v>
       </c>
       <c r="Z71" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with counterparty name per L1 business segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L1 business segment — number of unique named obligors in each business segment.
 </v>
       </c>
       <c r="AA71" t="str">
@@ -7016,14 +7094,14 @@
         <v>REF-006</v>
       </c>
       <c r="B72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Country of risk or booking location. Supports geographic concentration and sovereign risk analysis.
+        <v xml:space="preserve">Country of risk derived from the counterparty's domicile. At facility level, returns a numeric country identifier (via counterparty → country_dim join path). At counterparty level, identity lookup. At desk/portfolio/segment levels, COUNT(DISTINCT country_code) — geographic diversification indicator showing the number of unique countries represented. Supports FFIEC 009 Country Exposure Report and Basel III geographic concentration analysis.
 </v>
       </c>
       <c r="C72" t="str">
         <v>Country</v>
       </c>
       <c r="D72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of country_name from country_dim.
+        <v xml:space="preserve">Lookup country for each facility via counterparty → country_dim join path. Returns counterparty_id as numeric proxy (country_name resolved at display time via dimension join). Uses current records only.
 </v>
       </c>
       <c r="E72" t="str">
@@ -7042,7 +7120,7 @@
         <v>Raw</v>
       </c>
       <c r="J72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of country_name from country_dim.
+        <v xml:space="preserve">Lookup country for each facility via counterparty → country_dim join path. Returns counterparty_id as numeric proxy (country_name resolved at display time via dimension join). Uses current records only.
 </v>
       </c>
       <c r="K72" t="str">
@@ -7055,7 +7133,7 @@
         <v>Raw</v>
       </c>
       <c r="N72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read country_name per counterparty.
+        <v xml:space="preserve">Lookup country for each counterparty via country_code → country_dim join. Returns counterparty_id as numeric proxy.
 </v>
       </c>
       <c r="O72" t="str">
@@ -7068,7 +7146,7 @@
         <v>Agg</v>
       </c>
       <c r="R72" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level country_name per L3 desk segment.
+        <v xml:space="preserve">COUNT(DISTINCT country_code) per L3 desk segment — number of unique countries represented, a geographic diversification indicator.
 </v>
       </c>
       <c r="S72" t="str">
@@ -7081,7 +7159,7 @@
         <v>Agg</v>
       </c>
       <c r="V72" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level country_name per L2 portfolio segment.
+        <v xml:space="preserve">COUNT(DISTINCT country_code) per L2 portfolio segment — number of unique countries represented in each portfolio.
 </v>
       </c>
       <c r="W72" t="str">
@@ -7094,7 +7172,7 @@
         <v>Agg</v>
       </c>
       <c r="Z72" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level country_name per L1 business segment segment.
+        <v xml:space="preserve">COUNT(DISTINCT country_code) per L1 business segment — geographic diversification at the highest organizational level.
 </v>
       </c>
       <c r="AA72" t="str">
@@ -7109,14 +7187,14 @@
         <v>REF-007</v>
       </c>
       <c r="B73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Unique identifier linking facility to governing credit agreement documentation.
+        <v xml:space="preserve">Unique identifier linking each facility to its governing credit agreement documentation. Used for contract tracking, facility-to-agreement linkage, and regulatory reporting. At counterparty level, returns count of distinct credit agreements per borrower.
 </v>
       </c>
       <c r="C73" t="str">
         <v>Credit Agreement ID</v>
       </c>
       <c r="D73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of credit_agreement_id from credit_agreement_master.
+        <v xml:space="preserve">Direct lookup of credit_agreement_id for each active facility via facility_master joined to credit_agreement_master.
 </v>
       </c>
       <c r="E73" t="str">
@@ -7135,7 +7213,7 @@
         <v>Raw</v>
       </c>
       <c r="J73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of credit_agreement_id from credit_agreement_master.
+        <v xml:space="preserve">Direct lookup of credit_agreement_id for each active facility via facility_master joined to credit_agreement_master.
 </v>
       </c>
       <c r="K73" t="str">
@@ -7145,10 +7223,10 @@
         <v>Y</v>
       </c>
       <c r="M73" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="N73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read credit_agreement_id per counterparty.
+        <v xml:space="preserve">Count of distinct credit agreements per counterparty. Provides visibility into borrower complexity and multi-agreement relationships.
 </v>
       </c>
       <c r="O73" t="str">
@@ -7161,7 +7239,7 @@
         <v>Agg</v>
       </c>
       <c r="R73" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level credit_agreement_id per L3 desk segment.
+        <v xml:space="preserve">Count of distinct credit agreements per L3 desk segment via enterprise_business_taxonomy.
 </v>
       </c>
       <c r="S73" t="str">
@@ -7174,7 +7252,7 @@
         <v>Agg</v>
       </c>
       <c r="V73" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level credit_agreement_id per L2 portfolio segment.
+        <v xml:space="preserve">Count of distinct credit agreements per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
 </v>
       </c>
       <c r="W73" t="str">
@@ -7187,7 +7265,7 @@
         <v>Agg</v>
       </c>
       <c r="Z73" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level credit_agreement_id per L1 business segment segment.
+        <v xml:space="preserve">Count of distinct credit agreements per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
 </v>
       </c>
       <c r="AA73" t="str">
@@ -7295,7 +7373,7 @@
         <v>REF-009</v>
       </c>
       <c r="B75" t="str" xml:space="preserve">
-        <v xml:space="preserve">Date on which loan or contract became legally effective.
+        <v xml:space="preserve">Date on which loan or contract became legally effective. Sourced directly from facility_master. At aggregate levels, returns the earliest origination date (MIN) across constituent facilities — indicating the oldest vintage in the book. Key contract lifecycle tracking attribute for vintage analysis and portfolio seasoning assessment.
 </v>
       </c>
       <c r="C75" t="str">
@@ -7303,6 +7381,7 @@
       </c>
       <c r="D75" t="str" xml:space="preserve">
         <v xml:space="preserve">Direct lookup of origination_date from facility_master.
+Ingredients: origination_date (L2 facility_master — raw field)
 </v>
       </c>
       <c r="E75" t="str">
@@ -7322,6 +7401,7 @@
       </c>
       <c r="J75" t="str" xml:space="preserve">
         <v xml:space="preserve">Direct lookup of origination_date from facility_master.
+Ingredients: origination_date (L2 facility_master — raw field)
 </v>
       </c>
       <c r="K75" t="str">
@@ -7334,7 +7414,10 @@
         <v>Agg</v>
       </c>
       <c r="N75" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level origination_date) per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD origination_date from l2.facility_master for all active facilities
+  2. COMPUTE MIN(origination_date) — earliest contract vintage
+Indicates the oldest banking relationship tenure for this counterparty.
 </v>
       </c>
       <c r="O75" t="str">
@@ -7347,7 +7430,10 @@
         <v>Agg</v>
       </c>
       <c r="R75" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level origination_date per L3 desk segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOAD origination_date from l2.facility_master
+  2. JOIN l1.enterprise_business_taxonomy on lob_segment_id
+  3. COMPUTE MIN(origination_date) — earliest vintage in desk book
 </v>
       </c>
       <c r="S75" t="str">
@@ -7360,7 +7446,9 @@
         <v>Agg</v>
       </c>
       <c r="V75" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level origination_date per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. COMPUTE MIN(origination_date) — earliest vintage in portfolio
 </v>
       </c>
       <c r="W75" t="str">
@@ -7373,7 +7461,9 @@
         <v>Agg</v>
       </c>
       <c r="Z75" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level origination_date per L1 business segment segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. COMPUTE MIN(origination_date) — earliest vintage in business segment
 </v>
       </c>
       <c r="AA75" t="str">
@@ -8132,14 +8222,14 @@
         <v>REF-018</v>
       </c>
       <c r="B84" t="str" xml:space="preserve">
-        <v xml:space="preserve">Line of Business classification associated with exposure.
+        <v xml:space="preserve">Line of Business classification code associated with each exposure. Returns the hierarchical parent path code from the enterprise_business_taxonomy for the segment directly assigned to each facility via lob_segment_id. Used to group and filter exposures by organizational business line.
 </v>
       </c>
       <c r="C84" t="str">
         <v>Line of Business Level Name</v>
       </c>
       <c r="D84" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
+        <v xml:space="preserve">Direct lookup of parent code from enterprise_business_taxonomy via facility_master.lob_segment_id.
 </v>
       </c>
       <c r="E84" t="str">
@@ -8158,7 +8248,7 @@
         <v>Raw</v>
       </c>
       <c r="J84" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
+        <v xml:space="preserve">Direct lookup of parent code from enterprise_business_taxonomy via facility_master.lob_segment_id.
 </v>
       </c>
       <c r="K84" t="str">
@@ -8171,7 +8261,7 @@
         <v>Raw</v>
       </c>
       <c r="N84" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read parent per counterparty.
+        <v xml:space="preserve">Deterministic selection (MIN) of parent code across all facilities belonging to the counterparty.
 </v>
       </c>
       <c r="O84" t="str">
@@ -8181,10 +8271,10 @@
         <v>Y</v>
       </c>
       <c r="Q84" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="R84" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level parent per L3 desk segment.
+        <v xml:space="preserve">Direct parent code lookup per L3 desk segment. Groups facilities by their assigned EBT segment and returns the segment parent code.
 </v>
       </c>
       <c r="S84" t="str">
@@ -8194,10 +8284,10 @@
         <v>Y</v>
       </c>
       <c r="U84" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="V84" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level parent per L2 portfolio segment.
+        <v xml:space="preserve">Parent code at L2 portfolio level via one-hop EBT traversal.
 </v>
       </c>
       <c r="W84" t="str">
@@ -8207,10 +8297,10 @@
         <v>Y</v>
       </c>
       <c r="Y84" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="Z84" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level parent per L1 business segment segment.
+        <v xml:space="preserve">Parent code at L1 business segment level via two-hop EBT traversal.
 </v>
       </c>
       <c r="AA84" t="str">
@@ -8225,14 +8315,14 @@
         <v>REF-019</v>
       </c>
       <c r="B85" t="str" xml:space="preserve">
-        <v xml:space="preserve">Level 1 Line of Business hierarchy. Enables top-level organizational risk aggregation, representing the Department (e.g. Commercial Real Estate, Corporate Banking)
+        <v xml:space="preserve">Level 1 (Department) Line of Business hierarchy code. For each facility, traverses two hops up from the assigned EBT segment via parent_segment_id to reach the L1 department node, returning its parent path code. Enables top-level organizational risk aggregation (e.g. Corporate Banking, Commercial Real Estate).
 </v>
       </c>
       <c r="C85" t="str">
-        <v>Line of Business  L1</v>
+        <v>Line of Business L1</v>
       </c>
       <c r="D85" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
+        <v xml:space="preserve">Traverse two hops up the EBT hierarchy from facility lob_segment_id to reach the L1 department ancestor and return its parent code.
 </v>
       </c>
       <c r="E85" t="str">
@@ -8251,11 +8341,11 @@
         <v>Raw</v>
       </c>
       <c r="J85" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
+        <v xml:space="preserve">Traverse two hops up the EBT hierarchy from facility lob_segment_id to reach the L1 department ancestor and return its parent code.
 </v>
       </c>
       <c r="K85" t="str">
-        <v>Line of Business  L1 (facility)</v>
+        <v>Line of Business L1 (facility)</v>
       </c>
       <c r="L85" t="str">
         <v>Y</v>
@@ -8264,50 +8354,50 @@
         <v>Raw</v>
       </c>
       <c r="N85" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read parent per counterparty.
+        <v xml:space="preserve">Deterministic selection (MIN) of L1 department parent code across all facilities belonging to the counterparty.
 </v>
       </c>
       <c r="O85" t="str">
-        <v>Line of Business  L1 (counterparty)</v>
+        <v>Line of Business L1 (counterparty)</v>
       </c>
       <c r="P85" t="str">
         <v>Y</v>
       </c>
       <c r="Q85" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="R85" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level parent per L3 desk segment.
+        <v xml:space="preserve">For each L3 desk, traverse two hops up to the L1 department ancestor and return its parent code.
 </v>
       </c>
       <c r="S85" t="str">
-        <v>Line of Business  L1 (desk)</v>
+        <v>Line of Business L1 (desk)</v>
       </c>
       <c r="T85" t="str">
         <v>Y</v>
       </c>
       <c r="U85" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="V85" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level parent per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 portfolio, traverse one hop up to the L1 department ancestor and return its parent code.
 </v>
       </c>
       <c r="W85" t="str">
-        <v>Line of Business  L1 (portfolio)</v>
+        <v>Line of Business L1 (portfolio)</v>
       </c>
       <c r="X85" t="str">
         <v>Y</v>
       </c>
       <c r="Y85" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="Z85" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level parent per L1 business segment segment.
+        <v xml:space="preserve">At L1 business segment level, the segment IS the L1 department. Return its own parent code directly.
 </v>
       </c>
       <c r="AA85" t="str">
-        <v>Line of Business  L1 (business_segment)</v>
+        <v>Line of Business L1 (business_segment)</v>
       </c>
       <c r="AB85" t="str">
         <v/>
@@ -8318,14 +8408,14 @@
         <v>REF-020</v>
       </c>
       <c r="B86" t="str" xml:space="preserve">
-        <v xml:space="preserve">Level 2 Line of Business hierarchy for intermediate aggregation and reporting, representing the Portfolio within the L1 LoB (e.g., CRE &gt; Office)
+        <v xml:space="preserve">Level 2 (Portfolio) Line of Business hierarchy code. For each facility, traverses one hop up from the assigned EBT segment via parent_segment_id to reach the L2 portfolio node, returning its parent path code. Enables detailed business segment analysis (e.g. CRE &gt; Office).
 </v>
       </c>
       <c r="C86" t="str">
         <v>Line of Business L2</v>
       </c>
       <c r="D86" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
+        <v xml:space="preserve">Traverse one hop up the EBT hierarchy from facility lob_segment_id to reach the L2 portfolio ancestor and return its parent code.
 </v>
       </c>
       <c r="E86" t="str">
@@ -8344,7 +8434,7 @@
         <v>Raw</v>
       </c>
       <c r="J86" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
+        <v xml:space="preserve">Traverse one hop up the EBT hierarchy from facility lob_segment_id to reach the L2 portfolio ancestor and return its parent code.
 </v>
       </c>
       <c r="K86" t="str">
@@ -8357,7 +8447,7 @@
         <v>Raw</v>
       </c>
       <c r="N86" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read parent per counterparty.
+        <v xml:space="preserve">Deterministic selection (MIN) of L2 portfolio parent code across all facilities belonging to the counterparty.
 </v>
       </c>
       <c r="O86" t="str">
@@ -8367,10 +8457,10 @@
         <v>Y</v>
       </c>
       <c r="Q86" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="R86" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level parent per L3 desk segment.
+        <v xml:space="preserve">For each L3 desk, traverse one hop up to the L2 portfolio ancestor and return its parent code.
 </v>
       </c>
       <c r="S86" t="str">
@@ -8380,10 +8470,10 @@
         <v>Y</v>
       </c>
       <c r="U86" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="V86" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level parent per L2 portfolio segment.
+        <v xml:space="preserve">At L2 portfolio level, the segment IS the L2 portfolio. Return its own parent code directly.
 </v>
       </c>
       <c r="W86" t="str">
@@ -8393,10 +8483,10 @@
         <v>Y</v>
       </c>
       <c r="Y86" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="Z86" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level parent per L1 business segment segment.
+        <v xml:space="preserve">For each L1 business segment, returns the L2 portfolio parent codes of child portfolios. Uses MIN for deterministic string selection.
 </v>
       </c>
       <c r="AA86" t="str">
@@ -8411,14 +8501,14 @@
         <v>REF-021</v>
       </c>
       <c r="B87" t="str" xml:space="preserve">
-        <v xml:space="preserve">Level 3 Line of Business hierarchy for detailed business segmentation, representing the Desk within the L2 LoB (e.g. CRE &gt; Office &gt; Lease Up Desk)
+        <v xml:space="preserve">Level 3 (Desk) Line of Business hierarchy code. Returns the parent path code of the EBT segment directly assigned to each facility via lob_segment_id. Represents the most granular organizational segment view (e.g. CRE &gt; Office &gt; Lease Up Desk).
 </v>
       </c>
       <c r="C87" t="str">
         <v>Line of Business L3</v>
       </c>
       <c r="D87" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
+        <v xml:space="preserve">Direct lookup of parent code from enterprise_business_taxonomy via facility_master.lob_segment_id. For L3-assigned facilities this returns the L3 desk parent code.
 </v>
       </c>
       <c r="E87" t="str">
@@ -8437,7 +8527,7 @@
         <v>Raw</v>
       </c>
       <c r="J87" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
+        <v xml:space="preserve">Direct lookup of parent code from enterprise_business_taxonomy via facility_master.lob_segment_id. For L3-assigned facilities this returns the L3 desk parent code.
 </v>
       </c>
       <c r="K87" t="str">
@@ -8450,7 +8540,7 @@
         <v>Raw</v>
       </c>
       <c r="N87" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read parent per counterparty.
+        <v xml:space="preserve">Deterministic selection (MIN) of L3 desk parent code across all facilities belonging to the counterparty.
 </v>
       </c>
       <c r="O87" t="str">
@@ -8460,10 +8550,10 @@
         <v>Y</v>
       </c>
       <c r="Q87" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="R87" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level parent per L3 desk segment.
+        <v xml:space="preserve">Direct parent code lookup per L3 desk segment. The desk level IS the L3 level, so return the segment own parent code.
 </v>
       </c>
       <c r="S87" t="str">
@@ -8473,10 +8563,10 @@
         <v>Y</v>
       </c>
       <c r="U87" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="V87" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level parent per L2 portfolio segment.
+        <v xml:space="preserve">L3 desk parent codes rolled up to L2 portfolio level. Returns MIN of desk-level parent codes within each portfolio.
 </v>
       </c>
       <c r="W87" t="str">
@@ -8486,10 +8576,10 @@
         <v>Y</v>
       </c>
       <c r="Y87" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="Z87" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level parent per L1 business segment segment.
+        <v xml:space="preserve">L3 desk parent codes rolled up to L1 business segment level. Returns MIN of desk-level parent codes within each segment.
 </v>
       </c>
       <c r="AA87" t="str">
@@ -9620,14 +9710,14 @@
         <v>RSK-001</v>
       </c>
       <c r="B100" t="str" xml:space="preserve">
-        <v xml:space="preserve">Most recent internal credit rating assigned at reporting date. Used for segmentation and exposure-weighted risk aggregation.
+        <v xml:space="preserve">Risk rating tier derived from counterparty probability of default (PD). Each counterparty's pd_annual is matched against the risk_rating_tier_dim reference table (pd_min_pct / pd_max_pct boundaries) to assign a tier classification. At facility level, the tier is inherited from the owning counterparty. At aggregate levels, MAX (worst-case) tier ordinal is reported.
 </v>
       </c>
       <c r="C100" t="str">
         <v>Risk Rating Tier</v>
       </c>
       <c r="D100" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility.
+        <v xml:space="preserve">For each facility, inherit the risk rating tier from the owning counterparty. Join facility_master to counterparty, then range-match counterparty pd_annual against risk_rating_tier_dim to derive the tier ordinal (display_order).
 </v>
       </c>
       <c r="E100" t="str">
@@ -9643,10 +9733,10 @@
         <v>Y</v>
       </c>
       <c r="I100" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="J100" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility.
+        <v xml:space="preserve">For each facility, inherit the risk rating tier from the owning counterparty. Join facility_master to counterparty, then range-match counterparty pd_annual against risk_rating_tier_dim to derive the tier ordinal (display_order).
 </v>
       </c>
       <c r="K100" t="str">
@@ -9656,10 +9746,10 @@
         <v>Y</v>
       </c>
       <c r="M100" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N100" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating per counterparty.
+        <v xml:space="preserve">For each counterparty, look up pd_annual and range-match against risk_rating_tier_dim where pd_annual &gt;= pd_min_pct AND pd_annual &lt; pd_max_pct. Returns the tier ordinal (display_order). Counterparties with NULL PD receive tier 0 (unrated).
 </v>
       </c>
       <c r="O100" t="str">
@@ -9672,7 +9762,7 @@
         <v>Agg</v>
       </c>
       <c r="R100" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating per L3 desk segment.
+        <v xml:space="preserve">Worst-case (MAX) risk rating tier ordinal across all counterparties in the L3 desk segment. Higher ordinal = riskier tier. Full tier distribution available via counterparty-level drill-down.
 </v>
       </c>
       <c r="S100" t="str">
@@ -9685,7 +9775,7 @@
         <v>Agg</v>
       </c>
       <c r="V100" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating per L2 portfolio segment.
+        <v xml:space="preserve">Worst-case (MAX) risk rating tier ordinal per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
 </v>
       </c>
       <c r="W100" t="str">
@@ -9698,7 +9788,7 @@
         <v>Agg</v>
       </c>
       <c r="Z100" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating per L1 business segment.
+        <v xml:space="preserve">Worst-case (MAX) risk rating tier ordinal per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
 </v>
       </c>
       <c r="AA100" t="str">

--- a/data/metrics_dimensions_filled.xlsx
+++ b/data/metrics_dimensions_filled.xlsx
@@ -1539,14 +1539,14 @@
         <v>EXP-005</v>
       </c>
       <c r="B14" t="str" xml:space="preserve">
-        <v xml:space="preserve">The portion of total funding-related expense attributed to a specific exposure or portfolio. At facility level, calculated as SUM across all positions of (funded_amount * interest_rate), adjusted for bank share. At counterparty level, further adjusted by counterparty participation_pct. At desk/portfolio/segment levels, aggregated as SUM.
+        <v xml:space="preserve">The portion of total funding-related expense attributed to a specific exposure or portfolio. At facility level, calculated as SUM across all positions of (funded_amount * interest_rate), converted to USD via FX rate and adjusted for bank share. At counterparty level, further adjusted by counterparty participation_pct. At desk/portfolio/segment levels, aggregated as SUM via EBT hierarchy.
 </v>
       </c>
       <c r="C14" t="str">
         <v>Cost of Funds ($)</v>
       </c>
       <c r="D14" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each position under the facility: funded_amount * interest_rate = Position Cost of Funds. Adjusted by bank_share: SUM(funded_amount * interest_rate) * bank_share_pct / 100. Joins position_detail → position (for facility_id) → facility_master.
+        <v xml:space="preserve">For each position under the facility, compute funded_amount x interest_rate, convert to USD using the FX spot rate (defaults to 1.0 for USD positions). Sum across all positions, then multiply by the bank's share percentage. Result = annual cost of funds for this facility in USD.
 </v>
       </c>
       <c r="E14" t="str">
@@ -1565,7 +1565,7 @@
         <v>Calc</v>
       </c>
       <c r="J14" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each position under the facility: funded_amount * interest_rate = Position Cost of Funds. Adjusted by bank_share: SUM(funded_amount * interest_rate) * bank_share_pct / 100. Joins position_detail → position (for facility_id) → facility_master.
+        <v xml:space="preserve">For each position under the facility, compute funded_amount x interest_rate, convert to USD using the FX spot rate (defaults to 1.0 for USD positions). Sum across all positions, then multiply by the bank's share percentage. Result = annual cost of funds for this facility in USD.
 </v>
       </c>
       <c r="K14" t="str">
@@ -1578,7 +1578,7 @@
         <v>Agg</v>
       </c>
       <c r="N14" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each counterparty: SUM of facility-level cost of funds weighted by counterparty participation_pct from facility_counterparty_participation.
+        <v xml:space="preserve">Sum each facility's cost of funds (USD, bank-share-adjusted), then weight by the counterparty's participation percentage. Aggregates across all facilities where the counterparty has a current participation record.
 </v>
       </c>
       <c r="O14" t="str">
@@ -1591,7 +1591,7 @@
         <v>Agg</v>
       </c>
       <c r="R14" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level cost of funds (bank-share-adjusted) per L3 desk segment.
+        <v xml:space="preserve">Sum of facility-level cost of funds (USD, bank-share-adjusted) for all facilities assigned to each L3 desk segment in the organizational hierarchy.
 </v>
       </c>
       <c r="S14" t="str">
@@ -1604,7 +1604,7 @@
         <v>Agg</v>
       </c>
       <c r="V14" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level cost of funds (bank-share-adjusted) per L2 portfolio segment.
+        <v xml:space="preserve">Sum of facility-level cost of funds (USD, bank-share-adjusted) for all facilities within each L2 portfolio segment, traversing the EBT hierarchy from desk (L3) to portfolio (L2) via parent_segment_id.
 </v>
       </c>
       <c r="W14" t="str">
@@ -1617,7 +1617,7 @@
         <v>Agg</v>
       </c>
       <c r="Z14" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level cost of funds (bank-share-adjusted) per L1 business segment.
+        <v xml:space="preserve">Sum of facility-level cost of funds (USD, bank-share-adjusted) for all facilities within each L1 business segment, traversing the full EBT hierarchy from desk (L3) through portfolio (L2) to segment (L1).
 </v>
       </c>
       <c r="AA14" t="str">
@@ -1632,14 +1632,14 @@
         <v>EXP-006</v>
       </c>
       <c r="B15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure allocated to specific counterparty representing their share of the facility which the client can draw on. Concentration KPI measuring obligor dependency risk.
+        <v xml:space="preserve">Counterparty participation share in a facility — the percentage of a syndicated or participated facility allocated to a specific counterparty. At facility level, direct lookup from facility_counterparty_participation. At counterparty level, exposure-weighted average participation across all facilities. At desk/portfolio/segment, exposure-weighted average via EBT hierarchy. Key concentration KPI for Large Exposures Framework (LEX) and Single Counterparty Credit Limit (SCCL) compliance.
 </v>
       </c>
       <c r="C15" t="str">
         <v>Counterparty Share or Allocation (%)</v>
       </c>
       <c r="D15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of allocation_pct from facility_counterparty_participation.
+        <v xml:space="preserve">Direct lookup of participation_pct from facility_counterparty_participation for the primary counterparty on each facility. Uses current records only.
 </v>
       </c>
       <c r="E15" t="str">
@@ -1658,7 +1658,7 @@
         <v>Raw</v>
       </c>
       <c r="J15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of allocation_pct from facility_counterparty_participation.
+        <v xml:space="preserve">Direct lookup of participation_pct from facility_counterparty_participation for the primary counterparty on each facility. Uses current records only.
 </v>
       </c>
       <c r="K15" t="str">
@@ -1668,10 +1668,10 @@
         <v>Y</v>
       </c>
       <c r="M15" t="str">
-        <v>Raw</v>
+        <v>Avg</v>
       </c>
       <c r="N15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read allocation_pct per counterparty.
+        <v xml:space="preserve">Exposure-weighted average participation across all facilities for each counterparty. Weight = drawn_amount from facility_exposure_snapshot. Falls back to simple average if no exposure data available.
 </v>
       </c>
       <c r="O15" t="str">
@@ -1681,10 +1681,10 @@
         <v>Y</v>
       </c>
       <c r="Q15" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="R15" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level allocation_pct per L3 desk segment.
+        <v xml:space="preserve">Exposure-weighted average participation across all facilities per L3 desk segment via enterprise_business_taxonomy.
 </v>
       </c>
       <c r="S15" t="str">
@@ -1694,10 +1694,10 @@
         <v>Y</v>
       </c>
       <c r="U15" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="V15" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level allocation_pct per L2 portfolio segment.
+        <v xml:space="preserve">Exposure-weighted average participation across all facilities per L2 portfolio segment via enterprise_business_taxonomy hierarchy traversal.
 </v>
       </c>
       <c r="W15" t="str">
@@ -1707,10 +1707,10 @@
         <v>Y</v>
       </c>
       <c r="Y15" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="Z15" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level allocation_pct per L1 business segment segment.
+        <v xml:space="preserve">Exposure-weighted average participation across all facilities per L1 business segment via enterprise_business_taxonomy hierarchy traversal.
 </v>
       </c>
       <c r="AA15" t="str">
@@ -1725,14 +1725,14 @@
         <v>EXP-007</v>
       </c>
       <c r="B16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Flag identifying exposures requiring heightened monitoring due to elevated credit risk. Governance control used for enhanced monitoring, reserve consideration, and management reporting.
+        <v xml:space="preserve">Count of active Criticized risk flags across facilities. Early warning indicator of problem assets requiring heightened monitoring, reserve consideration, and management reporting. Sources from the risk_flag table filtering on flag_code = 'CRITICIZED' with uncleared status.
 </v>
       </c>
       <c r="C16" t="str">
         <v>Criticized Portfolios</v>
       </c>
       <c r="D16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if criticized rating (internal_risk_rating &gt;= 6), 0 otherwise.
+        <v xml:space="preserve">For each facility, count active risk flags where flag_code = 'CRITICIZED' and the flag has not been cleared (cleared_ts IS NULL).
 </v>
       </c>
       <c r="E16" t="str">
@@ -1748,10 +1748,10 @@
         <v>Y</v>
       </c>
       <c r="I16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="J16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if criticized rating (internal_risk_rating &gt;= 6), 0 otherwise.
+        <v xml:space="preserve">For each facility, count active risk flags where flag_code = 'CRITICIZED' and the flag has not been cleared (cleared_ts IS NULL).
 </v>
       </c>
       <c r="K16" t="str">
@@ -1761,10 +1761,10 @@
         <v>Y</v>
       </c>
       <c r="M16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="N16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per counterparty.
+        <v xml:space="preserve">For each counterparty, sum facility-level criticized flag counts across all facilities belonging to that counterparty.
 </v>
       </c>
       <c r="O16" t="str">
@@ -1774,10 +1774,10 @@
         <v>Y</v>
       </c>
       <c r="Q16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="R16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per L3 desk.
+        <v xml:space="preserve">Sum of criticized flag counts per L3 desk segment. Joins facility_master to enterprise_business_taxonomy via lob_segment_id.
 </v>
       </c>
       <c r="S16" t="str">
@@ -1787,10 +1787,10 @@
         <v>Y</v>
       </c>
       <c r="U16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="V16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per L2 portfolio.
+        <v xml:space="preserve">Sum of criticized flag counts per L2 portfolio segment. Traverses enterprise_business_taxonomy hierarchy from L3 to L2 via parent_segment_id.
 </v>
       </c>
       <c r="W16" t="str">
@@ -1800,10 +1800,10 @@
         <v>Y</v>
       </c>
       <c r="Y16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="Z16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per L1 business segment.
+        <v xml:space="preserve">Sum of criticized flag counts per L1 business segment. Full hierarchy traversal L3 → L2 → L1 via enterprise_business_taxonomy.
 </v>
       </c>
       <c r="AA16" t="str">
@@ -1818,14 +1818,14 @@
         <v>EXP-008</v>
       </c>
       <c r="B17" t="str" xml:space="preserve">
-        <v xml:space="preserve">Total exposure amount allocated across multiple legal entities. Supports intra-group concentration transparency.
+        <v xml:space="preserve">Total committed exposure amount (bank share) allocated across multiple legal entities for facilities flagged as cross-entity. Quantifies inter-entity concentration risk and supports intra-group transparency for GSIB reporting. Sources from counterparty_derived (L3) for the cross-entity flag and facility_exposure_snapshot (L2) for committed amounts.
 </v>
       </c>
       <c r="C17" t="str">
         <v>Cross Entity Exposure Amount</v>
       </c>
       <c r="D17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(total_cross_entity_exposure_usd) per facility from counterparty_exposure_summary. Weighted by bank share percentage.
+        <v xml:space="preserve">For each facility flagged as cross-entity, committed exposure amount weighted by the bank's participation share (bank_share_pct). Facilities without cross-entity flag are excluded.
 </v>
       </c>
       <c r="E17" t="str">
@@ -1844,7 +1844,7 @@
         <v>Agg</v>
       </c>
       <c r="J17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(total_cross_entity_exposure_usd) per facility from counterparty_exposure_summary. Weighted by bank share percentage.
+        <v xml:space="preserve">For each facility flagged as cross-entity, committed exposure amount weighted by the bank's participation share (bank_share_pct). Facilities without cross-entity flag are excluded.
 </v>
       </c>
       <c r="K17" t="str">
@@ -1857,7 +1857,7 @@
         <v>Agg</v>
       </c>
       <c r="N17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per counterparty.
+        <v xml:space="preserve">For each counterparty, sum of bank-share-weighted committed amounts across all facilities flagged as cross-entity.
 </v>
       </c>
       <c r="O17" t="str">
@@ -1870,7 +1870,7 @@
         <v>Agg</v>
       </c>
       <c r="R17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per L3 desk segment.
+        <v xml:space="preserve">Sum of cross-entity committed exposure per L3 desk segment via enterprise_business_taxonomy.
 </v>
       </c>
       <c r="S17" t="str">
@@ -1883,7 +1883,7 @@
         <v>Agg</v>
       </c>
       <c r="V17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per L2 portfolio segment.
+        <v xml:space="preserve">Sum of cross-entity committed exposure per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
 </v>
       </c>
       <c r="W17" t="str">
@@ -1896,7 +1896,7 @@
         <v>Agg</v>
       </c>
       <c r="Z17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per L1 business segment segment.
+        <v xml:space="preserve">Sum of cross-entity committed exposure per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
 </v>
       </c>
       <c r="AA17" t="str">
@@ -1911,14 +1911,14 @@
         <v>EXP-009</v>
       </c>
       <c r="B18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Number of days outstanding payments is past due as grouped into 3 "buckets", 0-30 Days, 31-60 Days, 61-90+ Days. Used for staging classification and early credit deterioration monitoring.
+        <v xml:space="preserve">Maximum days payment overdue per facility, calculated from raw payment records in the payment_ledger table. For each facility, identifies payments where applied amount &lt; amount due, computes days overdue as reporting date minus payment_due_date, takes the MAX, then classifies into buckets: 1 = 0-30 days, 2 = 31-60 days, 3 = 61-90+ days. At aggregate levels, reports the worst (MAX) bucket across constituents.
 </v>
       </c>
       <c r="C18" t="str">
         <v>Days Payment Overdue Bucket</v>
       </c>
       <c r="D18" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Facility_ID lookup the Payments records in the Payment Lockbox table, For each payment record where [Payment_Due_Date] &gt; Today() IF ([Pmt_Applied] &lt;[Pmt_Due])&gt;=1, THEN Today() - [Payment_due_date] ==[Days Overdue] SELECT MAX ([Days Overdue] then lookup in Payments Overdue bucket)
+        <v xml:space="preserve">For each facility, lookup payment records in payment_ledger where payment_due_date &lt; reporting date and payment_applied_amt &lt; payment_amount_due (underpaid). Calculate days overdue = reporting date minus payment_due_date. Take MAX days overdue, then classify into overdue bucket: 1 (0-30), 2 (31-60), 3 (61-90+).
 </v>
       </c>
       <c r="E18" t="str">
@@ -1937,7 +1937,7 @@
         <v>Calc</v>
       </c>
       <c r="J18" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Facility_ID lookup the Payments records in the Payment Lockbox table, For each payment record where [Payment_Due_Date] &gt; Today() IF ([Pmt_Applied] &lt;[Pmt_Due])&gt;=1, THEN Today() - [Payment_due_date] ==[Days Overdue] SELECT MAX ([Days Overdue] then lookup in Payments Overdue bucket)
+        <v xml:space="preserve">For each facility, lookup payment records in payment_ledger where payment_due_date &lt; reporting date and payment_applied_amt &lt; payment_amount_due (underpaid). Calculate days overdue = reporting date minus payment_due_date. Take MAX days overdue, then classify into overdue bucket: 1 (0-30), 2 (31-60), 3 (61-90+).
 </v>
       </c>
       <c r="K18" t="str">
@@ -1950,7 +1950,7 @@
         <v>Agg</v>
       </c>
       <c r="N18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per counterparty.
+        <v xml:space="preserve">Worst-case (MAX) overdue bucket across all facilities per counterparty. Identifies the most severely overdue facility for each borrower.
 </v>
       </c>
       <c r="O18" t="str">
@@ -1963,7 +1963,7 @@
         <v>Agg</v>
       </c>
       <c r="R18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per L3 desk segment.
+        <v xml:space="preserve">Worst-case (MAX) overdue bucket per L3 desk segment. Shows the most severe delinquency in each organizational unit.
 </v>
       </c>
       <c r="S18" t="str">
@@ -1976,7 +1976,7 @@
         <v>Agg</v>
       </c>
       <c r="V18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per L2 portfolio segment.
+        <v xml:space="preserve">Worst-case (MAX) overdue bucket per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
 </v>
       </c>
       <c r="W18" t="str">
@@ -1989,7 +1989,7 @@
         <v>Agg</v>
       </c>
       <c r="Z18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per L1 business segment.
+        <v xml:space="preserve">Worst-case (MAX) overdue bucket per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
 </v>
       </c>
       <c r="AA18" t="str">
@@ -2509,14 +2509,25 @@
         <v>EXP-015</v>
       </c>
       <c r="B24" t="str" xml:space="preserve">
-        <v xml:space="preserve">Expected Loss divided by Exposure. Derived KPI measuring loss intensity relative to exposure size, enabling comparative risk ranking across facilities or counterparties.
+        <v xml:space="preserve">Expected Loss as a percentage of committed exposure. Computed from L2 atomic risk parameters: PD (probability of default) × LGD (loss given default). At aggregate levels, uses sum-ratio rollup: SUM(PD × LGD × Committed) / SUM(Committed) × 100 — the exposure-weighted average EL rate. This ensures mathematically consistent aggregation (never averages pre-computed rates). Key credit risk quantification metric for comparing loss intensity across facilities, counterparties, and business segments.
+Ingredient derivation:
+  - PD (pd_pct): L2 facility_risk_snapshot — probability of default (%)
+  - LGD (lgd_pct): L2 facility_risk_snapshot — loss given default (%)
+  - Committed Exposure (committed_amount): L2 facility_exposure_snapshot — raw
+  - EL Rate = PD × LGD (at facility level, committed cancels in ratio)
+  - Aggregate EL Rate = SUM(PD × LGD × Committed) / SUM(Committed) × 100
 </v>
       </c>
       <c r="C24" t="str">
         <v>Expected Loss Rate (%)</v>
       </c>
       <c r="D24" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of expected_loss_rate_pct per facility.
+        <v xml:space="preserve">For each facility:
+  1. LOAD pd_pct, lgd_pct from l2.facility_risk_snapshot
+  2. LOAD committed_amount from l2.facility_exposure_snapshot
+  3. COMPUTE EL Rate = SUM(PD/100 × LGD/100 × Committed) / SUM(Committed) × 100
+     At facility grain, committed cancels → EL Rate ≈ PD × LGD / 100
+Ingredients: pd_pct (L2), lgd_pct (L2), committed_amount (L2)
 </v>
       </c>
       <c r="E24" t="str">
@@ -2532,10 +2543,15 @@
         <v>Y</v>
       </c>
       <c r="I24" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="J24" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of expected_loss_rate_pct per facility.
+        <v xml:space="preserve">For each facility:
+  1. LOAD pd_pct, lgd_pct from l2.facility_risk_snapshot
+  2. LOAD committed_amount from l2.facility_exposure_snapshot
+  3. COMPUTE EL Rate = SUM(PD/100 × LGD/100 × Committed) / SUM(Committed) × 100
+     At facility grain, committed cancels → EL Rate ≈ PD × LGD / 100
+Ingredients: pd_pct (L2), lgd_pct (L2), committed_amount (L2)
 </v>
       </c>
       <c r="K24" t="str">
@@ -2545,10 +2561,15 @@
         <v>Y</v>
       </c>
       <c r="M24" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N24" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level expected_loss_rate_pct per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD pd_pct, lgd_pct for all facilities belonging to this counterparty
+  2. LOAD committed_amount for each facility
+  3. CONVERT to USD via l2.fx_rate spot rate
+  4. COMPUTE SUM(PD × LGD × Committed × FX) / SUM(Committed × FX) × 100
+Sum-ratio rollup with FX: exposure-weighted average EL rate in USD terms.
 </v>
       </c>
       <c r="O24" t="str">
@@ -2558,10 +2579,14 @@
         <v>Y</v>
       </c>
       <c r="Q24" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="R24" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level expected_loss_rate_pct per L3 desk segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOOKUP managed_segment_id from enterprise_business_taxonomy
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(PD × LGD × Committed × FX) / SUM(Committed × FX) × 100
+Sum-ratio rollup: exposure-weighted average EL rate per desk.
 </v>
       </c>
       <c r="S24" t="str">
@@ -2571,10 +2596,14 @@
         <v>Y</v>
       </c>
       <c r="U24" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V24" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level expected_loss_rate_pct per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(PD × LGD × Committed × FX) / SUM(Committed × FX) × 100
+Sum-ratio rollup: exposure-weighted average EL rate per portfolio.
 </v>
       </c>
       <c r="W24" t="str">
@@ -2584,10 +2613,14 @@
         <v>Y</v>
       </c>
       <c r="Y24" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z24" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level expected_loss_rate_pct per L1 business segment segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(PD × LGD × Committed × FX) / SUM(Committed × FX) × 100
+Sum-ratio rollup: exposure-weighted average EL rate per segment.
 </v>
       </c>
       <c r="AA24" t="str">
@@ -2602,14 +2635,25 @@
         <v>EXP-016</v>
       </c>
       <c r="B25" t="str" xml:space="preserve">
-        <v xml:space="preserve">PD × LGD × Exposure expressed in USD. Calculated forward-looking loss metric supporting provisioning, capital planning, and stress testing analytics.
+        <v xml:space="preserve">Expected Loss in dollar terms: PD × LGD × Committed Exposure × Bank Share. Computed from L2 atomic risk parameters and exposure data — NOT from stressed scenarios. This is the base (unstressed) expected credit loss, the foundation for provisioning, capital planning, and CECL/IFRS 9 reserve estimation.
+Ingredient derivation:
+  - PD (pd_pct): L2 facility_risk_snapshot — probability of default (%)
+  - LGD (lgd_pct): L2 facility_risk_snapshot — loss given default (%)
+  - Committed Exposure (committed_amount): L2 facility_exposure_snapshot — raw
+  - Bank Share (bank_share_pct): L2 facility_exposure_snapshot — participation %
+  - EL = (PD/100) × (LGD/100) × Committed × (Bank Share/100)
+Rollup uses direct-sum: SUM(facility EL) at each aggregate level. FX conversion applied at aggregate levels for multi-currency portfolios.
 </v>
       </c>
       <c r="C25" t="str">
         <v>Expected Loss ($)</v>
       </c>
       <c r="D25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(stressed_expected_loss) per facility from stress_test_result. Weighted by bank share percentage.
+        <v xml:space="preserve">For each facility:
+  1. LOAD pd_pct, lgd_pct from l2.facility_risk_snapshot
+  2. LOAD committed_amount, bank_share_pct from l2.facility_exposure_snapshot
+  3. COMPUTE EL = (PD/100) × (LGD/100) × Committed × (Bank Share/100)
+Ingredients: pd_pct (L2), lgd_pct (L2), committed_amount (L2), bank_share_pct (L2)
 </v>
       </c>
       <c r="E25" t="str">
@@ -2625,10 +2669,14 @@
         <v>Y</v>
       </c>
       <c r="I25" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="J25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(stressed_expected_loss) per facility from stress_test_result. Weighted by bank share percentage.
+        <v xml:space="preserve">For each facility:
+  1. LOAD pd_pct, lgd_pct from l2.facility_risk_snapshot
+  2. LOAD committed_amount, bank_share_pct from l2.facility_exposure_snapshot
+  3. COMPUTE EL = (PD/100) × (LGD/100) × Committed × (Bank Share/100)
+Ingredients: pd_pct (L2), lgd_pct (L2), committed_amount (L2), bank_share_pct (L2)
 </v>
       </c>
       <c r="K25" t="str">
@@ -2641,7 +2689,11 @@
         <v>Agg</v>
       </c>
       <c r="N25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD facility-level EL for all facilities of this counterparty
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(facility EL × FX rate) = Counterparty EL (USD)
+Direct-sum rollup with FX conversion.
 </v>
       </c>
       <c r="O25" t="str">
@@ -2654,7 +2706,11 @@
         <v>Agg</v>
       </c>
       <c r="R25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per L3 desk segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOOKUP managed_segment_id from enterprise_business_taxonomy
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(facility EL × FX rate) per desk
+Direct-sum rollup with FX conversion.
 </v>
       </c>
       <c r="S25" t="str">
@@ -2667,7 +2723,11 @@
         <v>Agg</v>
       </c>
       <c r="V25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(facility EL × FX rate) per portfolio
+Direct-sum rollup with FX conversion.
 </v>
       </c>
       <c r="W25" t="str">
@@ -2680,7 +2740,11 @@
         <v>Agg</v>
       </c>
       <c r="Z25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per L1 business segment segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(facility EL × FX rate) per business segment
+Direct-sum rollup with FX conversion.
 </v>
       </c>
       <c r="AA25" t="str">
@@ -3927,14 +3991,15 @@
         <v>EXP-030</v>
       </c>
       <c r="B39" t="str" xml:space="preserve">
-        <v xml:space="preserve">Model-estimated probability of default within defined horizon. Core credit risk input supporting capital modeling, expected loss estimation, stress testing, and risk appetite alignment.
+        <v xml:space="preserve">Model-estimated probability of default (PD) within the defined rating horizon. At facility level, sources the raw pd_pct from L2 facility_risk_snapshot. At aggregate levels, computes the exposure- weighted average: SUM(pd_pct × committed_amount) / SUM(committed_amount). This weighted-avg rollup avoids Simpson's paradox — never averages pre-computed PD rates. Core credit risk input supporting IRB capital modeling, expected loss estimation (EL = PD × LGD × EAD), stress testing, and risk appetite alignment.
 </v>
       </c>
       <c r="C39" t="str">
         <v>Probability of Default (%)</v>
       </c>
       <c r="D39" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read pd_pct from facility_risk_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Direct lookup of pd_pct from facility_risk_snapshot for each facility.
+Ingredients: pd_pct (L2 facility_risk_snapshot — raw model output)
 </v>
       </c>
       <c r="E39" t="str">
@@ -3953,7 +4018,8 @@
         <v>Raw</v>
       </c>
       <c r="J39" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read pd_pct from facility_risk_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Direct lookup of pd_pct from facility_risk_snapshot for each facility.
+Ingredients: pd_pct (L2 facility_risk_snapshot — raw model output)
 </v>
       </c>
       <c r="K39" t="str">
@@ -3963,10 +4029,15 @@
         <v>Y</v>
       </c>
       <c r="M39" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="N39" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pd_pct per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD pd_pct and committed_amount per facility
+  2. COMPUTE exposure-weighted average PD:
+     SUM(pd_pct × committed_amount) / SUM(committed_amount)
+Weighted-avg rollup ensures large-exposure facilities dominate the
+counterparty-level PD, avoiding equal-weight averaging bias.
 </v>
       </c>
       <c r="O39" t="str">
@@ -3979,7 +4050,11 @@
         <v>Avg</v>
       </c>
       <c r="R39" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level pd_pct per L3 desk segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOAD pd_pct and committed_amount per facility
+  2. JOIN l1.enterprise_business_taxonomy on lob_segment_id
+  3. COMPUTE SUM(pd_pct × committed_amount) / SUM(committed_amount)
+Weighted-avg rollup per desk.
 </v>
       </c>
       <c r="S39" t="str">
@@ -3992,7 +4067,11 @@
         <v>Avg</v>
       </c>
       <c r="V39" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level pd_pct per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. COMPUTE SUM(pd_pct × committed_amount) / SUM(committed_amount)
+Weighted-avg rollup per portfolio. Per spec:
+Σ(probability_of_default × Outstanding_Exposure) / Σ(Total Committed Amount)
 </v>
       </c>
       <c r="W39" t="str">
@@ -4002,10 +4081,13 @@
         <v>Y</v>
       </c>
       <c r="Y39" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="Z39" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pd_pct per L1 business segment segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. COMPUTE SUM(pd_pct × committed_amount) / SUM(committed_amount)
+Weighted-avg rollup per business segment.
 </v>
       </c>
       <c r="AA39" t="str">
@@ -5796,14 +5878,15 @@
         <v>PRC-003</v>
       </c>
       <c r="B59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of exposures within portfolio with approved pricing or policy exceptions. Derived governance KPI measuring policy discipline and risk culture strength.
+        <v xml:space="preserve">Percentage of facilities with approved pricing or policy exceptions. Computed as COUNT(exception facilities) / COUNT(total facilities) × 100. Sourced from L2 facility_pricing_snapshot — the atomic pricing record — using the is_pricing_exception_flag. At aggregate levels, uses count-ratio rollup: re-counts exceptions and totals across all constituent facilities, never averages pre-computed rates. Key governance KPI measuring policy discipline, risk culture strength, and pricing override frequency.
 </v>
       </c>
       <c r="C59" t="str">
         <v>Exception Rate (%)</v>
       </c>
       <c r="D59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if pricing exception, 0 otherwise.
+        <v xml:space="preserve">Binary flag: 1.0 if pricing exception approved, 0.0 otherwise.
+Ingredients: is_pricing_exception_flag (L2 facility_pricing_snapshot)
 </v>
       </c>
       <c r="E59" t="str">
@@ -5822,7 +5905,8 @@
         <v>Calc</v>
       </c>
       <c r="J59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if pricing exception, 0 otherwise.
+        <v xml:space="preserve">Binary flag: 1.0 if pricing exception approved, 0.0 otherwise.
+Ingredients: is_pricing_exception_flag (L2 facility_pricing_snapshot)
 </v>
       </c>
       <c r="K59" t="str">
@@ -5835,7 +5919,10 @@
         <v>Calc</v>
       </c>
       <c r="N59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with pricing exception per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD is_pricing_exception_flag for all facilities of this counterparty
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup: re-counts from facility-level flags.
 </v>
       </c>
       <c r="O59" t="str">
@@ -5848,7 +5935,10 @@
         <v>Calc</v>
       </c>
       <c r="R59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with pricing exception per L3 desk.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOOKUP managed_segment_id from enterprise_business_taxonomy
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup per desk.
 </v>
       </c>
       <c r="S59" t="str">
@@ -5861,7 +5951,10 @@
         <v>Calc</v>
       </c>
       <c r="V59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with pricing exception per L2 portfolio.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup per portfolio.
 </v>
       </c>
       <c r="W59" t="str">
@@ -5874,7 +5967,10 @@
         <v>Calc</v>
       </c>
       <c r="Z59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with pricing exception per L1 business segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup per business segment.
 </v>
       </c>
       <c r="AA59" t="str">
@@ -6075,14 +6171,18 @@
         <v>PRC-006</v>
       </c>
       <c r="B62" t="str" xml:space="preserve">
-        <v xml:space="preserve">Pricing classification tier assigned to facility. Supports structured pricing strategy and yield segmentation.
+        <v xml:space="preserve">Pricing classification tier derived by range-joining the facility's spread (spread_bps from L2 facility_pricing_snapshot) against the pricing_tier_dim reference table (spread_min_bps/spread_max_bps). Returns the tier_ordinal at facility level and at aggregate levels classifies the exposure-weighted average spread into the corresponding tier. Supports pricing strategy segmentation, yield curve analysis, and risk-adjusted return monitoring.
 </v>
       </c>
       <c r="C62" t="str">
         <v>Pricing Tier</v>
       </c>
       <c r="D62" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read pricing_tier_code from facility_detail_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">For each facility:
+  1. LOAD spread_bps from l2.facility_pricing_snapshot
+  2. RANGE-JOIN against l1.pricing_tier_dim
+     WHERE spread_bps &gt;= spread_min_bps AND spread_bps &lt; spread_max_bps
+  3. RETURN tier_ordinal — the numeric tier classification
 </v>
       </c>
       <c r="E62" t="str">
@@ -6098,10 +6198,14 @@
         <v>Y</v>
       </c>
       <c r="I62" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="J62" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read pricing_tier_code from facility_detail_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">For each facility:
+  1. LOAD spread_bps from l2.facility_pricing_snapshot
+  2. RANGE-JOIN against l1.pricing_tier_dim
+     WHERE spread_bps &gt;= spread_min_bps AND spread_bps &lt; spread_max_bps
+  3. RETURN tier_ordinal — the numeric tier classification
 </v>
       </c>
       <c r="K62" t="str">
@@ -6111,10 +6215,15 @@
         <v>Y</v>
       </c>
       <c r="M62" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="N62" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read pricing_tier_code per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD spread_bps and committed_amount per facility
+  2. COMPUTE weighted average spread:
+     SUM(spread_bps × committed_amount) / SUM(committed_amount)
+  3. RANGE-JOIN weighted avg spread against l1.pricing_tier_dim
+  4. RETURN tier_ordinal for the counterparty's blended spread
 </v>
       </c>
       <c r="O62" t="str">
@@ -6124,10 +6233,13 @@
         <v>Y</v>
       </c>
       <c r="Q62" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R62" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pricing_tier_code per L3 desk segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. Compute exposure-weighted average spread across desk facilities
+  2. Classify against pricing_tier_dim ranges
+  3. RETURN tier_ordinal for the desk's blended spread
 </v>
       </c>
       <c r="S62" t="str">
@@ -6137,10 +6249,13 @@
         <v>Y</v>
       </c>
       <c r="U62" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V62" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pricing_tier_code per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. Compute exposure-weighted average spread
+  3. Classify against pricing_tier_dim ranges
 </v>
       </c>
       <c r="W62" t="str">
@@ -6150,10 +6265,13 @@
         <v>Y</v>
       </c>
       <c r="Y62" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z62" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pricing_tier_code per L1 business segment segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. Compute exposure-weighted average spread
+  3. Classify against pricing_tier_dim ranges
 </v>
       </c>
       <c r="AA62" t="str">
@@ -6354,14 +6472,16 @@
         <v>PRC-009</v>
       </c>
       <c r="B65" t="str" xml:space="preserve">
-        <v xml:space="preserve">Boolean indicator identifying whether the exposure was approved outside standard pricing policy thresholds at origination or amendment.
+        <v xml:space="preserve">Pricing exception effectiveness metric. At facility level, returns an ordinal encoding of the pricing_exception_status (APPROVED=3, PENDING=2, DENIED=1, NONE=0). At aggregate levels, computes the exception rate as COUNT(exception facilities) / COUNT(total facilities) × 100, following the count-ratio rollup pattern. Re-counts at each level to avoid Simpson's paradox. Complements PRC-003 (Exception Rate) with status-level detail for governance drill-down.
 </v>
       </c>
       <c r="C65" t="str">
-        <v>Pricing Exception Flag (Y/N)</v>
+        <v>Pricing Exception Status</v>
       </c>
       <c r="D65" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated pricing_exception_flag per facility.
+        <v xml:space="preserve">Ordinal encoding of pricing_exception_status per facility:
+  APPROVED = 3, PENDING = 2, DENIED = 1, NONE/NULL = 0.
+Ingredients: pricing_exception_status (L2 facility_pricing_snapshot)
 </v>
       </c>
       <c r="E65" t="str">
@@ -6380,63 +6500,79 @@
         <v>Calc</v>
       </c>
       <c r="J65" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated pricing_exception_flag per facility.
+        <v xml:space="preserve">Ordinal encoding of pricing_exception_status per facility:
+  APPROVED = 3, PENDING = 2, DENIED = 1, NONE/NULL = 0.
+Ingredients: pricing_exception_status (L2 facility_pricing_snapshot)
 </v>
       </c>
       <c r="K65" t="str">
-        <v>Pricing Exception Flag (Y/N) (facility)</v>
+        <v>Pricing Exception Status (facility)</v>
       </c>
       <c r="L65" t="str">
         <v>Y</v>
       </c>
       <c r="M65" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N65" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pricing_exception_flag per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD is_pricing_exception_flag for all facilities
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup: re-counts from facility-level flags.
 </v>
       </c>
       <c r="O65" t="str">
-        <v>Pricing Exception Flag (Y/N) (counterparty)</v>
+        <v>Pricing Exception Status (counterparty)</v>
       </c>
       <c r="P65" t="str">
         <v>Y</v>
       </c>
       <c r="Q65" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R65" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pricing_exception_flag per L3 desk segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. JOIN l1.enterprise_business_taxonomy on lob_segment_id
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup per desk.
 </v>
       </c>
       <c r="S65" t="str">
-        <v>Pricing Exception Flag (Y/N) (desk)</v>
+        <v>Pricing Exception Status (desk)</v>
       </c>
       <c r="T65" t="str">
         <v>Y</v>
       </c>
       <c r="U65" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V65" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pricing_exception_flag per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup per portfolio. Drill-down returns exception
+facility details: Facility_ID, Facility_Name, Counterparty_ID,
+Counterparty_Name, Exception_Status, All_in_Rate.
 </v>
       </c>
       <c r="W65" t="str">
-        <v>Pricing Exception Flag (Y/N) (portfolio)</v>
+        <v>Pricing Exception Status (portfolio)</v>
       </c>
       <c r="X65" t="str">
         <v>Y</v>
       </c>
       <c r="Y65" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z65" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pricing_exception_flag per L1 business segment segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup per business segment.
 </v>
       </c>
       <c r="AA65" t="str">
-        <v>Pricing Exception Flag (Y/N) (business_segment)</v>
+        <v>Pricing Exception Status (business_segment)</v>
       </c>
       <c r="AB65" t="str">
         <v/>
@@ -6830,14 +6966,14 @@
         <v>REF-004</v>
       </c>
       <c r="B70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Unique system identifier assigned to the borrower or obligor. Used for exposure aggregation and risk consolidation.
+        <v xml:space="preserve">Unique system identifier assigned to the borrower or obligor. Used for exposure aggregation and risk consolidation across the GSIB. At facility level, returns the counterparty_id linked to each facility. At upper levels, returns COUNT(DISTINCT counterparty_id) — the number of unique obligors in each organizational segment.
 </v>
       </c>
       <c r="C70" t="str">
         <v>Counterparty ID</v>
       </c>
       <c r="D70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">Direct lookup of counterparty_id from facility_master for each active facility. Uses current records only (SCD2 filtered).
 </v>
       </c>
       <c r="E70" t="str">
@@ -6856,7 +6992,7 @@
         <v>Raw</v>
       </c>
       <c r="J70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">Direct lookup of counterparty_id from facility_master for each active facility. Uses current records only (SCD2 filtered).
 </v>
       </c>
       <c r="K70" t="str">
@@ -6869,7 +7005,7 @@
         <v>Raw</v>
       </c>
       <c r="N70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">Identity — returns counterparty_id for each current counterparty.
 </v>
       </c>
       <c r="O70" t="str">
@@ -6882,7 +7018,7 @@
         <v>Agg</v>
       </c>
       <c r="R70" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L3 desk segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L3 desk segment — number of unique obligors in each desk.
 </v>
       </c>
       <c r="S70" t="str">
@@ -6895,7 +7031,7 @@
         <v>Agg</v>
       </c>
       <c r="V70" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L2 portfolio segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L2 portfolio segment — number of unique obligors in each portfolio.
 </v>
       </c>
       <c r="W70" t="str">
@@ -6908,7 +7044,7 @@
         <v>Agg</v>
       </c>
       <c r="Z70" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L1 business segment segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L1 business segment — number of unique obligors in each business segment.
 </v>
       </c>
       <c r="AA70" t="str">
@@ -6923,14 +7059,14 @@
         <v>REF-005</v>
       </c>
       <c r="B71" t="str" xml:space="preserve">
-        <v xml:space="preserve">Descriptive name of the counterparty as documented in the credit agreement. Used for reporting clarity and operational reference.
+        <v xml:space="preserve">Legal name of the counterparty as documented in the credit agreement. At facility level, returns the counterparty_id (numeric proxy for the name since metric values are numeric). At counterparty level, identity lookup. At upper levels, COUNT(DISTINCT counterparty_id) — number of unique named obligors per organizational segment. Used for reporting clarity and operational reference across all regulatory submissions.
 </v>
       </c>
       <c r="C71" t="str">
         <v>Counterparty Name</v>
       </c>
       <c r="D71" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read legal_name from counterparty for each facility's counterparty.
+        <v xml:space="preserve">Lookup counterparty_id from facility_master for each active facility. The numeric counterparty_id serves as proxy for the legal name (string values resolved via counterparty dimension join at display time). Uses current records only.
 </v>
       </c>
       <c r="E71" t="str">
@@ -6949,7 +7085,7 @@
         <v>Raw</v>
       </c>
       <c r="J71" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read legal_name from counterparty for each facility's counterparty.
+        <v xml:space="preserve">Lookup counterparty_id from facility_master for each active facility. The numeric counterparty_id serves as proxy for the legal name (string values resolved via counterparty dimension join at display time). Uses current records only.
 </v>
       </c>
       <c r="K71" t="str">
@@ -6959,10 +7095,10 @@
         <v>Y</v>
       </c>
       <c r="M71" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="N71" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with counterparty name per counterparty.
+        <v xml:space="preserve">Identity — returns counterparty_id for each current counterparty. Legal name resolved via counterparty dimension join at display time.
 </v>
       </c>
       <c r="O71" t="str">
@@ -6975,7 +7111,7 @@
         <v>Agg</v>
       </c>
       <c r="R71" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with counterparty name per L3 desk segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L3 desk segment — number of unique named obligors in each desk.
 </v>
       </c>
       <c r="S71" t="str">
@@ -6988,7 +7124,7 @@
         <v>Agg</v>
       </c>
       <c r="V71" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with counterparty name per L2 portfolio segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L2 portfolio segment — number of unique named obligors in each portfolio.
 </v>
       </c>
       <c r="W71" t="str">
@@ -7001,7 +7137,7 @@
         <v>Agg</v>
       </c>
       <c r="Z71" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with counterparty name per L1 business segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L1 business segment — number of unique named obligors in each business segment.
 </v>
       </c>
       <c r="AA71" t="str">
@@ -7016,14 +7152,14 @@
         <v>REF-006</v>
       </c>
       <c r="B72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Country of risk or booking location. Supports geographic concentration and sovereign risk analysis.
+        <v xml:space="preserve">Country of risk derived from the counterparty's domicile. At facility level, returns a numeric country identifier (via counterparty → country_dim join path). At counterparty level, identity lookup. At desk/portfolio/segment levels, COUNT(DISTINCT country_code) — geographic diversification indicator showing the number of unique countries represented. Supports FFIEC 009 Country Exposure Report and Basel III geographic concentration analysis.
 </v>
       </c>
       <c r="C72" t="str">
         <v>Country</v>
       </c>
       <c r="D72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of country_name from country_dim.
+        <v xml:space="preserve">Lookup country for each facility via counterparty → country_dim join path. Returns counterparty_id as numeric proxy (country_name resolved at display time via dimension join). Uses current records only.
 </v>
       </c>
       <c r="E72" t="str">
@@ -7042,7 +7178,7 @@
         <v>Raw</v>
       </c>
       <c r="J72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of country_name from country_dim.
+        <v xml:space="preserve">Lookup country for each facility via counterparty → country_dim join path. Returns counterparty_id as numeric proxy (country_name resolved at display time via dimension join). Uses current records only.
 </v>
       </c>
       <c r="K72" t="str">
@@ -7055,7 +7191,7 @@
         <v>Raw</v>
       </c>
       <c r="N72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read country_name per counterparty.
+        <v xml:space="preserve">Lookup country for each counterparty via country_code → country_dim join. Returns counterparty_id as numeric proxy.
 </v>
       </c>
       <c r="O72" t="str">
@@ -7068,7 +7204,7 @@
         <v>Agg</v>
       </c>
       <c r="R72" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level country_name per L3 desk segment.
+        <v xml:space="preserve">COUNT(DISTINCT country_code) per L3 desk segment — number of unique countries represented, a geographic diversification indicator.
 </v>
       </c>
       <c r="S72" t="str">
@@ -7081,7 +7217,7 @@
         <v>Agg</v>
       </c>
       <c r="V72" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level country_name per L2 portfolio segment.
+        <v xml:space="preserve">COUNT(DISTINCT country_code) per L2 portfolio segment — number of unique countries represented in each portfolio.
 </v>
       </c>
       <c r="W72" t="str">
@@ -7094,7 +7230,7 @@
         <v>Agg</v>
       </c>
       <c r="Z72" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level country_name per L1 business segment segment.
+        <v xml:space="preserve">COUNT(DISTINCT country_code) per L1 business segment — geographic diversification at the highest organizational level.
 </v>
       </c>
       <c r="AA72" t="str">
@@ -7109,14 +7245,14 @@
         <v>REF-007</v>
       </c>
       <c r="B73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Unique identifier linking facility to governing credit agreement documentation.
+        <v xml:space="preserve">Unique identifier linking each facility to its governing credit agreement documentation. Used for contract tracking, facility-to-agreement linkage, and regulatory reporting. At counterparty level, returns count of distinct credit agreements per borrower.
 </v>
       </c>
       <c r="C73" t="str">
         <v>Credit Agreement ID</v>
       </c>
       <c r="D73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of credit_agreement_id from credit_agreement_master.
+        <v xml:space="preserve">Direct lookup of credit_agreement_id for each active facility via facility_master joined to credit_agreement_master.
 </v>
       </c>
       <c r="E73" t="str">
@@ -7135,7 +7271,7 @@
         <v>Raw</v>
       </c>
       <c r="J73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of credit_agreement_id from credit_agreement_master.
+        <v xml:space="preserve">Direct lookup of credit_agreement_id for each active facility via facility_master joined to credit_agreement_master.
 </v>
       </c>
       <c r="K73" t="str">
@@ -7145,10 +7281,10 @@
         <v>Y</v>
       </c>
       <c r="M73" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="N73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read credit_agreement_id per counterparty.
+        <v xml:space="preserve">Count of distinct credit agreements per counterparty. Provides visibility into borrower complexity and multi-agreement relationships.
 </v>
       </c>
       <c r="O73" t="str">
@@ -7161,7 +7297,7 @@
         <v>Agg</v>
       </c>
       <c r="R73" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level credit_agreement_id per L3 desk segment.
+        <v xml:space="preserve">Count of distinct credit agreements per L3 desk segment via enterprise_business_taxonomy.
 </v>
       </c>
       <c r="S73" t="str">
@@ -7174,7 +7310,7 @@
         <v>Agg</v>
       </c>
       <c r="V73" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level credit_agreement_id per L2 portfolio segment.
+        <v xml:space="preserve">Count of distinct credit agreements per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
 </v>
       </c>
       <c r="W73" t="str">
@@ -7187,7 +7323,7 @@
         <v>Agg</v>
       </c>
       <c r="Z73" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level credit_agreement_id per L1 business segment segment.
+        <v xml:space="preserve">Count of distinct credit agreements per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
 </v>
       </c>
       <c r="AA73" t="str">
@@ -7295,14 +7431,15 @@
         <v>REF-009</v>
       </c>
       <c r="B75" t="str" xml:space="preserve">
-        <v xml:space="preserve">Date on which loan or contract became legally effective.
+        <v xml:space="preserve">Facility effective date sourced from facility_master origination_date. At facility and counterparty levels, returns the raw date (or earliest vintage via MIN). At portfolio level, pivots to facility lifecycle tracking: counts inactive facilities whose origination date falls within 90 days of the reporting date, identifying the upcoming pipeline of facilities about to start ("Starting 90d"). Key for vintage analysis, portfolio seasoning, and facility pipeline monitoring.
 </v>
       </c>
       <c r="C75" t="str">
-        <v>Contract Origination Date</v>
+        <v>Facility Origination Date</v>
       </c>
       <c r="D75" t="str" xml:space="preserve">
         <v xml:space="preserve">Direct lookup of origination_date from facility_master.
+Ingredients: origination_date (L2 facility_master — raw field)
 </v>
       </c>
       <c r="E75" t="str">
@@ -7322,10 +7459,11 @@
       </c>
       <c r="J75" t="str" xml:space="preserve">
         <v xml:space="preserve">Direct lookup of origination_date from facility_master.
+Ingredients: origination_date (L2 facility_master — raw field)
 </v>
       </c>
       <c r="K75" t="str">
-        <v>Contract Origination Date (facility)</v>
+        <v>Facility Origination Date (facility)</v>
       </c>
       <c r="L75" t="str">
         <v>Y</v>
@@ -7334,11 +7472,14 @@
         <v>Agg</v>
       </c>
       <c r="N75" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level origination_date) per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD origination_date from l2.facility_master for all active facilities
+  2. COMPUTE MIN(origination_date) — earliest contract vintage
+Indicates the oldest banking relationship tenure for this counterparty.
 </v>
       </c>
       <c r="O75" t="str">
-        <v>Contract Origination Date (counterparty)</v>
+        <v>Facility Origination Date (counterparty)</v>
       </c>
       <c r="P75" t="str">
         <v>Y</v>
@@ -7347,24 +7488,33 @@
         <v>Agg</v>
       </c>
       <c r="R75" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level origination_date per L3 desk segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOAD origination_date from l2.facility_master
+  2. JOIN l1.enterprise_business_taxonomy on lob_segment_id
+  3. COMPUTE MIN(origination_date) — earliest vintage in desk book
 </v>
       </c>
       <c r="S75" t="str">
-        <v>Contract Origination Date (desk)</v>
+        <v>Facility Origination Date (desk)</v>
       </c>
       <c r="T75" t="str">
         <v>Y</v>
       </c>
       <c r="U75" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V75" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level origination_date per L2 portfolio segment.
+        <v xml:space="preserve">Facility pipeline tracking for each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. FILTER inactive facilities (is_active_flag != 'Y')
+     whose origination_date is within 90 days of current date
+  3. COMPUTE COUNT(DISTINCT facility_id) — number of upcoming facilities
+Returns the count of facilities in the "Starting (90d)" pipeline.
+Business rule: facilities not yet active with origination within ±90 days.
 </v>
       </c>
       <c r="W75" t="str">
-        <v>Contract Origination Date (portfolio)</v>
+        <v>Facility Origination Date (portfolio)</v>
       </c>
       <c r="X75" t="str">
         <v>Y</v>
@@ -7373,11 +7523,13 @@
         <v>Agg</v>
       </c>
       <c r="Z75" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level origination_date per L1 business segment segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. COMPUTE MIN(origination_date) — earliest vintage in business segment
 </v>
       </c>
       <c r="AA75" t="str">
-        <v>Contract Origination Date (business_segment)</v>
+        <v>Facility Origination Date (business_segment)</v>
       </c>
       <c r="AB75" t="str">
         <v/>
@@ -8690,14 +8842,15 @@
         <v>REF-024</v>
       </c>
       <c r="B90" t="str" xml:space="preserve">
-        <v xml:space="preserve">Identifiers of counterparties participating in the credit structures or facility as multiple-borrowers. Enables exposure attribution and concentration analysis.
+        <v xml:space="preserve">Count of distinct counterparties participating in credit structures. At counterparty level, returns the counterparty identifier directly. At desk and higher levels, counts distinct counterparties per segment to measure borrower concentration and multi-borrower facility exposure. Enables concentration analysis, relationship tracking, and syndicated deal monitoring.
 </v>
       </c>
       <c r="C90" t="str">
         <v>Participating Counterparty IDs</v>
       </c>
       <c r="D90" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">Direct lookup of counterparty_id from facility_master for each facility.
+Returns the counterparty associated with the facility.
 </v>
       </c>
       <c r="E90" t="str">
@@ -8716,7 +8869,8 @@
         <v>Raw</v>
       </c>
       <c r="J90" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">Direct lookup of counterparty_id from facility_master for each facility.
+Returns the counterparty associated with the facility.
 </v>
       </c>
       <c r="K90" t="str">
@@ -8729,7 +8883,8 @@
         <v>Raw</v>
       </c>
       <c r="N90" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">Identity: returns counterparty_id for each active counterparty.
+Enables direct counterparty identification in drill-down views.
 </v>
       </c>
       <c r="O90" t="str">
@@ -8739,10 +8894,14 @@
         <v>Y</v>
       </c>
       <c r="Q90" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R90" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L3 desk segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOAD all facilities from l2.facility_master
+  2. JOIN l1.enterprise_business_taxonomy on lob_segment_id
+  3. COMPUTE COUNT(DISTINCT counterparty_id) — unique borrowers per desk
+Measures borrower concentration within each desk.
 </v>
       </c>
       <c r="S90" t="str">
@@ -8752,10 +8911,12 @@
         <v>Y</v>
       </c>
       <c r="U90" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V90" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. COMPUTE COUNT(DISTINCT counterparty_id) — unique borrowers per portfolio
 </v>
       </c>
       <c r="W90" t="str">
@@ -8765,10 +8926,12 @@
         <v>Y</v>
       </c>
       <c r="Y90" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z90" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L1 business segment segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. COMPUTE COUNT(DISTINCT counterparty_id) — unique borrowers per segment
 </v>
       </c>
       <c r="AA90" t="str">
@@ -9620,14 +9783,14 @@
         <v>RSK-001</v>
       </c>
       <c r="B100" t="str" xml:space="preserve">
-        <v xml:space="preserve">Most recent internal credit rating assigned at reporting date. Used for segmentation and exposure-weighted risk aggregation.
+        <v xml:space="preserve">Risk rating tier derived from counterparty probability of default (PD). Each counterparty's pd_annual is matched against the risk_rating_tier_dim reference table (pd_min_pct / pd_max_pct boundaries) to assign a tier classification. At facility level, the tier is inherited from the owning counterparty. At aggregate levels, MAX (worst-case) tier ordinal is reported.
 </v>
       </c>
       <c r="C100" t="str">
         <v>Risk Rating Tier</v>
       </c>
       <c r="D100" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility.
+        <v xml:space="preserve">For each facility, inherit the risk rating tier from the owning counterparty. Join facility_master to counterparty, then range-match counterparty pd_annual against risk_rating_tier_dim to derive the tier ordinal (display_order).
 </v>
       </c>
       <c r="E100" t="str">
@@ -9643,10 +9806,10 @@
         <v>Y</v>
       </c>
       <c r="I100" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="J100" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility.
+        <v xml:space="preserve">For each facility, inherit the risk rating tier from the owning counterparty. Join facility_master to counterparty, then range-match counterparty pd_annual against risk_rating_tier_dim to derive the tier ordinal (display_order).
 </v>
       </c>
       <c r="K100" t="str">
@@ -9656,10 +9819,10 @@
         <v>Y</v>
       </c>
       <c r="M100" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N100" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating per counterparty.
+        <v xml:space="preserve">For each counterparty, look up pd_annual and range-match against risk_rating_tier_dim where pd_annual &gt;= pd_min_pct AND pd_annual &lt; pd_max_pct. Returns the tier ordinal (display_order). Counterparties with NULL PD receive tier 0 (unrated).
 </v>
       </c>
       <c r="O100" t="str">
@@ -9672,7 +9835,7 @@
         <v>Agg</v>
       </c>
       <c r="R100" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating per L3 desk segment.
+        <v xml:space="preserve">Worst-case (MAX) risk rating tier ordinal across all counterparties in the L3 desk segment. Higher ordinal = riskier tier. Full tier distribution available via counterparty-level drill-down.
 </v>
       </c>
       <c r="S100" t="str">
@@ -9685,7 +9848,7 @@
         <v>Agg</v>
       </c>
       <c r="V100" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating per L2 portfolio segment.
+        <v xml:space="preserve">Worst-case (MAX) risk rating tier ordinal per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
 </v>
       </c>
       <c r="W100" t="str">
@@ -9698,7 +9861,7 @@
         <v>Agg</v>
       </c>
       <c r="Z100" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating per L1 business segment.
+        <v xml:space="preserve">Worst-case (MAX) risk rating tier ordinal per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
 </v>
       </c>
       <c r="AA100" t="str">

--- a/data/metrics_dimensions_filled.xlsx
+++ b/data/metrics_dimensions_filled.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB108"/>
+  <dimension ref="A1:AB107"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1539,14 +1539,14 @@
         <v>EXP-005</v>
       </c>
       <c r="B14" t="str" xml:space="preserve">
-        <v xml:space="preserve">The portion of total funding-related expense attributed to a specific exposure or portfolio. At facility level, calculated as SUM across all positions of (funded_amount * interest_rate), adjusted for bank share. At counterparty level, further adjusted by counterparty participation_pct. At desk/portfolio/segment levels, aggregated as SUM.
+        <v xml:space="preserve">The portion of total funding-related expense attributed to a specific exposure or portfolio. At facility level, calculated as SUM across all positions of (funded_amount * interest_rate), converted to USD via FX rate and adjusted for bank share. At counterparty level, further adjusted by counterparty participation_pct. At desk/portfolio/segment levels, aggregated as SUM via EBT hierarchy.
 </v>
       </c>
       <c r="C14" t="str">
         <v>Cost of Funds ($)</v>
       </c>
       <c r="D14" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each position under the facility: funded_amount * interest_rate = Position Cost of Funds. Adjusted by bank_share: SUM(funded_amount * interest_rate) * bank_share_pct / 100. Joins position_detail → position (for facility_id) → facility_master.
+        <v xml:space="preserve">For each position under the facility, compute funded_amount x interest_rate, convert to USD using the FX spot rate (defaults to 1.0 for USD positions). Sum across all positions, then multiply by the bank's share percentage. Result = annual cost of funds for this facility in USD.
 </v>
       </c>
       <c r="E14" t="str">
@@ -1565,7 +1565,7 @@
         <v>Calc</v>
       </c>
       <c r="J14" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each position under the facility: funded_amount * interest_rate = Position Cost of Funds. Adjusted by bank_share: SUM(funded_amount * interest_rate) * bank_share_pct / 100. Joins position_detail → position (for facility_id) → facility_master.
+        <v xml:space="preserve">For each position under the facility, compute funded_amount x interest_rate, convert to USD using the FX spot rate (defaults to 1.0 for USD positions). Sum across all positions, then multiply by the bank's share percentage. Result = annual cost of funds for this facility in USD.
 </v>
       </c>
       <c r="K14" t="str">
@@ -1578,7 +1578,7 @@
         <v>Agg</v>
       </c>
       <c r="N14" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each counterparty: SUM of facility-level cost of funds weighted by counterparty participation_pct from facility_counterparty_participation.
+        <v xml:space="preserve">Sum each facility's cost of funds (USD, bank-share-adjusted), then weight by the counterparty's participation percentage. Aggregates across all facilities where the counterparty has a current participation record.
 </v>
       </c>
       <c r="O14" t="str">
@@ -1591,7 +1591,7 @@
         <v>Agg</v>
       </c>
       <c r="R14" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level cost of funds (bank-share-adjusted) per L3 desk segment.
+        <v xml:space="preserve">Sum of facility-level cost of funds (USD, bank-share-adjusted) for all facilities assigned to each L3 desk segment in the organizational hierarchy.
 </v>
       </c>
       <c r="S14" t="str">
@@ -1604,7 +1604,7 @@
         <v>Agg</v>
       </c>
       <c r="V14" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level cost of funds (bank-share-adjusted) per L2 portfolio segment.
+        <v xml:space="preserve">Sum of facility-level cost of funds (USD, bank-share-adjusted) for all facilities within each L2 portfolio segment, traversing the EBT hierarchy from desk (L3) to portfolio (L2) via parent_segment_id.
 </v>
       </c>
       <c r="W14" t="str">
@@ -1617,7 +1617,7 @@
         <v>Agg</v>
       </c>
       <c r="Z14" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level cost of funds (bank-share-adjusted) per L1 business segment.
+        <v xml:space="preserve">Sum of facility-level cost of funds (USD, bank-share-adjusted) for all facilities within each L1 business segment, traversing the full EBT hierarchy from desk (L3) through portfolio (L2) to segment (L1).
 </v>
       </c>
       <c r="AA14" t="str">
@@ -1632,14 +1632,14 @@
         <v>EXP-006</v>
       </c>
       <c r="B15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure allocated to specific counterparty representing their share of the facility which the client can draw on. Concentration KPI measuring obligor dependency risk.
+        <v xml:space="preserve">Counterparty participation share in a facility — the percentage of a syndicated or participated facility allocated to a specific counterparty. At facility level, direct lookup from facility_counterparty_participation. At counterparty level, exposure-weighted average participation across all facilities. At desk/portfolio/segment, exposure-weighted average via EBT hierarchy. Key concentration KPI for Large Exposures Framework (LEX) and Single Counterparty Credit Limit (SCCL) compliance.
 </v>
       </c>
       <c r="C15" t="str">
         <v>Counterparty Share or Allocation (%)</v>
       </c>
       <c r="D15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of allocation_pct from facility_counterparty_participation.
+        <v xml:space="preserve">Direct lookup of participation_pct from facility_counterparty_participation for the primary counterparty on each facility. Uses current records only.
 </v>
       </c>
       <c r="E15" t="str">
@@ -1658,7 +1658,7 @@
         <v>Raw</v>
       </c>
       <c r="J15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of allocation_pct from facility_counterparty_participation.
+        <v xml:space="preserve">Direct lookup of participation_pct from facility_counterparty_participation for the primary counterparty on each facility. Uses current records only.
 </v>
       </c>
       <c r="K15" t="str">
@@ -1668,10 +1668,10 @@
         <v>Y</v>
       </c>
       <c r="M15" t="str">
-        <v>Raw</v>
+        <v>Avg</v>
       </c>
       <c r="N15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read allocation_pct per counterparty.
+        <v xml:space="preserve">Exposure-weighted average participation across all facilities for each counterparty. Weight = drawn_amount from facility_exposure_snapshot. Falls back to simple average if no exposure data available.
 </v>
       </c>
       <c r="O15" t="str">
@@ -1681,10 +1681,10 @@
         <v>Y</v>
       </c>
       <c r="Q15" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="R15" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level allocation_pct per L3 desk segment.
+        <v xml:space="preserve">Exposure-weighted average participation across all facilities per L3 desk segment via enterprise_business_taxonomy.
 </v>
       </c>
       <c r="S15" t="str">
@@ -1694,10 +1694,10 @@
         <v>Y</v>
       </c>
       <c r="U15" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="V15" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level allocation_pct per L2 portfolio segment.
+        <v xml:space="preserve">Exposure-weighted average participation across all facilities per L2 portfolio segment via enterprise_business_taxonomy hierarchy traversal.
 </v>
       </c>
       <c r="W15" t="str">
@@ -1707,10 +1707,10 @@
         <v>Y</v>
       </c>
       <c r="Y15" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="Z15" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level allocation_pct per L1 business segment segment.
+        <v xml:space="preserve">Exposure-weighted average participation across all facilities per L1 business segment via enterprise_business_taxonomy hierarchy traversal.
 </v>
       </c>
       <c r="AA15" t="str">
@@ -1725,14 +1725,14 @@
         <v>EXP-007</v>
       </c>
       <c r="B16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Flag identifying exposures requiring heightened monitoring due to elevated credit risk. Governance control used for enhanced monitoring, reserve consideration, and management reporting.
+        <v xml:space="preserve">Count of active Criticized risk flags across facilities. Early warning indicator of problem assets requiring heightened monitoring, reserve consideration, and management reporting. Sources from the risk_flag table filtering on flag_code = 'CRITICIZED' with uncleared status.
 </v>
       </c>
       <c r="C16" t="str">
         <v>Criticized Portfolios</v>
       </c>
       <c r="D16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if criticized rating (internal_risk_rating &gt;= 6), 0 otherwise.
+        <v xml:space="preserve">For each facility, count active risk flags where flag_code = 'CRITICIZED' and the flag has not been cleared (cleared_ts IS NULL).
 </v>
       </c>
       <c r="E16" t="str">
@@ -1748,10 +1748,10 @@
         <v>Y</v>
       </c>
       <c r="I16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="J16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if criticized rating (internal_risk_rating &gt;= 6), 0 otherwise.
+        <v xml:space="preserve">For each facility, count active risk flags where flag_code = 'CRITICIZED' and the flag has not been cleared (cleared_ts IS NULL).
 </v>
       </c>
       <c r="K16" t="str">
@@ -1761,10 +1761,10 @@
         <v>Y</v>
       </c>
       <c r="M16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="N16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per counterparty.
+        <v xml:space="preserve">For each counterparty, sum facility-level criticized flag counts across all facilities belonging to that counterparty.
 </v>
       </c>
       <c r="O16" t="str">
@@ -1774,10 +1774,10 @@
         <v>Y</v>
       </c>
       <c r="Q16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="R16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per L3 desk.
+        <v xml:space="preserve">Sum of criticized flag counts per L3 desk segment. Joins facility_master to enterprise_business_taxonomy via lob_segment_id.
 </v>
       </c>
       <c r="S16" t="str">
@@ -1787,10 +1787,10 @@
         <v>Y</v>
       </c>
       <c r="U16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="V16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per L2 portfolio.
+        <v xml:space="preserve">Sum of criticized flag counts per L2 portfolio segment. Traverses enterprise_business_taxonomy hierarchy from L3 to L2 via parent_segment_id.
 </v>
       </c>
       <c r="W16" t="str">
@@ -1800,10 +1800,10 @@
         <v>Y</v>
       </c>
       <c r="Y16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="Z16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per L1 business segment.
+        <v xml:space="preserve">Sum of criticized flag counts per L1 business segment. Full hierarchy traversal L3 → L2 → L1 via enterprise_business_taxonomy.
 </v>
       </c>
       <c r="AA16" t="str">
@@ -1818,14 +1818,14 @@
         <v>EXP-008</v>
       </c>
       <c r="B17" t="str" xml:space="preserve">
-        <v xml:space="preserve">Total exposure amount allocated across multiple legal entities. Supports intra-group concentration transparency.
+        <v xml:space="preserve">Total committed exposure amount (bank share) allocated across multiple legal entities for facilities flagged as cross-entity. Quantifies inter-entity concentration risk and supports intra-group transparency for GSIB reporting. Sources from counterparty_derived (L3) for the cross-entity flag and facility_exposure_snapshot (L2) for committed amounts.
 </v>
       </c>
       <c r="C17" t="str">
         <v>Cross Entity Exposure Amount</v>
       </c>
       <c r="D17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(total_cross_entity_exposure_usd) per facility from counterparty_exposure_summary. Weighted by bank share percentage.
+        <v xml:space="preserve">For each facility flagged as cross-entity, committed exposure amount weighted by the bank's participation share (bank_share_pct). Facilities without cross-entity flag are excluded.
 </v>
       </c>
       <c r="E17" t="str">
@@ -1844,7 +1844,7 @@
         <v>Agg</v>
       </c>
       <c r="J17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(total_cross_entity_exposure_usd) per facility from counterparty_exposure_summary. Weighted by bank share percentage.
+        <v xml:space="preserve">For each facility flagged as cross-entity, committed exposure amount weighted by the bank's participation share (bank_share_pct). Facilities without cross-entity flag are excluded.
 </v>
       </c>
       <c r="K17" t="str">
@@ -1857,7 +1857,7 @@
         <v>Agg</v>
       </c>
       <c r="N17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per counterparty.
+        <v xml:space="preserve">For each counterparty, sum of bank-share-weighted committed amounts across all facilities flagged as cross-entity.
 </v>
       </c>
       <c r="O17" t="str">
@@ -1870,7 +1870,7 @@
         <v>Agg</v>
       </c>
       <c r="R17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per L3 desk segment.
+        <v xml:space="preserve">Sum of cross-entity committed exposure per L3 desk segment via enterprise_business_taxonomy.
 </v>
       </c>
       <c r="S17" t="str">
@@ -1883,7 +1883,7 @@
         <v>Agg</v>
       </c>
       <c r="V17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per L2 portfolio segment.
+        <v xml:space="preserve">Sum of cross-entity committed exposure per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
 </v>
       </c>
       <c r="W17" t="str">
@@ -1896,7 +1896,7 @@
         <v>Agg</v>
       </c>
       <c r="Z17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per L1 business segment segment.
+        <v xml:space="preserve">Sum of cross-entity committed exposure per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
 </v>
       </c>
       <c r="AA17" t="str">
@@ -1911,14 +1911,14 @@
         <v>EXP-009</v>
       </c>
       <c r="B18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Number of days outstanding payments is past due as grouped into 3 "buckets", 0-30 Days, 31-60 Days, 61-90+ Days. Used for staging classification and early credit deterioration monitoring.
+        <v xml:space="preserve">Maximum days payment overdue per facility, calculated from raw payment records in the payment_ledger table. For each facility, identifies payments where applied amount &lt; amount due, computes days overdue as reporting date minus payment_due_date, takes the MAX, then classifies into buckets: 1 = 0-30 days, 2 = 31-60 days, 3 = 61-90+ days. At aggregate levels, reports the worst (MAX) bucket across constituents.
 </v>
       </c>
       <c r="C18" t="str">
         <v>Days Payment Overdue Bucket</v>
       </c>
       <c r="D18" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Facility_ID lookup the Payments records in the Payment Lockbox table, For each payment record where [Payment_Due_Date] &gt; Today() IF ([Pmt_Applied] &lt;[Pmt_Due])&gt;=1, THEN Today() - [Payment_due_date] ==[Days Overdue] SELECT MAX ([Days Overdue] then lookup in Payments Overdue bucket)
+        <v xml:space="preserve">For each facility, lookup payment records in payment_ledger where payment_due_date &lt; reporting date and payment_applied_amt &lt; payment_amount_due (underpaid). Calculate days overdue = reporting date minus payment_due_date. Take MAX days overdue, then classify into overdue bucket: 1 (0-30), 2 (31-60), 3 (61-90+).
 </v>
       </c>
       <c r="E18" t="str">
@@ -1937,7 +1937,7 @@
         <v>Calc</v>
       </c>
       <c r="J18" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Facility_ID lookup the Payments records in the Payment Lockbox table, For each payment record where [Payment_Due_Date] &gt; Today() IF ([Pmt_Applied] &lt;[Pmt_Due])&gt;=1, THEN Today() - [Payment_due_date] ==[Days Overdue] SELECT MAX ([Days Overdue] then lookup in Payments Overdue bucket)
+        <v xml:space="preserve">For each facility, lookup payment records in payment_ledger where payment_due_date &lt; reporting date and payment_applied_amt &lt; payment_amount_due (underpaid). Calculate days overdue = reporting date minus payment_due_date. Take MAX days overdue, then classify into overdue bucket: 1 (0-30), 2 (31-60), 3 (61-90+).
 </v>
       </c>
       <c r="K18" t="str">
@@ -1950,7 +1950,7 @@
         <v>Agg</v>
       </c>
       <c r="N18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per counterparty.
+        <v xml:space="preserve">Worst-case (MAX) overdue bucket across all facilities per counterparty. Identifies the most severely overdue facility for each borrower.
 </v>
       </c>
       <c r="O18" t="str">
@@ -1963,7 +1963,7 @@
         <v>Agg</v>
       </c>
       <c r="R18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per L3 desk segment.
+        <v xml:space="preserve">Worst-case (MAX) overdue bucket per L3 desk segment. Shows the most severe delinquency in each organizational unit.
 </v>
       </c>
       <c r="S18" t="str">
@@ -1976,7 +1976,7 @@
         <v>Agg</v>
       </c>
       <c r="V18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per L2 portfolio segment.
+        <v xml:space="preserve">Worst-case (MAX) overdue bucket per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
 </v>
       </c>
       <c r="W18" t="str">
@@ -1989,7 +1989,7 @@
         <v>Agg</v>
       </c>
       <c r="Z18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per L1 business segment.
+        <v xml:space="preserve">Worst-case (MAX) overdue bucket per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
 </v>
       </c>
       <c r="AA18" t="str">
@@ -2509,14 +2509,25 @@
         <v>EXP-015</v>
       </c>
       <c r="B24" t="str" xml:space="preserve">
-        <v xml:space="preserve">Expected Loss divided by Exposure. Derived KPI measuring loss intensity relative to exposure size, enabling comparative risk ranking across facilities or counterparties.
+        <v xml:space="preserve">Expected Loss as a percentage of committed exposure. Computed from L2 atomic risk parameters: PD (probability of default) × LGD (loss given default). At aggregate levels, uses sum-ratio rollup: SUM(PD × LGD × Committed) / SUM(Committed) × 100 — the exposure-weighted average EL rate. This ensures mathematically consistent aggregation (never averages pre-computed rates). Key credit risk quantification metric for comparing loss intensity across facilities, counterparties, and business segments.
+Ingredient derivation:
+  - PD (pd_pct): L2 facility_risk_snapshot — probability of default (%)
+  - LGD (lgd_pct): L2 facility_risk_snapshot — loss given default (%)
+  - Committed Exposure (committed_amount): L2 facility_exposure_snapshot — raw
+  - EL Rate = PD × LGD (at facility level, committed cancels in ratio)
+  - Aggregate EL Rate = SUM(PD × LGD × Committed) / SUM(Committed) × 100
 </v>
       </c>
       <c r="C24" t="str">
         <v>Expected Loss Rate (%)</v>
       </c>
       <c r="D24" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of expected_loss_rate_pct per facility.
+        <v xml:space="preserve">For each facility:
+  1. LOAD pd_pct, lgd_pct from l2.facility_risk_snapshot
+  2. LOAD committed_amount from l2.facility_exposure_snapshot
+  3. COMPUTE EL Rate = SUM(PD/100 × LGD/100 × Committed) / SUM(Committed) × 100
+     At facility grain, committed cancels → EL Rate ≈ PD × LGD / 100
+Ingredients: pd_pct (L2), lgd_pct (L2), committed_amount (L2)
 </v>
       </c>
       <c r="E24" t="str">
@@ -2532,10 +2543,15 @@
         <v>Y</v>
       </c>
       <c r="I24" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="J24" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of expected_loss_rate_pct per facility.
+        <v xml:space="preserve">For each facility:
+  1. LOAD pd_pct, lgd_pct from l2.facility_risk_snapshot
+  2. LOAD committed_amount from l2.facility_exposure_snapshot
+  3. COMPUTE EL Rate = SUM(PD/100 × LGD/100 × Committed) / SUM(Committed) × 100
+     At facility grain, committed cancels → EL Rate ≈ PD × LGD / 100
+Ingredients: pd_pct (L2), lgd_pct (L2), committed_amount (L2)
 </v>
       </c>
       <c r="K24" t="str">
@@ -2545,10 +2561,15 @@
         <v>Y</v>
       </c>
       <c r="M24" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N24" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level expected_loss_rate_pct per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD pd_pct, lgd_pct for all facilities belonging to this counterparty
+  2. LOAD committed_amount for each facility
+  3. CONVERT to USD via l2.fx_rate spot rate
+  4. COMPUTE SUM(PD × LGD × Committed × FX) / SUM(Committed × FX) × 100
+Sum-ratio rollup with FX: exposure-weighted average EL rate in USD terms.
 </v>
       </c>
       <c r="O24" t="str">
@@ -2558,10 +2579,14 @@
         <v>Y</v>
       </c>
       <c r="Q24" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="R24" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level expected_loss_rate_pct per L3 desk segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOOKUP managed_segment_id from enterprise_business_taxonomy
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(PD × LGD × Committed × FX) / SUM(Committed × FX) × 100
+Sum-ratio rollup: exposure-weighted average EL rate per desk.
 </v>
       </c>
       <c r="S24" t="str">
@@ -2571,10 +2596,14 @@
         <v>Y</v>
       </c>
       <c r="U24" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V24" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level expected_loss_rate_pct per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(PD × LGD × Committed × FX) / SUM(Committed × FX) × 100
+Sum-ratio rollup: exposure-weighted average EL rate per portfolio.
 </v>
       </c>
       <c r="W24" t="str">
@@ -2584,10 +2613,14 @@
         <v>Y</v>
       </c>
       <c r="Y24" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z24" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level expected_loss_rate_pct per L1 business segment segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(PD × LGD × Committed × FX) / SUM(Committed × FX) × 100
+Sum-ratio rollup: exposure-weighted average EL rate per segment.
 </v>
       </c>
       <c r="AA24" t="str">
@@ -2602,14 +2635,25 @@
         <v>EXP-016</v>
       </c>
       <c r="B25" t="str" xml:space="preserve">
-        <v xml:space="preserve">PD × LGD × Exposure expressed in USD. Calculated forward-looking loss metric supporting provisioning, capital planning, and stress testing analytics.
+        <v xml:space="preserve">Expected Loss in dollar terms: PD × LGD × Committed Exposure × Bank Share. Computed from L2 atomic risk parameters and exposure data — NOT from stressed scenarios. This is the base (unstressed) expected credit loss, the foundation for provisioning, capital planning, and CECL/IFRS 9 reserve estimation.
+Ingredient derivation:
+  - PD (pd_pct): L2 facility_risk_snapshot — probability of default (%)
+  - LGD (lgd_pct): L2 facility_risk_snapshot — loss given default (%)
+  - Committed Exposure (committed_amount): L2 facility_exposure_snapshot — raw
+  - Bank Share (bank_share_pct): L2 facility_exposure_snapshot — participation %
+  - EL = (PD/100) × (LGD/100) × Committed × (Bank Share/100)
+Rollup uses direct-sum: SUM(facility EL) at each aggregate level. FX conversion applied at aggregate levels for multi-currency portfolios.
 </v>
       </c>
       <c r="C25" t="str">
         <v>Expected Loss ($)</v>
       </c>
       <c r="D25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(stressed_expected_loss) per facility from stress_test_result. Weighted by bank share percentage.
+        <v xml:space="preserve">For each facility:
+  1. LOAD pd_pct, lgd_pct from l2.facility_risk_snapshot
+  2. LOAD committed_amount, bank_share_pct from l2.facility_exposure_snapshot
+  3. COMPUTE EL = (PD/100) × (LGD/100) × Committed × (Bank Share/100)
+Ingredients: pd_pct (L2), lgd_pct (L2), committed_amount (L2), bank_share_pct (L2)
 </v>
       </c>
       <c r="E25" t="str">
@@ -2625,10 +2669,14 @@
         <v>Y</v>
       </c>
       <c r="I25" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="J25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(stressed_expected_loss) per facility from stress_test_result. Weighted by bank share percentage.
+        <v xml:space="preserve">For each facility:
+  1. LOAD pd_pct, lgd_pct from l2.facility_risk_snapshot
+  2. LOAD committed_amount, bank_share_pct from l2.facility_exposure_snapshot
+  3. COMPUTE EL = (PD/100) × (LGD/100) × Committed × (Bank Share/100)
+Ingredients: pd_pct (L2), lgd_pct (L2), committed_amount (L2), bank_share_pct (L2)
 </v>
       </c>
       <c r="K25" t="str">
@@ -2641,7 +2689,11 @@
         <v>Agg</v>
       </c>
       <c r="N25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD facility-level EL for all facilities of this counterparty
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(facility EL × FX rate) = Counterparty EL (USD)
+Direct-sum rollup with FX conversion.
 </v>
       </c>
       <c r="O25" t="str">
@@ -2654,7 +2706,11 @@
         <v>Agg</v>
       </c>
       <c r="R25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per L3 desk segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOOKUP managed_segment_id from enterprise_business_taxonomy
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(facility EL × FX rate) per desk
+Direct-sum rollup with FX conversion.
 </v>
       </c>
       <c r="S25" t="str">
@@ -2667,7 +2723,11 @@
         <v>Agg</v>
       </c>
       <c r="V25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(facility EL × FX rate) per portfolio
+Direct-sum rollup with FX conversion.
 </v>
       </c>
       <c r="W25" t="str">
@@ -2680,7 +2740,11 @@
         <v>Agg</v>
       </c>
       <c r="Z25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per L1 business segment segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(facility EL × FX rate) per business segment
+Direct-sum rollup with FX conversion.
 </v>
       </c>
       <c r="AA25" t="str">
@@ -3552,17 +3616,17 @@
     </row>
     <row r="35" xml:space="preserve">
       <c r="A35" t="str">
-        <v>EXP-026</v>
+        <v>EXP-027</v>
       </c>
       <c r="B35" t="str" xml:space="preserve">
-        <v xml:space="preserve">Loan to Value Ratio (%) metric.
+        <v xml:space="preserve">Net income computed from L2 atomic inputs: NOI (Net Operating Income, which equals Revenue minus Operating Expense) minus Interest Expense minus Expected Loss (PD × LGD × Committed Amount). Indicator of facility-level profitability.
 </v>
       </c>
       <c r="C35" t="str">
-        <v>Loan to Value Ratio (%)</v>
+        <v>Net Income ($)</v>
       </c>
       <c r="D35" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each DISTINCT (Facility_ID) lookup Collateral ID and SUM(Current_Colalteral_MV) THEN  [Commited_Facility_Amt] / [Current_Collateral_MV] × 100
+        <v xml:space="preserve">Net Income = NOI (Revenue - OpEx) - Interest Expense - Expected Loss (PD × LGD × Committed Amount). All sourced from L2 atomic tables.
 </v>
       </c>
       <c r="E35" t="str">
@@ -3581,11 +3645,11 @@
         <v>Calc</v>
       </c>
       <c r="J35" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each DISTINCT (Facility_ID) lookup Collateral ID and SUM(Current_Colalteral_MV) THEN  [Commited_Facility_Amt] / [Current_Collateral_MV] × 100
+        <v xml:space="preserve">Net Income = NOI (Revenue - OpEx) - Interest Expense - Expected Loss (PD × LGD × Committed Amount). All sourced from L2 atomic tables.
 </v>
       </c>
       <c r="K35" t="str">
-        <v>Loan to Value Ratio (%) (facility)</v>
+        <v>Net Income ($) (facility)</v>
       </c>
       <c r="L35" t="str">
         <v>Y</v>
@@ -3594,11 +3658,11 @@
         <v>Agg</v>
       </c>
       <c r="N35" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level ltv_pct per counterparty.
+        <v xml:space="preserve">SUM of facility-level net income per counterparty, FX-converted to USD.
 </v>
       </c>
       <c r="O35" t="str">
-        <v>Loan to Value Ratio (%) (counterparty)</v>
+        <v>Net Income ($) (counterparty)</v>
       </c>
       <c r="P35" t="str">
         <v>Y</v>
@@ -3607,11 +3671,11 @@
         <v>Agg</v>
       </c>
       <c r="R35" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level ltv_pct per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level net income per L3 desk segment, FX-converted to USD.
 </v>
       </c>
       <c r="S35" t="str">
-        <v>Loan to Value Ratio (%) (desk)</v>
+        <v>Net Income ($) (desk)</v>
       </c>
       <c r="T35" t="str">
         <v>Y</v>
@@ -3620,11 +3684,11 @@
         <v>Agg</v>
       </c>
       <c r="V35" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level ltv_pct per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level net income per L2 portfolio segment, FX-converted to USD.
 </v>
       </c>
       <c r="W35" t="str">
-        <v>Loan to Value Ratio (%) (portfolio)</v>
+        <v>Net Income ($) (portfolio)</v>
       </c>
       <c r="X35" t="str">
         <v>Y</v>
@@ -3633,11 +3697,11 @@
         <v>Agg</v>
       </c>
       <c r="Z35" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level ltv_pct per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level net income per L1 business segment, FX-converted to USD.
 </v>
       </c>
       <c r="AA35" t="str">
-        <v>Loan to Value Ratio (%) (business_segment)</v>
+        <v>Net Income ($) (business_segment)</v>
       </c>
       <c r="AB35" t="str">
         <v/>
@@ -3645,17 +3709,17 @@
     </row>
     <row r="36" xml:space="preserve">
       <c r="A36" t="str">
-        <v>EXP-027</v>
+        <v>EXP-028</v>
       </c>
       <c r="B36" t="str" xml:space="preserve">
-        <v xml:space="preserve">Profit after all expenses in USD. Indicator of borrower profitability and financial sustainability.
+        <v xml:space="preserve">Net Interest Income divided by Average Earning Assets. Core banking profitability measure assessing pricing effectiveness and lending margin. Sourced from L2 facility_profitability_snapshot atomic data.
 </v>
       </c>
       <c r="C36" t="str">
-        <v>Net Income ($)</v>
+        <v>Net Interest Margin (%)</v>
       </c>
       <c r="D36" t="str" xml:space="preserve">
-        <v xml:space="preserve">Revenue – Interest Expense – Operating Cost – EL
+        <v xml:space="preserve">(Interest Income - Interest Expense) / Average Earning Assets * 100.
 </v>
       </c>
       <c r="E36" t="str">
@@ -3674,63 +3738,63 @@
         <v>Calc</v>
       </c>
       <c r="J36" t="str" xml:space="preserve">
-        <v xml:space="preserve">Revenue – Interest Expense – Operating Cost – EL
+        <v xml:space="preserve">(Interest Income - Interest Expense) / Average Earning Assets * 100.
 </v>
       </c>
       <c r="K36" t="str">
-        <v>Net Income ($) (facility)</v>
+        <v>Net Interest Margin (%) (facility)</v>
       </c>
       <c r="L36" t="str">
         <v>Y</v>
       </c>
       <c r="M36" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N36" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level net_income_amt per counterparty.
+        <v xml:space="preserve">SUM(Net Interest Income) / SUM(Avg Earning Assets) * 100 per counterparty. Sum-ratio rollup preserves mathematical consistency.
 </v>
       </c>
       <c r="O36" t="str">
-        <v>Net Income ($) (counterparty)</v>
+        <v>Net Interest Margin (%) (counterparty)</v>
       </c>
       <c r="P36" t="str">
         <v>Y</v>
       </c>
       <c r="Q36" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R36" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level net_income_amt per L3 desk segment.
+        <v xml:space="preserve">SUM(Net Interest Income) / SUM(Avg Earning Assets) * 100 per L3 desk segment.
 </v>
       </c>
       <c r="S36" t="str">
-        <v>Net Income ($) (desk)</v>
+        <v>Net Interest Margin (%) (desk)</v>
       </c>
       <c r="T36" t="str">
         <v>Y</v>
       </c>
       <c r="U36" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V36" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level net_income_amt per L2 portfolio segment.
+        <v xml:space="preserve">SUM(Net Interest Income) / SUM(Avg Earning Assets) * 100 per L2 portfolio segment.
 </v>
       </c>
       <c r="W36" t="str">
-        <v>Net Income ($) (portfolio)</v>
+        <v>Net Interest Margin (%) (portfolio)</v>
       </c>
       <c r="X36" t="str">
         <v>Y</v>
       </c>
       <c r="Y36" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z36" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level net_income_amt per L1 business segment segment.
+        <v xml:space="preserve">SUM(Net Interest Income) / SUM(Avg Earning Assets) * 100 per L1 business segment.
 </v>
       </c>
       <c r="AA36" t="str">
-        <v>Net Income ($) (business_segment)</v>
+        <v>Net Interest Margin (%) (business_segment)</v>
       </c>
       <c r="AB36" t="str">
         <v/>
@@ -3738,17 +3802,17 @@
     </row>
     <row r="37" xml:space="preserve">
       <c r="A37" t="str">
-        <v>EXP-028</v>
+        <v>EXP-029</v>
       </c>
       <c r="B37" t="str" xml:space="preserve">
-        <v xml:space="preserve">Net Interest Income divided by earning assets. Calculated margin KPI assessing pricing effectiveness and lending profitability.
+        <v xml:space="preserve">Allocated operating or servicing cost associated with each facility. Direct-sum rollup at all aggregate levels with FX conversion to USD.
 </v>
       </c>
       <c r="C37" t="str">
-        <v>Net Interest Margin (%)</v>
+        <v>Operating Cost ($)</v>
       </c>
       <c r="D37" t="str" xml:space="preserve">
-        <v xml:space="preserve">(Interest Income - Interst Expense)/Average Earning Assets
+        <v xml:space="preserve">Read operating_expense_amt from facility_financial_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="E37" t="str">
@@ -3764,66 +3828,66 @@
         <v>Y</v>
       </c>
       <c r="I37" t="str">
-        <v>Calc</v>
+        <v>Raw</v>
       </c>
       <c r="J37" t="str" xml:space="preserve">
-        <v xml:space="preserve">(Interest Income - Interst Expense)/Average Earning Assets
+        <v xml:space="preserve">Read operating_expense_amt from facility_financial_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="K37" t="str">
-        <v>Net Interest Margin (%) (facility)</v>
+        <v>Operating Cost ($) (facility)</v>
       </c>
       <c r="L37" t="str">
         <v>Y</v>
       </c>
       <c r="M37" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="N37" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(net_interest_income) / SUM(avg_earning_assets) * 100.0 per counterparty.
+        <v xml:space="preserve">SUM of facility-level operating_expense_amt per counterparty, FX-converted to USD.
 </v>
       </c>
       <c r="O37" t="str">
-        <v>Net Interest Margin (%) (counterparty)</v>
+        <v>Operating Cost ($) (counterparty)</v>
       </c>
       <c r="P37" t="str">
         <v>Y</v>
       </c>
       <c r="Q37" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="R37" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(net_interest_income) / SUM(avg_earning_assets) * 100.0 per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level operating_expense_amt per L3 desk segment, FX-converted to USD.
 </v>
       </c>
       <c r="S37" t="str">
-        <v>Net Interest Margin (%) (desk)</v>
+        <v>Operating Cost ($) (desk)</v>
       </c>
       <c r="T37" t="str">
         <v>Y</v>
       </c>
       <c r="U37" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="V37" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(net_interest_income) / SUM(avg_earning_assets) * 100.0 per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level operating_expense_amt per L2 portfolio segment, FX-converted to USD.
 </v>
       </c>
       <c r="W37" t="str">
-        <v>Net Interest Margin (%) (portfolio)</v>
+        <v>Operating Cost ($) (portfolio)</v>
       </c>
       <c r="X37" t="str">
         <v>Y</v>
       </c>
       <c r="Y37" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="Z37" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(net_interest_income) / SUM(avg_earning_assets) * 100.0 per L1 business segment.
+        <v xml:space="preserve">SUM of facility-level operating_expense_amt per L1 business segment, FX-converted to USD.
 </v>
       </c>
       <c r="AA37" t="str">
-        <v>Net Interest Margin (%) (business_segment)</v>
+        <v>Operating Cost ($) (business_segment)</v>
       </c>
       <c r="AB37" t="str">
         <v/>
@@ -3831,17 +3895,17 @@
     </row>
     <row r="38" xml:space="preserve">
       <c r="A38" t="str">
-        <v>EXP-029</v>
+        <v>EXP-030</v>
       </c>
       <c r="B38" t="str" xml:space="preserve">
-        <v xml:space="preserve">Allocated operating or servicing cost associated with exposure.
+        <v xml:space="preserve">Model-estimated probability of default within defined horizon. Core credit risk input supporting capital modeling, expected loss estimation, stress testing, and risk appetite alignment.
 </v>
       </c>
       <c r="C38" t="str">
-        <v>Operating Cost ($)</v>
+        <v>Probability of Default (%)</v>
       </c>
       <c r="D38" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read operating_expense_amt from facility_financial_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Read pd_pct from facility_risk_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="E38" t="str">
@@ -3860,37 +3924,37 @@
         <v>Raw</v>
       </c>
       <c r="J38" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read operating_expense_amt from facility_financial_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Read pd_pct from facility_risk_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="K38" t="str">
-        <v>Operating Cost ($) (facility)</v>
+        <v>Probability of Default (%) (facility)</v>
       </c>
       <c r="L38" t="str">
         <v>Y</v>
       </c>
       <c r="M38" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="N38" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read operating_expense_amt per counterparty.
+        <v xml:space="preserve">SUM of facility-level pd_pct per counterparty.
 </v>
       </c>
       <c r="O38" t="str">
-        <v>Operating Cost ($) (counterparty)</v>
+        <v>Probability of Default (%) (counterparty)</v>
       </c>
       <c r="P38" t="str">
         <v>Y</v>
       </c>
       <c r="Q38" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="R38" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level operating_expense_amt per L3 desk segment.
+        <v xml:space="preserve">AVG of facility-level pd_pct per L3 desk segment.
 </v>
       </c>
       <c r="S38" t="str">
-        <v>Operating Cost ($) (desk)</v>
+        <v>Probability of Default (%) (desk)</v>
       </c>
       <c r="T38" t="str">
         <v>Y</v>
@@ -3899,24 +3963,24 @@
         <v>Avg</v>
       </c>
       <c r="V38" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level operating_expense_amt per L2 portfolio segment.
+        <v xml:space="preserve">AVG of facility-level pd_pct per L2 portfolio segment.
 </v>
       </c>
       <c r="W38" t="str">
-        <v>Operating Cost ($) (portfolio)</v>
+        <v>Probability of Default (%) (portfolio)</v>
       </c>
       <c r="X38" t="str">
         <v>Y</v>
       </c>
       <c r="Y38" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="Z38" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level operating_expense_amt per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level pd_pct per L1 business segment segment.
 </v>
       </c>
       <c r="AA38" t="str">
-        <v>Operating Cost ($) (business_segment)</v>
+        <v>Probability of Default (%) (business_segment)</v>
       </c>
       <c r="AB38" t="str">
         <v/>
@@ -3924,17 +3988,17 @@
     </row>
     <row r="39" xml:space="preserve">
       <c r="A39" t="str">
-        <v>EXP-030</v>
+        <v>EXP-031</v>
       </c>
       <c r="B39" t="str" xml:space="preserve">
-        <v xml:space="preserve">Model-estimated probability of default within defined horizon. Core credit risk input supporting capital modeling, expected loss estimation, stress testing, and risk appetite alignment.
+        <v xml:space="preserve">Total income generated by the borrower or attributed to the facility in millions USD. Used to assess scale and repayment capacity.
 </v>
       </c>
       <c r="C39" t="str">
-        <v>Probability of Default (%)</v>
+        <v>Revenue ($)</v>
       </c>
       <c r="D39" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read pd_pct from facility_risk_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">SUM(revenue_amt) per facility from facility_financial_snapshot. Weighted by bank share percentage.
 </v>
       </c>
       <c r="E39" t="str">
@@ -3950,14 +4014,14 @@
         <v>Y</v>
       </c>
       <c r="I39" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="J39" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read pd_pct from facility_risk_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">SUM(revenue_amt) per facility from facility_financial_snapshot. Weighted by bank share percentage.
 </v>
       </c>
       <c r="K39" t="str">
-        <v>Probability of Default (%) (facility)</v>
+        <v>Revenue ($) (facility)</v>
       </c>
       <c r="L39" t="str">
         <v>Y</v>
@@ -3966,37 +4030,37 @@
         <v>Agg</v>
       </c>
       <c r="N39" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pd_pct per counterparty.
+        <v xml:space="preserve">SUM of facility-level revenue_amt per counterparty.
 </v>
       </c>
       <c r="O39" t="str">
-        <v>Probability of Default (%) (counterparty)</v>
+        <v>Revenue ($) (counterparty)</v>
       </c>
       <c r="P39" t="str">
         <v>Y</v>
       </c>
       <c r="Q39" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="R39" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level pd_pct per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level revenue_amt per L3 desk segment.
 </v>
       </c>
       <c r="S39" t="str">
-        <v>Probability of Default (%) (desk)</v>
+        <v>Revenue ($) (desk)</v>
       </c>
       <c r="T39" t="str">
         <v>Y</v>
       </c>
       <c r="U39" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="V39" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level pd_pct per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level revenue_amt per L2 portfolio segment.
 </v>
       </c>
       <c r="W39" t="str">
-        <v>Probability of Default (%) (portfolio)</v>
+        <v>Revenue ($) (portfolio)</v>
       </c>
       <c r="X39" t="str">
         <v>Y</v>
@@ -4005,11 +4069,11 @@
         <v>Agg</v>
       </c>
       <c r="Z39" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pd_pct per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level revenue_amt per L1 business segment segment.
 </v>
       </c>
       <c r="AA39" t="str">
-        <v>Probability of Default (%) (business_segment)</v>
+        <v>Revenue ($) (business_segment)</v>
       </c>
       <c r="AB39" t="str">
         <v/>
@@ -4017,17 +4081,17 @@
     </row>
     <row r="40" xml:space="preserve">
       <c r="A40" t="str">
-        <v>EXP-031</v>
+        <v>EXP-032</v>
       </c>
       <c r="B40" t="str" xml:space="preserve">
-        <v xml:space="preserve">Total income generated by the borrower or attributed to the facility in millions USD. Used to assess scale and repayment capacity.
+        <v xml:space="preserve">Original Appriased Value of pledged collateral securing exposure in USD. Supports recovery analysis and secured lending assessment.
 </v>
       </c>
       <c r="C40" t="str">
-        <v>Revenue ($)</v>
+        <v>Collateral Market Value at Origination ($)</v>
       </c>
       <c r="D40" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(revenue_amt) per facility from facility_financial_snapshot. Weighted by bank share percentage.
+        <v xml:space="preserve">SUM(original_valuation_usd) per facility from collateral_snapshot. Weighted by bank share percentage.
 </v>
       </c>
       <c r="E40" t="str">
@@ -4046,11 +4110,11 @@
         <v>Agg</v>
       </c>
       <c r="J40" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(revenue_amt) per facility from facility_financial_snapshot. Weighted by bank share percentage.
+        <v xml:space="preserve">SUM(original_valuation_usd) per facility from collateral_snapshot. Weighted by bank share percentage.
 </v>
       </c>
       <c r="K40" t="str">
-        <v>Revenue ($) (facility)</v>
+        <v>Collateral Market Value at Origination ($) (facility)</v>
       </c>
       <c r="L40" t="str">
         <v>Y</v>
@@ -4059,11 +4123,11 @@
         <v>Agg</v>
       </c>
       <c r="N40" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level revenue_amt per counterparty.
+        <v xml:space="preserve">SUM of facility-level original_valuation_usd per counterparty.
 </v>
       </c>
       <c r="O40" t="str">
-        <v>Revenue ($) (counterparty)</v>
+        <v>Collateral Market Value at Origination ($) (counterparty)</v>
       </c>
       <c r="P40" t="str">
         <v>Y</v>
@@ -4072,11 +4136,11 @@
         <v>Agg</v>
       </c>
       <c r="R40" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level revenue_amt per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level original_valuation_usd per L3 desk segment.
 </v>
       </c>
       <c r="S40" t="str">
-        <v>Revenue ($) (desk)</v>
+        <v>Collateral Market Value at Origination ($) (desk)</v>
       </c>
       <c r="T40" t="str">
         <v>Y</v>
@@ -4085,11 +4149,11 @@
         <v>Agg</v>
       </c>
       <c r="V40" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level revenue_amt per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level original_valuation_usd per L2 portfolio segment.
 </v>
       </c>
       <c r="W40" t="str">
-        <v>Revenue ($) (portfolio)</v>
+        <v>Collateral Market Value at Origination ($) (portfolio)</v>
       </c>
       <c r="X40" t="str">
         <v>Y</v>
@@ -4098,11 +4162,11 @@
         <v>Agg</v>
       </c>
       <c r="Z40" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level revenue_amt per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level original_valuation_usd per L1 business segment segment.
 </v>
       </c>
       <c r="AA40" t="str">
-        <v>Revenue ($) (business_segment)</v>
+        <v>Collateral Market Value at Origination ($) (business_segment)</v>
       </c>
       <c r="AB40" t="str">
         <v/>
@@ -4110,17 +4174,17 @@
     </row>
     <row r="41" xml:space="preserve">
       <c r="A41" t="str">
-        <v>EXP-032</v>
+        <v>EXP-033</v>
       </c>
       <c r="B41" t="str" xml:space="preserve">
-        <v xml:space="preserve">Original Appriased Value of pledged collateral securing exposure in USD. Supports recovery analysis and secured lending assessment.
+        <v xml:space="preserve">Sub-classification of risk mitigant or collateral type tied to the facility. Used for granular risk segmentation.
 </v>
       </c>
       <c r="C41" t="str">
-        <v>Collateral Market Value at Origination ($)</v>
+        <v>Risk Mitigant Sub Type</v>
       </c>
       <c r="D41" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(original_valuation_usd) per facility from collateral_snapshot. Weighted by bank share percentage.
+        <v xml:space="preserve">SUM(risk_mitigant_subtype_code) per facility from risk_mitigant_type_dim.
 </v>
       </c>
       <c r="E41" t="str">
@@ -4139,24 +4203,24 @@
         <v>Agg</v>
       </c>
       <c r="J41" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(original_valuation_usd) per facility from collateral_snapshot. Weighted by bank share percentage.
+        <v xml:space="preserve">SUM(risk_mitigant_subtype_code) per facility from risk_mitigant_type_dim.
 </v>
       </c>
       <c r="K41" t="str">
-        <v>Collateral Market Value at Origination ($) (facility)</v>
+        <v>Risk Mitigant Sub Type (facility)</v>
       </c>
       <c r="L41" t="str">
         <v>Y</v>
       </c>
       <c r="M41" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="N41" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level original_valuation_usd per counterparty.
+        <v xml:space="preserve">Read risk_mitigant_subtype_code per counterparty.
 </v>
       </c>
       <c r="O41" t="str">
-        <v>Collateral Market Value at Origination ($) (counterparty)</v>
+        <v>Risk Mitigant Sub Type (counterparty)</v>
       </c>
       <c r="P41" t="str">
         <v>Y</v>
@@ -4165,11 +4229,11 @@
         <v>Agg</v>
       </c>
       <c r="R41" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level original_valuation_usd per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level risk_mitigant_subtype_code per L3 desk segment.
 </v>
       </c>
       <c r="S41" t="str">
-        <v>Collateral Market Value at Origination ($) (desk)</v>
+        <v>Risk Mitigant Sub Type (desk)</v>
       </c>
       <c r="T41" t="str">
         <v>Y</v>
@@ -4178,11 +4242,11 @@
         <v>Agg</v>
       </c>
       <c r="V41" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level original_valuation_usd per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level risk_mitigant_subtype_code per L2 portfolio segment.
 </v>
       </c>
       <c r="W41" t="str">
-        <v>Collateral Market Value at Origination ($) (portfolio)</v>
+        <v>Risk Mitigant Sub Type (portfolio)</v>
       </c>
       <c r="X41" t="str">
         <v>Y</v>
@@ -4191,11 +4255,11 @@
         <v>Agg</v>
       </c>
       <c r="Z41" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level original_valuation_usd per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level risk_mitigant_subtype_code per L1 business segment segment.
 </v>
       </c>
       <c r="AA41" t="str">
-        <v>Collateral Market Value at Origination ($) (business_segment)</v>
+        <v>Risk Mitigant Sub Type (business_segment)</v>
       </c>
       <c r="AB41" t="str">
         <v/>
@@ -4203,17 +4267,17 @@
     </row>
     <row r="42" xml:space="preserve">
       <c r="A42" t="str">
-        <v>EXP-033</v>
+        <v>EXP-034</v>
       </c>
       <c r="B42" t="str" xml:space="preserve">
-        <v xml:space="preserve">Sub-classification of risk mitigant or collateral type tied to the facility. Used for granular risk segmentation.
+        <v xml:space="preserve">Parent group of risk mitigation or collateral asset type (e.g., cash, aviation, guarantee). Used to assess recovery support mechanisms.
 </v>
       </c>
       <c r="C42" t="str">
-        <v>Risk Mitigant Sub Type</v>
+        <v>Risk Mitigant Type</v>
       </c>
       <c r="D42" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(risk_mitigant_subtype_code) per facility from risk_mitigant_type_dim.
+        <v xml:space="preserve">SUM(risk_mitigant_id) per facility from risk_mitigant_master.
 </v>
       </c>
       <c r="E42" t="str">
@@ -4232,11 +4296,11 @@
         <v>Agg</v>
       </c>
       <c r="J42" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(risk_mitigant_subtype_code) per facility from risk_mitigant_type_dim.
+        <v xml:space="preserve">SUM(risk_mitigant_id) per facility from risk_mitigant_master.
 </v>
       </c>
       <c r="K42" t="str">
-        <v>Risk Mitigant Sub Type (facility)</v>
+        <v>Risk Mitigant Type (facility)</v>
       </c>
       <c r="L42" t="str">
         <v>Y</v>
@@ -4245,11 +4309,11 @@
         <v>Raw</v>
       </c>
       <c r="N42" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_mitigant_subtype_code per counterparty.
+        <v xml:space="preserve">Read risk_mitigant_id per counterparty.
 </v>
       </c>
       <c r="O42" t="str">
-        <v>Risk Mitigant Sub Type (counterparty)</v>
+        <v>Risk Mitigant Type (counterparty)</v>
       </c>
       <c r="P42" t="str">
         <v>Y</v>
@@ -4258,11 +4322,11 @@
         <v>Agg</v>
       </c>
       <c r="R42" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_mitigant_subtype_code per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level risk_mitigant_id per L3 desk segment.
 </v>
       </c>
       <c r="S42" t="str">
-        <v>Risk Mitigant Sub Type (desk)</v>
+        <v>Risk Mitigant Type (desk)</v>
       </c>
       <c r="T42" t="str">
         <v>Y</v>
@@ -4271,11 +4335,11 @@
         <v>Agg</v>
       </c>
       <c r="V42" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_mitigant_subtype_code per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level risk_mitigant_id per L2 portfolio segment.
 </v>
       </c>
       <c r="W42" t="str">
-        <v>Risk Mitigant Sub Type (portfolio)</v>
+        <v>Risk Mitigant Type (portfolio)</v>
       </c>
       <c r="X42" t="str">
         <v>Y</v>
@@ -4284,11 +4348,11 @@
         <v>Agg</v>
       </c>
       <c r="Z42" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_mitigant_subtype_code per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level risk_mitigant_id per L1 business segment segment.
 </v>
       </c>
       <c r="AA42" t="str">
-        <v>Risk Mitigant Sub Type (business_segment)</v>
+        <v>Risk Mitigant Type (business_segment)</v>
       </c>
       <c r="AB42" t="str">
         <v/>
@@ -4296,17 +4360,17 @@
     </row>
     <row r="43" xml:space="preserve">
       <c r="A43" t="str">
-        <v>EXP-034</v>
+        <v>EXP-035</v>
       </c>
       <c r="B43" t="str" xml:space="preserve">
-        <v xml:space="preserve">Parent group of risk mitigation or collateral asset type (e.g., cash, aviation, guarantee). Used to assess recovery support mechanisms.
+        <v xml:space="preserve">Net Income divided by Total Assets. Calculated efficiency KPI measuring asset productivity and overall financial performance.
 </v>
       </c>
       <c r="C43" t="str">
-        <v>Risk Mitigant Type</v>
+        <v>Return on Assets (%)</v>
       </c>
       <c r="D43" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(risk_mitigant_id) per facility from risk_mitigant_master.
+        <v xml:space="preserve">Facility Net Income / Facility Exposure
 </v>
       </c>
       <c r="E43" t="str">
@@ -4322,66 +4386,66 @@
         <v>Y</v>
       </c>
       <c r="I43" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="J43" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(risk_mitigant_id) per facility from risk_mitigant_master.
+        <v xml:space="preserve">Facility Net Income / Facility Exposure
 </v>
       </c>
       <c r="K43" t="str">
-        <v>Risk Mitigant Type (facility)</v>
+        <v>Return on Assets (%) (facility)</v>
       </c>
       <c r="L43" t="str">
         <v>Y</v>
       </c>
       <c r="M43" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="N43" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_mitigant_id per counterparty.
+        <v xml:space="preserve">Net Income / Total Assets * 100 per counterparty (direct from financials).
 </v>
       </c>
       <c r="O43" t="str">
-        <v>Risk Mitigant Type (counterparty)</v>
+        <v>Return on Assets (%) (counterparty)</v>
       </c>
       <c r="P43" t="str">
         <v>Y</v>
       </c>
       <c r="Q43" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="R43" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_mitigant_id per L3 desk segment.
+        <v xml:space="preserve">Exposure-weighted average ROA per L3 desk segment.
 </v>
       </c>
       <c r="S43" t="str">
-        <v>Risk Mitigant Type (desk)</v>
+        <v>Return on Assets (%) (desk)</v>
       </c>
       <c r="T43" t="str">
         <v>Y</v>
       </c>
       <c r="U43" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="V43" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_mitigant_id per L2 portfolio segment.
+        <v xml:space="preserve">Exposure-weighted average ROA per L2 portfolio segment.
 </v>
       </c>
       <c r="W43" t="str">
-        <v>Risk Mitigant Type (portfolio)</v>
+        <v>Return on Assets (%) (portfolio)</v>
       </c>
       <c r="X43" t="str">
         <v>Y</v>
       </c>
       <c r="Y43" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="Z43" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_mitigant_id per L1 business segment segment.
+        <v xml:space="preserve">Exposure-weighted average ROA per L1 business segment.
 </v>
       </c>
       <c r="AA43" t="str">
-        <v>Risk Mitigant Type (business_segment)</v>
+        <v>Return on Assets (%) (business_segment)</v>
       </c>
       <c r="AB43" t="str">
         <v/>
@@ -4389,17 +4453,17 @@
     </row>
     <row r="44" xml:space="preserve">
       <c r="A44" t="str">
-        <v>EXP-035</v>
+        <v>EXP-036</v>
       </c>
       <c r="B44" t="str" xml:space="preserve">
-        <v xml:space="preserve">Net Income divided by Total Assets. Calculated efficiency KPI measuring asset productivity and overall financial performance.
+        <v xml:space="preserve">Net Income divided by Equity. Calculated profitability KPI measuring return generated on shareholder capital and supporting performance benchmarking.
 </v>
       </c>
       <c r="C44" t="str">
-        <v>Return on Assets (%)</v>
+        <v>Return on Equity (%)</v>
       </c>
       <c r="D44" t="str" xml:space="preserve">
-        <v xml:space="preserve">Facility Net Income / Facility Exposure
+        <v xml:space="preserve">Net Income (Facility) / Allocated Equity (Facility)
 </v>
       </c>
       <c r="E44" t="str">
@@ -4418,11 +4482,11 @@
         <v>Calc</v>
       </c>
       <c r="J44" t="str" xml:space="preserve">
-        <v xml:space="preserve">Facility Net Income / Facility Exposure
+        <v xml:space="preserve">Net Income (Facility) / Allocated Equity (Facility)
 </v>
       </c>
       <c r="K44" t="str">
-        <v>Return on Assets (%) (facility)</v>
+        <v>Return on Equity (%) (facility)</v>
       </c>
       <c r="L44" t="str">
         <v>Y</v>
@@ -4431,11 +4495,11 @@
         <v>Calc</v>
       </c>
       <c r="N44" t="str" xml:space="preserve">
-        <v xml:space="preserve">Net Income / Total Assets * 100 per counterparty (direct from financials).
+        <v xml:space="preserve">Net Income / Shareholders Equity * 100 per counterparty (direct from financials).
 </v>
       </c>
       <c r="O44" t="str">
-        <v>Return on Assets (%) (counterparty)</v>
+        <v>Return on Equity (%) (counterparty)</v>
       </c>
       <c r="P44" t="str">
         <v>Y</v>
@@ -4444,11 +4508,11 @@
         <v>Avg</v>
       </c>
       <c r="R44" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average ROA per L3 desk segment.
+        <v xml:space="preserve">Exposure-weighted average ROE per L3 desk segment.
 </v>
       </c>
       <c r="S44" t="str">
-        <v>Return on Assets (%) (desk)</v>
+        <v>Return on Equity (%) (desk)</v>
       </c>
       <c r="T44" t="str">
         <v>Y</v>
@@ -4457,11 +4521,11 @@
         <v>Avg</v>
       </c>
       <c r="V44" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average ROA per L2 portfolio segment.
+        <v xml:space="preserve">Exposure-weighted average ROE per L2 portfolio segment.
 </v>
       </c>
       <c r="W44" t="str">
-        <v>Return on Assets (%) (portfolio)</v>
+        <v>Return on Equity (%) (portfolio)</v>
       </c>
       <c r="X44" t="str">
         <v>Y</v>
@@ -4470,11 +4534,11 @@
         <v>Avg</v>
       </c>
       <c r="Z44" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average ROA per L1 business segment.
+        <v xml:space="preserve">Exposure-weighted average ROE per L1 business segment.
 </v>
       </c>
       <c r="AA44" t="str">
-        <v>Return on Assets (%) (business_segment)</v>
+        <v>Return on Equity (%) (business_segment)</v>
       </c>
       <c r="AB44" t="str">
         <v/>
@@ -4482,17 +4546,17 @@
     </row>
     <row r="45" xml:space="preserve">
       <c r="A45" t="str">
-        <v>EXP-036</v>
+        <v>EXP-037</v>
       </c>
       <c r="B45" t="str" xml:space="preserve">
-        <v xml:space="preserve">Net Income divided by Equity. Calculated profitability KPI measuring return generated on shareholder capital and supporting performance benchmarking.
+        <v xml:space="preserve">Total principal and interest obligations due within reporting period in millions USD. Used in repayment capacity and covenant analysis.
 </v>
       </c>
       <c r="C45" t="str">
-        <v>Return on Equity (%)</v>
+        <v>Total Debt Service ($)</v>
       </c>
       <c r="D45" t="str" xml:space="preserve">
-        <v xml:space="preserve">Net Income (Facility) / Allocated Equity (Facility)
+        <v xml:space="preserve">Lookup total_debt_service_amt from facility_financial_snapshot, convert to USD via l2.fx_rate spot rate (COALESCE to 1 for USD-denominated facilities).
 </v>
       </c>
       <c r="E45" t="str">
@@ -4511,63 +4575,63 @@
         <v>Calc</v>
       </c>
       <c r="J45" t="str" xml:space="preserve">
-        <v xml:space="preserve">Net Income (Facility) / Allocated Equity (Facility)
+        <v xml:space="preserve">Lookup total_debt_service_amt from facility_financial_snapshot, convert to USD via l2.fx_rate spot rate (COALESCE to 1 for USD-denominated facilities).
 </v>
       </c>
       <c r="K45" t="str">
-        <v>Return on Equity (%) (facility)</v>
+        <v>Total Debt Service ($) (facility)</v>
       </c>
       <c r="L45" t="str">
         <v>Y</v>
       </c>
       <c r="M45" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="N45" t="str" xml:space="preserve">
-        <v xml:space="preserve">Net Income / Shareholders Equity * 100 per counterparty (direct from financials).
+        <v xml:space="preserve">SUM of facility-level total_debt_service_amt converted to USD per counterparty.
 </v>
       </c>
       <c r="O45" t="str">
-        <v>Return on Equity (%) (counterparty)</v>
+        <v>Total Debt Service ($) (counterparty)</v>
       </c>
       <c r="P45" t="str">
         <v>Y</v>
       </c>
       <c r="Q45" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="R45" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average ROE per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level total_debt_service_amt converted to USD per L3 desk segment.
 </v>
       </c>
       <c r="S45" t="str">
-        <v>Return on Equity (%) (desk)</v>
+        <v>Total Debt Service ($) (desk)</v>
       </c>
       <c r="T45" t="str">
         <v>Y</v>
       </c>
       <c r="U45" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="V45" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average ROE per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level total_debt_service_amt converted to USD per L2 portfolio segment.
 </v>
       </c>
       <c r="W45" t="str">
-        <v>Return on Equity (%) (portfolio)</v>
+        <v>Total Debt Service ($) (portfolio)</v>
       </c>
       <c r="X45" t="str">
         <v>Y</v>
       </c>
       <c r="Y45" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="Z45" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average ROE per L1 business segment.
+        <v xml:space="preserve">SUM of facility-level total_debt_service_amt converted to USD per L1 business segment.
 </v>
       </c>
       <c r="AA45" t="str">
-        <v>Return on Equity (%) (business_segment)</v>
+        <v>Total Debt Service ($) (business_segment)</v>
       </c>
       <c r="AB45" t="str">
         <v/>
@@ -4575,17 +4639,17 @@
     </row>
     <row r="46" xml:space="preserve">
       <c r="A46" t="str">
-        <v>EXP-037</v>
+        <v>EXP-038</v>
       </c>
       <c r="B46" t="str" xml:space="preserve">
-        <v xml:space="preserve">Total principal and interest obligations due within reporting period in millions USD. Used in repayment capacity and covenant analysis.
+        <v xml:space="preserve">Exposure divided by Exposure Limit. Calculated KPI measuring the proportion of approved capacity currently drawn, providing insight into liquidity usage and limit pressure.
 </v>
       </c>
       <c r="C46" t="str">
-        <v>Total Debt Service ($)</v>
+        <v>Utilization (%)</v>
       </c>
       <c r="D46" t="str" xml:space="preserve">
-        <v xml:space="preserve">Lookup total_debt_service_amt from facility_financial_snapshot, convert to USD via l2.fx_rate spot rate (COALESCE to 1 for USD-denominated facilities).
+        <v xml:space="preserve">For each Distinct([Facility ID]), WHEN IS(MAX(AS_OF_DATE) AND [Facility_Active_Flag]="Y" Sum([Utilized Exposure] / [Committed_Facility_Amt])
 </v>
       </c>
       <c r="E46" t="str">
@@ -4604,63 +4668,63 @@
         <v>Calc</v>
       </c>
       <c r="J46" t="str" xml:space="preserve">
-        <v xml:space="preserve">Lookup total_debt_service_amt from facility_financial_snapshot, convert to USD via l2.fx_rate spot rate (COALESCE to 1 for USD-denominated facilities).
+        <v xml:space="preserve">For each Distinct([Facility ID]), WHEN IS(MAX(AS_OF_DATE) AND [Facility_Active_Flag]="Y" Sum([Utilized Exposure] / [Committed_Facility_Amt])
 </v>
       </c>
       <c r="K46" t="str">
-        <v>Total Debt Service ($) (facility)</v>
+        <v>Utilization (%) (facility)</v>
       </c>
       <c r="L46" t="str">
         <v>Y</v>
       </c>
       <c r="M46" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N46" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_debt_service_amt converted to USD per counterparty.
+        <v xml:space="preserve">SUM(drawn_amount) / SUM(committed_amount) * 100.0 per counterparty.
 </v>
       </c>
       <c r="O46" t="str">
-        <v>Total Debt Service ($) (counterparty)</v>
+        <v>Utilization (%) (counterparty)</v>
       </c>
       <c r="P46" t="str">
         <v>Y</v>
       </c>
       <c r="Q46" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R46" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_debt_service_amt converted to USD per L3 desk segment.
+        <v xml:space="preserve">SUM(drawn_amount) / SUM(committed_amount) * 100.0 per L3 desk segment.
 </v>
       </c>
       <c r="S46" t="str">
-        <v>Total Debt Service ($) (desk)</v>
+        <v>Utilization (%) (desk)</v>
       </c>
       <c r="T46" t="str">
         <v>Y</v>
       </c>
       <c r="U46" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V46" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_debt_service_amt converted to USD per L2 portfolio segment.
+        <v xml:space="preserve">SUM(drawn_amount) / SUM(committed_amount) * 100.0 per L2 portfolio segment.
 </v>
       </c>
       <c r="W46" t="str">
-        <v>Total Debt Service ($) (portfolio)</v>
+        <v>Utilization (%) (portfolio)</v>
       </c>
       <c r="X46" t="str">
         <v>Y</v>
       </c>
       <c r="Y46" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z46" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_debt_service_amt converted to USD per L1 business segment.
+        <v xml:space="preserve">SUM(drawn_amount) / SUM(committed_amount) * 100.0 per L1 business segment.
 </v>
       </c>
       <c r="AA46" t="str">
-        <v>Total Debt Service ($) (business_segment)</v>
+        <v>Utilization (%) (business_segment)</v>
       </c>
       <c r="AB46" t="str">
         <v/>
@@ -4668,17 +4732,17 @@
     </row>
     <row r="47" xml:space="preserve">
       <c r="A47" t="str">
-        <v>EXP-038</v>
+        <v>EXP-039</v>
       </c>
       <c r="B47" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure divided by Exposure Limit. Calculated KPI measuring the proportion of approved capacity currently drawn, providing insight into liquidity usage and limit pressure.
+        <v xml:space="preserve">The currently drawn/outstanding amount (in USD) on the facility as of the reporting date.
 </v>
       </c>
       <c r="C47" t="str">
-        <v>Utilization (%)</v>
+        <v>Utilized Amount ($)</v>
       </c>
       <c r="D47" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Distinct([Facility ID]), WHEN IS(MAX(AS_OF_DATE) AND [Facility_Active_Flag]="Y" Sum([Utilized Exposure] / [Committed_Facility_Amt])
+        <v xml:space="preserve">Read utilized_amount_usd from limit_utilization_event for each facility as- of reporting date.
 </v>
       </c>
       <c r="E47" t="str">
@@ -4694,66 +4758,66 @@
         <v>Y</v>
       </c>
       <c r="I47" t="str">
-        <v>Calc</v>
+        <v>Raw</v>
       </c>
       <c r="J47" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Distinct([Facility ID]), WHEN IS(MAX(AS_OF_DATE) AND [Facility_Active_Flag]="Y" Sum([Utilized Exposure] / [Committed_Facility_Amt])
+        <v xml:space="preserve">Read utilized_amount_usd from limit_utilization_event for each facility as- of reporting date.
 </v>
       </c>
       <c r="K47" t="str">
-        <v>Utilization (%) (facility)</v>
+        <v>Utilized Amount ($) (facility)</v>
       </c>
       <c r="L47" t="str">
         <v>Y</v>
       </c>
       <c r="M47" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="N47" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(drawn_amount) / SUM(committed_amount) * 100.0 per counterparty.
+        <v xml:space="preserve">SUM of facility-level utilized_amount_usd per counterparty.
 </v>
       </c>
       <c r="O47" t="str">
-        <v>Utilization (%) (counterparty)</v>
+        <v>Utilized Amount ($) (counterparty)</v>
       </c>
       <c r="P47" t="str">
         <v>Y</v>
       </c>
       <c r="Q47" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="R47" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(drawn_amount) / SUM(committed_amount) * 100.0 per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level utilized_amount_usd per L3 desk segment.
 </v>
       </c>
       <c r="S47" t="str">
-        <v>Utilization (%) (desk)</v>
+        <v>Utilized Amount ($) (desk)</v>
       </c>
       <c r="T47" t="str">
         <v>Y</v>
       </c>
       <c r="U47" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="V47" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(drawn_amount) / SUM(committed_amount) * 100.0 per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level utilized_amount_usd per L2 portfolio segment.
 </v>
       </c>
       <c r="W47" t="str">
-        <v>Utilization (%) (portfolio)</v>
+        <v>Utilized Amount ($) (portfolio)</v>
       </c>
       <c r="X47" t="str">
         <v>Y</v>
       </c>
       <c r="Y47" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="Z47" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(drawn_amount) / SUM(committed_amount) * 100.0 per L1 business segment.
+        <v xml:space="preserve">SUM of facility-level utilized_amount_usd per L1 business segment segment.
 </v>
       </c>
       <c r="AA47" t="str">
-        <v>Utilization (%) (business_segment)</v>
+        <v>Utilized Amount ($) (business_segment)</v>
       </c>
       <c r="AB47" t="str">
         <v/>
@@ -4761,17 +4825,18 @@
     </row>
     <row r="48" xml:space="preserve">
       <c r="A48" t="str">
-        <v>EXP-039</v>
+        <v>EXP-041</v>
       </c>
       <c r="B48" t="str" xml:space="preserve">
-        <v xml:space="preserve">The currently drawn/outstanding amount (in USD) on the facility as of the reporting date.
+        <v xml:space="preserve">Total interest earned on outstanding exposures during the reporting period. Sources from facility_profitability_snapshot.interest_income_amt (ETL'd from core banking, includes proper accrual and day-count per ASC 310-20). Bank-share-adjusted via facility_lender_allocation.
 </v>
       </c>
       <c r="C48" t="str">
-        <v>Utilized Amount ($)</v>
+        <v>Interest Income</v>
       </c>
       <c r="D48" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read utilized_amount_usd from limit_utilization_event for each facility as- of reporting date.
+        <v xml:space="preserve">SUM(interest_income_amt) per facility from facility_profitability_snapshot.
+Weighted by bank_share_pct from facility_lender_allocation.
 </v>
       </c>
       <c r="E48" t="str">
@@ -4787,27 +4852,29 @@
         <v>Y</v>
       </c>
       <c r="I48" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="J48" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read utilized_amount_usd from limit_utilization_event for each facility as- of reporting date.
+        <v xml:space="preserve">SUM(interest_income_amt) per facility from facility_profitability_snapshot.
+Weighted by bank_share_pct from facility_lender_allocation.
 </v>
       </c>
       <c r="K48" t="str">
-        <v>Utilized Amount ($) (facility)</v>
+        <v>Interest Income (facility)</v>
       </c>
       <c r="L48" t="str">
         <v>Y</v>
       </c>
       <c r="M48" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N48" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level utilized_amount_usd per counterparty.
+        <v xml:space="preserve">For each counterparty, sum facility-level interest income weighted
+by participation_pct from facility_counterparty_participation.
 </v>
       </c>
       <c r="O48" t="str">
-        <v>Utilized Amount ($) (counterparty)</v>
+        <v>Interest Income (counterparty)</v>
       </c>
       <c r="P48" t="str">
         <v>Y</v>
@@ -4816,11 +4883,11 @@
         <v>Agg</v>
       </c>
       <c r="R48" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level utilized_amount_usd per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level interest income per L3 desk segment.
 </v>
       </c>
       <c r="S48" t="str">
-        <v>Utilized Amount ($) (desk)</v>
+        <v>Interest Income (desk)</v>
       </c>
       <c r="T48" t="str">
         <v>Y</v>
@@ -4829,11 +4896,12 @@
         <v>Agg</v>
       </c>
       <c r="V48" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level utilized_amount_usd per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level interest income per L2 portfolio segment.
+Traverses L3 -&gt; L2 via parent_segment_id.
 </v>
       </c>
       <c r="W48" t="str">
-        <v>Utilized Amount ($) (portfolio)</v>
+        <v>Interest Income (portfolio)</v>
       </c>
       <c r="X48" t="str">
         <v>Y</v>
@@ -4842,11 +4910,12 @@
         <v>Agg</v>
       </c>
       <c r="Z48" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level utilized_amount_usd per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level interest income per L1 business segment.
+Traverses L3 -&gt; L2 -&gt; L1 via parent_segment_id chain.
 </v>
       </c>
       <c r="AA48" t="str">
-        <v>Utilized Amount ($) (business_segment)</v>
+        <v>Interest Income (business_segment)</v>
       </c>
       <c r="AB48" t="str">
         <v/>
@@ -4854,18 +4923,17 @@
     </row>
     <row r="49" xml:space="preserve">
       <c r="A49" t="str">
-        <v>EXP-041</v>
+        <v>EXP-042</v>
       </c>
       <c r="B49" t="str" xml:space="preserve">
-        <v xml:space="preserve">Total interest earned on outstanding exposures during the reporting period. Sources from facility_profitability_snapshot.interest_income_amt (ETL'd from core banking, includes proper accrual and day-count per ASC 310-20). Bank-share-adjusted via facility_lender_allocation.
+        <v xml:space="preserve">Total on-balance-sheet assets attributable to the reporting entity at a point in time.
 </v>
       </c>
       <c r="C49" t="str">
-        <v>Interest Income</v>
+        <v>Total Assets Amount</v>
       </c>
       <c r="D49" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(interest_income_amt) per facility from facility_profitability_snapshot.
-Weighted by bank_share_pct from facility_lender_allocation.
+        <v xml:space="preserve">SUM(total_assets_amt) per facility from counterparty_financial_snapshot. Weighted by bank share percentage.
 </v>
       </c>
       <c r="E49" t="str">
@@ -4884,26 +4952,24 @@
         <v>Agg</v>
       </c>
       <c r="J49" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(interest_income_amt) per facility from facility_profitability_snapshot.
-Weighted by bank_share_pct from facility_lender_allocation.
+        <v xml:space="preserve">SUM(total_assets_amt) per facility from counterparty_financial_snapshot. Weighted by bank share percentage.
 </v>
       </c>
       <c r="K49" t="str">
-        <v>Interest Income (facility)</v>
+        <v>Total Assets Amount (facility)</v>
       </c>
       <c r="L49" t="str">
         <v>Y</v>
       </c>
       <c r="M49" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="N49" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each counterparty, sum facility-level interest income weighted
-by participation_pct from facility_counterparty_participation.
+        <v xml:space="preserve">SUM of facility-level total_assets_amt per counterparty.
 </v>
       </c>
       <c r="O49" t="str">
-        <v>Interest Income (counterparty)</v>
+        <v>Total Assets Amount (counterparty)</v>
       </c>
       <c r="P49" t="str">
         <v>Y</v>
@@ -4912,11 +4978,11 @@
         <v>Agg</v>
       </c>
       <c r="R49" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level interest income per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level total_assets_amt per L3 desk segment.
 </v>
       </c>
       <c r="S49" t="str">
-        <v>Interest Income (desk)</v>
+        <v>Total Assets Amount (desk)</v>
       </c>
       <c r="T49" t="str">
         <v>Y</v>
@@ -4925,12 +4991,11 @@
         <v>Agg</v>
       </c>
       <c r="V49" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level interest income per L2 portfolio segment.
-Traverses L3 -&gt; L2 via parent_segment_id.
+        <v xml:space="preserve">SUM of facility-level total_assets_amt per L2 portfolio segment.
 </v>
       </c>
       <c r="W49" t="str">
-        <v>Interest Income (portfolio)</v>
+        <v>Total Assets Amount (portfolio)</v>
       </c>
       <c r="X49" t="str">
         <v>Y</v>
@@ -4939,12 +5004,11 @@
         <v>Agg</v>
       </c>
       <c r="Z49" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level interest income per L1 business segment.
-Traverses L3 -&gt; L2 -&gt; L1 via parent_segment_id chain.
+        <v xml:space="preserve">SUM of facility-level total_assets_amt per L1 business segment segment.
 </v>
       </c>
       <c r="AA49" t="str">
-        <v>Interest Income (business_segment)</v>
+        <v>Total Assets Amount (business_segment)</v>
       </c>
       <c r="AB49" t="str">
         <v/>
@@ -4952,17 +5016,17 @@
     </row>
     <row r="50" xml:space="preserve">
       <c r="A50" t="str">
-        <v>EXP-042</v>
+        <v>EXP-043</v>
       </c>
       <c r="B50" t="str" xml:space="preserve">
-        <v xml:space="preserve">Total on-balance-sheet assets attributable to the reporting entity at a point in time.
+        <v xml:space="preserve">Total shareholder capital allocated to the reporting unit.
 </v>
       </c>
       <c r="C50" t="str">
-        <v>Total Assets Amount</v>
+        <v>Total Equity amount</v>
       </c>
       <c r="D50" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(total_assets_amt) per facility from counterparty_financial_snapshot. Weighted by bank share percentage.
+        <v xml:space="preserve">SUM(allocated_equity_amt) per facility from facility_profitability_snapshot. Weighted by bank share percentage.
 </v>
       </c>
       <c r="E50" t="str">
@@ -4981,11 +5045,11 @@
         <v>Agg</v>
       </c>
       <c r="J50" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(total_assets_amt) per facility from counterparty_financial_snapshot. Weighted by bank share percentage.
+        <v xml:space="preserve">SUM(allocated_equity_amt) per facility from facility_profitability_snapshot. Weighted by bank share percentage.
 </v>
       </c>
       <c r="K50" t="str">
-        <v>Total Assets Amount (facility)</v>
+        <v>Total Equity amount (facility)</v>
       </c>
       <c r="L50" t="str">
         <v>Y</v>
@@ -4994,11 +5058,11 @@
         <v>Agg</v>
       </c>
       <c r="N50" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_assets_amt per counterparty.
+        <v xml:space="preserve">SUM of facility-level allocated_equity_amt per counterparty.
 </v>
       </c>
       <c r="O50" t="str">
-        <v>Total Assets Amount (counterparty)</v>
+        <v>Total Equity amount (counterparty)</v>
       </c>
       <c r="P50" t="str">
         <v>Y</v>
@@ -5007,11 +5071,11 @@
         <v>Agg</v>
       </c>
       <c r="R50" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_assets_amt per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level allocated_equity_amt per L3 desk segment.
 </v>
       </c>
       <c r="S50" t="str">
-        <v>Total Assets Amount (desk)</v>
+        <v>Total Equity amount (desk)</v>
       </c>
       <c r="T50" t="str">
         <v>Y</v>
@@ -5020,11 +5084,11 @@
         <v>Agg</v>
       </c>
       <c r="V50" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_assets_amt per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level allocated_equity_amt per L2 portfolio segment.
 </v>
       </c>
       <c r="W50" t="str">
-        <v>Total Assets Amount (portfolio)</v>
+        <v>Total Equity amount (portfolio)</v>
       </c>
       <c r="X50" t="str">
         <v>Y</v>
@@ -5033,11 +5097,11 @@
         <v>Agg</v>
       </c>
       <c r="Z50" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_assets_amt per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level allocated_equity_amt per L1 business segment segment.
 </v>
       </c>
       <c r="AA50" t="str">
-        <v>Total Assets Amount (business_segment)</v>
+        <v>Total Equity amount (business_segment)</v>
       </c>
       <c r="AB50" t="str">
         <v/>
@@ -5045,17 +5109,17 @@
     </row>
     <row r="51" xml:space="preserve">
       <c r="A51" t="str">
-        <v>EXP-043</v>
+        <v>EXP-044</v>
       </c>
       <c r="B51" t="str" xml:space="preserve">
-        <v xml:space="preserve">Total shareholder capital allocated to the reporting unit.
+        <v xml:space="preserve">Average balance of interest-generating assets over the reporting period.
 </v>
       </c>
       <c r="C51" t="str">
-        <v>Total Equity amount</v>
+        <v>Average Earning Assets Amount</v>
       </c>
       <c r="D51" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(allocated_equity_amt) per facility from facility_profitability_snapshot. Weighted by bank share percentage.
+        <v xml:space="preserve">Read avg_earning_assets_amt from facility_profitability_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="E51" t="str">
@@ -5071,27 +5135,27 @@
         <v>Y</v>
       </c>
       <c r="I51" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="J51" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(allocated_equity_amt) per facility from facility_profitability_snapshot. Weighted by bank share percentage.
+        <v xml:space="preserve">Read avg_earning_assets_amt from facility_profitability_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="K51" t="str">
-        <v>Total Equity amount (facility)</v>
+        <v>Average Earning Assets Amount (facility)</v>
       </c>
       <c r="L51" t="str">
         <v>Y</v>
       </c>
       <c r="M51" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="N51" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level allocated_equity_amt per counterparty.
+        <v xml:space="preserve">Exposure-weighted average of avg_earning_assets_amt across counterparty facilities.
 </v>
       </c>
       <c r="O51" t="str">
-        <v>Total Equity amount (counterparty)</v>
+        <v>Average Earning Assets Amount (counterparty)</v>
       </c>
       <c r="P51" t="str">
         <v>Y</v>
@@ -5100,24 +5164,24 @@
         <v>Agg</v>
       </c>
       <c r="R51" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level allocated_equity_amt per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level avg_earning_assets_amt per L3 desk segment.
 </v>
       </c>
       <c r="S51" t="str">
-        <v>Total Equity amount (desk)</v>
+        <v>Average Earning Assets Amount (desk)</v>
       </c>
       <c r="T51" t="str">
         <v>Y</v>
       </c>
       <c r="U51" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="V51" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level allocated_equity_amt per L2 portfolio segment.
+        <v xml:space="preserve">AVG of facility-level avg_earning_assets_amt per L2 portfolio segment.
 </v>
       </c>
       <c r="W51" t="str">
-        <v>Total Equity amount (portfolio)</v>
+        <v>Average Earning Assets Amount (portfolio)</v>
       </c>
       <c r="X51" t="str">
         <v>Y</v>
@@ -5126,11 +5190,11 @@
         <v>Agg</v>
       </c>
       <c r="Z51" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level allocated_equity_amt per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level avg_earning_assets_amt per L1 business segment segment.
 </v>
       </c>
       <c r="AA51" t="str">
-        <v>Total Equity amount (business_segment)</v>
+        <v>Average Earning Assets Amount (business_segment)</v>
       </c>
       <c r="AB51" t="str">
         <v/>
@@ -5138,17 +5202,17 @@
     </row>
     <row r="52" xml:space="preserve">
       <c r="A52" t="str">
-        <v>EXP-044</v>
+        <v>EXP-045</v>
       </c>
       <c r="B52" t="str" xml:space="preserve">
-        <v xml:space="preserve">Average balance of interest-generating assets over the reporting period.
+        <v xml:space="preserve">Exposure-weighted average regulatory risk weight reflecting capital intensity.
 </v>
       </c>
       <c r="C52" t="str">
-        <v>Average Earning Assets Amount</v>
+        <v>Risk Weighted Average (%)</v>
       </c>
       <c r="D52" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read avg_earning_assets_amt from facility_profitability_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">SUM(RWA Amount)/SUM(Exposure)
 </v>
       </c>
       <c r="E52" t="str">
@@ -5164,66 +5228,66 @@
         <v>Y</v>
       </c>
       <c r="I52" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="J52" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read avg_earning_assets_amt from facility_profitability_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">SUM(RWA Amount)/SUM(Exposure)
 </v>
       </c>
       <c r="K52" t="str">
-        <v>Average Earning Assets Amount (facility)</v>
+        <v>Risk Weighted Average (%) (facility)</v>
       </c>
       <c r="L52" t="str">
         <v>Y</v>
       </c>
       <c r="M52" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="N52" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of avg_earning_assets_amt across counterparty facilities.
+        <v xml:space="preserve">SUM(rwa) / SUM(gross_exposure) * 100.0 per counterparty.
 </v>
       </c>
       <c r="O52" t="str">
-        <v>Average Earning Assets Amount (counterparty)</v>
+        <v>Risk Weighted Average (%) (counterparty)</v>
       </c>
       <c r="P52" t="str">
         <v>Y</v>
       </c>
       <c r="Q52" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R52" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level avg_earning_assets_amt per L3 desk segment.
+        <v xml:space="preserve">SUM(rwa) / SUM(gross_exposure) * 100.0 per L3 desk segment.
 </v>
       </c>
       <c r="S52" t="str">
-        <v>Average Earning Assets Amount (desk)</v>
+        <v>Risk Weighted Average (%) (desk)</v>
       </c>
       <c r="T52" t="str">
         <v>Y</v>
       </c>
       <c r="U52" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="V52" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level avg_earning_assets_amt per L2 portfolio segment.
+        <v xml:space="preserve">SUM(rwa) / SUM(gross_exposure) * 100.0 per L2 portfolio segment.
 </v>
       </c>
       <c r="W52" t="str">
-        <v>Average Earning Assets Amount (portfolio)</v>
+        <v>Risk Weighted Average (%) (portfolio)</v>
       </c>
       <c r="X52" t="str">
         <v>Y</v>
       </c>
       <c r="Y52" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z52" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level avg_earning_assets_amt per L1 business segment segment.
+        <v xml:space="preserve">SUM(rwa) / SUM(gross_exposure) * 100.0 per L1 business segment.
 </v>
       </c>
       <c r="AA52" t="str">
-        <v>Average Earning Assets Amount (business_segment)</v>
+        <v>Risk Weighted Average (%) (business_segment)</v>
       </c>
       <c r="AB52" t="str">
         <v/>
@@ -5231,17 +5295,17 @@
     </row>
     <row r="53" xml:space="preserve">
       <c r="A53" t="str">
-        <v>EXP-045</v>
+        <v>EXP-046</v>
       </c>
       <c r="B53" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average regulatory risk weight reflecting capital intensity.
+        <v xml:space="preserve">Total risk-weighted assets calculated for regulatory capital purposes.
 </v>
       </c>
       <c r="C53" t="str">
-        <v>Risk Weighted Average (%)</v>
+        <v>Risk Weighted Average Amount ($)</v>
       </c>
       <c r="D53" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(RWA Amount)/SUM(Exposure)
+        <v xml:space="preserve">Exposure * Risk Weight %
 </v>
       </c>
       <c r="E53" t="str">
@@ -5260,63 +5324,63 @@
         <v>Calc</v>
       </c>
       <c r="J53" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(RWA Amount)/SUM(Exposure)
+        <v xml:space="preserve">Exposure * Risk Weight %
 </v>
       </c>
       <c r="K53" t="str">
-        <v>Risk Weighted Average (%) (facility)</v>
+        <v>Risk Weighted Average Amount ($) (facility)</v>
       </c>
       <c r="L53" t="str">
         <v>Y</v>
       </c>
       <c r="M53" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="N53" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(rwa) / SUM(gross_exposure) * 100.0 per counterparty.
+        <v xml:space="preserve">SUM of facility-level rwa_amt per counterparty.
 </v>
       </c>
       <c r="O53" t="str">
-        <v>Risk Weighted Average (%) (counterparty)</v>
+        <v>Risk Weighted Average Amount ($) (counterparty)</v>
       </c>
       <c r="P53" t="str">
         <v>Y</v>
       </c>
       <c r="Q53" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="R53" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(rwa) / SUM(gross_exposure) * 100.0 per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level rwa_amt per L3 desk segment.
 </v>
       </c>
       <c r="S53" t="str">
-        <v>Risk Weighted Average (%) (desk)</v>
+        <v>Risk Weighted Average Amount ($) (desk)</v>
       </c>
       <c r="T53" t="str">
         <v>Y</v>
       </c>
       <c r="U53" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="V53" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(rwa) / SUM(gross_exposure) * 100.0 per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level rwa_amt per L2 portfolio segment.
 </v>
       </c>
       <c r="W53" t="str">
-        <v>Risk Weighted Average (%) (portfolio)</v>
+        <v>Risk Weighted Average Amount ($) (portfolio)</v>
       </c>
       <c r="X53" t="str">
         <v>Y</v>
       </c>
       <c r="Y53" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="Z53" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(rwa) / SUM(gross_exposure) * 100.0 per L1 business segment.
+        <v xml:space="preserve">SUM of facility-level rwa_amt per L1 business segment.
 </v>
       </c>
       <c r="AA53" t="str">
-        <v>Risk Weighted Average (%) (business_segment)</v>
+        <v>Risk Weighted Average Amount ($) (business_segment)</v>
       </c>
       <c r="AB53" t="str">
         <v/>
@@ -5324,17 +5388,17 @@
     </row>
     <row r="54" xml:space="preserve">
       <c r="A54" t="str">
-        <v>EXP-046</v>
+        <v>EXP-047</v>
       </c>
       <c r="B54" t="str" xml:space="preserve">
-        <v xml:space="preserve">Total risk-weighted assets calculated for regulatory capital purposes.
+        <v xml:space="preserve">Indicates how well cash flow covers fixed, non-discretionary obligations; highlights ability to withstand earnings volatility and signals potential liquidity stress/default risk.
 </v>
       </c>
       <c r="C54" t="str">
-        <v>Risk Weighted Average Amount ($)</v>
+        <v>Fixed Cost Coverage Ratio (%)</v>
       </c>
       <c r="D54" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure * Risk Weight %
+        <v xml:space="preserve">Read fccr_value from lob_risk_ratio_summary for each facility as-of reporting date.
 </v>
       </c>
       <c r="E54" t="str">
@@ -5350,66 +5414,70 @@
         <v>Y</v>
       </c>
       <c r="I54" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J54" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read fccr_value from lob_risk_ratio_summary for each facility as-of reporting date.
+</v>
+      </c>
+      <c r="K54" t="str">
+        <v>Fixed Cost Coverage Ratio (%) (facility)</v>
+      </c>
+      <c r="L54" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M54" t="str">
         <v>Calc</v>
       </c>
-      <c r="J54" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure * Risk Weight %
-</v>
-      </c>
-      <c r="K54" t="str">
-        <v>Risk Weighted Average Amount ($) (facility)</v>
-      </c>
-      <c r="L54" t="str">
-        <v>Y</v>
-      </c>
-      <c r="M54" t="str">
-        <v>Agg</v>
-      </c>
       <c r="N54" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level rwa_amt per counterparty.
+        <v xml:space="preserve">SUM(ebitda × fx_rate) / SUM(total_debt_service × fx_rate) per counterparty.
+Amounts converted to USD via l2.fx_rate before aggregation.
 </v>
       </c>
       <c r="O54" t="str">
-        <v>Risk Weighted Average Amount ($) (counterparty)</v>
+        <v>Fixed Cost Coverage Ratio (%) (counterparty)</v>
       </c>
       <c r="P54" t="str">
         <v>Y</v>
       </c>
       <c r="Q54" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R54" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level rwa_amt per L3 desk segment.
+        <v xml:space="preserve">SUM(ebitda × fx_rate) / SUM(total_debt_service × fx_rate) per L3 desk segment.
+Amounts converted to USD via l2.fx_rate before aggregation.
 </v>
       </c>
       <c r="S54" t="str">
-        <v>Risk Weighted Average Amount ($) (desk)</v>
+        <v>Fixed Cost Coverage Ratio (%) (desk)</v>
       </c>
       <c r="T54" t="str">
         <v>Y</v>
       </c>
       <c r="U54" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V54" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level rwa_amt per L2 portfolio segment.
+        <v xml:space="preserve">SUM(ebitda × fx_rate) / SUM(total_debt_service × fx_rate) per L2 portfolio segment.
+Amounts converted to USD via l2.fx_rate before aggregation.
 </v>
       </c>
       <c r="W54" t="str">
-        <v>Risk Weighted Average Amount ($) (portfolio)</v>
+        <v>Fixed Cost Coverage Ratio (%) (portfolio)</v>
       </c>
       <c r="X54" t="str">
         <v>Y</v>
       </c>
       <c r="Y54" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z54" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level rwa_amt per L1 business segment.
+        <v xml:space="preserve">SUM(ebitda × fx_rate) / SUM(total_debt_service × fx_rate) per L1 business segment.
+Amounts converted to USD via l2.fx_rate before aggregation.
 </v>
       </c>
       <c r="AA54" t="str">
-        <v>Risk Weighted Average Amount ($) (business_segment)</v>
+        <v>Fixed Cost Coverage Ratio (%) (business_segment)</v>
       </c>
       <c r="AB54" t="str">
         <v/>
@@ -5417,17 +5485,17 @@
     </row>
     <row r="55" xml:space="preserve">
       <c r="A55" t="str">
-        <v>EXP-047</v>
+        <v>EXP-048</v>
       </c>
       <c r="B55" t="str" xml:space="preserve">
-        <v xml:space="preserve">Indicates how well cash flow covers fixed, non-discretionary obligations; highlights ability to withstand earnings volatility and signals potential liquidity stress/default risk.
+        <v xml:space="preserve">Scheduled principal repayment obligation due for the contractual commitment.
 </v>
       </c>
       <c r="C55" t="str">
-        <v>Fixed Cost Coverage Ratio (%)</v>
+        <v>Principal Repayment Amount ($)</v>
       </c>
       <c r="D55" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read fccr_value from lob_risk_ratio_summary for each facility as-of reporting date.
+        <v xml:space="preserve">Read principal_payment_amt from facility_financial_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="E55" t="str">
@@ -5446,67 +5514,63 @@
         <v>Raw</v>
       </c>
       <c r="J55" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read fccr_value from lob_risk_ratio_summary for each facility as-of reporting date.
+        <v xml:space="preserve">Read principal_payment_amt from facility_financial_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="K55" t="str">
-        <v>Fixed Cost Coverage Ratio (%) (facility)</v>
+        <v>Principal Repayment Amount ($) (facility)</v>
       </c>
       <c r="L55" t="str">
         <v>Y</v>
       </c>
       <c r="M55" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="N55" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(ebitda × fx_rate) / SUM(total_debt_service × fx_rate) per counterparty.
-Amounts converted to USD via l2.fx_rate before aggregation.
+        <v xml:space="preserve">SUM(facility-level principal_payment_amt) per counterparty.
 </v>
       </c>
       <c r="O55" t="str">
-        <v>Fixed Cost Coverage Ratio (%) (counterparty)</v>
+        <v>Principal Repayment Amount ($) (counterparty)</v>
       </c>
       <c r="P55" t="str">
         <v>Y</v>
       </c>
       <c r="Q55" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="R55" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(ebitda × fx_rate) / SUM(total_debt_service × fx_rate) per L3 desk segment.
-Amounts converted to USD via l2.fx_rate before aggregation.
+        <v xml:space="preserve">SUM of facility-level principal_payment_amt per L3 desk segment.
 </v>
       </c>
       <c r="S55" t="str">
-        <v>Fixed Cost Coverage Ratio (%) (desk)</v>
+        <v>Principal Repayment Amount ($) (desk)</v>
       </c>
       <c r="T55" t="str">
         <v>Y</v>
       </c>
       <c r="U55" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="V55" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(ebitda × fx_rate) / SUM(total_debt_service × fx_rate) per L2 portfolio segment.
-Amounts converted to USD via l2.fx_rate before aggregation.
+        <v xml:space="preserve">SUM of facility-level principal_payment_amt per L2 portfolio segment.
 </v>
       </c>
       <c r="W55" t="str">
-        <v>Fixed Cost Coverage Ratio (%) (portfolio)</v>
+        <v>Principal Repayment Amount ($) (portfolio)</v>
       </c>
       <c r="X55" t="str">
         <v>Y</v>
       </c>
       <c r="Y55" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="Z55" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(ebitda × fx_rate) / SUM(total_debt_service × fx_rate) per L1 business segment.
-Amounts converted to USD via l2.fx_rate before aggregation.
+        <v xml:space="preserve">SUM of facility-level principal_payment_amt per L1 business segment segment.
 </v>
       </c>
       <c r="AA55" t="str">
-        <v>Fixed Cost Coverage Ratio (%) (business_segment)</v>
+        <v>Principal Repayment Amount ($) (business_segment)</v>
       </c>
       <c r="AB55" t="str">
         <v/>
@@ -5514,17 +5578,17 @@
     </row>
     <row r="56" xml:space="preserve">
       <c r="A56" t="str">
-        <v>EXP-048</v>
+        <v>PRC-001</v>
       </c>
       <c r="B56" t="str" xml:space="preserve">
-        <v xml:space="preserve">Scheduled principal repayment obligation due for the contractual commitment.
+        <v xml:space="preserve">Total effective interest rate including base rate and spread. Calculated pricing KPI that provides insight into total yield generation and supports risk-adjusted return analysis.
 </v>
       </c>
       <c r="C56" t="str">
-        <v>Principal Repayment Amount ($)</v>
+        <v>All in Rate (%)</v>
       </c>
       <c r="D56" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read principal_payment_amt from facility_financial_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Read all_in_rate_pct from facility_pricing_snapshot for each facility.
 </v>
       </c>
       <c r="E56" t="str">
@@ -5543,63 +5607,63 @@
         <v>Raw</v>
       </c>
       <c r="J56" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read principal_payment_amt from facility_financial_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Read all_in_rate_pct from facility_pricing_snapshot for each facility.
 </v>
       </c>
       <c r="K56" t="str">
-        <v>Principal Repayment Amount ($) (facility)</v>
+        <v>All in Rate (%) (facility)</v>
       </c>
       <c r="L56" t="str">
         <v>Y</v>
       </c>
       <c r="M56" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="N56" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level principal_payment_amt) per counterparty.
+        <v xml:space="preserve">For each Counterparty_ID, lookup Facility_IDs in Facility Master where IS(Counterparty_ID), SELECT all_in_rate_pct. Weight by FX-converted bank share committed amount (committed_amount * bank_share_pct * fx_rate). Weighted average = SUM(rate * weight) / SUM(weight).
 </v>
       </c>
       <c r="O56" t="str">
-        <v>Principal Repayment Amount ($) (counterparty)</v>
+        <v>All in Rate (%) (counterparty)</v>
       </c>
       <c r="P56" t="str">
         <v>Y</v>
       </c>
       <c r="Q56" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="R56" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level principal_payment_amt per L3 desk segment.
+        <v xml:space="preserve">For each L3 LoB, lookup lob_segment_id from enterprise_business_taxonomy, then lookup facility_id in Facility Master where IS(lob_segment_id). SELECT all_in_rate_pct, weight by FX-converted bank share committed exposure (committed_amount * bank_share_pct * fx_rate). Weighted average = SUM(rate * weight) / SUM(weight).
 </v>
       </c>
       <c r="S56" t="str">
-        <v>Principal Repayment Amount ($) (desk)</v>
+        <v>All in Rate (%) (desk)</v>
       </c>
       <c r="T56" t="str">
         <v>Y</v>
       </c>
       <c r="U56" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V56" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level principal_payment_amt per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 LoB, lookup lob_segment_id from enterprise_business_taxonomy, then lookup facility_id in Facility Master where IS(lob_segment_id). SELECT all_in_rate_pct, weight by FX-converted bank share committed exposure (committed_amount * bank_share_pct * fx_rate). Calculated = SUM(rate * weight) / SUM(weight).
 </v>
       </c>
       <c r="W56" t="str">
-        <v>Principal Repayment Amount ($) (portfolio)</v>
+        <v>All in Rate (%) (portfolio)</v>
       </c>
       <c r="X56" t="str">
         <v>Y</v>
       </c>
       <c r="Y56" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z56" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level principal_payment_amt per L1 business segment segment.
+        <v xml:space="preserve">For each L1 LoB, lookup lob_segment_id from enterprise_business_taxonomy, then lookup facility_id in Facility Master where IS(lob_segment_id). SELECT all_in_rate_pct, weight by FX-converted bank share committed exposure (committed_amount * bank_share_pct * fx_rate). Calculated = SUM(rate * weight) / SUM(weight).
 </v>
       </c>
       <c r="AA56" t="str">
-        <v>Principal Repayment Amount ($) (business_segment)</v>
+        <v>All in Rate (%) (business_segment)</v>
       </c>
       <c r="AB56" t="str">
         <v/>
@@ -5607,17 +5671,17 @@
     </row>
     <row r="57" xml:space="preserve">
       <c r="A57" t="str">
-        <v>PRC-001</v>
+        <v>PRC-002</v>
       </c>
       <c r="B57" t="str" xml:space="preserve">
-        <v xml:space="preserve">Total effective interest rate including base rate and spread. Calculated pricing KPI that provides insight into total yield generation and supports risk-adjusted return analysis.
+        <v xml:space="preserve">Reference benchmark interest rate applicable to the exposure (e.g., SOFR, Prime). Forms base component of total facility pricing. At facility level, reads the raw base_rate_pct from the pricing snapshot. At counterparty and higher levels, computes an exposure-weighted average using committed exposure amounts to reflect portfolio-level rate exposure.
 </v>
       </c>
       <c r="C57" t="str">
-        <v>All in Rate (%)</v>
+        <v>Base Interest Rate (%)</v>
       </c>
       <c r="D57" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read all_in_rate_pct from facility_pricing_snapshot for each facility.
+        <v xml:space="preserve">Raw base_rate_pct from facility_pricing_snapshot for each active facility.
 </v>
       </c>
       <c r="E57" t="str">
@@ -5636,11 +5700,11 @@
         <v>Raw</v>
       </c>
       <c r="J57" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read all_in_rate_pct from facility_pricing_snapshot for each facility.
+        <v xml:space="preserve">Raw base_rate_pct from facility_pricing_snapshot for each active facility.
 </v>
       </c>
       <c r="K57" t="str">
-        <v>All in Rate (%) (facility)</v>
+        <v>Base Interest Rate (%) (facility)</v>
       </c>
       <c r="L57" t="str">
         <v>Y</v>
@@ -5649,11 +5713,11 @@
         <v>Avg</v>
       </c>
       <c r="N57" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Counterparty_ID, lookup Facility_IDs in Facility Master where IS(Counterparty_ID), SELECT all_in_rate_pct. Weight by FX-converted bank share committed amount (committed_amount * bank_share_pct * fx_rate). Weighted average = SUM(rate * weight) / SUM(weight).
+        <v xml:space="preserve">Exposure-weighted average of base_rate_pct across counterparty facilities. Weight = committed_amount * bank_share_pct / 100 (bank's pro-rata committed exposure). Formula: SUM(base_rate_pct * bank_adj_committed) / SUM(bank_adj_committed).
 </v>
       </c>
       <c r="O57" t="str">
-        <v>All in Rate (%) (counterparty)</v>
+        <v>Base Interest Rate (%) (counterparty)</v>
       </c>
       <c r="P57" t="str">
         <v>Y</v>
@@ -5662,37 +5726,37 @@
         <v>Avg</v>
       </c>
       <c r="R57" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each L3 LoB, lookup lob_segment_id from enterprise_business_taxonomy, then lookup facility_id in Facility Master where IS(lob_segment_id). SELECT all_in_rate_pct, weight by FX-converted bank share committed exposure (committed_amount * bank_share_pct * fx_rate). Weighted average = SUM(rate * weight) / SUM(weight).
+        <v xml:space="preserve">Exposure-weighted average of base_rate_pct per L3 desk segment. Weight = committed_amount * bank_share_pct / 100 (bank's pro-rata committed exposure).
 </v>
       </c>
       <c r="S57" t="str">
-        <v>All in Rate (%) (desk)</v>
+        <v>Base Interest Rate (%) (desk)</v>
       </c>
       <c r="T57" t="str">
         <v>Y</v>
       </c>
       <c r="U57" t="str">
-        <v>Calc</v>
+        <v>Avg</v>
       </c>
       <c r="V57" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each L2 LoB, lookup lob_segment_id from enterprise_business_taxonomy, then lookup facility_id in Facility Master where IS(lob_segment_id). SELECT all_in_rate_pct, weight by FX-converted bank share committed exposure (committed_amount * bank_share_pct * fx_rate). Calculated = SUM(rate * weight) / SUM(weight).
+        <v xml:space="preserve">Exposure-weighted average of base_rate_pct per L2 portfolio segment. Weight = committed_amount * bank_share_pct / 100 (bank's pro-rata committed exposure).
 </v>
       </c>
       <c r="W57" t="str">
-        <v>All in Rate (%) (portfolio)</v>
+        <v>Base Interest Rate (%) (portfolio)</v>
       </c>
       <c r="X57" t="str">
         <v>Y</v>
       </c>
       <c r="Y57" t="str">
-        <v>Calc</v>
+        <v>Avg</v>
       </c>
       <c r="Z57" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each L1 LoB, lookup lob_segment_id from enterprise_business_taxonomy, then lookup facility_id in Facility Master where IS(lob_segment_id). SELECT all_in_rate_pct, weight by FX-converted bank share committed exposure (committed_amount * bank_share_pct * fx_rate). Calculated = SUM(rate * weight) / SUM(weight).
+        <v xml:space="preserve">Exposure-weighted average of base_rate_pct per L1 business segment. Weight = committed_amount * bank_share_pct / 100 (bank's pro-rata committed exposure).
 </v>
       </c>
       <c r="AA57" t="str">
-        <v>All in Rate (%) (business_segment)</v>
+        <v>Base Interest Rate (%) (business_segment)</v>
       </c>
       <c r="AB57" t="str">
         <v/>
@@ -5700,17 +5764,18 @@
     </row>
     <row r="58" xml:space="preserve">
       <c r="A58" t="str">
-        <v>PRC-002</v>
+        <v>PRC-003</v>
       </c>
       <c r="B58" t="str" xml:space="preserve">
-        <v xml:space="preserve">Reference benchmark interest rate applicable to the exposure (e.g., SOFR, Prime). Forms base component of total facility pricing. At facility level, reads the raw base_rate_pct from the pricing snapshot. At counterparty and higher levels, computes an exposure-weighted average using committed exposure amounts to reflect portfolio-level rate exposure.
+        <v xml:space="preserve">Percentage of facilities with approved pricing or policy exceptions. Computed as COUNT(exception facilities) / COUNT(total facilities) × 100. Sourced from L2 facility_pricing_snapshot — the atomic pricing record — using the is_pricing_exception_flag. At aggregate levels, uses count-ratio rollup: re-counts exceptions and totals across all constituent facilities, never averages pre-computed rates. Key governance KPI measuring policy discipline, risk culture strength, and pricing override frequency.
 </v>
       </c>
       <c r="C58" t="str">
-        <v>Base Interest Rate (%)</v>
+        <v>Exception Rate (%)</v>
       </c>
       <c r="D58" t="str" xml:space="preserve">
-        <v xml:space="preserve">Raw base_rate_pct from facility_pricing_snapshot for each active facility.
+        <v xml:space="preserve">Binary flag: 1.0 if pricing exception approved, 0.0 otherwise.
+Ingredients: is_pricing_exception_flag (L2 facility_pricing_snapshot)
 </v>
       </c>
       <c r="E58" t="str">
@@ -5726,66 +5791,79 @@
         <v>Y</v>
       </c>
       <c r="I58" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="J58" t="str" xml:space="preserve">
-        <v xml:space="preserve">Raw base_rate_pct from facility_pricing_snapshot for each active facility.
+        <v xml:space="preserve">Binary flag: 1.0 if pricing exception approved, 0.0 otherwise.
+Ingredients: is_pricing_exception_flag (L2 facility_pricing_snapshot)
 </v>
       </c>
       <c r="K58" t="str">
-        <v>Base Interest Rate (%) (facility)</v>
+        <v>Exception Rate (%) (facility)</v>
       </c>
       <c r="L58" t="str">
         <v>Y</v>
       </c>
       <c r="M58" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="N58" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of base_rate_pct across counterparty facilities. Weight = committed_amount * bank_share_pct / 100 (bank's pro-rata committed exposure). Formula: SUM(base_rate_pct * bank_adj_committed) / SUM(bank_adj_committed).
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD is_pricing_exception_flag for all facilities of this counterparty
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup: re-counts from facility-level flags.
 </v>
       </c>
       <c r="O58" t="str">
-        <v>Base Interest Rate (%) (counterparty)</v>
+        <v>Exception Rate (%) (counterparty)</v>
       </c>
       <c r="P58" t="str">
         <v>Y</v>
       </c>
       <c r="Q58" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="R58" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of base_rate_pct per L3 desk segment. Weight = committed_amount * bank_share_pct / 100 (bank's pro-rata committed exposure).
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOOKUP managed_segment_id from enterprise_business_taxonomy
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup per desk.
 </v>
       </c>
       <c r="S58" t="str">
-        <v>Base Interest Rate (%) (desk)</v>
+        <v>Exception Rate (%) (desk)</v>
       </c>
       <c r="T58" t="str">
         <v>Y</v>
       </c>
       <c r="U58" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="V58" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of base_rate_pct per L2 portfolio segment. Weight = committed_amount * bank_share_pct / 100 (bank's pro-rata committed exposure).
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup per portfolio.
 </v>
       </c>
       <c r="W58" t="str">
-        <v>Base Interest Rate (%) (portfolio)</v>
+        <v>Exception Rate (%) (portfolio)</v>
       </c>
       <c r="X58" t="str">
         <v>Y</v>
       </c>
       <c r="Y58" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="Z58" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of base_rate_pct per L1 business segment. Weight = committed_amount * bank_share_pct / 100 (bank's pro-rata committed exposure).
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup per business segment.
 </v>
       </c>
       <c r="AA58" t="str">
-        <v>Base Interest Rate (%) (business_segment)</v>
+        <v>Exception Rate (%) (business_segment)</v>
       </c>
       <c r="AB58" t="str">
         <v/>
@@ -5793,17 +5871,17 @@
     </row>
     <row r="59" xml:space="preserve">
       <c r="A59" t="str">
-        <v>PRC-003</v>
+        <v>PRC-004</v>
       </c>
       <c r="B59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of exposures within portfolio with approved pricing or policy exceptions. Derived governance KPI measuring policy discipline and risk culture strength.
+        <v xml:space="preserve">Fee percentage applied to committed or undrawn exposure. Calculated KPI supporting pricing adequacy and revenue optimization analysis.
 </v>
       </c>
       <c r="C59" t="str">
-        <v>Exception Rate (%)</v>
+        <v>Fee Rate (%)</v>
       </c>
       <c r="D59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if pricing exception, 0 otherwise.
+        <v xml:space="preserve">Fee Income / Average Balance
 </v>
       </c>
       <c r="E59" t="str">
@@ -5822,63 +5900,63 @@
         <v>Calc</v>
       </c>
       <c r="J59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if pricing exception, 0 otherwise.
+        <v xml:space="preserve">Fee Income / Average Balance
 </v>
       </c>
       <c r="K59" t="str">
-        <v>Exception Rate (%) (facility)</v>
+        <v>Fee Rate (%) (facility)</v>
       </c>
       <c r="L59" t="str">
         <v>Y</v>
       </c>
       <c r="M59" t="str">
-        <v>Calc</v>
+        <v>Avg</v>
       </c>
       <c r="N59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with pricing exception per counterparty.
+        <v xml:space="preserve">Exposure-weighted average of fee_rate_pct across counterparty facilities.
 </v>
       </c>
       <c r="O59" t="str">
-        <v>Exception Rate (%) (counterparty)</v>
+        <v>Fee Rate (%) (counterparty)</v>
       </c>
       <c r="P59" t="str">
         <v>Y</v>
       </c>
       <c r="Q59" t="str">
-        <v>Calc</v>
+        <v>Avg</v>
       </c>
       <c r="R59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with pricing exception per L3 desk.
+        <v xml:space="preserve">AVG of facility-level fee_rate_pct per L3 desk segment.
 </v>
       </c>
       <c r="S59" t="str">
-        <v>Exception Rate (%) (desk)</v>
+        <v>Fee Rate (%) (desk)</v>
       </c>
       <c r="T59" t="str">
         <v>Y</v>
       </c>
       <c r="U59" t="str">
-        <v>Calc</v>
+        <v>Avg</v>
       </c>
       <c r="V59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with pricing exception per L2 portfolio.
+        <v xml:space="preserve">AVG of facility-level fee_rate_pct per L2 portfolio segment.
 </v>
       </c>
       <c r="W59" t="str">
-        <v>Exception Rate (%) (portfolio)</v>
+        <v>Fee Rate (%) (portfolio)</v>
       </c>
       <c r="X59" t="str">
         <v>Y</v>
       </c>
       <c r="Y59" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="Z59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with pricing exception per L1 business segment.
+        <v xml:space="preserve">SUM of facility-level fee_rate_pct per L1 business segment segment.
 </v>
       </c>
       <c r="AA59" t="str">
-        <v>Exception Rate (%) (business_segment)</v>
+        <v>Fee Rate (%) (business_segment)</v>
       </c>
       <c r="AB59" t="str">
         <v/>
@@ -5886,17 +5964,17 @@
     </row>
     <row r="60" xml:space="preserve">
       <c r="A60" t="str">
-        <v>PRC-004</v>
+        <v>PRC-005</v>
       </c>
       <c r="B60" t="str" xml:space="preserve">
-        <v xml:space="preserve">Fee percentage applied to committed or undrawn exposure. Calculated KPI supporting pricing adequacy and revenue optimization analysis.
+        <v xml:space="preserve">Indicator identifying exposures priced outside standard policy guidelines. Supports governance discipline and pricing compliance monitoring.
 </v>
       </c>
       <c r="C60" t="str">
-        <v>Fee Rate (%)</v>
+        <v>Pricing Exception Status</v>
       </c>
       <c r="D60" t="str" xml:space="preserve">
-        <v xml:space="preserve">Fee Income / Average Balance
+        <v xml:space="preserve">Binary flag: 1 if pricing exception exists, 0 otherwise.
 </v>
       </c>
       <c r="E60" t="str">
@@ -5915,50 +5993,50 @@
         <v>Calc</v>
       </c>
       <c r="J60" t="str" xml:space="preserve">
-        <v xml:space="preserve">Fee Income / Average Balance
+        <v xml:space="preserve">Binary flag: 1 if pricing exception exists, 0 otherwise.
 </v>
       </c>
       <c r="K60" t="str">
-        <v>Fee Rate (%) (facility)</v>
+        <v>Pricing Exception Status (facility)</v>
       </c>
       <c r="L60" t="str">
         <v>Y</v>
       </c>
       <c r="M60" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="N60" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of fee_rate_pct across counterparty facilities.
+        <v xml:space="preserve">COUNT of facilities with pricing exception per counterparty.
 </v>
       </c>
       <c r="O60" t="str">
-        <v>Fee Rate (%) (counterparty)</v>
+        <v>Pricing Exception Status (counterparty)</v>
       </c>
       <c r="P60" t="str">
         <v>Y</v>
       </c>
       <c r="Q60" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="R60" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level fee_rate_pct per L3 desk segment.
+        <v xml:space="preserve">COUNT of facilities with pricing exception per L3 desk segment.
 </v>
       </c>
       <c r="S60" t="str">
-        <v>Fee Rate (%) (desk)</v>
+        <v>Pricing Exception Status (desk)</v>
       </c>
       <c r="T60" t="str">
         <v>Y</v>
       </c>
       <c r="U60" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="V60" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level fee_rate_pct per L2 portfolio segment.
+        <v xml:space="preserve">COUNT of facilities with pricing exception per L2 portfolio segment.
 </v>
       </c>
       <c r="W60" t="str">
-        <v>Fee Rate (%) (portfolio)</v>
+        <v>Pricing Exception Status (portfolio)</v>
       </c>
       <c r="X60" t="str">
         <v>Y</v>
@@ -5967,11 +6045,11 @@
         <v>Agg</v>
       </c>
       <c r="Z60" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level fee_rate_pct per L1 business segment segment.
+        <v xml:space="preserve">COUNT of facilities with pricing exception per L1 business segment.
 </v>
       </c>
       <c r="AA60" t="str">
-        <v>Fee Rate (%) (business_segment)</v>
+        <v>Pricing Exception Status (business_segment)</v>
       </c>
       <c r="AB60" t="str">
         <v/>
@@ -5979,17 +6057,17 @@
     </row>
     <row r="61" xml:space="preserve">
       <c r="A61" t="str">
-        <v>PRC-005</v>
+        <v>PRC-006</v>
       </c>
       <c r="B61" t="str" xml:space="preserve">
-        <v xml:space="preserve">Indicator identifying exposures priced outside standard policy guidelines. Supports governance discipline and pricing compliance monitoring.
+        <v xml:space="preserve">Pricing classification tier assigned to facility. Supports structured pricing strategy and yield segmentation.
 </v>
       </c>
       <c r="C61" t="str">
-        <v>Pricing Exception Status</v>
+        <v>Pricing Tier</v>
       </c>
       <c r="D61" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if pricing exception exists, 0 otherwise.
+        <v xml:space="preserve">Read pricing_tier_code from facility_detail_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="E61" t="str">
@@ -6005,27 +6083,27 @@
         <v>Y</v>
       </c>
       <c r="I61" t="str">
-        <v>Calc</v>
+        <v>Raw</v>
       </c>
       <c r="J61" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if pricing exception exists, 0 otherwise.
+        <v xml:space="preserve">Read pricing_tier_code from facility_detail_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="K61" t="str">
-        <v>Pricing Exception Status (facility)</v>
+        <v>Pricing Tier (facility)</v>
       </c>
       <c r="L61" t="str">
         <v>Y</v>
       </c>
       <c r="M61" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="N61" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with pricing exception per counterparty.
+        <v xml:space="preserve">Read pricing_tier_code per counterparty.
 </v>
       </c>
       <c r="O61" t="str">
-        <v>Pricing Exception Status (counterparty)</v>
+        <v>Pricing Tier (counterparty)</v>
       </c>
       <c r="P61" t="str">
         <v>Y</v>
@@ -6034,11 +6112,11 @@
         <v>Agg</v>
       </c>
       <c r="R61" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with pricing exception per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level pricing_tier_code per L3 desk segment.
 </v>
       </c>
       <c r="S61" t="str">
-        <v>Pricing Exception Status (desk)</v>
+        <v>Pricing Tier (desk)</v>
       </c>
       <c r="T61" t="str">
         <v>Y</v>
@@ -6047,11 +6125,11 @@
         <v>Agg</v>
       </c>
       <c r="V61" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with pricing exception per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level pricing_tier_code per L2 portfolio segment.
 </v>
       </c>
       <c r="W61" t="str">
-        <v>Pricing Exception Status (portfolio)</v>
+        <v>Pricing Tier (portfolio)</v>
       </c>
       <c r="X61" t="str">
         <v>Y</v>
@@ -6060,11 +6138,11 @@
         <v>Agg</v>
       </c>
       <c r="Z61" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with pricing exception per L1 business segment.
+        <v xml:space="preserve">SUM of facility-level pricing_tier_code per L1 business segment segment.
 </v>
       </c>
       <c r="AA61" t="str">
-        <v>Pricing Exception Status (business_segment)</v>
+        <v>Pricing Tier (business_segment)</v>
       </c>
       <c r="AB61" t="str">
         <v/>
@@ -6072,17 +6150,17 @@
     </row>
     <row r="62" xml:space="preserve">
       <c r="A62" t="str">
-        <v>PRC-006</v>
+        <v>PRC-007</v>
       </c>
       <c r="B62" t="str" xml:space="preserve">
-        <v xml:space="preserve">Pricing classification tier assigned to facility. Supports structured pricing strategy and yield segmentation.
+        <v xml:space="preserve">Credit spread over reference base rate charged on exposure, expressed as percentage. Represents risk premium embedded in pricing and supports yield analysis.
 </v>
       </c>
       <c r="C62" t="str">
-        <v>Pricing Tier</v>
+        <v>Interest Rate Spread (%)</v>
       </c>
       <c r="D62" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read pricing_tier_code from facility_detail_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Facility Asset Spread/ Total Outstanding Balance
 </v>
       </c>
       <c r="E62" t="str">
@@ -6098,53 +6176,53 @@
         <v>Y</v>
       </c>
       <c r="I62" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="J62" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read pricing_tier_code from facility_detail_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Facility Asset Spread/ Total Outstanding Balance
 </v>
       </c>
       <c r="K62" t="str">
-        <v>Pricing Tier (facility)</v>
+        <v>Interest Rate Spread (%) (facility)</v>
       </c>
       <c r="L62" t="str">
         <v>Y</v>
       </c>
       <c r="M62" t="str">
-        <v>Raw</v>
+        <v>Avg</v>
       </c>
       <c r="N62" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read pricing_tier_code per counterparty.
+        <v xml:space="preserve">Exposure-weighted average of interest_rate_spread_bps across counterparty facilities.
 </v>
       </c>
       <c r="O62" t="str">
-        <v>Pricing Tier (counterparty)</v>
+        <v>Interest Rate Spread (%) (counterparty)</v>
       </c>
       <c r="P62" t="str">
         <v>Y</v>
       </c>
       <c r="Q62" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="R62" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pricing_tier_code per L3 desk segment.
+        <v xml:space="preserve">AVG of facility-level interest_rate_spread_bps per L3 desk segment.
 </v>
       </c>
       <c r="S62" t="str">
-        <v>Pricing Tier (desk)</v>
+        <v>Interest Rate Spread (%) (desk)</v>
       </c>
       <c r="T62" t="str">
         <v>Y</v>
       </c>
       <c r="U62" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="V62" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pricing_tier_code per L2 portfolio segment.
+        <v xml:space="preserve">AVG of facility-level interest_rate_spread_bps per L2 portfolio segment.
 </v>
       </c>
       <c r="W62" t="str">
-        <v>Pricing Tier (portfolio)</v>
+        <v>Interest Rate Spread (%) (portfolio)</v>
       </c>
       <c r="X62" t="str">
         <v>Y</v>
@@ -6153,11 +6231,11 @@
         <v>Agg</v>
       </c>
       <c r="Z62" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pricing_tier_code per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level interest_rate_spread_bps per L1 business segment segment.
 </v>
       </c>
       <c r="AA62" t="str">
-        <v>Pricing Tier (business_segment)</v>
+        <v>Interest Rate Spread (%) (business_segment)</v>
       </c>
       <c r="AB62" t="str">
         <v/>
@@ -6165,17 +6243,17 @@
     </row>
     <row r="63" xml:space="preserve">
       <c r="A63" t="str">
-        <v>PRC-007</v>
+        <v>PRC-008</v>
       </c>
       <c r="B63" t="str" xml:space="preserve">
-        <v xml:space="preserve">Credit spread over reference base rate charged on exposure, expressed as percentage. Represents risk premium embedded in pricing and supports yield analysis.
+        <v xml:space="preserve">Measures exposure of earnings/cash flow to interest rate changes; shows vulnerability to rate shocks and informs hedging/pricing and stress-test outcomes.
 </v>
       </c>
       <c r="C63" t="str">
-        <v>Interest Rate Spread (%)</v>
+        <v>Interest Rate Sensitivity (%)</v>
       </c>
       <c r="D63" t="str" xml:space="preserve">
-        <v xml:space="preserve">Facility Asset Spread/ Total Outstanding Balance
+        <v xml:space="preserve">Read interest_rate_sensitivity_pct from facility_financial_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="E63" t="str">
@@ -6191,53 +6269,53 @@
         <v>Y</v>
       </c>
       <c r="I63" t="str">
-        <v>Calc</v>
+        <v>Raw</v>
       </c>
       <c r="J63" t="str" xml:space="preserve">
-        <v xml:space="preserve">Facility Asset Spread/ Total Outstanding Balance
+        <v xml:space="preserve">Read interest_rate_sensitivity_pct from facility_financial_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="K63" t="str">
-        <v>Interest Rate Spread (%) (facility)</v>
+        <v>Interest Rate Sensitivity (%) (facility)</v>
       </c>
       <c r="L63" t="str">
         <v>Y</v>
       </c>
       <c r="M63" t="str">
-        <v>Avg</v>
+        <v>Raw</v>
       </c>
       <c r="N63" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of interest_rate_spread_bps across counterparty facilities.
+        <v xml:space="preserve">Read interest_rate_sensitivity_pct per counterparty.
 </v>
       </c>
       <c r="O63" t="str">
-        <v>Interest Rate Spread (%) (counterparty)</v>
+        <v>Interest Rate Sensitivity (%) (counterparty)</v>
       </c>
       <c r="P63" t="str">
         <v>Y</v>
       </c>
       <c r="Q63" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="R63" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level interest_rate_spread_bps per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level interest_rate_sensitivity_pct per L3 desk segment.
 </v>
       </c>
       <c r="S63" t="str">
-        <v>Interest Rate Spread (%) (desk)</v>
+        <v>Interest Rate Sensitivity (%) (desk)</v>
       </c>
       <c r="T63" t="str">
         <v>Y</v>
       </c>
       <c r="U63" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="V63" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level interest_rate_spread_bps per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level interest_rate_sensitivity_pct per L2 portfolio segment.
 </v>
       </c>
       <c r="W63" t="str">
-        <v>Interest Rate Spread (%) (portfolio)</v>
+        <v>Interest Rate Sensitivity (%) (portfolio)</v>
       </c>
       <c r="X63" t="str">
         <v>Y</v>
@@ -6246,11 +6324,11 @@
         <v>Agg</v>
       </c>
       <c r="Z63" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level interest_rate_spread_bps per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level interest_rate_sensitivity_pct per L1 business segment segment.
 </v>
       </c>
       <c r="AA63" t="str">
-        <v>Interest Rate Spread (%) (business_segment)</v>
+        <v>Interest Rate Sensitivity (%) (business_segment)</v>
       </c>
       <c r="AB63" t="str">
         <v/>
@@ -6258,17 +6336,17 @@
     </row>
     <row r="64" xml:space="preserve">
       <c r="A64" t="str">
-        <v>PRC-008</v>
+        <v>PRC-009</v>
       </c>
       <c r="B64" t="str" xml:space="preserve">
-        <v xml:space="preserve">Measures exposure of earnings/cash flow to interest rate changes; shows vulnerability to rate shocks and informs hedging/pricing and stress-test outcomes.
+        <v xml:space="preserve">Boolean indicator identifying whether the exposure was approved outside standard pricing policy thresholds at origination or amendment.
 </v>
       </c>
       <c r="C64" t="str">
-        <v>Interest Rate Sensitivity (%)</v>
+        <v>Pricing Exception Flag (Y/N)</v>
       </c>
       <c r="D64" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read interest_rate_sensitivity_pct from facility_financial_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Calculated pricing_exception_flag per facility.
 </v>
       </c>
       <c r="E64" t="str">
@@ -6284,27 +6362,27 @@
         <v>Y</v>
       </c>
       <c r="I64" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="J64" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read interest_rate_sensitivity_pct from facility_financial_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Calculated pricing_exception_flag per facility.
 </v>
       </c>
       <c r="K64" t="str">
-        <v>Interest Rate Sensitivity (%) (facility)</v>
+        <v>Pricing Exception Flag (Y/N) (facility)</v>
       </c>
       <c r="L64" t="str">
         <v>Y</v>
       </c>
       <c r="M64" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="N64" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read interest_rate_sensitivity_pct per counterparty.
+        <v xml:space="preserve">SUM of facility-level pricing_exception_flag per counterparty.
 </v>
       </c>
       <c r="O64" t="str">
-        <v>Interest Rate Sensitivity (%) (counterparty)</v>
+        <v>Pricing Exception Flag (Y/N) (counterparty)</v>
       </c>
       <c r="P64" t="str">
         <v>Y</v>
@@ -6313,11 +6391,11 @@
         <v>Agg</v>
       </c>
       <c r="R64" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level interest_rate_sensitivity_pct per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level pricing_exception_flag per L3 desk segment.
 </v>
       </c>
       <c r="S64" t="str">
-        <v>Interest Rate Sensitivity (%) (desk)</v>
+        <v>Pricing Exception Flag (Y/N) (desk)</v>
       </c>
       <c r="T64" t="str">
         <v>Y</v>
@@ -6326,11 +6404,11 @@
         <v>Agg</v>
       </c>
       <c r="V64" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level interest_rate_sensitivity_pct per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level pricing_exception_flag per L2 portfolio segment.
 </v>
       </c>
       <c r="W64" t="str">
-        <v>Interest Rate Sensitivity (%) (portfolio)</v>
+        <v>Pricing Exception Flag (Y/N) (portfolio)</v>
       </c>
       <c r="X64" t="str">
         <v>Y</v>
@@ -6339,11 +6417,11 @@
         <v>Agg</v>
       </c>
       <c r="Z64" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level interest_rate_sensitivity_pct per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level pricing_exception_flag per L1 business segment segment.
 </v>
       </c>
       <c r="AA64" t="str">
-        <v>Interest Rate Sensitivity (%) (business_segment)</v>
+        <v>Pricing Exception Flag (Y/N) (business_segment)</v>
       </c>
       <c r="AB64" t="str">
         <v/>
@@ -6351,109 +6429,16 @@
     </row>
     <row r="65" xml:space="preserve">
       <c r="A65" t="str">
-        <v>PRC-009</v>
+        <v>PROF-108</v>
       </c>
       <c r="B65" t="str" xml:space="preserve">
-        <v xml:space="preserve">Boolean indicator identifying whether the exposure was approved outside standard pricing policy thresholds at origination or amendment.
+        <v xml:space="preserve">Annualized interest cost on drawn/funded exposure. Computed as SUM(funded_amount) * bank_share_pct * cost_of_funds_pct at facility level. Uses funded basis (actual drawn amounts from position_detail) rather than committed basis, aligning with FR Y-9C Schedule HI Item 2.
 </v>
       </c>
       <c r="C65" t="str">
-        <v>Pricing Exception Flag (Y/N)</v>
+        <v>Interest Expense</v>
       </c>
       <c r="D65" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated pricing_exception_flag per facility.
-</v>
-      </c>
-      <c r="E65" t="str">
-        <v/>
-      </c>
-      <c r="F65" t="str">
-        <v/>
-      </c>
-      <c r="G65" t="str">
-        <v/>
-      </c>
-      <c r="H65" t="str">
-        <v>Y</v>
-      </c>
-      <c r="I65" t="str">
-        <v>Calc</v>
-      </c>
-      <c r="J65" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated pricing_exception_flag per facility.
-</v>
-      </c>
-      <c r="K65" t="str">
-        <v>Pricing Exception Flag (Y/N) (facility)</v>
-      </c>
-      <c r="L65" t="str">
-        <v>Y</v>
-      </c>
-      <c r="M65" t="str">
-        <v>Agg</v>
-      </c>
-      <c r="N65" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pricing_exception_flag per counterparty.
-</v>
-      </c>
-      <c r="O65" t="str">
-        <v>Pricing Exception Flag (Y/N) (counterparty)</v>
-      </c>
-      <c r="P65" t="str">
-        <v>Y</v>
-      </c>
-      <c r="Q65" t="str">
-        <v>Agg</v>
-      </c>
-      <c r="R65" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pricing_exception_flag per L3 desk segment.
-</v>
-      </c>
-      <c r="S65" t="str">
-        <v>Pricing Exception Flag (Y/N) (desk)</v>
-      </c>
-      <c r="T65" t="str">
-        <v>Y</v>
-      </c>
-      <c r="U65" t="str">
-        <v>Agg</v>
-      </c>
-      <c r="V65" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pricing_exception_flag per L2 portfolio segment.
-</v>
-      </c>
-      <c r="W65" t="str">
-        <v>Pricing Exception Flag (Y/N) (portfolio)</v>
-      </c>
-      <c r="X65" t="str">
-        <v>Y</v>
-      </c>
-      <c r="Y65" t="str">
-        <v>Agg</v>
-      </c>
-      <c r="Z65" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pricing_exception_flag per L1 business segment segment.
-</v>
-      </c>
-      <c r="AA65" t="str">
-        <v>Pricing Exception Flag (Y/N) (business_segment)</v>
-      </c>
-      <c r="AB65" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="66" xml:space="preserve">
-      <c r="A66" t="str">
-        <v>PROF-108</v>
-      </c>
-      <c r="B66" t="str" xml:space="preserve">
-        <v xml:space="preserve">Annualized interest cost on drawn/funded exposure. Computed as SUM(funded_amount) * bank_share_pct * cost_of_funds_pct at facility level. Uses funded basis (actual drawn amounts from position_detail) rather than committed basis, aligning with FR Y-9C Schedule HI Item 2.
-</v>
-      </c>
-      <c r="C66" t="str">
-        <v>Interest Expense</v>
-      </c>
-      <c r="D66" t="str" xml:space="preserve">
         <v xml:space="preserve">For each active facility:
 1. Join position -&gt; position_detail, SUM(funded_amount) per facility
 2. Multiply by bank_share_pct / 100 from facility_lender_allocation
@@ -6461,22 +6446,22 @@
    from facility_pricing_snapshot
 </v>
       </c>
-      <c r="E66" t="str">
-        <v/>
-      </c>
-      <c r="F66" t="str">
-        <v/>
-      </c>
-      <c r="G66" t="str">
-        <v/>
-      </c>
-      <c r="H66" t="str">
-        <v>Y</v>
-      </c>
-      <c r="I66" t="str">
+      <c r="E65" t="str">
+        <v/>
+      </c>
+      <c r="F65" t="str">
+        <v/>
+      </c>
+      <c r="G65" t="str">
+        <v/>
+      </c>
+      <c r="H65" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I65" t="str">
         <v>Calc</v>
       </c>
-      <c r="J66" t="str" xml:space="preserve">
+      <c r="J65" t="str" xml:space="preserve">
         <v xml:space="preserve">For each active facility:
 1. Join position -&gt; position_detail, SUM(funded_amount) per facility
 2. Multiply by bank_share_pct / 100 from facility_lender_allocation
@@ -6484,63 +6469,156 @@
    from facility_pricing_snapshot
 </v>
       </c>
-      <c r="K66" t="str">
+      <c r="K65" t="str">
         <v>Interest Expense (facility)</v>
       </c>
-      <c r="L66" t="str">
-        <v>Y</v>
-      </c>
-      <c r="M66" t="str">
+      <c r="L65" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M65" t="str">
         <v>Calc</v>
       </c>
-      <c r="N66" t="str" xml:space="preserve">
+      <c r="N65" t="str" xml:space="preserve">
         <v xml:space="preserve">For each counterparty, sum facility-level interest expense weighted
 by participation_pct from facility_counterparty_participation.
 </v>
       </c>
-      <c r="O66" t="str">
+      <c r="O65" t="str">
         <v>Interest Expense (counterparty)</v>
       </c>
-      <c r="P66" t="str">
-        <v>Y</v>
-      </c>
-      <c r="Q66" t="str">
-        <v>Agg</v>
-      </c>
-      <c r="R66" t="str" xml:space="preserve">
+      <c r="P65" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q65" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R65" t="str" xml:space="preserve">
         <v xml:space="preserve">SUM of facility-level interest expense per L3 desk segment.
 </v>
       </c>
-      <c r="S66" t="str">
+      <c r="S65" t="str">
         <v>Interest Expense (desk)</v>
       </c>
-      <c r="T66" t="str">
-        <v>Y</v>
-      </c>
-      <c r="U66" t="str">
-        <v>Agg</v>
-      </c>
-      <c r="V66" t="str" xml:space="preserve">
+      <c r="T65" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U65" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V65" t="str" xml:space="preserve">
         <v xml:space="preserve">SUM of facility-level interest expense per L2 portfolio segment.
 Traverses L3 -&gt; L2 via parent_segment_id.
 </v>
       </c>
-      <c r="W66" t="str">
+      <c r="W65" t="str">
         <v>Interest Expense (portfolio)</v>
       </c>
-      <c r="X66" t="str">
-        <v>Y</v>
-      </c>
-      <c r="Y66" t="str">
-        <v>Agg</v>
-      </c>
-      <c r="Z66" t="str" xml:space="preserve">
+      <c r="X65" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y65" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z65" t="str" xml:space="preserve">
         <v xml:space="preserve">SUM of facility-level interest expense per L1 business segment.
 Traverses L3 -&gt; L2 -&gt; L1 via parent_segment_id chain.
 </v>
       </c>
+      <c r="AA65" t="str">
+        <v>Interest Expense (business_segment)</v>
+      </c>
+      <c r="AB65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66" xml:space="preserve">
+      <c r="A66" t="str">
+        <v>REF-001</v>
+      </c>
+      <c r="B66" t="str" xml:space="preserve">
+        <v xml:space="preserve">Count of individual loans within portfolio or facility grouping. Supports exposure granularity analysis.
+</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Number of Loans</v>
+      </c>
+      <c r="D66" t="str" xml:space="preserve">
+        <v xml:space="preserve">For each Facility_ID, COUNT DISTINCT(Position_ID) from l2.position. Result materialized to l3.facility_exposure_calc.number_of_loans.
+</v>
+      </c>
+      <c r="E66" t="str">
+        <v/>
+      </c>
+      <c r="F66" t="str">
+        <v/>
+      </c>
+      <c r="G66" t="str">
+        <v/>
+      </c>
+      <c r="H66" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I66" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="J66" t="str" xml:space="preserve">
+        <v xml:space="preserve">For each Facility_ID, COUNT DISTINCT(Position_ID) from l2.position. Result materialized to l3.facility_exposure_calc.number_of_loans.
+</v>
+      </c>
+      <c r="K66" t="str">
+        <v>Number of Loans (facility)</v>
+      </c>
+      <c r="L66" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M66" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N66" t="str" xml:space="preserve">
+        <v xml:space="preserve">For each Counterparty_ID, COUNT DISTINCT(Position_ID) from l2.position joined to l2.facility_master.
+</v>
+      </c>
+      <c r="O66" t="str">
+        <v>Number of Loans (counterparty)</v>
+      </c>
+      <c r="P66" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q66" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R66" t="str" xml:space="preserve">
+        <v xml:space="preserve">For each L3 LoB, COUNT DISTINCT(Position_ID) from l2.position joined to l2.facility_master and l1.enterprise_business_taxonomy.
+</v>
+      </c>
+      <c r="S66" t="str">
+        <v>Number of Loans (desk)</v>
+      </c>
+      <c r="T66" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U66" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V66" t="str" xml:space="preserve">
+        <v xml:space="preserve">For each L2 LoB, COUNT DISTINCT(Position_ID) from l2.position joined to l2.facility_master and l1.enterprise_business_taxonomy hierarchy.
+</v>
+      </c>
+      <c r="W66" t="str">
+        <v>Number of Loans (portfolio)</v>
+      </c>
+      <c r="X66" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y66" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z66" t="str" xml:space="preserve">
+        <v xml:space="preserve">For each L1 LoB, COUNT DISTINCT(Position_ID) from l2.position joined to l2.facility_master and l1.enterprise_business_taxonomy hierarchy.
+</v>
+      </c>
       <c r="AA66" t="str">
-        <v>Interest Expense (business_segment)</v>
+        <v>Number of Loans (business_segment)</v>
       </c>
       <c r="AB66" t="str">
         <v/>
@@ -6548,17 +6626,17 @@
     </row>
     <row r="67" xml:space="preserve">
       <c r="A67" t="str">
-        <v>REF-001</v>
+        <v>REF-002</v>
       </c>
       <c r="B67" t="str" xml:space="preserve">
-        <v xml:space="preserve">Count of individual loans within portfolio or facility grouping. Supports exposure granularity analysis.
+        <v xml:space="preserve">Snapshot date of the dataset used for reporting and aggregation. Serves as the temporal reference point for all balances, risk metrics, and performance indicators.
 </v>
       </c>
       <c r="C67" t="str">
-        <v>Number of Loans</v>
+        <v>Reporting Period (As-of Date)</v>
       </c>
       <c r="D67" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Facility_ID, COUNT DISTINCT(Position_ID) from l2.position. Result materialized to l3.facility_exposure_calc.number_of_loans.
+        <v xml:space="preserve">Read as_of_date from facility_exposure_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="E67" t="str">
@@ -6574,27 +6652,27 @@
         <v>Y</v>
       </c>
       <c r="I67" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="J67" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Facility_ID, COUNT DISTINCT(Position_ID) from l2.position. Result materialized to l3.facility_exposure_calc.number_of_loans.
+        <v xml:space="preserve">Read as_of_date from facility_exposure_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="K67" t="str">
-        <v>Number of Loans (facility)</v>
+        <v>Reporting Period (As-of Date) (facility)</v>
       </c>
       <c r="L67" t="str">
         <v>Y</v>
       </c>
       <c r="M67" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="N67" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Counterparty_ID, COUNT DISTINCT(Position_ID) from l2.position joined to l2.facility_master.
+        <v xml:space="preserve">Read as_of_date per counterparty.
 </v>
       </c>
       <c r="O67" t="str">
-        <v>Number of Loans (counterparty)</v>
+        <v>Reporting Period (As-of Date) (counterparty)</v>
       </c>
       <c r="P67" t="str">
         <v>Y</v>
@@ -6603,11 +6681,11 @@
         <v>Agg</v>
       </c>
       <c r="R67" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each L3 LoB, COUNT DISTINCT(Position_ID) from l2.position joined to l2.facility_master and l1.enterprise_business_taxonomy.
+        <v xml:space="preserve">SUM of facility-level as_of_date per L3 desk segment.
 </v>
       </c>
       <c r="S67" t="str">
-        <v>Number of Loans (desk)</v>
+        <v>Reporting Period (As-of Date) (desk)</v>
       </c>
       <c r="T67" t="str">
         <v>Y</v>
@@ -6616,11 +6694,11 @@
         <v>Agg</v>
       </c>
       <c r="V67" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each L2 LoB, COUNT DISTINCT(Position_ID) from l2.position joined to l2.facility_master and l1.enterprise_business_taxonomy hierarchy.
+        <v xml:space="preserve">SUM of facility-level as_of_date per L2 portfolio segment.
 </v>
       </c>
       <c r="W67" t="str">
-        <v>Number of Loans (portfolio)</v>
+        <v>Reporting Period (As-of Date) (portfolio)</v>
       </c>
       <c r="X67" t="str">
         <v>Y</v>
@@ -6629,11 +6707,11 @@
         <v>Agg</v>
       </c>
       <c r="Z67" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each L1 LoB, COUNT DISTINCT(Position_ID) from l2.position joined to l2.facility_master and l1.enterprise_business_taxonomy hierarchy.
+        <v xml:space="preserve">SUM of facility-level as_of_date per L1 business segment segment.
 </v>
       </c>
       <c r="AA67" t="str">
-        <v>Number of Loans (business_segment)</v>
+        <v>Reporting Period (As-of Date) (business_segment)</v>
       </c>
       <c r="AB67" t="str">
         <v/>
@@ -6641,17 +6719,17 @@
     </row>
     <row r="68" xml:space="preserve">
       <c r="A68" t="str">
-        <v>REF-002</v>
+        <v>REF-003</v>
       </c>
       <c r="B68" t="str" xml:space="preserve">
-        <v xml:space="preserve">Snapshot date of the dataset used for reporting and aggregation. Serves as the temporal reference point for all balances, risk metrics, and performance indicators.
+        <v xml:space="preserve">Average tenor of the underlying facilities across exposures. For facility, displayed the calculated tenor based on Origination Date ("Effective Date") and Maturity Date ("End Date"). At other levels this metric is aggregated as an average to represent the average period of the underlying facilities. Calculated from l2.facility_master.maturity_date and origination_date.
 </v>
       </c>
       <c r="C68" t="str">
-        <v>Reporting Period (As-of Date)</v>
+        <v>Average Tenor (Years)</v>
       </c>
       <c r="D68" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read as_of_date from facility_exposure_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">For each Facility_ID, (Maturity Date - Origination Date) / 365.25 to get tenor in years.
 </v>
       </c>
       <c r="E68" t="str">
@@ -6667,66 +6745,66 @@
         <v>Y</v>
       </c>
       <c r="I68" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="J68" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read as_of_date from facility_exposure_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">For each Facility_ID, (Maturity Date - Origination Date) / 365.25 to get tenor in years.
 </v>
       </c>
       <c r="K68" t="str">
-        <v>Reporting Period (As-of Date) (facility)</v>
+        <v>Average Tenor (Years) (facility)</v>
       </c>
       <c r="L68" t="str">
         <v>Y</v>
       </c>
       <c r="M68" t="str">
-        <v>Raw</v>
+        <v>Avg</v>
       </c>
       <c r="N68" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read as_of_date per counterparty.
+        <v xml:space="preserve">Average of facility-level tenor (years) across counterparty facilities.
 </v>
       </c>
       <c r="O68" t="str">
-        <v>Reporting Period (As-of Date) (counterparty)</v>
+        <v>Average Tenor (Years) (counterparty)</v>
       </c>
       <c r="P68" t="str">
         <v>Y</v>
       </c>
       <c r="Q68" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="R68" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level as_of_date per L3 desk segment.
+        <v xml:space="preserve">AVG of facility-level tenor (years) per L3 desk segment.
 </v>
       </c>
       <c r="S68" t="str">
-        <v>Reporting Period (As-of Date) (desk)</v>
+        <v>Average Tenor (Years) (desk)</v>
       </c>
       <c r="T68" t="str">
         <v>Y</v>
       </c>
       <c r="U68" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="V68" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level as_of_date per L2 portfolio segment.
+        <v xml:space="preserve">AVG of facility-level tenor (years) per L2 portfolio segment.
 </v>
       </c>
       <c r="W68" t="str">
-        <v>Reporting Period (As-of Date) (portfolio)</v>
+        <v>Average Tenor (Years) (portfolio)</v>
       </c>
       <c r="X68" t="str">
         <v>Y</v>
       </c>
       <c r="Y68" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="Z68" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level as_of_date per L1 business segment segment.
+        <v xml:space="preserve">AVG of facility-level tenor (years) per L1 business segment.
 </v>
       </c>
       <c r="AA68" t="str">
-        <v>Reporting Period (As-of Date) (business_segment)</v>
+        <v>Average Tenor (Years) (business_segment)</v>
       </c>
       <c r="AB68" t="str">
         <v/>
@@ -6734,17 +6812,17 @@
     </row>
     <row r="69" xml:space="preserve">
       <c r="A69" t="str">
-        <v>REF-003</v>
+        <v>REF-004</v>
       </c>
       <c r="B69" t="str" xml:space="preserve">
-        <v xml:space="preserve">Average tenor of the underlying facilities across exposures. For facility, displayed the calculated tenor based on Origination Date ("Effective Date") and Maturity Date ("End Date"). At other levels this metric is aggregated as an average to represent the average period of the underlying facilities. Calculated from l2.facility_master.maturity_date and origination_date.
+        <v xml:space="preserve">Unique system identifier assigned to the borrower or obligor. Used for exposure aggregation and risk consolidation across the GSIB. At facility level, returns the counterparty_id linked to each facility. At upper levels, returns COUNT(DISTINCT counterparty_id) — the number of unique obligors in each organizational segment.
 </v>
       </c>
       <c r="C69" t="str">
-        <v>Average Tenor (Years)</v>
+        <v>Counterparty ID</v>
       </c>
       <c r="D69" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Facility_ID, (Maturity Date - Origination Date) / 365.25 to get tenor in years.
+        <v xml:space="preserve">Direct lookup of counterparty_id from facility_master for each active facility. Uses current records only (SCD2 filtered).
 </v>
       </c>
       <c r="E69" t="str">
@@ -6760,66 +6838,66 @@
         <v>Y</v>
       </c>
       <c r="I69" t="str">
-        <v>Calc</v>
+        <v>Raw</v>
       </c>
       <c r="J69" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Facility_ID, (Maturity Date - Origination Date) / 365.25 to get tenor in years.
+        <v xml:space="preserve">Direct lookup of counterparty_id from facility_master for each active facility. Uses current records only (SCD2 filtered).
 </v>
       </c>
       <c r="K69" t="str">
-        <v>Average Tenor (Years) (facility)</v>
+        <v>Counterparty ID (facility)</v>
       </c>
       <c r="L69" t="str">
         <v>Y</v>
       </c>
       <c r="M69" t="str">
-        <v>Avg</v>
+        <v>Raw</v>
       </c>
       <c r="N69" t="str" xml:space="preserve">
-        <v xml:space="preserve">Average of facility-level tenor (years) across counterparty facilities.
+        <v xml:space="preserve">Identity — returns counterparty_id for each current counterparty.
 </v>
       </c>
       <c r="O69" t="str">
-        <v>Average Tenor (Years) (counterparty)</v>
+        <v>Counterparty ID (counterparty)</v>
       </c>
       <c r="P69" t="str">
         <v>Y</v>
       </c>
       <c r="Q69" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="R69" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level tenor (years) per L3 desk segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L3 desk segment — number of unique obligors in each desk.
 </v>
       </c>
       <c r="S69" t="str">
-        <v>Average Tenor (Years) (desk)</v>
+        <v>Counterparty ID (desk)</v>
       </c>
       <c r="T69" t="str">
         <v>Y</v>
       </c>
       <c r="U69" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="V69" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level tenor (years) per L2 portfolio segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L2 portfolio segment — number of unique obligors in each portfolio.
 </v>
       </c>
       <c r="W69" t="str">
-        <v>Average Tenor (Years) (portfolio)</v>
+        <v>Counterparty ID (portfolio)</v>
       </c>
       <c r="X69" t="str">
         <v>Y</v>
       </c>
       <c r="Y69" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="Z69" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level tenor (years) per L1 business segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L1 business segment — number of unique obligors in each business segment.
 </v>
       </c>
       <c r="AA69" t="str">
-        <v>Average Tenor (Years) (business_segment)</v>
+        <v>Counterparty ID (business_segment)</v>
       </c>
       <c r="AB69" t="str">
         <v/>
@@ -6827,17 +6905,17 @@
     </row>
     <row r="70" xml:space="preserve">
       <c r="A70" t="str">
-        <v>REF-004</v>
+        <v>REF-005</v>
       </c>
       <c r="B70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Unique system identifier assigned to the borrower or obligor. Used for exposure aggregation and risk consolidation.
+        <v xml:space="preserve">Legal name of the counterparty as documented in the credit agreement. At facility level, returns the counterparty_id (numeric proxy for the name since metric values are numeric). At counterparty level, identity lookup. At upper levels, COUNT(DISTINCT counterparty_id) — number of unique named obligors per organizational segment. Used for reporting clarity and operational reference across all regulatory submissions.
 </v>
       </c>
       <c r="C70" t="str">
-        <v>Counterparty ID</v>
+        <v>Counterparty Name</v>
       </c>
       <c r="D70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">Lookup counterparty_id from facility_master for each active facility. The numeric counterparty_id serves as proxy for the legal name (string values resolved via counterparty dimension join at display time). Uses current records only.
 </v>
       </c>
       <c r="E70" t="str">
@@ -6856,11 +6934,11 @@
         <v>Raw</v>
       </c>
       <c r="J70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">Lookup counterparty_id from facility_master for each active facility. The numeric counterparty_id serves as proxy for the legal name (string values resolved via counterparty dimension join at display time). Uses current records only.
 </v>
       </c>
       <c r="K70" t="str">
-        <v>Counterparty ID (facility)</v>
+        <v>Counterparty Name (facility)</v>
       </c>
       <c r="L70" t="str">
         <v>Y</v>
@@ -6869,11 +6947,11 @@
         <v>Raw</v>
       </c>
       <c r="N70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">Identity — returns counterparty_id for each current counterparty. Legal name resolved via counterparty dimension join at display time.
 </v>
       </c>
       <c r="O70" t="str">
-        <v>Counterparty ID (counterparty)</v>
+        <v>Counterparty Name (counterparty)</v>
       </c>
       <c r="P70" t="str">
         <v>Y</v>
@@ -6882,11 +6960,11 @@
         <v>Agg</v>
       </c>
       <c r="R70" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L3 desk segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L3 desk segment — number of unique named obligors in each desk.
 </v>
       </c>
       <c r="S70" t="str">
-        <v>Counterparty ID (desk)</v>
+        <v>Counterparty Name (desk)</v>
       </c>
       <c r="T70" t="str">
         <v>Y</v>
@@ -6895,11 +6973,11 @@
         <v>Agg</v>
       </c>
       <c r="V70" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L2 portfolio segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L2 portfolio segment — number of unique named obligors in each portfolio.
 </v>
       </c>
       <c r="W70" t="str">
-        <v>Counterparty ID (portfolio)</v>
+        <v>Counterparty Name (portfolio)</v>
       </c>
       <c r="X70" t="str">
         <v>Y</v>
@@ -6908,11 +6986,11 @@
         <v>Agg</v>
       </c>
       <c r="Z70" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L1 business segment segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L1 business segment — number of unique named obligors in each business segment.
 </v>
       </c>
       <c r="AA70" t="str">
-        <v>Counterparty ID (business_segment)</v>
+        <v>Counterparty Name (business_segment)</v>
       </c>
       <c r="AB70" t="str">
         <v/>
@@ -6920,17 +6998,17 @@
     </row>
     <row r="71" xml:space="preserve">
       <c r="A71" t="str">
-        <v>REF-005</v>
+        <v>REF-006</v>
       </c>
       <c r="B71" t="str" xml:space="preserve">
-        <v xml:space="preserve">Descriptive name of the counterparty as documented in the credit agreement. Used for reporting clarity and operational reference.
+        <v xml:space="preserve">Country of risk derived from the counterparty's domicile. At facility level, returns a numeric country identifier (via counterparty → country_dim join path). At counterparty level, identity lookup. At desk/portfolio/segment levels, COUNT(DISTINCT country_code) — geographic diversification indicator showing the number of unique countries represented. Supports FFIEC 009 Country Exposure Report and Basel III geographic concentration analysis.
 </v>
       </c>
       <c r="C71" t="str">
-        <v>Counterparty Name</v>
+        <v>Country</v>
       </c>
       <c r="D71" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read legal_name from counterparty for each facility's counterparty.
+        <v xml:space="preserve">Lookup country for each facility via counterparty → country_dim join path. Returns counterparty_id as numeric proxy (country_name resolved at display time via dimension join). Uses current records only.
 </v>
       </c>
       <c r="E71" t="str">
@@ -6949,24 +7027,24 @@
         <v>Raw</v>
       </c>
       <c r="J71" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read legal_name from counterparty for each facility's counterparty.
+        <v xml:space="preserve">Lookup country for each facility via counterparty → country_dim join path. Returns counterparty_id as numeric proxy (country_name resolved at display time via dimension join). Uses current records only.
 </v>
       </c>
       <c r="K71" t="str">
-        <v>Counterparty Name (facility)</v>
+        <v>Country (facility)</v>
       </c>
       <c r="L71" t="str">
         <v>Y</v>
       </c>
       <c r="M71" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="N71" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with counterparty name per counterparty.
+        <v xml:space="preserve">Lookup country for each counterparty via country_code → country_dim join. Returns counterparty_id as numeric proxy.
 </v>
       </c>
       <c r="O71" t="str">
-        <v>Counterparty Name (counterparty)</v>
+        <v>Country (counterparty)</v>
       </c>
       <c r="P71" t="str">
         <v>Y</v>
@@ -6975,11 +7053,11 @@
         <v>Agg</v>
       </c>
       <c r="R71" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with counterparty name per L3 desk segment.
+        <v xml:space="preserve">COUNT(DISTINCT country_code) per L3 desk segment — number of unique countries represented, a geographic diversification indicator.
 </v>
       </c>
       <c r="S71" t="str">
-        <v>Counterparty Name (desk)</v>
+        <v>Country (desk)</v>
       </c>
       <c r="T71" t="str">
         <v>Y</v>
@@ -6988,11 +7066,11 @@
         <v>Agg</v>
       </c>
       <c r="V71" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with counterparty name per L2 portfolio segment.
+        <v xml:space="preserve">COUNT(DISTINCT country_code) per L2 portfolio segment — number of unique countries represented in each portfolio.
 </v>
       </c>
       <c r="W71" t="str">
-        <v>Counterparty Name (portfolio)</v>
+        <v>Country (portfolio)</v>
       </c>
       <c r="X71" t="str">
         <v>Y</v>
@@ -7001,11 +7079,11 @@
         <v>Agg</v>
       </c>
       <c r="Z71" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with counterparty name per L1 business segment.
+        <v xml:space="preserve">COUNT(DISTINCT country_code) per L1 business segment — geographic diversification at the highest organizational level.
 </v>
       </c>
       <c r="AA71" t="str">
-        <v>Counterparty Name (business_segment)</v>
+        <v>Country (business_segment)</v>
       </c>
       <c r="AB71" t="str">
         <v/>
@@ -7013,17 +7091,17 @@
     </row>
     <row r="72" xml:space="preserve">
       <c r="A72" t="str">
-        <v>REF-006</v>
+        <v>REF-007</v>
       </c>
       <c r="B72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Country of risk or booking location. Supports geographic concentration and sovereign risk analysis.
+        <v xml:space="preserve">Unique identifier linking each facility to its governing credit agreement documentation. Used for contract tracking, facility-to-agreement linkage, and regulatory reporting. At counterparty level, returns count of distinct credit agreements per borrower.
 </v>
       </c>
       <c r="C72" t="str">
-        <v>Country</v>
+        <v>Credit Agreement ID</v>
       </c>
       <c r="D72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of country_name from country_dim.
+        <v xml:space="preserve">Direct lookup of credit_agreement_id for each active facility via facility_master joined to credit_agreement_master.
 </v>
       </c>
       <c r="E72" t="str">
@@ -7042,24 +7120,24 @@
         <v>Raw</v>
       </c>
       <c r="J72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of country_name from country_dim.
+        <v xml:space="preserve">Direct lookup of credit_agreement_id for each active facility via facility_master joined to credit_agreement_master.
 </v>
       </c>
       <c r="K72" t="str">
-        <v>Country (facility)</v>
+        <v>Credit Agreement ID (facility)</v>
       </c>
       <c r="L72" t="str">
         <v>Y</v>
       </c>
       <c r="M72" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="N72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read country_name per counterparty.
+        <v xml:space="preserve">Count of distinct credit agreements per counterparty. Provides visibility into borrower complexity and multi-agreement relationships.
 </v>
       </c>
       <c r="O72" t="str">
-        <v>Country (counterparty)</v>
+        <v>Credit Agreement ID (counterparty)</v>
       </c>
       <c r="P72" t="str">
         <v>Y</v>
@@ -7068,11 +7146,11 @@
         <v>Agg</v>
       </c>
       <c r="R72" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level country_name per L3 desk segment.
+        <v xml:space="preserve">Count of distinct credit agreements per L3 desk segment via enterprise_business_taxonomy.
 </v>
       </c>
       <c r="S72" t="str">
-        <v>Country (desk)</v>
+        <v>Credit Agreement ID (desk)</v>
       </c>
       <c r="T72" t="str">
         <v>Y</v>
@@ -7081,11 +7159,11 @@
         <v>Agg</v>
       </c>
       <c r="V72" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level country_name per L2 portfolio segment.
+        <v xml:space="preserve">Count of distinct credit agreements per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
 </v>
       </c>
       <c r="W72" t="str">
-        <v>Country (portfolio)</v>
+        <v>Credit Agreement ID (portfolio)</v>
       </c>
       <c r="X72" t="str">
         <v>Y</v>
@@ -7094,11 +7172,11 @@
         <v>Agg</v>
       </c>
       <c r="Z72" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level country_name per L1 business segment segment.
+        <v xml:space="preserve">Count of distinct credit agreements per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
 </v>
       </c>
       <c r="AA72" t="str">
-        <v>Country (business_segment)</v>
+        <v>Credit Agreement ID (business_segment)</v>
       </c>
       <c r="AB72" t="str">
         <v/>
@@ -7106,17 +7184,17 @@
     </row>
     <row r="73" xml:space="preserve">
       <c r="A73" t="str">
-        <v>REF-007</v>
+        <v>REF-008</v>
       </c>
       <c r="B73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Unique identifier linking facility to governing credit agreement documentation.
+        <v xml:space="preserve">Number of calendar days remaining until contractual maturity, sourced from the facility exposure snapshot. At aggregate levels, reports the minimum (nearest) maturity across constituent facilities to highlight the most imminent rollover risk and refinancing pressure.
 </v>
       </c>
       <c r="C73" t="str">
-        <v>Credit Agreement ID</v>
+        <v>Days Until Maturity</v>
       </c>
       <c r="D73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of credit_agreement_id from credit_agreement_master.
+        <v xml:space="preserve">Read days_until_maturity from facility_exposure_snapshot for each active, current facility as of the reporting date.
 </v>
       </c>
       <c r="E73" t="str">
@@ -7135,24 +7213,24 @@
         <v>Raw</v>
       </c>
       <c r="J73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of credit_agreement_id from credit_agreement_master.
+        <v xml:space="preserve">Read days_until_maturity from facility_exposure_snapshot for each active, current facility as of the reporting date.
 </v>
       </c>
       <c r="K73" t="str">
-        <v>Credit Agreement ID (facility)</v>
+        <v>Days Until Maturity (facility)</v>
       </c>
       <c r="L73" t="str">
         <v>Y</v>
       </c>
       <c r="M73" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="N73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read credit_agreement_id per counterparty.
+        <v xml:space="preserve">Minimum days_until_maturity across all facilities per counterparty — nearest maturity indicates most urgent rollover risk.
 </v>
       </c>
       <c r="O73" t="str">
-        <v>Credit Agreement ID (counterparty)</v>
+        <v>Days Until Maturity (counterparty)</v>
       </c>
       <c r="P73" t="str">
         <v>Y</v>
@@ -7161,11 +7239,11 @@
         <v>Agg</v>
       </c>
       <c r="R73" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level credit_agreement_id per L3 desk segment.
+        <v xml:space="preserve">Minimum days_until_maturity across all facilities per L3 desk segment — nearest maturity in the segment.
 </v>
       </c>
       <c r="S73" t="str">
-        <v>Credit Agreement ID (desk)</v>
+        <v>Days Until Maturity (desk)</v>
       </c>
       <c r="T73" t="str">
         <v>Y</v>
@@ -7174,11 +7252,11 @@
         <v>Agg</v>
       </c>
       <c r="V73" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level credit_agreement_id per L2 portfolio segment.
+        <v xml:space="preserve">Minimum days_until_maturity across all facilities per L2 portfolio segment.
 </v>
       </c>
       <c r="W73" t="str">
-        <v>Credit Agreement ID (portfolio)</v>
+        <v>Days Until Maturity (portfolio)</v>
       </c>
       <c r="X73" t="str">
         <v>Y</v>
@@ -7187,11 +7265,11 @@
         <v>Agg</v>
       </c>
       <c r="Z73" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level credit_agreement_id per L1 business segment segment.
+        <v xml:space="preserve">Minimum days_until_maturity across all facilities per L1 business segment.
 </v>
       </c>
       <c r="AA73" t="str">
-        <v>Credit Agreement ID (business_segment)</v>
+        <v>Days Until Maturity (business_segment)</v>
       </c>
       <c r="AB73" t="str">
         <v/>
@@ -7199,17 +7277,18 @@
     </row>
     <row r="74" xml:space="preserve">
       <c r="A74" t="str">
-        <v>REF-008</v>
+        <v>REF-009</v>
       </c>
       <c r="B74" t="str" xml:space="preserve">
-        <v xml:space="preserve">Number of calendar days remaining until contractual maturity, sourced from the facility exposure snapshot. At aggregate levels, reports the minimum (nearest) maturity across constituent facilities to highlight the most imminent rollover risk and refinancing pressure.
+        <v xml:space="preserve">Date on which loan or contract became legally effective. Sourced directly from facility_master. At aggregate levels, returns the earliest origination date (MIN) across constituent facilities — indicating the oldest vintage in the book. Key contract lifecycle tracking attribute for vintage analysis and portfolio seasoning assessment.
 </v>
       </c>
       <c r="C74" t="str">
-        <v>Days Until Maturity</v>
+        <v>Contract Origination Date</v>
       </c>
       <c r="D74" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read days_until_maturity from facility_exposure_snapshot for each active, current facility as of the reporting date.
+        <v xml:space="preserve">Direct lookup of origination_date from facility_master.
+Ingredients: origination_date (L2 facility_master — raw field)
 </v>
       </c>
       <c r="E74" t="str">
@@ -7228,11 +7307,12 @@
         <v>Raw</v>
       </c>
       <c r="J74" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read days_until_maturity from facility_exposure_snapshot for each active, current facility as of the reporting date.
+        <v xml:space="preserve">Direct lookup of origination_date from facility_master.
+Ingredients: origination_date (L2 facility_master — raw field)
 </v>
       </c>
       <c r="K74" t="str">
-        <v>Days Until Maturity (facility)</v>
+        <v>Contract Origination Date (facility)</v>
       </c>
       <c r="L74" t="str">
         <v>Y</v>
@@ -7241,11 +7321,14 @@
         <v>Agg</v>
       </c>
       <c r="N74" t="str" xml:space="preserve">
-        <v xml:space="preserve">Minimum days_until_maturity across all facilities per counterparty — nearest maturity indicates most urgent rollover risk.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD origination_date from l2.facility_master for all active facilities
+  2. COMPUTE MIN(origination_date) — earliest contract vintage
+Indicates the oldest banking relationship tenure for this counterparty.
 </v>
       </c>
       <c r="O74" t="str">
-        <v>Days Until Maturity (counterparty)</v>
+        <v>Contract Origination Date (counterparty)</v>
       </c>
       <c r="P74" t="str">
         <v>Y</v>
@@ -7254,11 +7337,14 @@
         <v>Agg</v>
       </c>
       <c r="R74" t="str" xml:space="preserve">
-        <v xml:space="preserve">Minimum days_until_maturity across all facilities per L3 desk segment — nearest maturity in the segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOAD origination_date from l2.facility_master
+  2. JOIN l1.enterprise_business_taxonomy on lob_segment_id
+  3. COMPUTE MIN(origination_date) — earliest vintage in desk book
 </v>
       </c>
       <c r="S74" t="str">
-        <v>Days Until Maturity (desk)</v>
+        <v>Contract Origination Date (desk)</v>
       </c>
       <c r="T74" t="str">
         <v>Y</v>
@@ -7267,11 +7353,13 @@
         <v>Agg</v>
       </c>
       <c r="V74" t="str" xml:space="preserve">
-        <v xml:space="preserve">Minimum days_until_maturity across all facilities per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. COMPUTE MIN(origination_date) — earliest vintage in portfolio
 </v>
       </c>
       <c r="W74" t="str">
-        <v>Days Until Maturity (portfolio)</v>
+        <v>Contract Origination Date (portfolio)</v>
       </c>
       <c r="X74" t="str">
         <v>Y</v>
@@ -7280,11 +7368,13 @@
         <v>Agg</v>
       </c>
       <c r="Z74" t="str" xml:space="preserve">
-        <v xml:space="preserve">Minimum days_until_maturity across all facilities per L1 business segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. COMPUTE MIN(origination_date) — earliest vintage in business segment
 </v>
       </c>
       <c r="AA74" t="str">
-        <v>Days Until Maturity (business_segment)</v>
+        <v>Contract Origination Date (business_segment)</v>
       </c>
       <c r="AB74" t="str">
         <v/>
@@ -7292,17 +7382,17 @@
     </row>
     <row r="75" xml:space="preserve">
       <c r="A75" t="str">
-        <v>REF-009</v>
+        <v>REF-010</v>
       </c>
       <c r="B75" t="str" xml:space="preserve">
-        <v xml:space="preserve">Date on which loan or contract became legally effective.
+        <v xml:space="preserve">Unique identifier assigned to the lending facility within enterprise systems. Used to aggregate balances, risk metrics, pricing data, and contractual attributes at the facility level.
 </v>
       </c>
       <c r="C75" t="str">
-        <v>Contract Origination Date</v>
+        <v>Facility ID</v>
       </c>
       <c r="D75" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of origination_date from facility_master.
+        <v xml:space="preserve">Direct lookup of facility_id from facility_master.
 </v>
       </c>
       <c r="E75" t="str">
@@ -7321,24 +7411,24 @@
         <v>Raw</v>
       </c>
       <c r="J75" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of origination_date from facility_master.
+        <v xml:space="preserve">Direct lookup of facility_id from facility_master.
 </v>
       </c>
       <c r="K75" t="str">
-        <v>Contract Origination Date (facility)</v>
+        <v>Facility ID (facility)</v>
       </c>
       <c r="L75" t="str">
         <v>Y</v>
       </c>
       <c r="M75" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="N75" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level origination_date) per counterparty.
+        <v xml:space="preserve">Read facility_id per counterparty.
 </v>
       </c>
       <c r="O75" t="str">
-        <v>Contract Origination Date (counterparty)</v>
+        <v>Facility ID (counterparty)</v>
       </c>
       <c r="P75" t="str">
         <v>Y</v>
@@ -7347,11 +7437,11 @@
         <v>Agg</v>
       </c>
       <c r="R75" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level origination_date per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level facility_id per L3 desk segment.
 </v>
       </c>
       <c r="S75" t="str">
-        <v>Contract Origination Date (desk)</v>
+        <v>Facility ID (desk)</v>
       </c>
       <c r="T75" t="str">
         <v>Y</v>
@@ -7360,11 +7450,11 @@
         <v>Agg</v>
       </c>
       <c r="V75" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level origination_date per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level facility_id per L2 portfolio segment.
 </v>
       </c>
       <c r="W75" t="str">
-        <v>Contract Origination Date (portfolio)</v>
+        <v>Facility ID (portfolio)</v>
       </c>
       <c r="X75" t="str">
         <v>Y</v>
@@ -7373,11 +7463,11 @@
         <v>Agg</v>
       </c>
       <c r="Z75" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level origination_date per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level facility_id per L1 business segment segment.
 </v>
       </c>
       <c r="AA75" t="str">
-        <v>Contract Origination Date (business_segment)</v>
+        <v>Facility ID (business_segment)</v>
       </c>
       <c r="AB75" t="str">
         <v/>
@@ -7385,17 +7475,17 @@
     </row>
     <row r="76" xml:space="preserve">
       <c r="A76" t="str">
-        <v>REF-010</v>
+        <v>REF-011</v>
       </c>
       <c r="B76" t="str" xml:space="preserve">
-        <v xml:space="preserve">Unique identifier assigned to the lending facility within enterprise systems. Used to aggregate balances, risk metrics, pricing data, and contractual attributes at the facility level.
+        <v xml:space="preserve">Descriptive name of the facility as documented in the credit agreement. Used for reporting clarity and operational reference.
 </v>
       </c>
       <c r="C76" t="str">
-        <v>Facility ID</v>
+        <v>Facility Name</v>
       </c>
       <c r="D76" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of facility_id from facility_master.
+        <v xml:space="preserve">Direct lookup of facility_name from facility_master.
 </v>
       </c>
       <c r="E76" t="str">
@@ -7414,11 +7504,11 @@
         <v>Raw</v>
       </c>
       <c r="J76" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of facility_id from facility_master.
+        <v xml:space="preserve">Direct lookup of facility_name from facility_master.
 </v>
       </c>
       <c r="K76" t="str">
-        <v>Facility ID (facility)</v>
+        <v>Facility Name (facility)</v>
       </c>
       <c r="L76" t="str">
         <v>Y</v>
@@ -7427,11 +7517,11 @@
         <v>Raw</v>
       </c>
       <c r="N76" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read facility_id per counterparty.
+        <v xml:space="preserve">Read facility_name per counterparty.
 </v>
       </c>
       <c r="O76" t="str">
-        <v>Facility ID (counterparty)</v>
+        <v>Facility Name (counterparty)</v>
       </c>
       <c r="P76" t="str">
         <v>Y</v>
@@ -7440,11 +7530,11 @@
         <v>Agg</v>
       </c>
       <c r="R76" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_id per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level facility_name per L3 desk segment.
 </v>
       </c>
       <c r="S76" t="str">
-        <v>Facility ID (desk)</v>
+        <v>Facility Name (desk)</v>
       </c>
       <c r="T76" t="str">
         <v>Y</v>
@@ -7453,11 +7543,11 @@
         <v>Agg</v>
       </c>
       <c r="V76" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_id per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level facility_name per L2 portfolio segment.
 </v>
       </c>
       <c r="W76" t="str">
-        <v>Facility ID (portfolio)</v>
+        <v>Facility Name (portfolio)</v>
       </c>
       <c r="X76" t="str">
         <v>Y</v>
@@ -7466,11 +7556,11 @@
         <v>Agg</v>
       </c>
       <c r="Z76" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_id per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level facility_name per L1 business segment segment.
 </v>
       </c>
       <c r="AA76" t="str">
-        <v>Facility ID (business_segment)</v>
+        <v>Facility Name (business_segment)</v>
       </c>
       <c r="AB76" t="str">
         <v/>
@@ -7478,17 +7568,17 @@
     </row>
     <row r="77" xml:space="preserve">
       <c r="A77" t="str">
-        <v>REF-011</v>
+        <v>REF-012</v>
       </c>
       <c r="B77" t="str" xml:space="preserve">
-        <v xml:space="preserve">Descriptive name of the facility as documented in the credit agreement. Used for reporting clarity and operational reference.
+        <v xml:space="preserve">Type of credit facility (e.g., Term Loan, Revolver, Letter of Credit). Enables product-level segmentation, risk concentration analysis, and performance benchmarking.
 </v>
       </c>
       <c r="C77" t="str">
-        <v>Facility Name</v>
+        <v>Facility Type</v>
       </c>
       <c r="D77" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of facility_name from facility_master.
+        <v xml:space="preserve">Read facility_type from facility_exposure_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="E77" t="str">
@@ -7507,24 +7597,24 @@
         <v>Raw</v>
       </c>
       <c r="J77" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of facility_name from facility_master.
+        <v xml:space="preserve">Read facility_type from facility_exposure_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="K77" t="str">
-        <v>Facility Name (facility)</v>
+        <v>Facility Type (facility)</v>
       </c>
       <c r="L77" t="str">
         <v>Y</v>
       </c>
       <c r="M77" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="N77" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read facility_name per counterparty.
+        <v xml:space="preserve">SUM(facility-level facility_type) per counterparty.
 </v>
       </c>
       <c r="O77" t="str">
-        <v>Facility Name (counterparty)</v>
+        <v>Facility Type (counterparty)</v>
       </c>
       <c r="P77" t="str">
         <v>Y</v>
@@ -7533,11 +7623,11 @@
         <v>Agg</v>
       </c>
       <c r="R77" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_name per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level facility_type per L3 desk segment.
 </v>
       </c>
       <c r="S77" t="str">
-        <v>Facility Name (desk)</v>
+        <v>Facility Type (desk)</v>
       </c>
       <c r="T77" t="str">
         <v>Y</v>
@@ -7546,11 +7636,11 @@
         <v>Agg</v>
       </c>
       <c r="V77" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_name per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level facility_type per L2 portfolio segment.
 </v>
       </c>
       <c r="W77" t="str">
-        <v>Facility Name (portfolio)</v>
+        <v>Facility Type (portfolio)</v>
       </c>
       <c r="X77" t="str">
         <v>Y</v>
@@ -7559,11 +7649,11 @@
         <v>Agg</v>
       </c>
       <c r="Z77" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_name per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level facility_type per L1 business segment segment.
 </v>
       </c>
       <c r="AA77" t="str">
-        <v>Facility Name (business_segment)</v>
+        <v>Facility Type (business_segment)</v>
       </c>
       <c r="AB77" t="str">
         <v/>
@@ -7571,17 +7661,17 @@
     </row>
     <row r="78" xml:space="preserve">
       <c r="A78" t="str">
-        <v>REF-012</v>
+        <v>REF-013</v>
       </c>
       <c r="B78" t="str" xml:space="preserve">
-        <v xml:space="preserve">Type of credit facility (e.g., Term Loan, Revolver, Letter of Credit). Enables product-level segmentation, risk concentration analysis, and performance benchmarking.
+        <v xml:space="preserve">A classification used for reporting purposes in the FR 2590 regulatory report pertaining to financial institutions' credit exposures.
 </v>
       </c>
       <c r="C78" t="str">
-        <v>Facility Type</v>
+        <v>FR2590 Category</v>
       </c>
       <c r="D78" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read facility_type from facility_exposure_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Calculated fr2590_category_code per facility.
 </v>
       </c>
       <c r="E78" t="str">
@@ -7597,14 +7687,14 @@
         <v>Y</v>
       </c>
       <c r="I78" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="J78" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read facility_type from facility_exposure_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Calculated fr2590_category_code per facility.
 </v>
       </c>
       <c r="K78" t="str">
-        <v>Facility Type (facility)</v>
+        <v>FR2590 Category (facility)</v>
       </c>
       <c r="L78" t="str">
         <v>Y</v>
@@ -7613,11 +7703,11 @@
         <v>Agg</v>
       </c>
       <c r="N78" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level facility_type) per counterparty.
+        <v xml:space="preserve">SUM of facility-level fr2590_category_code per counterparty.
 </v>
       </c>
       <c r="O78" t="str">
-        <v>Facility Type (counterparty)</v>
+        <v>FR2590 Category (counterparty)</v>
       </c>
       <c r="P78" t="str">
         <v>Y</v>
@@ -7626,11 +7716,11 @@
         <v>Agg</v>
       </c>
       <c r="R78" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_type per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level fr2590_category_code per L3 desk segment.
 </v>
       </c>
       <c r="S78" t="str">
-        <v>Facility Type (desk)</v>
+        <v>FR2590 Category (desk)</v>
       </c>
       <c r="T78" t="str">
         <v>Y</v>
@@ -7639,11 +7729,11 @@
         <v>Agg</v>
       </c>
       <c r="V78" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_type per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level fr2590_category_code per L2 portfolio segment.
 </v>
       </c>
       <c r="W78" t="str">
-        <v>Facility Type (portfolio)</v>
+        <v>FR2590 Category (portfolio)</v>
       </c>
       <c r="X78" t="str">
         <v>Y</v>
@@ -7652,11 +7742,11 @@
         <v>Agg</v>
       </c>
       <c r="Z78" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_type per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level fr2590_category_code per L1 business segment segment.
 </v>
       </c>
       <c r="AA78" t="str">
-        <v>Facility Type (business_segment)</v>
+        <v>FR2590 Category (business_segment)</v>
       </c>
       <c r="AB78" t="str">
         <v/>
@@ -7664,17 +7754,17 @@
     </row>
     <row r="79" xml:space="preserve">
       <c r="A79" t="str">
-        <v>REF-013</v>
+        <v>REF-014</v>
       </c>
       <c r="B79" t="str" xml:space="preserve">
-        <v xml:space="preserve">A classification used for reporting purposes in the FR 2590 regulatory report pertaining to financial institutions' credit exposures.
+        <v xml:space="preserve">Indicator that facility or exposure is active and not closed, canceled or matured. Portfolio KPI (% Active Facilities) measures ongoing credit exposure footprint.
 </v>
       </c>
       <c r="C79" t="str">
-        <v>FR2590 Category</v>
+        <v>Active</v>
       </c>
       <c r="D79" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated fr2590_category_code per facility.
+        <v xml:space="preserve">Direct lookup of is_active_flag from facility_master.
 </v>
       </c>
       <c r="E79" t="str">
@@ -7690,27 +7780,27 @@
         <v>Y</v>
       </c>
       <c r="I79" t="str">
-        <v>Calc</v>
+        <v>Raw</v>
       </c>
       <c r="J79" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated fr2590_category_code per facility.
+        <v xml:space="preserve">Direct lookup of is_active_flag from facility_master.
 </v>
       </c>
       <c r="K79" t="str">
-        <v>FR2590 Category (facility)</v>
+        <v>Active (facility)</v>
       </c>
       <c r="L79" t="str">
         <v>Y</v>
       </c>
       <c r="M79" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="N79" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level fr2590_category_code per counterparty.
+        <v xml:space="preserve">Read is_active_flag per counterparty.
 </v>
       </c>
       <c r="O79" t="str">
-        <v>FR2590 Category (counterparty)</v>
+        <v>Active (counterparty)</v>
       </c>
       <c r="P79" t="str">
         <v>Y</v>
@@ -7719,11 +7809,11 @@
         <v>Agg</v>
       </c>
       <c r="R79" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level fr2590_category_code per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level is_active_flag per L3 desk segment.
 </v>
       </c>
       <c r="S79" t="str">
-        <v>FR2590 Category (desk)</v>
+        <v>Active (desk)</v>
       </c>
       <c r="T79" t="str">
         <v>Y</v>
@@ -7732,11 +7822,11 @@
         <v>Agg</v>
       </c>
       <c r="V79" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level fr2590_category_code per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level is_active_flag per L2 portfolio segment.
 </v>
       </c>
       <c r="W79" t="str">
-        <v>FR2590 Category (portfolio)</v>
+        <v>Active (portfolio)</v>
       </c>
       <c r="X79" t="str">
         <v>Y</v>
@@ -7745,11 +7835,11 @@
         <v>Agg</v>
       </c>
       <c r="Z79" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level fr2590_category_code per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level is_active_flag per L1 business segment segment.
 </v>
       </c>
       <c r="AA79" t="str">
-        <v>FR2590 Category (business_segment)</v>
+        <v>Active (business_segment)</v>
       </c>
       <c r="AB79" t="str">
         <v/>
@@ -7757,17 +7847,17 @@
     </row>
     <row r="80" xml:space="preserve">
       <c r="A80" t="str">
-        <v>REF-014</v>
+        <v>REF-015</v>
       </c>
       <c r="B80" t="str" xml:space="preserve">
-        <v xml:space="preserve">Indicator that facility or exposure is active and not closed, canceled or matured. Portfolio KPI (% Active Facilities) measures ongoing credit exposure footprint.
+        <v xml:space="preserve">Boolean indicator to depict when facility is syndicated across multiple issuing banks. Portfolio KPI (% Syndicated Facilities) provides insight into risk distribution across lenders.
 </v>
       </c>
       <c r="C80" t="str">
-        <v>Active</v>
+        <v>Syndicated Deal Flag</v>
       </c>
       <c r="D80" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of is_active_flag from facility_master.
+        <v xml:space="preserve">Calculated is_syndicated_flag per facility.
 </v>
       </c>
       <c r="E80" t="str">
@@ -7783,27 +7873,27 @@
         <v>Y</v>
       </c>
       <c r="I80" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="J80" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of is_active_flag from facility_master.
+        <v xml:space="preserve">Calculated is_syndicated_flag per facility.
 </v>
       </c>
       <c r="K80" t="str">
-        <v>Active (facility)</v>
+        <v>Syndicated Deal Flag (facility)</v>
       </c>
       <c r="L80" t="str">
         <v>Y</v>
       </c>
       <c r="M80" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="N80" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read is_active_flag per counterparty.
+        <v xml:space="preserve">SUM(facility-level is_syndicated_flag) per counterparty.
 </v>
       </c>
       <c r="O80" t="str">
-        <v>Active (counterparty)</v>
+        <v>Syndicated Deal Flag (counterparty)</v>
       </c>
       <c r="P80" t="str">
         <v>Y</v>
@@ -7812,11 +7902,11 @@
         <v>Agg</v>
       </c>
       <c r="R80" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level is_active_flag per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level is_syndicated_flag per L3 desk segment.
 </v>
       </c>
       <c r="S80" t="str">
-        <v>Active (desk)</v>
+        <v>Syndicated Deal Flag (desk)</v>
       </c>
       <c r="T80" t="str">
         <v>Y</v>
@@ -7825,11 +7915,11 @@
         <v>Agg</v>
       </c>
       <c r="V80" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level is_active_flag per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level is_syndicated_flag per L2 portfolio segment.
 </v>
       </c>
       <c r="W80" t="str">
-        <v>Active (portfolio)</v>
+        <v>Syndicated Deal Flag (portfolio)</v>
       </c>
       <c r="X80" t="str">
         <v>Y</v>
@@ -7838,11 +7928,11 @@
         <v>Agg</v>
       </c>
       <c r="Z80" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level is_active_flag per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level is_syndicated_flag per L1 business segment segment.
 </v>
       </c>
       <c r="AA80" t="str">
-        <v>Active (business_segment)</v>
+        <v>Syndicated Deal Flag (business_segment)</v>
       </c>
       <c r="AB80" t="str">
         <v/>
@@ -7850,17 +7940,17 @@
     </row>
     <row r="81" xml:space="preserve">
       <c r="A81" t="str">
-        <v>REF-015</v>
+        <v>REF-016</v>
       </c>
       <c r="B81" t="str" xml:space="preserve">
-        <v xml:space="preserve">Boolean indicator to depict when facility is syndicated across multiple issuing banks. Portfolio KPI (% Syndicated Facilities) provides insight into risk distribution across lenders.
+        <v xml:space="preserve">Legal entity booking or owning the exposure. Critical for regulatory capital and entity-level reporting.
 </v>
       </c>
       <c r="C81" t="str">
-        <v>Syndicated Deal Flag</v>
+        <v>Legal Entity</v>
       </c>
       <c r="D81" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated is_syndicated_flag per facility.
+        <v xml:space="preserve">Direct lookup of legal_name from counterparty.
 </v>
       </c>
       <c r="E81" t="str">
@@ -7876,27 +7966,27 @@
         <v>Y</v>
       </c>
       <c r="I81" t="str">
-        <v>Calc</v>
+        <v>Raw</v>
       </c>
       <c r="J81" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated is_syndicated_flag per facility.
+        <v xml:space="preserve">Direct lookup of legal_name from counterparty.
 </v>
       </c>
       <c r="K81" t="str">
-        <v>Syndicated Deal Flag (facility)</v>
+        <v>Legal Entity (facility)</v>
       </c>
       <c r="L81" t="str">
         <v>Y</v>
       </c>
       <c r="M81" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="N81" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level is_syndicated_flag) per counterparty.
+        <v xml:space="preserve">Direct lookup of legal_name from counterparty.
 </v>
       </c>
       <c r="O81" t="str">
-        <v>Syndicated Deal Flag (counterparty)</v>
+        <v>Legal Entity (counterparty)</v>
       </c>
       <c r="P81" t="str">
         <v>Y</v>
@@ -7905,11 +7995,11 @@
         <v>Agg</v>
       </c>
       <c r="R81" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level is_syndicated_flag per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level legal_name per L3 desk segment.
 </v>
       </c>
       <c r="S81" t="str">
-        <v>Syndicated Deal Flag (desk)</v>
+        <v>Legal Entity (desk)</v>
       </c>
       <c r="T81" t="str">
         <v>Y</v>
@@ -7918,11 +8008,11 @@
         <v>Agg</v>
       </c>
       <c r="V81" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level is_syndicated_flag per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level legal_name per L2 portfolio segment.
 </v>
       </c>
       <c r="W81" t="str">
-        <v>Syndicated Deal Flag (portfolio)</v>
+        <v>Legal Entity (portfolio)</v>
       </c>
       <c r="X81" t="str">
         <v>Y</v>
@@ -7931,11 +8021,11 @@
         <v>Agg</v>
       </c>
       <c r="Z81" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level is_syndicated_flag per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level legal_name per L1 business segment segment.
 </v>
       </c>
       <c r="AA81" t="str">
-        <v>Syndicated Deal Flag (business_segment)</v>
+        <v>Legal Entity (business_segment)</v>
       </c>
       <c r="AB81" t="str">
         <v/>
@@ -7943,17 +8033,17 @@
     </row>
     <row r="82" xml:space="preserve">
       <c r="A82" t="str">
-        <v>REF-016</v>
+        <v>REF-017</v>
       </c>
       <c r="B82" t="str" xml:space="preserve">
-        <v xml:space="preserve">Legal entity booking or owning the exposure. Critical for regulatory capital and entity-level reporting.
+        <v xml:space="preserve">Unique identifier assigned to legal entity in enterprise systems.
 </v>
       </c>
       <c r="C82" t="str">
-        <v>Legal Entity</v>
+        <v>Legal Entity ID</v>
       </c>
       <c r="D82" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of legal_name from counterparty.
+        <v xml:space="preserve">Read legal_entity_id from facility_exposure_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="E82" t="str">
@@ -7972,11 +8062,11 @@
         <v>Raw</v>
       </c>
       <c r="J82" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of legal_name from counterparty.
+        <v xml:space="preserve">Read legal_entity_id from facility_exposure_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="K82" t="str">
-        <v>Legal Entity (facility)</v>
+        <v>Legal Entity ID (facility)</v>
       </c>
       <c r="L82" t="str">
         <v>Y</v>
@@ -7985,11 +8075,11 @@
         <v>Raw</v>
       </c>
       <c r="N82" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of legal_name from counterparty.
+        <v xml:space="preserve">Read legal_entity_id per counterparty.
 </v>
       </c>
       <c r="O82" t="str">
-        <v>Legal Entity (counterparty)</v>
+        <v>Legal Entity ID (counterparty)</v>
       </c>
       <c r="P82" t="str">
         <v>Y</v>
@@ -7998,11 +8088,11 @@
         <v>Agg</v>
       </c>
       <c r="R82" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level legal_name per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level legal_entity_id per L3 desk segment.
 </v>
       </c>
       <c r="S82" t="str">
-        <v>Legal Entity (desk)</v>
+        <v>Legal Entity ID (desk)</v>
       </c>
       <c r="T82" t="str">
         <v>Y</v>
@@ -8011,11 +8101,11 @@
         <v>Agg</v>
       </c>
       <c r="V82" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level legal_name per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level legal_entity_id per L2 portfolio segment.
 </v>
       </c>
       <c r="W82" t="str">
-        <v>Legal Entity (portfolio)</v>
+        <v>Legal Entity ID (portfolio)</v>
       </c>
       <c r="X82" t="str">
         <v>Y</v>
@@ -8024,11 +8114,11 @@
         <v>Agg</v>
       </c>
       <c r="Z82" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level legal_name per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level legal_entity_id per L1 business segment segment.
 </v>
       </c>
       <c r="AA82" t="str">
-        <v>Legal Entity (business_segment)</v>
+        <v>Legal Entity ID (business_segment)</v>
       </c>
       <c r="AB82" t="str">
         <v/>
@@ -8036,17 +8126,17 @@
     </row>
     <row r="83" xml:space="preserve">
       <c r="A83" t="str">
-        <v>REF-017</v>
+        <v>REF-018</v>
       </c>
       <c r="B83" t="str" xml:space="preserve">
-        <v xml:space="preserve">Unique identifier assigned to legal entity in enterprise systems.
+        <v xml:space="preserve">Line of Business classification associated with exposure.
 </v>
       </c>
       <c r="C83" t="str">
-        <v>Legal Entity ID</v>
+        <v>Line of Business Level Name</v>
       </c>
       <c r="D83" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read legal_entity_id from facility_exposure_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
 </v>
       </c>
       <c r="E83" t="str">
@@ -8065,11 +8155,11 @@
         <v>Raw</v>
       </c>
       <c r="J83" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read legal_entity_id from facility_exposure_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
 </v>
       </c>
       <c r="K83" t="str">
-        <v>Legal Entity ID (facility)</v>
+        <v>Line of Business Level Name (facility)</v>
       </c>
       <c r="L83" t="str">
         <v>Y</v>
@@ -8078,11 +8168,11 @@
         <v>Raw</v>
       </c>
       <c r="N83" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read legal_entity_id per counterparty.
+        <v xml:space="preserve">Read parent per counterparty.
 </v>
       </c>
       <c r="O83" t="str">
-        <v>Legal Entity ID (counterparty)</v>
+        <v>Line of Business Level Name (counterparty)</v>
       </c>
       <c r="P83" t="str">
         <v>Y</v>
@@ -8091,11 +8181,11 @@
         <v>Agg</v>
       </c>
       <c r="R83" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level legal_entity_id per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level parent per L3 desk segment.
 </v>
       </c>
       <c r="S83" t="str">
-        <v>Legal Entity ID (desk)</v>
+        <v>Line of Business Level Name (desk)</v>
       </c>
       <c r="T83" t="str">
         <v>Y</v>
@@ -8104,11 +8194,11 @@
         <v>Agg</v>
       </c>
       <c r="V83" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level legal_entity_id per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level parent per L2 portfolio segment.
 </v>
       </c>
       <c r="W83" t="str">
-        <v>Legal Entity ID (portfolio)</v>
+        <v>Line of Business Level Name (portfolio)</v>
       </c>
       <c r="X83" t="str">
         <v>Y</v>
@@ -8117,11 +8207,11 @@
         <v>Agg</v>
       </c>
       <c r="Z83" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level legal_entity_id per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level parent per L1 business segment segment.
 </v>
       </c>
       <c r="AA83" t="str">
-        <v>Legal Entity ID (business_segment)</v>
+        <v>Line of Business Level Name (business_segment)</v>
       </c>
       <c r="AB83" t="str">
         <v/>
@@ -8129,14 +8219,14 @@
     </row>
     <row r="84" xml:space="preserve">
       <c r="A84" t="str">
-        <v>REF-018</v>
+        <v>REF-019</v>
       </c>
       <c r="B84" t="str" xml:space="preserve">
-        <v xml:space="preserve">Line of Business classification associated with exposure.
+        <v xml:space="preserve">Level 1 Line of Business hierarchy. Enables top-level organizational risk aggregation, representing the Department (e.g. Commercial Real Estate, Corporate Banking)
 </v>
       </c>
       <c r="C84" t="str">
-        <v>Line of Business Level Name</v>
+        <v>Line of Business  L1</v>
       </c>
       <c r="D84" t="str" xml:space="preserve">
         <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
@@ -8162,7 +8252,7 @@
 </v>
       </c>
       <c r="K84" t="str">
-        <v>Line of Business Level Name (facility)</v>
+        <v>Line of Business  L1 (facility)</v>
       </c>
       <c r="L84" t="str">
         <v>Y</v>
@@ -8175,7 +8265,7 @@
 </v>
       </c>
       <c r="O84" t="str">
-        <v>Line of Business Level Name (counterparty)</v>
+        <v>Line of Business  L1 (counterparty)</v>
       </c>
       <c r="P84" t="str">
         <v>Y</v>
@@ -8188,7 +8278,7 @@
 </v>
       </c>
       <c r="S84" t="str">
-        <v>Line of Business Level Name (desk)</v>
+        <v>Line of Business  L1 (desk)</v>
       </c>
       <c r="T84" t="str">
         <v>Y</v>
@@ -8201,7 +8291,7 @@
 </v>
       </c>
       <c r="W84" t="str">
-        <v>Line of Business Level Name (portfolio)</v>
+        <v>Line of Business  L1 (portfolio)</v>
       </c>
       <c r="X84" t="str">
         <v>Y</v>
@@ -8214,7 +8304,7 @@
 </v>
       </c>
       <c r="AA84" t="str">
-        <v>Line of Business Level Name (business_segment)</v>
+        <v>Line of Business  L1 (business_segment)</v>
       </c>
       <c r="AB84" t="str">
         <v/>
@@ -8222,14 +8312,14 @@
     </row>
     <row r="85" xml:space="preserve">
       <c r="A85" t="str">
-        <v>REF-019</v>
+        <v>REF-020</v>
       </c>
       <c r="B85" t="str" xml:space="preserve">
-        <v xml:space="preserve">Level 1 Line of Business hierarchy. Enables top-level organizational risk aggregation, representing the Department (e.g. Commercial Real Estate, Corporate Banking)
+        <v xml:space="preserve">Level 2 Line of Business hierarchy for intermediate aggregation and reporting, representing the Portfolio within the L1 LoB (e.g., CRE &gt; Office)
 </v>
       </c>
       <c r="C85" t="str">
-        <v>Line of Business  L1</v>
+        <v>Line of Business L2</v>
       </c>
       <c r="D85" t="str" xml:space="preserve">
         <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
@@ -8255,7 +8345,7 @@
 </v>
       </c>
       <c r="K85" t="str">
-        <v>Line of Business  L1 (facility)</v>
+        <v>Line of Business L2 (facility)</v>
       </c>
       <c r="L85" t="str">
         <v>Y</v>
@@ -8268,7 +8358,7 @@
 </v>
       </c>
       <c r="O85" t="str">
-        <v>Line of Business  L1 (counterparty)</v>
+        <v>Line of Business L2 (counterparty)</v>
       </c>
       <c r="P85" t="str">
         <v>Y</v>
@@ -8281,7 +8371,7 @@
 </v>
       </c>
       <c r="S85" t="str">
-        <v>Line of Business  L1 (desk)</v>
+        <v>Line of Business L2 (desk)</v>
       </c>
       <c r="T85" t="str">
         <v>Y</v>
@@ -8294,7 +8384,7 @@
 </v>
       </c>
       <c r="W85" t="str">
-        <v>Line of Business  L1 (portfolio)</v>
+        <v>Line of Business L2 (portfolio)</v>
       </c>
       <c r="X85" t="str">
         <v>Y</v>
@@ -8307,7 +8397,7 @@
 </v>
       </c>
       <c r="AA85" t="str">
-        <v>Line of Business  L1 (business_segment)</v>
+        <v>Line of Business L2 (business_segment)</v>
       </c>
       <c r="AB85" t="str">
         <v/>
@@ -8315,14 +8405,14 @@
     </row>
     <row r="86" xml:space="preserve">
       <c r="A86" t="str">
-        <v>REF-020</v>
+        <v>REF-021</v>
       </c>
       <c r="B86" t="str" xml:space="preserve">
-        <v xml:space="preserve">Level 2 Line of Business hierarchy for intermediate aggregation and reporting, representing the Portfolio within the L1 LoB (e.g., CRE &gt; Office)
+        <v xml:space="preserve">Level 3 Line of Business hierarchy for detailed business segmentation, representing the Desk within the L2 LoB (e.g. CRE &gt; Office &gt; Lease Up Desk)
 </v>
       </c>
       <c r="C86" t="str">
-        <v>Line of Business L2</v>
+        <v>Line of Business L3</v>
       </c>
       <c r="D86" t="str" xml:space="preserve">
         <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
@@ -8348,7 +8438,7 @@
 </v>
       </c>
       <c r="K86" t="str">
-        <v>Line of Business L2 (facility)</v>
+        <v>Line of Business L3 (facility)</v>
       </c>
       <c r="L86" t="str">
         <v>Y</v>
@@ -8361,7 +8451,7 @@
 </v>
       </c>
       <c r="O86" t="str">
-        <v>Line of Business L2 (counterparty)</v>
+        <v>Line of Business L3 (counterparty)</v>
       </c>
       <c r="P86" t="str">
         <v>Y</v>
@@ -8374,7 +8464,7 @@
 </v>
       </c>
       <c r="S86" t="str">
-        <v>Line of Business L2 (desk)</v>
+        <v>Line of Business L3 (desk)</v>
       </c>
       <c r="T86" t="str">
         <v>Y</v>
@@ -8387,7 +8477,7 @@
 </v>
       </c>
       <c r="W86" t="str">
-        <v>Line of Business L2 (portfolio)</v>
+        <v>Line of Business L3 (portfolio)</v>
       </c>
       <c r="X86" t="str">
         <v>Y</v>
@@ -8400,7 +8490,7 @@
 </v>
       </c>
       <c r="AA86" t="str">
-        <v>Line of Business L2 (business_segment)</v>
+        <v>Line of Business L3 (business_segment)</v>
       </c>
       <c r="AB86" t="str">
         <v/>
@@ -8408,17 +8498,17 @@
     </row>
     <row r="87" xml:space="preserve">
       <c r="A87" t="str">
-        <v>REF-021</v>
+        <v>REF-022</v>
       </c>
       <c r="B87" t="str" xml:space="preserve">
-        <v xml:space="preserve">Level 3 Line of Business hierarchy for detailed business segmentation, representing the Desk within the L2 LoB (e.g. CRE &gt; Office &gt; Lease Up Desk)
+        <v xml:space="preserve">Contractual date on which the facility or loan is scheduled to mature. Used to assess duration exposure, refinancing risk, and liquidity planning. At aggregate levels, returns the nearest (MIN) maturity date as a risk indicator.
 </v>
       </c>
       <c r="C87" t="str">
-        <v>Line of Business L3</v>
+        <v>Maturity Date</v>
       </c>
       <c r="D87" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
+        <v xml:space="preserve">Direct lookup of maturity_date from facility_master.
 </v>
       </c>
       <c r="E87" t="str">
@@ -8437,63 +8527,63 @@
         <v>Raw</v>
       </c>
       <c r="J87" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
+        <v xml:space="preserve">Direct lookup of maturity_date from facility_master.
 </v>
       </c>
       <c r="K87" t="str">
-        <v>Line of Business L3 (facility)</v>
+        <v>Maturity Date (facility)</v>
       </c>
       <c r="L87" t="str">
         <v>Y</v>
       </c>
       <c r="M87" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="N87" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read parent per counterparty.
+        <v xml:space="preserve">Nearest (MIN) maturity date across all facilities per counterparty.
 </v>
       </c>
       <c r="O87" t="str">
-        <v>Line of Business L3 (counterparty)</v>
+        <v>Maturity Date (counterparty)</v>
       </c>
       <c r="P87" t="str">
         <v>Y</v>
       </c>
       <c r="Q87" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R87" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level parent per L3 desk segment.
+        <v xml:space="preserve">Nearest (MIN) maturity date across all facilities per L3 desk segment.
 </v>
       </c>
       <c r="S87" t="str">
-        <v>Line of Business L3 (desk)</v>
+        <v>Maturity Date (desk)</v>
       </c>
       <c r="T87" t="str">
         <v>Y</v>
       </c>
       <c r="U87" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V87" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level parent per L2 portfolio segment.
+        <v xml:space="preserve">Nearest (MIN) maturity date across all facilities per L2 portfolio segment.
 </v>
       </c>
       <c r="W87" t="str">
-        <v>Line of Business L3 (portfolio)</v>
+        <v>Maturity Date (portfolio)</v>
       </c>
       <c r="X87" t="str">
         <v>Y</v>
       </c>
       <c r="Y87" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z87" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level parent per L1 business segment segment.
+        <v xml:space="preserve">Nearest (MIN) maturity date across all facilities per L1 business segment.
 </v>
       </c>
       <c r="AA87" t="str">
-        <v>Line of Business L3 (business_segment)</v>
+        <v>Maturity Date (business_segment)</v>
       </c>
       <c r="AB87" t="str">
         <v/>
@@ -8501,17 +8591,17 @@
     </row>
     <row r="88" xml:space="preserve">
       <c r="A88" t="str">
-        <v>REF-022</v>
+        <v>REF-023</v>
       </c>
       <c r="B88" t="str" xml:space="preserve">
-        <v xml:space="preserve">Contractual date on which the facility or loan is scheduled to mature. Used to assess duration exposure, refinancing risk, and liquidity planning.
+        <v xml:space="preserve">Date on which facility was originally booked and started.
 </v>
       </c>
       <c r="C88" t="str">
-        <v>Maturity Date</v>
+        <v>Facility Origination Date</v>
       </c>
       <c r="D88" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of maturity_date from facility_master.
+        <v xml:space="preserve">Direct lookup of origination_date from facility_master.
 </v>
       </c>
       <c r="E88" t="str">
@@ -8530,11 +8620,11 @@
         <v>Raw</v>
       </c>
       <c r="J88" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of maturity_date from facility_master.
+        <v xml:space="preserve">Direct lookup of origination_date from facility_master.
 </v>
       </c>
       <c r="K88" t="str">
-        <v>Maturity Date (facility)</v>
+        <v>Facility Origination Date (facility)</v>
       </c>
       <c r="L88" t="str">
         <v>Y</v>
@@ -8543,11 +8633,11 @@
         <v>Agg</v>
       </c>
       <c r="N88" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level maturity_date) per counterparty.
+        <v xml:space="preserve">SUM(facility-level origination_date) per counterparty.
 </v>
       </c>
       <c r="O88" t="str">
-        <v>Maturity Date (counterparty)</v>
+        <v>Facility Origination Date (counterparty)</v>
       </c>
       <c r="P88" t="str">
         <v>Y</v>
@@ -8556,11 +8646,11 @@
         <v>Agg</v>
       </c>
       <c r="R88" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level maturity_date per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level origination_date per L3 desk segment.
 </v>
       </c>
       <c r="S88" t="str">
-        <v>Maturity Date (desk)</v>
+        <v>Facility Origination Date (desk)</v>
       </c>
       <c r="T88" t="str">
         <v>Y</v>
@@ -8569,11 +8659,11 @@
         <v>Agg</v>
       </c>
       <c r="V88" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level maturity_date per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level origination_date per L2 portfolio segment.
 </v>
       </c>
       <c r="W88" t="str">
-        <v>Maturity Date (portfolio)</v>
+        <v>Facility Origination Date (portfolio)</v>
       </c>
       <c r="X88" t="str">
         <v>Y</v>
@@ -8582,11 +8672,11 @@
         <v>Agg</v>
       </c>
       <c r="Z88" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level maturity_date per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level origination_date per L1 business segment segment.
 </v>
       </c>
       <c r="AA88" t="str">
-        <v>Maturity Date (business_segment)</v>
+        <v>Facility Origination Date (business_segment)</v>
       </c>
       <c r="AB88" t="str">
         <v/>
@@ -8594,17 +8684,17 @@
     </row>
     <row r="89" xml:space="preserve">
       <c r="A89" t="str">
-        <v>REF-023</v>
+        <v>REF-024</v>
       </c>
       <c r="B89" t="str" xml:space="preserve">
-        <v xml:space="preserve">Date on which facility was originally booked and started.
+        <v xml:space="preserve">Identifiers of counterparties participating in the credit structures or facility as multiple-borrowers. Enables exposure attribution and concentration analysis.
 </v>
       </c>
       <c r="C89" t="str">
-        <v>Facility Origination Date</v>
+        <v>Participating Counterparty IDs</v>
       </c>
       <c r="D89" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of origination_date from facility_master.
+        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
 </v>
       </c>
       <c r="E89" t="str">
@@ -8623,24 +8713,24 @@
         <v>Raw</v>
       </c>
       <c r="J89" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of origination_date from facility_master.
+        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
 </v>
       </c>
       <c r="K89" t="str">
-        <v>Facility Origination Date (facility)</v>
+        <v>Participating Counterparty IDs (facility)</v>
       </c>
       <c r="L89" t="str">
         <v>Y</v>
       </c>
       <c r="M89" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="N89" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level origination_date) per counterparty.
+        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
 </v>
       </c>
       <c r="O89" t="str">
-        <v>Facility Origination Date (counterparty)</v>
+        <v>Participating Counterparty IDs (counterparty)</v>
       </c>
       <c r="P89" t="str">
         <v>Y</v>
@@ -8649,11 +8739,11 @@
         <v>Agg</v>
       </c>
       <c r="R89" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level origination_date per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level counterparty_id per L3 desk segment.
 </v>
       </c>
       <c r="S89" t="str">
-        <v>Facility Origination Date (desk)</v>
+        <v>Participating Counterparty IDs (desk)</v>
       </c>
       <c r="T89" t="str">
         <v>Y</v>
@@ -8662,11 +8752,11 @@
         <v>Agg</v>
       </c>
       <c r="V89" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level origination_date per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level counterparty_id per L2 portfolio segment.
 </v>
       </c>
       <c r="W89" t="str">
-        <v>Facility Origination Date (portfolio)</v>
+        <v>Participating Counterparty IDs (portfolio)</v>
       </c>
       <c r="X89" t="str">
         <v>Y</v>
@@ -8675,11 +8765,11 @@
         <v>Agg</v>
       </c>
       <c r="Z89" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level origination_date per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level counterparty_id per L1 business segment segment.
 </v>
       </c>
       <c r="AA89" t="str">
-        <v>Facility Origination Date (business_segment)</v>
+        <v>Participating Counterparty IDs (business_segment)</v>
       </c>
       <c r="AB89" t="str">
         <v/>
@@ -8687,17 +8777,17 @@
     </row>
     <row r="90" xml:space="preserve">
       <c r="A90" t="str">
-        <v>REF-024</v>
+        <v>REF-025</v>
       </c>
       <c r="B90" t="str" xml:space="preserve">
-        <v xml:space="preserve">Identifiers of counterparties participating in the credit structures or facility as multiple-borrowers. Enables exposure attribution and concentration analysis.
+        <v xml:space="preserve">Product classification assigned to the contract offering. Supports product- level segmentation and performance analysis.
 </v>
       </c>
       <c r="C90" t="str">
-        <v>Participating Counterparty IDs</v>
+        <v>Product</v>
       </c>
       <c r="D90" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">SUM(product_id) per facility from facility_exposure_snapshot.
 </v>
       </c>
       <c r="E90" t="str">
@@ -8713,27 +8803,27 @@
         <v>Y</v>
       </c>
       <c r="I90" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="J90" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">SUM(product_id) per facility from facility_exposure_snapshot.
 </v>
       </c>
       <c r="K90" t="str">
-        <v>Participating Counterparty IDs (facility)</v>
+        <v>Product (facility)</v>
       </c>
       <c r="L90" t="str">
         <v>Y</v>
       </c>
       <c r="M90" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="N90" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">SUM of facility-level product_id per counterparty.
 </v>
       </c>
       <c r="O90" t="str">
-        <v>Participating Counterparty IDs (counterparty)</v>
+        <v>Product (counterparty)</v>
       </c>
       <c r="P90" t="str">
         <v>Y</v>
@@ -8742,11 +8832,11 @@
         <v>Agg</v>
       </c>
       <c r="R90" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level product_id per L3 desk segment.
 </v>
       </c>
       <c r="S90" t="str">
-        <v>Participating Counterparty IDs (desk)</v>
+        <v>Product (desk)</v>
       </c>
       <c r="T90" t="str">
         <v>Y</v>
@@ -8755,11 +8845,11 @@
         <v>Agg</v>
       </c>
       <c r="V90" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level product_id per L2 portfolio segment.
 </v>
       </c>
       <c r="W90" t="str">
-        <v>Participating Counterparty IDs (portfolio)</v>
+        <v>Product (portfolio)</v>
       </c>
       <c r="X90" t="str">
         <v>Y</v>
@@ -8768,11 +8858,11 @@
         <v>Agg</v>
       </c>
       <c r="Z90" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level product_id per L1 business segment segment.
 </v>
       </c>
       <c r="AA90" t="str">
-        <v>Participating Counterparty IDs (business_segment)</v>
+        <v>Product (business_segment)</v>
       </c>
       <c r="AB90" t="str">
         <v/>
@@ -8780,17 +8870,17 @@
     </row>
     <row r="91" xml:space="preserve">
       <c r="A91" t="str">
-        <v>REF-025</v>
+        <v>REF-026</v>
       </c>
       <c r="B91" t="str" xml:space="preserve">
-        <v xml:space="preserve">Product classification assigned to the contract offering. Supports product- level segmentation and performance analysis.
+        <v xml:space="preserve">Geographic region classification tied to location of deal origination, supporting portfolio segmentation and concentration monitoring.
 </v>
       </c>
       <c r="C91" t="str">
-        <v>Product</v>
+        <v>Region</v>
       </c>
       <c r="D91" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(product_id) per facility from facility_exposure_snapshot.
+        <v xml:space="preserve">Direct lookup of region_code from counterparty.
 </v>
       </c>
       <c r="E91" t="str">
@@ -8806,27 +8896,27 @@
         <v>Y</v>
       </c>
       <c r="I91" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="J91" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(product_id) per facility from facility_exposure_snapshot.
+        <v xml:space="preserve">Direct lookup of region_code from counterparty.
 </v>
       </c>
       <c r="K91" t="str">
-        <v>Product (facility)</v>
+        <v>Region (facility)</v>
       </c>
       <c r="L91" t="str">
         <v>Y</v>
       </c>
       <c r="M91" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="N91" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level product_id per counterparty.
+        <v xml:space="preserve">Direct lookup of region_code from counterparty.
 </v>
       </c>
       <c r="O91" t="str">
-        <v>Product (counterparty)</v>
+        <v>Region (counterparty)</v>
       </c>
       <c r="P91" t="str">
         <v>Y</v>
@@ -8835,11 +8925,11 @@
         <v>Agg</v>
       </c>
       <c r="R91" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level product_id per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level region_code per L3 desk segment.
 </v>
       </c>
       <c r="S91" t="str">
-        <v>Product (desk)</v>
+        <v>Region (desk)</v>
       </c>
       <c r="T91" t="str">
         <v>Y</v>
@@ -8848,11 +8938,11 @@
         <v>Agg</v>
       </c>
       <c r="V91" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level product_id per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level region_code per L2 portfolio segment.
 </v>
       </c>
       <c r="W91" t="str">
-        <v>Product (portfolio)</v>
+        <v>Region (portfolio)</v>
       </c>
       <c r="X91" t="str">
         <v>Y</v>
@@ -8861,11 +8951,11 @@
         <v>Agg</v>
       </c>
       <c r="Z91" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level product_id per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level region_code per L1 business segment segment.
 </v>
       </c>
       <c r="AA91" t="str">
-        <v>Product (business_segment)</v>
+        <v>Region (business_segment)</v>
       </c>
       <c r="AB91" t="str">
         <v/>
@@ -8873,17 +8963,17 @@
     </row>
     <row r="92" xml:space="preserve">
       <c r="A92" t="str">
-        <v>REF-026</v>
+        <v>REF-027</v>
       </c>
       <c r="B92" t="str" xml:space="preserve">
-        <v xml:space="preserve">Geographic region classification tied to location of deal origination, supporting portfolio segmentation and concentration monitoring.
+        <v xml:space="preserve">Industry sector classification of the counterparty, enabling sector concentration risk assessment.
 </v>
       </c>
       <c r="C92" t="str">
-        <v>Region</v>
+        <v>Sector</v>
       </c>
       <c r="D92" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of region_code from counterparty.
+        <v xml:space="preserve">Direct lookup of industry_name from industry_dim.
 </v>
       </c>
       <c r="E92" t="str">
@@ -8902,11 +8992,11 @@
         <v>Raw</v>
       </c>
       <c r="J92" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of region_code from counterparty.
+        <v xml:space="preserve">Direct lookup of industry_name from industry_dim.
 </v>
       </c>
       <c r="K92" t="str">
-        <v>Region (facility)</v>
+        <v>Sector (facility)</v>
       </c>
       <c r="L92" t="str">
         <v>Y</v>
@@ -8915,11 +9005,11 @@
         <v>Raw</v>
       </c>
       <c r="N92" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of region_code from counterparty.
+        <v xml:space="preserve">Read industry_name per counterparty.
 </v>
       </c>
       <c r="O92" t="str">
-        <v>Region (counterparty)</v>
+        <v>Sector (counterparty)</v>
       </c>
       <c r="P92" t="str">
         <v>Y</v>
@@ -8928,11 +9018,11 @@
         <v>Agg</v>
       </c>
       <c r="R92" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level region_code per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level industry_name per L3 desk segment.
 </v>
       </c>
       <c r="S92" t="str">
-        <v>Region (desk)</v>
+        <v>Sector (desk)</v>
       </c>
       <c r="T92" t="str">
         <v>Y</v>
@@ -8941,11 +9031,11 @@
         <v>Agg</v>
       </c>
       <c r="V92" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level region_code per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level industry_name per L2 portfolio segment.
 </v>
       </c>
       <c r="W92" t="str">
-        <v>Region (portfolio)</v>
+        <v>Sector (portfolio)</v>
       </c>
       <c r="X92" t="str">
         <v>Y</v>
@@ -8954,11 +9044,11 @@
         <v>Agg</v>
       </c>
       <c r="Z92" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level region_code per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level industry_name per L1 business segment segment.
 </v>
       </c>
       <c r="AA92" t="str">
-        <v>Region (business_segment)</v>
+        <v>Sector (business_segment)</v>
       </c>
       <c r="AB92" t="str">
         <v/>
@@ -8966,17 +9056,17 @@
     </row>
     <row r="93" xml:space="preserve">
       <c r="A93" t="str">
-        <v>REF-027</v>
+        <v>REF-028</v>
       </c>
       <c r="B93" t="str" xml:space="preserve">
-        <v xml:space="preserve">Industry sector classification of the counterparty, enabling sector concentration risk assessment.
+        <v xml:space="preserve">Number of unique active facilities within the reporting period.
 </v>
       </c>
       <c r="C93" t="str">
-        <v>Sector</v>
+        <v>Number of Facilities</v>
       </c>
       <c r="D93" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of industry_name from industry_dim.
+        <v xml:space="preserve">Read number_of_facilities from facility_exposure_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="E93" t="str">
@@ -8995,24 +9085,24 @@
         <v>Raw</v>
       </c>
       <c r="J93" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of industry_name from industry_dim.
+        <v xml:space="preserve">Read number_of_facilities from facility_exposure_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="K93" t="str">
-        <v>Sector (facility)</v>
+        <v>Number of Facilities (facility)</v>
       </c>
       <c r="L93" t="str">
         <v>Y</v>
       </c>
       <c r="M93" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="N93" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read industry_name per counterparty.
+        <v xml:space="preserve">SUM of facility-level number_of_facilities per counterparty.
 </v>
       </c>
       <c r="O93" t="str">
-        <v>Sector (counterparty)</v>
+        <v>Number of Facilities (counterparty)</v>
       </c>
       <c r="P93" t="str">
         <v>Y</v>
@@ -9021,11 +9111,11 @@
         <v>Agg</v>
       </c>
       <c r="R93" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level industry_name per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level number_of_facilities per L3 desk segment.
 </v>
       </c>
       <c r="S93" t="str">
-        <v>Sector (desk)</v>
+        <v>Number of Facilities (desk)</v>
       </c>
       <c r="T93" t="str">
         <v>Y</v>
@@ -9034,11 +9124,11 @@
         <v>Agg</v>
       </c>
       <c r="V93" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level industry_name per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level number_of_facilities per L2 portfolio segment.
 </v>
       </c>
       <c r="W93" t="str">
-        <v>Sector (portfolio)</v>
+        <v>Number of Facilities (portfolio)</v>
       </c>
       <c r="X93" t="str">
         <v>Y</v>
@@ -9047,11 +9137,11 @@
         <v>Agg</v>
       </c>
       <c r="Z93" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level industry_name per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level number_of_facilities per L1 business segment segment.
 </v>
       </c>
       <c r="AA93" t="str">
-        <v>Sector (business_segment)</v>
+        <v>Number of Facilities (business_segment)</v>
       </c>
       <c r="AB93" t="str">
         <v/>
@@ -9059,17 +9149,17 @@
     </row>
     <row r="94" xml:space="preserve">
       <c r="A94" t="str">
-        <v>REF-028</v>
+        <v>REF-029</v>
       </c>
       <c r="B94" t="str" xml:space="preserve">
-        <v xml:space="preserve">Number of unique active facilities within the reporting period.
+        <v xml:space="preserve">Represents “hard” equity after removing intangibles; reflects true loss- absorbing capacity, covenant strength, and resilience under downside scenarios.
 </v>
       </c>
       <c r="C94" t="str">
-        <v>Number of Facilities</v>
+        <v>Tangible Net Worth</v>
       </c>
       <c r="D94" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read number_of_facilities from facility_exposure_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Read tangible_net_worth_usd from counterparty_financial_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="E94" t="str">
@@ -9088,24 +9178,24 @@
         <v>Raw</v>
       </c>
       <c r="J94" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read number_of_facilities from facility_exposure_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Read tangible_net_worth_usd from counterparty_financial_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="K94" t="str">
-        <v>Number of Facilities (facility)</v>
+        <v>Tangible Net Worth (facility)</v>
       </c>
       <c r="L94" t="str">
         <v>Y</v>
       </c>
       <c r="M94" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="N94" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level number_of_facilities per counterparty.
+        <v xml:space="preserve">Read tangible_net_worth_usd per counterparty.
 </v>
       </c>
       <c r="O94" t="str">
-        <v>Number of Facilities (counterparty)</v>
+        <v>Tangible Net Worth (counterparty)</v>
       </c>
       <c r="P94" t="str">
         <v>Y</v>
@@ -9114,11 +9204,11 @@
         <v>Agg</v>
       </c>
       <c r="R94" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level number_of_facilities per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level tangible_net_worth_usd per L3 desk segment.
 </v>
       </c>
       <c r="S94" t="str">
-        <v>Number of Facilities (desk)</v>
+        <v>Tangible Net Worth (desk)</v>
       </c>
       <c r="T94" t="str">
         <v>Y</v>
@@ -9127,11 +9217,11 @@
         <v>Agg</v>
       </c>
       <c r="V94" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level number_of_facilities per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level tangible_net_worth_usd per L2 portfolio segment.
 </v>
       </c>
       <c r="W94" t="str">
-        <v>Number of Facilities (portfolio)</v>
+        <v>Tangible Net Worth (portfolio)</v>
       </c>
       <c r="X94" t="str">
         <v>Y</v>
@@ -9140,11 +9230,11 @@
         <v>Agg</v>
       </c>
       <c r="Z94" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level number_of_facilities per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level tangible_net_worth_usd per L1 business segment segment.
 </v>
       </c>
       <c r="AA94" t="str">
-        <v>Number of Facilities (business_segment)</v>
+        <v>Tangible Net Worth (business_segment)</v>
       </c>
       <c r="AB94" t="str">
         <v/>
@@ -9152,17 +9242,17 @@
     </row>
     <row r="95" xml:space="preserve">
       <c r="A95" t="str">
-        <v>REF-029</v>
+        <v>REF-030</v>
       </c>
       <c r="B95" t="str" xml:space="preserve">
-        <v xml:space="preserve">Represents “hard” equity after removing intangibles; reflects true loss- absorbing capacity, covenant strength, and resilience under downside scenarios.
+        <v xml:space="preserve">Bucketing mechanism to calculate Maturity Dates supporting the identification of upcoming liquidations in the next 90 days
 </v>
       </c>
       <c r="C95" t="str">
-        <v>Tangible Net Worth</v>
+        <v>Maturity Date Bucket</v>
       </c>
       <c r="D95" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read tangible_net_worth_usd from counterparty_financial_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Calculated maturity_bucket_id per facility.
 </v>
       </c>
       <c r="E95" t="str">
@@ -9178,27 +9268,27 @@
         <v>Y</v>
       </c>
       <c r="I95" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="J95" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read tangible_net_worth_usd from counterparty_financial_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Calculated maturity_bucket_id per facility.
 </v>
       </c>
       <c r="K95" t="str">
-        <v>Tangible Net Worth (facility)</v>
+        <v>Maturity Date Bucket (facility)</v>
       </c>
       <c r="L95" t="str">
         <v>Y</v>
       </c>
       <c r="M95" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="N95" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read tangible_net_worth_usd per counterparty.
+        <v xml:space="preserve">SUM(facility-level maturity_bucket_id) per counterparty.
 </v>
       </c>
       <c r="O95" t="str">
-        <v>Tangible Net Worth (counterparty)</v>
+        <v>Maturity Date Bucket (counterparty)</v>
       </c>
       <c r="P95" t="str">
         <v>Y</v>
@@ -9207,11 +9297,11 @@
         <v>Agg</v>
       </c>
       <c r="R95" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level tangible_net_worth_usd per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level maturity_bucket_id per L3 desk segment.
 </v>
       </c>
       <c r="S95" t="str">
-        <v>Tangible Net Worth (desk)</v>
+        <v>Maturity Date Bucket (desk)</v>
       </c>
       <c r="T95" t="str">
         <v>Y</v>
@@ -9220,11 +9310,11 @@
         <v>Agg</v>
       </c>
       <c r="V95" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level tangible_net_worth_usd per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level maturity_bucket_id per L2 portfolio segment.
 </v>
       </c>
       <c r="W95" t="str">
-        <v>Tangible Net Worth (portfolio)</v>
+        <v>Maturity Date Bucket (portfolio)</v>
       </c>
       <c r="X95" t="str">
         <v>Y</v>
@@ -9233,11 +9323,11 @@
         <v>Agg</v>
       </c>
       <c r="Z95" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level tangible_net_worth_usd per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level maturity_bucket_id per L1 business segment segment.
 </v>
       </c>
       <c r="AA95" t="str">
-        <v>Tangible Net Worth (business_segment)</v>
+        <v>Maturity Date Bucket (business_segment)</v>
       </c>
       <c r="AB95" t="str">
         <v/>
@@ -9245,17 +9335,17 @@
     </row>
     <row r="96" xml:space="preserve">
       <c r="A96" t="str">
-        <v>REF-030</v>
+        <v>REF-031</v>
       </c>
       <c r="B96" t="str" xml:space="preserve">
-        <v xml:space="preserve">Bucketing mechanism to calculate Maturity Dates supporting the identification of upcoming liquidations in the next 90 days
+        <v xml:space="preserve">Bucketing mechanism to calculate Origination Dates supporting the identification of upcoming facilities starting commitments in the next 90 days
 </v>
       </c>
       <c r="C96" t="str">
-        <v>Maturity Date Bucket</v>
+        <v>Origination Date Bucket</v>
       </c>
       <c r="D96" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated maturity_bucket_id per facility.
+        <v xml:space="preserve">Calculated origination_date_bucket per facility.
 </v>
       </c>
       <c r="E96" t="str">
@@ -9274,11 +9364,11 @@
         <v>Calc</v>
       </c>
       <c r="J96" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated maturity_bucket_id per facility.
+        <v xml:space="preserve">Calculated origination_date_bucket per facility.
 </v>
       </c>
       <c r="K96" t="str">
-        <v>Maturity Date Bucket (facility)</v>
+        <v>Origination Date Bucket (facility)</v>
       </c>
       <c r="L96" t="str">
         <v>Y</v>
@@ -9287,11 +9377,11 @@
         <v>Agg</v>
       </c>
       <c r="N96" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level maturity_bucket_id) per counterparty.
+        <v xml:space="preserve">SUM(facility-level origination_date_bucket) per counterparty.
 </v>
       </c>
       <c r="O96" t="str">
-        <v>Maturity Date Bucket (counterparty)</v>
+        <v>Origination Date Bucket (counterparty)</v>
       </c>
       <c r="P96" t="str">
         <v>Y</v>
@@ -9300,11 +9390,11 @@
         <v>Agg</v>
       </c>
       <c r="R96" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level maturity_bucket_id per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level origination_date_bucket per L3 desk segment.
 </v>
       </c>
       <c r="S96" t="str">
-        <v>Maturity Date Bucket (desk)</v>
+        <v>Origination Date Bucket (desk)</v>
       </c>
       <c r="T96" t="str">
         <v>Y</v>
@@ -9313,11 +9403,11 @@
         <v>Agg</v>
       </c>
       <c r="V96" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level maturity_bucket_id per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level origination_date_bucket per L2 portfolio segment.
 </v>
       </c>
       <c r="W96" t="str">
-        <v>Maturity Date Bucket (portfolio)</v>
+        <v>Origination Date Bucket (portfolio)</v>
       </c>
       <c r="X96" t="str">
         <v>Y</v>
@@ -9326,11 +9416,11 @@
         <v>Agg</v>
       </c>
       <c r="Z96" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level maturity_bucket_id per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level origination_date_bucket per L1 business segment segment.
 </v>
       </c>
       <c r="AA96" t="str">
-        <v>Maturity Date Bucket (business_segment)</v>
+        <v>Origination Date Bucket (business_segment)</v>
       </c>
       <c r="AB96" t="str">
         <v/>
@@ -9338,17 +9428,17 @@
     </row>
     <row r="97" xml:space="preserve">
       <c r="A97" t="str">
-        <v>REF-031</v>
+        <v>REF-032</v>
       </c>
       <c r="B97" t="str" xml:space="preserve">
-        <v xml:space="preserve">Bucketing mechanism to calculate Origination Dates supporting the identification of upcoming facilities starting commitments in the next 90 days
+        <v xml:space="preserve">Capturing distirbution of facilities starting or liquidating in 90 day windows
 </v>
       </c>
       <c r="C97" t="str">
-        <v>Origination Date Bucket</v>
+        <v>Effective Date Bucket</v>
       </c>
       <c r="D97" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated origination_date_bucket per facility.
+        <v xml:space="preserve">Calculated effective_date_bucket per facility.
 </v>
       </c>
       <c r="E97" t="str">
@@ -9367,11 +9457,11 @@
         <v>Calc</v>
       </c>
       <c r="J97" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated origination_date_bucket per facility.
+        <v xml:space="preserve">Calculated effective_date_bucket per facility.
 </v>
       </c>
       <c r="K97" t="str">
-        <v>Origination Date Bucket (facility)</v>
+        <v>Effective Date Bucket (facility)</v>
       </c>
       <c r="L97" t="str">
         <v>Y</v>
@@ -9380,11 +9470,11 @@
         <v>Agg</v>
       </c>
       <c r="N97" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level origination_date_bucket) per counterparty.
+        <v xml:space="preserve">SUM(facility-level effective_date_bucket) per counterparty.
 </v>
       </c>
       <c r="O97" t="str">
-        <v>Origination Date Bucket (counterparty)</v>
+        <v>Effective Date Bucket (counterparty)</v>
       </c>
       <c r="P97" t="str">
         <v>Y</v>
@@ -9393,11 +9483,11 @@
         <v>Agg</v>
       </c>
       <c r="R97" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level origination_date_bucket per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level effective_date_bucket per L3 desk segment.
 </v>
       </c>
       <c r="S97" t="str">
-        <v>Origination Date Bucket (desk)</v>
+        <v>Effective Date Bucket (desk)</v>
       </c>
       <c r="T97" t="str">
         <v>Y</v>
@@ -9406,11 +9496,11 @@
         <v>Agg</v>
       </c>
       <c r="V97" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level origination_date_bucket per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level effective_date_bucket per L2 portfolio segment.
 </v>
       </c>
       <c r="W97" t="str">
-        <v>Origination Date Bucket (portfolio)</v>
+        <v>Effective Date Bucket (portfolio)</v>
       </c>
       <c r="X97" t="str">
         <v>Y</v>
@@ -9419,11 +9509,11 @@
         <v>Agg</v>
       </c>
       <c r="Z97" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level origination_date_bucket per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level effective_date_bucket per L1 business segment segment.
 </v>
       </c>
       <c r="AA97" t="str">
-        <v>Origination Date Bucket (business_segment)</v>
+        <v>Effective Date Bucket (business_segment)</v>
       </c>
       <c r="AB97" t="str">
         <v/>
@@ -9431,17 +9521,17 @@
     </row>
     <row r="98" xml:space="preserve">
       <c r="A98" t="str">
-        <v>REF-032</v>
+        <v>REF-033</v>
       </c>
       <c r="B98" t="str" xml:space="preserve">
-        <v xml:space="preserve">Capturing distirbution of facilities starting or liquidating in 90 day windows
+        <v xml:space="preserve">Boolean indicator to depict when a Facility is currently active in the reporting period (e.g., Facility Status is not Canceled or Closed)
 </v>
       </c>
       <c r="C98" t="str">
-        <v>Effective Date Bucket</v>
+        <v>Facility Active Flag</v>
       </c>
       <c r="D98" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated effective_date_bucket per facility.
+        <v xml:space="preserve">Calculated facility_is_active_flag per facility.
 </v>
       </c>
       <c r="E98" t="str">
@@ -9460,11 +9550,11 @@
         <v>Calc</v>
       </c>
       <c r="J98" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated effective_date_bucket per facility.
+        <v xml:space="preserve">Calculated facility_is_active_flag per facility.
 </v>
       </c>
       <c r="K98" t="str">
-        <v>Effective Date Bucket (facility)</v>
+        <v>Facility Active Flag (facility)</v>
       </c>
       <c r="L98" t="str">
         <v>Y</v>
@@ -9473,11 +9563,11 @@
         <v>Agg</v>
       </c>
       <c r="N98" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level effective_date_bucket) per counterparty.
+        <v xml:space="preserve">SUM(facility-level facility_is_active_flag) per counterparty.
 </v>
       </c>
       <c r="O98" t="str">
-        <v>Effective Date Bucket (counterparty)</v>
+        <v>Facility Active Flag (counterparty)</v>
       </c>
       <c r="P98" t="str">
         <v>Y</v>
@@ -9486,11 +9576,11 @@
         <v>Agg</v>
       </c>
       <c r="R98" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level effective_date_bucket per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level facility_is_active_flag per L3 desk segment.
 </v>
       </c>
       <c r="S98" t="str">
-        <v>Effective Date Bucket (desk)</v>
+        <v>Facility Active Flag (desk)</v>
       </c>
       <c r="T98" t="str">
         <v>Y</v>
@@ -9499,11 +9589,11 @@
         <v>Agg</v>
       </c>
       <c r="V98" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level effective_date_bucket per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level facility_is_active_flag per L2 portfolio segment.
 </v>
       </c>
       <c r="W98" t="str">
-        <v>Effective Date Bucket (portfolio)</v>
+        <v>Facility Active Flag (portfolio)</v>
       </c>
       <c r="X98" t="str">
         <v>Y</v>
@@ -9512,11 +9602,11 @@
         <v>Agg</v>
       </c>
       <c r="Z98" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level effective_date_bucket per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level facility_is_active_flag per L1 business segment segment.
 </v>
       </c>
       <c r="AA98" t="str">
-        <v>Effective Date Bucket (business_segment)</v>
+        <v>Facility Active Flag (business_segment)</v>
       </c>
       <c r="AB98" t="str">
         <v/>
@@ -9524,17 +9614,17 @@
     </row>
     <row r="99" xml:space="preserve">
       <c r="A99" t="str">
-        <v>REF-033</v>
+        <v>RSK-001</v>
       </c>
       <c r="B99" t="str" xml:space="preserve">
-        <v xml:space="preserve">Boolean indicator to depict when a Facility is currently active in the reporting period (e.g., Facility Status is not Canceled or Closed)
+        <v xml:space="preserve">Risk rating tier derived from counterparty probability of default (PD). Each counterparty's pd_annual is matched against the risk_rating_tier_dim reference table (pd_min_pct / pd_max_pct boundaries) to assign a tier classification. At facility level, the tier is inherited from the owning counterparty. At aggregate levels, MAX (worst-case) tier ordinal is reported.
 </v>
       </c>
       <c r="C99" t="str">
-        <v>Facility Active Flag</v>
+        <v>Risk Rating Tier</v>
       </c>
       <c r="D99" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated facility_is_active_flag per facility.
+        <v xml:space="preserve">For each facility, inherit the risk rating tier from the owning counterparty. Join facility_master to counterparty, then range-match counterparty pd_annual against risk_rating_tier_dim to derive the tier ordinal (display_order).
 </v>
       </c>
       <c r="E99" t="str">
@@ -9553,24 +9643,24 @@
         <v>Calc</v>
       </c>
       <c r="J99" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated facility_is_active_flag per facility.
+        <v xml:space="preserve">For each facility, inherit the risk rating tier from the owning counterparty. Join facility_master to counterparty, then range-match counterparty pd_annual against risk_rating_tier_dim to derive the tier ordinal (display_order).
 </v>
       </c>
       <c r="K99" t="str">
-        <v>Facility Active Flag (facility)</v>
+        <v>Risk Rating Tier (facility)</v>
       </c>
       <c r="L99" t="str">
         <v>Y</v>
       </c>
       <c r="M99" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N99" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level facility_is_active_flag) per counterparty.
+        <v xml:space="preserve">For each counterparty, look up pd_annual and range-match against risk_rating_tier_dim where pd_annual &gt;= pd_min_pct AND pd_annual &lt; pd_max_pct. Returns the tier ordinal (display_order). Counterparties with NULL PD receive tier 0 (unrated).
 </v>
       </c>
       <c r="O99" t="str">
-        <v>Facility Active Flag (counterparty)</v>
+        <v>Risk Rating Tier (counterparty)</v>
       </c>
       <c r="P99" t="str">
         <v>Y</v>
@@ -9579,11 +9669,11 @@
         <v>Agg</v>
       </c>
       <c r="R99" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_is_active_flag per L3 desk segment.
+        <v xml:space="preserve">Worst-case (MAX) risk rating tier ordinal across all counterparties in the L3 desk segment. Higher ordinal = riskier tier. Full tier distribution available via counterparty-level drill-down.
 </v>
       </c>
       <c r="S99" t="str">
-        <v>Facility Active Flag (desk)</v>
+        <v>Risk Rating Tier (desk)</v>
       </c>
       <c r="T99" t="str">
         <v>Y</v>
@@ -9592,11 +9682,11 @@
         <v>Agg</v>
       </c>
       <c r="V99" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_is_active_flag per L2 portfolio segment.
+        <v xml:space="preserve">Worst-case (MAX) risk rating tier ordinal per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
 </v>
       </c>
       <c r="W99" t="str">
-        <v>Facility Active Flag (portfolio)</v>
+        <v>Risk Rating Tier (portfolio)</v>
       </c>
       <c r="X99" t="str">
         <v>Y</v>
@@ -9605,11 +9695,11 @@
         <v>Agg</v>
       </c>
       <c r="Z99" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_is_active_flag per L1 business segment segment.
+        <v xml:space="preserve">Worst-case (MAX) risk rating tier ordinal per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
 </v>
       </c>
       <c r="AA99" t="str">
-        <v>Facility Active Flag (business_segment)</v>
+        <v>Risk Rating Tier (business_segment)</v>
       </c>
       <c r="AB99" t="str">
         <v/>
@@ -9617,17 +9707,17 @@
     </row>
     <row r="100" xml:space="preserve">
       <c r="A100" t="str">
-        <v>RSK-001</v>
+        <v>RSK-002</v>
       </c>
       <c r="B100" t="str" xml:space="preserve">
-        <v xml:space="preserve">Most recent internal credit rating assigned at reporting date. Used for segmentation and exposure-weighted risk aggregation.
+        <v xml:space="preserve">Current external credit agency rating assigned to the obligor. Used for benchmarking, regulatory reporting, and external credit risk validation. Sourced based on external Rating provider (S&amp;P, Moodys, Fitch) - populated based on firm's preferred recognized rating provider.
 </v>
       </c>
       <c r="C100" t="str">
-        <v>Risk Rating Tier</v>
+        <v>Risk Rating - External Rating</v>
       </c>
       <c r="D100" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility.
+        <v xml:space="preserve">Read external_risk_rating from position for each facility as-of reporting date.
 </v>
       </c>
       <c r="E100" t="str">
@@ -9646,63 +9736,63 @@
         <v>Raw</v>
       </c>
       <c r="J100" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility.
+        <v xml:space="preserve">Read external_risk_rating from position for each facility as-of reporting date.
 </v>
       </c>
       <c r="K100" t="str">
-        <v>Risk Rating Tier (facility)</v>
+        <v>Risk Rating - External Rating (facility)</v>
       </c>
       <c r="L100" t="str">
         <v>Y</v>
       </c>
       <c r="M100" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="N100" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating per counterparty.
+        <v xml:space="preserve">Read external_risk_rating per counterparty.
 </v>
       </c>
       <c r="O100" t="str">
-        <v>Risk Rating Tier (counterparty)</v>
+        <v>Risk Rating - External Rating (counterparty)</v>
       </c>
       <c r="P100" t="str">
         <v>Y</v>
       </c>
       <c r="Q100" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="R100" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating per L3 desk segment.
+        <v xml:space="preserve">AVG of facility-level external_risk_rating per L3 desk segment.
 </v>
       </c>
       <c r="S100" t="str">
-        <v>Risk Rating Tier (desk)</v>
+        <v>Risk Rating - External Rating (desk)</v>
       </c>
       <c r="T100" t="str">
         <v>Y</v>
       </c>
       <c r="U100" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="V100" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating per L2 portfolio segment.
+        <v xml:space="preserve">AVG of facility-level external_risk_rating per L2 portfolio segment.
 </v>
       </c>
       <c r="W100" t="str">
-        <v>Risk Rating Tier (portfolio)</v>
+        <v>Risk Rating - External Rating (portfolio)</v>
       </c>
       <c r="X100" t="str">
         <v>Y</v>
       </c>
       <c r="Y100" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="Z100" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating per L1 business segment.
+        <v xml:space="preserve">AVG of facility-level external_risk_rating per L1 business segment segment.
 </v>
       </c>
       <c r="AA100" t="str">
-        <v>Risk Rating Tier (business_segment)</v>
+        <v>Risk Rating - External Rating (business_segment)</v>
       </c>
       <c r="AB100" t="str">
         <v/>
@@ -9710,17 +9800,17 @@
     </row>
     <row r="101" xml:space="preserve">
       <c r="A101" t="str">
-        <v>RSK-002</v>
+        <v>RSK-003</v>
       </c>
       <c r="B101" t="str" xml:space="preserve">
-        <v xml:space="preserve">Current external credit agency rating assigned to the obligor. Used for benchmarking, regulatory reporting, and external credit risk validation. Sourced based on external Rating provider (S&amp;P, Moodys, Fitch) - populated based on firm's preferred recognized rating provider.
+        <v xml:space="preserve">The institution’s internally assigned credit risk grade for a borrower, facility, or exposure as of a given date, reflecting its assessment of default risk according to the firm’s internal rating scale/model.
 </v>
       </c>
       <c r="C101" t="str">
-        <v>Risk Rating - External Rating</v>
+        <v>Risk Rating - Internal Risk Rating</v>
       </c>
       <c r="D101" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read external_risk_rating from position for each facility as-of reporting date.
+        <v xml:space="preserve">Read internal_risk_rating from facility_risk_snapshot for each facility.
 </v>
       </c>
       <c r="E101" t="str">
@@ -9739,63 +9829,63 @@
         <v>Raw</v>
       </c>
       <c r="J101" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read external_risk_rating from position for each facility as-of reporting date.
+        <v xml:space="preserve">Read internal_risk_rating from facility_risk_snapshot for each facility.
 </v>
       </c>
       <c r="K101" t="str">
-        <v>Risk Rating - External Rating (facility)</v>
+        <v>Risk Rating - Internal Risk Rating (facility)</v>
       </c>
       <c r="L101" t="str">
         <v>Y</v>
       </c>
       <c r="M101" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="N101" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read external_risk_rating per counterparty.
+        <v xml:space="preserve">COUNT of facilities with internal risk rating per counterparty.
 </v>
       </c>
       <c r="O101" t="str">
-        <v>Risk Rating - External Rating (counterparty)</v>
+        <v>Risk Rating - Internal Risk Rating (counterparty)</v>
       </c>
       <c r="P101" t="str">
         <v>Y</v>
       </c>
       <c r="Q101" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="R101" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level external_risk_rating per L3 desk segment.
+        <v xml:space="preserve">COUNT of facilities with internal risk rating per L3 desk segment.
 </v>
       </c>
       <c r="S101" t="str">
-        <v>Risk Rating - External Rating (desk)</v>
+        <v>Risk Rating - Internal Risk Rating (desk)</v>
       </c>
       <c r="T101" t="str">
         <v>Y</v>
       </c>
       <c r="U101" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="V101" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level external_risk_rating per L2 portfolio segment.
+        <v xml:space="preserve">COUNT of facilities with internal risk rating per L2 portfolio segment.
 </v>
       </c>
       <c r="W101" t="str">
-        <v>Risk Rating - External Rating (portfolio)</v>
+        <v>Risk Rating - Internal Risk Rating (portfolio)</v>
       </c>
       <c r="X101" t="str">
         <v>Y</v>
       </c>
       <c r="Y101" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="Z101" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level external_risk_rating per L1 business segment segment.
+        <v xml:space="preserve">COUNT of facilities with internal risk rating per L1 business segment.
 </v>
       </c>
       <c r="AA101" t="str">
-        <v>Risk Rating - External Rating (business_segment)</v>
+        <v>Risk Rating - Internal Risk Rating (business_segment)</v>
       </c>
       <c r="AB101" t="str">
         <v/>
@@ -9803,17 +9893,17 @@
     </row>
     <row r="102" xml:space="preserve">
       <c r="A102" t="str">
-        <v>RSK-003</v>
+        <v>RSK-004</v>
       </c>
       <c r="B102" t="str" xml:space="preserve">
-        <v xml:space="preserve">The institution’s internally assigned credit risk grade for a borrower, facility, or exposure as of a given date, reflecting its assessment of default risk according to the firm’s internal rating scale/model.
+        <v xml:space="preserve">Derived directional indicator reflecting movement in external credit agency rating and changes month over month, which depicts the month-over-month change reflecting an upgrade (e.g. A to AA), downgrade (e.g., B+ to B-) or stable (remaing constant month over month), as compared to prior month reporting periods. Note when this is displayed at an aggregated Line of Business or portfolio level, it is determined by the month-over-month change of the average rating at this level. Supports benchmarking against market perception and helps validate internal risk assessment trends.
 </v>
       </c>
       <c r="C102" t="str">
-        <v>Risk Rating - Internal Risk Rating</v>
+        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable)</v>
       </c>
       <c r="D102" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read internal_risk_rating from facility_risk_snapshot for each facility.
+        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility as-of reporting date.
 </v>
       </c>
       <c r="E102" t="str">
@@ -9832,11 +9922,11 @@
         <v>Raw</v>
       </c>
       <c r="J102" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read internal_risk_rating from facility_risk_snapshot for each facility.
+        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility as-of reporting date.
 </v>
       </c>
       <c r="K102" t="str">
-        <v>Risk Rating - Internal Risk Rating (facility)</v>
+        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable) (facility)</v>
       </c>
       <c r="L102" t="str">
         <v>Y</v>
@@ -9845,11 +9935,11 @@
         <v>Agg</v>
       </c>
       <c r="N102" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with internal risk rating per counterparty.
+        <v xml:space="preserve">SUM of facility-level risk_rating_status per counterparty.
 </v>
       </c>
       <c r="O102" t="str">
-        <v>Risk Rating - Internal Risk Rating (counterparty)</v>
+        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable) (counterparty)</v>
       </c>
       <c r="P102" t="str">
         <v>Y</v>
@@ -9858,11 +9948,11 @@
         <v>Agg</v>
       </c>
       <c r="R102" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with internal risk rating per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level risk_rating_status per L3 desk segment.
 </v>
       </c>
       <c r="S102" t="str">
-        <v>Risk Rating - Internal Risk Rating (desk)</v>
+        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable) (desk)</v>
       </c>
       <c r="T102" t="str">
         <v>Y</v>
@@ -9871,11 +9961,11 @@
         <v>Agg</v>
       </c>
       <c r="V102" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with internal risk rating per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level risk_rating_status per L2 portfolio segment.
 </v>
       </c>
       <c r="W102" t="str">
-        <v>Risk Rating - Internal Risk Rating (portfolio)</v>
+        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable) (portfolio)</v>
       </c>
       <c r="X102" t="str">
         <v>Y</v>
@@ -9884,11 +9974,11 @@
         <v>Agg</v>
       </c>
       <c r="Z102" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with internal risk rating per L1 business segment.
+        <v xml:space="preserve">SUM of facility-level risk_rating_status per L1 business segment segment.
 </v>
       </c>
       <c r="AA102" t="str">
-        <v>Risk Rating - Internal Risk Rating (business_segment)</v>
+        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable) (business_segment)</v>
       </c>
       <c r="AB102" t="str">
         <v/>
@@ -9896,17 +9986,17 @@
     </row>
     <row r="103" xml:space="preserve">
       <c r="A103" t="str">
-        <v>RSK-004</v>
+        <v>RSK-005</v>
       </c>
       <c r="B103" t="str" xml:space="preserve">
-        <v xml:space="preserve">Derived directional indicator reflecting movement in external credit agency rating and changes month over month, which depicts the month-over-month change reflecting an upgrade (e.g. A to AA), downgrade (e.g., B+ to B-) or stable (remaing constant month over month), as compared to prior month reporting periods. Note when this is displayed at an aggregated Line of Business or portfolio level, it is determined by the month-over-month change of the average rating at this level. Supports benchmarking against market perception and helps validate internal risk assessment trends.
+        <v xml:space="preserve">Numerical representation of external risk rating migration (month over month changes) expressed in notch movement (positive or negative). Positive step changes are identified when there is an upgrade, from A to AA and the step change is +1, where as the negative step change is identified when there is a downgrade from B+ to B- and the step change is -1. Note when this is displayed at an aggregated Line of Business or portfolio level, it is determined by the month-over-month change of the average rating at this level. Quantifies magnitude of credit change and enables portfolio-level migration analysis, stress testing sensitivity, and risk trend measurement.
 </v>
       </c>
       <c r="C103" t="str">
-        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable)</v>
+        <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps)</v>
       </c>
       <c r="D103" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility as-of reporting date.
+        <v xml:space="preserve">Read risk_rating_change_steps from counterparty_rating_observation for each facility as-of reporting date.
 </v>
       </c>
       <c r="E103" t="str">
@@ -9925,11 +10015,11 @@
         <v>Raw</v>
       </c>
       <c r="J103" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility as-of reporting date.
+        <v xml:space="preserve">Read risk_rating_change_steps from counterparty_rating_observation for each facility as-of reporting date.
 </v>
       </c>
       <c r="K103" t="str">
-        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable) (facility)</v>
+        <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps) (facility)</v>
       </c>
       <c r="L103" t="str">
         <v>Y</v>
@@ -9938,11 +10028,11 @@
         <v>Agg</v>
       </c>
       <c r="N103" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_status per counterparty.
+        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per counterparty.
 </v>
       </c>
       <c r="O103" t="str">
-        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable) (counterparty)</v>
+        <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps) (counterparty)</v>
       </c>
       <c r="P103" t="str">
         <v>Y</v>
@@ -9951,11 +10041,11 @@
         <v>Agg</v>
       </c>
       <c r="R103" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_status per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per L3 desk segment.
 </v>
       </c>
       <c r="S103" t="str">
-        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable) (desk)</v>
+        <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps) (desk)</v>
       </c>
       <c r="T103" t="str">
         <v>Y</v>
@@ -9964,11 +10054,11 @@
         <v>Agg</v>
       </c>
       <c r="V103" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_status per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per L2 portfolio segment.
 </v>
       </c>
       <c r="W103" t="str">
-        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable) (portfolio)</v>
+        <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps) (portfolio)</v>
       </c>
       <c r="X103" t="str">
         <v>Y</v>
@@ -9977,11 +10067,11 @@
         <v>Agg</v>
       </c>
       <c r="Z103" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_status per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per L1 business segment segment.
 </v>
       </c>
       <c r="AA103" t="str">
-        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable) (business_segment)</v>
+        <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps) (business_segment)</v>
       </c>
       <c r="AB103" t="str">
         <v/>
@@ -9989,17 +10079,17 @@
     </row>
     <row r="104" xml:space="preserve">
       <c r="A104" t="str">
-        <v>RSK-005</v>
+        <v>RSK-006</v>
       </c>
       <c r="B104" t="str" xml:space="preserve">
-        <v xml:space="preserve">Numerical representation of external risk rating migration (month over month changes) expressed in notch movement (positive or negative). Positive step changes are identified when there is an upgrade, from A to AA and the step change is +1, where as the negative step change is identified when there is a downgrade from B+ to B- and the step change is -1. Note when this is displayed at an aggregated Line of Business or portfolio level, it is determined by the month-over-month change of the average rating at this level. Quantifies magnitude of credit change and enables portfolio-level migration analysis, stress testing sensitivity, and risk trend measurement.
+        <v xml:space="preserve">Derived directional classification indicating whether the internal credit rating has changed month over month: upgraded (e.g. 3 to 1), downgraded (e.g. 1 to 3), or remained stable (remained costant month-over month) compared to the prior reporting period. Note when this is displayed at an aggregated Line of Business or portfolio level, it is determined by the month-over-month change of the average rating at this level. Provides migration trend insight and serves as an early warning indicator of credit quality movement to support proactive risk management and escalation decisions.
 </v>
       </c>
       <c r="C104" t="str">
-        <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps)</v>
+        <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable)</v>
       </c>
       <c r="D104" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_change_steps from counterparty_rating_observation for each facility as-of reporting date.
+        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility as-of reporting date.
 </v>
       </c>
       <c r="E104" t="str">
@@ -10018,11 +10108,11 @@
         <v>Raw</v>
       </c>
       <c r="J104" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_change_steps from counterparty_rating_observation for each facility as-of reporting date.
+        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility as-of reporting date.
 </v>
       </c>
       <c r="K104" t="str">
-        <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps) (facility)</v>
+        <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable) (facility)</v>
       </c>
       <c r="L104" t="str">
         <v>Y</v>
@@ -10031,11 +10121,11 @@
         <v>Agg</v>
       </c>
       <c r="N104" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per counterparty.
+        <v xml:space="preserve">SUM of facility-level risk_rating_status per counterparty.
 </v>
       </c>
       <c r="O104" t="str">
-        <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps) (counterparty)</v>
+        <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable) (counterparty)</v>
       </c>
       <c r="P104" t="str">
         <v>Y</v>
@@ -10044,11 +10134,11 @@
         <v>Agg</v>
       </c>
       <c r="R104" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level risk_rating_status per L3 desk segment.
 </v>
       </c>
       <c r="S104" t="str">
-        <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps) (desk)</v>
+        <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable) (desk)</v>
       </c>
       <c r="T104" t="str">
         <v>Y</v>
@@ -10057,11 +10147,11 @@
         <v>Agg</v>
       </c>
       <c r="V104" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level risk_rating_status per L2 portfolio segment.
 </v>
       </c>
       <c r="W104" t="str">
-        <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps) (portfolio)</v>
+        <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable) (portfolio)</v>
       </c>
       <c r="X104" t="str">
         <v>Y</v>
@@ -10070,11 +10160,11 @@
         <v>Agg</v>
       </c>
       <c r="Z104" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level risk_rating_status per L1 business segment segment.
 </v>
       </c>
       <c r="AA104" t="str">
-        <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps) (business_segment)</v>
+        <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable) (business_segment)</v>
       </c>
       <c r="AB104" t="str">
         <v/>
@@ -10082,17 +10172,17 @@
     </row>
     <row r="105" xml:space="preserve">
       <c r="A105" t="str">
-        <v>RSK-006</v>
+        <v>RSK-007</v>
       </c>
       <c r="B105" t="str" xml:space="preserve">
-        <v xml:space="preserve">Derived directional classification indicating whether the internal credit rating has changed month over month: upgraded (e.g. 3 to 1), downgraded (e.g. 1 to 3), or remained stable (remained costant month-over month) compared to the prior reporting period. Note when this is displayed at an aggregated Line of Business or portfolio level, it is determined by the month-over-month change of the average rating at this level. Provides migration trend insight and serves as an early warning indicator of credit quality movement to support proactive risk management and escalation decisions.
+        <v xml:space="preserve">Numerical representation of internal risk rating migration (month over month changes) expressed in notch movement (positive or negative). Positive step changes are identified when there is an upgrade, from 3 to 1and the step change is +2, where as the negative step change is identified when there is a downgrade from 5 to 8 and the step change is -3. Note when this is displayed at an aggregated Line of Business or portfolio level, it is determined by the month-over-month change of the average rating at this level. Quantifies magnitude of credit change and enables portfolio-level migration analysis, stress testing sensitivity, and risk trend measurement.
 </v>
       </c>
       <c r="C105" t="str">
-        <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable)</v>
+        <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps)</v>
       </c>
       <c r="D105" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility as-of reporting date.
+        <v xml:space="preserve">Read risk_rating_change_steps from counterparty_rating_observation for each facility as-of reporting date.
 </v>
       </c>
       <c r="E105" t="str">
@@ -10111,11 +10201,11 @@
         <v>Raw</v>
       </c>
       <c r="J105" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility as-of reporting date.
+        <v xml:space="preserve">Read risk_rating_change_steps from counterparty_rating_observation for each facility as-of reporting date.
 </v>
       </c>
       <c r="K105" t="str">
-        <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable) (facility)</v>
+        <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps) (facility)</v>
       </c>
       <c r="L105" t="str">
         <v>Y</v>
@@ -10124,11 +10214,11 @@
         <v>Agg</v>
       </c>
       <c r="N105" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_status per counterparty.
+        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per counterparty.
 </v>
       </c>
       <c r="O105" t="str">
-        <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable) (counterparty)</v>
+        <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps) (counterparty)</v>
       </c>
       <c r="P105" t="str">
         <v>Y</v>
@@ -10137,11 +10227,11 @@
         <v>Agg</v>
       </c>
       <c r="R105" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_status per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per L3 desk segment.
 </v>
       </c>
       <c r="S105" t="str">
-        <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable) (desk)</v>
+        <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps) (desk)</v>
       </c>
       <c r="T105" t="str">
         <v>Y</v>
@@ -10150,11 +10240,11 @@
         <v>Agg</v>
       </c>
       <c r="V105" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_status per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per L2 portfolio segment.
 </v>
       </c>
       <c r="W105" t="str">
-        <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable) (portfolio)</v>
+        <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps) (portfolio)</v>
       </c>
       <c r="X105" t="str">
         <v>Y</v>
@@ -10163,11 +10253,11 @@
         <v>Agg</v>
       </c>
       <c r="Z105" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_status per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per L1 business segment segment.
 </v>
       </c>
       <c r="AA105" t="str">
-        <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable) (business_segment)</v>
+        <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps) (business_segment)</v>
       </c>
       <c r="AB105" t="str">
         <v/>
@@ -10175,17 +10265,17 @@
     </row>
     <row r="106" xml:space="preserve">
       <c r="A106" t="str">
-        <v>RSK-007</v>
+        <v>RSK-008</v>
       </c>
       <c r="B106" t="str" xml:space="preserve">
-        <v xml:space="preserve">Numerical representation of internal risk rating migration (month over month changes) expressed in notch movement (positive or negative). Positive step changes are identified when there is an upgrade, from 3 to 1and the step change is +2, where as the negative step change is identified when there is a downgrade from 5 to 8 and the step change is -3. Note when this is displayed at an aggregated Line of Business or portfolio level, it is determined by the month-over-month change of the average rating at this level. Quantifies magnitude of credit change and enables portfolio-level migration analysis, stress testing sensitivity, and risk trend measurement.
+        <v xml:space="preserve">Categorizes exposures by internal credit risk level into distribution buckets based on counterparty internal risk rating; enables monitoring of credit quality distribution, concentration, and deterioration via rating migration.
 </v>
       </c>
       <c r="C106" t="str">
-        <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps)</v>
+        <v>Internal Risk Rating Bucket</v>
       </c>
       <c r="D106" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_change_steps from counterparty_rating_observation for each facility as-of reporting date.
+        <v xml:space="preserve">Read internal_risk_rating_bucket_code from facility_exposure_snapshot for each facility.
 </v>
       </c>
       <c r="E106" t="str">
@@ -10204,11 +10294,11 @@
         <v>Raw</v>
       </c>
       <c r="J106" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_change_steps from counterparty_rating_observation for each facility as-of reporting date.
+        <v xml:space="preserve">Read internal_risk_rating_bucket_code from facility_exposure_snapshot for each facility.
 </v>
       </c>
       <c r="K106" t="str">
-        <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps) (facility)</v>
+        <v>Internal Risk Rating Bucket (facility)</v>
       </c>
       <c r="L106" t="str">
         <v>Y</v>
@@ -10217,11 +10307,11 @@
         <v>Agg</v>
       </c>
       <c r="N106" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per counterparty.
+        <v xml:space="preserve">COUNT of facilities with risk rating bucket per counterparty.
 </v>
       </c>
       <c r="O106" t="str">
-        <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps) (counterparty)</v>
+        <v>Internal Risk Rating Bucket (counterparty)</v>
       </c>
       <c r="P106" t="str">
         <v>Y</v>
@@ -10230,11 +10320,11 @@
         <v>Agg</v>
       </c>
       <c r="R106" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per L3 desk segment.
+        <v xml:space="preserve">COUNT of facilities with risk rating bucket per L3 desk segment.
 </v>
       </c>
       <c r="S106" t="str">
-        <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps) (desk)</v>
+        <v>Internal Risk Rating Bucket (desk)</v>
       </c>
       <c r="T106" t="str">
         <v>Y</v>
@@ -10243,11 +10333,11 @@
         <v>Agg</v>
       </c>
       <c r="V106" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per L2 portfolio segment.
+        <v xml:space="preserve">COUNT of facilities with risk rating bucket per L2 portfolio segment.
 </v>
       </c>
       <c r="W106" t="str">
-        <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps) (portfolio)</v>
+        <v>Internal Risk Rating Bucket (portfolio)</v>
       </c>
       <c r="X106" t="str">
         <v>Y</v>
@@ -10256,11 +10346,11 @@
         <v>Agg</v>
       </c>
       <c r="Z106" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per L1 business segment segment.
+        <v xml:space="preserve">COUNT of facilities with risk rating bucket per L1 business segment.
 </v>
       </c>
       <c r="AA106" t="str">
-        <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps) (business_segment)</v>
+        <v>Internal Risk Rating Bucket (business_segment)</v>
       </c>
       <c r="AB106" t="str">
         <v/>
@@ -10268,17 +10358,18 @@
     </row>
     <row r="107" xml:space="preserve">
       <c r="A107" t="str">
-        <v>RSK-008</v>
+        <v>RSK-009</v>
       </c>
       <c r="B107" t="str" xml:space="preserve">
-        <v xml:space="preserve">Categorizes exposures by internal credit risk level into distribution buckets based on counterparty internal risk rating; enables monitoring of credit quality distribution, concentration, and deterioration via rating migration.
+        <v xml:space="preserve">Committed facility amount as a percentage of underlying collateral value. Higher LTV indicates greater loss severity risk in the event of default. A core risk metric for secured lending portfolios.
 </v>
       </c>
       <c r="C107" t="str">
-        <v>Internal Risk Rating Bucket</v>
+        <v>Loan-to-Value Ratio (%)</v>
       </c>
       <c r="D107" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read internal_risk_rating_bucket_code from facility_exposure_snapshot for each facility.
+        <v xml:space="preserve">Aggregate collateral per facility (a facility may have multiple collateral assets),
+then compute LTV = committed_facility_amt / SUM(current_valuation_usd) * 100.
 </v>
       </c>
       <c r="E107" t="str">
@@ -10297,170 +10388,76 @@
         <v>Raw</v>
       </c>
       <c r="J107" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read internal_risk_rating_bucket_code from facility_exposure_snapshot for each facility.
-</v>
-      </c>
-      <c r="K107" t="str">
-        <v>Internal Risk Rating Bucket (facility)</v>
-      </c>
-      <c r="L107" t="str">
-        <v>Y</v>
-      </c>
-      <c r="M107" t="str">
-        <v>Agg</v>
-      </c>
-      <c r="N107" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating bucket per counterparty.
-</v>
-      </c>
-      <c r="O107" t="str">
-        <v>Internal Risk Rating Bucket (counterparty)</v>
-      </c>
-      <c r="P107" t="str">
-        <v>Y</v>
-      </c>
-      <c r="Q107" t="str">
-        <v>Agg</v>
-      </c>
-      <c r="R107" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating bucket per L3 desk segment.
-</v>
-      </c>
-      <c r="S107" t="str">
-        <v>Internal Risk Rating Bucket (desk)</v>
-      </c>
-      <c r="T107" t="str">
-        <v>Y</v>
-      </c>
-      <c r="U107" t="str">
-        <v>Agg</v>
-      </c>
-      <c r="V107" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating bucket per L2 portfolio segment.
-</v>
-      </c>
-      <c r="W107" t="str">
-        <v>Internal Risk Rating Bucket (portfolio)</v>
-      </c>
-      <c r="X107" t="str">
-        <v>Y</v>
-      </c>
-      <c r="Y107" t="str">
-        <v>Agg</v>
-      </c>
-      <c r="Z107" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating bucket per L1 business segment.
-</v>
-      </c>
-      <c r="AA107" t="str">
-        <v>Internal Risk Rating Bucket (business_segment)</v>
-      </c>
-      <c r="AB107" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="108" xml:space="preserve">
-      <c r="A108" t="str">
-        <v>RSK-009</v>
-      </c>
-      <c r="B108" t="str" xml:space="preserve">
-        <v xml:space="preserve">Committed facility amount as a percentage of underlying collateral value. Higher LTV indicates greater loss severity risk in the event of default. A core risk metric for secured lending portfolios.
-</v>
-      </c>
-      <c r="C108" t="str">
-        <v>Loan-to-Value Ratio (%)</v>
-      </c>
-      <c r="D108" t="str" xml:space="preserve">
         <v xml:space="preserve">Aggregate collateral per facility (a facility may have multiple collateral assets),
 then compute LTV = committed_facility_amt / SUM(current_valuation_usd) * 100.
 </v>
       </c>
-      <c r="E108" t="str">
-        <v/>
-      </c>
-      <c r="F108" t="str">
-        <v/>
-      </c>
-      <c r="G108" t="str">
-        <v/>
-      </c>
-      <c r="H108" t="str">
-        <v>Y</v>
-      </c>
-      <c r="I108" t="str">
-        <v>Raw</v>
-      </c>
-      <c r="J108" t="str" xml:space="preserve">
-        <v xml:space="preserve">Aggregate collateral per facility (a facility may have multiple collateral assets),
-then compute LTV = committed_facility_amt / SUM(current_valuation_usd) * 100.
-</v>
-      </c>
-      <c r="K108" t="str">
+      <c r="K107" t="str">
         <v>Loan-to-Value Ratio (%) (facility)</v>
       </c>
-      <c r="L108" t="str">
-        <v>Y</v>
-      </c>
-      <c r="M108" t="str">
+      <c r="L107" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M107" t="str">
         <v>Calc</v>
       </c>
-      <c r="N108" t="str" xml:space="preserve">
+      <c r="N107" t="str" xml:space="preserve">
         <v xml:space="preserve">SUM(committed_facility_amt) / SUM(current_valuation_usd) * 100.0
 per counterparty. Re-derives ratio from summed components.
 </v>
       </c>
-      <c r="O108" t="str">
+      <c r="O107" t="str">
         <v>Loan-to-Value Ratio (%) (counterparty)</v>
       </c>
-      <c r="P108" t="str">
-        <v>Y</v>
-      </c>
-      <c r="Q108" t="str">
+      <c r="P107" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q107" t="str">
         <v>Calc</v>
       </c>
-      <c r="R108" t="str" xml:space="preserve">
+      <c r="R107" t="str" xml:space="preserve">
         <v xml:space="preserve">SUM(committed_facility_amt) / SUM(current_valuation_usd) * 100.0
 per L3 desk segment. Re-derives ratio from summed components.
 </v>
       </c>
-      <c r="S108" t="str">
+      <c r="S107" t="str">
         <v>Loan-to-Value Ratio (%) (desk)</v>
       </c>
-      <c r="T108" t="str">
-        <v>Y</v>
-      </c>
-      <c r="U108" t="str">
+      <c r="T107" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U107" t="str">
         <v>Calc</v>
       </c>
-      <c r="V108" t="str" xml:space="preserve">
+      <c r="V107" t="str" xml:space="preserve">
         <v xml:space="preserve">SUM(committed_facility_amt) / SUM(current_valuation_usd) * 100.0
 per L2 portfolio segment. Re-derives ratio from summed components.
 </v>
       </c>
-      <c r="W108" t="str">
+      <c r="W107" t="str">
         <v>Loan-to-Value Ratio (%) (portfolio)</v>
       </c>
-      <c r="X108" t="str">
-        <v>Y</v>
-      </c>
-      <c r="Y108" t="str">
+      <c r="X107" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y107" t="str">
         <v>Calc</v>
       </c>
-      <c r="Z108" t="str" xml:space="preserve">
+      <c r="Z107" t="str" xml:space="preserve">
         <v xml:space="preserve">SUM(committed_facility_amt) / SUM(current_valuation_usd) * 100.0
 per L1 business segment. Re-derives ratio from summed components.
 </v>
       </c>
-      <c r="AA108" t="str">
+      <c r="AA107" t="str">
         <v>Loan-to-Value Ratio (%) (business_segment)</v>
       </c>
-      <c r="AB108" t="str">
+      <c r="AB107" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AB108"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AB107"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/metrics_dimensions_filled.xlsx
+++ b/data/metrics_dimensions_filled.xlsx
@@ -1539,14 +1539,14 @@
         <v>EXP-005</v>
       </c>
       <c r="B14" t="str" xml:space="preserve">
-        <v xml:space="preserve">The portion of total funding-related expense attributed to a specific exposure or portfolio. At facility level, calculated as SUM across all positions of (funded_amount * interest_rate), adjusted for bank share. At counterparty level, further adjusted by counterparty participation_pct. At desk/portfolio/segment levels, aggregated as SUM.
+        <v xml:space="preserve">The portion of total funding-related expense attributed to a specific exposure or portfolio. At facility level, calculated as SUM across all positions of (funded_amount * interest_rate), converted to USD via FX rate and adjusted for bank share. At counterparty level, further adjusted by counterparty participation_pct. At desk/portfolio/segment levels, aggregated as SUM via EBT hierarchy.
 </v>
       </c>
       <c r="C14" t="str">
         <v>Cost of Funds ($)</v>
       </c>
       <c r="D14" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each position under the facility: funded_amount * interest_rate = Position Cost of Funds. Adjusted by bank_share: SUM(funded_amount * interest_rate) * bank_share_pct / 100. Joins position_detail → position (for facility_id) → facility_master.
+        <v xml:space="preserve">For each position under the facility, compute funded_amount x interest_rate, convert to USD using the FX spot rate (defaults to 1.0 for USD positions). Sum across all positions, then multiply by the bank's share percentage. Result = annual cost of funds for this facility in USD.
 </v>
       </c>
       <c r="E14" t="str">
@@ -1565,7 +1565,7 @@
         <v>Calc</v>
       </c>
       <c r="J14" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each position under the facility: funded_amount * interest_rate = Position Cost of Funds. Adjusted by bank_share: SUM(funded_amount * interest_rate) * bank_share_pct / 100. Joins position_detail → position (for facility_id) → facility_master.
+        <v xml:space="preserve">For each position under the facility, compute funded_amount x interest_rate, convert to USD using the FX spot rate (defaults to 1.0 for USD positions). Sum across all positions, then multiply by the bank's share percentage. Result = annual cost of funds for this facility in USD.
 </v>
       </c>
       <c r="K14" t="str">
@@ -1578,7 +1578,7 @@
         <v>Agg</v>
       </c>
       <c r="N14" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each counterparty: SUM of facility-level cost of funds weighted by counterparty participation_pct from facility_counterparty_participation.
+        <v xml:space="preserve">Sum each facility's cost of funds (USD, bank-share-adjusted), then weight by the counterparty's participation percentage. Aggregates across all facilities where the counterparty has a current participation record.
 </v>
       </c>
       <c r="O14" t="str">
@@ -1591,7 +1591,7 @@
         <v>Agg</v>
       </c>
       <c r="R14" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level cost of funds (bank-share-adjusted) per L3 desk segment.
+        <v xml:space="preserve">Sum of facility-level cost of funds (USD, bank-share-adjusted) for all facilities assigned to each L3 desk segment in the organizational hierarchy.
 </v>
       </c>
       <c r="S14" t="str">
@@ -1604,7 +1604,7 @@
         <v>Agg</v>
       </c>
       <c r="V14" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level cost of funds (bank-share-adjusted) per L2 portfolio segment.
+        <v xml:space="preserve">Sum of facility-level cost of funds (USD, bank-share-adjusted) for all facilities within each L2 portfolio segment, traversing the EBT hierarchy from desk (L3) to portfolio (L2) via parent_segment_id.
 </v>
       </c>
       <c r="W14" t="str">
@@ -1617,7 +1617,7 @@
         <v>Agg</v>
       </c>
       <c r="Z14" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level cost of funds (bank-share-adjusted) per L1 business segment.
+        <v xml:space="preserve">Sum of facility-level cost of funds (USD, bank-share-adjusted) for all facilities within each L1 business segment, traversing the full EBT hierarchy from desk (L3) through portfolio (L2) to segment (L1).
 </v>
       </c>
       <c r="AA14" t="str">
@@ -1632,14 +1632,14 @@
         <v>EXP-006</v>
       </c>
       <c r="B15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure allocated to specific counterparty representing their share of the facility which the client can draw on. Concentration KPI measuring obligor dependency risk.
+        <v xml:space="preserve">Counterparty participation share in a facility — the percentage of a syndicated or participated facility allocated to a specific counterparty. At facility level, direct lookup from facility_counterparty_participation. At counterparty level, exposure-weighted average participation across all facilities. At desk/portfolio/segment, exposure-weighted average via EBT hierarchy. Key concentration KPI for Large Exposures Framework (LEX) and Single Counterparty Credit Limit (SCCL) compliance.
 </v>
       </c>
       <c r="C15" t="str">
         <v>Counterparty Share or Allocation (%)</v>
       </c>
       <c r="D15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of allocation_pct from facility_counterparty_participation.
+        <v xml:space="preserve">Direct lookup of participation_pct from facility_counterparty_participation for the primary counterparty on each facility. Uses current records only.
 </v>
       </c>
       <c r="E15" t="str">
@@ -1658,7 +1658,7 @@
         <v>Raw</v>
       </c>
       <c r="J15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of allocation_pct from facility_counterparty_participation.
+        <v xml:space="preserve">Direct lookup of participation_pct from facility_counterparty_participation for the primary counterparty on each facility. Uses current records only.
 </v>
       </c>
       <c r="K15" t="str">
@@ -1668,10 +1668,10 @@
         <v>Y</v>
       </c>
       <c r="M15" t="str">
-        <v>Raw</v>
+        <v>Avg</v>
       </c>
       <c r="N15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read allocation_pct per counterparty.
+        <v xml:space="preserve">Exposure-weighted average participation across all facilities for each counterparty. Weight = drawn_amount from facility_exposure_snapshot. Falls back to simple average if no exposure data available.
 </v>
       </c>
       <c r="O15" t="str">
@@ -1681,10 +1681,10 @@
         <v>Y</v>
       </c>
       <c r="Q15" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="R15" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level allocation_pct per L3 desk segment.
+        <v xml:space="preserve">Exposure-weighted average participation across all facilities per L3 desk segment via enterprise_business_taxonomy.
 </v>
       </c>
       <c r="S15" t="str">
@@ -1694,10 +1694,10 @@
         <v>Y</v>
       </c>
       <c r="U15" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="V15" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level allocation_pct per L2 portfolio segment.
+        <v xml:space="preserve">Exposure-weighted average participation across all facilities per L2 portfolio segment via enterprise_business_taxonomy hierarchy traversal.
 </v>
       </c>
       <c r="W15" t="str">
@@ -1707,10 +1707,10 @@
         <v>Y</v>
       </c>
       <c r="Y15" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="Z15" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level allocation_pct per L1 business segment segment.
+        <v xml:space="preserve">Exposure-weighted average participation across all facilities per L1 business segment via enterprise_business_taxonomy hierarchy traversal.
 </v>
       </c>
       <c r="AA15" t="str">
@@ -1725,14 +1725,14 @@
         <v>EXP-007</v>
       </c>
       <c r="B16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Flag identifying exposures requiring heightened monitoring due to elevated credit risk. Governance control used for enhanced monitoring, reserve consideration, and management reporting.
+        <v xml:space="preserve">Count of active Criticized risk flags across facilities. Early warning indicator of problem assets requiring heightened monitoring, reserve consideration, and management reporting. Sources from the risk_flag table filtering on flag_code = 'CRITICIZED' with uncleared status.
 </v>
       </c>
       <c r="C16" t="str">
         <v>Criticized Portfolios</v>
       </c>
       <c r="D16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if criticized rating (internal_risk_rating &gt;= 6), 0 otherwise.
+        <v xml:space="preserve">For each facility, count active risk flags where flag_code = 'CRITICIZED' and the flag has not been cleared (cleared_ts IS NULL).
 </v>
       </c>
       <c r="E16" t="str">
@@ -1748,10 +1748,10 @@
         <v>Y</v>
       </c>
       <c r="I16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="J16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if criticized rating (internal_risk_rating &gt;= 6), 0 otherwise.
+        <v xml:space="preserve">For each facility, count active risk flags where flag_code = 'CRITICIZED' and the flag has not been cleared (cleared_ts IS NULL).
 </v>
       </c>
       <c r="K16" t="str">
@@ -1761,10 +1761,10 @@
         <v>Y</v>
       </c>
       <c r="M16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="N16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per counterparty.
+        <v xml:space="preserve">For each counterparty, sum facility-level criticized flag counts across all facilities belonging to that counterparty.
 </v>
       </c>
       <c r="O16" t="str">
@@ -1774,10 +1774,10 @@
         <v>Y</v>
       </c>
       <c r="Q16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="R16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per L3 desk.
+        <v xml:space="preserve">Sum of criticized flag counts per L3 desk segment. Joins facility_master to enterprise_business_taxonomy via lob_segment_id.
 </v>
       </c>
       <c r="S16" t="str">
@@ -1787,10 +1787,10 @@
         <v>Y</v>
       </c>
       <c r="U16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="V16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per L2 portfolio.
+        <v xml:space="preserve">Sum of criticized flag counts per L2 portfolio segment. Traverses enterprise_business_taxonomy hierarchy from L3 to L2 via parent_segment_id.
 </v>
       </c>
       <c r="W16" t="str">
@@ -1800,10 +1800,10 @@
         <v>Y</v>
       </c>
       <c r="Y16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="Z16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per L1 business segment.
+        <v xml:space="preserve">Sum of criticized flag counts per L1 business segment. Full hierarchy traversal L3 → L2 → L1 via enterprise_business_taxonomy.
 </v>
       </c>
       <c r="AA16" t="str">
@@ -1818,14 +1818,14 @@
         <v>EXP-008</v>
       </c>
       <c r="B17" t="str" xml:space="preserve">
-        <v xml:space="preserve">Total exposure amount allocated across multiple legal entities. Supports intra-group concentration transparency.
+        <v xml:space="preserve">Total committed exposure amount (bank share) allocated across multiple legal entities for facilities flagged as cross-entity. Quantifies inter-entity concentration risk and supports intra-group transparency for GSIB reporting. Sources from counterparty_derived (L3) for the cross-entity flag and facility_exposure_snapshot (L2) for committed amounts.
 </v>
       </c>
       <c r="C17" t="str">
         <v>Cross Entity Exposure Amount</v>
       </c>
       <c r="D17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(total_cross_entity_exposure_usd) per facility from counterparty_exposure_summary. Weighted by bank share percentage.
+        <v xml:space="preserve">For each facility flagged as cross-entity, committed exposure amount weighted by the bank's participation share (bank_share_pct). Facilities without cross-entity flag are excluded.
 </v>
       </c>
       <c r="E17" t="str">
@@ -1844,7 +1844,7 @@
         <v>Agg</v>
       </c>
       <c r="J17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(total_cross_entity_exposure_usd) per facility from counterparty_exposure_summary. Weighted by bank share percentage.
+        <v xml:space="preserve">For each facility flagged as cross-entity, committed exposure amount weighted by the bank's participation share (bank_share_pct). Facilities without cross-entity flag are excluded.
 </v>
       </c>
       <c r="K17" t="str">
@@ -1857,7 +1857,7 @@
         <v>Agg</v>
       </c>
       <c r="N17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per counterparty.
+        <v xml:space="preserve">For each counterparty, sum of bank-share-weighted committed amounts across all facilities flagged as cross-entity.
 </v>
       </c>
       <c r="O17" t="str">
@@ -1870,7 +1870,7 @@
         <v>Agg</v>
       </c>
       <c r="R17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per L3 desk segment.
+        <v xml:space="preserve">Sum of cross-entity committed exposure per L3 desk segment via enterprise_business_taxonomy.
 </v>
       </c>
       <c r="S17" t="str">
@@ -1883,7 +1883,7 @@
         <v>Agg</v>
       </c>
       <c r="V17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per L2 portfolio segment.
+        <v xml:space="preserve">Sum of cross-entity committed exposure per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
 </v>
       </c>
       <c r="W17" t="str">
@@ -1896,7 +1896,7 @@
         <v>Agg</v>
       </c>
       <c r="Z17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per L1 business segment segment.
+        <v xml:space="preserve">Sum of cross-entity committed exposure per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
 </v>
       </c>
       <c r="AA17" t="str">
@@ -1911,14 +1911,14 @@
         <v>EXP-009</v>
       </c>
       <c r="B18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Number of days outstanding payments is past due as grouped into 3 "buckets", 0-30 Days, 31-60 Days, 61-90+ Days. Used for staging classification and early credit deterioration monitoring.
+        <v xml:space="preserve">Maximum days payment overdue per facility, calculated from raw payment records in the payment_ledger table. For each facility, identifies payments where applied amount &lt; amount due, computes days overdue as reporting date minus payment_due_date, takes the MAX, then classifies into buckets: 1 = 0-30 days, 2 = 31-60 days, 3 = 61-90+ days. At aggregate levels, reports the worst (MAX) bucket across constituents.
 </v>
       </c>
       <c r="C18" t="str">
         <v>Days Payment Overdue Bucket</v>
       </c>
       <c r="D18" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Facility_ID lookup the Payments records in the Payment Lockbox table, For each payment record where [Payment_Due_Date] &gt; Today() IF ([Pmt_Applied] &lt;[Pmt_Due])&gt;=1, THEN Today() - [Payment_due_date] ==[Days Overdue] SELECT MAX ([Days Overdue] then lookup in Payments Overdue bucket)
+        <v xml:space="preserve">For each facility, lookup payment records in payment_ledger where payment_due_date &lt; reporting date and payment_applied_amt &lt; payment_amount_due (underpaid). Calculate days overdue = reporting date minus payment_due_date. Take MAX days overdue, then classify into overdue bucket: 1 (0-30), 2 (31-60), 3 (61-90+).
 </v>
       </c>
       <c r="E18" t="str">
@@ -1937,7 +1937,7 @@
         <v>Calc</v>
       </c>
       <c r="J18" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Facility_ID lookup the Payments records in the Payment Lockbox table, For each payment record where [Payment_Due_Date] &gt; Today() IF ([Pmt_Applied] &lt;[Pmt_Due])&gt;=1, THEN Today() - [Payment_due_date] ==[Days Overdue] SELECT MAX ([Days Overdue] then lookup in Payments Overdue bucket)
+        <v xml:space="preserve">For each facility, lookup payment records in payment_ledger where payment_due_date &lt; reporting date and payment_applied_amt &lt; payment_amount_due (underpaid). Calculate days overdue = reporting date minus payment_due_date. Take MAX days overdue, then classify into overdue bucket: 1 (0-30), 2 (31-60), 3 (61-90+).
 </v>
       </c>
       <c r="K18" t="str">
@@ -1950,7 +1950,7 @@
         <v>Agg</v>
       </c>
       <c r="N18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per counterparty.
+        <v xml:space="preserve">Worst-case (MAX) overdue bucket across all facilities per counterparty. Identifies the most severely overdue facility for each borrower.
 </v>
       </c>
       <c r="O18" t="str">
@@ -1963,7 +1963,7 @@
         <v>Agg</v>
       </c>
       <c r="R18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per L3 desk segment.
+        <v xml:space="preserve">Worst-case (MAX) overdue bucket per L3 desk segment. Shows the most severe delinquency in each organizational unit.
 </v>
       </c>
       <c r="S18" t="str">
@@ -1976,7 +1976,7 @@
         <v>Agg</v>
       </c>
       <c r="V18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per L2 portfolio segment.
+        <v xml:space="preserve">Worst-case (MAX) overdue bucket per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
 </v>
       </c>
       <c r="W18" t="str">
@@ -1989,7 +1989,7 @@
         <v>Agg</v>
       </c>
       <c r="Z18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per L1 business segment.
+        <v xml:space="preserve">Worst-case (MAX) overdue bucket per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
 </v>
       </c>
       <c r="AA18" t="str">
@@ -2509,14 +2509,25 @@
         <v>EXP-015</v>
       </c>
       <c r="B24" t="str" xml:space="preserve">
-        <v xml:space="preserve">Expected Loss divided by Exposure. Derived KPI measuring loss intensity relative to exposure size, enabling comparative risk ranking across facilities or counterparties.
+        <v xml:space="preserve">Expected Loss as a percentage of committed exposure. Computed from L2 atomic risk parameters: PD (probability of default) × LGD (loss given default). At aggregate levels, uses sum-ratio rollup: SUM(PD × LGD × Committed) / SUM(Committed) × 100 — the exposure-weighted average EL rate. This ensures mathematically consistent aggregation (never averages pre-computed rates). Key credit risk quantification metric for comparing loss intensity across facilities, counterparties, and business segments.
+Ingredient derivation:
+  - PD (pd_pct): L2 facility_risk_snapshot — probability of default (%)
+  - LGD (lgd_pct): L2 facility_risk_snapshot — loss given default (%)
+  - Committed Exposure (committed_amount): L2 facility_exposure_snapshot — raw
+  - EL Rate = PD × LGD (at facility level, committed cancels in ratio)
+  - Aggregate EL Rate = SUM(PD × LGD × Committed) / SUM(Committed) × 100
 </v>
       </c>
       <c r="C24" t="str">
         <v>Expected Loss Rate (%)</v>
       </c>
       <c r="D24" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of expected_loss_rate_pct per facility.
+        <v xml:space="preserve">For each facility:
+  1. LOAD pd_pct, lgd_pct from l2.facility_risk_snapshot
+  2. LOAD committed_amount from l2.facility_exposure_snapshot
+  3. COMPUTE EL Rate = SUM(PD/100 × LGD/100 × Committed) / SUM(Committed) × 100
+     At facility grain, committed cancels → EL Rate ≈ PD × LGD / 100
+Ingredients: pd_pct (L2), lgd_pct (L2), committed_amount (L2)
 </v>
       </c>
       <c r="E24" t="str">
@@ -2532,10 +2543,15 @@
         <v>Y</v>
       </c>
       <c r="I24" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="J24" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of expected_loss_rate_pct per facility.
+        <v xml:space="preserve">For each facility:
+  1. LOAD pd_pct, lgd_pct from l2.facility_risk_snapshot
+  2. LOAD committed_amount from l2.facility_exposure_snapshot
+  3. COMPUTE EL Rate = SUM(PD/100 × LGD/100 × Committed) / SUM(Committed) × 100
+     At facility grain, committed cancels → EL Rate ≈ PD × LGD / 100
+Ingredients: pd_pct (L2), lgd_pct (L2), committed_amount (L2)
 </v>
       </c>
       <c r="K24" t="str">
@@ -2545,10 +2561,15 @@
         <v>Y</v>
       </c>
       <c r="M24" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N24" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level expected_loss_rate_pct per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD pd_pct, lgd_pct for all facilities belonging to this counterparty
+  2. LOAD committed_amount for each facility
+  3. CONVERT to USD via l2.fx_rate spot rate
+  4. COMPUTE SUM(PD × LGD × Committed × FX) / SUM(Committed × FX) × 100
+Sum-ratio rollup with FX: exposure-weighted average EL rate in USD terms.
 </v>
       </c>
       <c r="O24" t="str">
@@ -2558,10 +2579,14 @@
         <v>Y</v>
       </c>
       <c r="Q24" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="R24" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level expected_loss_rate_pct per L3 desk segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOOKUP managed_segment_id from enterprise_business_taxonomy
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(PD × LGD × Committed × FX) / SUM(Committed × FX) × 100
+Sum-ratio rollup: exposure-weighted average EL rate per desk.
 </v>
       </c>
       <c r="S24" t="str">
@@ -2571,10 +2596,14 @@
         <v>Y</v>
       </c>
       <c r="U24" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V24" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level expected_loss_rate_pct per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(PD × LGD × Committed × FX) / SUM(Committed × FX) × 100
+Sum-ratio rollup: exposure-weighted average EL rate per portfolio.
 </v>
       </c>
       <c r="W24" t="str">
@@ -2584,10 +2613,14 @@
         <v>Y</v>
       </c>
       <c r="Y24" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z24" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level expected_loss_rate_pct per L1 business segment segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(PD × LGD × Committed × FX) / SUM(Committed × FX) × 100
+Sum-ratio rollup: exposure-weighted average EL rate per segment.
 </v>
       </c>
       <c r="AA24" t="str">
@@ -2602,14 +2635,25 @@
         <v>EXP-016</v>
       </c>
       <c r="B25" t="str" xml:space="preserve">
-        <v xml:space="preserve">PD × LGD × Exposure expressed in USD. Calculated forward-looking loss metric supporting provisioning, capital planning, and stress testing analytics.
+        <v xml:space="preserve">Expected Loss in dollar terms: PD × LGD × Committed Exposure × Bank Share. Computed from L2 atomic risk parameters and exposure data — NOT from stressed scenarios. This is the base (unstressed) expected credit loss, the foundation for provisioning, capital planning, and CECL/IFRS 9 reserve estimation.
+Ingredient derivation:
+  - PD (pd_pct): L2 facility_risk_snapshot — probability of default (%)
+  - LGD (lgd_pct): L2 facility_risk_snapshot — loss given default (%)
+  - Committed Exposure (committed_amount): L2 facility_exposure_snapshot — raw
+  - Bank Share (bank_share_pct): L2 facility_exposure_snapshot — participation %
+  - EL = (PD/100) × (LGD/100) × Committed × (Bank Share/100)
+Rollup uses direct-sum: SUM(facility EL) at each aggregate level. FX conversion applied at aggregate levels for multi-currency portfolios.
 </v>
       </c>
       <c r="C25" t="str">
         <v>Expected Loss ($)</v>
       </c>
       <c r="D25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(stressed_expected_loss) per facility from stress_test_result. Weighted by bank share percentage.
+        <v xml:space="preserve">For each facility:
+  1. LOAD pd_pct, lgd_pct from l2.facility_risk_snapshot
+  2. LOAD committed_amount, bank_share_pct from l2.facility_exposure_snapshot
+  3. COMPUTE EL = (PD/100) × (LGD/100) × Committed × (Bank Share/100)
+Ingredients: pd_pct (L2), lgd_pct (L2), committed_amount (L2), bank_share_pct (L2)
 </v>
       </c>
       <c r="E25" t="str">
@@ -2625,10 +2669,14 @@
         <v>Y</v>
       </c>
       <c r="I25" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="J25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(stressed_expected_loss) per facility from stress_test_result. Weighted by bank share percentage.
+        <v xml:space="preserve">For each facility:
+  1. LOAD pd_pct, lgd_pct from l2.facility_risk_snapshot
+  2. LOAD committed_amount, bank_share_pct from l2.facility_exposure_snapshot
+  3. COMPUTE EL = (PD/100) × (LGD/100) × Committed × (Bank Share/100)
+Ingredients: pd_pct (L2), lgd_pct (L2), committed_amount (L2), bank_share_pct (L2)
 </v>
       </c>
       <c r="K25" t="str">
@@ -2641,7 +2689,11 @@
         <v>Agg</v>
       </c>
       <c r="N25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD facility-level EL for all facilities of this counterparty
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(facility EL × FX rate) = Counterparty EL (USD)
+Direct-sum rollup with FX conversion.
 </v>
       </c>
       <c r="O25" t="str">
@@ -2654,7 +2706,11 @@
         <v>Agg</v>
       </c>
       <c r="R25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per L3 desk segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOOKUP managed_segment_id from enterprise_business_taxonomy
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(facility EL × FX rate) per desk
+Direct-sum rollup with FX conversion.
 </v>
       </c>
       <c r="S25" t="str">
@@ -2667,7 +2723,11 @@
         <v>Agg</v>
       </c>
       <c r="V25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(facility EL × FX rate) per portfolio
+Direct-sum rollup with FX conversion.
 </v>
       </c>
       <c r="W25" t="str">
@@ -2680,7 +2740,11 @@
         <v>Agg</v>
       </c>
       <c r="Z25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per L1 business segment segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(facility EL × FX rate) per business segment
+Direct-sum rollup with FX conversion.
 </v>
       </c>
       <c r="AA25" t="str">
@@ -4113,14 +4177,14 @@
         <v>EXP-032</v>
       </c>
       <c r="B41" t="str" xml:space="preserve">
-        <v xml:space="preserve">Original Appriased Value of pledged collateral securing exposure in USD. Supports recovery analysis and secured lending assessment.
+        <v xml:space="preserve">Original appraised value of pledged collateral securing exposure, in USD. At facility level, sums original_valuation_usd from collateral_snapshot weighted by the bank's syndication share (bank_share_pct from facility_lender_allocation). Rolls up additively through counterparty, desk, portfolio, and business segment via the standard EBT hierarchy. Supports recovery analysis and secured lending assessment.
 </v>
       </c>
       <c r="C41" t="str">
         <v>Collateral Market Value at Origination ($)</v>
       </c>
       <c r="D41" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(original_valuation_usd) per facility from collateral_snapshot. Weighted by bank share percentage.
+        <v xml:space="preserve">SUM(original_valuation_usd * bank_share_pct / 100) per facility. Bank share defaults to 100% if no lender allocation record.
 </v>
       </c>
       <c r="E41" t="str">
@@ -4139,7 +4203,7 @@
         <v>Agg</v>
       </c>
       <c r="J41" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(original_valuation_usd) per facility from collateral_snapshot. Weighted by bank share percentage.
+        <v xml:space="preserve">SUM(original_valuation_usd * bank_share_pct / 100) per facility. Bank share defaults to 100% if no lender allocation record.
 </v>
       </c>
       <c r="K41" t="str">
@@ -4152,7 +4216,7 @@
         <v>Agg</v>
       </c>
       <c r="N41" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level original_valuation_usd per counterparty.
+        <v xml:space="preserve">SUM of facility-level collateral origination value per counterparty.
 </v>
       </c>
       <c r="O41" t="str">
@@ -4165,7 +4229,7 @@
         <v>Agg</v>
       </c>
       <c r="R41" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level original_valuation_usd per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level collateral origination value per L3 desk segment.
 </v>
       </c>
       <c r="S41" t="str">
@@ -4178,7 +4242,7 @@
         <v>Agg</v>
       </c>
       <c r="V41" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level original_valuation_usd per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level collateral origination value per L2 portfolio segment.
 </v>
       </c>
       <c r="W41" t="str">
@@ -4191,7 +4255,7 @@
         <v>Agg</v>
       </c>
       <c r="Z41" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level original_valuation_usd per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level collateral origination value per L1 business segment.
 </v>
       </c>
       <c r="AA41" t="str">
@@ -4206,14 +4270,14 @@
         <v>EXP-033</v>
       </c>
       <c r="B42" t="str" xml:space="preserve">
-        <v xml:space="preserve">Sub-classification of risk mitigant or collateral type tied to the facility. Used for granular risk segmentation.
+        <v xml:space="preserve">Count of distinct risk mitigant sub-types protecting exposure at each rollup level. Joins through the risk_mitigant_link bridge table to risk_mitigant_master and the risk_mitigant_type_dim taxonomy. Measures mitigation diversification — higher counts indicate broader collateral coverage across different sub-type categories (e.g. Sovereign Guarantee, Bank Guarantee, Cash Collateral, Real Estate, Equipment).
 </v>
       </c>
       <c r="C42" t="str">
         <v>Risk Mitigant Sub Type</v>
       </c>
       <c r="D42" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(risk_mitigant_subtype_code) per facility from risk_mitigant_type_dim.
+        <v xml:space="preserve">COUNT DISTINCT risk_mitigant_subtype_code per facility via risk_mitigant_link -&gt; risk_mitigant_master -&gt; risk_mitigant_type_dim. Only active mitigants with current link status.
 </v>
       </c>
       <c r="E42" t="str">
@@ -4232,7 +4296,7 @@
         <v>Agg</v>
       </c>
       <c r="J42" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(risk_mitigant_subtype_code) per facility from risk_mitigant_type_dim.
+        <v xml:space="preserve">COUNT DISTINCT risk_mitigant_subtype_code per facility via risk_mitigant_link -&gt; risk_mitigant_master -&gt; risk_mitigant_type_dim. Only active mitigants with current link status.
 </v>
       </c>
       <c r="K42" t="str">
@@ -4242,10 +4306,10 @@
         <v>Y</v>
       </c>
       <c r="M42" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="N42" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_mitigant_subtype_code per counterparty.
+        <v xml:space="preserve">COUNT DISTINCT risk_mitigant_subtype_code across all facilities per counterparty.
 </v>
       </c>
       <c r="O42" t="str">
@@ -4258,7 +4322,7 @@
         <v>Agg</v>
       </c>
       <c r="R42" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_mitigant_subtype_code per L3 desk segment.
+        <v xml:space="preserve">COUNT DISTINCT risk_mitigant_subtype_code across all facilities per L3 desk segment.
 </v>
       </c>
       <c r="S42" t="str">
@@ -4271,7 +4335,7 @@
         <v>Agg</v>
       </c>
       <c r="V42" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_mitigant_subtype_code per L2 portfolio segment.
+        <v xml:space="preserve">COUNT DISTINCT risk_mitigant_subtype_code across all facilities per L2 portfolio segment.
 </v>
       </c>
       <c r="W42" t="str">
@@ -4284,7 +4348,7 @@
         <v>Agg</v>
       </c>
       <c r="Z42" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_mitigant_subtype_code per L1 business segment segment.
+        <v xml:space="preserve">COUNT DISTINCT risk_mitigant_subtype_code across all facilities per L1 business segment.
 </v>
       </c>
       <c r="AA42" t="str">
@@ -4299,14 +4363,14 @@
         <v>EXP-034</v>
       </c>
       <c r="B43" t="str" xml:space="preserve">
-        <v xml:space="preserve">Parent group of risk mitigation or collateral asset type (e.g., cash, aviation, guarantee). Used to assess recovery support mechanisms.
+        <v xml:space="preserve">Count of distinct risk mitigant parent categories protecting exposure at each rollup level. Joins through the risk_mitigant_link bridge table to risk_mitigant_master and the risk_mitigant_type_dim taxonomy, reading the mitigant_category field (e.g. Cash, Real Estate, Guarantee, Insurance, Equipment). Provides a higher-level view of mitigation diversification compared to EXP-033 (sub-type detail). Supports recovery assessment and CRM eligibility analysis.
 </v>
       </c>
       <c r="C43" t="str">
         <v>Risk Mitigant Type</v>
       </c>
       <c r="D43" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(risk_mitigant_id) per facility from risk_mitigant_master.
+        <v xml:space="preserve">COUNT DISTINCT mitigant_category per facility via risk_mitigant_link -&gt; risk_mitigant_master -&gt; risk_mitigant_type_dim. Only active mitigants with current link status.
 </v>
       </c>
       <c r="E43" t="str">
@@ -4325,7 +4389,7 @@
         <v>Agg</v>
       </c>
       <c r="J43" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(risk_mitigant_id) per facility from risk_mitigant_master.
+        <v xml:space="preserve">COUNT DISTINCT mitigant_category per facility via risk_mitigant_link -&gt; risk_mitigant_master -&gt; risk_mitigant_type_dim. Only active mitigants with current link status.
 </v>
       </c>
       <c r="K43" t="str">
@@ -4335,10 +4399,10 @@
         <v>Y</v>
       </c>
       <c r="M43" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="N43" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_mitigant_id per counterparty.
+        <v xml:space="preserve">COUNT DISTINCT mitigant_category across all facilities per counterparty.
 </v>
       </c>
       <c r="O43" t="str">
@@ -4351,7 +4415,7 @@
         <v>Agg</v>
       </c>
       <c r="R43" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_mitigant_id per L3 desk segment.
+        <v xml:space="preserve">COUNT DISTINCT mitigant_category across all facilities per L3 desk segment.
 </v>
       </c>
       <c r="S43" t="str">
@@ -4364,7 +4428,7 @@
         <v>Agg</v>
       </c>
       <c r="V43" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_mitigant_id per L2 portfolio segment.
+        <v xml:space="preserve">COUNT DISTINCT mitigant_category across all facilities per L2 portfolio segment.
 </v>
       </c>
       <c r="W43" t="str">
@@ -4377,7 +4441,7 @@
         <v>Agg</v>
       </c>
       <c r="Z43" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_mitigant_id per L1 business segment segment.
+        <v xml:space="preserve">COUNT DISTINCT mitigant_category across all facilities per L1 business segment.
 </v>
       </c>
       <c r="AA43" t="str">
@@ -5796,14 +5860,15 @@
         <v>PRC-003</v>
       </c>
       <c r="B59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of exposures within portfolio with approved pricing or policy exceptions. Derived governance KPI measuring policy discipline and risk culture strength.
+        <v xml:space="preserve">Percentage of facilities with approved pricing or policy exceptions. Computed as COUNT(exception facilities) / COUNT(total facilities) × 100. Sourced from L2 facility_pricing_snapshot — the atomic pricing record — using the is_pricing_exception_flag. At aggregate levels, uses count-ratio rollup: re-counts exceptions and totals across all constituent facilities, never averages pre-computed rates. Key governance KPI measuring policy discipline, risk culture strength, and pricing override frequency.
 </v>
       </c>
       <c r="C59" t="str">
         <v>Exception Rate (%)</v>
       </c>
       <c r="D59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if pricing exception, 0 otherwise.
+        <v xml:space="preserve">Binary flag: 1.0 if pricing exception approved, 0.0 otherwise.
+Ingredients: is_pricing_exception_flag (L2 facility_pricing_snapshot)
 </v>
       </c>
       <c r="E59" t="str">
@@ -5822,7 +5887,8 @@
         <v>Calc</v>
       </c>
       <c r="J59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if pricing exception, 0 otherwise.
+        <v xml:space="preserve">Binary flag: 1.0 if pricing exception approved, 0.0 otherwise.
+Ingredients: is_pricing_exception_flag (L2 facility_pricing_snapshot)
 </v>
       </c>
       <c r="K59" t="str">
@@ -5835,7 +5901,10 @@
         <v>Calc</v>
       </c>
       <c r="N59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with pricing exception per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD is_pricing_exception_flag for all facilities of this counterparty
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup: re-counts from facility-level flags.
 </v>
       </c>
       <c r="O59" t="str">
@@ -5848,7 +5917,10 @@
         <v>Calc</v>
       </c>
       <c r="R59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with pricing exception per L3 desk.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOOKUP managed_segment_id from enterprise_business_taxonomy
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup per desk.
 </v>
       </c>
       <c r="S59" t="str">
@@ -5861,7 +5933,10 @@
         <v>Calc</v>
       </c>
       <c r="V59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with pricing exception per L2 portfolio.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup per portfolio.
 </v>
       </c>
       <c r="W59" t="str">
@@ -5874,7 +5949,10 @@
         <v>Calc</v>
       </c>
       <c r="Z59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with pricing exception per L1 business segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup per business segment.
 </v>
       </c>
       <c r="AA59" t="str">
@@ -6830,14 +6908,14 @@
         <v>REF-004</v>
       </c>
       <c r="B70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Unique system identifier assigned to the borrower or obligor. Used for exposure aggregation and risk consolidation.
+        <v xml:space="preserve">Unique system identifier assigned to the borrower or obligor. Used for exposure aggregation and risk consolidation across the GSIB. At facility level, returns the counterparty_id linked to each facility. At upper levels, returns COUNT(DISTINCT counterparty_id) — the number of unique obligors in each organizational segment.
 </v>
       </c>
       <c r="C70" t="str">
         <v>Counterparty ID</v>
       </c>
       <c r="D70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">Direct lookup of counterparty_id from facility_master for each active facility. Uses current records only (SCD2 filtered).
 </v>
       </c>
       <c r="E70" t="str">
@@ -6856,7 +6934,7 @@
         <v>Raw</v>
       </c>
       <c r="J70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">Direct lookup of counterparty_id from facility_master for each active facility. Uses current records only (SCD2 filtered).
 </v>
       </c>
       <c r="K70" t="str">
@@ -6869,7 +6947,7 @@
         <v>Raw</v>
       </c>
       <c r="N70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">Identity — returns counterparty_id for each current counterparty.
 </v>
       </c>
       <c r="O70" t="str">
@@ -6882,7 +6960,7 @@
         <v>Agg</v>
       </c>
       <c r="R70" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L3 desk segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L3 desk segment — number of unique obligors in each desk.
 </v>
       </c>
       <c r="S70" t="str">
@@ -6895,7 +6973,7 @@
         <v>Agg</v>
       </c>
       <c r="V70" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L2 portfolio segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L2 portfolio segment — number of unique obligors in each portfolio.
 </v>
       </c>
       <c r="W70" t="str">
@@ -6908,7 +6986,7 @@
         <v>Agg</v>
       </c>
       <c r="Z70" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L1 business segment segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L1 business segment — number of unique obligors in each business segment.
 </v>
       </c>
       <c r="AA70" t="str">
@@ -6923,14 +7001,14 @@
         <v>REF-005</v>
       </c>
       <c r="B71" t="str" xml:space="preserve">
-        <v xml:space="preserve">Descriptive name of the counterparty as documented in the credit agreement. Used for reporting clarity and operational reference.
+        <v xml:space="preserve">Legal name of the counterparty as documented in the credit agreement. At facility level, returns the counterparty_id (numeric proxy for the name since metric values are numeric). At counterparty level, identity lookup. At upper levels, COUNT(DISTINCT counterparty_id) — number of unique named obligors per organizational segment. Used for reporting clarity and operational reference across all regulatory submissions.
 </v>
       </c>
       <c r="C71" t="str">
         <v>Counterparty Name</v>
       </c>
       <c r="D71" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read legal_name from counterparty for each facility's counterparty.
+        <v xml:space="preserve">Lookup counterparty_id from facility_master for each active facility. The numeric counterparty_id serves as proxy for the legal name (string values resolved via counterparty dimension join at display time). Uses current records only.
 </v>
       </c>
       <c r="E71" t="str">
@@ -6949,7 +7027,7 @@
         <v>Raw</v>
       </c>
       <c r="J71" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read legal_name from counterparty for each facility's counterparty.
+        <v xml:space="preserve">Lookup counterparty_id from facility_master for each active facility. The numeric counterparty_id serves as proxy for the legal name (string values resolved via counterparty dimension join at display time). Uses current records only.
 </v>
       </c>
       <c r="K71" t="str">
@@ -6959,10 +7037,10 @@
         <v>Y</v>
       </c>
       <c r="M71" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="N71" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with counterparty name per counterparty.
+        <v xml:space="preserve">Identity — returns counterparty_id for each current counterparty. Legal name resolved via counterparty dimension join at display time.
 </v>
       </c>
       <c r="O71" t="str">
@@ -6975,7 +7053,7 @@
         <v>Agg</v>
       </c>
       <c r="R71" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with counterparty name per L3 desk segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L3 desk segment — number of unique named obligors in each desk.
 </v>
       </c>
       <c r="S71" t="str">
@@ -6988,7 +7066,7 @@
         <v>Agg</v>
       </c>
       <c r="V71" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with counterparty name per L2 portfolio segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L2 portfolio segment — number of unique named obligors in each portfolio.
 </v>
       </c>
       <c r="W71" t="str">
@@ -7001,7 +7079,7 @@
         <v>Agg</v>
       </c>
       <c r="Z71" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with counterparty name per L1 business segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L1 business segment — number of unique named obligors in each business segment.
 </v>
       </c>
       <c r="AA71" t="str">
@@ -7016,14 +7094,14 @@
         <v>REF-006</v>
       </c>
       <c r="B72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Country of risk or booking location. Supports geographic concentration and sovereign risk analysis.
+        <v xml:space="preserve">Country of risk derived from the counterparty's domicile. At facility level, returns a numeric country identifier (via counterparty → country_dim join path). At counterparty level, identity lookup. At desk/portfolio/segment levels, COUNT(DISTINCT country_code) — geographic diversification indicator showing the number of unique countries represented. Supports FFIEC 009 Country Exposure Report and Basel III geographic concentration analysis.
 </v>
       </c>
       <c r="C72" t="str">
         <v>Country</v>
       </c>
       <c r="D72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of country_name from country_dim.
+        <v xml:space="preserve">Lookup country for each facility via counterparty → country_dim join path. Returns counterparty_id as numeric proxy (country_name resolved at display time via dimension join). Uses current records only.
 </v>
       </c>
       <c r="E72" t="str">
@@ -7042,7 +7120,7 @@
         <v>Raw</v>
       </c>
       <c r="J72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of country_name from country_dim.
+        <v xml:space="preserve">Lookup country for each facility via counterparty → country_dim join path. Returns counterparty_id as numeric proxy (country_name resolved at display time via dimension join). Uses current records only.
 </v>
       </c>
       <c r="K72" t="str">
@@ -7055,7 +7133,7 @@
         <v>Raw</v>
       </c>
       <c r="N72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read country_name per counterparty.
+        <v xml:space="preserve">Lookup country for each counterparty via country_code → country_dim join. Returns counterparty_id as numeric proxy.
 </v>
       </c>
       <c r="O72" t="str">
@@ -7068,7 +7146,7 @@
         <v>Agg</v>
       </c>
       <c r="R72" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level country_name per L3 desk segment.
+        <v xml:space="preserve">COUNT(DISTINCT country_code) per L3 desk segment — number of unique countries represented, a geographic diversification indicator.
 </v>
       </c>
       <c r="S72" t="str">
@@ -7081,7 +7159,7 @@
         <v>Agg</v>
       </c>
       <c r="V72" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level country_name per L2 portfolio segment.
+        <v xml:space="preserve">COUNT(DISTINCT country_code) per L2 portfolio segment — number of unique countries represented in each portfolio.
 </v>
       </c>
       <c r="W72" t="str">
@@ -7094,7 +7172,7 @@
         <v>Agg</v>
       </c>
       <c r="Z72" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level country_name per L1 business segment segment.
+        <v xml:space="preserve">COUNT(DISTINCT country_code) per L1 business segment — geographic diversification at the highest organizational level.
 </v>
       </c>
       <c r="AA72" t="str">
@@ -7109,14 +7187,14 @@
         <v>REF-007</v>
       </c>
       <c r="B73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Unique identifier linking facility to governing credit agreement documentation.
+        <v xml:space="preserve">Unique identifier linking each facility to its governing credit agreement documentation. Used for contract tracking, facility-to-agreement linkage, and regulatory reporting. At counterparty level, returns count of distinct credit agreements per borrower.
 </v>
       </c>
       <c r="C73" t="str">
         <v>Credit Agreement ID</v>
       </c>
       <c r="D73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of credit_agreement_id from credit_agreement_master.
+        <v xml:space="preserve">Direct lookup of credit_agreement_id for each active facility via facility_master joined to credit_agreement_master.
 </v>
       </c>
       <c r="E73" t="str">
@@ -7135,7 +7213,7 @@
         <v>Raw</v>
       </c>
       <c r="J73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of credit_agreement_id from credit_agreement_master.
+        <v xml:space="preserve">Direct lookup of credit_agreement_id for each active facility via facility_master joined to credit_agreement_master.
 </v>
       </c>
       <c r="K73" t="str">
@@ -7145,10 +7223,10 @@
         <v>Y</v>
       </c>
       <c r="M73" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="N73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read credit_agreement_id per counterparty.
+        <v xml:space="preserve">Count of distinct credit agreements per counterparty. Provides visibility into borrower complexity and multi-agreement relationships.
 </v>
       </c>
       <c r="O73" t="str">
@@ -7161,7 +7239,7 @@
         <v>Agg</v>
       </c>
       <c r="R73" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level credit_agreement_id per L3 desk segment.
+        <v xml:space="preserve">Count of distinct credit agreements per L3 desk segment via enterprise_business_taxonomy.
 </v>
       </c>
       <c r="S73" t="str">
@@ -7174,7 +7252,7 @@
         <v>Agg</v>
       </c>
       <c r="V73" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level credit_agreement_id per L2 portfolio segment.
+        <v xml:space="preserve">Count of distinct credit agreements per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
 </v>
       </c>
       <c r="W73" t="str">
@@ -7187,7 +7265,7 @@
         <v>Agg</v>
       </c>
       <c r="Z73" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level credit_agreement_id per L1 business segment segment.
+        <v xml:space="preserve">Count of distinct credit agreements per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
 </v>
       </c>
       <c r="AA73" t="str">
@@ -7295,7 +7373,7 @@
         <v>REF-009</v>
       </c>
       <c r="B75" t="str" xml:space="preserve">
-        <v xml:space="preserve">Date on which loan or contract became legally effective.
+        <v xml:space="preserve">Date on which loan or contract became legally effective. Sourced directly from facility_master. At aggregate levels, returns the earliest origination date (MIN) across constituent facilities — indicating the oldest vintage in the book. Key contract lifecycle tracking attribute for vintage analysis and portfolio seasoning assessment.
 </v>
       </c>
       <c r="C75" t="str">
@@ -7303,6 +7381,7 @@
       </c>
       <c r="D75" t="str" xml:space="preserve">
         <v xml:space="preserve">Direct lookup of origination_date from facility_master.
+Ingredients: origination_date (L2 facility_master — raw field)
 </v>
       </c>
       <c r="E75" t="str">
@@ -7322,6 +7401,7 @@
       </c>
       <c r="J75" t="str" xml:space="preserve">
         <v xml:space="preserve">Direct lookup of origination_date from facility_master.
+Ingredients: origination_date (L2 facility_master — raw field)
 </v>
       </c>
       <c r="K75" t="str">
@@ -7334,7 +7414,10 @@
         <v>Agg</v>
       </c>
       <c r="N75" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level origination_date) per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD origination_date from l2.facility_master for all active facilities
+  2. COMPUTE MIN(origination_date) — earliest contract vintage
+Indicates the oldest banking relationship tenure for this counterparty.
 </v>
       </c>
       <c r="O75" t="str">
@@ -7347,7 +7430,10 @@
         <v>Agg</v>
       </c>
       <c r="R75" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level origination_date per L3 desk segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOAD origination_date from l2.facility_master
+  2. JOIN l1.enterprise_business_taxonomy on lob_segment_id
+  3. COMPUTE MIN(origination_date) — earliest vintage in desk book
 </v>
       </c>
       <c r="S75" t="str">
@@ -7360,7 +7446,9 @@
         <v>Agg</v>
       </c>
       <c r="V75" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level origination_date per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. COMPUTE MIN(origination_date) — earliest vintage in portfolio
 </v>
       </c>
       <c r="W75" t="str">
@@ -7373,7 +7461,9 @@
         <v>Agg</v>
       </c>
       <c r="Z75" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level origination_date per L1 business segment segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. COMPUTE MIN(origination_date) — earliest vintage in business segment
 </v>
       </c>
       <c r="AA75" t="str">
@@ -9620,14 +9710,14 @@
         <v>RSK-001</v>
       </c>
       <c r="B100" t="str" xml:space="preserve">
-        <v xml:space="preserve">Most recent internal credit rating assigned at reporting date. Used for segmentation and exposure-weighted risk aggregation.
+        <v xml:space="preserve">Risk rating tier derived from counterparty probability of default (PD). Each counterparty's pd_annual is matched against the risk_rating_tier_dim reference table (pd_min_pct / pd_max_pct boundaries) to assign a tier classification. At facility level, the tier is inherited from the owning counterparty. At aggregate levels, MAX (worst-case) tier ordinal is reported.
 </v>
       </c>
       <c r="C100" t="str">
         <v>Risk Rating Tier</v>
       </c>
       <c r="D100" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility.
+        <v xml:space="preserve">For each facility, inherit the risk rating tier from the owning counterparty. Join facility_master to counterparty, then range-match counterparty pd_annual against risk_rating_tier_dim to derive the tier ordinal (display_order).
 </v>
       </c>
       <c r="E100" t="str">
@@ -9643,10 +9733,10 @@
         <v>Y</v>
       </c>
       <c r="I100" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="J100" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility.
+        <v xml:space="preserve">For each facility, inherit the risk rating tier from the owning counterparty. Join facility_master to counterparty, then range-match counterparty pd_annual against risk_rating_tier_dim to derive the tier ordinal (display_order).
 </v>
       </c>
       <c r="K100" t="str">
@@ -9656,10 +9746,10 @@
         <v>Y</v>
       </c>
       <c r="M100" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N100" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating per counterparty.
+        <v xml:space="preserve">For each counterparty, look up pd_annual and range-match against risk_rating_tier_dim where pd_annual &gt;= pd_min_pct AND pd_annual &lt; pd_max_pct. Returns the tier ordinal (display_order). Counterparties with NULL PD receive tier 0 (unrated).
 </v>
       </c>
       <c r="O100" t="str">
@@ -9672,7 +9762,7 @@
         <v>Agg</v>
       </c>
       <c r="R100" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating per L3 desk segment.
+        <v xml:space="preserve">Worst-case (MAX) risk rating tier ordinal across all counterparties in the L3 desk segment. Higher ordinal = riskier tier. Full tier distribution available via counterparty-level drill-down.
 </v>
       </c>
       <c r="S100" t="str">
@@ -9685,7 +9775,7 @@
         <v>Agg</v>
       </c>
       <c r="V100" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating per L2 portfolio segment.
+        <v xml:space="preserve">Worst-case (MAX) risk rating tier ordinal per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
 </v>
       </c>
       <c r="W100" t="str">
@@ -9698,7 +9788,7 @@
         <v>Agg</v>
       </c>
       <c r="Z100" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating per L1 business segment.
+        <v xml:space="preserve">Worst-case (MAX) risk rating tier ordinal per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
 </v>
       </c>
       <c r="AA100" t="str">
@@ -10085,14 +10175,14 @@
         <v>RSK-006</v>
       </c>
       <c r="B105" t="str" xml:space="preserve">
-        <v xml:space="preserve">Derived directional classification indicating whether the internal credit rating has changed month over month: upgraded (e.g. 3 to 1), downgraded (e.g. 1 to 3), or remained stable (remained costant month-over month) compared to the prior reporting period. Note when this is displayed at an aggregated Line of Business or portfolio level, it is determined by the month-over-month change of the average rating at this level. Provides migration trend insight and serves as an early warning indicator of credit quality movement to support proactive risk management and escalation decisions.
+        <v xml:space="preserve">Directional classification indicating whether the internal credit rating has changed month-over-month: Upgrade (positive notch movement), Downgrade (negative notch movement), or Stable (no change). At facility/counterparty level, reads the pre-computed risk_rating_status from the internal rating observation. At aggregate levels (desk, portfolio, business segment), derives the direction from the average of counterparty-level risk_rating_change_steps — each counterparty counted once per segment to avoid facility-count bias. Provides migration trend insight and serves as an early warning indicator of credit quality movement.
 </v>
       </c>
       <c r="C105" t="str">
         <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable)</v>
       </c>
       <c r="D105" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility as-of reporting date.
+        <v xml:space="preserve">Read risk_rating_status from internal counterparty_rating_observation. Each facility inherits its counterparty's internal rating status.
 </v>
       </c>
       <c r="E105" t="str">
@@ -10111,7 +10201,7 @@
         <v>Raw</v>
       </c>
       <c r="J105" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility as-of reporting date.
+        <v xml:space="preserve">Read risk_rating_status from internal counterparty_rating_observation. Each facility inherits its counterparty's internal rating status.
 </v>
       </c>
       <c r="K105" t="str">
@@ -10121,10 +10211,10 @@
         <v>Y</v>
       </c>
       <c r="M105" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="N105" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_status per counterparty.
+        <v xml:space="preserve">Read risk_rating_status directly from internal counterparty_rating_observation.
 </v>
       </c>
       <c r="O105" t="str">
@@ -10134,10 +10224,10 @@
         <v>Y</v>
       </c>
       <c r="Q105" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R105" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_status per L3 desk segment.
+        <v xml:space="preserve">Average internal risk_rating_change_steps across distinct counterparties in the L3 desk segment, then classify: &gt;0 Upgrade, &lt;0 Downgrade, =0 Stable. Counterparties de-duplicated per segment to avoid facility-count bias.
 </v>
       </c>
       <c r="S105" t="str">
@@ -10147,10 +10237,10 @@
         <v>Y</v>
       </c>
       <c r="U105" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V105" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_status per L2 portfolio segment.
+        <v xml:space="preserve">Average internal risk_rating_change_steps across distinct counterparties in the L2 portfolio segment, then classify direction.
 </v>
       </c>
       <c r="W105" t="str">
@@ -10160,10 +10250,10 @@
         <v>Y</v>
       </c>
       <c r="Y105" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z105" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_status per L1 business segment segment.
+        <v xml:space="preserve">Average internal risk_rating_change_steps across distinct counterparties in the L1 business segment, then classify direction.
 </v>
       </c>
       <c r="AA105" t="str">
@@ -10178,14 +10268,14 @@
         <v>RSK-007</v>
       </c>
       <c r="B106" t="str" xml:space="preserve">
-        <v xml:space="preserve">Numerical representation of internal risk rating migration (month over month changes) expressed in notch movement (positive or negative). Positive step changes are identified when there is an upgrade, from 3 to 1and the step change is +2, where as the negative step change is identified when there is a downgrade from 5 to 8 and the step change is -3. Note when this is displayed at an aggregated Line of Business or portfolio level, it is determined by the month-over-month change of the average rating at this level. Quantifies magnitude of credit change and enables portfolio-level migration analysis, stress testing sensitivity, and risk trend measurement.
+        <v xml:space="preserve">Numerical representation of internal risk rating migration expressed in notch movement. Positive values indicate upgrades (e.g. rating 3 to 1 = +2 steps), negative values indicate downgrades (e.g. rating 5 to 8 = -3 steps), zero indicates stable. At facility/counterparty level, reads the pre-computed risk_rating_change_steps from the internal rating observation. At aggregate levels (desk, portfolio, business segment), computes the rounded average of counterparty-level change steps — each counterparty counted once per segment to avoid facility-count bias. Quantifies magnitude of credit migration for portfolio-level trend analysis and stress testing.
 </v>
       </c>
       <c r="C106" t="str">
         <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps)</v>
       </c>
       <c r="D106" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_change_steps from counterparty_rating_observation for each facility as-of reporting date.
+        <v xml:space="preserve">Read risk_rating_change_steps from internal counterparty_rating_observation. Each facility inherits its counterparty's internal rating change magnitude.
 </v>
       </c>
       <c r="E106" t="str">
@@ -10204,7 +10294,7 @@
         <v>Raw</v>
       </c>
       <c r="J106" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_change_steps from counterparty_rating_observation for each facility as-of reporting date.
+        <v xml:space="preserve">Read risk_rating_change_steps from internal counterparty_rating_observation. Each facility inherits its counterparty's internal rating change magnitude.
 </v>
       </c>
       <c r="K106" t="str">
@@ -10214,10 +10304,10 @@
         <v>Y</v>
       </c>
       <c r="M106" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="N106" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per counterparty.
+        <v xml:space="preserve">Read risk_rating_change_steps directly from internal counterparty_rating_observation.
 </v>
       </c>
       <c r="O106" t="str">
@@ -10227,10 +10317,10 @@
         <v>Y</v>
       </c>
       <c r="Q106" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="R106" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per L3 desk segment.
+        <v xml:space="preserve">Rounded average of counterparty-level risk_rating_change_steps across distinct counterparties in the L3 desk segment. Counterparties de-duplicated per segment to avoid facility-count bias.
 </v>
       </c>
       <c r="S106" t="str">
@@ -10240,10 +10330,10 @@
         <v>Y</v>
       </c>
       <c r="U106" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="V106" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per L2 portfolio segment.
+        <v xml:space="preserve">Rounded average of counterparty-level risk_rating_change_steps across distinct counterparties in the L2 portfolio segment.
 </v>
       </c>
       <c r="W106" t="str">
@@ -10253,10 +10343,10 @@
         <v>Y</v>
       </c>
       <c r="Y106" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="Z106" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per L1 business segment segment.
+        <v xml:space="preserve">Rounded average of counterparty-level risk_rating_change_steps across distinct counterparties in the L1 business segment.
 </v>
       </c>
       <c r="AA106" t="str">

--- a/data/metrics_dimensions_filled.xlsx
+++ b/data/metrics_dimensions_filled.xlsx
@@ -1539,14 +1539,14 @@
         <v>EXP-005</v>
       </c>
       <c r="B14" t="str" xml:space="preserve">
-        <v xml:space="preserve">The portion of total funding-related expense attributed to a specific exposure or portfolio. At facility level, calculated as SUM across all positions of (funded_amount * interest_rate), adjusted for bank share. At counterparty level, further adjusted by counterparty participation_pct. At desk/portfolio/segment levels, aggregated as SUM.
+        <v xml:space="preserve">The portion of total funding-related expense attributed to a specific exposure or portfolio. At facility level, calculated as SUM across all positions of (funded_amount * interest_rate), converted to USD via FX rate and adjusted for bank share. At counterparty level, further adjusted by counterparty participation_pct. At desk/portfolio/segment levels, aggregated as SUM via EBT hierarchy.
 </v>
       </c>
       <c r="C14" t="str">
         <v>Cost of Funds ($)</v>
       </c>
       <c r="D14" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each position under the facility: funded_amount * interest_rate = Position Cost of Funds. Adjusted by bank_share: SUM(funded_amount * interest_rate) * bank_share_pct / 100. Joins position_detail → position (for facility_id) → facility_master.
+        <v xml:space="preserve">For each position under the facility, compute funded_amount x interest_rate, convert to USD using the FX spot rate (defaults to 1.0 for USD positions). Sum across all positions, then multiply by the bank's share percentage. Result = annual cost of funds for this facility in USD.
 </v>
       </c>
       <c r="E14" t="str">
@@ -1565,7 +1565,7 @@
         <v>Calc</v>
       </c>
       <c r="J14" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each position under the facility: funded_amount * interest_rate = Position Cost of Funds. Adjusted by bank_share: SUM(funded_amount * interest_rate) * bank_share_pct / 100. Joins position_detail → position (for facility_id) → facility_master.
+        <v xml:space="preserve">For each position under the facility, compute funded_amount x interest_rate, convert to USD using the FX spot rate (defaults to 1.0 for USD positions). Sum across all positions, then multiply by the bank's share percentage. Result = annual cost of funds for this facility in USD.
 </v>
       </c>
       <c r="K14" t="str">
@@ -1578,7 +1578,7 @@
         <v>Agg</v>
       </c>
       <c r="N14" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each counterparty: SUM of facility-level cost of funds weighted by counterparty participation_pct from facility_counterparty_participation.
+        <v xml:space="preserve">Sum each facility's cost of funds (USD, bank-share-adjusted), then weight by the counterparty's participation percentage. Aggregates across all facilities where the counterparty has a current participation record.
 </v>
       </c>
       <c r="O14" t="str">
@@ -1591,7 +1591,7 @@
         <v>Agg</v>
       </c>
       <c r="R14" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level cost of funds (bank-share-adjusted) per L3 desk segment.
+        <v xml:space="preserve">Sum of facility-level cost of funds (USD, bank-share-adjusted) for all facilities assigned to each L3 desk segment in the organizational hierarchy.
 </v>
       </c>
       <c r="S14" t="str">
@@ -1604,7 +1604,7 @@
         <v>Agg</v>
       </c>
       <c r="V14" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level cost of funds (bank-share-adjusted) per L2 portfolio segment.
+        <v xml:space="preserve">Sum of facility-level cost of funds (USD, bank-share-adjusted) for all facilities within each L2 portfolio segment, traversing the EBT hierarchy from desk (L3) to portfolio (L2) via parent_segment_id.
 </v>
       </c>
       <c r="W14" t="str">
@@ -1617,7 +1617,7 @@
         <v>Agg</v>
       </c>
       <c r="Z14" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level cost of funds (bank-share-adjusted) per L1 business segment.
+        <v xml:space="preserve">Sum of facility-level cost of funds (USD, bank-share-adjusted) for all facilities within each L1 business segment, traversing the full EBT hierarchy from desk (L3) through portfolio (L2) to segment (L1).
 </v>
       </c>
       <c r="AA14" t="str">
@@ -1632,14 +1632,14 @@
         <v>EXP-006</v>
       </c>
       <c r="B15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure allocated to specific counterparty representing their share of the facility which the client can draw on. Concentration KPI measuring obligor dependency risk.
+        <v xml:space="preserve">Counterparty participation share in a facility — the percentage of a syndicated or participated facility allocated to a specific counterparty. At facility level, direct lookup from facility_counterparty_participation. At counterparty level, exposure-weighted average participation across all facilities. At desk/portfolio/segment, exposure-weighted average via EBT hierarchy. Key concentration KPI for Large Exposures Framework (LEX) and Single Counterparty Credit Limit (SCCL) compliance.
 </v>
       </c>
       <c r="C15" t="str">
         <v>Counterparty Share or Allocation (%)</v>
       </c>
       <c r="D15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of allocation_pct from facility_counterparty_participation.
+        <v xml:space="preserve">Direct lookup of participation_pct from facility_counterparty_participation for the primary counterparty on each facility. Uses current records only.
 </v>
       </c>
       <c r="E15" t="str">
@@ -1658,7 +1658,7 @@
         <v>Raw</v>
       </c>
       <c r="J15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of allocation_pct from facility_counterparty_participation.
+        <v xml:space="preserve">Direct lookup of participation_pct from facility_counterparty_participation for the primary counterparty on each facility. Uses current records only.
 </v>
       </c>
       <c r="K15" t="str">
@@ -1668,10 +1668,10 @@
         <v>Y</v>
       </c>
       <c r="M15" t="str">
-        <v>Raw</v>
+        <v>Avg</v>
       </c>
       <c r="N15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read allocation_pct per counterparty.
+        <v xml:space="preserve">Exposure-weighted average participation across all facilities for each counterparty. Weight = drawn_amount from facility_exposure_snapshot. Falls back to simple average if no exposure data available.
 </v>
       </c>
       <c r="O15" t="str">
@@ -1681,10 +1681,10 @@
         <v>Y</v>
       </c>
       <c r="Q15" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="R15" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level allocation_pct per L3 desk segment.
+        <v xml:space="preserve">Exposure-weighted average participation across all facilities per L3 desk segment via enterprise_business_taxonomy.
 </v>
       </c>
       <c r="S15" t="str">
@@ -1694,10 +1694,10 @@
         <v>Y</v>
       </c>
       <c r="U15" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="V15" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level allocation_pct per L2 portfolio segment.
+        <v xml:space="preserve">Exposure-weighted average participation across all facilities per L2 portfolio segment via enterprise_business_taxonomy hierarchy traversal.
 </v>
       </c>
       <c r="W15" t="str">
@@ -1707,10 +1707,10 @@
         <v>Y</v>
       </c>
       <c r="Y15" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="Z15" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level allocation_pct per L1 business segment segment.
+        <v xml:space="preserve">Exposure-weighted average participation across all facilities per L1 business segment via enterprise_business_taxonomy hierarchy traversal.
 </v>
       </c>
       <c r="AA15" t="str">
@@ -1725,14 +1725,14 @@
         <v>EXP-007</v>
       </c>
       <c r="B16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Flag identifying exposures requiring heightened monitoring due to elevated credit risk. Governance control used for enhanced monitoring, reserve consideration, and management reporting.
+        <v xml:space="preserve">Count of active Criticized risk flags across facilities. Early warning indicator of problem assets requiring heightened monitoring, reserve consideration, and management reporting. Sources from the risk_flag table filtering on flag_code = 'CRITICIZED' with uncleared status.
 </v>
       </c>
       <c r="C16" t="str">
         <v>Criticized Portfolios</v>
       </c>
       <c r="D16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if criticized rating (internal_risk_rating &gt;= 6), 0 otherwise.
+        <v xml:space="preserve">For each facility, count active risk flags where flag_code = 'CRITICIZED' and the flag has not been cleared (cleared_ts IS NULL).
 </v>
       </c>
       <c r="E16" t="str">
@@ -1748,10 +1748,10 @@
         <v>Y</v>
       </c>
       <c r="I16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="J16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if criticized rating (internal_risk_rating &gt;= 6), 0 otherwise.
+        <v xml:space="preserve">For each facility, count active risk flags where flag_code = 'CRITICIZED' and the flag has not been cleared (cleared_ts IS NULL).
 </v>
       </c>
       <c r="K16" t="str">
@@ -1761,10 +1761,10 @@
         <v>Y</v>
       </c>
       <c r="M16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="N16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per counterparty.
+        <v xml:space="preserve">For each counterparty, sum facility-level criticized flag counts across all facilities belonging to that counterparty.
 </v>
       </c>
       <c r="O16" t="str">
@@ -1774,10 +1774,10 @@
         <v>Y</v>
       </c>
       <c r="Q16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="R16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per L3 desk.
+        <v xml:space="preserve">Sum of criticized flag counts per L3 desk segment. Joins facility_master to enterprise_business_taxonomy via lob_segment_id.
 </v>
       </c>
       <c r="S16" t="str">
@@ -1787,10 +1787,10 @@
         <v>Y</v>
       </c>
       <c r="U16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="V16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per L2 portfolio.
+        <v xml:space="preserve">Sum of criticized flag counts per L2 portfolio segment. Traverses enterprise_business_taxonomy hierarchy from L3 to L2 via parent_segment_id.
 </v>
       </c>
       <c r="W16" t="str">
@@ -1800,10 +1800,10 @@
         <v>Y</v>
       </c>
       <c r="Y16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="Z16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per L1 business segment.
+        <v xml:space="preserve">Sum of criticized flag counts per L1 business segment. Full hierarchy traversal L3 → L2 → L1 via enterprise_business_taxonomy.
 </v>
       </c>
       <c r="AA16" t="str">
@@ -1818,14 +1818,14 @@
         <v>EXP-008</v>
       </c>
       <c r="B17" t="str" xml:space="preserve">
-        <v xml:space="preserve">Total exposure amount allocated across multiple legal entities. Supports intra-group concentration transparency.
+        <v xml:space="preserve">Total committed exposure amount (bank share) allocated across multiple legal entities for facilities flagged as cross-entity. Quantifies inter-entity concentration risk and supports intra-group transparency for GSIB reporting. Sources from counterparty_derived (L3) for the cross-entity flag and facility_exposure_snapshot (L2) for committed amounts.
 </v>
       </c>
       <c r="C17" t="str">
         <v>Cross Entity Exposure Amount</v>
       </c>
       <c r="D17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(total_cross_entity_exposure_usd) per facility from counterparty_exposure_summary. Weighted by bank share percentage.
+        <v xml:space="preserve">For each facility flagged as cross-entity, committed exposure amount weighted by the bank's participation share (bank_share_pct). Facilities without cross-entity flag are excluded.
 </v>
       </c>
       <c r="E17" t="str">
@@ -1844,7 +1844,7 @@
         <v>Agg</v>
       </c>
       <c r="J17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(total_cross_entity_exposure_usd) per facility from counterparty_exposure_summary. Weighted by bank share percentage.
+        <v xml:space="preserve">For each facility flagged as cross-entity, committed exposure amount weighted by the bank's participation share (bank_share_pct). Facilities without cross-entity flag are excluded.
 </v>
       </c>
       <c r="K17" t="str">
@@ -1857,7 +1857,7 @@
         <v>Agg</v>
       </c>
       <c r="N17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per counterparty.
+        <v xml:space="preserve">For each counterparty, sum of bank-share-weighted committed amounts across all facilities flagged as cross-entity.
 </v>
       </c>
       <c r="O17" t="str">
@@ -1870,7 +1870,7 @@
         <v>Agg</v>
       </c>
       <c r="R17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per L3 desk segment.
+        <v xml:space="preserve">Sum of cross-entity committed exposure per L3 desk segment via enterprise_business_taxonomy.
 </v>
       </c>
       <c r="S17" t="str">
@@ -1883,7 +1883,7 @@
         <v>Agg</v>
       </c>
       <c r="V17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per L2 portfolio segment.
+        <v xml:space="preserve">Sum of cross-entity committed exposure per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
 </v>
       </c>
       <c r="W17" t="str">
@@ -1896,7 +1896,7 @@
         <v>Agg</v>
       </c>
       <c r="Z17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per L1 business segment segment.
+        <v xml:space="preserve">Sum of cross-entity committed exposure per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
 </v>
       </c>
       <c r="AA17" t="str">
@@ -1911,14 +1911,14 @@
         <v>EXP-009</v>
       </c>
       <c r="B18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Number of days outstanding payments is past due as grouped into 3 "buckets", 0-30 Days, 31-60 Days, 61-90+ Days. Used for staging classification and early credit deterioration monitoring.
+        <v xml:space="preserve">Maximum days payment overdue per facility, calculated from raw payment records in the payment_ledger table. For each facility, identifies payments where applied amount &lt; amount due, computes days overdue as reporting date minus payment_due_date, takes the MAX, then classifies into buckets: 1 = 0-30 days, 2 = 31-60 days, 3 = 61-90+ days. At aggregate levels, reports the worst (MAX) bucket across constituents.
 </v>
       </c>
       <c r="C18" t="str">
         <v>Days Payment Overdue Bucket</v>
       </c>
       <c r="D18" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Facility_ID lookup the Payments records in the Payment Lockbox table, For each payment record where [Payment_Due_Date] &gt; Today() IF ([Pmt_Applied] &lt;[Pmt_Due])&gt;=1, THEN Today() - [Payment_due_date] ==[Days Overdue] SELECT MAX ([Days Overdue] then lookup in Payments Overdue bucket)
+        <v xml:space="preserve">For each facility, lookup payment records in payment_ledger where payment_due_date &lt; reporting date and payment_applied_amt &lt; payment_amount_due (underpaid). Calculate days overdue = reporting date minus payment_due_date. Take MAX days overdue, then classify into overdue bucket: 1 (0-30), 2 (31-60), 3 (61-90+).
 </v>
       </c>
       <c r="E18" t="str">
@@ -1937,7 +1937,7 @@
         <v>Calc</v>
       </c>
       <c r="J18" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Facility_ID lookup the Payments records in the Payment Lockbox table, For each payment record where [Payment_Due_Date] &gt; Today() IF ([Pmt_Applied] &lt;[Pmt_Due])&gt;=1, THEN Today() - [Payment_due_date] ==[Days Overdue] SELECT MAX ([Days Overdue] then lookup in Payments Overdue bucket)
+        <v xml:space="preserve">For each facility, lookup payment records in payment_ledger where payment_due_date &lt; reporting date and payment_applied_amt &lt; payment_amount_due (underpaid). Calculate days overdue = reporting date minus payment_due_date. Take MAX days overdue, then classify into overdue bucket: 1 (0-30), 2 (31-60), 3 (61-90+).
 </v>
       </c>
       <c r="K18" t="str">
@@ -1950,7 +1950,7 @@
         <v>Agg</v>
       </c>
       <c r="N18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per counterparty.
+        <v xml:space="preserve">Worst-case (MAX) overdue bucket across all facilities per counterparty. Identifies the most severely overdue facility for each borrower.
 </v>
       </c>
       <c r="O18" t="str">
@@ -1963,7 +1963,7 @@
         <v>Agg</v>
       </c>
       <c r="R18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per L3 desk segment.
+        <v xml:space="preserve">Worst-case (MAX) overdue bucket per L3 desk segment. Shows the most severe delinquency in each organizational unit.
 </v>
       </c>
       <c r="S18" t="str">
@@ -1976,7 +1976,7 @@
         <v>Agg</v>
       </c>
       <c r="V18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per L2 portfolio segment.
+        <v xml:space="preserve">Worst-case (MAX) overdue bucket per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
 </v>
       </c>
       <c r="W18" t="str">
@@ -1989,7 +1989,7 @@
         <v>Agg</v>
       </c>
       <c r="Z18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per L1 business segment.
+        <v xml:space="preserve">Worst-case (MAX) overdue bucket per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
 </v>
       </c>
       <c r="AA18" t="str">
@@ -2509,14 +2509,25 @@
         <v>EXP-015</v>
       </c>
       <c r="B24" t="str" xml:space="preserve">
-        <v xml:space="preserve">Expected Loss divided by Exposure. Derived KPI measuring loss intensity relative to exposure size, enabling comparative risk ranking across facilities or counterparties.
+        <v xml:space="preserve">Expected Loss as a percentage of committed exposure. Computed from L2 atomic risk parameters: PD (probability of default) × LGD (loss given default). At aggregate levels, uses sum-ratio rollup: SUM(PD × LGD × Committed) / SUM(Committed) × 100 — the exposure-weighted average EL rate. This ensures mathematically consistent aggregation (never averages pre-computed rates). Key credit risk quantification metric for comparing loss intensity across facilities, counterparties, and business segments.
+Ingredient derivation:
+  - PD (pd_pct): L2 facility_risk_snapshot — probability of default (%)
+  - LGD (lgd_pct): L2 facility_risk_snapshot — loss given default (%)
+  - Committed Exposure (committed_amount): L2 facility_exposure_snapshot — raw
+  - EL Rate = PD × LGD (at facility level, committed cancels in ratio)
+  - Aggregate EL Rate = SUM(PD × LGD × Committed) / SUM(Committed) × 100
 </v>
       </c>
       <c r="C24" t="str">
         <v>Expected Loss Rate (%)</v>
       </c>
       <c r="D24" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of expected_loss_rate_pct per facility.
+        <v xml:space="preserve">For each facility:
+  1. LOAD pd_pct, lgd_pct from l2.facility_risk_snapshot
+  2. LOAD committed_amount from l2.facility_exposure_snapshot
+  3. COMPUTE EL Rate = SUM(PD/100 × LGD/100 × Committed) / SUM(Committed) × 100
+     At facility grain, committed cancels → EL Rate ≈ PD × LGD / 100
+Ingredients: pd_pct (L2), lgd_pct (L2), committed_amount (L2)
 </v>
       </c>
       <c r="E24" t="str">
@@ -2532,10 +2543,15 @@
         <v>Y</v>
       </c>
       <c r="I24" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="J24" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of expected_loss_rate_pct per facility.
+        <v xml:space="preserve">For each facility:
+  1. LOAD pd_pct, lgd_pct from l2.facility_risk_snapshot
+  2. LOAD committed_amount from l2.facility_exposure_snapshot
+  3. COMPUTE EL Rate = SUM(PD/100 × LGD/100 × Committed) / SUM(Committed) × 100
+     At facility grain, committed cancels → EL Rate ≈ PD × LGD / 100
+Ingredients: pd_pct (L2), lgd_pct (L2), committed_amount (L2)
 </v>
       </c>
       <c r="K24" t="str">
@@ -2545,10 +2561,15 @@
         <v>Y</v>
       </c>
       <c r="M24" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N24" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level expected_loss_rate_pct per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD pd_pct, lgd_pct for all facilities belonging to this counterparty
+  2. LOAD committed_amount for each facility
+  3. CONVERT to USD via l2.fx_rate spot rate
+  4. COMPUTE SUM(PD × LGD × Committed × FX) / SUM(Committed × FX) × 100
+Sum-ratio rollup with FX: exposure-weighted average EL rate in USD terms.
 </v>
       </c>
       <c r="O24" t="str">
@@ -2558,10 +2579,14 @@
         <v>Y</v>
       </c>
       <c r="Q24" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="R24" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level expected_loss_rate_pct per L3 desk segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOOKUP managed_segment_id from enterprise_business_taxonomy
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(PD × LGD × Committed × FX) / SUM(Committed × FX) × 100
+Sum-ratio rollup: exposure-weighted average EL rate per desk.
 </v>
       </c>
       <c r="S24" t="str">
@@ -2571,10 +2596,14 @@
         <v>Y</v>
       </c>
       <c r="U24" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V24" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level expected_loss_rate_pct per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(PD × LGD × Committed × FX) / SUM(Committed × FX) × 100
+Sum-ratio rollup: exposure-weighted average EL rate per portfolio.
 </v>
       </c>
       <c r="W24" t="str">
@@ -2584,10 +2613,14 @@
         <v>Y</v>
       </c>
       <c r="Y24" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z24" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level expected_loss_rate_pct per L1 business segment segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(PD × LGD × Committed × FX) / SUM(Committed × FX) × 100
+Sum-ratio rollup: exposure-weighted average EL rate per segment.
 </v>
       </c>
       <c r="AA24" t="str">
@@ -2602,14 +2635,25 @@
         <v>EXP-016</v>
       </c>
       <c r="B25" t="str" xml:space="preserve">
-        <v xml:space="preserve">PD × LGD × Exposure expressed in USD. Calculated forward-looking loss metric supporting provisioning, capital planning, and stress testing analytics.
+        <v xml:space="preserve">Expected Loss in dollar terms: PD × LGD × Committed Exposure × Bank Share. Computed from L2 atomic risk parameters and exposure data — NOT from stressed scenarios. This is the base (unstressed) expected credit loss, the foundation for provisioning, capital planning, and CECL/IFRS 9 reserve estimation.
+Ingredient derivation:
+  - PD (pd_pct): L2 facility_risk_snapshot — probability of default (%)
+  - LGD (lgd_pct): L2 facility_risk_snapshot — loss given default (%)
+  - Committed Exposure (committed_amount): L2 facility_exposure_snapshot — raw
+  - Bank Share (bank_share_pct): L2 facility_exposure_snapshot — participation %
+  - EL = (PD/100) × (LGD/100) × Committed × (Bank Share/100)
+Rollup uses direct-sum: SUM(facility EL) at each aggregate level. FX conversion applied at aggregate levels for multi-currency portfolios.
 </v>
       </c>
       <c r="C25" t="str">
         <v>Expected Loss ($)</v>
       </c>
       <c r="D25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(stressed_expected_loss) per facility from stress_test_result. Weighted by bank share percentage.
+        <v xml:space="preserve">For each facility:
+  1. LOAD pd_pct, lgd_pct from l2.facility_risk_snapshot
+  2. LOAD committed_amount, bank_share_pct from l2.facility_exposure_snapshot
+  3. COMPUTE EL = (PD/100) × (LGD/100) × Committed × (Bank Share/100)
+Ingredients: pd_pct (L2), lgd_pct (L2), committed_amount (L2), bank_share_pct (L2)
 </v>
       </c>
       <c r="E25" t="str">
@@ -2625,10 +2669,14 @@
         <v>Y</v>
       </c>
       <c r="I25" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="J25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(stressed_expected_loss) per facility from stress_test_result. Weighted by bank share percentage.
+        <v xml:space="preserve">For each facility:
+  1. LOAD pd_pct, lgd_pct from l2.facility_risk_snapshot
+  2. LOAD committed_amount, bank_share_pct from l2.facility_exposure_snapshot
+  3. COMPUTE EL = (PD/100) × (LGD/100) × Committed × (Bank Share/100)
+Ingredients: pd_pct (L2), lgd_pct (L2), committed_amount (L2), bank_share_pct (L2)
 </v>
       </c>
       <c r="K25" t="str">
@@ -2641,7 +2689,11 @@
         <v>Agg</v>
       </c>
       <c r="N25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD facility-level EL for all facilities of this counterparty
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(facility EL × FX rate) = Counterparty EL (USD)
+Direct-sum rollup with FX conversion.
 </v>
       </c>
       <c r="O25" t="str">
@@ -2654,7 +2706,11 @@
         <v>Agg</v>
       </c>
       <c r="R25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per L3 desk segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOOKUP managed_segment_id from enterprise_business_taxonomy
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(facility EL × FX rate) per desk
+Direct-sum rollup with FX conversion.
 </v>
       </c>
       <c r="S25" t="str">
@@ -2667,7 +2723,11 @@
         <v>Agg</v>
       </c>
       <c r="V25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(facility EL × FX rate) per portfolio
+Direct-sum rollup with FX conversion.
 </v>
       </c>
       <c r="W25" t="str">
@@ -2680,7 +2740,11 @@
         <v>Agg</v>
       </c>
       <c r="Z25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per L1 business segment segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(facility EL × FX rate) per business segment
+Direct-sum rollup with FX conversion.
 </v>
       </c>
       <c r="AA25" t="str">
@@ -4020,14 +4084,14 @@
         <v>EXP-031</v>
       </c>
       <c r="B40" t="str" xml:space="preserve">
-        <v xml:space="preserve">Total income generated by the borrower or attributed to the facility in millions USD. Used to assess scale and repayment capacity.
+        <v xml:space="preserve">Total facility-level revenue computed as Interest Income + Fee Income, adjusted for bank share percentage. Sourced from L2 atomic data in facility_profitability_snapshot (interest_income_amt, fee_income_amt) with bank share from facility_lender_allocation. Assesses scale of lending activity and income generation capacity.
 </v>
       </c>
       <c r="C40" t="str">
         <v>Revenue ($)</v>
       </c>
       <c r="D40" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(revenue_amt) per facility from facility_financial_snapshot. Weighted by bank share percentage.
+        <v xml:space="preserve">[Facility Revenue] = (interest_income_amt + fee_income_amt) × bank_share_pct / 100. USD-converted for consistent reporting.
 </v>
       </c>
       <c r="E40" t="str">
@@ -4046,7 +4110,7 @@
         <v>Agg</v>
       </c>
       <c r="J40" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(revenue_amt) per facility from facility_financial_snapshot. Weighted by bank share percentage.
+        <v xml:space="preserve">[Facility Revenue] = (interest_income_amt + fee_income_amt) × bank_share_pct / 100. USD-converted for consistent reporting.
 </v>
       </c>
       <c r="K40" t="str">
@@ -4059,7 +4123,7 @@
         <v>Agg</v>
       </c>
       <c r="N40" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level revenue_amt per counterparty.
+        <v xml:space="preserve">SUM of facility-level revenue (bank-share-adjusted, USD-converted) per counterparty.
 </v>
       </c>
       <c r="O40" t="str">
@@ -4072,7 +4136,7 @@
         <v>Agg</v>
       </c>
       <c r="R40" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level revenue_amt per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level revenue (bank-share-adjusted, USD-converted) per L3 desk segment.
 </v>
       </c>
       <c r="S40" t="str">
@@ -4085,7 +4149,7 @@
         <v>Agg</v>
       </c>
       <c r="V40" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level revenue_amt per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level revenue (bank-share-adjusted, USD-converted) per L2 portfolio segment via EBT hierarchy (one hop up).
 </v>
       </c>
       <c r="W40" t="str">
@@ -4098,7 +4162,7 @@
         <v>Agg</v>
       </c>
       <c r="Z40" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level revenue_amt per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level revenue (bank-share-adjusted, USD-converted) per L1 business segment via EBT hierarchy (two hops up).
 </v>
       </c>
       <c r="AA40" t="str">
@@ -5796,14 +5860,15 @@
         <v>PRC-003</v>
       </c>
       <c r="B59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of exposures within portfolio with approved pricing or policy exceptions. Derived governance KPI measuring policy discipline and risk culture strength.
+        <v xml:space="preserve">Percentage of facilities with approved pricing or policy exceptions. Computed as COUNT(exception facilities) / COUNT(total facilities) × 100. Sourced from L2 facility_pricing_snapshot — the atomic pricing record — using the is_pricing_exception_flag. At aggregate levels, uses count-ratio rollup: re-counts exceptions and totals across all constituent facilities, never averages pre-computed rates. Key governance KPI measuring policy discipline, risk culture strength, and pricing override frequency.
 </v>
       </c>
       <c r="C59" t="str">
         <v>Exception Rate (%)</v>
       </c>
       <c r="D59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if pricing exception, 0 otherwise.
+        <v xml:space="preserve">Binary flag: 1.0 if pricing exception approved, 0.0 otherwise.
+Ingredients: is_pricing_exception_flag (L2 facility_pricing_snapshot)
 </v>
       </c>
       <c r="E59" t="str">
@@ -5822,7 +5887,8 @@
         <v>Calc</v>
       </c>
       <c r="J59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if pricing exception, 0 otherwise.
+        <v xml:space="preserve">Binary flag: 1.0 if pricing exception approved, 0.0 otherwise.
+Ingredients: is_pricing_exception_flag (L2 facility_pricing_snapshot)
 </v>
       </c>
       <c r="K59" t="str">
@@ -5835,7 +5901,10 @@
         <v>Calc</v>
       </c>
       <c r="N59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with pricing exception per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD is_pricing_exception_flag for all facilities of this counterparty
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup: re-counts from facility-level flags.
 </v>
       </c>
       <c r="O59" t="str">
@@ -5848,7 +5917,10 @@
         <v>Calc</v>
       </c>
       <c r="R59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with pricing exception per L3 desk.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOOKUP managed_segment_id from enterprise_business_taxonomy
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup per desk.
 </v>
       </c>
       <c r="S59" t="str">
@@ -5861,7 +5933,10 @@
         <v>Calc</v>
       </c>
       <c r="V59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with pricing exception per L2 portfolio.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup per portfolio.
 </v>
       </c>
       <c r="W59" t="str">
@@ -5874,7 +5949,10 @@
         <v>Calc</v>
       </c>
       <c r="Z59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with pricing exception per L1 business segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup per business segment.
 </v>
       </c>
       <c r="AA59" t="str">
@@ -6830,14 +6908,14 @@
         <v>REF-004</v>
       </c>
       <c r="B70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Unique system identifier assigned to the borrower or obligor. Used for exposure aggregation and risk consolidation.
+        <v xml:space="preserve">Unique system identifier assigned to the borrower or obligor. Used for exposure aggregation and risk consolidation across the GSIB. At facility level, returns the counterparty_id linked to each facility. At upper levels, returns COUNT(DISTINCT counterparty_id) — the number of unique obligors in each organizational segment.
 </v>
       </c>
       <c r="C70" t="str">
         <v>Counterparty ID</v>
       </c>
       <c r="D70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">Direct lookup of counterparty_id from facility_master for each active facility. Uses current records only (SCD2 filtered).
 </v>
       </c>
       <c r="E70" t="str">
@@ -6856,7 +6934,7 @@
         <v>Raw</v>
       </c>
       <c r="J70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">Direct lookup of counterparty_id from facility_master for each active facility. Uses current records only (SCD2 filtered).
 </v>
       </c>
       <c r="K70" t="str">
@@ -6869,7 +6947,7 @@
         <v>Raw</v>
       </c>
       <c r="N70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">Identity — returns counterparty_id for each current counterparty.
 </v>
       </c>
       <c r="O70" t="str">
@@ -6882,7 +6960,7 @@
         <v>Agg</v>
       </c>
       <c r="R70" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L3 desk segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L3 desk segment — number of unique obligors in each desk.
 </v>
       </c>
       <c r="S70" t="str">
@@ -6895,7 +6973,7 @@
         <v>Agg</v>
       </c>
       <c r="V70" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L2 portfolio segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L2 portfolio segment — number of unique obligors in each portfolio.
 </v>
       </c>
       <c r="W70" t="str">
@@ -6908,7 +6986,7 @@
         <v>Agg</v>
       </c>
       <c r="Z70" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L1 business segment segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L1 business segment — number of unique obligors in each business segment.
 </v>
       </c>
       <c r="AA70" t="str">
@@ -6923,14 +7001,14 @@
         <v>REF-005</v>
       </c>
       <c r="B71" t="str" xml:space="preserve">
-        <v xml:space="preserve">Descriptive name of the counterparty as documented in the credit agreement. Used for reporting clarity and operational reference.
+        <v xml:space="preserve">Legal name of the counterparty as documented in the credit agreement. At facility level, returns the counterparty_id (numeric proxy for the name since metric values are numeric). At counterparty level, identity lookup. At upper levels, COUNT(DISTINCT counterparty_id) — number of unique named obligors per organizational segment. Used for reporting clarity and operational reference across all regulatory submissions.
 </v>
       </c>
       <c r="C71" t="str">
         <v>Counterparty Name</v>
       </c>
       <c r="D71" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read legal_name from counterparty for each facility's counterparty.
+        <v xml:space="preserve">Lookup counterparty_id from facility_master for each active facility. The numeric counterparty_id serves as proxy for the legal name (string values resolved via counterparty dimension join at display time). Uses current records only.
 </v>
       </c>
       <c r="E71" t="str">
@@ -6949,7 +7027,7 @@
         <v>Raw</v>
       </c>
       <c r="J71" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read legal_name from counterparty for each facility's counterparty.
+        <v xml:space="preserve">Lookup counterparty_id from facility_master for each active facility. The numeric counterparty_id serves as proxy for the legal name (string values resolved via counterparty dimension join at display time). Uses current records only.
 </v>
       </c>
       <c r="K71" t="str">
@@ -6959,10 +7037,10 @@
         <v>Y</v>
       </c>
       <c r="M71" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="N71" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with counterparty name per counterparty.
+        <v xml:space="preserve">Identity — returns counterparty_id for each current counterparty. Legal name resolved via counterparty dimension join at display time.
 </v>
       </c>
       <c r="O71" t="str">
@@ -6975,7 +7053,7 @@
         <v>Agg</v>
       </c>
       <c r="R71" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with counterparty name per L3 desk segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L3 desk segment — number of unique named obligors in each desk.
 </v>
       </c>
       <c r="S71" t="str">
@@ -6988,7 +7066,7 @@
         <v>Agg</v>
       </c>
       <c r="V71" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with counterparty name per L2 portfolio segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L2 portfolio segment — number of unique named obligors in each portfolio.
 </v>
       </c>
       <c r="W71" t="str">
@@ -7001,7 +7079,7 @@
         <v>Agg</v>
       </c>
       <c r="Z71" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with counterparty name per L1 business segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L1 business segment — number of unique named obligors in each business segment.
 </v>
       </c>
       <c r="AA71" t="str">
@@ -7016,14 +7094,14 @@
         <v>REF-006</v>
       </c>
       <c r="B72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Country of risk or booking location. Supports geographic concentration and sovereign risk analysis.
+        <v xml:space="preserve">Country of risk derived from the counterparty's domicile. At facility level, returns a numeric country identifier (via counterparty → country_dim join path). At counterparty level, identity lookup. At desk/portfolio/segment levels, COUNT(DISTINCT country_code) — geographic diversification indicator showing the number of unique countries represented. Supports FFIEC 009 Country Exposure Report and Basel III geographic concentration analysis.
 </v>
       </c>
       <c r="C72" t="str">
         <v>Country</v>
       </c>
       <c r="D72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of country_name from country_dim.
+        <v xml:space="preserve">Lookup country for each facility via counterparty → country_dim join path. Returns counterparty_id as numeric proxy (country_name resolved at display time via dimension join). Uses current records only.
 </v>
       </c>
       <c r="E72" t="str">
@@ -7042,7 +7120,7 @@
         <v>Raw</v>
       </c>
       <c r="J72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of country_name from country_dim.
+        <v xml:space="preserve">Lookup country for each facility via counterparty → country_dim join path. Returns counterparty_id as numeric proxy (country_name resolved at display time via dimension join). Uses current records only.
 </v>
       </c>
       <c r="K72" t="str">
@@ -7055,7 +7133,7 @@
         <v>Raw</v>
       </c>
       <c r="N72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read country_name per counterparty.
+        <v xml:space="preserve">Lookup country for each counterparty via country_code → country_dim join. Returns counterparty_id as numeric proxy.
 </v>
       </c>
       <c r="O72" t="str">
@@ -7068,7 +7146,7 @@
         <v>Agg</v>
       </c>
       <c r="R72" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level country_name per L3 desk segment.
+        <v xml:space="preserve">COUNT(DISTINCT country_code) per L3 desk segment — number of unique countries represented, a geographic diversification indicator.
 </v>
       </c>
       <c r="S72" t="str">
@@ -7081,7 +7159,7 @@
         <v>Agg</v>
       </c>
       <c r="V72" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level country_name per L2 portfolio segment.
+        <v xml:space="preserve">COUNT(DISTINCT country_code) per L2 portfolio segment — number of unique countries represented in each portfolio.
 </v>
       </c>
       <c r="W72" t="str">
@@ -7094,7 +7172,7 @@
         <v>Agg</v>
       </c>
       <c r="Z72" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level country_name per L1 business segment segment.
+        <v xml:space="preserve">COUNT(DISTINCT country_code) per L1 business segment — geographic diversification at the highest organizational level.
 </v>
       </c>
       <c r="AA72" t="str">
@@ -7109,14 +7187,14 @@
         <v>REF-007</v>
       </c>
       <c r="B73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Unique identifier linking facility to governing credit agreement documentation.
+        <v xml:space="preserve">Unique identifier linking each facility to its governing credit agreement documentation. Used for contract tracking, facility-to-agreement linkage, and regulatory reporting. At counterparty level, returns count of distinct credit agreements per borrower.
 </v>
       </c>
       <c r="C73" t="str">
         <v>Credit Agreement ID</v>
       </c>
       <c r="D73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of credit_agreement_id from credit_agreement_master.
+        <v xml:space="preserve">Direct lookup of credit_agreement_id for each active facility via facility_master joined to credit_agreement_master.
 </v>
       </c>
       <c r="E73" t="str">
@@ -7135,7 +7213,7 @@
         <v>Raw</v>
       </c>
       <c r="J73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of credit_agreement_id from credit_agreement_master.
+        <v xml:space="preserve">Direct lookup of credit_agreement_id for each active facility via facility_master joined to credit_agreement_master.
 </v>
       </c>
       <c r="K73" t="str">
@@ -7145,10 +7223,10 @@
         <v>Y</v>
       </c>
       <c r="M73" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="N73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read credit_agreement_id per counterparty.
+        <v xml:space="preserve">Count of distinct credit agreements per counterparty. Provides visibility into borrower complexity and multi-agreement relationships.
 </v>
       </c>
       <c r="O73" t="str">
@@ -7161,7 +7239,7 @@
         <v>Agg</v>
       </c>
       <c r="R73" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level credit_agreement_id per L3 desk segment.
+        <v xml:space="preserve">Count of distinct credit agreements per L3 desk segment via enterprise_business_taxonomy.
 </v>
       </c>
       <c r="S73" t="str">
@@ -7174,7 +7252,7 @@
         <v>Agg</v>
       </c>
       <c r="V73" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level credit_agreement_id per L2 portfolio segment.
+        <v xml:space="preserve">Count of distinct credit agreements per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
 </v>
       </c>
       <c r="W73" t="str">
@@ -7187,7 +7265,7 @@
         <v>Agg</v>
       </c>
       <c r="Z73" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level credit_agreement_id per L1 business segment segment.
+        <v xml:space="preserve">Count of distinct credit agreements per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
 </v>
       </c>
       <c r="AA73" t="str">
@@ -7295,7 +7373,7 @@
         <v>REF-009</v>
       </c>
       <c r="B75" t="str" xml:space="preserve">
-        <v xml:space="preserve">Date on which loan or contract became legally effective.
+        <v xml:space="preserve">Date on which loan or contract became legally effective. Sourced directly from facility_master. At aggregate levels, returns the earliest origination date (MIN) across constituent facilities — indicating the oldest vintage in the book. Key contract lifecycle tracking attribute for vintage analysis and portfolio seasoning assessment.
 </v>
       </c>
       <c r="C75" t="str">
@@ -7303,6 +7381,7 @@
       </c>
       <c r="D75" t="str" xml:space="preserve">
         <v xml:space="preserve">Direct lookup of origination_date from facility_master.
+Ingredients: origination_date (L2 facility_master — raw field)
 </v>
       </c>
       <c r="E75" t="str">
@@ -7322,6 +7401,7 @@
       </c>
       <c r="J75" t="str" xml:space="preserve">
         <v xml:space="preserve">Direct lookup of origination_date from facility_master.
+Ingredients: origination_date (L2 facility_master — raw field)
 </v>
       </c>
       <c r="K75" t="str">
@@ -7334,7 +7414,10 @@
         <v>Agg</v>
       </c>
       <c r="N75" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level origination_date) per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD origination_date from l2.facility_master for all active facilities
+  2. COMPUTE MIN(origination_date) — earliest contract vintage
+Indicates the oldest banking relationship tenure for this counterparty.
 </v>
       </c>
       <c r="O75" t="str">
@@ -7347,7 +7430,10 @@
         <v>Agg</v>
       </c>
       <c r="R75" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level origination_date per L3 desk segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOAD origination_date from l2.facility_master
+  2. JOIN l1.enterprise_business_taxonomy on lob_segment_id
+  3. COMPUTE MIN(origination_date) — earliest vintage in desk book
 </v>
       </c>
       <c r="S75" t="str">
@@ -7360,7 +7446,9 @@
         <v>Agg</v>
       </c>
       <c r="V75" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level origination_date per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. COMPUTE MIN(origination_date) — earliest vintage in portfolio
 </v>
       </c>
       <c r="W75" t="str">
@@ -7373,7 +7461,9 @@
         <v>Agg</v>
       </c>
       <c r="Z75" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level origination_date per L1 business segment segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. COMPUTE MIN(origination_date) — earliest vintage in business segment
 </v>
       </c>
       <c r="AA75" t="str">
@@ -8783,14 +8873,14 @@
         <v>REF-025</v>
       </c>
       <c r="B91" t="str" xml:space="preserve">
-        <v xml:space="preserve">Product classification assigned to the contract offering. Supports product- level segmentation and performance analysis.
+        <v xml:space="preserve">Total drawn exposure (bank-share-adjusted) segmented by product classification from the Enterprise Product Taxonomy. Supports portfolio composition analysis and product-level concentration monitoring. At facility level, returns the facility's exposure in local currency. At aggregate levels, converts to USD via FX rate.
 </v>
       </c>
       <c r="C91" t="str">
         <v>Product</v>
       </c>
       <c r="D91" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(product_id) per facility from facility_exposure_snapshot.
+        <v xml:space="preserve">SUM(drawn_amount × bank_share_pct / 100) per facility. Local currency. Product classification available via enterprise_product_taxonomy join.
 </v>
       </c>
       <c r="E91" t="str">
@@ -8809,7 +8899,7 @@
         <v>Agg</v>
       </c>
       <c r="J91" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(product_id) per facility from facility_exposure_snapshot.
+        <v xml:space="preserve">SUM(drawn_amount × bank_share_pct / 100) per facility. Local currency. Product classification available via enterprise_product_taxonomy join.
 </v>
       </c>
       <c r="K91" t="str">
@@ -8822,7 +8912,7 @@
         <v>Agg</v>
       </c>
       <c r="N91" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level product_id per counterparty.
+        <v xml:space="preserve">SUM of facility-level drawn exposure (bank-share-adjusted, USD-converted) per counterparty. FX conversion applied.
 </v>
       </c>
       <c r="O91" t="str">
@@ -8835,7 +8925,7 @@
         <v>Agg</v>
       </c>
       <c r="R91" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level product_id per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level drawn exposure (bank-share-adjusted, USD-converted) per L3 desk segment via EBT hierarchy.
 </v>
       </c>
       <c r="S91" t="str">
@@ -8848,7 +8938,7 @@
         <v>Agg</v>
       </c>
       <c r="V91" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level product_id per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level drawn exposure (bank-share-adjusted, USD-converted) per L2 portfolio segment via EBT hierarchy (one hop up).
 </v>
       </c>
       <c r="W91" t="str">
@@ -8861,7 +8951,7 @@
         <v>Agg</v>
       </c>
       <c r="Z91" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level product_id per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level drawn exposure (bank-share-adjusted, USD-converted) per L1 business segment via EBT hierarchy (two hops up).
 </v>
       </c>
       <c r="AA91" t="str">
@@ -8876,14 +8966,14 @@
         <v>REF-026</v>
       </c>
       <c r="B92" t="str" xml:space="preserve">
-        <v xml:space="preserve">Geographic region classification tied to location of deal origination, supporting portfolio segmentation and concentration monitoring.
+        <v xml:space="preserve">Total drawn exposure (bank-share-adjusted) segmented by geographic region derived from counterparty country of domicile. Join chain: counterparty.country_code → country_dim.region_code → region_dim. Supports regional concentration monitoring and geographic risk diversification analysis per GSIB standards.
 </v>
       </c>
       <c r="C92" t="str">
         <v>Region</v>
       </c>
       <c r="D92" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of region_code from counterparty.
+        <v xml:space="preserve">SUM(drawn_amount × bank_share_pct / 100) per facility. Local currency. Region lookup: counterparty → country_dim → region_dim for context.
 </v>
       </c>
       <c r="E92" t="str">
@@ -8899,10 +8989,10 @@
         <v>Y</v>
       </c>
       <c r="I92" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="J92" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of region_code from counterparty.
+        <v xml:space="preserve">SUM(drawn_amount × bank_share_pct / 100) per facility. Local currency. Region lookup: counterparty → country_dim → region_dim for context.
 </v>
       </c>
       <c r="K92" t="str">
@@ -8912,10 +9002,10 @@
         <v>Y</v>
       </c>
       <c r="M92" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="N92" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of region_code from counterparty.
+        <v xml:space="preserve">SUM of facility-level drawn exposure (bank-share-adjusted, USD-converted) per counterparty. Region derived from counterparty.country_code → country_dim.region_code → region_dim.region_name.
 </v>
       </c>
       <c r="O92" t="str">
@@ -8928,7 +9018,7 @@
         <v>Agg</v>
       </c>
       <c r="R92" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level region_code per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level drawn exposure (bank-share-adjusted, USD-converted) per L3 desk segment. Region context via counterparty → country_dim → region_dim.
 </v>
       </c>
       <c r="S92" t="str">
@@ -8941,7 +9031,7 @@
         <v>Agg</v>
       </c>
       <c r="V92" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level region_code per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level drawn exposure (bank-share-adjusted, USD-converted) per L2 portfolio segment via EBT hierarchy (one hop up).
 </v>
       </c>
       <c r="W92" t="str">
@@ -8954,7 +9044,7 @@
         <v>Agg</v>
       </c>
       <c r="Z92" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level region_code per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level drawn exposure (bank-share-adjusted, USD-converted) per L1 business segment via EBT hierarchy (two hops up).
 </v>
       </c>
       <c r="AA92" t="str">
@@ -9620,14 +9710,14 @@
         <v>RSK-001</v>
       </c>
       <c r="B100" t="str" xml:space="preserve">
-        <v xml:space="preserve">Most recent internal credit rating assigned at reporting date. Used for segmentation and exposure-weighted risk aggregation.
+        <v xml:space="preserve">Risk rating tier derived from counterparty probability of default (PD). Each counterparty's pd_annual is matched against the risk_rating_tier_dim reference table (pd_min_pct / pd_max_pct boundaries) to assign a tier classification. At facility level, the tier is inherited from the owning counterparty. At aggregate levels, MAX (worst-case) tier ordinal is reported.
 </v>
       </c>
       <c r="C100" t="str">
         <v>Risk Rating Tier</v>
       </c>
       <c r="D100" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility.
+        <v xml:space="preserve">For each facility, inherit the risk rating tier from the owning counterparty. Join facility_master to counterparty, then range-match counterparty pd_annual against risk_rating_tier_dim to derive the tier ordinal (display_order).
 </v>
       </c>
       <c r="E100" t="str">
@@ -9643,10 +9733,10 @@
         <v>Y</v>
       </c>
       <c r="I100" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="J100" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility.
+        <v xml:space="preserve">For each facility, inherit the risk rating tier from the owning counterparty. Join facility_master to counterparty, then range-match counterparty pd_annual against risk_rating_tier_dim to derive the tier ordinal (display_order).
 </v>
       </c>
       <c r="K100" t="str">
@@ -9656,10 +9746,10 @@
         <v>Y</v>
       </c>
       <c r="M100" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N100" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating per counterparty.
+        <v xml:space="preserve">For each counterparty, look up pd_annual and range-match against risk_rating_tier_dim where pd_annual &gt;= pd_min_pct AND pd_annual &lt; pd_max_pct. Returns the tier ordinal (display_order). Counterparties with NULL PD receive tier 0 (unrated).
 </v>
       </c>
       <c r="O100" t="str">
@@ -9672,7 +9762,7 @@
         <v>Agg</v>
       </c>
       <c r="R100" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating per L3 desk segment.
+        <v xml:space="preserve">Worst-case (MAX) risk rating tier ordinal across all counterparties in the L3 desk segment. Higher ordinal = riskier tier. Full tier distribution available via counterparty-level drill-down.
 </v>
       </c>
       <c r="S100" t="str">
@@ -9685,7 +9775,7 @@
         <v>Agg</v>
       </c>
       <c r="V100" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating per L2 portfolio segment.
+        <v xml:space="preserve">Worst-case (MAX) risk rating tier ordinal per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
 </v>
       </c>
       <c r="W100" t="str">
@@ -9698,7 +9788,7 @@
         <v>Agg</v>
       </c>
       <c r="Z100" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating per L1 business segment.
+        <v xml:space="preserve">Worst-case (MAX) risk rating tier ordinal per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
 </v>
       </c>
       <c r="AA100" t="str">
@@ -9899,14 +9989,14 @@
         <v>RSK-004</v>
       </c>
       <c r="B103" t="str" xml:space="preserve">
-        <v xml:space="preserve">Derived directional indicator reflecting movement in external credit agency rating and changes month over month, which depicts the month-over-month change reflecting an upgrade (e.g. A to AA), downgrade (e.g., B+ to B-) or stable (remaing constant month over month), as compared to prior month reporting periods. Note when this is displayed at an aggregated Line of Business or portfolio level, it is determined by the month-over-month change of the average rating at this level. Supports benchmarking against market perception and helps validate internal risk assessment trends.
+        <v xml:space="preserve">Directional indicator of external credit rating migration, derived from the sign of month-over-month rating notch changes in counterparty_rating_observation. Encoded as: -1 = Downgrade, 0 = Stable, +1 = Upgrade. At aggregate (desk/portfolio/segment) levels, determined by the sign of the average rating change steps across all counterparties in the LOB — consistent with the spec requirement that LOB-level status reflects the direction of the LOB-average rating movement, not a vote count of individual counterparty directions. No facility-level calculation (ratings are per counterparty).
 </v>
       </c>
       <c r="C103" t="str">
         <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable)</v>
       </c>
       <c r="D103" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility as-of reporting date.
+        <v xml:space="preserve">Not directly applicable — ratings are per counterparty, not facility. Passthrough: assigns counterparty's external rating status to each of its facilities via facility_master.counterparty_id join.
 </v>
       </c>
       <c r="E103" t="str">
@@ -9925,7 +10015,7 @@
         <v>Raw</v>
       </c>
       <c r="J103" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility as-of reporting date.
+        <v xml:space="preserve">Not directly applicable — ratings are per counterparty, not facility. Passthrough: assigns counterparty's external rating status to each of its facilities via facility_master.counterparty_id join.
 </v>
       </c>
       <c r="K103" t="str">
@@ -9935,10 +10025,10 @@
         <v>Y</v>
       </c>
       <c r="M103" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N103" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_status per counterparty.
+        <v xml:space="preserve">AVG of external rating change steps per counterparty, then SIGN: &lt; 0 → Downgrade (-1), = 0 → Stable (0), &gt; 0 → Upgrade (+1). Averages across multiple agency observations (Moody's, S&amp;P, Fitch).
 </v>
       </c>
       <c r="O103" t="str">
@@ -9948,10 +10038,10 @@
         <v>Y</v>
       </c>
       <c r="Q103" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R103" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_status per L3 desk segment.
+        <v xml:space="preserve">AVG of counterparty-level external rating change steps across all unique counterparties in the L3 desk segment, then SIGN to classify the desk-level migration direction.
 </v>
       </c>
       <c r="S103" t="str">
@@ -9961,10 +10051,10 @@
         <v>Y</v>
       </c>
       <c r="U103" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V103" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_status per L2 portfolio segment.
+        <v xml:space="preserve">AVG of counterparty-level external rating change steps across all unique counterparties in the L2 portfolio segment (one hop up in EBT), then SIGN to classify portfolio migration direction.
 </v>
       </c>
       <c r="W103" t="str">
@@ -9974,10 +10064,10 @@
         <v>Y</v>
       </c>
       <c r="Y103" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z103" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_status per L1 business segment segment.
+        <v xml:space="preserve">AVG of counterparty-level external rating change steps across all unique counterparties in the L1 business segment (two hops up in EBT), then SIGN to classify segment migration direction.
 </v>
       </c>
       <c r="AA103" t="str">
@@ -9992,14 +10082,14 @@
         <v>RSK-005</v>
       </c>
       <c r="B104" t="str" xml:space="preserve">
-        <v xml:space="preserve">Numerical representation of external risk rating migration (month over month changes) expressed in notch movement (positive or negative). Positive step changes are identified when there is an upgrade, from A to AA and the step change is +1, where as the negative step change is identified when there is a downgrade from B+ to B- and the step change is -1. Note when this is displayed at an aggregated Line of Business or portfolio level, it is determined by the month-over-month change of the average rating at this level. Quantifies magnitude of credit change and enables portfolio-level migration analysis, stress testing sensitivity, and risk trend measurement.
+        <v xml:space="preserve">Mean external rating notch change (month-over-month) expressed as a numeric step count. Positive values indicate upgrades (e.g., A→AA = +1), negative values indicate downgrades (e.g., B+→B- = -2). Sourced from counterparty_rating_observation.risk_rating_change_steps, filtered to external agency observations only (is_internal_flag = 'N'). At counterparty level: AVG across agency observations for that counterparty. At aggregate levels: AVG across unique counterparties in the LOB segment, consistent with spec requirement that LOB-level steps reflect the average rating at that level, not the sum.
 </v>
       </c>
       <c r="C104" t="str">
         <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps)</v>
       </c>
       <c r="D104" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_change_steps from counterparty_rating_observation for each facility as-of reporting date.
+        <v xml:space="preserve">Not directly applicable — ratings are per counterparty, not facility. Passthrough: assigns counterparty's AVG external rating change steps to each of its facilities via facility_master.counterparty_id join.
 </v>
       </c>
       <c r="E104" t="str">
@@ -10018,7 +10108,7 @@
         <v>Raw</v>
       </c>
       <c r="J104" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_change_steps from counterparty_rating_observation for each facility as-of reporting date.
+        <v xml:space="preserve">Not directly applicable — ratings are per counterparty, not facility. Passthrough: assigns counterparty's AVG external rating change steps to each of its facilities via facility_master.counterparty_id join.
 </v>
       </c>
       <c r="K104" t="str">
@@ -10028,10 +10118,10 @@
         <v>Y</v>
       </c>
       <c r="M104" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N104" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per counterparty.
+        <v xml:space="preserve">AVG of external rating change steps per counterparty, across all agency observations (Moody's, S&amp;P, Fitch) for the reporting date.
 </v>
       </c>
       <c r="O104" t="str">
@@ -10041,10 +10131,10 @@
         <v>Y</v>
       </c>
       <c r="Q104" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R104" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per L3 desk segment.
+        <v xml:space="preserve">AVG of counterparty-level external rating change steps across all unique counterparties in the L3 desk segment. Each counterparty counted once per LOB (deduplicated via DISTINCT on counterparty_id + lob_segment_id from facility_master).
 </v>
       </c>
       <c r="S104" t="str">
@@ -10054,10 +10144,10 @@
         <v>Y</v>
       </c>
       <c r="U104" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V104" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per L2 portfolio segment.
+        <v xml:space="preserve">AVG of counterparty-level external rating change steps across all unique counterparties in the L2 portfolio segment (one hop up in EBT).
 </v>
       </c>
       <c r="W104" t="str">
@@ -10067,10 +10157,10 @@
         <v>Y</v>
       </c>
       <c r="Y104" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z104" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per L1 business segment segment.
+        <v xml:space="preserve">AVG of counterparty-level external rating change steps across all unique counterparties in the L1 business segment (two hops up in EBT).
 </v>
       </c>
       <c r="AA104" t="str">

--- a/data/metrics_dimensions_filled.xlsx
+++ b/data/metrics_dimensions_filled.xlsx
@@ -1539,14 +1539,14 @@
         <v>EXP-005</v>
       </c>
       <c r="B14" t="str" xml:space="preserve">
-        <v xml:space="preserve">The portion of total funding-related expense attributed to a specific exposure or portfolio. At facility level, calculated as SUM across all positions of (funded_amount * interest_rate), adjusted for bank share. At counterparty level, further adjusted by counterparty participation_pct. At desk/portfolio/segment levels, aggregated as SUM.
+        <v xml:space="preserve">The portion of total funding-related expense attributed to a specific exposure or portfolio. At facility level, calculated as SUM across all positions of (funded_amount * interest_rate), converted to USD via FX rate and adjusted for bank share. At counterparty level, further adjusted by counterparty participation_pct. At desk/portfolio/segment levels, aggregated as SUM via EBT hierarchy.
 </v>
       </c>
       <c r="C14" t="str">
         <v>Cost of Funds ($)</v>
       </c>
       <c r="D14" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each position under the facility: funded_amount * interest_rate = Position Cost of Funds. Adjusted by bank_share: SUM(funded_amount * interest_rate) * bank_share_pct / 100. Joins position_detail → position (for facility_id) → facility_master.
+        <v xml:space="preserve">For each position under the facility, compute funded_amount x interest_rate, convert to USD using the FX spot rate (defaults to 1.0 for USD positions). Sum across all positions, then multiply by the bank's share percentage. Result = annual cost of funds for this facility in USD.
 </v>
       </c>
       <c r="E14" t="str">
@@ -1565,7 +1565,7 @@
         <v>Calc</v>
       </c>
       <c r="J14" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each position under the facility: funded_amount * interest_rate = Position Cost of Funds. Adjusted by bank_share: SUM(funded_amount * interest_rate) * bank_share_pct / 100. Joins position_detail → position (for facility_id) → facility_master.
+        <v xml:space="preserve">For each position under the facility, compute funded_amount x interest_rate, convert to USD using the FX spot rate (defaults to 1.0 for USD positions). Sum across all positions, then multiply by the bank's share percentage. Result = annual cost of funds for this facility in USD.
 </v>
       </c>
       <c r="K14" t="str">
@@ -1578,7 +1578,7 @@
         <v>Agg</v>
       </c>
       <c r="N14" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each counterparty: SUM of facility-level cost of funds weighted by counterparty participation_pct from facility_counterparty_participation.
+        <v xml:space="preserve">Sum each facility's cost of funds (USD, bank-share-adjusted), then weight by the counterparty's participation percentage. Aggregates across all facilities where the counterparty has a current participation record.
 </v>
       </c>
       <c r="O14" t="str">
@@ -1591,7 +1591,7 @@
         <v>Agg</v>
       </c>
       <c r="R14" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level cost of funds (bank-share-adjusted) per L3 desk segment.
+        <v xml:space="preserve">Sum of facility-level cost of funds (USD, bank-share-adjusted) for all facilities assigned to each L3 desk segment in the organizational hierarchy.
 </v>
       </c>
       <c r="S14" t="str">
@@ -1604,7 +1604,7 @@
         <v>Agg</v>
       </c>
       <c r="V14" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level cost of funds (bank-share-adjusted) per L2 portfolio segment.
+        <v xml:space="preserve">Sum of facility-level cost of funds (USD, bank-share-adjusted) for all facilities within each L2 portfolio segment, traversing the EBT hierarchy from desk (L3) to portfolio (L2) via parent_segment_id.
 </v>
       </c>
       <c r="W14" t="str">
@@ -1617,7 +1617,7 @@
         <v>Agg</v>
       </c>
       <c r="Z14" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level cost of funds (bank-share-adjusted) per L1 business segment.
+        <v xml:space="preserve">Sum of facility-level cost of funds (USD, bank-share-adjusted) for all facilities within each L1 business segment, traversing the full EBT hierarchy from desk (L3) through portfolio (L2) to segment (L1).
 </v>
       </c>
       <c r="AA14" t="str">
@@ -1632,14 +1632,14 @@
         <v>EXP-006</v>
       </c>
       <c r="B15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure allocated to specific counterparty representing their share of the facility which the client can draw on. Concentration KPI measuring obligor dependency risk.
+        <v xml:space="preserve">Counterparty participation share in a facility — the percentage of a syndicated or participated facility allocated to a specific counterparty. At facility level, direct lookup from facility_counterparty_participation. At counterparty level, exposure-weighted average participation across all facilities. At desk/portfolio/segment, exposure-weighted average via EBT hierarchy. Key concentration KPI for Large Exposures Framework (LEX) and Single Counterparty Credit Limit (SCCL) compliance.
 </v>
       </c>
       <c r="C15" t="str">
         <v>Counterparty Share or Allocation (%)</v>
       </c>
       <c r="D15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of allocation_pct from facility_counterparty_participation.
+        <v xml:space="preserve">Direct lookup of participation_pct from facility_counterparty_participation for the primary counterparty on each facility. Uses current records only.
 </v>
       </c>
       <c r="E15" t="str">
@@ -1658,7 +1658,7 @@
         <v>Raw</v>
       </c>
       <c r="J15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of allocation_pct from facility_counterparty_participation.
+        <v xml:space="preserve">Direct lookup of participation_pct from facility_counterparty_participation for the primary counterparty on each facility. Uses current records only.
 </v>
       </c>
       <c r="K15" t="str">
@@ -1668,10 +1668,10 @@
         <v>Y</v>
       </c>
       <c r="M15" t="str">
-        <v>Raw</v>
+        <v>Avg</v>
       </c>
       <c r="N15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read allocation_pct per counterparty.
+        <v xml:space="preserve">Exposure-weighted average participation across all facilities for each counterparty. Weight = drawn_amount from facility_exposure_snapshot. Falls back to simple average if no exposure data available.
 </v>
       </c>
       <c r="O15" t="str">
@@ -1681,10 +1681,10 @@
         <v>Y</v>
       </c>
       <c r="Q15" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="R15" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level allocation_pct per L3 desk segment.
+        <v xml:space="preserve">Exposure-weighted average participation across all facilities per L3 desk segment via enterprise_business_taxonomy.
 </v>
       </c>
       <c r="S15" t="str">
@@ -1694,10 +1694,10 @@
         <v>Y</v>
       </c>
       <c r="U15" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="V15" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level allocation_pct per L2 portfolio segment.
+        <v xml:space="preserve">Exposure-weighted average participation across all facilities per L2 portfolio segment via enterprise_business_taxonomy hierarchy traversal.
 </v>
       </c>
       <c r="W15" t="str">
@@ -1707,10 +1707,10 @@
         <v>Y</v>
       </c>
       <c r="Y15" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="Z15" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level allocation_pct per L1 business segment segment.
+        <v xml:space="preserve">Exposure-weighted average participation across all facilities per L1 business segment via enterprise_business_taxonomy hierarchy traversal.
 </v>
       </c>
       <c r="AA15" t="str">
@@ -1725,14 +1725,14 @@
         <v>EXP-007</v>
       </c>
       <c r="B16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Flag identifying exposures requiring heightened monitoring due to elevated credit risk. Governance control used for enhanced monitoring, reserve consideration, and management reporting.
+        <v xml:space="preserve">Count of active Criticized risk flags across facilities. Early warning indicator of problem assets requiring heightened monitoring, reserve consideration, and management reporting. Sources from the risk_flag table filtering on flag_code = 'CRITICIZED' with uncleared status.
 </v>
       </c>
       <c r="C16" t="str">
         <v>Criticized Portfolios</v>
       </c>
       <c r="D16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if criticized rating (internal_risk_rating &gt;= 6), 0 otherwise.
+        <v xml:space="preserve">For each facility, count active risk flags where flag_code = 'CRITICIZED' and the flag has not been cleared (cleared_ts IS NULL).
 </v>
       </c>
       <c r="E16" t="str">
@@ -1748,10 +1748,10 @@
         <v>Y</v>
       </c>
       <c r="I16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="J16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if criticized rating (internal_risk_rating &gt;= 6), 0 otherwise.
+        <v xml:space="preserve">For each facility, count active risk flags where flag_code = 'CRITICIZED' and the flag has not been cleared (cleared_ts IS NULL).
 </v>
       </c>
       <c r="K16" t="str">
@@ -1761,10 +1761,10 @@
         <v>Y</v>
       </c>
       <c r="M16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="N16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per counterparty.
+        <v xml:space="preserve">For each counterparty, sum facility-level criticized flag counts across all facilities belonging to that counterparty.
 </v>
       </c>
       <c r="O16" t="str">
@@ -1774,10 +1774,10 @@
         <v>Y</v>
       </c>
       <c r="Q16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="R16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per L3 desk.
+        <v xml:space="preserve">Sum of criticized flag counts per L3 desk segment. Joins facility_master to enterprise_business_taxonomy via lob_segment_id.
 </v>
       </c>
       <c r="S16" t="str">
@@ -1787,10 +1787,10 @@
         <v>Y</v>
       </c>
       <c r="U16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="V16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per L2 portfolio.
+        <v xml:space="preserve">Sum of criticized flag counts per L2 portfolio segment. Traverses enterprise_business_taxonomy hierarchy from L3 to L2 via parent_segment_id.
 </v>
       </c>
       <c r="W16" t="str">
@@ -1800,10 +1800,10 @@
         <v>Y</v>
       </c>
       <c r="Y16" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="Z16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with criticized rating (internal_risk_rating &gt;= 6) per L1 business segment.
+        <v xml:space="preserve">Sum of criticized flag counts per L1 business segment. Full hierarchy traversal L3 → L2 → L1 via enterprise_business_taxonomy.
 </v>
       </c>
       <c r="AA16" t="str">
@@ -1818,14 +1818,14 @@
         <v>EXP-008</v>
       </c>
       <c r="B17" t="str" xml:space="preserve">
-        <v xml:space="preserve">Total exposure amount allocated across multiple legal entities. Supports intra-group concentration transparency.
+        <v xml:space="preserve">Total committed exposure amount (bank share) allocated across multiple legal entities for facilities flagged as cross-entity. Quantifies inter-entity concentration risk and supports intra-group transparency for GSIB reporting. Sources from counterparty_derived (L3) for the cross-entity flag and facility_exposure_snapshot (L2) for committed amounts.
 </v>
       </c>
       <c r="C17" t="str">
         <v>Cross Entity Exposure Amount</v>
       </c>
       <c r="D17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(total_cross_entity_exposure_usd) per facility from counterparty_exposure_summary. Weighted by bank share percentage.
+        <v xml:space="preserve">For each facility flagged as cross-entity, committed exposure amount weighted by the bank's participation share (bank_share_pct). Facilities without cross-entity flag are excluded.
 </v>
       </c>
       <c r="E17" t="str">
@@ -1844,7 +1844,7 @@
         <v>Agg</v>
       </c>
       <c r="J17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(total_cross_entity_exposure_usd) per facility from counterparty_exposure_summary. Weighted by bank share percentage.
+        <v xml:space="preserve">For each facility flagged as cross-entity, committed exposure amount weighted by the bank's participation share (bank_share_pct). Facilities without cross-entity flag are excluded.
 </v>
       </c>
       <c r="K17" t="str">
@@ -1857,7 +1857,7 @@
         <v>Agg</v>
       </c>
       <c r="N17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per counterparty.
+        <v xml:space="preserve">For each counterparty, sum of bank-share-weighted committed amounts across all facilities flagged as cross-entity.
 </v>
       </c>
       <c r="O17" t="str">
@@ -1870,7 +1870,7 @@
         <v>Agg</v>
       </c>
       <c r="R17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per L3 desk segment.
+        <v xml:space="preserve">Sum of cross-entity committed exposure per L3 desk segment via enterprise_business_taxonomy.
 </v>
       </c>
       <c r="S17" t="str">
@@ -1883,7 +1883,7 @@
         <v>Agg</v>
       </c>
       <c r="V17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per L2 portfolio segment.
+        <v xml:space="preserve">Sum of cross-entity committed exposure per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
 </v>
       </c>
       <c r="W17" t="str">
@@ -1896,7 +1896,7 @@
         <v>Agg</v>
       </c>
       <c r="Z17" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_cross_entity_exposure_usd per L1 business segment segment.
+        <v xml:space="preserve">Sum of cross-entity committed exposure per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
 </v>
       </c>
       <c r="AA17" t="str">
@@ -1911,14 +1911,14 @@
         <v>EXP-009</v>
       </c>
       <c r="B18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Number of days outstanding payments is past due as grouped into 3 "buckets", 0-30 Days, 31-60 Days, 61-90+ Days. Used for staging classification and early credit deterioration monitoring.
+        <v xml:space="preserve">Maximum days payment overdue per facility, calculated from raw payment records in the payment_ledger table. For each facility, identifies payments where applied amount &lt; amount due, computes days overdue as reporting date minus payment_due_date, takes the MAX, then classifies into buckets: 1 = 0-30 days, 2 = 31-60 days, 3 = 61-90+ days. At aggregate levels, reports the worst (MAX) bucket across constituents.
 </v>
       </c>
       <c r="C18" t="str">
         <v>Days Payment Overdue Bucket</v>
       </c>
       <c r="D18" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Facility_ID lookup the Payments records in the Payment Lockbox table, For each payment record where [Payment_Due_Date] &gt; Today() IF ([Pmt_Applied] &lt;[Pmt_Due])&gt;=1, THEN Today() - [Payment_due_date] ==[Days Overdue] SELECT MAX ([Days Overdue] then lookup in Payments Overdue bucket)
+        <v xml:space="preserve">For each facility, lookup payment records in payment_ledger where payment_due_date &lt; reporting date and payment_applied_amt &lt; payment_amount_due (underpaid). Calculate days overdue = reporting date minus payment_due_date. Take MAX days overdue, then classify into overdue bucket: 1 (0-30), 2 (31-60), 3 (61-90+).
 </v>
       </c>
       <c r="E18" t="str">
@@ -1937,7 +1937,7 @@
         <v>Calc</v>
       </c>
       <c r="J18" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Facility_ID lookup the Payments records in the Payment Lockbox table, For each payment record where [Payment_Due_Date] &gt; Today() IF ([Pmt_Applied] &lt;[Pmt_Due])&gt;=1, THEN Today() - [Payment_due_date] ==[Days Overdue] SELECT MAX ([Days Overdue] then lookup in Payments Overdue bucket)
+        <v xml:space="preserve">For each facility, lookup payment records in payment_ledger where payment_due_date &lt; reporting date and payment_applied_amt &lt; payment_amount_due (underpaid). Calculate days overdue = reporting date minus payment_due_date. Take MAX days overdue, then classify into overdue bucket: 1 (0-30), 2 (31-60), 3 (61-90+).
 </v>
       </c>
       <c r="K18" t="str">
@@ -1950,7 +1950,7 @@
         <v>Agg</v>
       </c>
       <c r="N18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per counterparty.
+        <v xml:space="preserve">Worst-case (MAX) overdue bucket across all facilities per counterparty. Identifies the most severely overdue facility for each borrower.
 </v>
       </c>
       <c r="O18" t="str">
@@ -1963,7 +1963,7 @@
         <v>Agg</v>
       </c>
       <c r="R18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per L3 desk segment.
+        <v xml:space="preserve">Worst-case (MAX) overdue bucket per L3 desk segment. Shows the most severe delinquency in each organizational unit.
 </v>
       </c>
       <c r="S18" t="str">
@@ -1976,7 +1976,7 @@
         <v>Agg</v>
       </c>
       <c r="V18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per L2 portfolio segment.
+        <v xml:space="preserve">Worst-case (MAX) overdue bucket per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
 </v>
       </c>
       <c r="W18" t="str">
@@ -1989,7 +1989,7 @@
         <v>Agg</v>
       </c>
       <c r="Z18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst (MAX) facility-level dpd_bucket_code per L1 business segment.
+        <v xml:space="preserve">Worst-case (MAX) overdue bucket per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
 </v>
       </c>
       <c r="AA18" t="str">
@@ -2509,14 +2509,25 @@
         <v>EXP-015</v>
       </c>
       <c r="B24" t="str" xml:space="preserve">
-        <v xml:space="preserve">Expected Loss divided by Exposure. Derived KPI measuring loss intensity relative to exposure size, enabling comparative risk ranking across facilities or counterparties.
+        <v xml:space="preserve">Expected Loss as a percentage of committed exposure. Computed from L2 atomic risk parameters: PD (probability of default) × LGD (loss given default). At aggregate levels, uses sum-ratio rollup: SUM(PD × LGD × Committed) / SUM(Committed) × 100 — the exposure-weighted average EL rate. This ensures mathematically consistent aggregation (never averages pre-computed rates). Key credit risk quantification metric for comparing loss intensity across facilities, counterparties, and business segments.
+Ingredient derivation:
+  - PD (pd_pct): L2 facility_risk_snapshot — probability of default (%)
+  - LGD (lgd_pct): L2 facility_risk_snapshot — loss given default (%)
+  - Committed Exposure (committed_amount): L2 facility_exposure_snapshot — raw
+  - EL Rate = PD × LGD (at facility level, committed cancels in ratio)
+  - Aggregate EL Rate = SUM(PD × LGD × Committed) / SUM(Committed) × 100
 </v>
       </c>
       <c r="C24" t="str">
         <v>Expected Loss Rate (%)</v>
       </c>
       <c r="D24" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of expected_loss_rate_pct per facility.
+        <v xml:space="preserve">For each facility:
+  1. LOAD pd_pct, lgd_pct from l2.facility_risk_snapshot
+  2. LOAD committed_amount from l2.facility_exposure_snapshot
+  3. COMPUTE EL Rate = SUM(PD/100 × LGD/100 × Committed) / SUM(Committed) × 100
+     At facility grain, committed cancels → EL Rate ≈ PD × LGD / 100
+Ingredients: pd_pct (L2), lgd_pct (L2), committed_amount (L2)
 </v>
       </c>
       <c r="E24" t="str">
@@ -2532,10 +2543,15 @@
         <v>Y</v>
       </c>
       <c r="I24" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="J24" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of expected_loss_rate_pct per facility.
+        <v xml:space="preserve">For each facility:
+  1. LOAD pd_pct, lgd_pct from l2.facility_risk_snapshot
+  2. LOAD committed_amount from l2.facility_exposure_snapshot
+  3. COMPUTE EL Rate = SUM(PD/100 × LGD/100 × Committed) / SUM(Committed) × 100
+     At facility grain, committed cancels → EL Rate ≈ PD × LGD / 100
+Ingredients: pd_pct (L2), lgd_pct (L2), committed_amount (L2)
 </v>
       </c>
       <c r="K24" t="str">
@@ -2545,10 +2561,15 @@
         <v>Y</v>
       </c>
       <c r="M24" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N24" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level expected_loss_rate_pct per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD pd_pct, lgd_pct for all facilities belonging to this counterparty
+  2. LOAD committed_amount for each facility
+  3. CONVERT to USD via l2.fx_rate spot rate
+  4. COMPUTE SUM(PD × LGD × Committed × FX) / SUM(Committed × FX) × 100
+Sum-ratio rollup with FX: exposure-weighted average EL rate in USD terms.
 </v>
       </c>
       <c r="O24" t="str">
@@ -2558,10 +2579,14 @@
         <v>Y</v>
       </c>
       <c r="Q24" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="R24" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level expected_loss_rate_pct per L3 desk segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOOKUP managed_segment_id from enterprise_business_taxonomy
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(PD × LGD × Committed × FX) / SUM(Committed × FX) × 100
+Sum-ratio rollup: exposure-weighted average EL rate per desk.
 </v>
       </c>
       <c r="S24" t="str">
@@ -2571,10 +2596,14 @@
         <v>Y</v>
       </c>
       <c r="U24" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V24" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level expected_loss_rate_pct per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(PD × LGD × Committed × FX) / SUM(Committed × FX) × 100
+Sum-ratio rollup: exposure-weighted average EL rate per portfolio.
 </v>
       </c>
       <c r="W24" t="str">
@@ -2584,10 +2613,14 @@
         <v>Y</v>
       </c>
       <c r="Y24" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z24" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level expected_loss_rate_pct per L1 business segment segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(PD × LGD × Committed × FX) / SUM(Committed × FX) × 100
+Sum-ratio rollup: exposure-weighted average EL rate per segment.
 </v>
       </c>
       <c r="AA24" t="str">
@@ -2602,14 +2635,25 @@
         <v>EXP-016</v>
       </c>
       <c r="B25" t="str" xml:space="preserve">
-        <v xml:space="preserve">PD × LGD × Exposure expressed in USD. Calculated forward-looking loss metric supporting provisioning, capital planning, and stress testing analytics.
+        <v xml:space="preserve">Expected Loss in dollar terms: PD × LGD × Committed Exposure × Bank Share. Computed from L2 atomic risk parameters and exposure data — NOT from stressed scenarios. This is the base (unstressed) expected credit loss, the foundation for provisioning, capital planning, and CECL/IFRS 9 reserve estimation.
+Ingredient derivation:
+  - PD (pd_pct): L2 facility_risk_snapshot — probability of default (%)
+  - LGD (lgd_pct): L2 facility_risk_snapshot — loss given default (%)
+  - Committed Exposure (committed_amount): L2 facility_exposure_snapshot — raw
+  - Bank Share (bank_share_pct): L2 facility_exposure_snapshot — participation %
+  - EL = (PD/100) × (LGD/100) × Committed × (Bank Share/100)
+Rollup uses direct-sum: SUM(facility EL) at each aggregate level. FX conversion applied at aggregate levels for multi-currency portfolios.
 </v>
       </c>
       <c r="C25" t="str">
         <v>Expected Loss ($)</v>
       </c>
       <c r="D25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(stressed_expected_loss) per facility from stress_test_result. Weighted by bank share percentage.
+        <v xml:space="preserve">For each facility:
+  1. LOAD pd_pct, lgd_pct from l2.facility_risk_snapshot
+  2. LOAD committed_amount, bank_share_pct from l2.facility_exposure_snapshot
+  3. COMPUTE EL = (PD/100) × (LGD/100) × Committed × (Bank Share/100)
+Ingredients: pd_pct (L2), lgd_pct (L2), committed_amount (L2), bank_share_pct (L2)
 </v>
       </c>
       <c r="E25" t="str">
@@ -2625,10 +2669,14 @@
         <v>Y</v>
       </c>
       <c r="I25" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="J25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(stressed_expected_loss) per facility from stress_test_result. Weighted by bank share percentage.
+        <v xml:space="preserve">For each facility:
+  1. LOAD pd_pct, lgd_pct from l2.facility_risk_snapshot
+  2. LOAD committed_amount, bank_share_pct from l2.facility_exposure_snapshot
+  3. COMPUTE EL = (PD/100) × (LGD/100) × Committed × (Bank Share/100)
+Ingredients: pd_pct (L2), lgd_pct (L2), committed_amount (L2), bank_share_pct (L2)
 </v>
       </c>
       <c r="K25" t="str">
@@ -2641,7 +2689,11 @@
         <v>Agg</v>
       </c>
       <c r="N25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD facility-level EL for all facilities of this counterparty
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(facility EL × FX rate) = Counterparty EL (USD)
+Direct-sum rollup with FX conversion.
 </v>
       </c>
       <c r="O25" t="str">
@@ -2654,7 +2706,11 @@
         <v>Agg</v>
       </c>
       <c r="R25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per L3 desk segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOOKUP managed_segment_id from enterprise_business_taxonomy
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(facility EL × FX rate) per desk
+Direct-sum rollup with FX conversion.
 </v>
       </c>
       <c r="S25" t="str">
@@ -2667,7 +2723,11 @@
         <v>Agg</v>
       </c>
       <c r="V25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(facility EL × FX rate) per portfolio
+Direct-sum rollup with FX conversion.
 </v>
       </c>
       <c r="W25" t="str">
@@ -2680,7 +2740,11 @@
         <v>Agg</v>
       </c>
       <c r="Z25" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level stressed_expected_loss per L1 business segment segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. CONVERT to USD via l2.fx_rate spot rate
+  3. COMPUTE SUM(facility EL × FX rate) per business segment
+Direct-sum rollup with FX conversion.
 </v>
       </c>
       <c r="AA25" t="str">
@@ -4392,14 +4456,14 @@
         <v>EXP-035</v>
       </c>
       <c r="B44" t="str" xml:space="preserve">
-        <v xml:space="preserve">Net Income divided by Total Assets. Calculated efficiency KPI measuring asset productivity and overall financial performance.
+        <v xml:space="preserve">Net Income divided by Total Assets (at counterparty level) or Committed Exposure bank-share (at facility level). Measures asset utilization efficiency and overall financial performance.
 </v>
       </c>
       <c r="C44" t="str">
         <v>Return on Assets (%)</v>
       </c>
       <c r="D44" t="str" xml:space="preserve">
-        <v xml:space="preserve">Facility Net Income / Facility Exposure
+        <v xml:space="preserve">Facility Net Income / Committed Exposure (Bank Share portion only).
 </v>
       </c>
       <c r="E44" t="str">
@@ -4418,7 +4482,7 @@
         <v>Calc</v>
       </c>
       <c r="J44" t="str" xml:space="preserve">
-        <v xml:space="preserve">Facility Net Income / Facility Exposure
+        <v xml:space="preserve">Facility Net Income / Committed Exposure (Bank Share portion only).
 </v>
       </c>
       <c r="K44" t="str">
@@ -4431,7 +4495,7 @@
         <v>Calc</v>
       </c>
       <c r="N44" t="str" xml:space="preserve">
-        <v xml:space="preserve">Net Income / Total Assets * 100 per counterparty (direct from financials).
+        <v xml:space="preserve">Counterparty Net Income / Total Assets * 100. Net income computed from revenue minus expenses.
 </v>
       </c>
       <c r="O44" t="str">
@@ -4485,14 +4549,14 @@
         <v>EXP-036</v>
       </c>
       <c r="B45" t="str" xml:space="preserve">
-        <v xml:space="preserve">Net Income divided by Equity. Calculated profitability KPI measuring return generated on shareholder capital and supporting performance benchmarking.
+        <v xml:space="preserve">Net Income divided by Shareholders Equity. Profitability KPI measuring return generated on shareholder capital. At facility level uses committed exposure (bank share) as denominator proxy.
 </v>
       </c>
       <c r="C45" t="str">
         <v>Return on Equity (%)</v>
       </c>
       <c r="D45" t="str" xml:space="preserve">
-        <v xml:space="preserve">Net Income (Facility) / Allocated Equity (Facility)
+        <v xml:space="preserve">Facility Net Income / Committed Exposure (Bank Share portion only).
 </v>
       </c>
       <c r="E45" t="str">
@@ -4511,7 +4575,7 @@
         <v>Calc</v>
       </c>
       <c r="J45" t="str" xml:space="preserve">
-        <v xml:space="preserve">Net Income (Facility) / Allocated Equity (Facility)
+        <v xml:space="preserve">Facility Net Income / Committed Exposure (Bank Share portion only).
 </v>
       </c>
       <c r="K45" t="str">
@@ -4524,7 +4588,7 @@
         <v>Calc</v>
       </c>
       <c r="N45" t="str" xml:space="preserve">
-        <v xml:space="preserve">Net Income / Shareholders Equity * 100 per counterparty (direct from financials).
+        <v xml:space="preserve">Counterparty Net Income / Shareholders Equity * 100. Net income computed from revenue minus expenses.
 </v>
       </c>
       <c r="O45" t="str">
@@ -4578,14 +4642,14 @@
         <v>EXP-037</v>
       </c>
       <c r="B46" t="str" xml:space="preserve">
-        <v xml:space="preserve">Total principal and interest obligations due within reporting period in millions USD. Used in repayment capacity and covenant analysis.
+        <v xml:space="preserve">Total principal and interest obligations due within reporting period. Facility level in local currency; counterparty and above converted to USD. Used in repayment capacity and covenant analysis.
 </v>
       </c>
       <c r="C46" t="str">
         <v>Total Debt Service ($)</v>
       </c>
       <c r="D46" t="str" xml:space="preserve">
-        <v xml:space="preserve">Lookup total_debt_service_amt from facility_financial_snapshot, convert to USD via l2.fx_rate spot rate (COALESCE to 1 for USD-denominated facilities).
+        <v xml:space="preserve">Interest Expense + Principal Payment from facility_financial_snapshot. Facility level stays in local currency (no FX conversion).
 </v>
       </c>
       <c r="E46" t="str">
@@ -4604,7 +4668,7 @@
         <v>Calc</v>
       </c>
       <c r="J46" t="str" xml:space="preserve">
-        <v xml:space="preserve">Lookup total_debt_service_amt from facility_financial_snapshot, convert to USD via l2.fx_rate spot rate (COALESCE to 1 for USD-denominated facilities).
+        <v xml:space="preserve">Interest Expense + Principal Payment from facility_financial_snapshot. Facility level stays in local currency (no FX conversion).
 </v>
       </c>
       <c r="K46" t="str">
@@ -4617,7 +4681,7 @@
         <v>Agg</v>
       </c>
       <c r="N46" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_debt_service_amt converted to USD per counterparty.
+        <v xml:space="preserve">SUM of facility-level TDS converted to USD per counterparty.
 </v>
       </c>
       <c r="O46" t="str">
@@ -4630,7 +4694,7 @@
         <v>Agg</v>
       </c>
       <c r="R46" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_debt_service_amt converted to USD per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level TDS converted to USD per L3 desk segment.
 </v>
       </c>
       <c r="S46" t="str">
@@ -4643,7 +4707,7 @@
         <v>Agg</v>
       </c>
       <c r="V46" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_debt_service_amt converted to USD per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level TDS converted to USD per L2 portfolio segment.
 </v>
       </c>
       <c r="W46" t="str">
@@ -4656,7 +4720,7 @@
         <v>Agg</v>
       </c>
       <c r="Z46" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_debt_service_amt converted to USD per L1 business segment.
+        <v xml:space="preserve">SUM of facility-level TDS converted to USD per L1 business segment.
 </v>
       </c>
       <c r="AA46" t="str">
@@ -5796,14 +5860,15 @@
         <v>PRC-003</v>
       </c>
       <c r="B59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of exposures within portfolio with approved pricing or policy exceptions. Derived governance KPI measuring policy discipline and risk culture strength.
+        <v xml:space="preserve">Percentage of facilities with approved pricing or policy exceptions. Computed as COUNT(exception facilities) / COUNT(total facilities) × 100. Sourced from L2 facility_pricing_snapshot — the atomic pricing record — using the is_pricing_exception_flag. At aggregate levels, uses count-ratio rollup: re-counts exceptions and totals across all constituent facilities, never averages pre-computed rates. Key governance KPI measuring policy discipline, risk culture strength, and pricing override frequency.
 </v>
       </c>
       <c r="C59" t="str">
         <v>Exception Rate (%)</v>
       </c>
       <c r="D59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if pricing exception, 0 otherwise.
+        <v xml:space="preserve">Binary flag: 1.0 if pricing exception approved, 0.0 otherwise.
+Ingredients: is_pricing_exception_flag (L2 facility_pricing_snapshot)
 </v>
       </c>
       <c r="E59" t="str">
@@ -5822,7 +5887,8 @@
         <v>Calc</v>
       </c>
       <c r="J59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Binary flag: 1 if pricing exception, 0 otherwise.
+        <v xml:space="preserve">Binary flag: 1.0 if pricing exception approved, 0.0 otherwise.
+Ingredients: is_pricing_exception_flag (L2 facility_pricing_snapshot)
 </v>
       </c>
       <c r="K59" t="str">
@@ -5835,7 +5901,10 @@
         <v>Calc</v>
       </c>
       <c r="N59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with pricing exception per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD is_pricing_exception_flag for all facilities of this counterparty
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup: re-counts from facility-level flags.
 </v>
       </c>
       <c r="O59" t="str">
@@ -5848,7 +5917,10 @@
         <v>Calc</v>
       </c>
       <c r="R59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with pricing exception per L3 desk.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOOKUP managed_segment_id from enterprise_business_taxonomy
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup per desk.
 </v>
       </c>
       <c r="S59" t="str">
@@ -5861,7 +5933,10 @@
         <v>Calc</v>
       </c>
       <c r="V59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with pricing exception per L2 portfolio.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup per portfolio.
 </v>
       </c>
       <c r="W59" t="str">
@@ -5874,7 +5949,10 @@
         <v>Calc</v>
       </c>
       <c r="Z59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Percentage of facilities with pricing exception per L1 business segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup per business segment.
 </v>
       </c>
       <c r="AA59" t="str">
@@ -6168,14 +6246,14 @@
         <v>PRC-007</v>
       </c>
       <c r="B63" t="str" xml:space="preserve">
-        <v xml:space="preserve">Credit spread over reference base rate charged on exposure, expressed as percentage. Represents risk premium embedded in pricing and supports yield analysis.
+        <v xml:space="preserve">Credit spread over reference base rate charged on exposure, expressed in basis points. Represents risk premium embedded in pricing. Aggregated using exposure-weighted average to avoid Simpson's paradox.
 </v>
       </c>
       <c r="C63" t="str">
         <v>Interest Rate Spread (%)</v>
       </c>
       <c r="D63" t="str" xml:space="preserve">
-        <v xml:space="preserve">Facility Asset Spread/ Total Outstanding Balance
+        <v xml:space="preserve">Raw spread_bps from facility_pricing_snapshot for each facility.
 </v>
       </c>
       <c r="E63" t="str">
@@ -6191,10 +6269,10 @@
         <v>Y</v>
       </c>
       <c r="I63" t="str">
-        <v>Calc</v>
+        <v>Raw</v>
       </c>
       <c r="J63" t="str" xml:space="preserve">
-        <v xml:space="preserve">Facility Asset Spread/ Total Outstanding Balance
+        <v xml:space="preserve">Raw spread_bps from facility_pricing_snapshot for each facility.
 </v>
       </c>
       <c r="K63" t="str">
@@ -6207,7 +6285,7 @@
         <v>Avg</v>
       </c>
       <c r="N63" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of interest_rate_spread_bps across counterparty facilities.
+        <v xml:space="preserve">Exposure-weighted average of spread_bps across counterparty facilities. Weight = committed_amount * bank_share_pct.
 </v>
       </c>
       <c r="O63" t="str">
@@ -6220,7 +6298,7 @@
         <v>Avg</v>
       </c>
       <c r="R63" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level interest_rate_spread_bps per L3 desk segment.
+        <v xml:space="preserve">Exposure-weighted average of spread_bps per L3 desk segment.
 </v>
       </c>
       <c r="S63" t="str">
@@ -6233,7 +6311,7 @@
         <v>Avg</v>
       </c>
       <c r="V63" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level interest_rate_spread_bps per L2 portfolio segment.
+        <v xml:space="preserve">Exposure-weighted average of spread_bps per L2 portfolio segment.
 </v>
       </c>
       <c r="W63" t="str">
@@ -6243,10 +6321,10 @@
         <v>Y</v>
       </c>
       <c r="Y63" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="Z63" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level interest_rate_spread_bps per L1 business segment segment.
+        <v xml:space="preserve">Exposure-weighted average of spread_bps per L1 business segment.
 </v>
       </c>
       <c r="AA63" t="str">
@@ -6830,14 +6908,14 @@
         <v>REF-004</v>
       </c>
       <c r="B70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Unique system identifier assigned to the borrower or obligor. Used for exposure aggregation and risk consolidation.
+        <v xml:space="preserve">Unique system identifier assigned to the borrower or obligor. Used for exposure aggregation and risk consolidation across the GSIB. At facility level, returns the counterparty_id linked to each facility. At upper levels, returns COUNT(DISTINCT counterparty_id) — the number of unique obligors in each organizational segment.
 </v>
       </c>
       <c r="C70" t="str">
         <v>Counterparty ID</v>
       </c>
       <c r="D70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">Direct lookup of counterparty_id from facility_master for each active facility. Uses current records only (SCD2 filtered).
 </v>
       </c>
       <c r="E70" t="str">
@@ -6856,7 +6934,7 @@
         <v>Raw</v>
       </c>
       <c r="J70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">Direct lookup of counterparty_id from facility_master for each active facility. Uses current records only (SCD2 filtered).
 </v>
       </c>
       <c r="K70" t="str">
@@ -6869,7 +6947,7 @@
         <v>Raw</v>
       </c>
       <c r="N70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">Identity — returns counterparty_id for each current counterparty.
 </v>
       </c>
       <c r="O70" t="str">
@@ -6882,7 +6960,7 @@
         <v>Agg</v>
       </c>
       <c r="R70" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L3 desk segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L3 desk segment — number of unique obligors in each desk.
 </v>
       </c>
       <c r="S70" t="str">
@@ -6895,7 +6973,7 @@
         <v>Agg</v>
       </c>
       <c r="V70" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L2 portfolio segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L2 portfolio segment — number of unique obligors in each portfolio.
 </v>
       </c>
       <c r="W70" t="str">
@@ -6908,7 +6986,7 @@
         <v>Agg</v>
       </c>
       <c r="Z70" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L1 business segment segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L1 business segment — number of unique obligors in each business segment.
 </v>
       </c>
       <c r="AA70" t="str">
@@ -6923,14 +7001,14 @@
         <v>REF-005</v>
       </c>
       <c r="B71" t="str" xml:space="preserve">
-        <v xml:space="preserve">Descriptive name of the counterparty as documented in the credit agreement. Used for reporting clarity and operational reference.
+        <v xml:space="preserve">Legal name of the counterparty as documented in the credit agreement. At facility level, returns the counterparty_id (numeric proxy for the name since metric values are numeric). At counterparty level, identity lookup. At upper levels, COUNT(DISTINCT counterparty_id) — number of unique named obligors per organizational segment. Used for reporting clarity and operational reference across all regulatory submissions.
 </v>
       </c>
       <c r="C71" t="str">
         <v>Counterparty Name</v>
       </c>
       <c r="D71" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read legal_name from counterparty for each facility's counterparty.
+        <v xml:space="preserve">Lookup counterparty_id from facility_master for each active facility. The numeric counterparty_id serves as proxy for the legal name (string values resolved via counterparty dimension join at display time). Uses current records only.
 </v>
       </c>
       <c r="E71" t="str">
@@ -6949,7 +7027,7 @@
         <v>Raw</v>
       </c>
       <c r="J71" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read legal_name from counterparty for each facility's counterparty.
+        <v xml:space="preserve">Lookup counterparty_id from facility_master for each active facility. The numeric counterparty_id serves as proxy for the legal name (string values resolved via counterparty dimension join at display time). Uses current records only.
 </v>
       </c>
       <c r="K71" t="str">
@@ -6959,10 +7037,10 @@
         <v>Y</v>
       </c>
       <c r="M71" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="N71" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with counterparty name per counterparty.
+        <v xml:space="preserve">Identity — returns counterparty_id for each current counterparty. Legal name resolved via counterparty dimension join at display time.
 </v>
       </c>
       <c r="O71" t="str">
@@ -6975,7 +7053,7 @@
         <v>Agg</v>
       </c>
       <c r="R71" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with counterparty name per L3 desk segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L3 desk segment — number of unique named obligors in each desk.
 </v>
       </c>
       <c r="S71" t="str">
@@ -6988,7 +7066,7 @@
         <v>Agg</v>
       </c>
       <c r="V71" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with counterparty name per L2 portfolio segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L2 portfolio segment — number of unique named obligors in each portfolio.
 </v>
       </c>
       <c r="W71" t="str">
@@ -7001,7 +7079,7 @@
         <v>Agg</v>
       </c>
       <c r="Z71" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with counterparty name per L1 business segment.
+        <v xml:space="preserve">COUNT(DISTINCT counterparty_id) per L1 business segment — number of unique named obligors in each business segment.
 </v>
       </c>
       <c r="AA71" t="str">
@@ -7016,14 +7094,14 @@
         <v>REF-006</v>
       </c>
       <c r="B72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Country of risk or booking location. Supports geographic concentration and sovereign risk analysis.
+        <v xml:space="preserve">Country of risk derived from the counterparty's domicile. At facility level, returns a numeric country identifier (via counterparty → country_dim join path). At counterparty level, identity lookup. At desk/portfolio/segment levels, COUNT(DISTINCT country_code) — geographic diversification indicator showing the number of unique countries represented. Supports FFIEC 009 Country Exposure Report and Basel III geographic concentration analysis.
 </v>
       </c>
       <c r="C72" t="str">
         <v>Country</v>
       </c>
       <c r="D72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of country_name from country_dim.
+        <v xml:space="preserve">Lookup country for each facility via counterparty → country_dim join path. Returns counterparty_id as numeric proxy (country_name resolved at display time via dimension join). Uses current records only.
 </v>
       </c>
       <c r="E72" t="str">
@@ -7042,7 +7120,7 @@
         <v>Raw</v>
       </c>
       <c r="J72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of country_name from country_dim.
+        <v xml:space="preserve">Lookup country for each facility via counterparty → country_dim join path. Returns counterparty_id as numeric proxy (country_name resolved at display time via dimension join). Uses current records only.
 </v>
       </c>
       <c r="K72" t="str">
@@ -7055,7 +7133,7 @@
         <v>Raw</v>
       </c>
       <c r="N72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read country_name per counterparty.
+        <v xml:space="preserve">Lookup country for each counterparty via country_code → country_dim join. Returns counterparty_id as numeric proxy.
 </v>
       </c>
       <c r="O72" t="str">
@@ -7068,7 +7146,7 @@
         <v>Agg</v>
       </c>
       <c r="R72" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level country_name per L3 desk segment.
+        <v xml:space="preserve">COUNT(DISTINCT country_code) per L3 desk segment — number of unique countries represented, a geographic diversification indicator.
 </v>
       </c>
       <c r="S72" t="str">
@@ -7081,7 +7159,7 @@
         <v>Agg</v>
       </c>
       <c r="V72" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level country_name per L2 portfolio segment.
+        <v xml:space="preserve">COUNT(DISTINCT country_code) per L2 portfolio segment — number of unique countries represented in each portfolio.
 </v>
       </c>
       <c r="W72" t="str">
@@ -7094,7 +7172,7 @@
         <v>Agg</v>
       </c>
       <c r="Z72" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level country_name per L1 business segment segment.
+        <v xml:space="preserve">COUNT(DISTINCT country_code) per L1 business segment — geographic diversification at the highest organizational level.
 </v>
       </c>
       <c r="AA72" t="str">
@@ -7109,14 +7187,14 @@
         <v>REF-007</v>
       </c>
       <c r="B73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Unique identifier linking facility to governing credit agreement documentation.
+        <v xml:space="preserve">Unique identifier linking each facility to its governing credit agreement documentation. Used for contract tracking, facility-to-agreement linkage, and regulatory reporting. At counterparty level, returns count of distinct credit agreements per borrower.
 </v>
       </c>
       <c r="C73" t="str">
         <v>Credit Agreement ID</v>
       </c>
       <c r="D73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of credit_agreement_id from credit_agreement_master.
+        <v xml:space="preserve">Direct lookup of credit_agreement_id for each active facility via facility_master joined to credit_agreement_master.
 </v>
       </c>
       <c r="E73" t="str">
@@ -7135,7 +7213,7 @@
         <v>Raw</v>
       </c>
       <c r="J73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of credit_agreement_id from credit_agreement_master.
+        <v xml:space="preserve">Direct lookup of credit_agreement_id for each active facility via facility_master joined to credit_agreement_master.
 </v>
       </c>
       <c r="K73" t="str">
@@ -7145,10 +7223,10 @@
         <v>Y</v>
       </c>
       <c r="M73" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="N73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read credit_agreement_id per counterparty.
+        <v xml:space="preserve">Count of distinct credit agreements per counterparty. Provides visibility into borrower complexity and multi-agreement relationships.
 </v>
       </c>
       <c r="O73" t="str">
@@ -7161,7 +7239,7 @@
         <v>Agg</v>
       </c>
       <c r="R73" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level credit_agreement_id per L3 desk segment.
+        <v xml:space="preserve">Count of distinct credit agreements per L3 desk segment via enterprise_business_taxonomy.
 </v>
       </c>
       <c r="S73" t="str">
@@ -7174,7 +7252,7 @@
         <v>Agg</v>
       </c>
       <c r="V73" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level credit_agreement_id per L2 portfolio segment.
+        <v xml:space="preserve">Count of distinct credit agreements per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
 </v>
       </c>
       <c r="W73" t="str">
@@ -7187,7 +7265,7 @@
         <v>Agg</v>
       </c>
       <c r="Z73" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level credit_agreement_id per L1 business segment segment.
+        <v xml:space="preserve">Count of distinct credit agreements per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
 </v>
       </c>
       <c r="AA73" t="str">
@@ -7295,7 +7373,7 @@
         <v>REF-009</v>
       </c>
       <c r="B75" t="str" xml:space="preserve">
-        <v xml:space="preserve">Date on which loan or contract became legally effective.
+        <v xml:space="preserve">Date on which loan or contract became legally effective. Sourced directly from facility_master. At aggregate levels, returns the earliest origination date (MIN) across constituent facilities — indicating the oldest vintage in the book. Key contract lifecycle tracking attribute for vintage analysis and portfolio seasoning assessment.
 </v>
       </c>
       <c r="C75" t="str">
@@ -7303,6 +7381,7 @@
       </c>
       <c r="D75" t="str" xml:space="preserve">
         <v xml:space="preserve">Direct lookup of origination_date from facility_master.
+Ingredients: origination_date (L2 facility_master — raw field)
 </v>
       </c>
       <c r="E75" t="str">
@@ -7322,6 +7401,7 @@
       </c>
       <c r="J75" t="str" xml:space="preserve">
         <v xml:space="preserve">Direct lookup of origination_date from facility_master.
+Ingredients: origination_date (L2 facility_master — raw field)
 </v>
       </c>
       <c r="K75" t="str">
@@ -7334,7 +7414,10 @@
         <v>Agg</v>
       </c>
       <c r="N75" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level origination_date) per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD origination_date from l2.facility_master for all active facilities
+  2. COMPUTE MIN(origination_date) — earliest contract vintage
+Indicates the oldest banking relationship tenure for this counterparty.
 </v>
       </c>
       <c r="O75" t="str">
@@ -7347,7 +7430,10 @@
         <v>Agg</v>
       </c>
       <c r="R75" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level origination_date per L3 desk segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOAD origination_date from l2.facility_master
+  2. JOIN l1.enterprise_business_taxonomy on lob_segment_id
+  3. COMPUTE MIN(origination_date) — earliest vintage in desk book
 </v>
       </c>
       <c r="S75" t="str">
@@ -7360,7 +7446,9 @@
         <v>Agg</v>
       </c>
       <c r="V75" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level origination_date per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. COMPUTE MIN(origination_date) — earliest vintage in portfolio
 </v>
       </c>
       <c r="W75" t="str">
@@ -7373,7 +7461,9 @@
         <v>Agg</v>
       </c>
       <c r="Z75" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level origination_date per L1 business segment segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. COMPUTE MIN(origination_date) — earliest vintage in business segment
 </v>
       </c>
       <c r="AA75" t="str">
@@ -8969,14 +9059,14 @@
         <v>REF-027</v>
       </c>
       <c r="B93" t="str" xml:space="preserve">
-        <v xml:space="preserve">Industry sector classification of the counterparty, enabling sector concentration risk assessment.
+        <v xml:space="preserve">Industry sector classification of the counterparty, enabling sector concentration risk assessment. Facility and counterparty levels return industry_name. Aggregate levels return the dominant industry (highest total exposure) per segment.
 </v>
       </c>
       <c r="C93" t="str">
         <v>Sector</v>
       </c>
       <c r="D93" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of industry_name from industry_dim.
+        <v xml:space="preserve">Lookup industry_name via facility_master -&gt; counterparty -&gt; industry_dim.
 </v>
       </c>
       <c r="E93" t="str">
@@ -8995,7 +9085,7 @@
         <v>Raw</v>
       </c>
       <c r="J93" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of industry_name from industry_dim.
+        <v xml:space="preserve">Lookup industry_name via facility_master -&gt; counterparty -&gt; industry_dim.
 </v>
       </c>
       <c r="K93" t="str">
@@ -9008,7 +9098,7 @@
         <v>Raw</v>
       </c>
       <c r="N93" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read industry_name per counterparty.
+        <v xml:space="preserve">Lookup industry_name directly from counterparty -&gt; industry_dim.
 </v>
       </c>
       <c r="O93" t="str">
@@ -9018,10 +9108,10 @@
         <v>Y</v>
       </c>
       <c r="Q93" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R93" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level industry_name per L3 desk segment.
+        <v xml:space="preserve">Dominant industry (highest gross exposure) per L3 desk segment.
 </v>
       </c>
       <c r="S93" t="str">
@@ -9031,10 +9121,10 @@
         <v>Y</v>
       </c>
       <c r="U93" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V93" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level industry_name per L2 portfolio segment.
+        <v xml:space="preserve">Dominant industry (highest gross exposure) per L2 portfolio segment.
 </v>
       </c>
       <c r="W93" t="str">
@@ -9044,10 +9134,10 @@
         <v>Y</v>
       </c>
       <c r="Y93" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z93" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level industry_name per L1 business segment segment.
+        <v xml:space="preserve">Dominant industry (highest gross exposure) per L1 business segment.
 </v>
       </c>
       <c r="AA93" t="str">
@@ -9620,14 +9710,14 @@
         <v>RSK-001</v>
       </c>
       <c r="B100" t="str" xml:space="preserve">
-        <v xml:space="preserve">Most recent internal credit rating assigned at reporting date. Used for segmentation and exposure-weighted risk aggregation.
+        <v xml:space="preserve">Risk rating tier derived from counterparty probability of default (PD). Each counterparty's pd_annual is matched against the risk_rating_tier_dim reference table (pd_min_pct / pd_max_pct boundaries) to assign a tier classification. At facility level, the tier is inherited from the owning counterparty. At aggregate levels, MAX (worst-case) tier ordinal is reported.
 </v>
       </c>
       <c r="C100" t="str">
         <v>Risk Rating Tier</v>
       </c>
       <c r="D100" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility.
+        <v xml:space="preserve">For each facility, inherit the risk rating tier from the owning counterparty. Join facility_master to counterparty, then range-match counterparty pd_annual against risk_rating_tier_dim to derive the tier ordinal (display_order).
 </v>
       </c>
       <c r="E100" t="str">
@@ -9643,10 +9733,10 @@
         <v>Y</v>
       </c>
       <c r="I100" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="J100" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility.
+        <v xml:space="preserve">For each facility, inherit the risk rating tier from the owning counterparty. Join facility_master to counterparty, then range-match counterparty pd_annual against risk_rating_tier_dim to derive the tier ordinal (display_order).
 </v>
       </c>
       <c r="K100" t="str">
@@ -9656,10 +9746,10 @@
         <v>Y</v>
       </c>
       <c r="M100" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N100" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating per counterparty.
+        <v xml:space="preserve">For each counterparty, look up pd_annual and range-match against risk_rating_tier_dim where pd_annual &gt;= pd_min_pct AND pd_annual &lt; pd_max_pct. Returns the tier ordinal (display_order). Counterparties with NULL PD receive tier 0 (unrated).
 </v>
       </c>
       <c r="O100" t="str">
@@ -9672,7 +9762,7 @@
         <v>Agg</v>
       </c>
       <c r="R100" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating per L3 desk segment.
+        <v xml:space="preserve">Worst-case (MAX) risk rating tier ordinal across all counterparties in the L3 desk segment. Higher ordinal = riskier tier. Full tier distribution available via counterparty-level drill-down.
 </v>
       </c>
       <c r="S100" t="str">
@@ -9685,7 +9775,7 @@
         <v>Agg</v>
       </c>
       <c r="V100" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating per L2 portfolio segment.
+        <v xml:space="preserve">Worst-case (MAX) risk rating tier ordinal per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
 </v>
       </c>
       <c r="W100" t="str">
@@ -9698,7 +9788,7 @@
         <v>Agg</v>
       </c>
       <c r="Z100" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating per L1 business segment.
+        <v xml:space="preserve">Worst-case (MAX) risk rating tier ordinal per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
 </v>
       </c>
       <c r="AA100" t="str">

--- a/data/metrics_dimensions_filled.xlsx
+++ b/data/metrics_dimensions_filled.xlsx
@@ -2766,11 +2766,21 @@
         <v>Undrawn Exposure ($)</v>
       </c>
       <c r="D26" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each active facility:
-1. SUM(funded_amount) from PRINCIPAL position_detail rows per facility
-2. Subtract from committed_facility_amt to get unfunded amount
-3. Multiply by COALESCE(bank_share_pct, 100) / 100 from facility_lender_allocation
-Ensures: Committed Exposure = Outstanding Exposure + Undrawn Exposure
+        <v xml:space="preserve">1. LOAD  l2.position  (pos)
+   WHERE pos.as_of_date = :as_of_date
+2. JOIN  l2.position_detail  (pdtl)
+   ON    pdtl.position_id = pos.position_id
+   AND   pdtl.detail_type = 'PRINCIPAL'
+3. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = pos.facility_id
+   WHERE fm.is_active_flag = 'Y'
+4. LEFT JOIN  l2.facility_lender_allocation  (fla)
+   ON    fla.facility_id = fm.facility_id
+   AND   fla.is_current_flag = 'Y'
+5. GROUP BY fm.facility_id
+6. COMPUTE
+   metric_value = (committed_facility_amt - SUM(funded_amount))
+                  * COALESCE(bank_share_pct, 100) / 100
 </v>
       </c>
       <c r="E26" t="str">
@@ -2789,11 +2799,21 @@
         <v>Calc</v>
       </c>
       <c r="J26" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each active facility:
-1. SUM(funded_amount) from PRINCIPAL position_detail rows per facility
-2. Subtract from committed_facility_amt to get unfunded amount
-3. Multiply by COALESCE(bank_share_pct, 100) / 100 from facility_lender_allocation
-Ensures: Committed Exposure = Outstanding Exposure + Undrawn Exposure
+        <v xml:space="preserve">1. LOAD  l2.position  (pos)
+   WHERE pos.as_of_date = :as_of_date
+2. JOIN  l2.position_detail  (pdtl)
+   ON    pdtl.position_id = pos.position_id
+   AND   pdtl.detail_type = 'PRINCIPAL'
+3. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = pos.facility_id
+   WHERE fm.is_active_flag = 'Y'
+4. LEFT JOIN  l2.facility_lender_allocation  (fla)
+   ON    fla.facility_id = fm.facility_id
+   AND   fla.is_current_flag = 'Y'
+5. GROUP BY fm.facility_id
+6. COMPUTE
+   metric_value = (committed_facility_amt - SUM(funded_amount))
+                  * COALESCE(bank_share_pct, 100) / 100
 </v>
       </c>
       <c r="K26" t="str">
@@ -2806,8 +2826,13 @@
         <v>Calc</v>
       </c>
       <c r="N26" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each counterparty, sum facility-level undrawn exposure weighted
-by participation_pct from facility_counterparty_participation.
+        <v xml:space="preserve">1. LOAD  facility-level undrawn exposure (subquery)
+2. JOIN  l2.facility_counterparty_participation  (fcp)
+   ON    fcp.facility_id = fac.facility_id
+   AND   fcp.is_current_flag = 'Y'
+3. GROUP BY fcp.counterparty_id
+4. COMPUTE
+   metric_value = SUM(facility_undrawn * participation_pct)
 </v>
       </c>
       <c r="O26" t="str">
@@ -2820,8 +2845,15 @@
         <v>Agg</v>
       </c>
       <c r="R26" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level undrawn exposure per L3 desk segment.
-Joins facility_master.lob_segment_id to enterprise_business_taxonomy.managed_segment_id.
+        <v xml:space="preserve">1. LOAD  facility-level undrawn exposure (subquery)
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = fac.facility_id
+3. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt)
+   ON    ebt.managed_segment_id = fm.lob_segment_id
+   AND   ebt.is_current_flag = 'Y'
+4. GROUP BY ebt.managed_segment_id
+5. COMPUTE
+   metric_value = SUM(facility_undrawn)
 </v>
       </c>
       <c r="S26" t="str">
@@ -2834,8 +2866,16 @@
         <v>Agg</v>
       </c>
       <c r="V26" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level undrawn exposure per L2 portfolio segment.
-Traverses L3 -&gt; L2 via parent_segment_id.
+        <v xml:space="preserve">1. LOAD  facility-level undrawn exposure (subquery)
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = fac.facility_id
+3. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l3)
+   ON    ebt_l3.managed_segment_id = fm.lob_segment_id
+4. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l2)
+   ON    ebt_l2.managed_segment_id = ebt_l3.parent_segment_id
+5. GROUP BY ebt_l2.managed_segment_id
+6. COMPUTE
+   metric_value = SUM(facility_undrawn)
 </v>
       </c>
       <c r="W26" t="str">
@@ -2848,8 +2888,18 @@
         <v>Agg</v>
       </c>
       <c r="Z26" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level undrawn exposure per L1 business segment.
-Traverses L3 -&gt; L2 -&gt; L1 via parent_segment_id chain.
+        <v xml:space="preserve">1. LOAD  facility-level undrawn exposure (subquery)
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = fac.facility_id
+3. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l3)
+   ON    ebt_l3.managed_segment_id = fm.lob_segment_id
+4. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l2)
+   ON    ebt_l2.managed_segment_id = ebt_l3.parent_segment_id
+5. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l1)
+   ON    ebt_l1.managed_segment_id = ebt_l2.parent_segment_id
+6. GROUP BY ebt_l1.managed_segment_id
+7. COMPUTE
+   metric_value = SUM(facility_undrawn)
 </v>
       </c>
       <c r="AA26" t="str">
@@ -2864,17 +2914,28 @@
         <v>EXP-018</v>
       </c>
       <c r="B27" t="str" xml:space="preserve">
-        <v xml:space="preserve">Bank-share-adjusted funded (drawn) exposure amount. Represents the portion of committed credit currently utilized by the borrower. Maps to FR Y-14Q Field 25 (Utilized Exposure Global, MDRM G075).
+        <v xml:space="preserve">Bank-share-adjusted funded (drawn) exposure amount. Represents the portion of committed credit currently utilized by the borrower. Maps to FR Y-14Q Field 25 (Utilized Exposure Global, MDRM G075). Counterparty level uses exposure_counterparty_attribution for risk-shifted attribution weighting per Basel III requirements.
 </v>
       </c>
       <c r="C27" t="str">
         <v>Outstanding Exposure ($)</v>
       </c>
       <c r="D27" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each active facility:
-1. Join position -&gt; position_detail on position_id (both as_of_date filtered)
-2. SUM(funded_amount) across all positions for the facility
-3. Multiply by COALESCE(bank_share_pct, 100) / 100 from facility_lender_allocation
+        <v xml:space="preserve">1. LOAD  l2.position  (pos)
+   WHERE pos.as_of_date = :as_of_date
+2. JOIN  l2.position_detail  (pdtl)
+   ON    pdtl.position_id = pos.position_id
+   AND   pdtl.detail_type = 'PRINCIPAL'
+3. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = pos.facility_id
+   WHERE fm.is_active_flag = 'Y'
+4. LEFT JOIN  l2.facility_lender_allocation  (fla)
+   ON    fla.facility_id = fm.facility_id
+   AND   fla.is_current_flag = 'Y'
+5. GROUP BY pos.facility_id
+6. COMPUTE
+   metric_value = SUM(funded_amount)
+                  * COALESCE(bank_share_pct, 100) / 100
 </v>
       </c>
       <c r="E27" t="str">
@@ -2893,10 +2954,21 @@
         <v>Calc</v>
       </c>
       <c r="J27" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each active facility:
-1. Join position -&gt; position_detail on position_id (both as_of_date filtered)
-2. SUM(funded_amount) across all positions for the facility
-3. Multiply by COALESCE(bank_share_pct, 100) / 100 from facility_lender_allocation
+        <v xml:space="preserve">1. LOAD  l2.position  (pos)
+   WHERE pos.as_of_date = :as_of_date
+2. JOIN  l2.position_detail  (pdtl)
+   ON    pdtl.position_id = pos.position_id
+   AND   pdtl.detail_type = 'PRINCIPAL'
+3. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = pos.facility_id
+   WHERE fm.is_active_flag = 'Y'
+4. LEFT JOIN  l2.facility_lender_allocation  (fla)
+   ON    fla.facility_id = fm.facility_id
+   AND   fla.is_current_flag = 'Y'
+5. GROUP BY pos.facility_id
+6. COMPUTE
+   metric_value = SUM(funded_amount)
+                  * COALESCE(bank_share_pct, 100) / 100
 </v>
       </c>
       <c r="K27" t="str">
@@ -2909,9 +2981,13 @@
         <v>Calc</v>
       </c>
       <c r="N27" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each counterparty, sum facility-level outstanding exposure weighted
-by participation_pct from facility_counterparty_participation.
-Uses contractual pro-rata basis per FR Y-14Q requirements.
+        <v xml:space="preserve">1. LOAD  facility-level outstanding exposure (subquery)
+2. JOIN  l2.exposure_counterparty_attribution  (eca)
+   ON    eca.facility_id = fac.facility_id
+   AND   eca.as_of_date = :as_of_date
+3. GROUP BY eca.counterparty_id
+4. COMPUTE
+   metric_value = SUM(facility_outstanding * attribution_pct)
 </v>
       </c>
       <c r="O27" t="str">
@@ -2924,8 +3000,15 @@
         <v>Agg</v>
       </c>
       <c r="R27" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level outstanding exposure per L3 desk segment.
-Joins facility_master.lob_segment_id to enterprise_business_taxonomy.managed_segment_id.
+        <v xml:space="preserve">1. LOAD  facility-level outstanding exposure (subquery)
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = fac.facility_id
+3. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt)
+   ON    ebt.managed_segment_id = fm.lob_segment_id
+   AND   ebt.is_current_flag = 'Y'
+4. GROUP BY ebt.managed_segment_id
+5. COMPUTE
+   metric_value = SUM(facility_outstanding)
 </v>
       </c>
       <c r="S27" t="str">
@@ -2938,8 +3021,16 @@
         <v>Agg</v>
       </c>
       <c r="V27" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level outstanding exposure per L2 portfolio segment.
-Traverses L3 -&gt; L2 via parent_segment_id.
+        <v xml:space="preserve">1. LOAD  facility-level outstanding exposure (subquery)
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = fac.facility_id
+3. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l3)
+   ON    ebt_l3.managed_segment_id = fm.lob_segment_id
+4. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l2)
+   ON    ebt_l2.managed_segment_id = ebt_l3.parent_segment_id
+5. GROUP BY ebt_l2.managed_segment_id
+6. COMPUTE
+   metric_value = SUM(facility_outstanding)
 </v>
       </c>
       <c r="W27" t="str">
@@ -2952,8 +3043,14 @@
         <v>Agg</v>
       </c>
       <c r="Z27" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level outstanding exposure per L1 business segment.
-Traverses L3 -&gt; L2 -&gt; L1 via parent_segment_id chain.
+        <v xml:space="preserve">1. LOAD  facility-level outstanding exposure (subquery)
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = fac.facility_id
+3. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l3, ebt_l2, ebt_l1)
+   Traverse L3 -&gt; L2 -&gt; L1 via parent_segment_id chain
+4. GROUP BY ebt_l1.managed_segment_id
+5. COMPUTE
+   metric_value = SUM(facility_outstanding)
 </v>
       </c>
       <c r="AA27" t="str">
@@ -2968,14 +3065,15 @@
         <v>EXP-019</v>
       </c>
       <c r="B28" t="str" xml:space="preserve">
-        <v xml:space="preserve">Maximum approved credit exposure authorized for the counterparty or Line of Business segment in USD. Represents formal risk appetite allocation and governance control threshold.
+        <v xml:space="preserve">Maximum approved credit exposure authorized for the counterparty or Line of Business segment in USD. Sourced directly from the limit_rule reference table. Represents formal risk appetite allocation and governance control threshold set by the Credit Risk Committee. Not applicable at individual facility level — limits are set at counterparty and organizational hierarchy levels.
 </v>
       </c>
       <c r="C28" t="str">
         <v>Exposure Limit ($)</v>
       </c>
       <c r="D28" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read limit_amt from lob_exposure_summary for each facility as-of reporting date.
+        <v xml:space="preserve">Not applicable — exposure limits are set at counterparty and
+organizational levels, not per individual facility. Returns NULL.
 </v>
       </c>
       <c r="E28" t="str">
@@ -2994,7 +3092,8 @@
         <v>Raw</v>
       </c>
       <c r="J28" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read limit_amt from lob_exposure_summary for each facility as-of reporting date.
+        <v xml:space="preserve">Not applicable — exposure limits are set at counterparty and
+organizational levels, not per individual facility. Returns NULL.
 </v>
       </c>
       <c r="K28" t="str">
@@ -3007,7 +3106,12 @@
         <v>Raw</v>
       </c>
       <c r="N28" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read limit_amt per counterparty.
+        <v xml:space="preserve">1. LOAD  l1.limit_rule  (lr)
+   WHERE lr.is_current_flag = 'Y'
+   AND   lr.counterparty_id IS NOT NULL
+2. GROUP BY lr.counterparty_id
+3. COMPUTE
+   metric_value = SUM(limit_amount_usd)
 </v>
       </c>
       <c r="O28" t="str">
@@ -3017,10 +3121,18 @@
         <v>Y</v>
       </c>
       <c r="Q28" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="R28" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level limit_amt per L3 desk segment.
+        <v xml:space="preserve">1. LOAD  l1.limit_rule  (lr)
+   WHERE lr.is_current_flag = 'Y'
+   AND   lr.lob_segment_id IS NOT NULL
+2. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt)
+   ON    ebt.managed_segment_id = lr.lob_segment_id
+   AND   ebt.is_current_flag = 'Y'
+3. GROUP BY lr.lob_segment_id
+4. COMPUTE
+   metric_value = SUM(limit_amount_usd)
 </v>
       </c>
       <c r="S28" t="str">
@@ -3030,10 +3142,18 @@
         <v>Y</v>
       </c>
       <c r="U28" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="V28" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level limit_amt per L2 portfolio segment.
+        <v xml:space="preserve">1. LOAD  l1.limit_rule  (lr)
+   WHERE lr.is_current_flag = 'Y'
+   AND   lr.lob_segment_id IS NOT NULL
+2. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt)
+   ON    ebt.managed_segment_id = lr.lob_segment_id
+   AND   ebt.is_current_flag = 'Y'
+3. GROUP BY lr.lob_segment_id
+4. COMPUTE
+   metric_value = SUM(limit_amount_usd)
 </v>
       </c>
       <c r="W28" t="str">
@@ -3043,10 +3163,18 @@
         <v>Y</v>
       </c>
       <c r="Y28" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="Z28" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level limit_amt per L1 business segment segment.
+        <v xml:space="preserve">1. LOAD  l1.limit_rule  (lr)
+   WHERE lr.is_current_flag = 'Y'
+   AND   lr.lob_segment_id IS NOT NULL
+2. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt)
+   ON    ebt.managed_segment_id = lr.lob_segment_id
+   AND   ebt.is_current_flag = 'Y'
+3. GROUP BY lr.lob_segment_id
+4. COMPUTE
+   metric_value = SUM(limit_amount_usd)
 </v>
       </c>
       <c r="AA28" t="str">
@@ -3061,14 +3189,25 @@
         <v>EXP-020</v>
       </c>
       <c r="B29" t="str" xml:space="preserve">
-        <v xml:space="preserve">The estimated exposure amount (in USD) expected to be outstanding if the borrower defaults.
+        <v xml:space="preserve">Estimated exposure amount outstanding if the borrower defaults, computed from L2 atomic inputs per Basel III: EAD = OB + CCF × Undrawn, where OB = drawn/funded amount, CCF = credit conversion factor from facility_risk_snapshot, and Undrawn = committed minus drawn from facility_exposure_snapshot. Bank-share adjusted via facility_exposure_snapshot. At counterparty level, weighted by participation_pct from facility_counterparty_participation per FR Y-14Q requirements.
 </v>
       </c>
       <c r="C29" t="str">
         <v>Exposure at Default ($)</v>
       </c>
       <c r="D29" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read exposure_at_default from credit_event_facility_link for each facility as-of reporting date.
+        <v xml:space="preserve">1. LOAD  l2.facility_exposure_snapshot  (fes)
+   WHERE fes.as_of_date = :as_of_date
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = fes.facility_id
+   WHERE fm.is_active_flag = 'Y'
+3. LEFT JOIN  l2.facility_risk_snapshot  (frs)
+   ON    frs.facility_id = fes.facility_id
+   AND   frs.as_of_date = fes.as_of_date
+4. GROUP BY fes.facility_id
+5. COMPUTE
+   metric_value = (drawn_amount + CCF * undrawn_amount)
+                  * bank_share_pct / 100
 </v>
       </c>
       <c r="E29" t="str">
@@ -3084,10 +3223,21 @@
         <v>Y</v>
       </c>
       <c r="I29" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="J29" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read exposure_at_default from credit_event_facility_link for each facility as-of reporting date.
+        <v xml:space="preserve">1. LOAD  l2.facility_exposure_snapshot  (fes)
+   WHERE fes.as_of_date = :as_of_date
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = fes.facility_id
+   WHERE fm.is_active_flag = 'Y'
+3. LEFT JOIN  l2.facility_risk_snapshot  (frs)
+   ON    frs.facility_id = fes.facility_id
+   AND   frs.as_of_date = fes.as_of_date
+4. GROUP BY fes.facility_id
+5. COMPUTE
+   metric_value = (drawn_amount + CCF * undrawn_amount)
+                  * bank_share_pct / 100
 </v>
       </c>
       <c r="K29" t="str">
@@ -3097,10 +3247,22 @@
         <v>Y</v>
       </c>
       <c r="M29" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N29" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level exposure_at_default per counterparty.
+        <v xml:space="preserve">1. LOAD  l2.facility_exposure_snapshot  (fes)
+   WHERE fes.as_of_date = :as_of_date
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = fes.facility_id
+3. LEFT JOIN  l2.facility_risk_snapshot  (frs)
+   ON    frs.facility_id = fes.facility_id
+4. JOIN  l2.facility_counterparty_participation  (fcp)
+   ON    fcp.facility_id = fes.facility_id
+   AND   fcp.is_current_flag = 'Y'
+5. GROUP BY fcp.counterparty_id
+6. COMPUTE
+   metric_value = SUM((drawn + CCF * undrawn) * bank_share / 100
+                  * participation_pct)
 </v>
       </c>
       <c r="O29" t="str">
@@ -3113,7 +3275,15 @@
         <v>Agg</v>
       </c>
       <c r="R29" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level exposure_at_default per L3 desk segment.
+        <v xml:space="preserve">1. LOAD  facility-level EAD (subquery)
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = fac.facility_id
+3. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt)
+   ON    ebt.managed_segment_id = fm.lob_segment_id
+   AND   ebt.is_current_flag = 'Y'
+4. GROUP BY ebt.managed_segment_id
+5. COMPUTE
+   metric_value = SUM(facility_ead)
 </v>
       </c>
       <c r="S29" t="str">
@@ -3126,7 +3296,13 @@
         <v>Agg</v>
       </c>
       <c r="V29" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level exposure_at_default per L2 portfolio segment.
+        <v xml:space="preserve">1. LOAD  facility-level EAD (subquery)
+2. JOIN  l2.facility_master  (fm)
+3. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l3, ebt_l2)
+   Traverse L3 -&gt; L2 via parent_segment_id
+4. GROUP BY ebt_l2.managed_segment_id
+5. COMPUTE
+   metric_value = SUM(facility_ead)
 </v>
       </c>
       <c r="W29" t="str">
@@ -3139,7 +3315,13 @@
         <v>Agg</v>
       </c>
       <c r="Z29" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level exposure_at_default per L1 business segment segment.
+        <v xml:space="preserve">1. LOAD  facility-level EAD (subquery)
+2. JOIN  l2.facility_master  (fm)
+3. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l3, ebt_l2, ebt_l1)
+   Traverse L3 -&gt; L2 -&gt; L1 via parent_segment_id chain
+4. GROUP BY ebt_l1.managed_segment_id
+5. COMPUTE
+   metric_value = SUM(facility_ead)
 </v>
       </c>
       <c r="AA29" t="str">
@@ -3154,14 +3336,14 @@
         <v>EXP-021</v>
       </c>
       <c r="B30" t="str" xml:space="preserve">
-        <v xml:space="preserve">Derived categorical classification (Sufficient, Approaching, Fully Utilized) of utilization level based on current drawn exposure relative to committed amount. Operational KPI providing early warning insight into limit pressure, liquidity usage, and potential capacity constraints.
+        <v xml:space="preserve">Derived categorical classification of utilization level based on current drawn exposure relative to committed amount. Maps facility utilization percentage against l1.utilization_status_dim threshold ranges to return status labels (e.g., Sufficient, Approaching, Fully Utilized). Operational KPI providing early warning insight into limit pressure, liquidity usage, and potential capacity constraints.
 </v>
       </c>
       <c r="C30" t="str">
-        <v>Facility Utilization Status (e.g., Sufficient, Approaching, Fully Utilized)</v>
+        <v>Utilization Status (Utilized Exposure to Committed Exposure)</v>
       </c>
       <c r="D30" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated utilization_status_code per facility.
+        <v xml:space="preserve">For each facility, compute utilization_pct from L2 atomic data (drawn_amount / committed_amount * 100), then match against l1.utilization_status_dim threshold ranges (utilization_min_pct &lt;= pct &lt; utilization_max_pct) to return status_name.
 </v>
       </c>
       <c r="E30" t="str">
@@ -3180,63 +3362,63 @@
         <v>Calc</v>
       </c>
       <c r="J30" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated utilization_status_code per facility.
+        <v xml:space="preserve">For each facility, compute utilization_pct from L2 atomic data (drawn_amount / committed_amount * 100), then match against l1.utilization_status_dim threshold ranges (utilization_min_pct &lt;= pct &lt; utilization_max_pct) to return status_name.
 </v>
       </c>
       <c r="K30" t="str">
-        <v>Facility Utilization Status (e.g., Sufficient, Approaching, Fully Utilized) (facility)</v>
+        <v>Utilization Status (Utilized Exposure to Committed Exposure) (facility)</v>
       </c>
       <c r="L30" t="str">
         <v>Y</v>
       </c>
       <c r="M30" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N30" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level utilization_status_code) per counterparty.
+        <v xml:space="preserve">Compute counterparty-level utilization pct via sum-ratio with FX conversion: SUM(drawn * fx) / SUM(committed * fx) * 100. Then look up status from utilization_status_dim threshold ranges.
 </v>
       </c>
       <c r="O30" t="str">
-        <v>Facility Utilization Status (e.g., Sufficient, Approaching, Fully Utilized) (counterparty)</v>
+        <v>Utilization Status (Utilized Exposure to Committed Exposure) (counterparty)</v>
       </c>
       <c r="P30" t="str">
         <v>Y</v>
       </c>
       <c r="Q30" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R30" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level utilization_status_code per L3 desk segment.
+        <v xml:space="preserve">Compute L3 desk-level utilization pct via sum-ratio with FX conversion, then look up status from utilization_status_dim threshold ranges.
 </v>
       </c>
       <c r="S30" t="str">
-        <v>Facility Utilization Status (e.g., Sufficient, Approaching, Fully Utilized) (desk)</v>
+        <v>Utilization Status (Utilized Exposure to Committed Exposure) (desk)</v>
       </c>
       <c r="T30" t="str">
         <v>Y</v>
       </c>
       <c r="U30" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V30" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level utilization_status_code per L2 portfolio segment.
+        <v xml:space="preserve">Compute L2 portfolio-level utilization pct via sum-ratio with FX conversion (one-hop EBT hierarchy), then look up status from utilization_status_dim threshold ranges.
 </v>
       </c>
       <c r="W30" t="str">
-        <v>Facility Utilization Status (e.g., Sufficient, Approaching, Fully Utilized) (portfolio)</v>
+        <v>Utilization Status (Utilized Exposure to Committed Exposure) (portfolio)</v>
       </c>
       <c r="X30" t="str">
         <v>Y</v>
       </c>
       <c r="Y30" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z30" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level utilization_status_code per L1 business segment segment.
+        <v xml:space="preserve">Compute L1 business segment-level utilization pct via sum-ratio with FX conversion (two-hop EBT hierarchy), then look up status from utilization_status_dim threshold ranges.
 </v>
       </c>
       <c r="AA30" t="str">
-        <v>Facility Utilization Status (e.g., Sufficient, Approaching, Fully Utilized) (business_segment)</v>
+        <v>Utilization Status (Utilized Exposure to Committed Exposure) (business_segment)</v>
       </c>
       <c r="AB30" t="str">
         <v/>
@@ -3340,14 +3522,14 @@
         <v>EXP-023</v>
       </c>
       <c r="B32" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure × LGD expressed in dollar terms weighted based on facility-level exposure. Derived loss severity metric estimating expected recovery-adjusted loss magnitude.
+        <v xml:space="preserve">Expected dollar loss given default. Computed as EAD (drawn amount, bank share) multiplied by LGD percentage from facility risk snapshot. Expressed in local currency at facility level and FX-converted to USD at aggregate levels. Quantifies loss severity per facility and across rollup hierarchy.
 </v>
       </c>
       <c r="C32" t="str">
         <v>Loss Given Default ($)</v>
       </c>
       <c r="D32" t="str" xml:space="preserve">
-        <v xml:space="preserve">EAD * LGD (in Percentage) for all facilities across Counterparties
+        <v xml:space="preserve">EAD (bank share) x LGD% per facility in local currency.
 </v>
       </c>
       <c r="E32" t="str">
@@ -3366,7 +3548,7 @@
         <v>Calc</v>
       </c>
       <c r="J32" t="str" xml:space="preserve">
-        <v xml:space="preserve">EAD * LGD (in Percentage) for all facilities across Counterparties
+        <v xml:space="preserve">EAD (bank share) x LGD% per facility in local currency.
 </v>
       </c>
       <c r="K32" t="str">
@@ -3379,7 +3561,7 @@
         <v>Agg</v>
       </c>
       <c r="N32" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level lgd_estimate per counterparty.
+        <v xml:space="preserve">SUM of facility-level LGD$ per counterparty, FX-converted to USD.
 </v>
       </c>
       <c r="O32" t="str">
@@ -3392,7 +3574,7 @@
         <v>Agg</v>
       </c>
       <c r="R32" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level lgd_estimate per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level LGD$ per L3 desk segment, FX-converted to USD.
 </v>
       </c>
       <c r="S32" t="str">
@@ -3405,7 +3587,7 @@
         <v>Agg</v>
       </c>
       <c r="V32" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level lgd_estimate per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level LGD$ per L2 portfolio segment, FX-converted to USD.
 </v>
       </c>
       <c r="W32" t="str">
@@ -3418,7 +3600,7 @@
         <v>Agg</v>
       </c>
       <c r="Z32" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level lgd_estimate per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level LGD$ per L1 business segment, FX-converted to USD.
 </v>
       </c>
       <c r="AA32" t="str">
@@ -3433,14 +3615,14 @@
         <v>EXP-024</v>
       </c>
       <c r="B33" t="str" xml:space="preserve">
-        <v xml:space="preserve">Status of credit limit (Active, Warning, Breach). Used to monitor risk appetite breaches and exposure governance compliance.
+        <v xml:space="preserve">Utilization-based limit compliance status. At facility level reads the pre-computed limit_status_code. At aggregate levels computes drawn-to- committed utilization percentage (FX-converted to USD) and maps to a status code via utilization_status_dim thresholds. Used for credit limit monitoring and risk appetite breach detection.
 </v>
       </c>
       <c r="C33" t="str">
         <v>Limit Status</v>
       </c>
       <c r="D33" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated limit_status_code per facility.
+        <v xml:space="preserve">Read pre-computed limit_status_code from facility_exposure_snapshot.
 </v>
       </c>
       <c r="E33" t="str">
@@ -3456,10 +3638,10 @@
         <v>Y</v>
       </c>
       <c r="I33" t="str">
-        <v>Calc</v>
+        <v>Raw</v>
       </c>
       <c r="J33" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated limit_status_code per facility.
+        <v xml:space="preserve">Read pre-computed limit_status_code from facility_exposure_snapshot.
 </v>
       </c>
       <c r="K33" t="str">
@@ -3469,10 +3651,10 @@
         <v>Y</v>
       </c>
       <c r="M33" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N33" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level limit_status_code per counterparty.
+        <v xml:space="preserve">Compute drawn-to-committed utilization % per counterparty (FX-converted), then map to status via utilization_status_dim thresholds.
 </v>
       </c>
       <c r="O33" t="str">
@@ -3482,10 +3664,10 @@
         <v>Y</v>
       </c>
       <c r="Q33" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R33" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level limit_status_code per L3 desk segment.
+        <v xml:space="preserve">Compute drawn-to-committed utilization % per L3 desk segment (FX-converted), then map to status via utilization_status_dim.
 </v>
       </c>
       <c r="S33" t="str">
@@ -3495,10 +3677,10 @@
         <v>Y</v>
       </c>
       <c r="U33" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V33" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level limit_status_code per L2 portfolio segment.
+        <v xml:space="preserve">Compute drawn-to-committed utilization % per L2 portfolio segment (FX-converted), then map to status via utilization_status_dim.
 </v>
       </c>
       <c r="W33" t="str">
@@ -3508,10 +3690,10 @@
         <v>Y</v>
       </c>
       <c r="Y33" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z33" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level limit_status_code per L1 business segment segment.
+        <v xml:space="preserve">Compute drawn-to-committed utilization % per L1 business segment (FX-converted), then map to status via utilization_status_dim.
 </v>
       </c>
       <c r="AA33" t="str">
@@ -5967,14 +6149,14 @@
         <v>PRC-004</v>
       </c>
       <c r="B60" t="str" xml:space="preserve">
-        <v xml:space="preserve">Fee percentage applied to committed or undrawn exposure. Calculated KPI supporting pricing adequacy and revenue optimization analysis.
+        <v xml:space="preserve">Fee percentage applied to committed or undrawn exposure. Sourced from l2.facility_pricing_snapshot at facility level. Supports pricing adequacy and revenue optimization analysis. Aggregate levels use exposure-weighted average with FX conversion to USD.
 </v>
       </c>
       <c r="C60" t="str">
         <v>Fee Rate (%)</v>
       </c>
       <c r="D60" t="str" xml:space="preserve">
-        <v xml:space="preserve">Fee Income / Average Balance
+        <v xml:space="preserve">Direct lookup of fee_rate_pct from l2.facility_pricing_snapshot.
 </v>
       </c>
       <c r="E60" t="str">
@@ -5990,10 +6172,10 @@
         <v>Y</v>
       </c>
       <c r="I60" t="str">
-        <v>Calc</v>
+        <v>Raw</v>
       </c>
       <c r="J60" t="str" xml:space="preserve">
-        <v xml:space="preserve">Fee Income / Average Balance
+        <v xml:space="preserve">Direct lookup of fee_rate_pct from l2.facility_pricing_snapshot.
 </v>
       </c>
       <c r="K60" t="str">
@@ -6006,7 +6188,7 @@
         <v>Avg</v>
       </c>
       <c r="N60" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of fee_rate_pct across counterparty facilities.
+        <v xml:space="preserve">Supplementary (not in primary specification at counterparty level). Exposure-weighted average fee rate per counterparty with FX conversion: SUM(fee_rate * committed_amt * fx) / SUM(committed_amt * fx).
 </v>
       </c>
       <c r="O60" t="str">
@@ -6019,7 +6201,7 @@
         <v>Avg</v>
       </c>
       <c r="R60" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level fee_rate_pct per L3 desk segment.
+        <v xml:space="preserve">Supplementary. Exposure-weighted average fee rate per L3 desk segment with FX conversion.
 </v>
       </c>
       <c r="S60" t="str">
@@ -6032,7 +6214,7 @@
         <v>Avg</v>
       </c>
       <c r="V60" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level fee_rate_pct per L2 portfolio segment.
+        <v xml:space="preserve">Supplementary. Exposure-weighted average fee rate per L2 portfolio segment with FX conversion.
 </v>
       </c>
       <c r="W60" t="str">
@@ -6042,10 +6224,10 @@
         <v>Y</v>
       </c>
       <c r="Y60" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="Z60" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level fee_rate_pct per L1 business segment segment.
+        <v xml:space="preserve">Supplementary. Exposure-weighted average fee rate per L1 business segment with FX conversion.
 </v>
       </c>
       <c r="AA60" t="str">
@@ -7517,7 +7699,7 @@
         <v>Raw</v>
       </c>
       <c r="N76" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read facility_id per counterparty.
+        <v xml:space="preserve">Representative facility_id per counterparty (MIN).
 </v>
       </c>
       <c r="O76" t="str">
@@ -7527,10 +7709,10 @@
         <v>Y</v>
       </c>
       <c r="Q76" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="R76" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_id per L3 desk segment.
+        <v xml:space="preserve">Representative facility_id per L3 desk segment (MIN).
 </v>
       </c>
       <c r="S76" t="str">
@@ -7540,10 +7722,10 @@
         <v>Y</v>
       </c>
       <c r="U76" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="V76" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_id per L2 portfolio segment.
+        <v xml:space="preserve">Representative facility_id per L2 portfolio segment (MIN).
 </v>
       </c>
       <c r="W76" t="str">
@@ -7553,10 +7735,10 @@
         <v>Y</v>
       </c>
       <c r="Y76" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="Z76" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_id per L1 business segment segment.
+        <v xml:space="preserve">Representative facility_id per L1 business segment (MIN).
 </v>
       </c>
       <c r="AA76" t="str">
@@ -7610,7 +7792,7 @@
         <v>Raw</v>
       </c>
       <c r="N77" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read facility_name per counterparty.
+        <v xml:space="preserve">Representative facility_name per counterparty (MIN alphabetical).
 </v>
       </c>
       <c r="O77" t="str">
@@ -7620,10 +7802,10 @@
         <v>Y</v>
       </c>
       <c r="Q77" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="R77" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_name per L3 desk segment.
+        <v xml:space="preserve">Representative facility_name per L3 desk segment (MIN alphabetical).
 </v>
       </c>
       <c r="S77" t="str">
@@ -7633,10 +7815,10 @@
         <v>Y</v>
       </c>
       <c r="U77" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="V77" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_name per L2 portfolio segment.
+        <v xml:space="preserve">Representative facility_name per L2 portfolio segment (MIN alphabetical).
 </v>
       </c>
       <c r="W77" t="str">
@@ -7646,10 +7828,10 @@
         <v>Y</v>
       </c>
       <c r="Y77" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="Z77" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_name per L1 business segment segment.
+        <v xml:space="preserve">Representative facility_name per L1 business segment (MIN alphabetical).
 </v>
       </c>
       <c r="AA77" t="str">
@@ -7664,14 +7846,14 @@
         <v>REF-012</v>
       </c>
       <c r="B78" t="str" xml:space="preserve">
-        <v xml:space="preserve">Type of credit facility (e.g., Term Loan, Revolver, Letter of Credit). Enables product-level segmentation, risk concentration analysis, and performance benchmarking.
+        <v xml:space="preserve">Type of credit facility (e.g., Term Loan, Revolver, Letter of Credit). Enables product-level segmentation, risk concentration analysis, and performance benchmarking. At facility level returns the facility type string; at aggregate levels returns the count of distinct active facilities in the segment for distribution analysis.
 </v>
       </c>
       <c r="C78" t="str">
         <v>Facility Type</v>
       </c>
       <c r="D78" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read facility_type from facility_exposure_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Direct lookup of facility_type from facility_master.
 </v>
       </c>
       <c r="E78" t="str">
@@ -7690,7 +7872,7 @@
         <v>Raw</v>
       </c>
       <c r="J78" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read facility_type from facility_exposure_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Direct lookup of facility_type from facility_master.
 </v>
       </c>
       <c r="K78" t="str">
@@ -7700,10 +7882,10 @@
         <v>Y</v>
       </c>
       <c r="M78" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="N78" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level facility_type) per counterparty.
+        <v xml:space="preserve">Not in primary specification at counterparty level. Supplementary: representative facility_type per counterparty (MIN).
 </v>
       </c>
       <c r="O78" t="str">
@@ -7716,7 +7898,7 @@
         <v>Agg</v>
       </c>
       <c r="R78" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_type per L3 desk segment.
+        <v xml:space="preserve">Count distinct active facilities per L3 desk segment. Provides facility distribution for product mix analysis.
 </v>
       </c>
       <c r="S78" t="str">
@@ -7729,7 +7911,7 @@
         <v>Agg</v>
       </c>
       <c r="V78" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_type per L2 portfolio segment.
+        <v xml:space="preserve">Count distinct active facilities per L2 portfolio segment. Provides facility distribution for product mix analysis.
 </v>
       </c>
       <c r="W78" t="str">
@@ -7742,7 +7924,7 @@
         <v>Agg</v>
       </c>
       <c r="Z78" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_type per L1 business segment segment.
+        <v xml:space="preserve">Count distinct active facilities per L1 business segment. Provides facility distribution for product mix analysis.
 </v>
       </c>
       <c r="AA78" t="str">
@@ -8036,14 +8218,14 @@
         <v>REF-016</v>
       </c>
       <c r="B82" t="str" xml:space="preserve">
-        <v xml:space="preserve">Legal entity booking or owning the exposure. Critical for regulatory capital and entity-level reporting.
+        <v xml:space="preserve">Booking legal entity for each facility exposure. At facility level returns the entity name from the legal_entity table. At aggregate levels returns the count of distinct booking entities for risk concentration analysis.
 </v>
       </c>
       <c r="C82" t="str">
         <v>Legal Entity</v>
       </c>
       <c r="D82" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of legal_name from counterparty.
+        <v xml:space="preserve">Lookup legal_entity_name from legal_entity table via facility_exposure_snapshot.legal_entity_id.
 </v>
       </c>
       <c r="E82" t="str">
@@ -8062,7 +8244,7 @@
         <v>Raw</v>
       </c>
       <c r="J82" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of legal_name from counterparty.
+        <v xml:space="preserve">Lookup legal_entity_name from legal_entity table via facility_exposure_snapshot.legal_entity_id.
 </v>
       </c>
       <c r="K82" t="str">
@@ -8072,10 +8254,10 @@
         <v>Y</v>
       </c>
       <c r="M82" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="N82" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of legal_name from counterparty.
+        <v xml:space="preserve">Count of distinct booking legal entities per counterparty.
 </v>
       </c>
       <c r="O82" t="str">
@@ -8085,10 +8267,10 @@
         <v>Y</v>
       </c>
       <c r="Q82" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R82" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level legal_name per L3 desk segment.
+        <v xml:space="preserve">Count of distinct booking legal entities per L3 desk segment.
 </v>
       </c>
       <c r="S82" t="str">
@@ -8098,10 +8280,10 @@
         <v>Y</v>
       </c>
       <c r="U82" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V82" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level legal_name per L2 portfolio segment.
+        <v xml:space="preserve">Count of distinct booking legal entities per L2 portfolio segment.
 </v>
       </c>
       <c r="W82" t="str">
@@ -8111,10 +8293,10 @@
         <v>Y</v>
       </c>
       <c r="Y82" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z82" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level legal_name per L1 business segment segment.
+        <v xml:space="preserve">Count of distinct booking legal entities per L1 business segment.
 </v>
       </c>
       <c r="AA82" t="str">
@@ -8129,14 +8311,14 @@
         <v>REF-017</v>
       </c>
       <c r="B83" t="str" xml:space="preserve">
-        <v xml:space="preserve">Unique identifier assigned to legal entity in enterprise systems.
+        <v xml:space="preserve">Unique identifier for the booking legal entity. At facility level returns the entity ID. At aggregate levels returns count of distinct booking entities for entity concentration tracking.
 </v>
       </c>
       <c r="C83" t="str">
         <v>Legal Entity ID</v>
       </c>
       <c r="D83" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read legal_entity_id from facility_exposure_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Read legal_entity_id from facility_exposure_snapshot for each facility.
 </v>
       </c>
       <c r="E83" t="str">
@@ -8155,7 +8337,7 @@
         <v>Raw</v>
       </c>
       <c r="J83" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read legal_entity_id from facility_exposure_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Read legal_entity_id from facility_exposure_snapshot for each facility.
 </v>
       </c>
       <c r="K83" t="str">
@@ -8165,10 +8347,10 @@
         <v>Y</v>
       </c>
       <c r="M83" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="N83" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read legal_entity_id per counterparty.
+        <v xml:space="preserve">Count of distinct booking legal entities per counterparty.
 </v>
       </c>
       <c r="O83" t="str">
@@ -8178,10 +8360,10 @@
         <v>Y</v>
       </c>
       <c r="Q83" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R83" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level legal_entity_id per L3 desk segment.
+        <v xml:space="preserve">Count of distinct booking legal entities per L3 desk segment.
 </v>
       </c>
       <c r="S83" t="str">
@@ -8191,10 +8373,10 @@
         <v>Y</v>
       </c>
       <c r="U83" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V83" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level legal_entity_id per L2 portfolio segment.
+        <v xml:space="preserve">Count of distinct booking legal entities per L2 portfolio segment.
 </v>
       </c>
       <c r="W83" t="str">
@@ -8204,10 +8386,10 @@
         <v>Y</v>
       </c>
       <c r="Y83" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z83" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level legal_entity_id per L1 business segment segment.
+        <v xml:space="preserve">Count of distinct booking legal entities per L1 business segment.
 </v>
       </c>
       <c r="AA83" t="str">
@@ -9803,14 +9985,23 @@
         <v>RSK-002</v>
       </c>
       <c r="B101" t="str" xml:space="preserve">
-        <v xml:space="preserve">Current external credit agency rating assigned to the obligor. Used for benchmarking, regulatory reporting, and external credit risk validation. Sourced based on external Rating provider (S&amp;P, Moodys, Fitch) - populated based on firm's preferred recognized rating provider.
+        <v xml:space="preserve">External credit agency rating expressed as a numeric notch value from the rating_scale_dim. At facility/counterparty levels, returns the raw notch of the external rating. At aggregate levels (desk, portfolio, segment), computes the exposure-weighted average notch across all positions, rounded to the nearest whole notch. Lower notch = better rating (e.g., 1=AAA, 21=D). Sourced from position.external_risk_rating, mapped to rating_scale_dim.rating_value.
 </v>
       </c>
       <c r="C101" t="str">
         <v>Risk Rating - External Rating</v>
       </c>
       <c r="D101" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read external_risk_rating from position for each facility as-of reporting date.
+        <v xml:space="preserve">1. LOAD  l2.position  (pos)
+   WHERE pos.as_of_date = :as_of_date
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = pos.facility_id
+   WHERE fm.is_active_flag = 'Y'
+3. LEFT JOIN  l1.rating_scale_dim  (rs)
+   ON    rs.rating_notch = pos.external_risk_rating
+   AND   rs.is_current_flag = 'Y'
+4. COMPUTE
+   metric_value = rs.rating_value
 </v>
       </c>
       <c r="E101" t="str">
@@ -9829,7 +10020,16 @@
         <v>Raw</v>
       </c>
       <c r="J101" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read external_risk_rating from position for each facility as-of reporting date.
+        <v xml:space="preserve">1. LOAD  l2.position  (pos)
+   WHERE pos.as_of_date = :as_of_date
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = pos.facility_id
+   WHERE fm.is_active_flag = 'Y'
+3. LEFT JOIN  l1.rating_scale_dim  (rs)
+   ON    rs.rating_notch = pos.external_risk_rating
+   AND   rs.is_current_flag = 'Y'
+4. COMPUTE
+   metric_value = rs.rating_value
 </v>
       </c>
       <c r="K101" t="str">
@@ -9842,7 +10042,15 @@
         <v>Raw</v>
       </c>
       <c r="N101" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read external_risk_rating per counterparty.
+        <v xml:space="preserve">1. LOAD  l2.position  (pos)
+   WHERE pos.as_of_date = :as_of_date
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = pos.facility_id
+3. LEFT JOIN  l1.rating_scale_dim  (rs)
+   ON    rs.rating_notch = pos.external_risk_rating
+4. GROUP BY fm.counterparty_id
+5. COMPUTE
+   metric_value = ROUND(AVG(rating_value))
 </v>
       </c>
       <c r="O101" t="str">
@@ -9852,10 +10060,20 @@
         <v>Y</v>
       </c>
       <c r="Q101" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="R101" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level external_risk_rating per L3 desk segment.
+        <v xml:space="preserve">1. LOAD  l2.position  (pos)
+   WHERE pos.as_of_date = :as_of_date
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = pos.facility_id
+3. LEFT JOIN  l1.rating_scale_dim  (rs)
+   ON    rs.rating_notch = pos.external_risk_rating
+4. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt)
+   ON    ebt.managed_segment_id = fm.lob_segment_id
+5. GROUP BY ebt.managed_segment_id
+6. COMPUTE
+   metric_value = ROUND(AVG(rating_value))
 </v>
       </c>
       <c r="S101" t="str">
@@ -9865,10 +10083,19 @@
         <v>Y</v>
       </c>
       <c r="U101" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="V101" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level external_risk_rating per L2 portfolio segment.
+        <v xml:space="preserve">1. LOAD  l2.position  (pos)
+   WHERE pos.as_of_date = :as_of_date
+2. JOIN  l2.facility_master  (fm)
+3. LEFT JOIN  l1.rating_scale_dim  (rs)
+   ON    rs.rating_notch = pos.external_risk_rating
+4. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l3, ebt_l2)
+   Traverse L3 -&gt; L2 via parent_segment_id
+5. GROUP BY ebt_l2.managed_segment_id
+6. COMPUTE
+   metric_value = ROUND(AVG(rating_value))
 </v>
       </c>
       <c r="W101" t="str">
@@ -9878,10 +10105,19 @@
         <v>Y</v>
       </c>
       <c r="Y101" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="Z101" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level external_risk_rating per L1 business segment segment.
+        <v xml:space="preserve">1. LOAD  l2.position  (pos)
+   WHERE pos.as_of_date = :as_of_date
+2. JOIN  l2.facility_master  (fm)
+3. LEFT JOIN  l1.rating_scale_dim  (rs)
+   ON    rs.rating_notch = pos.external_risk_rating
+4. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l3, ebt_l2, ebt_l1)
+   Traverse L3 -&gt; L2 -&gt; L1 via parent_segment_id chain
+5. GROUP BY ebt_l1.managed_segment_id
+6. COMPUTE
+   metric_value = ROUND(AVG(rating_value))
 </v>
       </c>
       <c r="AA101" t="str">

--- a/data/metrics_dimensions_filled.xlsx
+++ b/data/metrics_dimensions_filled.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB108"/>
+  <dimension ref="A1:AB110"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -795,14 +795,14 @@
         <v>AMD-004</v>
       </c>
       <c r="B6" t="str" xml:space="preserve">
-        <v xml:space="preserve">Indicator that facility agreement has undergone amendment. Portfolio KPI (% Facilities with Amendments) signals restructuring activity.
+        <v xml:space="preserve">Percentage of active facilities that have undergone at least one contractual amendment. At facility level, returns a binary flag (1 = has amendment, 0 = no amendment). At counterparty and aggregate levels, computes the count-ratio: COUNT(amended facilities) / COUNT(total facilities) x 100. High amendment rates may signal portfolio stress, widespread restructuring activity, or covenant relief campaigns.
 </v>
       </c>
       <c r="C6" t="str">
-        <v>Amendment ID</v>
+        <v>Amendment Rate</v>
       </c>
       <c r="D6" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read amendment_event_id from amendment_event for each facility as-of reporting date.
+        <v xml:space="preserve">For each active facility, check whether any amendment_event records exist via LEFT JOIN. Returns 1 (has amendment) or 0 (no amendment). A facility is considered amended if it has at least one record in the amendment_event table regardless of amendment type or status.
 </v>
       </c>
       <c r="E6" t="str">
@@ -818,66 +818,66 @@
         <v>Y</v>
       </c>
       <c r="I6" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="J6" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read amendment_event_id from amendment_event for each facility as-of reporting date.
+        <v xml:space="preserve">For each active facility, check whether any amendment_event records exist via LEFT JOIN. Returns 1 (has amendment) or 0 (no amendment). A facility is considered amended if it has at least one record in the amendment_event table regardless of amendment type or status.
 </v>
       </c>
       <c r="K6" t="str">
-        <v>Amendment ID (facility)</v>
+        <v>Amendment Rate (facility)</v>
       </c>
       <c r="L6" t="str">
         <v>Y</v>
       </c>
       <c r="M6" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N6" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level amendment_event_id) per counterparty.
+        <v xml:space="preserve">Count-ratio: number of amended facilities divided by total active facilities for each counterparty, expressed as a percentage. Uses a DISTINCT subquery on amendment_event to avoid double-counting facilities with multiple amendments.
 </v>
       </c>
       <c r="O6" t="str">
-        <v>Amendment ID (counterparty)</v>
+        <v>Amendment Rate (counterparty)</v>
       </c>
       <c r="P6" t="str">
         <v>Y</v>
       </c>
       <c r="Q6" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R6" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level amendment_event_id per L3 desk segment.
+        <v xml:space="preserve">Count-ratio: percentage of amended facilities per L3 desk segment. Re-counts at segment level (never averages pre-computed ratios) to avoid Simpson's paradox. Uses EBT direct join for L3.
 </v>
       </c>
       <c r="S6" t="str">
-        <v>Amendment ID (desk)</v>
+        <v>Amendment Rate (desk)</v>
       </c>
       <c r="T6" t="str">
         <v>Y</v>
       </c>
       <c r="U6" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V6" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level amendment_event_id per L2 portfolio segment.
+        <v xml:space="preserve">Count-ratio: percentage of amended facilities per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id. Re-counts at portfolio level for mathematical consistency.
 </v>
       </c>
       <c r="W6" t="str">
-        <v>Amendment ID (portfolio)</v>
+        <v>Amendment Rate (portfolio)</v>
       </c>
       <c r="X6" t="str">
         <v>Y</v>
       </c>
       <c r="Y6" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z6" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level amendment_event_id per L1 business segment segment.
+        <v xml:space="preserve">Count-ratio: percentage of amended facilities per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1. Re-counts at segment level for mathematical consistency across the rollup hierarchy.
 </v>
       </c>
       <c r="AA6" t="str">
-        <v>Amendment ID (business_segment)</v>
+        <v>Amendment Rate (business_segment)</v>
       </c>
       <c r="AB6" t="str">
         <v/>
@@ -2766,11 +2766,21 @@
         <v>Undrawn Exposure ($)</v>
       </c>
       <c r="D26" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each active facility:
-1. SUM(funded_amount) from PRINCIPAL position_detail rows per facility
-2. Subtract from committed_facility_amt to get unfunded amount
-3. Multiply by COALESCE(bank_share_pct, 100) / 100 from facility_lender_allocation
-Ensures: Committed Exposure = Outstanding Exposure + Undrawn Exposure
+        <v xml:space="preserve">1. LOAD  l2.position  (pos)
+   WHERE pos.as_of_date = :as_of_date
+2. JOIN  l2.position_detail  (pdtl)
+   ON    pdtl.position_id = pos.position_id
+   AND   pdtl.detail_type = 'PRINCIPAL'
+3. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = pos.facility_id
+   WHERE fm.is_active_flag = 'Y'
+4. LEFT JOIN  l2.facility_lender_allocation  (fla)
+   ON    fla.facility_id = fm.facility_id
+   AND   fla.is_current_flag = 'Y'
+5. GROUP BY fm.facility_id
+6. COMPUTE
+   metric_value = (committed_facility_amt - SUM(funded_amount))
+                  * COALESCE(bank_share_pct, 100) / 100
 </v>
       </c>
       <c r="E26" t="str">
@@ -2789,11 +2799,21 @@
         <v>Calc</v>
       </c>
       <c r="J26" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each active facility:
-1. SUM(funded_amount) from PRINCIPAL position_detail rows per facility
-2. Subtract from committed_facility_amt to get unfunded amount
-3. Multiply by COALESCE(bank_share_pct, 100) / 100 from facility_lender_allocation
-Ensures: Committed Exposure = Outstanding Exposure + Undrawn Exposure
+        <v xml:space="preserve">1. LOAD  l2.position  (pos)
+   WHERE pos.as_of_date = :as_of_date
+2. JOIN  l2.position_detail  (pdtl)
+   ON    pdtl.position_id = pos.position_id
+   AND   pdtl.detail_type = 'PRINCIPAL'
+3. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = pos.facility_id
+   WHERE fm.is_active_flag = 'Y'
+4. LEFT JOIN  l2.facility_lender_allocation  (fla)
+   ON    fla.facility_id = fm.facility_id
+   AND   fla.is_current_flag = 'Y'
+5. GROUP BY fm.facility_id
+6. COMPUTE
+   metric_value = (committed_facility_amt - SUM(funded_amount))
+                  * COALESCE(bank_share_pct, 100) / 100
 </v>
       </c>
       <c r="K26" t="str">
@@ -2806,8 +2826,13 @@
         <v>Calc</v>
       </c>
       <c r="N26" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each counterparty, sum facility-level undrawn exposure weighted
-by participation_pct from facility_counterparty_participation.
+        <v xml:space="preserve">1. LOAD  facility-level undrawn exposure (subquery)
+2. JOIN  l2.facility_counterparty_participation  (fcp)
+   ON    fcp.facility_id = fac.facility_id
+   AND   fcp.is_current_flag = 'Y'
+3. GROUP BY fcp.counterparty_id
+4. COMPUTE
+   metric_value = SUM(facility_undrawn * participation_pct)
 </v>
       </c>
       <c r="O26" t="str">
@@ -2820,8 +2845,15 @@
         <v>Agg</v>
       </c>
       <c r="R26" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level undrawn exposure per L3 desk segment.
-Joins facility_master.lob_segment_id to enterprise_business_taxonomy.managed_segment_id.
+        <v xml:space="preserve">1. LOAD  facility-level undrawn exposure (subquery)
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = fac.facility_id
+3. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt)
+   ON    ebt.managed_segment_id = fm.lob_segment_id
+   AND   ebt.is_current_flag = 'Y'
+4. GROUP BY ebt.managed_segment_id
+5. COMPUTE
+   metric_value = SUM(facility_undrawn)
 </v>
       </c>
       <c r="S26" t="str">
@@ -2834,8 +2866,18 @@
         <v>Agg</v>
       </c>
       <c r="V26" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level undrawn exposure per L2 portfolio segment.
-Traverses L3 -&gt; L2 via parent_segment_id.
+        <v xml:space="preserve">1. LOAD  facility-level undrawn exposure (subquery)
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = fac.facility_id
+3. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l3)
+   ON    ebt_l3.managed_segment_id = fm.lob_segment_id
+     AND ebt_l3.is_current_flag = 'Y'
+4. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l2)
+   ON    ebt_l2.managed_segment_id = ebt_l3.parent_segment_id
+     AND ebt_l2.is_current_flag = 'Y'
+5. GROUP BY ebt_l2.managed_segment_id
+6. COMPUTE
+   metric_value = SUM(facility_undrawn)
 </v>
       </c>
       <c r="W26" t="str">
@@ -2848,8 +2890,21 @@
         <v>Agg</v>
       </c>
       <c r="Z26" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level undrawn exposure per L1 business segment.
-Traverses L3 -&gt; L2 -&gt; L1 via parent_segment_id chain.
+        <v xml:space="preserve">1. LOAD  facility-level undrawn exposure (subquery)
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = fac.facility_id
+3. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l3)
+   ON    ebt_l3.managed_segment_id = fm.lob_segment_id
+     AND ebt_l3.is_current_flag = 'Y'
+4. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l2)
+   ON    ebt_l2.managed_segment_id = ebt_l3.parent_segment_id
+     AND ebt_l2.is_current_flag = 'Y'
+5. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l1)
+   ON    ebt_l1.managed_segment_id = ebt_l2.parent_segment_id
+     AND ebt_l1.is_current_flag = 'Y'
+6. GROUP BY ebt_l1.managed_segment_id
+7. COMPUTE
+   metric_value = SUM(facility_undrawn)
 </v>
       </c>
       <c r="AA26" t="str">
@@ -2864,17 +2919,28 @@
         <v>EXP-018</v>
       </c>
       <c r="B27" t="str" xml:space="preserve">
-        <v xml:space="preserve">Bank-share-adjusted funded (drawn) exposure amount. Represents the portion of committed credit currently utilized by the borrower. Maps to FR Y-14Q Field 25 (Utilized Exposure Global, MDRM G075).
+        <v xml:space="preserve">Bank-share-adjusted funded (drawn) exposure amount. Represents the portion of committed credit currently utilized by the borrower. Maps to FR Y-14Q Field 25 (Utilized Exposure Global, MDRM G075). Counterparty level uses exposure_counterparty_attribution for risk-shifted attribution weighting per Basel III requirements.
 </v>
       </c>
       <c r="C27" t="str">
         <v>Outstanding Exposure ($)</v>
       </c>
       <c r="D27" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each active facility:
-1. Join position -&gt; position_detail on position_id (both as_of_date filtered)
-2. SUM(funded_amount) across all positions for the facility
-3. Multiply by COALESCE(bank_share_pct, 100) / 100 from facility_lender_allocation
+        <v xml:space="preserve">1. LOAD  l2.position  (pos)
+   WHERE pos.as_of_date = :as_of_date
+2. JOIN  l2.position_detail  (pdtl)
+   ON    pdtl.position_id = pos.position_id
+   AND   pdtl.detail_type = 'PRINCIPAL'
+3. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = pos.facility_id
+   WHERE fm.is_active_flag = 'Y'
+4. LEFT JOIN  l2.facility_lender_allocation  (fla)
+   ON    fla.facility_id = fm.facility_id
+   AND   fla.is_current_flag = 'Y'
+5. GROUP BY pos.facility_id
+6. COMPUTE
+   metric_value = SUM(funded_amount)
+                  * COALESCE(bank_share_pct, 100) / 100
 </v>
       </c>
       <c r="E27" t="str">
@@ -2893,10 +2959,21 @@
         <v>Calc</v>
       </c>
       <c r="J27" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each active facility:
-1. Join position -&gt; position_detail on position_id (both as_of_date filtered)
-2. SUM(funded_amount) across all positions for the facility
-3. Multiply by COALESCE(bank_share_pct, 100) / 100 from facility_lender_allocation
+        <v xml:space="preserve">1. LOAD  l2.position  (pos)
+   WHERE pos.as_of_date = :as_of_date
+2. JOIN  l2.position_detail  (pdtl)
+   ON    pdtl.position_id = pos.position_id
+   AND   pdtl.detail_type = 'PRINCIPAL'
+3. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = pos.facility_id
+   WHERE fm.is_active_flag = 'Y'
+4. LEFT JOIN  l2.facility_lender_allocation  (fla)
+   ON    fla.facility_id = fm.facility_id
+   AND   fla.is_current_flag = 'Y'
+5. GROUP BY pos.facility_id
+6. COMPUTE
+   metric_value = SUM(funded_amount)
+                  * COALESCE(bank_share_pct, 100) / 100
 </v>
       </c>
       <c r="K27" t="str">
@@ -2909,9 +2986,13 @@
         <v>Calc</v>
       </c>
       <c r="N27" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each counterparty, sum facility-level outstanding exposure weighted
-by participation_pct from facility_counterparty_participation.
-Uses contractual pro-rata basis per FR Y-14Q requirements.
+        <v xml:space="preserve">1. LOAD  facility-level outstanding exposure (subquery)
+2. JOIN  l2.exposure_counterparty_attribution  (eca)
+   ON    eca.facility_id = fac.facility_id
+   AND   eca.as_of_date = :as_of_date
+3. GROUP BY eca.counterparty_id
+4. COMPUTE
+   metric_value = SUM(facility_outstanding * attribution_pct)
 </v>
       </c>
       <c r="O27" t="str">
@@ -2924,8 +3005,15 @@
         <v>Agg</v>
       </c>
       <c r="R27" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level outstanding exposure per L3 desk segment.
-Joins facility_master.lob_segment_id to enterprise_business_taxonomy.managed_segment_id.
+        <v xml:space="preserve">1. LOAD  facility-level outstanding exposure (subquery)
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = fac.facility_id
+3. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt)
+   ON    ebt.managed_segment_id = fm.lob_segment_id
+   AND   ebt.is_current_flag = 'Y'
+4. GROUP BY ebt.managed_segment_id
+5. COMPUTE
+   metric_value = SUM(facility_outstanding)
 </v>
       </c>
       <c r="S27" t="str">
@@ -2938,8 +3026,18 @@
         <v>Agg</v>
       </c>
       <c r="V27" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level outstanding exposure per L2 portfolio segment.
-Traverses L3 -&gt; L2 via parent_segment_id.
+        <v xml:space="preserve">1. LOAD  facility-level outstanding exposure (subquery)
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = fac.facility_id
+3. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l3)
+   ON    ebt_l3.managed_segment_id = fm.lob_segment_id
+     AND ebt_l3.is_current_flag = 'Y'
+4. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l2)
+   ON    ebt_l2.managed_segment_id = ebt_l3.parent_segment_id
+     AND ebt_l2.is_current_flag = 'Y'
+5. GROUP BY ebt_l2.managed_segment_id
+6. COMPUTE
+   metric_value = SUM(facility_outstanding)
 </v>
       </c>
       <c r="W27" t="str">
@@ -2952,8 +3050,14 @@
         <v>Agg</v>
       </c>
       <c r="Z27" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level outstanding exposure per L1 business segment.
-Traverses L3 -&gt; L2 -&gt; L1 via parent_segment_id chain.
+        <v xml:space="preserve">1. LOAD  facility-level outstanding exposure (subquery)
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = fac.facility_id
+3. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l3, ebt_l2, ebt_l1)
+   Traverse L3 -&gt; L2 -&gt; L1 via parent_segment_id chain
+4. GROUP BY ebt_l1.managed_segment_id
+5. COMPUTE
+   metric_value = SUM(facility_outstanding)
 </v>
       </c>
       <c r="AA27" t="str">
@@ -2968,14 +3072,15 @@
         <v>EXP-019</v>
       </c>
       <c r="B28" t="str" xml:space="preserve">
-        <v xml:space="preserve">Maximum approved credit exposure authorized for the counterparty or Line of Business segment in USD. Represents formal risk appetite allocation and governance control threshold.
+        <v xml:space="preserve">Maximum approved credit exposure authorized for the counterparty or Line of Business segment in USD. Sourced directly from the limit_rule reference table. Represents formal risk appetite allocation and governance control threshold set by the Credit Risk Committee. Not applicable at individual facility level — limits are set at counterparty and organizational hierarchy levels.
 </v>
       </c>
       <c r="C28" t="str">
         <v>Exposure Limit ($)</v>
       </c>
       <c r="D28" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read limit_amt from lob_exposure_summary for each facility as-of reporting date.
+        <v xml:space="preserve">Not applicable — exposure limits are set at counterparty and
+organizational levels, not per individual facility. Returns NULL.
 </v>
       </c>
       <c r="E28" t="str">
@@ -2994,7 +3099,8 @@
         <v>Raw</v>
       </c>
       <c r="J28" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read limit_amt from lob_exposure_summary for each facility as-of reporting date.
+        <v xml:space="preserve">Not applicable — exposure limits are set at counterparty and
+organizational levels, not per individual facility. Returns NULL.
 </v>
       </c>
       <c r="K28" t="str">
@@ -3007,7 +3113,12 @@
         <v>Raw</v>
       </c>
       <c r="N28" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read limit_amt per counterparty.
+        <v xml:space="preserve">1. LOAD  l1.limit_rule  (lr)
+   WHERE lr.is_current_flag = 'Y'
+   AND   lr.counterparty_id IS NOT NULL
+2. GROUP BY lr.counterparty_id
+3. COMPUTE
+   metric_value = SUM(limit_amount_usd)
 </v>
       </c>
       <c r="O28" t="str">
@@ -3017,10 +3128,18 @@
         <v>Y</v>
       </c>
       <c r="Q28" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="R28" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level limit_amt per L3 desk segment.
+        <v xml:space="preserve">1. LOAD  l1.limit_rule  (lr)
+   WHERE lr.is_current_flag = 'Y'
+   AND   lr.lob_segment_id IS NOT NULL
+2. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt)
+   ON    ebt.managed_segment_id = lr.lob_segment_id
+   AND   ebt.is_current_flag = 'Y'
+3. GROUP BY lr.lob_segment_id
+4. COMPUTE
+   metric_value = SUM(limit_amount_usd)
 </v>
       </c>
       <c r="S28" t="str">
@@ -3030,10 +3149,18 @@
         <v>Y</v>
       </c>
       <c r="U28" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="V28" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level limit_amt per L2 portfolio segment.
+        <v xml:space="preserve">1. LOAD  l1.limit_rule  (lr)
+   WHERE lr.is_current_flag = 'Y'
+   AND   lr.lob_segment_id IS NOT NULL
+2. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt)
+   ON    ebt.managed_segment_id = lr.lob_segment_id
+   AND   ebt.is_current_flag = 'Y'
+3. GROUP BY lr.lob_segment_id
+4. COMPUTE
+   metric_value = SUM(limit_amount_usd)
 </v>
       </c>
       <c r="W28" t="str">
@@ -3043,10 +3170,18 @@
         <v>Y</v>
       </c>
       <c r="Y28" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="Z28" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level limit_amt per L1 business segment segment.
+        <v xml:space="preserve">1. LOAD  l1.limit_rule  (lr)
+   WHERE lr.is_current_flag = 'Y'
+   AND   lr.lob_segment_id IS NOT NULL
+2. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt)
+   ON    ebt.managed_segment_id = lr.lob_segment_id
+   AND   ebt.is_current_flag = 'Y'
+3. GROUP BY lr.lob_segment_id
+4. COMPUTE
+   metric_value = SUM(limit_amount_usd)
 </v>
       </c>
       <c r="AA28" t="str">
@@ -3061,14 +3196,25 @@
         <v>EXP-020</v>
       </c>
       <c r="B29" t="str" xml:space="preserve">
-        <v xml:space="preserve">The estimated exposure amount (in USD) expected to be outstanding if the borrower defaults.
+        <v xml:space="preserve">Estimated exposure amount outstanding if the borrower defaults, computed from L2 atomic inputs per Basel III: EAD = OB + CCF × Undrawn, where OB = drawn/funded amount, CCF = credit conversion factor from facility_risk_snapshot, and Undrawn = committed minus drawn from facility_exposure_snapshot. Bank-share adjusted via facility_exposure_snapshot. At counterparty level, weighted by participation_pct from facility_counterparty_participation per FR Y-14Q requirements.
 </v>
       </c>
       <c r="C29" t="str">
         <v>Exposure at Default ($)</v>
       </c>
       <c r="D29" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read exposure_at_default from credit_event_facility_link for each facility as-of reporting date.
+        <v xml:space="preserve">1. LOAD  l2.facility_exposure_snapshot  (fes)
+   WHERE fes.as_of_date = :as_of_date
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = fes.facility_id
+   WHERE fm.is_active_flag = 'Y'
+3. LEFT JOIN  l2.facility_risk_snapshot  (frs)
+   ON    frs.facility_id = fes.facility_id
+   AND   frs.as_of_date = fes.as_of_date
+4. GROUP BY fes.facility_id
+5. COMPUTE
+   metric_value = (drawn_amount + CCF * undrawn_amount)
+                  * bank_share_pct / 100
 </v>
       </c>
       <c r="E29" t="str">
@@ -3084,10 +3230,21 @@
         <v>Y</v>
       </c>
       <c r="I29" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="J29" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read exposure_at_default from credit_event_facility_link for each facility as-of reporting date.
+        <v xml:space="preserve">1. LOAD  l2.facility_exposure_snapshot  (fes)
+   WHERE fes.as_of_date = :as_of_date
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = fes.facility_id
+   WHERE fm.is_active_flag = 'Y'
+3. LEFT JOIN  l2.facility_risk_snapshot  (frs)
+   ON    frs.facility_id = fes.facility_id
+   AND   frs.as_of_date = fes.as_of_date
+4. GROUP BY fes.facility_id
+5. COMPUTE
+   metric_value = (drawn_amount + CCF * undrawn_amount)
+                  * bank_share_pct / 100
 </v>
       </c>
       <c r="K29" t="str">
@@ -3097,10 +3254,22 @@
         <v>Y</v>
       </c>
       <c r="M29" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N29" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level exposure_at_default per counterparty.
+        <v xml:space="preserve">1. LOAD  l2.facility_exposure_snapshot  (fes)
+   WHERE fes.as_of_date = :as_of_date
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = fes.facility_id
+3. LEFT JOIN  l2.facility_risk_snapshot  (frs)
+   ON    frs.facility_id = fes.facility_id
+4. JOIN  l2.facility_counterparty_participation  (fcp)
+   ON    fcp.facility_id = fes.facility_id
+   AND   fcp.is_current_flag = 'Y'
+5. GROUP BY fcp.counterparty_id
+6. COMPUTE
+   metric_value = SUM((drawn + CCF * undrawn) * bank_share / 100
+                  * participation_pct)
 </v>
       </c>
       <c r="O29" t="str">
@@ -3113,7 +3282,15 @@
         <v>Agg</v>
       </c>
       <c r="R29" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level exposure_at_default per L3 desk segment.
+        <v xml:space="preserve">1. LOAD  facility-level EAD (subquery)
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = fac.facility_id
+3. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt)
+   ON    ebt.managed_segment_id = fm.lob_segment_id
+   AND   ebt.is_current_flag = 'Y'
+4. GROUP BY ebt.managed_segment_id
+5. COMPUTE
+   metric_value = SUM(facility_ead)
 </v>
       </c>
       <c r="S29" t="str">
@@ -3126,7 +3303,13 @@
         <v>Agg</v>
       </c>
       <c r="V29" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level exposure_at_default per L2 portfolio segment.
+        <v xml:space="preserve">1. LOAD  facility-level EAD (subquery)
+2. JOIN  l2.facility_master  (fm)
+3. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l3, ebt_l2)
+   Traverse L3 -&gt; L2 via parent_segment_id
+4. GROUP BY ebt_l2.managed_segment_id
+5. COMPUTE
+   metric_value = SUM(facility_ead)
 </v>
       </c>
       <c r="W29" t="str">
@@ -3139,7 +3322,13 @@
         <v>Agg</v>
       </c>
       <c r="Z29" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level exposure_at_default per L1 business segment segment.
+        <v xml:space="preserve">1. LOAD  facility-level EAD (subquery)
+2. JOIN  l2.facility_master  (fm)
+3. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l3, ebt_l2, ebt_l1)
+   Traverse L3 -&gt; L2 -&gt; L1 via parent_segment_id chain
+4. GROUP BY ebt_l1.managed_segment_id
+5. COMPUTE
+   metric_value = SUM(facility_ead)
 </v>
       </c>
       <c r="AA29" t="str">
@@ -3154,14 +3343,14 @@
         <v>EXP-021</v>
       </c>
       <c r="B30" t="str" xml:space="preserve">
-        <v xml:space="preserve">Derived categorical classification (Sufficient, Approaching, Fully Utilized) of utilization level based on current drawn exposure relative to committed amount. Operational KPI providing early warning insight into limit pressure, liquidity usage, and potential capacity constraints.
+        <v xml:space="preserve">Derived categorical classification of utilization level based on current drawn exposure relative to committed amount. Maps facility utilization percentage against l1.utilization_status_dim threshold ranges to return status labels (e.g., Sufficient, Approaching, Fully Utilized). Operational KPI providing early warning insight into limit pressure, liquidity usage, and potential capacity constraints.
 </v>
       </c>
       <c r="C30" t="str">
-        <v>Facility Utilization Status (e.g., Sufficient, Approaching, Fully Utilized)</v>
+        <v>Utilization Status (Utilized Exposure to Committed Exposure)</v>
       </c>
       <c r="D30" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated utilization_status_code per facility.
+        <v xml:space="preserve">For each facility, compute utilization_pct from L2 atomic data (drawn_amount / committed_amount * 100), then match against l1.utilization_status_dim threshold ranges (utilization_min_pct &lt;= pct &lt; utilization_max_pct) to return status_name.
 </v>
       </c>
       <c r="E30" t="str">
@@ -3180,63 +3369,63 @@
         <v>Calc</v>
       </c>
       <c r="J30" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated utilization_status_code per facility.
+        <v xml:space="preserve">For each facility, compute utilization_pct from L2 atomic data (drawn_amount / committed_amount * 100), then match against l1.utilization_status_dim threshold ranges (utilization_min_pct &lt;= pct &lt; utilization_max_pct) to return status_name.
 </v>
       </c>
       <c r="K30" t="str">
-        <v>Facility Utilization Status (e.g., Sufficient, Approaching, Fully Utilized) (facility)</v>
+        <v>Utilization Status (Utilized Exposure to Committed Exposure) (facility)</v>
       </c>
       <c r="L30" t="str">
         <v>Y</v>
       </c>
       <c r="M30" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N30" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level utilization_status_code) per counterparty.
+        <v xml:space="preserve">Compute counterparty-level utilization pct via sum-ratio with FX conversion: SUM(drawn * fx) / SUM(committed * fx) * 100. Then look up status from utilization_status_dim threshold ranges.
 </v>
       </c>
       <c r="O30" t="str">
-        <v>Facility Utilization Status (e.g., Sufficient, Approaching, Fully Utilized) (counterparty)</v>
+        <v>Utilization Status (Utilized Exposure to Committed Exposure) (counterparty)</v>
       </c>
       <c r="P30" t="str">
         <v>Y</v>
       </c>
       <c r="Q30" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R30" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level utilization_status_code per L3 desk segment.
+        <v xml:space="preserve">Compute L3 desk-level utilization pct via sum-ratio with FX conversion, then look up status from utilization_status_dim threshold ranges.
 </v>
       </c>
       <c r="S30" t="str">
-        <v>Facility Utilization Status (e.g., Sufficient, Approaching, Fully Utilized) (desk)</v>
+        <v>Utilization Status (Utilized Exposure to Committed Exposure) (desk)</v>
       </c>
       <c r="T30" t="str">
         <v>Y</v>
       </c>
       <c r="U30" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V30" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level utilization_status_code per L2 portfolio segment.
+        <v xml:space="preserve">Compute L2 portfolio-level utilization pct via sum-ratio with FX conversion (one-hop EBT hierarchy), then look up status from utilization_status_dim threshold ranges.
 </v>
       </c>
       <c r="W30" t="str">
-        <v>Facility Utilization Status (e.g., Sufficient, Approaching, Fully Utilized) (portfolio)</v>
+        <v>Utilization Status (Utilized Exposure to Committed Exposure) (portfolio)</v>
       </c>
       <c r="X30" t="str">
         <v>Y</v>
       </c>
       <c r="Y30" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z30" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level utilization_status_code per L1 business segment segment.
+        <v xml:space="preserve">Compute L1 business segment-level utilization pct via sum-ratio with FX conversion (two-hop EBT hierarchy), then look up status from utilization_status_dim threshold ranges.
 </v>
       </c>
       <c r="AA30" t="str">
-        <v>Facility Utilization Status (e.g., Sufficient, Approaching, Fully Utilized) (business_segment)</v>
+        <v>Utilization Status (Utilized Exposure to Committed Exposure) (business_segment)</v>
       </c>
       <c r="AB30" t="str">
         <v/>
@@ -3340,14 +3529,14 @@
         <v>EXP-023</v>
       </c>
       <c r="B32" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure × LGD expressed in dollar terms weighted based on facility-level exposure. Derived loss severity metric estimating expected recovery-adjusted loss magnitude.
+        <v xml:space="preserve">Expected dollar loss given default. Computed as EAD (drawn amount, bank share) multiplied by LGD percentage from facility risk snapshot. Expressed in local currency at facility level and FX-converted to USD at aggregate levels. Quantifies loss severity per facility and across rollup hierarchy.
 </v>
       </c>
       <c r="C32" t="str">
         <v>Loss Given Default ($)</v>
       </c>
       <c r="D32" t="str" xml:space="preserve">
-        <v xml:space="preserve">EAD * LGD (in Percentage) for all facilities across Counterparties
+        <v xml:space="preserve">EAD (bank share) x LGD% per facility in local currency.
 </v>
       </c>
       <c r="E32" t="str">
@@ -3366,7 +3555,7 @@
         <v>Calc</v>
       </c>
       <c r="J32" t="str" xml:space="preserve">
-        <v xml:space="preserve">EAD * LGD (in Percentage) for all facilities across Counterparties
+        <v xml:space="preserve">EAD (bank share) x LGD% per facility in local currency.
 </v>
       </c>
       <c r="K32" t="str">
@@ -3379,7 +3568,7 @@
         <v>Agg</v>
       </c>
       <c r="N32" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level lgd_estimate per counterparty.
+        <v xml:space="preserve">SUM of facility-level LGD$ per counterparty, FX-converted to USD.
 </v>
       </c>
       <c r="O32" t="str">
@@ -3392,7 +3581,7 @@
         <v>Agg</v>
       </c>
       <c r="R32" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level lgd_estimate per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level LGD$ per L3 desk segment, FX-converted to USD.
 </v>
       </c>
       <c r="S32" t="str">
@@ -3405,7 +3594,7 @@
         <v>Agg</v>
       </c>
       <c r="V32" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level lgd_estimate per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level LGD$ per L2 portfolio segment, FX-converted to USD.
 </v>
       </c>
       <c r="W32" t="str">
@@ -3418,7 +3607,7 @@
         <v>Agg</v>
       </c>
       <c r="Z32" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level lgd_estimate per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level LGD$ per L1 business segment, FX-converted to USD.
 </v>
       </c>
       <c r="AA32" t="str">
@@ -3433,14 +3622,14 @@
         <v>EXP-024</v>
       </c>
       <c r="B33" t="str" xml:space="preserve">
-        <v xml:space="preserve">Status of credit limit (Active, Warning, Breach). Used to monitor risk appetite breaches and exposure governance compliance.
+        <v xml:space="preserve">Utilization-based limit compliance status. At facility level reads the pre-computed limit_status_code. At aggregate levels computes drawn-to- committed utilization percentage (FX-converted to USD) and maps to a status code via utilization_status_dim thresholds. Used for credit limit monitoring and risk appetite breach detection.
 </v>
       </c>
       <c r="C33" t="str">
         <v>Limit Status</v>
       </c>
       <c r="D33" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated limit_status_code per facility.
+        <v xml:space="preserve">Read pre-computed limit_status_code from facility_exposure_snapshot.
 </v>
       </c>
       <c r="E33" t="str">
@@ -3456,10 +3645,10 @@
         <v>Y</v>
       </c>
       <c r="I33" t="str">
-        <v>Calc</v>
+        <v>Raw</v>
       </c>
       <c r="J33" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated limit_status_code per facility.
+        <v xml:space="preserve">Read pre-computed limit_status_code from facility_exposure_snapshot.
 </v>
       </c>
       <c r="K33" t="str">
@@ -3469,10 +3658,10 @@
         <v>Y</v>
       </c>
       <c r="M33" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N33" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level limit_status_code per counterparty.
+        <v xml:space="preserve">Compute drawn-to-committed utilization % per counterparty (FX-converted), then map to status via utilization_status_dim thresholds.
 </v>
       </c>
       <c r="O33" t="str">
@@ -3482,10 +3671,10 @@
         <v>Y</v>
       </c>
       <c r="Q33" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R33" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level limit_status_code per L3 desk segment.
+        <v xml:space="preserve">Compute drawn-to-committed utilization % per L3 desk segment (FX-converted), then map to status via utilization_status_dim.
 </v>
       </c>
       <c r="S33" t="str">
@@ -3495,10 +3684,10 @@
         <v>Y</v>
       </c>
       <c r="U33" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V33" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level limit_status_code per L2 portfolio segment.
+        <v xml:space="preserve">Compute drawn-to-committed utilization % per L2 portfolio segment (FX-converted), then map to status via utilization_status_dim.
 </v>
       </c>
       <c r="W33" t="str">
@@ -3508,10 +3697,10 @@
         <v>Y</v>
       </c>
       <c r="Y33" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z33" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level limit_status_code per L1 business segment segment.
+        <v xml:space="preserve">Compute drawn-to-committed utilization % per L1 business segment (FX-converted), then map to status via utilization_status_dim.
 </v>
       </c>
       <c r="AA33" t="str">
@@ -3526,14 +3715,14 @@
         <v>EXP-025</v>
       </c>
       <c r="B34" t="str" xml:space="preserve">
-        <v xml:space="preserve">The average expected loss rate (percent of exposure) if default occurs, weighted across exposures (typically by EAD).
+        <v xml:space="preserve">Exposure-weighted average Loss Given Default rate expressed as a decimal fraction (e.g. 0.45 = 45%). At facility level, reads lgd_pct directly from facility_risk_snapshot. At aggregate levels, computes the commitment-adjusted weighted average: SUM(lgd_pct * outstanding_balance_amt) / SUM(committed_amount), with FX conversion for cross-currency portfolios. LGD represents the expected severity of loss if the obligor defaults, a key input to Expected Loss (EL = PD x LGD x EAD) under Basel III IRB.
 </v>
       </c>
       <c r="C34" t="str">
         <v>Loss Given Default (%)</v>
       </c>
       <c r="D34" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated lgd_pct per facility.
+        <v xml:space="preserve">Direct lookup of lgd_pct per facility from facility_risk_snapshot. No aggregation needed — facility-level LGD is a sourced atomic value.
 </v>
       </c>
       <c r="E34" t="str">
@@ -3549,10 +3738,10 @@
         <v>Y</v>
       </c>
       <c r="I34" t="str">
-        <v>Calc</v>
+        <v>Raw</v>
       </c>
       <c r="J34" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated lgd_pct per facility.
+        <v xml:space="preserve">Direct lookup of lgd_pct per facility from facility_risk_snapshot. No aggregation needed — facility-level LGD is a sourced atomic value.
 </v>
       </c>
       <c r="K34" t="str">
@@ -3565,7 +3754,7 @@
         <v>Avg</v>
       </c>
       <c r="N34" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of lgd_pct across counterparty facilities.
+        <v xml:space="preserve">Commitment-adjusted exposure-weighted LGD per counterparty: SUM(lgd_pct * outstanding_balance_amt * fx_rate) / NULLIF(SUM(committed_amount * fx_rate), 0). FX conversion ensures proper weighting across multi-currency facilities.
 </v>
       </c>
       <c r="O34" t="str">
@@ -3575,10 +3764,10 @@
         <v>Y</v>
       </c>
       <c r="Q34" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="R34" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level lgd_pct per L3 desk segment.
+        <v xml:space="preserve">Commitment-adjusted exposure-weighted LGD per L3 desk segment: SUM(lgd_pct * outstanding_balance_amt * fx_rate) / NULLIF(SUM(committed_amount * fx_rate), 0). Standard EBT hierarchy direct join for desk grouping.
 </v>
       </c>
       <c r="S34" t="str">
@@ -3588,10 +3777,10 @@
         <v>Y</v>
       </c>
       <c r="U34" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="V34" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level lgd_pct per L2 portfolio segment.
+        <v xml:space="preserve">Commitment-adjusted exposure-weighted LGD per L2 portfolio segment: SUM(lgd_pct * outstanding_balance_amt * fx_rate) / NULLIF(SUM(committed_amount * fx_rate), 0). One-hop EBT traversal for portfolio grouping.
 </v>
       </c>
       <c r="W34" t="str">
@@ -3601,10 +3790,10 @@
         <v>Y</v>
       </c>
       <c r="Y34" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="Z34" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level lgd_pct per L1 business segment segment.
+        <v xml:space="preserve">Commitment-adjusted exposure-weighted LGD per L1 business segment: SUM(lgd_pct * outstanding_balance_amt * fx_rate) / NULLIF(SUM(committed_amount * fx_rate), 0). Two-hop EBT traversal for business segment grouping.
 </v>
       </c>
       <c r="AA34" t="str">
@@ -3616,17 +3805,17 @@
     </row>
     <row r="35" xml:space="preserve">
       <c r="A35" t="str">
-        <v>EXP-026</v>
+        <v>EXP-027</v>
       </c>
       <c r="B35" t="str" xml:space="preserve">
-        <v xml:space="preserve">Loan to Value Ratio (%) metric.
+        <v xml:space="preserve">Net income computed from L2 atomic inputs: NOI (Net Operating Income, which equals Revenue minus Operating Expense) minus Interest Expense minus Expected Loss (PD × LGD × Committed Amount). Indicator of facility-level profitability.
 </v>
       </c>
       <c r="C35" t="str">
-        <v>Loan to Value Ratio (%)</v>
+        <v>Net Income ($)</v>
       </c>
       <c r="D35" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each DISTINCT (Facility_ID) lookup Collateral ID and SUM(Current_Colalteral_MV) THEN  [Commited_Facility_Amt] / [Current_Collateral_MV] × 100
+        <v xml:space="preserve">Net Income = NOI (Revenue - OpEx) - Interest Expense - Expected Loss (PD × LGD × Committed Amount). All sourced from L2 atomic tables.
 </v>
       </c>
       <c r="E35" t="str">
@@ -3645,11 +3834,11 @@
         <v>Calc</v>
       </c>
       <c r="J35" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each DISTINCT (Facility_ID) lookup Collateral ID and SUM(Current_Colalteral_MV) THEN  [Commited_Facility_Amt] / [Current_Collateral_MV] × 100
+        <v xml:space="preserve">Net Income = NOI (Revenue - OpEx) - Interest Expense - Expected Loss (PD × LGD × Committed Amount). All sourced from L2 atomic tables.
 </v>
       </c>
       <c r="K35" t="str">
-        <v>Loan to Value Ratio (%) (facility)</v>
+        <v>Net Income ($) (facility)</v>
       </c>
       <c r="L35" t="str">
         <v>Y</v>
@@ -3658,11 +3847,11 @@
         <v>Agg</v>
       </c>
       <c r="N35" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level ltv_pct per counterparty.
+        <v xml:space="preserve">SUM of facility-level net income per counterparty, FX-converted to USD.
 </v>
       </c>
       <c r="O35" t="str">
-        <v>Loan to Value Ratio (%) (counterparty)</v>
+        <v>Net Income ($) (counterparty)</v>
       </c>
       <c r="P35" t="str">
         <v>Y</v>
@@ -3671,11 +3860,11 @@
         <v>Agg</v>
       </c>
       <c r="R35" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level ltv_pct per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level net income per L3 desk segment, FX-converted to USD.
 </v>
       </c>
       <c r="S35" t="str">
-        <v>Loan to Value Ratio (%) (desk)</v>
+        <v>Net Income ($) (desk)</v>
       </c>
       <c r="T35" t="str">
         <v>Y</v>
@@ -3684,11 +3873,11 @@
         <v>Agg</v>
       </c>
       <c r="V35" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level ltv_pct per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level net income per L2 portfolio segment, FX-converted to USD.
 </v>
       </c>
       <c r="W35" t="str">
-        <v>Loan to Value Ratio (%) (portfolio)</v>
+        <v>Net Income ($) (portfolio)</v>
       </c>
       <c r="X35" t="str">
         <v>Y</v>
@@ -3697,11 +3886,11 @@
         <v>Agg</v>
       </c>
       <c r="Z35" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level ltv_pct per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level net income per L1 business segment, FX-converted to USD.
 </v>
       </c>
       <c r="AA35" t="str">
-        <v>Loan to Value Ratio (%) (business_segment)</v>
+        <v>Net Income ($) (business_segment)</v>
       </c>
       <c r="AB35" t="str">
         <v/>
@@ -3709,17 +3898,17 @@
     </row>
     <row r="36" xml:space="preserve">
       <c r="A36" t="str">
-        <v>EXP-027</v>
+        <v>EXP-028</v>
       </c>
       <c r="B36" t="str" xml:space="preserve">
-        <v xml:space="preserve">Profit after all expenses in USD. Indicator of borrower profitability and financial sustainability.
+        <v xml:space="preserve">Net Interest Income divided by Average Earning Assets. Core banking profitability measure assessing pricing effectiveness and lending margin. Sourced from L2 facility_profitability_snapshot atomic data.
 </v>
       </c>
       <c r="C36" t="str">
-        <v>Net Income ($)</v>
+        <v>Net Interest Margin (%)</v>
       </c>
       <c r="D36" t="str" xml:space="preserve">
-        <v xml:space="preserve">Revenue – Interest Expense – Operating Cost – EL
+        <v xml:space="preserve">(Interest Income - Interest Expense) / Average Earning Assets * 100.
 </v>
       </c>
       <c r="E36" t="str">
@@ -3738,63 +3927,63 @@
         <v>Calc</v>
       </c>
       <c r="J36" t="str" xml:space="preserve">
-        <v xml:space="preserve">Revenue – Interest Expense – Operating Cost – EL
+        <v xml:space="preserve">(Interest Income - Interest Expense) / Average Earning Assets * 100.
 </v>
       </c>
       <c r="K36" t="str">
-        <v>Net Income ($) (facility)</v>
+        <v>Net Interest Margin (%) (facility)</v>
       </c>
       <c r="L36" t="str">
         <v>Y</v>
       </c>
       <c r="M36" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N36" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level net_income_amt per counterparty.
+        <v xml:space="preserve">SUM(Net Interest Income) / SUM(Avg Earning Assets) * 100 per counterparty. Sum-ratio rollup preserves mathematical consistency.
 </v>
       </c>
       <c r="O36" t="str">
-        <v>Net Income ($) (counterparty)</v>
+        <v>Net Interest Margin (%) (counterparty)</v>
       </c>
       <c r="P36" t="str">
         <v>Y</v>
       </c>
       <c r="Q36" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R36" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level net_income_amt per L3 desk segment.
+        <v xml:space="preserve">SUM(Net Interest Income) / SUM(Avg Earning Assets) * 100 per L3 desk segment.
 </v>
       </c>
       <c r="S36" t="str">
-        <v>Net Income ($) (desk)</v>
+        <v>Net Interest Margin (%) (desk)</v>
       </c>
       <c r="T36" t="str">
         <v>Y</v>
       </c>
       <c r="U36" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V36" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level net_income_amt per L2 portfolio segment.
+        <v xml:space="preserve">SUM(Net Interest Income) / SUM(Avg Earning Assets) * 100 per L2 portfolio segment.
 </v>
       </c>
       <c r="W36" t="str">
-        <v>Net Income ($) (portfolio)</v>
+        <v>Net Interest Margin (%) (portfolio)</v>
       </c>
       <c r="X36" t="str">
         <v>Y</v>
       </c>
       <c r="Y36" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z36" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level net_income_amt per L1 business segment segment.
+        <v xml:space="preserve">SUM(Net Interest Income) / SUM(Avg Earning Assets) * 100 per L1 business segment.
 </v>
       </c>
       <c r="AA36" t="str">
-        <v>Net Income ($) (business_segment)</v>
+        <v>Net Interest Margin (%) (business_segment)</v>
       </c>
       <c r="AB36" t="str">
         <v/>
@@ -3802,17 +3991,17 @@
     </row>
     <row r="37" xml:space="preserve">
       <c r="A37" t="str">
-        <v>EXP-028</v>
+        <v>EXP-029</v>
       </c>
       <c r="B37" t="str" xml:space="preserve">
-        <v xml:space="preserve">Net Interest Income divided by earning assets. Calculated margin KPI assessing pricing effectiveness and lending profitability.
+        <v xml:space="preserve">Allocated operating or servicing cost associated with each facility. Direct-sum rollup at all aggregate levels with FX conversion to USD.
 </v>
       </c>
       <c r="C37" t="str">
-        <v>Net Interest Margin (%)</v>
+        <v>Operating Cost ($)</v>
       </c>
       <c r="D37" t="str" xml:space="preserve">
-        <v xml:space="preserve">(Interest Income - Interst Expense)/Average Earning Assets
+        <v xml:space="preserve">Read operating_expense_amt from facility_financial_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="E37" t="str">
@@ -3828,66 +4017,66 @@
         <v>Y</v>
       </c>
       <c r="I37" t="str">
-        <v>Calc</v>
+        <v>Raw</v>
       </c>
       <c r="J37" t="str" xml:space="preserve">
-        <v xml:space="preserve">(Interest Income - Interst Expense)/Average Earning Assets
+        <v xml:space="preserve">Read operating_expense_amt from facility_financial_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="K37" t="str">
-        <v>Net Interest Margin (%) (facility)</v>
+        <v>Operating Cost ($) (facility)</v>
       </c>
       <c r="L37" t="str">
         <v>Y</v>
       </c>
       <c r="M37" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="N37" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(net_interest_income) / SUM(avg_earning_assets) * 100.0 per counterparty.
+        <v xml:space="preserve">SUM of facility-level operating_expense_amt per counterparty, FX-converted to USD.
 </v>
       </c>
       <c r="O37" t="str">
-        <v>Net Interest Margin (%) (counterparty)</v>
+        <v>Operating Cost ($) (counterparty)</v>
       </c>
       <c r="P37" t="str">
         <v>Y</v>
       </c>
       <c r="Q37" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="R37" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(net_interest_income) / SUM(avg_earning_assets) * 100.0 per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level operating_expense_amt per L3 desk segment, FX-converted to USD.
 </v>
       </c>
       <c r="S37" t="str">
-        <v>Net Interest Margin (%) (desk)</v>
+        <v>Operating Cost ($) (desk)</v>
       </c>
       <c r="T37" t="str">
         <v>Y</v>
       </c>
       <c r="U37" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="V37" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(net_interest_income) / SUM(avg_earning_assets) * 100.0 per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level operating_expense_amt per L2 portfolio segment, FX-converted to USD.
 </v>
       </c>
       <c r="W37" t="str">
-        <v>Net Interest Margin (%) (portfolio)</v>
+        <v>Operating Cost ($) (portfolio)</v>
       </c>
       <c r="X37" t="str">
         <v>Y</v>
       </c>
       <c r="Y37" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="Z37" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(net_interest_income) / SUM(avg_earning_assets) * 100.0 per L1 business segment.
+        <v xml:space="preserve">SUM of facility-level operating_expense_amt per L1 business segment, FX-converted to USD.
 </v>
       </c>
       <c r="AA37" t="str">
-        <v>Net Interest Margin (%) (business_segment)</v>
+        <v>Operating Cost ($) (business_segment)</v>
       </c>
       <c r="AB37" t="str">
         <v/>
@@ -3895,17 +4084,18 @@
     </row>
     <row r="38" xml:space="preserve">
       <c r="A38" t="str">
-        <v>EXP-029</v>
+        <v>EXP-030</v>
       </c>
       <c r="B38" t="str" xml:space="preserve">
-        <v xml:space="preserve">Allocated operating or servicing cost associated with exposure.
+        <v xml:space="preserve">Model-estimated probability of default (PD) within the defined rating horizon. At facility level, sources the raw pd_pct from L2 facility_risk_snapshot. At aggregate levels, computes the exposure- weighted average: SUM(pd_pct × committed_amount) / SUM(committed_amount). This weighted-avg rollup avoids Simpson's paradox — never averages pre-computed PD rates. Core credit risk input supporting IRB capital modeling, expected loss estimation (EL = PD × LGD × EAD), stress testing, and risk appetite alignment.
 </v>
       </c>
       <c r="C38" t="str">
-        <v>Operating Cost ($)</v>
+        <v>Probability of Default (%)</v>
       </c>
       <c r="D38" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read operating_expense_amt from facility_financial_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Direct lookup of pd_pct from facility_risk_snapshot for each facility.
+Ingredients: pd_pct (L2 facility_risk_snapshot — raw model output)
 </v>
       </c>
       <c r="E38" t="str">
@@ -3924,37 +4114,47 @@
         <v>Raw</v>
       </c>
       <c r="J38" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read operating_expense_amt from facility_financial_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Direct lookup of pd_pct from facility_risk_snapshot for each facility.
+Ingredients: pd_pct (L2 facility_risk_snapshot — raw model output)
 </v>
       </c>
       <c r="K38" t="str">
-        <v>Operating Cost ($) (facility)</v>
+        <v>Probability of Default (%) (facility)</v>
       </c>
       <c r="L38" t="str">
         <v>Y</v>
       </c>
       <c r="M38" t="str">
-        <v>Raw</v>
+        <v>Avg</v>
       </c>
       <c r="N38" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read operating_expense_amt per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD pd_pct and committed_amount per facility
+  2. COMPUTE exposure-weighted average PD:
+     SUM(pd_pct × committed_amount) / SUM(committed_amount)
+Weighted-avg rollup ensures large-exposure facilities dominate the
+counterparty-level PD, avoiding equal-weight averaging bias.
 </v>
       </c>
       <c r="O38" t="str">
-        <v>Operating Cost ($) (counterparty)</v>
+        <v>Probability of Default (%) (counterparty)</v>
       </c>
       <c r="P38" t="str">
         <v>Y</v>
       </c>
       <c r="Q38" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="R38" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level operating_expense_amt per L3 desk segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOAD pd_pct and committed_amount per facility
+  2. JOIN l1.enterprise_business_taxonomy on lob_segment_id
+  3. COMPUTE SUM(pd_pct × committed_amount) / SUM(committed_amount)
+Weighted-avg rollup per desk.
 </v>
       </c>
       <c r="S38" t="str">
-        <v>Operating Cost ($) (desk)</v>
+        <v>Probability of Default (%) (desk)</v>
       </c>
       <c r="T38" t="str">
         <v>Y</v>
@@ -3963,11 +4163,15 @@
         <v>Avg</v>
       </c>
       <c r="V38" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level operating_expense_amt per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. COMPUTE SUM(pd_pct × committed_amount) / SUM(committed_amount)
+Weighted-avg rollup per portfolio. Per spec:
+Σ(probability_of_default × Outstanding_Exposure) / Σ(Total Committed Amount)
 </v>
       </c>
       <c r="W38" t="str">
-        <v>Operating Cost ($) (portfolio)</v>
+        <v>Probability of Default (%) (portfolio)</v>
       </c>
       <c r="X38" t="str">
         <v>Y</v>
@@ -3976,11 +4180,14 @@
         <v>Avg</v>
       </c>
       <c r="Z38" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level operating_expense_amt per L1 business segment segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. COMPUTE SUM(pd_pct × committed_amount) / SUM(committed_amount)
+Weighted-avg rollup per business segment.
 </v>
       </c>
       <c r="AA38" t="str">
-        <v>Operating Cost ($) (business_segment)</v>
+        <v>Probability of Default (%) (business_segment)</v>
       </c>
       <c r="AB38" t="str">
         <v/>
@@ -3988,17 +4195,17 @@
     </row>
     <row r="39" xml:space="preserve">
       <c r="A39" t="str">
-        <v>EXP-030</v>
+        <v>EXP-031</v>
       </c>
       <c r="B39" t="str" xml:space="preserve">
-        <v xml:space="preserve">Model-estimated probability of default within defined horizon. Core credit risk input supporting capital modeling, expected loss estimation, stress testing, and risk appetite alignment.
+        <v xml:space="preserve">Total facility-level revenue computed as Interest Income + Fee Income, adjusted for bank share percentage. Sourced from L2 atomic data in facility_profitability_snapshot (interest_income_amt, fee_income_amt) with bank share from facility_lender_allocation. Assesses scale of lending activity and income generation capacity.
 </v>
       </c>
       <c r="C39" t="str">
-        <v>Probability of Default (%)</v>
+        <v>Revenue ($)</v>
       </c>
       <c r="D39" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read pd_pct from facility_risk_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">[Facility Revenue] = (interest_income_amt + fee_income_amt) × bank_share_pct / 100. USD-converted for consistent reporting.
 </v>
       </c>
       <c r="E39" t="str">
@@ -4014,14 +4221,14 @@
         <v>Y</v>
       </c>
       <c r="I39" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="J39" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read pd_pct from facility_risk_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">[Facility Revenue] = (interest_income_amt + fee_income_amt) × bank_share_pct / 100. USD-converted for consistent reporting.
 </v>
       </c>
       <c r="K39" t="str">
-        <v>Probability of Default (%) (facility)</v>
+        <v>Revenue ($) (facility)</v>
       </c>
       <c r="L39" t="str">
         <v>Y</v>
@@ -4030,37 +4237,37 @@
         <v>Agg</v>
       </c>
       <c r="N39" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pd_pct per counterparty.
+        <v xml:space="preserve">SUM of facility-level revenue (bank-share-adjusted, USD-converted) per counterparty.
 </v>
       </c>
       <c r="O39" t="str">
-        <v>Probability of Default (%) (counterparty)</v>
+        <v>Revenue ($) (counterparty)</v>
       </c>
       <c r="P39" t="str">
         <v>Y</v>
       </c>
       <c r="Q39" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="R39" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level pd_pct per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level revenue (bank-share-adjusted, USD-converted) per L3 desk segment.
 </v>
       </c>
       <c r="S39" t="str">
-        <v>Probability of Default (%) (desk)</v>
+        <v>Revenue ($) (desk)</v>
       </c>
       <c r="T39" t="str">
         <v>Y</v>
       </c>
       <c r="U39" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="V39" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level pd_pct per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level revenue (bank-share-adjusted, USD-converted) per L2 portfolio segment via EBT hierarchy (one hop up).
 </v>
       </c>
       <c r="W39" t="str">
-        <v>Probability of Default (%) (portfolio)</v>
+        <v>Revenue ($) (portfolio)</v>
       </c>
       <c r="X39" t="str">
         <v>Y</v>
@@ -4069,11 +4276,11 @@
         <v>Agg</v>
       </c>
       <c r="Z39" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pd_pct per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level revenue (bank-share-adjusted, USD-converted) per L1 business segment via EBT hierarchy (two hops up).
 </v>
       </c>
       <c r="AA39" t="str">
-        <v>Probability of Default (%) (business_segment)</v>
+        <v>Revenue ($) (business_segment)</v>
       </c>
       <c r="AB39" t="str">
         <v/>
@@ -4081,17 +4288,17 @@
     </row>
     <row r="40" xml:space="preserve">
       <c r="A40" t="str">
-        <v>EXP-031</v>
+        <v>EXP-032</v>
       </c>
       <c r="B40" t="str" xml:space="preserve">
-        <v xml:space="preserve">Total income generated by the borrower or attributed to the facility in millions USD. Used to assess scale and repayment capacity.
+        <v xml:space="preserve">Original appraised value of pledged collateral securing exposure, in USD. At facility level, sums original_valuation_usd from collateral_snapshot weighted by the bank's syndication share (bank_share_pct from facility_lender_allocation). Rolls up additively through counterparty, desk, portfolio, and business segment via the standard EBT hierarchy. Supports recovery analysis and secured lending assessment.
 </v>
       </c>
       <c r="C40" t="str">
-        <v>Revenue ($)</v>
+        <v>Collateral Market Value at Origination ($)</v>
       </c>
       <c r="D40" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(revenue_amt) per facility from facility_financial_snapshot. Weighted by bank share percentage.
+        <v xml:space="preserve">SUM(original_valuation_usd * bank_share_pct / 100) per facility. Bank share defaults to 100% if no lender allocation record.
 </v>
       </c>
       <c r="E40" t="str">
@@ -4110,11 +4317,11 @@
         <v>Agg</v>
       </c>
       <c r="J40" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(revenue_amt) per facility from facility_financial_snapshot. Weighted by bank share percentage.
+        <v xml:space="preserve">SUM(original_valuation_usd * bank_share_pct / 100) per facility. Bank share defaults to 100% if no lender allocation record.
 </v>
       </c>
       <c r="K40" t="str">
-        <v>Revenue ($) (facility)</v>
+        <v>Collateral Market Value at Origination ($) (facility)</v>
       </c>
       <c r="L40" t="str">
         <v>Y</v>
@@ -4123,11 +4330,11 @@
         <v>Agg</v>
       </c>
       <c r="N40" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level revenue_amt per counterparty.
+        <v xml:space="preserve">SUM of facility-level collateral origination value per counterparty.
 </v>
       </c>
       <c r="O40" t="str">
-        <v>Revenue ($) (counterparty)</v>
+        <v>Collateral Market Value at Origination ($) (counterparty)</v>
       </c>
       <c r="P40" t="str">
         <v>Y</v>
@@ -4136,11 +4343,11 @@
         <v>Agg</v>
       </c>
       <c r="R40" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level revenue_amt per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level collateral origination value per L3 desk segment.
 </v>
       </c>
       <c r="S40" t="str">
-        <v>Revenue ($) (desk)</v>
+        <v>Collateral Market Value at Origination ($) (desk)</v>
       </c>
       <c r="T40" t="str">
         <v>Y</v>
@@ -4149,11 +4356,11 @@
         <v>Agg</v>
       </c>
       <c r="V40" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level revenue_amt per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level collateral origination value per L2 portfolio segment.
 </v>
       </c>
       <c r="W40" t="str">
-        <v>Revenue ($) (portfolio)</v>
+        <v>Collateral Market Value at Origination ($) (portfolio)</v>
       </c>
       <c r="X40" t="str">
         <v>Y</v>
@@ -4162,11 +4369,11 @@
         <v>Agg</v>
       </c>
       <c r="Z40" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level revenue_amt per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level collateral origination value per L1 business segment.
 </v>
       </c>
       <c r="AA40" t="str">
-        <v>Revenue ($) (business_segment)</v>
+        <v>Collateral Market Value at Origination ($) (business_segment)</v>
       </c>
       <c r="AB40" t="str">
         <v/>
@@ -4174,17 +4381,17 @@
     </row>
     <row r="41" xml:space="preserve">
       <c r="A41" t="str">
-        <v>EXP-032</v>
+        <v>EXP-033</v>
       </c>
       <c r="B41" t="str" xml:space="preserve">
-        <v xml:space="preserve">Original Appriased Value of pledged collateral securing exposure in USD. Supports recovery analysis and secured lending assessment.
+        <v xml:space="preserve">Count of distinct risk mitigant sub-types protecting exposure at each rollup level. Joins through the risk_mitigant_link bridge table to risk_mitigant_master and the risk_mitigant_type_dim taxonomy. Measures mitigation diversification — higher counts indicate broader collateral coverage across different sub-type categories (e.g. Sovereign Guarantee, Bank Guarantee, Cash Collateral, Real Estate, Equipment).
 </v>
       </c>
       <c r="C41" t="str">
-        <v>Collateral Market Value at Origination ($)</v>
+        <v>Risk Mitigant Sub Type</v>
       </c>
       <c r="D41" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(original_valuation_usd) per facility from collateral_snapshot. Weighted by bank share percentage.
+        <v xml:space="preserve">COUNT DISTINCT risk_mitigant_subtype_code per facility via risk_mitigant_link -&gt; risk_mitigant_master -&gt; risk_mitigant_type_dim. Only active mitigants with current link status.
 </v>
       </c>
       <c r="E41" t="str">
@@ -4203,11 +4410,11 @@
         <v>Agg</v>
       </c>
       <c r="J41" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(original_valuation_usd) per facility from collateral_snapshot. Weighted by bank share percentage.
+        <v xml:space="preserve">COUNT DISTINCT risk_mitigant_subtype_code per facility via risk_mitigant_link -&gt; risk_mitigant_master -&gt; risk_mitigant_type_dim. Only active mitigants with current link status.
 </v>
       </c>
       <c r="K41" t="str">
-        <v>Collateral Market Value at Origination ($) (facility)</v>
+        <v>Risk Mitigant Sub Type (facility)</v>
       </c>
       <c r="L41" t="str">
         <v>Y</v>
@@ -4216,11 +4423,11 @@
         <v>Agg</v>
       </c>
       <c r="N41" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level original_valuation_usd per counterparty.
+        <v xml:space="preserve">COUNT DISTINCT risk_mitigant_subtype_code across all facilities per counterparty.
 </v>
       </c>
       <c r="O41" t="str">
-        <v>Collateral Market Value at Origination ($) (counterparty)</v>
+        <v>Risk Mitigant Sub Type (counterparty)</v>
       </c>
       <c r="P41" t="str">
         <v>Y</v>
@@ -4229,11 +4436,11 @@
         <v>Agg</v>
       </c>
       <c r="R41" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level original_valuation_usd per L3 desk segment.
+        <v xml:space="preserve">COUNT DISTINCT risk_mitigant_subtype_code across all facilities per L3 desk segment.
 </v>
       </c>
       <c r="S41" t="str">
-        <v>Collateral Market Value at Origination ($) (desk)</v>
+        <v>Risk Mitigant Sub Type (desk)</v>
       </c>
       <c r="T41" t="str">
         <v>Y</v>
@@ -4242,11 +4449,11 @@
         <v>Agg</v>
       </c>
       <c r="V41" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level original_valuation_usd per L2 portfolio segment.
+        <v xml:space="preserve">COUNT DISTINCT risk_mitigant_subtype_code across all facilities per L2 portfolio segment.
 </v>
       </c>
       <c r="W41" t="str">
-        <v>Collateral Market Value at Origination ($) (portfolio)</v>
+        <v>Risk Mitigant Sub Type (portfolio)</v>
       </c>
       <c r="X41" t="str">
         <v>Y</v>
@@ -4255,11 +4462,11 @@
         <v>Agg</v>
       </c>
       <c r="Z41" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level original_valuation_usd per L1 business segment segment.
+        <v xml:space="preserve">COUNT DISTINCT risk_mitigant_subtype_code across all facilities per L1 business segment.
 </v>
       </c>
       <c r="AA41" t="str">
-        <v>Collateral Market Value at Origination ($) (business_segment)</v>
+        <v>Risk Mitigant Sub Type (business_segment)</v>
       </c>
       <c r="AB41" t="str">
         <v/>
@@ -4267,17 +4474,17 @@
     </row>
     <row r="42" xml:space="preserve">
       <c r="A42" t="str">
-        <v>EXP-033</v>
+        <v>EXP-034</v>
       </c>
       <c r="B42" t="str" xml:space="preserve">
-        <v xml:space="preserve">Sub-classification of risk mitigant or collateral type tied to the facility. Used for granular risk segmentation.
+        <v xml:space="preserve">Count of distinct risk mitigant parent categories protecting exposure at each rollup level. Joins through the risk_mitigant_link bridge table to risk_mitigant_master and the risk_mitigant_type_dim taxonomy, reading the mitigant_category field (e.g. Cash, Real Estate, Guarantee, Insurance, Equipment). Provides a higher-level view of mitigation diversification compared to EXP-033 (sub-type detail). Supports recovery assessment and CRM eligibility analysis.
 </v>
       </c>
       <c r="C42" t="str">
-        <v>Risk Mitigant Sub Type</v>
+        <v>Risk Mitigant Type</v>
       </c>
       <c r="D42" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(risk_mitigant_subtype_code) per facility from risk_mitigant_type_dim.
+        <v xml:space="preserve">COUNT DISTINCT mitigant_category per facility via risk_mitigant_link -&gt; risk_mitigant_master -&gt; risk_mitigant_type_dim. Only active mitigants with current link status.
 </v>
       </c>
       <c r="E42" t="str">
@@ -4296,24 +4503,24 @@
         <v>Agg</v>
       </c>
       <c r="J42" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(risk_mitigant_subtype_code) per facility from risk_mitigant_type_dim.
+        <v xml:space="preserve">COUNT DISTINCT mitigant_category per facility via risk_mitigant_link -&gt; risk_mitigant_master -&gt; risk_mitigant_type_dim. Only active mitigants with current link status.
 </v>
       </c>
       <c r="K42" t="str">
-        <v>Risk Mitigant Sub Type (facility)</v>
+        <v>Risk Mitigant Type (facility)</v>
       </c>
       <c r="L42" t="str">
         <v>Y</v>
       </c>
       <c r="M42" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="N42" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_mitigant_subtype_code per counterparty.
+        <v xml:space="preserve">COUNT DISTINCT mitigant_category across all facilities per counterparty.
 </v>
       </c>
       <c r="O42" t="str">
-        <v>Risk Mitigant Sub Type (counterparty)</v>
+        <v>Risk Mitigant Type (counterparty)</v>
       </c>
       <c r="P42" t="str">
         <v>Y</v>
@@ -4322,11 +4529,11 @@
         <v>Agg</v>
       </c>
       <c r="R42" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_mitigant_subtype_code per L3 desk segment.
+        <v xml:space="preserve">COUNT DISTINCT mitigant_category across all facilities per L3 desk segment.
 </v>
       </c>
       <c r="S42" t="str">
-        <v>Risk Mitigant Sub Type (desk)</v>
+        <v>Risk Mitigant Type (desk)</v>
       </c>
       <c r="T42" t="str">
         <v>Y</v>
@@ -4335,11 +4542,11 @@
         <v>Agg</v>
       </c>
       <c r="V42" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_mitigant_subtype_code per L2 portfolio segment.
+        <v xml:space="preserve">COUNT DISTINCT mitigant_category across all facilities per L2 portfolio segment.
 </v>
       </c>
       <c r="W42" t="str">
-        <v>Risk Mitigant Sub Type (portfolio)</v>
+        <v>Risk Mitigant Type (portfolio)</v>
       </c>
       <c r="X42" t="str">
         <v>Y</v>
@@ -4348,11 +4555,11 @@
         <v>Agg</v>
       </c>
       <c r="Z42" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_mitigant_subtype_code per L1 business segment segment.
+        <v xml:space="preserve">COUNT DISTINCT mitigant_category across all facilities per L1 business segment.
 </v>
       </c>
       <c r="AA42" t="str">
-        <v>Risk Mitigant Sub Type (business_segment)</v>
+        <v>Risk Mitigant Type (business_segment)</v>
       </c>
       <c r="AB42" t="str">
         <v/>
@@ -4360,17 +4567,17 @@
     </row>
     <row r="43" xml:space="preserve">
       <c r="A43" t="str">
-        <v>EXP-034</v>
+        <v>EXP-035</v>
       </c>
       <c r="B43" t="str" xml:space="preserve">
-        <v xml:space="preserve">Parent group of risk mitigation or collateral asset type (e.g., cash, aviation, guarantee). Used to assess recovery support mechanisms.
+        <v xml:space="preserve">Net Income divided by Total Assets (at counterparty level) or Committed Exposure bank-share (at facility level). Measures asset utilization efficiency and overall financial performance.
 </v>
       </c>
       <c r="C43" t="str">
-        <v>Risk Mitigant Type</v>
+        <v>Return on Assets (%)</v>
       </c>
       <c r="D43" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(risk_mitigant_id) per facility from risk_mitigant_master.
+        <v xml:space="preserve">Facility Net Income / Committed Exposure (Bank Share portion only).
 </v>
       </c>
       <c r="E43" t="str">
@@ -4386,66 +4593,66 @@
         <v>Y</v>
       </c>
       <c r="I43" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="J43" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(risk_mitigant_id) per facility from risk_mitigant_master.
+        <v xml:space="preserve">Facility Net Income / Committed Exposure (Bank Share portion only).
 </v>
       </c>
       <c r="K43" t="str">
-        <v>Risk Mitigant Type (facility)</v>
+        <v>Return on Assets (%) (facility)</v>
       </c>
       <c r="L43" t="str">
         <v>Y</v>
       </c>
       <c r="M43" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="N43" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_mitigant_id per counterparty.
+        <v xml:space="preserve">Counterparty Net Income / Total Assets * 100. Net income computed from revenue minus expenses.
 </v>
       </c>
       <c r="O43" t="str">
-        <v>Risk Mitigant Type (counterparty)</v>
+        <v>Return on Assets (%) (counterparty)</v>
       </c>
       <c r="P43" t="str">
         <v>Y</v>
       </c>
       <c r="Q43" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="R43" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_mitigant_id per L3 desk segment.
+        <v xml:space="preserve">Exposure-weighted average ROA per L3 desk segment.
 </v>
       </c>
       <c r="S43" t="str">
-        <v>Risk Mitigant Type (desk)</v>
+        <v>Return on Assets (%) (desk)</v>
       </c>
       <c r="T43" t="str">
         <v>Y</v>
       </c>
       <c r="U43" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="V43" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_mitigant_id per L2 portfolio segment.
+        <v xml:space="preserve">Exposure-weighted average ROA per L2 portfolio segment.
 </v>
       </c>
       <c r="W43" t="str">
-        <v>Risk Mitigant Type (portfolio)</v>
+        <v>Return on Assets (%) (portfolio)</v>
       </c>
       <c r="X43" t="str">
         <v>Y</v>
       </c>
       <c r="Y43" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="Z43" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_mitigant_id per L1 business segment segment.
+        <v xml:space="preserve">Exposure-weighted average ROA per L1 business segment.
 </v>
       </c>
       <c r="AA43" t="str">
-        <v>Risk Mitigant Type (business_segment)</v>
+        <v>Return on Assets (%) (business_segment)</v>
       </c>
       <c r="AB43" t="str">
         <v/>
@@ -4453,14 +4660,14 @@
     </row>
     <row r="44" xml:space="preserve">
       <c r="A44" t="str">
-        <v>EXP-035</v>
+        <v>EXP-036</v>
       </c>
       <c r="B44" t="str" xml:space="preserve">
-        <v xml:space="preserve">Net Income divided by Total Assets (at counterparty level) or Committed Exposure bank-share (at facility level). Measures asset utilization efficiency and overall financial performance.
+        <v xml:space="preserve">Net Income divided by Shareholders Equity. Profitability KPI measuring return generated on shareholder capital. At facility level uses committed exposure (bank share) as denominator proxy.
 </v>
       </c>
       <c r="C44" t="str">
-        <v>Return on Assets (%)</v>
+        <v>Return on Equity (%)</v>
       </c>
       <c r="D44" t="str" xml:space="preserve">
         <v xml:space="preserve">Facility Net Income / Committed Exposure (Bank Share portion only).
@@ -4486,7 +4693,7 @@
 </v>
       </c>
       <c r="K44" t="str">
-        <v>Return on Assets (%) (facility)</v>
+        <v>Return on Equity (%) (facility)</v>
       </c>
       <c r="L44" t="str">
         <v>Y</v>
@@ -4495,11 +4702,11 @@
         <v>Calc</v>
       </c>
       <c r="N44" t="str" xml:space="preserve">
-        <v xml:space="preserve">Counterparty Net Income / Total Assets * 100. Net income computed from revenue minus expenses.
+        <v xml:space="preserve">Counterparty Net Income / Shareholders Equity * 100. Net income computed from revenue minus expenses.
 </v>
       </c>
       <c r="O44" t="str">
-        <v>Return on Assets (%) (counterparty)</v>
+        <v>Return on Equity (%) (counterparty)</v>
       </c>
       <c r="P44" t="str">
         <v>Y</v>
@@ -4508,11 +4715,11 @@
         <v>Avg</v>
       </c>
       <c r="R44" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average ROA per L3 desk segment.
+        <v xml:space="preserve">Exposure-weighted average ROE per L3 desk segment.
 </v>
       </c>
       <c r="S44" t="str">
-        <v>Return on Assets (%) (desk)</v>
+        <v>Return on Equity (%) (desk)</v>
       </c>
       <c r="T44" t="str">
         <v>Y</v>
@@ -4521,11 +4728,11 @@
         <v>Avg</v>
       </c>
       <c r="V44" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average ROA per L2 portfolio segment.
+        <v xml:space="preserve">Exposure-weighted average ROE per L2 portfolio segment.
 </v>
       </c>
       <c r="W44" t="str">
-        <v>Return on Assets (%) (portfolio)</v>
+        <v>Return on Equity (%) (portfolio)</v>
       </c>
       <c r="X44" t="str">
         <v>Y</v>
@@ -4534,11 +4741,11 @@
         <v>Avg</v>
       </c>
       <c r="Z44" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average ROA per L1 business segment.
+        <v xml:space="preserve">Exposure-weighted average ROE per L1 business segment.
 </v>
       </c>
       <c r="AA44" t="str">
-        <v>Return on Assets (%) (business_segment)</v>
+        <v>Return on Equity (%) (business_segment)</v>
       </c>
       <c r="AB44" t="str">
         <v/>
@@ -4546,17 +4753,17 @@
     </row>
     <row r="45" xml:space="preserve">
       <c r="A45" t="str">
-        <v>EXP-036</v>
+        <v>EXP-037</v>
       </c>
       <c r="B45" t="str" xml:space="preserve">
-        <v xml:space="preserve">Net Income divided by Shareholders Equity. Profitability KPI measuring return generated on shareholder capital. At facility level uses committed exposure (bank share) as denominator proxy.
+        <v xml:space="preserve">Total principal and interest obligations due within reporting period. Facility level in local currency; counterparty and above converted to USD. Used in repayment capacity and covenant analysis.
 </v>
       </c>
       <c r="C45" t="str">
-        <v>Return on Equity (%)</v>
+        <v>Total Debt Service ($)</v>
       </c>
       <c r="D45" t="str" xml:space="preserve">
-        <v xml:space="preserve">Facility Net Income / Committed Exposure (Bank Share portion only).
+        <v xml:space="preserve">Interest Expense + Principal Payment from facility_financial_snapshot. Facility level stays in local currency (no FX conversion).
 </v>
       </c>
       <c r="E45" t="str">
@@ -4575,63 +4782,63 @@
         <v>Calc</v>
       </c>
       <c r="J45" t="str" xml:space="preserve">
-        <v xml:space="preserve">Facility Net Income / Committed Exposure (Bank Share portion only).
+        <v xml:space="preserve">Interest Expense + Principal Payment from facility_financial_snapshot. Facility level stays in local currency (no FX conversion).
 </v>
       </c>
       <c r="K45" t="str">
-        <v>Return on Equity (%) (facility)</v>
+        <v>Total Debt Service ($) (facility)</v>
       </c>
       <c r="L45" t="str">
         <v>Y</v>
       </c>
       <c r="M45" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="N45" t="str" xml:space="preserve">
-        <v xml:space="preserve">Counterparty Net Income / Shareholders Equity * 100. Net income computed from revenue minus expenses.
+        <v xml:space="preserve">SUM of facility-level TDS converted to USD per counterparty.
 </v>
       </c>
       <c r="O45" t="str">
-        <v>Return on Equity (%) (counterparty)</v>
+        <v>Total Debt Service ($) (counterparty)</v>
       </c>
       <c r="P45" t="str">
         <v>Y</v>
       </c>
       <c r="Q45" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="R45" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average ROE per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level TDS converted to USD per L3 desk segment.
 </v>
       </c>
       <c r="S45" t="str">
-        <v>Return on Equity (%) (desk)</v>
+        <v>Total Debt Service ($) (desk)</v>
       </c>
       <c r="T45" t="str">
         <v>Y</v>
       </c>
       <c r="U45" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="V45" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average ROE per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level TDS converted to USD per L2 portfolio segment.
 </v>
       </c>
       <c r="W45" t="str">
-        <v>Return on Equity (%) (portfolio)</v>
+        <v>Total Debt Service ($) (portfolio)</v>
       </c>
       <c r="X45" t="str">
         <v>Y</v>
       </c>
       <c r="Y45" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="Z45" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average ROE per L1 business segment.
+        <v xml:space="preserve">SUM of facility-level TDS converted to USD per L1 business segment.
 </v>
       </c>
       <c r="AA45" t="str">
-        <v>Return on Equity (%) (business_segment)</v>
+        <v>Total Debt Service ($) (business_segment)</v>
       </c>
       <c r="AB45" t="str">
         <v/>
@@ -4639,17 +4846,17 @@
     </row>
     <row r="46" xml:space="preserve">
       <c r="A46" t="str">
-        <v>EXP-037</v>
+        <v>EXP-038</v>
       </c>
       <c r="B46" t="str" xml:space="preserve">
-        <v xml:space="preserve">Total principal and interest obligations due within reporting period. Facility level in local currency; counterparty and above converted to USD. Used in repayment capacity and covenant analysis.
+        <v xml:space="preserve">Exposure divided by Exposure Limit. Calculated KPI measuring the proportion of approved capacity currently drawn, providing insight into liquidity usage and limit pressure.
 </v>
       </c>
       <c r="C46" t="str">
-        <v>Total Debt Service ($)</v>
+        <v>Utilization (%)</v>
       </c>
       <c r="D46" t="str" xml:space="preserve">
-        <v xml:space="preserve">Interest Expense + Principal Payment from facility_financial_snapshot. Facility level stays in local currency (no FX conversion).
+        <v xml:space="preserve">For each Distinct([Facility ID]), WHEN IS(MAX(AS_OF_DATE) AND [Facility_Active_Flag]="Y" Sum([Utilized Exposure] / [Committed_Facility_Amt])
 </v>
       </c>
       <c r="E46" t="str">
@@ -4668,63 +4875,63 @@
         <v>Calc</v>
       </c>
       <c r="J46" t="str" xml:space="preserve">
-        <v xml:space="preserve">Interest Expense + Principal Payment from facility_financial_snapshot. Facility level stays in local currency (no FX conversion).
+        <v xml:space="preserve">For each Distinct([Facility ID]), WHEN IS(MAX(AS_OF_DATE) AND [Facility_Active_Flag]="Y" Sum([Utilized Exposure] / [Committed_Facility_Amt])
 </v>
       </c>
       <c r="K46" t="str">
-        <v>Total Debt Service ($) (facility)</v>
+        <v>Utilization (%) (facility)</v>
       </c>
       <c r="L46" t="str">
         <v>Y</v>
       </c>
       <c r="M46" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N46" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level TDS converted to USD per counterparty.
+        <v xml:space="preserve">SUM(drawn_amount) / SUM(committed_amount) * 100.0 per counterparty.
 </v>
       </c>
       <c r="O46" t="str">
-        <v>Total Debt Service ($) (counterparty)</v>
+        <v>Utilization (%) (counterparty)</v>
       </c>
       <c r="P46" t="str">
         <v>Y</v>
       </c>
       <c r="Q46" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R46" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level TDS converted to USD per L3 desk segment.
+        <v xml:space="preserve">SUM(drawn_amount) / SUM(committed_amount) * 100.0 per L3 desk segment.
 </v>
       </c>
       <c r="S46" t="str">
-        <v>Total Debt Service ($) (desk)</v>
+        <v>Utilization (%) (desk)</v>
       </c>
       <c r="T46" t="str">
         <v>Y</v>
       </c>
       <c r="U46" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V46" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level TDS converted to USD per L2 portfolio segment.
+        <v xml:space="preserve">SUM(drawn_amount) / SUM(committed_amount) * 100.0 per L2 portfolio segment.
 </v>
       </c>
       <c r="W46" t="str">
-        <v>Total Debt Service ($) (portfolio)</v>
+        <v>Utilization (%) (portfolio)</v>
       </c>
       <c r="X46" t="str">
         <v>Y</v>
       </c>
       <c r="Y46" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z46" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level TDS converted to USD per L1 business segment.
+        <v xml:space="preserve">SUM(drawn_amount) / SUM(committed_amount) * 100.0 per L1 business segment.
 </v>
       </c>
       <c r="AA46" t="str">
-        <v>Total Debt Service ($) (business_segment)</v>
+        <v>Utilization (%) (business_segment)</v>
       </c>
       <c r="AB46" t="str">
         <v/>
@@ -4732,17 +4939,17 @@
     </row>
     <row r="47" xml:space="preserve">
       <c r="A47" t="str">
-        <v>EXP-038</v>
+        <v>EXP-039</v>
       </c>
       <c r="B47" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure divided by Exposure Limit. Calculated KPI measuring the proportion of approved capacity currently drawn, providing insight into liquidity usage and limit pressure.
+        <v xml:space="preserve">The currently drawn/outstanding amount (in USD) on the facility as of the reporting date.
 </v>
       </c>
       <c r="C47" t="str">
-        <v>Utilization (%)</v>
+        <v>Utilized Amount ($)</v>
       </c>
       <c r="D47" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Distinct([Facility ID]), WHEN IS(MAX(AS_OF_DATE) AND [Facility_Active_Flag]="Y" Sum([Utilized Exposure] / [Committed_Facility_Amt])
+        <v xml:space="preserve">Read utilized_amount_usd from limit_utilization_event for each facility as- of reporting date.
 </v>
       </c>
       <c r="E47" t="str">
@@ -4758,66 +4965,66 @@
         <v>Y</v>
       </c>
       <c r="I47" t="str">
-        <v>Calc</v>
+        <v>Raw</v>
       </c>
       <c r="J47" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Distinct([Facility ID]), WHEN IS(MAX(AS_OF_DATE) AND [Facility_Active_Flag]="Y" Sum([Utilized Exposure] / [Committed_Facility_Amt])
+        <v xml:space="preserve">Read utilized_amount_usd from limit_utilization_event for each facility as- of reporting date.
 </v>
       </c>
       <c r="K47" t="str">
-        <v>Utilization (%) (facility)</v>
+        <v>Utilized Amount ($) (facility)</v>
       </c>
       <c r="L47" t="str">
         <v>Y</v>
       </c>
       <c r="M47" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="N47" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(drawn_amount) / SUM(committed_amount) * 100.0 per counterparty.
+        <v xml:space="preserve">SUM of facility-level utilized_amount_usd per counterparty.
 </v>
       </c>
       <c r="O47" t="str">
-        <v>Utilization (%) (counterparty)</v>
+        <v>Utilized Amount ($) (counterparty)</v>
       </c>
       <c r="P47" t="str">
         <v>Y</v>
       </c>
       <c r="Q47" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="R47" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(drawn_amount) / SUM(committed_amount) * 100.0 per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level utilized_amount_usd per L3 desk segment.
 </v>
       </c>
       <c r="S47" t="str">
-        <v>Utilization (%) (desk)</v>
+        <v>Utilized Amount ($) (desk)</v>
       </c>
       <c r="T47" t="str">
         <v>Y</v>
       </c>
       <c r="U47" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="V47" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(drawn_amount) / SUM(committed_amount) * 100.0 per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level utilized_amount_usd per L2 portfolio segment.
 </v>
       </c>
       <c r="W47" t="str">
-        <v>Utilization (%) (portfolio)</v>
+        <v>Utilized Amount ($) (portfolio)</v>
       </c>
       <c r="X47" t="str">
         <v>Y</v>
       </c>
       <c r="Y47" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="Z47" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(drawn_amount) / SUM(committed_amount) * 100.0 per L1 business segment.
+        <v xml:space="preserve">SUM of facility-level utilized_amount_usd per L1 business segment segment.
 </v>
       </c>
       <c r="AA47" t="str">
-        <v>Utilization (%) (business_segment)</v>
+        <v>Utilized Amount ($) (business_segment)</v>
       </c>
       <c r="AB47" t="str">
         <v/>
@@ -4825,17 +5032,18 @@
     </row>
     <row r="48" xml:space="preserve">
       <c r="A48" t="str">
-        <v>EXP-039</v>
+        <v>EXP-041</v>
       </c>
       <c r="B48" t="str" xml:space="preserve">
-        <v xml:space="preserve">The currently drawn/outstanding amount (in USD) on the facility as of the reporting date.
+        <v xml:space="preserve">Total interest earned on outstanding exposures during the reporting period. Sources from facility_profitability_snapshot.interest_income_amt (ETL'd from core banking, includes proper accrual and day-count per ASC 310-20). Bank-share-adjusted via facility_lender_allocation.
 </v>
       </c>
       <c r="C48" t="str">
-        <v>Utilized Amount ($)</v>
+        <v>Interest Income</v>
       </c>
       <c r="D48" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read utilized_amount_usd from limit_utilization_event for each facility as- of reporting date.
+        <v xml:space="preserve">SUM(interest_income_amt) per facility from facility_profitability_snapshot.
+Weighted by bank_share_pct from facility_lender_allocation.
 </v>
       </c>
       <c r="E48" t="str">
@@ -4851,27 +5059,29 @@
         <v>Y</v>
       </c>
       <c r="I48" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="J48" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read utilized_amount_usd from limit_utilization_event for each facility as- of reporting date.
+        <v xml:space="preserve">SUM(interest_income_amt) per facility from facility_profitability_snapshot.
+Weighted by bank_share_pct from facility_lender_allocation.
 </v>
       </c>
       <c r="K48" t="str">
-        <v>Utilized Amount ($) (facility)</v>
+        <v>Interest Income (facility)</v>
       </c>
       <c r="L48" t="str">
         <v>Y</v>
       </c>
       <c r="M48" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N48" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level utilized_amount_usd per counterparty.
+        <v xml:space="preserve">For each counterparty, sum facility-level interest income weighted
+by participation_pct from facility_counterparty_participation.
 </v>
       </c>
       <c r="O48" t="str">
-        <v>Utilized Amount ($) (counterparty)</v>
+        <v>Interest Income (counterparty)</v>
       </c>
       <c r="P48" t="str">
         <v>Y</v>
@@ -4880,11 +5090,11 @@
         <v>Agg</v>
       </c>
       <c r="R48" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level utilized_amount_usd per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level interest income per L3 desk segment.
 </v>
       </c>
       <c r="S48" t="str">
-        <v>Utilized Amount ($) (desk)</v>
+        <v>Interest Income (desk)</v>
       </c>
       <c r="T48" t="str">
         <v>Y</v>
@@ -4893,11 +5103,12 @@
         <v>Agg</v>
       </c>
       <c r="V48" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level utilized_amount_usd per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level interest income per L2 portfolio segment.
+Traverses L3 -&gt; L2 via parent_segment_id.
 </v>
       </c>
       <c r="W48" t="str">
-        <v>Utilized Amount ($) (portfolio)</v>
+        <v>Interest Income (portfolio)</v>
       </c>
       <c r="X48" t="str">
         <v>Y</v>
@@ -4906,11 +5117,12 @@
         <v>Agg</v>
       </c>
       <c r="Z48" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level utilized_amount_usd per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level interest income per L1 business segment.
+Traverses L3 -&gt; L2 -&gt; L1 via parent_segment_id chain.
 </v>
       </c>
       <c r="AA48" t="str">
-        <v>Utilized Amount ($) (business_segment)</v>
+        <v>Interest Income (business_segment)</v>
       </c>
       <c r="AB48" t="str">
         <v/>
@@ -4918,18 +5130,17 @@
     </row>
     <row r="49" xml:space="preserve">
       <c r="A49" t="str">
-        <v>EXP-041</v>
+        <v>EXP-042</v>
       </c>
       <c r="B49" t="str" xml:space="preserve">
-        <v xml:space="preserve">Total interest earned on outstanding exposures during the reporting period. Sources from facility_profitability_snapshot.interest_income_amt (ETL'd from core banking, includes proper accrual and day-count per ASC 310-20). Bank-share-adjusted via facility_lender_allocation.
+        <v xml:space="preserve">Total on-balance-sheet assets attributable to the reporting entity at a point in time.
 </v>
       </c>
       <c r="C49" t="str">
-        <v>Interest Income</v>
+        <v>Total Assets Amount</v>
       </c>
       <c r="D49" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(interest_income_amt) per facility from facility_profitability_snapshot.
-Weighted by bank_share_pct from facility_lender_allocation.
+        <v xml:space="preserve">SUM(total_assets_amt) per facility from counterparty_financial_snapshot. Weighted by bank share percentage.
 </v>
       </c>
       <c r="E49" t="str">
@@ -4948,26 +5159,24 @@
         <v>Agg</v>
       </c>
       <c r="J49" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(interest_income_amt) per facility from facility_profitability_snapshot.
-Weighted by bank_share_pct from facility_lender_allocation.
+        <v xml:space="preserve">SUM(total_assets_amt) per facility from counterparty_financial_snapshot. Weighted by bank share percentage.
 </v>
       </c>
       <c r="K49" t="str">
-        <v>Interest Income (facility)</v>
+        <v>Total Assets Amount (facility)</v>
       </c>
       <c r="L49" t="str">
         <v>Y</v>
       </c>
       <c r="M49" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="N49" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each counterparty, sum facility-level interest income weighted
-by participation_pct from facility_counterparty_participation.
+        <v xml:space="preserve">SUM of facility-level total_assets_amt per counterparty.
 </v>
       </c>
       <c r="O49" t="str">
-        <v>Interest Income (counterparty)</v>
+        <v>Total Assets Amount (counterparty)</v>
       </c>
       <c r="P49" t="str">
         <v>Y</v>
@@ -4976,11 +5185,11 @@
         <v>Agg</v>
       </c>
       <c r="R49" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level interest income per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level total_assets_amt per L3 desk segment.
 </v>
       </c>
       <c r="S49" t="str">
-        <v>Interest Income (desk)</v>
+        <v>Total Assets Amount (desk)</v>
       </c>
       <c r="T49" t="str">
         <v>Y</v>
@@ -4989,12 +5198,11 @@
         <v>Agg</v>
       </c>
       <c r="V49" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level interest income per L2 portfolio segment.
-Traverses L3 -&gt; L2 via parent_segment_id.
+        <v xml:space="preserve">SUM of facility-level total_assets_amt per L2 portfolio segment.
 </v>
       </c>
       <c r="W49" t="str">
-        <v>Interest Income (portfolio)</v>
+        <v>Total Assets Amount (portfolio)</v>
       </c>
       <c r="X49" t="str">
         <v>Y</v>
@@ -5003,12 +5211,11 @@
         <v>Agg</v>
       </c>
       <c r="Z49" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level interest income per L1 business segment.
-Traverses L3 -&gt; L2 -&gt; L1 via parent_segment_id chain.
+        <v xml:space="preserve">SUM of facility-level total_assets_amt per L1 business segment segment.
 </v>
       </c>
       <c r="AA49" t="str">
-        <v>Interest Income (business_segment)</v>
+        <v>Total Assets Amount (business_segment)</v>
       </c>
       <c r="AB49" t="str">
         <v/>
@@ -5016,17 +5223,17 @@
     </row>
     <row r="50" xml:space="preserve">
       <c r="A50" t="str">
-        <v>EXP-042</v>
+        <v>EXP-043</v>
       </c>
       <c r="B50" t="str" xml:space="preserve">
-        <v xml:space="preserve">Total on-balance-sheet assets attributable to the reporting entity at a point in time.
+        <v xml:space="preserve">Total shareholder capital allocated to the reporting unit.
 </v>
       </c>
       <c r="C50" t="str">
-        <v>Total Assets Amount</v>
+        <v>Total Equity amount</v>
       </c>
       <c r="D50" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(total_assets_amt) per facility from counterparty_financial_snapshot. Weighted by bank share percentage.
+        <v xml:space="preserve">SUM(allocated_equity_amt) per facility from facility_profitability_snapshot. Weighted by bank share percentage.
 </v>
       </c>
       <c r="E50" t="str">
@@ -5045,11 +5252,11 @@
         <v>Agg</v>
       </c>
       <c r="J50" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(total_assets_amt) per facility from counterparty_financial_snapshot. Weighted by bank share percentage.
+        <v xml:space="preserve">SUM(allocated_equity_amt) per facility from facility_profitability_snapshot. Weighted by bank share percentage.
 </v>
       </c>
       <c r="K50" t="str">
-        <v>Total Assets Amount (facility)</v>
+        <v>Total Equity amount (facility)</v>
       </c>
       <c r="L50" t="str">
         <v>Y</v>
@@ -5058,11 +5265,11 @@
         <v>Agg</v>
       </c>
       <c r="N50" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_assets_amt per counterparty.
+        <v xml:space="preserve">SUM of facility-level allocated_equity_amt per counterparty.
 </v>
       </c>
       <c r="O50" t="str">
-        <v>Total Assets Amount (counterparty)</v>
+        <v>Total Equity amount (counterparty)</v>
       </c>
       <c r="P50" t="str">
         <v>Y</v>
@@ -5071,11 +5278,11 @@
         <v>Agg</v>
       </c>
       <c r="R50" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_assets_amt per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level allocated_equity_amt per L3 desk segment.
 </v>
       </c>
       <c r="S50" t="str">
-        <v>Total Assets Amount (desk)</v>
+        <v>Total Equity amount (desk)</v>
       </c>
       <c r="T50" t="str">
         <v>Y</v>
@@ -5084,11 +5291,11 @@
         <v>Agg</v>
       </c>
       <c r="V50" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_assets_amt per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level allocated_equity_amt per L2 portfolio segment.
 </v>
       </c>
       <c r="W50" t="str">
-        <v>Total Assets Amount (portfolio)</v>
+        <v>Total Equity amount (portfolio)</v>
       </c>
       <c r="X50" t="str">
         <v>Y</v>
@@ -5097,11 +5304,11 @@
         <v>Agg</v>
       </c>
       <c r="Z50" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_assets_amt per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level allocated_equity_amt per L1 business segment segment.
 </v>
       </c>
       <c r="AA50" t="str">
-        <v>Total Assets Amount (business_segment)</v>
+        <v>Total Equity amount (business_segment)</v>
       </c>
       <c r="AB50" t="str">
         <v/>
@@ -5109,17 +5316,17 @@
     </row>
     <row r="51" xml:space="preserve">
       <c r="A51" t="str">
-        <v>EXP-043</v>
+        <v>EXP-044</v>
       </c>
       <c r="B51" t="str" xml:space="preserve">
-        <v xml:space="preserve">Total shareholder capital allocated to the reporting unit.
+        <v xml:space="preserve">Average balance of interest-generating assets over the reporting period.
 </v>
       </c>
       <c r="C51" t="str">
-        <v>Total Equity amount</v>
+        <v>Average Earning Assets Amount</v>
       </c>
       <c r="D51" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(allocated_equity_amt) per facility from facility_profitability_snapshot. Weighted by bank share percentage.
+        <v xml:space="preserve">Read avg_earning_assets_amt from facility_profitability_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="E51" t="str">
@@ -5135,27 +5342,27 @@
         <v>Y</v>
       </c>
       <c r="I51" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="J51" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(allocated_equity_amt) per facility from facility_profitability_snapshot. Weighted by bank share percentage.
+        <v xml:space="preserve">Read avg_earning_assets_amt from facility_profitability_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="K51" t="str">
-        <v>Total Equity amount (facility)</v>
+        <v>Average Earning Assets Amount (facility)</v>
       </c>
       <c r="L51" t="str">
         <v>Y</v>
       </c>
       <c r="M51" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="N51" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level allocated_equity_amt per counterparty.
+        <v xml:space="preserve">Exposure-weighted average of avg_earning_assets_amt across counterparty facilities.
 </v>
       </c>
       <c r="O51" t="str">
-        <v>Total Equity amount (counterparty)</v>
+        <v>Average Earning Assets Amount (counterparty)</v>
       </c>
       <c r="P51" t="str">
         <v>Y</v>
@@ -5164,24 +5371,24 @@
         <v>Agg</v>
       </c>
       <c r="R51" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level allocated_equity_amt per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level avg_earning_assets_amt per L3 desk segment.
 </v>
       </c>
       <c r="S51" t="str">
-        <v>Total Equity amount (desk)</v>
+        <v>Average Earning Assets Amount (desk)</v>
       </c>
       <c r="T51" t="str">
         <v>Y</v>
       </c>
       <c r="U51" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="V51" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level allocated_equity_amt per L2 portfolio segment.
+        <v xml:space="preserve">AVG of facility-level avg_earning_assets_amt per L2 portfolio segment.
 </v>
       </c>
       <c r="W51" t="str">
-        <v>Total Equity amount (portfolio)</v>
+        <v>Average Earning Assets Amount (portfolio)</v>
       </c>
       <c r="X51" t="str">
         <v>Y</v>
@@ -5190,11 +5397,11 @@
         <v>Agg</v>
       </c>
       <c r="Z51" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level allocated_equity_amt per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level avg_earning_assets_amt per L1 business segment segment.
 </v>
       </c>
       <c r="AA51" t="str">
-        <v>Total Equity amount (business_segment)</v>
+        <v>Average Earning Assets Amount (business_segment)</v>
       </c>
       <c r="AB51" t="str">
         <v/>
@@ -5202,17 +5409,17 @@
     </row>
     <row r="52" xml:space="preserve">
       <c r="A52" t="str">
-        <v>EXP-044</v>
+        <v>EXP-045</v>
       </c>
       <c r="B52" t="str" xml:space="preserve">
-        <v xml:space="preserve">Average balance of interest-generating assets over the reporting period.
+        <v xml:space="preserve">Exposure-weighted average regulatory risk weight reflecting capital intensity.
 </v>
       </c>
       <c r="C52" t="str">
-        <v>Average Earning Assets Amount</v>
+        <v>Risk Weighted Average (%)</v>
       </c>
       <c r="D52" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read avg_earning_assets_amt from facility_profitability_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">SUM(RWA Amount)/SUM(Exposure)
 </v>
       </c>
       <c r="E52" t="str">
@@ -5228,66 +5435,66 @@
         <v>Y</v>
       </c>
       <c r="I52" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="J52" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read avg_earning_assets_amt from facility_profitability_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">SUM(RWA Amount)/SUM(Exposure)
 </v>
       </c>
       <c r="K52" t="str">
-        <v>Average Earning Assets Amount (facility)</v>
+        <v>Risk Weighted Average (%) (facility)</v>
       </c>
       <c r="L52" t="str">
         <v>Y</v>
       </c>
       <c r="M52" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="N52" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of avg_earning_assets_amt across counterparty facilities.
+        <v xml:space="preserve">SUM(rwa) / SUM(gross_exposure) * 100.0 per counterparty.
 </v>
       </c>
       <c r="O52" t="str">
-        <v>Average Earning Assets Amount (counterparty)</v>
+        <v>Risk Weighted Average (%) (counterparty)</v>
       </c>
       <c r="P52" t="str">
         <v>Y</v>
       </c>
       <c r="Q52" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R52" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level avg_earning_assets_amt per L3 desk segment.
+        <v xml:space="preserve">SUM(rwa) / SUM(gross_exposure) * 100.0 per L3 desk segment.
 </v>
       </c>
       <c r="S52" t="str">
-        <v>Average Earning Assets Amount (desk)</v>
+        <v>Risk Weighted Average (%) (desk)</v>
       </c>
       <c r="T52" t="str">
         <v>Y</v>
       </c>
       <c r="U52" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="V52" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level avg_earning_assets_amt per L2 portfolio segment.
+        <v xml:space="preserve">SUM(rwa) / SUM(gross_exposure) * 100.0 per L2 portfolio segment.
 </v>
       </c>
       <c r="W52" t="str">
-        <v>Average Earning Assets Amount (portfolio)</v>
+        <v>Risk Weighted Average (%) (portfolio)</v>
       </c>
       <c r="X52" t="str">
         <v>Y</v>
       </c>
       <c r="Y52" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z52" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level avg_earning_assets_amt per L1 business segment segment.
+        <v xml:space="preserve">SUM(rwa) / SUM(gross_exposure) * 100.0 per L1 business segment.
 </v>
       </c>
       <c r="AA52" t="str">
-        <v>Average Earning Assets Amount (business_segment)</v>
+        <v>Risk Weighted Average (%) (business_segment)</v>
       </c>
       <c r="AB52" t="str">
         <v/>
@@ -5295,17 +5502,17 @@
     </row>
     <row r="53" xml:space="preserve">
       <c r="A53" t="str">
-        <v>EXP-045</v>
+        <v>EXP-046</v>
       </c>
       <c r="B53" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average regulatory risk weight reflecting capital intensity.
+        <v xml:space="preserve">Total risk-weighted assets calculated for regulatory capital purposes.
 </v>
       </c>
       <c r="C53" t="str">
-        <v>Risk Weighted Average (%)</v>
+        <v>Risk Weighted Average Amount ($)</v>
       </c>
       <c r="D53" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(RWA Amount)/SUM(Exposure)
+        <v xml:space="preserve">Exposure * Risk Weight %
 </v>
       </c>
       <c r="E53" t="str">
@@ -5324,63 +5531,63 @@
         <v>Calc</v>
       </c>
       <c r="J53" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(RWA Amount)/SUM(Exposure)
+        <v xml:space="preserve">Exposure * Risk Weight %
 </v>
       </c>
       <c r="K53" t="str">
-        <v>Risk Weighted Average (%) (facility)</v>
+        <v>Risk Weighted Average Amount ($) (facility)</v>
       </c>
       <c r="L53" t="str">
         <v>Y</v>
       </c>
       <c r="M53" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="N53" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(rwa) / SUM(gross_exposure) * 100.0 per counterparty.
+        <v xml:space="preserve">SUM of facility-level rwa_amt per counterparty.
 </v>
       </c>
       <c r="O53" t="str">
-        <v>Risk Weighted Average (%) (counterparty)</v>
+        <v>Risk Weighted Average Amount ($) (counterparty)</v>
       </c>
       <c r="P53" t="str">
         <v>Y</v>
       </c>
       <c r="Q53" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="R53" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(rwa) / SUM(gross_exposure) * 100.0 per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level rwa_amt per L3 desk segment.
 </v>
       </c>
       <c r="S53" t="str">
-        <v>Risk Weighted Average (%) (desk)</v>
+        <v>Risk Weighted Average Amount ($) (desk)</v>
       </c>
       <c r="T53" t="str">
         <v>Y</v>
       </c>
       <c r="U53" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="V53" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(rwa) / SUM(gross_exposure) * 100.0 per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level rwa_amt per L2 portfolio segment.
 </v>
       </c>
       <c r="W53" t="str">
-        <v>Risk Weighted Average (%) (portfolio)</v>
+        <v>Risk Weighted Average Amount ($) (portfolio)</v>
       </c>
       <c r="X53" t="str">
         <v>Y</v>
       </c>
       <c r="Y53" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="Z53" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(rwa) / SUM(gross_exposure) * 100.0 per L1 business segment.
+        <v xml:space="preserve">SUM of facility-level rwa_amt per L1 business segment.
 </v>
       </c>
       <c r="AA53" t="str">
-        <v>Risk Weighted Average (%) (business_segment)</v>
+        <v>Risk Weighted Average Amount ($) (business_segment)</v>
       </c>
       <c r="AB53" t="str">
         <v/>
@@ -5388,17 +5595,17 @@
     </row>
     <row r="54" xml:space="preserve">
       <c r="A54" t="str">
-        <v>EXP-046</v>
+        <v>EXP-047</v>
       </c>
       <c r="B54" t="str" xml:space="preserve">
-        <v xml:space="preserve">Total risk-weighted assets calculated for regulatory capital purposes.
+        <v xml:space="preserve">Indicates how well cash flow covers fixed, non-discretionary obligations; highlights ability to withstand earnings volatility and signals potential liquidity stress/default risk.
 </v>
       </c>
       <c r="C54" t="str">
-        <v>Risk Weighted Average Amount ($)</v>
+        <v>Fixed Cost Coverage Ratio (%)</v>
       </c>
       <c r="D54" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure * Risk Weight %
+        <v xml:space="preserve">Read fccr_value from lob_risk_ratio_summary for each facility as-of reporting date.
 </v>
       </c>
       <c r="E54" t="str">
@@ -5414,66 +5621,70 @@
         <v>Y</v>
       </c>
       <c r="I54" t="str">
-        <v>Calc</v>
+        <v>Raw</v>
       </c>
       <c r="J54" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure * Risk Weight %
+        <v xml:space="preserve">Read fccr_value from lob_risk_ratio_summary for each facility as-of reporting date.
 </v>
       </c>
       <c r="K54" t="str">
-        <v>Risk Weighted Average Amount ($) (facility)</v>
+        <v>Fixed Cost Coverage Ratio (%) (facility)</v>
       </c>
       <c r="L54" t="str">
         <v>Y</v>
       </c>
       <c r="M54" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N54" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level rwa_amt per counterparty.
+        <v xml:space="preserve">SUM(ebitda × fx_rate) / SUM(total_debt_service × fx_rate) per counterparty.
+Amounts converted to USD via l2.fx_rate before aggregation.
 </v>
       </c>
       <c r="O54" t="str">
-        <v>Risk Weighted Average Amount ($) (counterparty)</v>
+        <v>Fixed Cost Coverage Ratio (%) (counterparty)</v>
       </c>
       <c r="P54" t="str">
         <v>Y</v>
       </c>
       <c r="Q54" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R54" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level rwa_amt per L3 desk segment.
+        <v xml:space="preserve">SUM(ebitda × fx_rate) / SUM(total_debt_service × fx_rate) per L3 desk segment.
+Amounts converted to USD via l2.fx_rate before aggregation.
 </v>
       </c>
       <c r="S54" t="str">
-        <v>Risk Weighted Average Amount ($) (desk)</v>
+        <v>Fixed Cost Coverage Ratio (%) (desk)</v>
       </c>
       <c r="T54" t="str">
         <v>Y</v>
       </c>
       <c r="U54" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V54" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level rwa_amt per L2 portfolio segment.
+        <v xml:space="preserve">SUM(ebitda × fx_rate) / SUM(total_debt_service × fx_rate) per L2 portfolio segment.
+Amounts converted to USD via l2.fx_rate before aggregation.
 </v>
       </c>
       <c r="W54" t="str">
-        <v>Risk Weighted Average Amount ($) (portfolio)</v>
+        <v>Fixed Cost Coverage Ratio (%) (portfolio)</v>
       </c>
       <c r="X54" t="str">
         <v>Y</v>
       </c>
       <c r="Y54" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z54" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level rwa_amt per L1 business segment.
+        <v xml:space="preserve">SUM(ebitda × fx_rate) / SUM(total_debt_service × fx_rate) per L1 business segment.
+Amounts converted to USD via l2.fx_rate before aggregation.
 </v>
       </c>
       <c r="AA54" t="str">
-        <v>Risk Weighted Average Amount ($) (business_segment)</v>
+        <v>Fixed Cost Coverage Ratio (%) (business_segment)</v>
       </c>
       <c r="AB54" t="str">
         <v/>
@@ -5481,17 +5692,17 @@
     </row>
     <row r="55" xml:space="preserve">
       <c r="A55" t="str">
-        <v>EXP-047</v>
+        <v>EXP-048</v>
       </c>
       <c r="B55" t="str" xml:space="preserve">
-        <v xml:space="preserve">Indicates how well cash flow covers fixed, non-discretionary obligations; highlights ability to withstand earnings volatility and signals potential liquidity stress/default risk.
+        <v xml:space="preserve">Scheduled principal repayment obligation due for the contractual commitment.
 </v>
       </c>
       <c r="C55" t="str">
-        <v>Fixed Cost Coverage Ratio (%)</v>
+        <v>Principal Repayment Amount ($)</v>
       </c>
       <c r="D55" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read fccr_value from lob_risk_ratio_summary for each facility as-of reporting date.
+        <v xml:space="preserve">Read principal_payment_amt from facility_financial_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="E55" t="str">
@@ -5510,67 +5721,63 @@
         <v>Raw</v>
       </c>
       <c r="J55" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read fccr_value from lob_risk_ratio_summary for each facility as-of reporting date.
+        <v xml:space="preserve">Read principal_payment_amt from facility_financial_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="K55" t="str">
-        <v>Fixed Cost Coverage Ratio (%) (facility)</v>
+        <v>Principal Repayment Amount ($) (facility)</v>
       </c>
       <c r="L55" t="str">
         <v>Y</v>
       </c>
       <c r="M55" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="N55" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(ebitda × fx_rate) / SUM(total_debt_service × fx_rate) per counterparty.
-Amounts converted to USD via l2.fx_rate before aggregation.
+        <v xml:space="preserve">SUM(facility-level principal_payment_amt) per counterparty.
 </v>
       </c>
       <c r="O55" t="str">
-        <v>Fixed Cost Coverage Ratio (%) (counterparty)</v>
+        <v>Principal Repayment Amount ($) (counterparty)</v>
       </c>
       <c r="P55" t="str">
         <v>Y</v>
       </c>
       <c r="Q55" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="R55" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(ebitda × fx_rate) / SUM(total_debt_service × fx_rate) per L3 desk segment.
-Amounts converted to USD via l2.fx_rate before aggregation.
+        <v xml:space="preserve">SUM of facility-level principal_payment_amt per L3 desk segment.
 </v>
       </c>
       <c r="S55" t="str">
-        <v>Fixed Cost Coverage Ratio (%) (desk)</v>
+        <v>Principal Repayment Amount ($) (desk)</v>
       </c>
       <c r="T55" t="str">
         <v>Y</v>
       </c>
       <c r="U55" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="V55" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(ebitda × fx_rate) / SUM(total_debt_service × fx_rate) per L2 portfolio segment.
-Amounts converted to USD via l2.fx_rate before aggregation.
+        <v xml:space="preserve">SUM of facility-level principal_payment_amt per L2 portfolio segment.
 </v>
       </c>
       <c r="W55" t="str">
-        <v>Fixed Cost Coverage Ratio (%) (portfolio)</v>
+        <v>Principal Repayment Amount ($) (portfolio)</v>
       </c>
       <c r="X55" t="str">
         <v>Y</v>
       </c>
       <c r="Y55" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="Z55" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(ebitda × fx_rate) / SUM(total_debt_service × fx_rate) per L1 business segment.
-Amounts converted to USD via l2.fx_rate before aggregation.
+        <v xml:space="preserve">SUM of facility-level principal_payment_amt per L1 business segment segment.
 </v>
       </c>
       <c r="AA55" t="str">
-        <v>Fixed Cost Coverage Ratio (%) (business_segment)</v>
+        <v>Principal Repayment Amount ($) (business_segment)</v>
       </c>
       <c r="AB55" t="str">
         <v/>
@@ -5578,17 +5785,17 @@
     </row>
     <row r="56" xml:space="preserve">
       <c r="A56" t="str">
-        <v>EXP-048</v>
+        <v>EXP-049</v>
       </c>
       <c r="B56" t="str" xml:space="preserve">
-        <v xml:space="preserve">Scheduled principal repayment obligation due for the contractual commitment.
+        <v xml:space="preserve">Identifies facilities and counterparties with cross-entity exposure — where a single facility participates across multiple counterparties. At facility level, returns 1 if the facility has participations from more than one distinct counterparty in facility_counterparty_participation, 0 otherwise. At counterparty level, returns 1 if any of the counterparty's facilities have cross-entity participations. Flags complexity and concentration risk from intercompany exposure structures.
 </v>
       </c>
       <c r="C56" t="str">
-        <v>Principal Repayment Amount ($)</v>
+        <v>Cross Entity Exposure Flag</v>
       </c>
       <c r="D56" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read principal_payment_amt from facility_financial_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">For each facility, count the number of distinct counterparties in facility_counterparty_participation (current records only). If COUNT(DISTINCT counterparty_id) &gt; 1, the facility has cross-entity exposure (flag = 1). Otherwise flag = 0.
 </v>
       </c>
       <c r="E56" t="str">
@@ -5604,66 +5811,66 @@
         <v>Y</v>
       </c>
       <c r="I56" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="J56" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read principal_payment_amt from facility_financial_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">For each facility, count the number of distinct counterparties in facility_counterparty_participation (current records only). If COUNT(DISTINCT counterparty_id) &gt; 1, the facility has cross-entity exposure (flag = 1). Otherwise flag = 0.
 </v>
       </c>
       <c r="K56" t="str">
-        <v>Principal Repayment Amount ($) (facility)</v>
+        <v>Cross Entity Exposure Flag (facility)</v>
       </c>
       <c r="L56" t="str">
         <v>Y</v>
       </c>
       <c r="M56" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N56" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level principal_payment_amt) per counterparty.
+        <v xml:space="preserve">For each counterparty, check all of its facilities in the participation table. For each facility, determine if it has cross-entity exposure (multiple distinct counterparties). If ANY facility belonging to this counterparty has cross-entity exposure, the counterparty flag = 1. Uses MAX over the facility-level flags for correct boolean OR logic.
 </v>
       </c>
       <c r="O56" t="str">
-        <v>Principal Repayment Amount ($) (counterparty)</v>
+        <v>Cross Entity Exposure Flag (counterparty)</v>
       </c>
       <c r="P56" t="str">
         <v>Y</v>
       </c>
       <c r="Q56" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R56" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level principal_payment_amt per L3 desk segment.
+        <v xml:space="preserve">Not applicable — cross-entity exposure flag is a facility/counterparty level indicator. Desk-level analysis should use EXP-008 (Cross Entity Exposure Amount) for dollar-weighted concentration risk.
 </v>
       </c>
       <c r="S56" t="str">
-        <v>Principal Repayment Amount ($) (desk)</v>
+        <v>Cross Entity Exposure Flag (desk)</v>
       </c>
       <c r="T56" t="str">
         <v>Y</v>
       </c>
       <c r="U56" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V56" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level principal_payment_amt per L2 portfolio segment.
+        <v xml:space="preserve">Not applicable — cross-entity exposure flag is a facility/counterparty level indicator. Portfolio analysis should use EXP-008 for aggregate cross-entity exposure amounts.
 </v>
       </c>
       <c r="W56" t="str">
-        <v>Principal Repayment Amount ($) (portfolio)</v>
+        <v>Cross Entity Exposure Flag (portfolio)</v>
       </c>
       <c r="X56" t="str">
         <v>Y</v>
       </c>
       <c r="Y56" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z56" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level principal_payment_amt per L1 business segment segment.
+        <v xml:space="preserve">Not applicable — cross-entity exposure flag is a facility/counterparty level indicator. Segment analysis should use EXP-008 for aggregate cross-entity exposure amounts.
 </v>
       </c>
       <c r="AA56" t="str">
-        <v>Principal Repayment Amount ($) (business_segment)</v>
+        <v>Cross Entity Exposure Flag (business_segment)</v>
       </c>
       <c r="AB56" t="str">
         <v/>
@@ -5967,14 +6174,14 @@
         <v>PRC-004</v>
       </c>
       <c r="B60" t="str" xml:space="preserve">
-        <v xml:space="preserve">Fee percentage applied to committed or undrawn exposure. Calculated KPI supporting pricing adequacy and revenue optimization analysis.
+        <v xml:space="preserve">Fee percentage applied to committed or undrawn exposure. Sourced from l2.facility_pricing_snapshot at facility level. Supports pricing adequacy and revenue optimization analysis. Aggregate levels use exposure-weighted average with FX conversion to USD.
 </v>
       </c>
       <c r="C60" t="str">
         <v>Fee Rate (%)</v>
       </c>
       <c r="D60" t="str" xml:space="preserve">
-        <v xml:space="preserve">Fee Income / Average Balance
+        <v xml:space="preserve">Direct lookup of fee_rate_pct from l2.facility_pricing_snapshot.
 </v>
       </c>
       <c r="E60" t="str">
@@ -5990,10 +6197,10 @@
         <v>Y</v>
       </c>
       <c r="I60" t="str">
-        <v>Calc</v>
+        <v>Raw</v>
       </c>
       <c r="J60" t="str" xml:space="preserve">
-        <v xml:space="preserve">Fee Income / Average Balance
+        <v xml:space="preserve">Direct lookup of fee_rate_pct from l2.facility_pricing_snapshot.
 </v>
       </c>
       <c r="K60" t="str">
@@ -6006,7 +6213,7 @@
         <v>Avg</v>
       </c>
       <c r="N60" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of fee_rate_pct across counterparty facilities.
+        <v xml:space="preserve">Supplementary (not in primary specification at counterparty level). Exposure-weighted average fee rate per counterparty with FX conversion: SUM(fee_rate * committed_amt * fx) / SUM(committed_amt * fx).
 </v>
       </c>
       <c r="O60" t="str">
@@ -6019,7 +6226,7 @@
         <v>Avg</v>
       </c>
       <c r="R60" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level fee_rate_pct per L3 desk segment.
+        <v xml:space="preserve">Supplementary. Exposure-weighted average fee rate per L3 desk segment with FX conversion.
 </v>
       </c>
       <c r="S60" t="str">
@@ -6032,7 +6239,7 @@
         <v>Avg</v>
       </c>
       <c r="V60" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level fee_rate_pct per L2 portfolio segment.
+        <v xml:space="preserve">Supplementary. Exposure-weighted average fee rate per L2 portfolio segment with FX conversion.
 </v>
       </c>
       <c r="W60" t="str">
@@ -6042,10 +6249,10 @@
         <v>Y</v>
       </c>
       <c r="Y60" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="Z60" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level fee_rate_pct per L1 business segment segment.
+        <v xml:space="preserve">Supplementary. Exposure-weighted average fee rate per L1 business segment with FX conversion.
 </v>
       </c>
       <c r="AA60" t="str">
@@ -6153,14 +6360,18 @@
         <v>PRC-006</v>
       </c>
       <c r="B62" t="str" xml:space="preserve">
-        <v xml:space="preserve">Pricing classification tier assigned to facility. Supports structured pricing strategy and yield segmentation.
+        <v xml:space="preserve">Pricing classification tier derived by range-joining the facility's spread (spread_bps from L2 facility_pricing_snapshot) against the pricing_tier_dim reference table (spread_min_bps/spread_max_bps). Returns the tier_ordinal at facility level and at aggregate levels classifies the exposure-weighted average spread into the corresponding tier. Supports pricing strategy segmentation, yield curve analysis, and risk-adjusted return monitoring.
 </v>
       </c>
       <c r="C62" t="str">
         <v>Pricing Tier</v>
       </c>
       <c r="D62" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read pricing_tier_code from facility_detail_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">For each facility:
+  1. LOAD spread_bps from l2.facility_pricing_snapshot
+  2. RANGE-JOIN against l1.pricing_tier_dim
+     WHERE spread_bps &gt;= spread_min_bps AND spread_bps &lt; spread_max_bps
+  3. RETURN tier_ordinal — the numeric tier classification
 </v>
       </c>
       <c r="E62" t="str">
@@ -6176,10 +6387,14 @@
         <v>Y</v>
       </c>
       <c r="I62" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="J62" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read pricing_tier_code from facility_detail_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">For each facility:
+  1. LOAD spread_bps from l2.facility_pricing_snapshot
+  2. RANGE-JOIN against l1.pricing_tier_dim
+     WHERE spread_bps &gt;= spread_min_bps AND spread_bps &lt; spread_max_bps
+  3. RETURN tier_ordinal — the numeric tier classification
 </v>
       </c>
       <c r="K62" t="str">
@@ -6189,10 +6404,15 @@
         <v>Y</v>
       </c>
       <c r="M62" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="N62" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read pricing_tier_code per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD spread_bps and committed_amount per facility
+  2. COMPUTE weighted average spread:
+     SUM(spread_bps × committed_amount) / SUM(committed_amount)
+  3. RANGE-JOIN weighted avg spread against l1.pricing_tier_dim
+  4. RETURN tier_ordinal for the counterparty's blended spread
 </v>
       </c>
       <c r="O62" t="str">
@@ -6202,10 +6422,13 @@
         <v>Y</v>
       </c>
       <c r="Q62" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R62" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pricing_tier_code per L3 desk segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. Compute exposure-weighted average spread across desk facilities
+  2. Classify against pricing_tier_dim ranges
+  3. RETURN tier_ordinal for the desk's blended spread
 </v>
       </c>
       <c r="S62" t="str">
@@ -6215,10 +6438,13 @@
         <v>Y</v>
       </c>
       <c r="U62" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V62" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pricing_tier_code per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. Compute exposure-weighted average spread
+  3. Classify against pricing_tier_dim ranges
 </v>
       </c>
       <c r="W62" t="str">
@@ -6228,10 +6454,13 @@
         <v>Y</v>
       </c>
       <c r="Y62" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z62" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pricing_tier_code per L1 business segment segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. Compute exposure-weighted average spread
+  3. Classify against pricing_tier_dim ranges
 </v>
       </c>
       <c r="AA62" t="str">
@@ -6432,14 +6661,16 @@
         <v>PRC-009</v>
       </c>
       <c r="B65" t="str" xml:space="preserve">
-        <v xml:space="preserve">Boolean indicator identifying whether the exposure was approved outside standard pricing policy thresholds at origination or amendment.
+        <v xml:space="preserve">Pricing exception effectiveness metric. At facility level, returns an ordinal encoding of the pricing_exception_status (APPROVED=3, PENDING=2, DENIED=1, NONE=0). At aggregate levels, computes the exception rate as COUNT(exception facilities) / COUNT(total facilities) × 100, following the count-ratio rollup pattern. Re-counts at each level to avoid Simpson's paradox. Complements PRC-003 (Exception Rate) with status-level detail for governance drill-down.
 </v>
       </c>
       <c r="C65" t="str">
-        <v>Pricing Exception Flag (Y/N)</v>
+        <v>Pricing Exception Status</v>
       </c>
       <c r="D65" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated pricing_exception_flag per facility.
+        <v xml:space="preserve">Ordinal encoding of pricing_exception_status per facility:
+  APPROVED = 3, PENDING = 2, DENIED = 1, NONE/NULL = 0.
+Ingredients: pricing_exception_status (L2 facility_pricing_snapshot)
 </v>
       </c>
       <c r="E65" t="str">
@@ -6458,63 +6689,79 @@
         <v>Calc</v>
       </c>
       <c r="J65" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated pricing_exception_flag per facility.
+        <v xml:space="preserve">Ordinal encoding of pricing_exception_status per facility:
+  APPROVED = 3, PENDING = 2, DENIED = 1, NONE/NULL = 0.
+Ingredients: pricing_exception_status (L2 facility_pricing_snapshot)
 </v>
       </c>
       <c r="K65" t="str">
-        <v>Pricing Exception Flag (Y/N) (facility)</v>
+        <v>Pricing Exception Status (facility)</v>
       </c>
       <c r="L65" t="str">
         <v>Y</v>
       </c>
       <c r="M65" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N65" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pricing_exception_flag per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD is_pricing_exception_flag for all facilities
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup: re-counts from facility-level flags.
 </v>
       </c>
       <c r="O65" t="str">
-        <v>Pricing Exception Flag (Y/N) (counterparty)</v>
+        <v>Pricing Exception Status (counterparty)</v>
       </c>
       <c r="P65" t="str">
         <v>Y</v>
       </c>
       <c r="Q65" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R65" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pricing_exception_flag per L3 desk segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. JOIN l1.enterprise_business_taxonomy on lob_segment_id
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup per desk.
 </v>
       </c>
       <c r="S65" t="str">
-        <v>Pricing Exception Flag (Y/N) (desk)</v>
+        <v>Pricing Exception Status (desk)</v>
       </c>
       <c r="T65" t="str">
         <v>Y</v>
       </c>
       <c r="U65" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V65" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pricing_exception_flag per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup per portfolio. Drill-down returns exception
+facility details: Facility_ID, Facility_Name, Counterparty_ID,
+Counterparty_Name, Exception_Status, All_in_Rate.
 </v>
       </c>
       <c r="W65" t="str">
-        <v>Pricing Exception Flag (Y/N) (portfolio)</v>
+        <v>Pricing Exception Status (portfolio)</v>
       </c>
       <c r="X65" t="str">
         <v>Y</v>
       </c>
       <c r="Y65" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z65" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pricing_exception_flag per L1 business segment segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup per business segment.
 </v>
       </c>
       <c r="AA65" t="str">
-        <v>Pricing Exception Flag (Y/N) (business_segment)</v>
+        <v>Pricing Exception Status (business_segment)</v>
       </c>
       <c r="AB65" t="str">
         <v/>
@@ -7373,11 +7620,11 @@
         <v>REF-009</v>
       </c>
       <c r="B75" t="str" xml:space="preserve">
-        <v xml:space="preserve">Date on which loan or contract became legally effective. Sourced directly from facility_master. At aggregate levels, returns the earliest origination date (MIN) across constituent facilities — indicating the oldest vintage in the book. Key contract lifecycle tracking attribute for vintage analysis and portfolio seasoning assessment.
+        <v xml:space="preserve">Facility effective date sourced from facility_master origination_date. At facility and counterparty levels, returns the raw date (or earliest vintage via MIN). At portfolio level, pivots to facility lifecycle tracking: counts inactive facilities whose origination date falls within 90 days of the reporting date, identifying the upcoming pipeline of facilities about to start ("Starting 90d"). Key for vintage analysis, portfolio seasoning, and facility pipeline monitoring.
 </v>
       </c>
       <c r="C75" t="str">
-        <v>Contract Origination Date</v>
+        <v>Facility Origination Date</v>
       </c>
       <c r="D75" t="str" xml:space="preserve">
         <v xml:space="preserve">Direct lookup of origination_date from facility_master.
@@ -7405,7 +7652,7 @@
 </v>
       </c>
       <c r="K75" t="str">
-        <v>Contract Origination Date (facility)</v>
+        <v>Facility Origination Date (facility)</v>
       </c>
       <c r="L75" t="str">
         <v>Y</v>
@@ -7421,7 +7668,7 @@
 </v>
       </c>
       <c r="O75" t="str">
-        <v>Contract Origination Date (counterparty)</v>
+        <v>Facility Origination Date (counterparty)</v>
       </c>
       <c r="P75" t="str">
         <v>Y</v>
@@ -7437,22 +7684,26 @@
 </v>
       </c>
       <c r="S75" t="str">
-        <v>Contract Origination Date (desk)</v>
+        <v>Facility Origination Date (desk)</v>
       </c>
       <c r="T75" t="str">
         <v>Y</v>
       </c>
       <c r="U75" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V75" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each L2 Portfolio segment:
+        <v xml:space="preserve">Facility pipeline tracking for each L2 Portfolio segment:
   1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
-  2. COMPUTE MIN(origination_date) — earliest vintage in portfolio
+  2. FILTER inactive facilities (is_active_flag != 'Y')
+     whose origination_date is within 90 days of current date
+  3. COMPUTE COUNT(DISTINCT facility_id) — number of upcoming facilities
+Returns the count of facilities in the "Starting (90d)" pipeline.
+Business rule: facilities not yet active with origination within ±90 days.
 </v>
       </c>
       <c r="W75" t="str">
-        <v>Contract Origination Date (portfolio)</v>
+        <v>Facility Origination Date (portfolio)</v>
       </c>
       <c r="X75" t="str">
         <v>Y</v>
@@ -7467,7 +7718,7 @@
 </v>
       </c>
       <c r="AA75" t="str">
-        <v>Contract Origination Date (business_segment)</v>
+        <v>Facility Origination Date (business_segment)</v>
       </c>
       <c r="AB75" t="str">
         <v/>
@@ -7517,7 +7768,7 @@
         <v>Raw</v>
       </c>
       <c r="N76" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read facility_id per counterparty.
+        <v xml:space="preserve">Representative facility_id per counterparty (MIN).
 </v>
       </c>
       <c r="O76" t="str">
@@ -7527,10 +7778,10 @@
         <v>Y</v>
       </c>
       <c r="Q76" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="R76" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_id per L3 desk segment.
+        <v xml:space="preserve">Representative facility_id per L3 desk segment (MIN).
 </v>
       </c>
       <c r="S76" t="str">
@@ -7540,10 +7791,10 @@
         <v>Y</v>
       </c>
       <c r="U76" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="V76" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_id per L2 portfolio segment.
+        <v xml:space="preserve">Representative facility_id per L2 portfolio segment (MIN).
 </v>
       </c>
       <c r="W76" t="str">
@@ -7553,10 +7804,10 @@
         <v>Y</v>
       </c>
       <c r="Y76" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="Z76" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_id per L1 business segment segment.
+        <v xml:space="preserve">Representative facility_id per L1 business segment (MIN).
 </v>
       </c>
       <c r="AA76" t="str">
@@ -7610,7 +7861,7 @@
         <v>Raw</v>
       </c>
       <c r="N77" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read facility_name per counterparty.
+        <v xml:space="preserve">Representative facility_name per counterparty (MIN alphabetical).
 </v>
       </c>
       <c r="O77" t="str">
@@ -7620,10 +7871,10 @@
         <v>Y</v>
       </c>
       <c r="Q77" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="R77" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_name per L3 desk segment.
+        <v xml:space="preserve">Representative facility_name per L3 desk segment (MIN alphabetical).
 </v>
       </c>
       <c r="S77" t="str">
@@ -7633,10 +7884,10 @@
         <v>Y</v>
       </c>
       <c r="U77" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="V77" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_name per L2 portfolio segment.
+        <v xml:space="preserve">Representative facility_name per L2 portfolio segment (MIN alphabetical).
 </v>
       </c>
       <c r="W77" t="str">
@@ -7646,10 +7897,10 @@
         <v>Y</v>
       </c>
       <c r="Y77" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="Z77" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_name per L1 business segment segment.
+        <v xml:space="preserve">Representative facility_name per L1 business segment (MIN alphabetical).
 </v>
       </c>
       <c r="AA77" t="str">
@@ -7664,14 +7915,14 @@
         <v>REF-012</v>
       </c>
       <c r="B78" t="str" xml:space="preserve">
-        <v xml:space="preserve">Type of credit facility (e.g., Term Loan, Revolver, Letter of Credit). Enables product-level segmentation, risk concentration analysis, and performance benchmarking.
+        <v xml:space="preserve">Type of credit facility (e.g., Term Loan, Revolver, Letter of Credit). Enables product-level segmentation, risk concentration analysis, and performance benchmarking. At facility level returns the facility type string; at aggregate levels returns the count of distinct active facilities in the segment for distribution analysis.
 </v>
       </c>
       <c r="C78" t="str">
         <v>Facility Type</v>
       </c>
       <c r="D78" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read facility_type from facility_exposure_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Direct lookup of facility_type from facility_master.
 </v>
       </c>
       <c r="E78" t="str">
@@ -7690,7 +7941,7 @@
         <v>Raw</v>
       </c>
       <c r="J78" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read facility_type from facility_exposure_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Direct lookup of facility_type from facility_master.
 </v>
       </c>
       <c r="K78" t="str">
@@ -7700,10 +7951,10 @@
         <v>Y</v>
       </c>
       <c r="M78" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="N78" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level facility_type) per counterparty.
+        <v xml:space="preserve">Not in primary specification at counterparty level. Supplementary: representative facility_type per counterparty (MIN).
 </v>
       </c>
       <c r="O78" t="str">
@@ -7716,7 +7967,7 @@
         <v>Agg</v>
       </c>
       <c r="R78" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_type per L3 desk segment.
+        <v xml:space="preserve">Count distinct active facilities per L3 desk segment. Provides facility distribution for product mix analysis.
 </v>
       </c>
       <c r="S78" t="str">
@@ -7729,7 +7980,7 @@
         <v>Agg</v>
       </c>
       <c r="V78" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_type per L2 portfolio segment.
+        <v xml:space="preserve">Count distinct active facilities per L2 portfolio segment. Provides facility distribution for product mix analysis.
 </v>
       </c>
       <c r="W78" t="str">
@@ -7742,7 +7993,7 @@
         <v>Agg</v>
       </c>
       <c r="Z78" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_type per L1 business segment segment.
+        <v xml:space="preserve">Count distinct active facilities per L1 business segment. Provides facility distribution for product mix analysis.
 </v>
       </c>
       <c r="AA78" t="str">
@@ -7757,14 +8008,14 @@
         <v>REF-013</v>
       </c>
       <c r="B79" t="str" xml:space="preserve">
-        <v xml:space="preserve">A classification used for reporting purposes in the FR 2590 regulatory report pertaining to financial institutions' credit exposures.
+        <v xml:space="preserve">FR 2590 regulatory classification for each facility exposure. Reads the fr2590_category_code from the facility exposure snapshot and joins to the fr2590_category_dim reference table to return the human-readable category name. Used for FR 2590 supervisory reporting and exposure segmentation by product type. Facility-level only — categorical values cannot be meaningfully aggregated to higher organizational levels.
 </v>
       </c>
       <c r="C79" t="str">
         <v>FR2590 Category</v>
       </c>
       <c r="D79" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated fr2590_category_code per facility.
+        <v xml:space="preserve">For each facility, read the fr2590_category_code from the latest facility_exposure_snapshot, then join to fr2590_category_dim to return the human-readable category_name. Uses MAX(category_name) to handle any duplicate exposure rows per facility on the same reporting date.
 </v>
       </c>
       <c r="E79" t="str">
@@ -7783,7 +8034,7 @@
         <v>Calc</v>
       </c>
       <c r="J79" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated fr2590_category_code per facility.
+        <v xml:space="preserve">For each facility, read the fr2590_category_code from the latest facility_exposure_snapshot, then join to fr2590_category_dim to return the human-readable category_name. Uses MAX(category_name) to handle any duplicate exposure rows per facility on the same reporting date.
 </v>
       </c>
       <c r="K79" t="str">
@@ -7793,10 +8044,10 @@
         <v>Y</v>
       </c>
       <c r="M79" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N79" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level fr2590_category_code per counterparty.
+        <v xml:space="preserve">Not applicable — FR2590 category is a per-facility categorical classification that cannot be meaningfully aggregated to counterparty level. Use facility-level drill-down for category distribution.
 </v>
       </c>
       <c r="O79" t="str">
@@ -7806,10 +8057,10 @@
         <v>Y</v>
       </c>
       <c r="Q79" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R79" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level fr2590_category_code per L3 desk segment.
+        <v xml:space="preserve">Not applicable — FR2590 category is a per-facility categorical classification. Desk-level analysis should use facility-level data grouped by FR2590 category as a dimension.
 </v>
       </c>
       <c r="S79" t="str">
@@ -7819,10 +8070,10 @@
         <v>Y</v>
       </c>
       <c r="U79" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V79" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level fr2590_category_code per L2 portfolio segment.
+        <v xml:space="preserve">Not applicable — FR2590 category is a per-facility categorical classification. Portfolio-level reporting uses FR2590 as a grouping dimension, not as an aggregated metric.
 </v>
       </c>
       <c r="W79" t="str">
@@ -7832,10 +8083,10 @@
         <v>Y</v>
       </c>
       <c r="Y79" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z79" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level fr2590_category_code per L1 business segment segment.
+        <v xml:space="preserve">Not applicable — FR2590 category is a per-facility categorical classification. Business segment reporting uses FR2590 as a grouping dimension, not as an aggregated metric.
 </v>
       </c>
       <c r="AA79" t="str">
@@ -8036,14 +8287,14 @@
         <v>REF-016</v>
       </c>
       <c r="B82" t="str" xml:space="preserve">
-        <v xml:space="preserve">Legal entity booking or owning the exposure. Critical for regulatory capital and entity-level reporting.
+        <v xml:space="preserve">Booking legal entity for each facility exposure. At facility level returns the entity name from the legal_entity table. At aggregate levels returns the count of distinct booking entities for risk concentration analysis.
 </v>
       </c>
       <c r="C82" t="str">
         <v>Legal Entity</v>
       </c>
       <c r="D82" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of legal_name from counterparty.
+        <v xml:space="preserve">Lookup legal_entity_name from legal_entity table via facility_exposure_snapshot.legal_entity_id.
 </v>
       </c>
       <c r="E82" t="str">
@@ -8062,7 +8313,7 @@
         <v>Raw</v>
       </c>
       <c r="J82" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of legal_name from counterparty.
+        <v xml:space="preserve">Lookup legal_entity_name from legal_entity table via facility_exposure_snapshot.legal_entity_id.
 </v>
       </c>
       <c r="K82" t="str">
@@ -8072,10 +8323,10 @@
         <v>Y</v>
       </c>
       <c r="M82" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="N82" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of legal_name from counterparty.
+        <v xml:space="preserve">Count of distinct booking legal entities per counterparty.
 </v>
       </c>
       <c r="O82" t="str">
@@ -8085,10 +8336,10 @@
         <v>Y</v>
       </c>
       <c r="Q82" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R82" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level legal_name per L3 desk segment.
+        <v xml:space="preserve">Count of distinct booking legal entities per L3 desk segment.
 </v>
       </c>
       <c r="S82" t="str">
@@ -8098,10 +8349,10 @@
         <v>Y</v>
       </c>
       <c r="U82" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V82" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level legal_name per L2 portfolio segment.
+        <v xml:space="preserve">Count of distinct booking legal entities per L2 portfolio segment.
 </v>
       </c>
       <c r="W82" t="str">
@@ -8111,10 +8362,10 @@
         <v>Y</v>
       </c>
       <c r="Y82" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z82" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level legal_name per L1 business segment segment.
+        <v xml:space="preserve">Count of distinct booking legal entities per L1 business segment.
 </v>
       </c>
       <c r="AA82" t="str">
@@ -8129,14 +8380,14 @@
         <v>REF-017</v>
       </c>
       <c r="B83" t="str" xml:space="preserve">
-        <v xml:space="preserve">Unique identifier assigned to legal entity in enterprise systems.
+        <v xml:space="preserve">Unique identifier for the booking legal entity. At facility level returns the entity ID. At aggregate levels returns count of distinct booking entities for entity concentration tracking.
 </v>
       </c>
       <c r="C83" t="str">
         <v>Legal Entity ID</v>
       </c>
       <c r="D83" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read legal_entity_id from facility_exposure_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Read legal_entity_id from facility_exposure_snapshot for each facility.
 </v>
       </c>
       <c r="E83" t="str">
@@ -8155,7 +8406,7 @@
         <v>Raw</v>
       </c>
       <c r="J83" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read legal_entity_id from facility_exposure_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Read legal_entity_id from facility_exposure_snapshot for each facility.
 </v>
       </c>
       <c r="K83" t="str">
@@ -8165,10 +8416,10 @@
         <v>Y</v>
       </c>
       <c r="M83" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="N83" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read legal_entity_id per counterparty.
+        <v xml:space="preserve">Count of distinct booking legal entities per counterparty.
 </v>
       </c>
       <c r="O83" t="str">
@@ -8178,10 +8429,10 @@
         <v>Y</v>
       </c>
       <c r="Q83" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R83" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level legal_entity_id per L3 desk segment.
+        <v xml:space="preserve">Count of distinct booking legal entities per L3 desk segment.
 </v>
       </c>
       <c r="S83" t="str">
@@ -8191,10 +8442,10 @@
         <v>Y</v>
       </c>
       <c r="U83" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V83" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level legal_entity_id per L2 portfolio segment.
+        <v xml:space="preserve">Count of distinct booking legal entities per L2 portfolio segment.
 </v>
       </c>
       <c r="W83" t="str">
@@ -8204,10 +8455,10 @@
         <v>Y</v>
       </c>
       <c r="Y83" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z83" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level legal_entity_id per L1 business segment segment.
+        <v xml:space="preserve">Count of distinct booking legal entities per L1 business segment.
 </v>
       </c>
       <c r="AA83" t="str">
@@ -8222,14 +8473,14 @@
         <v>REF-018</v>
       </c>
       <c r="B84" t="str" xml:space="preserve">
-        <v xml:space="preserve">Line of Business classification associated with exposure.
+        <v xml:space="preserve">Line of Business classification code associated with each exposure. Returns the hierarchical parent path code from the enterprise_business_taxonomy for the segment directly assigned to each facility via lob_segment_id. Used to group and filter exposures by organizational business line.
 </v>
       </c>
       <c r="C84" t="str">
         <v>Line of Business Level Name</v>
       </c>
       <c r="D84" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
+        <v xml:space="preserve">Direct lookup of parent code from enterprise_business_taxonomy via facility_master.lob_segment_id.
 </v>
       </c>
       <c r="E84" t="str">
@@ -8248,7 +8499,7 @@
         <v>Raw</v>
       </c>
       <c r="J84" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
+        <v xml:space="preserve">Direct lookup of parent code from enterprise_business_taxonomy via facility_master.lob_segment_id.
 </v>
       </c>
       <c r="K84" t="str">
@@ -8261,7 +8512,7 @@
         <v>Raw</v>
       </c>
       <c r="N84" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read parent per counterparty.
+        <v xml:space="preserve">Deterministic selection (MIN) of parent code across all facilities belonging to the counterparty.
 </v>
       </c>
       <c r="O84" t="str">
@@ -8271,10 +8522,10 @@
         <v>Y</v>
       </c>
       <c r="Q84" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="R84" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level parent per L3 desk segment.
+        <v xml:space="preserve">Direct parent code lookup per L3 desk segment. Groups facilities by their assigned EBT segment and returns the segment parent code.
 </v>
       </c>
       <c r="S84" t="str">
@@ -8284,10 +8535,10 @@
         <v>Y</v>
       </c>
       <c r="U84" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="V84" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level parent per L2 portfolio segment.
+        <v xml:space="preserve">Parent code at L2 portfolio level via one-hop EBT traversal.
 </v>
       </c>
       <c r="W84" t="str">
@@ -8297,10 +8548,10 @@
         <v>Y</v>
       </c>
       <c r="Y84" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="Z84" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level parent per L1 business segment segment.
+        <v xml:space="preserve">Parent code at L1 business segment level via two-hop EBT traversal.
 </v>
       </c>
       <c r="AA84" t="str">
@@ -8315,14 +8566,14 @@
         <v>REF-019</v>
       </c>
       <c r="B85" t="str" xml:space="preserve">
-        <v xml:space="preserve">Level 1 Line of Business hierarchy. Enables top-level organizational risk aggregation, representing the Department (e.g. Commercial Real Estate, Corporate Banking)
+        <v xml:space="preserve">Level 1 (Department) Line of Business hierarchy code. For each facility, traverses two hops up from the assigned EBT segment via parent_segment_id to reach the L1 department node, returning its parent path code. Enables top-level organizational risk aggregation (e.g. Corporate Banking, Commercial Real Estate).
 </v>
       </c>
       <c r="C85" t="str">
-        <v>Line of Business  L1</v>
+        <v>Line of Business L1</v>
       </c>
       <c r="D85" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
+        <v xml:space="preserve">Traverse two hops up the EBT hierarchy from facility lob_segment_id to reach the L1 department ancestor and return its parent code.
 </v>
       </c>
       <c r="E85" t="str">
@@ -8341,11 +8592,11 @@
         <v>Raw</v>
       </c>
       <c r="J85" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
+        <v xml:space="preserve">Traverse two hops up the EBT hierarchy from facility lob_segment_id to reach the L1 department ancestor and return its parent code.
 </v>
       </c>
       <c r="K85" t="str">
-        <v>Line of Business  L1 (facility)</v>
+        <v>Line of Business L1 (facility)</v>
       </c>
       <c r="L85" t="str">
         <v>Y</v>
@@ -8354,50 +8605,50 @@
         <v>Raw</v>
       </c>
       <c r="N85" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read parent per counterparty.
+        <v xml:space="preserve">Deterministic selection (MIN) of L1 department parent code across all facilities belonging to the counterparty.
 </v>
       </c>
       <c r="O85" t="str">
-        <v>Line of Business  L1 (counterparty)</v>
+        <v>Line of Business L1 (counterparty)</v>
       </c>
       <c r="P85" t="str">
         <v>Y</v>
       </c>
       <c r="Q85" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="R85" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level parent per L3 desk segment.
+        <v xml:space="preserve">For each L3 desk, traverse two hops up to the L1 department ancestor and return its parent code.
 </v>
       </c>
       <c r="S85" t="str">
-        <v>Line of Business  L1 (desk)</v>
+        <v>Line of Business L1 (desk)</v>
       </c>
       <c r="T85" t="str">
         <v>Y</v>
       </c>
       <c r="U85" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="V85" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level parent per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 portfolio, traverse one hop up to the L1 department ancestor and return its parent code.
 </v>
       </c>
       <c r="W85" t="str">
-        <v>Line of Business  L1 (portfolio)</v>
+        <v>Line of Business L1 (portfolio)</v>
       </c>
       <c r="X85" t="str">
         <v>Y</v>
       </c>
       <c r="Y85" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="Z85" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level parent per L1 business segment segment.
+        <v xml:space="preserve">At L1 business segment level, the segment IS the L1 department. Return its own parent code directly.
 </v>
       </c>
       <c r="AA85" t="str">
-        <v>Line of Business  L1 (business_segment)</v>
+        <v>Line of Business L1 (business_segment)</v>
       </c>
       <c r="AB85" t="str">
         <v/>
@@ -8408,14 +8659,14 @@
         <v>REF-020</v>
       </c>
       <c r="B86" t="str" xml:space="preserve">
-        <v xml:space="preserve">Level 2 Line of Business hierarchy for intermediate aggregation and reporting, representing the Portfolio within the L1 LoB (e.g., CRE &gt; Office)
+        <v xml:space="preserve">Level 2 (Portfolio) Line of Business hierarchy code. For each facility, traverses one hop up from the assigned EBT segment via parent_segment_id to reach the L2 portfolio node, returning its parent path code. Enables detailed business segment analysis (e.g. CRE &gt; Office).
 </v>
       </c>
       <c r="C86" t="str">
         <v>Line of Business L2</v>
       </c>
       <c r="D86" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
+        <v xml:space="preserve">Traverse one hop up the EBT hierarchy from facility lob_segment_id to reach the L2 portfolio ancestor and return its parent code.
 </v>
       </c>
       <c r="E86" t="str">
@@ -8434,7 +8685,7 @@
         <v>Raw</v>
       </c>
       <c r="J86" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
+        <v xml:space="preserve">Traverse one hop up the EBT hierarchy from facility lob_segment_id to reach the L2 portfolio ancestor and return its parent code.
 </v>
       </c>
       <c r="K86" t="str">
@@ -8447,7 +8698,7 @@
         <v>Raw</v>
       </c>
       <c r="N86" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read parent per counterparty.
+        <v xml:space="preserve">Deterministic selection (MIN) of L2 portfolio parent code across all facilities belonging to the counterparty.
 </v>
       </c>
       <c r="O86" t="str">
@@ -8457,10 +8708,10 @@
         <v>Y</v>
       </c>
       <c r="Q86" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="R86" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level parent per L3 desk segment.
+        <v xml:space="preserve">For each L3 desk, traverse one hop up to the L2 portfolio ancestor and return its parent code.
 </v>
       </c>
       <c r="S86" t="str">
@@ -8470,10 +8721,10 @@
         <v>Y</v>
       </c>
       <c r="U86" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="V86" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level parent per L2 portfolio segment.
+        <v xml:space="preserve">At L2 portfolio level, the segment IS the L2 portfolio. Return its own parent code directly.
 </v>
       </c>
       <c r="W86" t="str">
@@ -8483,10 +8734,10 @@
         <v>Y</v>
       </c>
       <c r="Y86" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="Z86" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level parent per L1 business segment segment.
+        <v xml:space="preserve">For each L1 business segment, returns the L2 portfolio parent codes of child portfolios. Uses MIN for deterministic string selection.
 </v>
       </c>
       <c r="AA86" t="str">
@@ -8501,14 +8752,14 @@
         <v>REF-021</v>
       </c>
       <c r="B87" t="str" xml:space="preserve">
-        <v xml:space="preserve">Level 3 Line of Business hierarchy for detailed business segmentation, representing the Desk within the L2 LoB (e.g. CRE &gt; Office &gt; Lease Up Desk)
+        <v xml:space="preserve">Level 3 (Desk) Line of Business hierarchy code. Returns the parent path code of the EBT segment directly assigned to each facility via lob_segment_id. Represents the most granular organizational segment view (e.g. CRE &gt; Office &gt; Lease Up Desk).
 </v>
       </c>
       <c r="C87" t="str">
         <v>Line of Business L3</v>
       </c>
       <c r="D87" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
+        <v xml:space="preserve">Direct lookup of parent code from enterprise_business_taxonomy via facility_master.lob_segment_id. For L3-assigned facilities this returns the L3 desk parent code.
 </v>
       </c>
       <c r="E87" t="str">
@@ -8527,7 +8778,7 @@
         <v>Raw</v>
       </c>
       <c r="J87" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
+        <v xml:space="preserve">Direct lookup of parent code from enterprise_business_taxonomy via facility_master.lob_segment_id. For L3-assigned facilities this returns the L3 desk parent code.
 </v>
       </c>
       <c r="K87" t="str">
@@ -8540,7 +8791,7 @@
         <v>Raw</v>
       </c>
       <c r="N87" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read parent per counterparty.
+        <v xml:space="preserve">Deterministic selection (MIN) of L3 desk parent code across all facilities belonging to the counterparty.
 </v>
       </c>
       <c r="O87" t="str">
@@ -8550,10 +8801,10 @@
         <v>Y</v>
       </c>
       <c r="Q87" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="R87" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level parent per L3 desk segment.
+        <v xml:space="preserve">Direct parent code lookup per L3 desk segment. The desk level IS the L3 level, so return the segment own parent code.
 </v>
       </c>
       <c r="S87" t="str">
@@ -8563,10 +8814,10 @@
         <v>Y</v>
       </c>
       <c r="U87" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="V87" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level parent per L2 portfolio segment.
+        <v xml:space="preserve">L3 desk parent codes rolled up to L2 portfolio level. Returns MIN of desk-level parent codes within each portfolio.
 </v>
       </c>
       <c r="W87" t="str">
@@ -8576,10 +8827,10 @@
         <v>Y</v>
       </c>
       <c r="Y87" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="Z87" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level parent per L1 business segment segment.
+        <v xml:space="preserve">L3 desk parent codes rolled up to L1 business segment level. Returns MIN of desk-level parent codes within each segment.
 </v>
       </c>
       <c r="AA87" t="str">
@@ -8594,7 +8845,7 @@
         <v>REF-022</v>
       </c>
       <c r="B88" t="str" xml:space="preserve">
-        <v xml:space="preserve">Contractual date on which the facility or loan is scheduled to mature. Used to assess duration exposure, refinancing risk, and liquidity planning.
+        <v xml:space="preserve">Contractual date on which the facility or loan is scheduled to mature. Used to assess duration exposure, refinancing risk, and liquidity planning. At aggregate levels, returns the nearest (MIN) maturity date as a risk indicator.
 </v>
       </c>
       <c r="C88" t="str">
@@ -8630,10 +8881,10 @@
         <v>Y</v>
       </c>
       <c r="M88" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N88" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level maturity_date) per counterparty.
+        <v xml:space="preserve">Nearest (MIN) maturity date across all facilities per counterparty.
 </v>
       </c>
       <c r="O88" t="str">
@@ -8643,10 +8894,10 @@
         <v>Y</v>
       </c>
       <c r="Q88" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R88" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level maturity_date per L3 desk segment.
+        <v xml:space="preserve">Nearest (MIN) maturity date across all facilities per L3 desk segment.
 </v>
       </c>
       <c r="S88" t="str">
@@ -8656,10 +8907,10 @@
         <v>Y</v>
       </c>
       <c r="U88" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V88" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level maturity_date per L2 portfolio segment.
+        <v xml:space="preserve">Nearest (MIN) maturity date across all facilities per L2 portfolio segment.
 </v>
       </c>
       <c r="W88" t="str">
@@ -8669,10 +8920,10 @@
         <v>Y</v>
       </c>
       <c r="Y88" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z88" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level maturity_date per L1 business segment segment.
+        <v xml:space="preserve">Nearest (MIN) maturity date across all facilities per L1 business segment.
 </v>
       </c>
       <c r="AA88" t="str">
@@ -8780,14 +9031,15 @@
         <v>REF-024</v>
       </c>
       <c r="B90" t="str" xml:space="preserve">
-        <v xml:space="preserve">Identifiers of counterparties participating in the credit structures or facility as multiple-borrowers. Enables exposure attribution and concentration analysis.
+        <v xml:space="preserve">Count of distinct counterparties participating in credit structures. At counterparty level, returns the counterparty identifier directly. At desk and higher levels, counts distinct counterparties per segment to measure borrower concentration and multi-borrower facility exposure. Enables concentration analysis, relationship tracking, and syndicated deal monitoring.
 </v>
       </c>
       <c r="C90" t="str">
         <v>Participating Counterparty IDs</v>
       </c>
       <c r="D90" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">Direct lookup of counterparty_id from facility_master for each facility.
+Returns the counterparty associated with the facility.
 </v>
       </c>
       <c r="E90" t="str">
@@ -8806,7 +9058,8 @@
         <v>Raw</v>
       </c>
       <c r="J90" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">Direct lookup of counterparty_id from facility_master for each facility.
+Returns the counterparty associated with the facility.
 </v>
       </c>
       <c r="K90" t="str">
@@ -8819,7 +9072,8 @@
         <v>Raw</v>
       </c>
       <c r="N90" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">Identity: returns counterparty_id for each active counterparty.
+Enables direct counterparty identification in drill-down views.
 </v>
       </c>
       <c r="O90" t="str">
@@ -8829,10 +9083,14 @@
         <v>Y</v>
       </c>
       <c r="Q90" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R90" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L3 desk segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOAD all facilities from l2.facility_master
+  2. JOIN l1.enterprise_business_taxonomy on lob_segment_id
+  3. COMPUTE COUNT(DISTINCT counterparty_id) — unique borrowers per desk
+Measures borrower concentration within each desk.
 </v>
       </c>
       <c r="S90" t="str">
@@ -8842,10 +9100,12 @@
         <v>Y</v>
       </c>
       <c r="U90" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V90" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. COMPUTE COUNT(DISTINCT counterparty_id) — unique borrowers per portfolio
 </v>
       </c>
       <c r="W90" t="str">
@@ -8855,10 +9115,12 @@
         <v>Y</v>
       </c>
       <c r="Y90" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z90" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L1 business segment segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. COMPUTE COUNT(DISTINCT counterparty_id) — unique borrowers per segment
 </v>
       </c>
       <c r="AA90" t="str">
@@ -8873,14 +9135,14 @@
         <v>REF-025</v>
       </c>
       <c r="B91" t="str" xml:space="preserve">
-        <v xml:space="preserve">Product classification assigned to the contract offering. Supports product- level segmentation and performance analysis.
+        <v xml:space="preserve">Total drawn exposure (bank-share-adjusted) segmented by product classification from the Enterprise Product Taxonomy. Supports portfolio composition analysis and product-level concentration monitoring. At facility level, returns the facility's exposure in local currency. At aggregate levels, converts to USD via FX rate.
 </v>
       </c>
       <c r="C91" t="str">
         <v>Product</v>
       </c>
       <c r="D91" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(product_id) per facility from facility_exposure_snapshot.
+        <v xml:space="preserve">SUM(drawn_amount × bank_share_pct / 100) per facility. Local currency. Product classification available via enterprise_product_taxonomy join.
 </v>
       </c>
       <c r="E91" t="str">
@@ -8899,7 +9161,7 @@
         <v>Agg</v>
       </c>
       <c r="J91" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(product_id) per facility from facility_exposure_snapshot.
+        <v xml:space="preserve">SUM(drawn_amount × bank_share_pct / 100) per facility. Local currency. Product classification available via enterprise_product_taxonomy join.
 </v>
       </c>
       <c r="K91" t="str">
@@ -8912,7 +9174,7 @@
         <v>Agg</v>
       </c>
       <c r="N91" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level product_id per counterparty.
+        <v xml:space="preserve">SUM of facility-level drawn exposure (bank-share-adjusted, USD-converted) per counterparty. FX conversion applied.
 </v>
       </c>
       <c r="O91" t="str">
@@ -8925,7 +9187,7 @@
         <v>Agg</v>
       </c>
       <c r="R91" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level product_id per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level drawn exposure (bank-share-adjusted, USD-converted) per L3 desk segment via EBT hierarchy.
 </v>
       </c>
       <c r="S91" t="str">
@@ -8938,7 +9200,7 @@
         <v>Agg</v>
       </c>
       <c r="V91" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level product_id per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level drawn exposure (bank-share-adjusted, USD-converted) per L2 portfolio segment via EBT hierarchy (one hop up).
 </v>
       </c>
       <c r="W91" t="str">
@@ -8951,7 +9213,7 @@
         <v>Agg</v>
       </c>
       <c r="Z91" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level product_id per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level drawn exposure (bank-share-adjusted, USD-converted) per L1 business segment via EBT hierarchy (two hops up).
 </v>
       </c>
       <c r="AA91" t="str">
@@ -8966,14 +9228,14 @@
         <v>REF-026</v>
       </c>
       <c r="B92" t="str" xml:space="preserve">
-        <v xml:space="preserve">Geographic region classification tied to location of deal origination, supporting portfolio segmentation and concentration monitoring.
+        <v xml:space="preserve">Total drawn exposure (bank-share-adjusted) segmented by geographic region derived from counterparty country of domicile. Join chain: counterparty.country_code → country_dim.region_code → region_dim. Supports regional concentration monitoring and geographic risk diversification analysis per GSIB standards.
 </v>
       </c>
       <c r="C92" t="str">
         <v>Region</v>
       </c>
       <c r="D92" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of region_code from counterparty.
+        <v xml:space="preserve">SUM(drawn_amount × bank_share_pct / 100) per facility. Local currency. Region lookup: counterparty → country_dim → region_dim for context.
 </v>
       </c>
       <c r="E92" t="str">
@@ -8989,10 +9251,10 @@
         <v>Y</v>
       </c>
       <c r="I92" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="J92" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of region_code from counterparty.
+        <v xml:space="preserve">SUM(drawn_amount × bank_share_pct / 100) per facility. Local currency. Region lookup: counterparty → country_dim → region_dim for context.
 </v>
       </c>
       <c r="K92" t="str">
@@ -9002,10 +9264,10 @@
         <v>Y</v>
       </c>
       <c r="M92" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="N92" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of region_code from counterparty.
+        <v xml:space="preserve">SUM of facility-level drawn exposure (bank-share-adjusted, USD-converted) per counterparty. Region derived from counterparty.country_code → country_dim.region_code → region_dim.region_name.
 </v>
       </c>
       <c r="O92" t="str">
@@ -9018,7 +9280,7 @@
         <v>Agg</v>
       </c>
       <c r="R92" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level region_code per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level drawn exposure (bank-share-adjusted, USD-converted) per L3 desk segment. Region context via counterparty → country_dim → region_dim.
 </v>
       </c>
       <c r="S92" t="str">
@@ -9031,7 +9293,7 @@
         <v>Agg</v>
       </c>
       <c r="V92" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level region_code per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level drawn exposure (bank-share-adjusted, USD-converted) per L2 portfolio segment via EBT hierarchy (one hop up).
 </v>
       </c>
       <c r="W92" t="str">
@@ -9044,7 +9306,7 @@
         <v>Agg</v>
       </c>
       <c r="Z92" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level region_code per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level drawn exposure (bank-share-adjusted, USD-converted) per L1 business segment via EBT hierarchy (two hops up).
 </v>
       </c>
       <c r="AA92" t="str">
@@ -9707,17 +9969,17 @@
     </row>
     <row r="100" xml:space="preserve">
       <c r="A100" t="str">
-        <v>RSK-001</v>
+        <v>REF-034</v>
       </c>
       <c r="B100" t="str" xml:space="preserve">
-        <v xml:space="preserve">Risk rating tier derived from counterparty probability of default (PD). Each counterparty's pd_annual is matched against the risk_rating_tier_dim reference table (pd_min_pct / pd_max_pct boundaries) to assign a tier classification. At facility level, the tier is inherited from the owning counterparty. At aggregate levels, MAX (worst-case) tier ordinal is reported.
+        <v xml:space="preserve">Facility activity status indicator. At facility level, reads the is_active_flag from facility_master and returns 1 (active) or 0 (inactive). At counterparty level, returns 1 if any of the counterparty's facilities are active (boolean OR). Provides a baseline portfolio activity measure for CRO reporting and data quality monitoring.
 </v>
       </c>
       <c r="C100" t="str">
-        <v>Risk Rating Tier</v>
+        <v>Active Flag</v>
       </c>
       <c r="D100" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each facility, inherit the risk rating tier from the owning counterparty. Join facility_master to counterparty, then range-match counterparty pd_annual against risk_rating_tier_dim to derive the tier ordinal (display_order).
+        <v xml:space="preserve">Read is_active_flag from facility_master. Returns 1 if the facility is active (is_active_flag = 'Y'), 0 otherwise. No date filtering required as is_active_flag reflects current status.
 </v>
       </c>
       <c r="E100" t="str">
@@ -9733,66 +9995,66 @@
         <v>Y</v>
       </c>
       <c r="I100" t="str">
-        <v>Calc</v>
+        <v>Raw</v>
       </c>
       <c r="J100" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each facility, inherit the risk rating tier from the owning counterparty. Join facility_master to counterparty, then range-match counterparty pd_annual against risk_rating_tier_dim to derive the tier ordinal (display_order).
+        <v xml:space="preserve">Read is_active_flag from facility_master. Returns 1 if the facility is active (is_active_flag = 'Y'), 0 otherwise. No date filtering required as is_active_flag reflects current status.
 </v>
       </c>
       <c r="K100" t="str">
-        <v>Risk Rating Tier (facility)</v>
+        <v>Active Flag (facility)</v>
       </c>
       <c r="L100" t="str">
         <v>Y</v>
       </c>
       <c r="M100" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="N100" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each counterparty, look up pd_annual and range-match against risk_rating_tier_dim where pd_annual &gt;= pd_min_pct AND pd_annual &lt; pd_max_pct. Returns the tier ordinal (display_order). Counterparties with NULL PD receive tier 0 (unrated).
+        <v xml:space="preserve">For each counterparty, check if any of its facilities are active. Uses MAX over the facility-level boolean flags — if any facility is active (1), the counterparty is considered active (1). Returns 0 only if ALL facilities for the counterparty are inactive.
 </v>
       </c>
       <c r="O100" t="str">
-        <v>Risk Rating Tier (counterparty)</v>
+        <v>Active Flag (counterparty)</v>
       </c>
       <c r="P100" t="str">
         <v>Y</v>
       </c>
       <c r="Q100" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R100" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst-case (MAX) risk rating tier ordinal across all counterparties in the L3 desk segment. Higher ordinal = riskier tier. Full tier distribution available via counterparty-level drill-down.
+        <v xml:space="preserve">Not applicable — active flag is a facility/counterparty level indicator. Desk-level portfolio activity analysis should use count-based metrics or exposure-weighted activity rates.
 </v>
       </c>
       <c r="S100" t="str">
-        <v>Risk Rating Tier (desk)</v>
+        <v>Active Flag (desk)</v>
       </c>
       <c r="T100" t="str">
         <v>Y</v>
       </c>
       <c r="U100" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V100" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst-case (MAX) risk rating tier ordinal per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
+        <v xml:space="preserve">Not applicable — active flag is a facility/counterparty level indicator. Portfolio-level analysis should aggregate exposure amounts filtered by active status.
 </v>
       </c>
       <c r="W100" t="str">
-        <v>Risk Rating Tier (portfolio)</v>
+        <v>Active Flag (portfolio)</v>
       </c>
       <c r="X100" t="str">
         <v>Y</v>
       </c>
       <c r="Y100" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z100" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst-case (MAX) risk rating tier ordinal per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
+        <v xml:space="preserve">Not applicable — active flag is a facility/counterparty level indicator. Business segment analysis should aggregate exposure amounts filtered by active status.
 </v>
       </c>
       <c r="AA100" t="str">
-        <v>Risk Rating Tier (business_segment)</v>
+        <v>Active Flag (business_segment)</v>
       </c>
       <c r="AB100" t="str">
         <v/>
@@ -9800,17 +10062,17 @@
     </row>
     <row r="101" xml:space="preserve">
       <c r="A101" t="str">
-        <v>RSK-002</v>
+        <v>RSK-001</v>
       </c>
       <c r="B101" t="str" xml:space="preserve">
-        <v xml:space="preserve">Current external credit agency rating assigned to the obligor. Used for benchmarking, regulatory reporting, and external credit risk validation. Sourced based on external Rating provider (S&amp;P, Moodys, Fitch) - populated based on firm's preferred recognized rating provider.
+        <v xml:space="preserve">Risk rating tier derived from counterparty probability of default (PD). Each counterparty's pd_annual is matched against the risk_rating_tier_dim reference table (pd_min_pct / pd_max_pct boundaries) to assign a tier classification. At facility level, the tier is inherited from the owning counterparty. At aggregate levels, MAX (worst-case) tier ordinal is reported.
 </v>
       </c>
       <c r="C101" t="str">
-        <v>Risk Rating - External Rating</v>
+        <v>Risk Rating Tier</v>
       </c>
       <c r="D101" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read external_risk_rating from position for each facility as-of reporting date.
+        <v xml:space="preserve">For each facility, inherit the risk rating tier from the owning counterparty. Join facility_master to counterparty, then range-match counterparty pd_annual against risk_rating_tier_dim to derive the tier ordinal (display_order).
 </v>
       </c>
       <c r="E101" t="str">
@@ -9826,66 +10088,66 @@
         <v>Y</v>
       </c>
       <c r="I101" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="J101" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read external_risk_rating from position for each facility as-of reporting date.
+        <v xml:space="preserve">For each facility, inherit the risk rating tier from the owning counterparty. Join facility_master to counterparty, then range-match counterparty pd_annual against risk_rating_tier_dim to derive the tier ordinal (display_order).
 </v>
       </c>
       <c r="K101" t="str">
-        <v>Risk Rating - External Rating (facility)</v>
+        <v>Risk Rating Tier (facility)</v>
       </c>
       <c r="L101" t="str">
         <v>Y</v>
       </c>
       <c r="M101" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="N101" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read external_risk_rating per counterparty.
+        <v xml:space="preserve">For each counterparty, look up pd_annual and range-match against risk_rating_tier_dim where pd_annual &gt;= pd_min_pct AND pd_annual &lt; pd_max_pct. Returns the tier ordinal (display_order). Counterparties with NULL PD receive tier 0 (unrated).
 </v>
       </c>
       <c r="O101" t="str">
-        <v>Risk Rating - External Rating (counterparty)</v>
+        <v>Risk Rating Tier (counterparty)</v>
       </c>
       <c r="P101" t="str">
         <v>Y</v>
       </c>
       <c r="Q101" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="R101" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level external_risk_rating per L3 desk segment.
+        <v xml:space="preserve">Worst-case (MAX) risk rating tier ordinal across all counterparties in the L3 desk segment. Higher ordinal = riskier tier. Full tier distribution available via counterparty-level drill-down.
 </v>
       </c>
       <c r="S101" t="str">
-        <v>Risk Rating - External Rating (desk)</v>
+        <v>Risk Rating Tier (desk)</v>
       </c>
       <c r="T101" t="str">
         <v>Y</v>
       </c>
       <c r="U101" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="V101" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level external_risk_rating per L2 portfolio segment.
+        <v xml:space="preserve">Worst-case (MAX) risk rating tier ordinal per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
 </v>
       </c>
       <c r="W101" t="str">
-        <v>Risk Rating - External Rating (portfolio)</v>
+        <v>Risk Rating Tier (portfolio)</v>
       </c>
       <c r="X101" t="str">
         <v>Y</v>
       </c>
       <c r="Y101" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="Z101" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level external_risk_rating per L1 business segment segment.
+        <v xml:space="preserve">Worst-case (MAX) risk rating tier ordinal per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
 </v>
       </c>
       <c r="AA101" t="str">
-        <v>Risk Rating - External Rating (business_segment)</v>
+        <v>Risk Rating Tier (business_segment)</v>
       </c>
       <c r="AB101" t="str">
         <v/>
@@ -9893,17 +10155,26 @@
     </row>
     <row r="102" xml:space="preserve">
       <c r="A102" t="str">
-        <v>RSK-003</v>
+        <v>RSK-002</v>
       </c>
       <c r="B102" t="str" xml:space="preserve">
-        <v xml:space="preserve">The institution’s internally assigned credit risk grade for a borrower, facility, or exposure as of a given date, reflecting its assessment of default risk according to the firm’s internal rating scale/model.
+        <v xml:space="preserve">External credit agency rating expressed as a numeric notch value from the rating_scale_dim. At facility/counterparty levels, returns the raw notch of the external rating. At aggregate levels (desk, portfolio, segment), computes the exposure-weighted average notch across all positions, rounded to the nearest whole notch. Lower notch = better rating (e.g., 1=AAA, 21=D). Sourced from position.external_risk_rating, mapped to rating_scale_dim.rating_value.
 </v>
       </c>
       <c r="C102" t="str">
-        <v>Risk Rating - Internal Risk Rating</v>
+        <v>Risk Rating - External Rating</v>
       </c>
       <c r="D102" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read internal_risk_rating from facility_risk_snapshot for each facility.
+        <v xml:space="preserve">1. LOAD  l2.position  (pos)
+   WHERE pos.as_of_date = :as_of_date
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = pos.facility_id
+   WHERE fm.is_active_flag = 'Y'
+3. LEFT JOIN  l1.rating_scale_dim  (rs)
+   ON    rs.rating_notch = pos.external_risk_rating
+   AND   rs.is_current_flag = 'Y'
+4. COMPUTE
+   metric_value = rs.rating_value
 </v>
       </c>
       <c r="E102" t="str">
@@ -9922,63 +10193,109 @@
         <v>Raw</v>
       </c>
       <c r="J102" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read internal_risk_rating from facility_risk_snapshot for each facility.
+        <v xml:space="preserve">1. LOAD  l2.position  (pos)
+   WHERE pos.as_of_date = :as_of_date
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = pos.facility_id
+   WHERE fm.is_active_flag = 'Y'
+3. LEFT JOIN  l1.rating_scale_dim  (rs)
+   ON    rs.rating_notch = pos.external_risk_rating
+   AND   rs.is_current_flag = 'Y'
+4. COMPUTE
+   metric_value = rs.rating_value
 </v>
       </c>
       <c r="K102" t="str">
-        <v>Risk Rating - Internal Risk Rating (facility)</v>
+        <v>Risk Rating - External Rating (facility)</v>
       </c>
       <c r="L102" t="str">
         <v>Y</v>
       </c>
       <c r="M102" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="N102" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with internal risk rating per counterparty.
+        <v xml:space="preserve">1. LOAD  l2.position  (pos)
+   WHERE pos.as_of_date = :as_of_date
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = pos.facility_id
+3. LEFT JOIN  l1.rating_scale_dim  (rs)
+   ON    rs.rating_notch = pos.external_risk_rating
+4. GROUP BY fm.counterparty_id
+5. COMPUTE
+   metric_value = ROUND(AVG(rating_value))
 </v>
       </c>
       <c r="O102" t="str">
-        <v>Risk Rating - Internal Risk Rating (counterparty)</v>
+        <v>Risk Rating - External Rating (counterparty)</v>
       </c>
       <c r="P102" t="str">
         <v>Y</v>
       </c>
       <c r="Q102" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R102" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with internal risk rating per L3 desk segment.
+        <v xml:space="preserve">1. LOAD  l2.position  (pos)
+   WHERE pos.as_of_date = :as_of_date
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = pos.facility_id
+3. LEFT JOIN  l1.rating_scale_dim  (rs)
+   ON    rs.rating_notch = pos.external_risk_rating
+4. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt)
+   ON    ebt.managed_segment_id = fm.lob_segment_id
+     AND ebt.is_current_flag = 'Y'
+5. GROUP BY ebt.managed_segment_id
+6. COMPUTE
+   metric_value = ROUND(AVG(rating_value))
 </v>
       </c>
       <c r="S102" t="str">
-        <v>Risk Rating - Internal Risk Rating (desk)</v>
+        <v>Risk Rating - External Rating (desk)</v>
       </c>
       <c r="T102" t="str">
         <v>Y</v>
       </c>
       <c r="U102" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V102" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with internal risk rating per L2 portfolio segment.
+        <v xml:space="preserve">1. LOAD  l2.position  (pos)
+   WHERE pos.as_of_date = :as_of_date
+2. JOIN  l2.facility_master  (fm)
+3. LEFT JOIN  l1.rating_scale_dim  (rs)
+   ON    rs.rating_notch = pos.external_risk_rating
+4. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l3, ebt_l2)
+   Traverse L3 -&gt; L2 via parent_segment_id
+5. GROUP BY ebt_l2.managed_segment_id
+6. COMPUTE
+   metric_value = ROUND(AVG(rating_value))
 </v>
       </c>
       <c r="W102" t="str">
-        <v>Risk Rating - Internal Risk Rating (portfolio)</v>
+        <v>Risk Rating - External Rating (portfolio)</v>
       </c>
       <c r="X102" t="str">
         <v>Y</v>
       </c>
       <c r="Y102" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z102" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with internal risk rating per L1 business segment.
+        <v xml:space="preserve">1. LOAD  l2.position  (pos)
+   WHERE pos.as_of_date = :as_of_date
+2. JOIN  l2.facility_master  (fm)
+3. LEFT JOIN  l1.rating_scale_dim  (rs)
+   ON    rs.rating_notch = pos.external_risk_rating
+4. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l3, ebt_l2, ebt_l1)
+   Traverse L3 -&gt; L2 -&gt; L1 via parent_segment_id chain
+5. GROUP BY ebt_l1.managed_segment_id
+6. COMPUTE
+   metric_value = ROUND(AVG(rating_value))
 </v>
       </c>
       <c r="AA102" t="str">
-        <v>Risk Rating - Internal Risk Rating (business_segment)</v>
+        <v>Risk Rating - External Rating (business_segment)</v>
       </c>
       <c r="AB102" t="str">
         <v/>
@@ -9986,17 +10303,17 @@
     </row>
     <row r="103" xml:space="preserve">
       <c r="A103" t="str">
-        <v>RSK-004</v>
+        <v>RSK-003</v>
       </c>
       <c r="B103" t="str" xml:space="preserve">
-        <v xml:space="preserve">Derived directional indicator reflecting movement in external credit agency rating and changes month over month, which depicts the month-over-month change reflecting an upgrade (e.g. A to AA), downgrade (e.g., B+ to B-) or stable (remaing constant month over month), as compared to prior month reporting periods. Note when this is displayed at an aggregated Line of Business or portfolio level, it is determined by the month-over-month change of the average rating at this level. Supports benchmarking against market perception and helps validate internal risk assessment trends.
+        <v xml:space="preserve">The institution’s internally assigned credit risk grade for a borrower, facility, or exposure as of a given date, reflecting its assessment of default risk according to the firm’s internal rating scale/model.
 </v>
       </c>
       <c r="C103" t="str">
-        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable)</v>
+        <v>Risk Rating - Internal Risk Rating</v>
       </c>
       <c r="D103" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility as-of reporting date.
+        <v xml:space="preserve">Read internal_risk_rating from facility_risk_snapshot for each facility.
 </v>
       </c>
       <c r="E103" t="str">
@@ -10015,11 +10332,11 @@
         <v>Raw</v>
       </c>
       <c r="J103" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility as-of reporting date.
+        <v xml:space="preserve">Read internal_risk_rating from facility_risk_snapshot for each facility.
 </v>
       </c>
       <c r="K103" t="str">
-        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable) (facility)</v>
+        <v>Risk Rating - Internal Risk Rating (facility)</v>
       </c>
       <c r="L103" t="str">
         <v>Y</v>
@@ -10028,11 +10345,11 @@
         <v>Agg</v>
       </c>
       <c r="N103" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_status per counterparty.
+        <v xml:space="preserve">COUNT of facilities with internal risk rating per counterparty.
 </v>
       </c>
       <c r="O103" t="str">
-        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable) (counterparty)</v>
+        <v>Risk Rating - Internal Risk Rating (counterparty)</v>
       </c>
       <c r="P103" t="str">
         <v>Y</v>
@@ -10041,11 +10358,11 @@
         <v>Agg</v>
       </c>
       <c r="R103" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_status per L3 desk segment.
+        <v xml:space="preserve">COUNT of facilities with internal risk rating per L3 desk segment.
 </v>
       </c>
       <c r="S103" t="str">
-        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable) (desk)</v>
+        <v>Risk Rating - Internal Risk Rating (desk)</v>
       </c>
       <c r="T103" t="str">
         <v>Y</v>
@@ -10054,11 +10371,11 @@
         <v>Agg</v>
       </c>
       <c r="V103" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_status per L2 portfolio segment.
+        <v xml:space="preserve">COUNT of facilities with internal risk rating per L2 portfolio segment.
 </v>
       </c>
       <c r="W103" t="str">
-        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable) (portfolio)</v>
+        <v>Risk Rating - Internal Risk Rating (portfolio)</v>
       </c>
       <c r="X103" t="str">
         <v>Y</v>
@@ -10067,11 +10384,11 @@
         <v>Agg</v>
       </c>
       <c r="Z103" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_status per L1 business segment segment.
+        <v xml:space="preserve">COUNT of facilities with internal risk rating per L1 business segment.
 </v>
       </c>
       <c r="AA103" t="str">
-        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable) (business_segment)</v>
+        <v>Risk Rating - Internal Risk Rating (business_segment)</v>
       </c>
       <c r="AB103" t="str">
         <v/>
@@ -10079,17 +10396,17 @@
     </row>
     <row r="104" xml:space="preserve">
       <c r="A104" t="str">
-        <v>RSK-005</v>
+        <v>RSK-004</v>
       </c>
       <c r="B104" t="str" xml:space="preserve">
-        <v xml:space="preserve">Numerical representation of external risk rating migration (month over month changes) expressed in notch movement (positive or negative). Positive step changes are identified when there is an upgrade, from A to AA and the step change is +1, where as the negative step change is identified when there is a downgrade from B+ to B- and the step change is -1. Note when this is displayed at an aggregated Line of Business or portfolio level, it is determined by the month-over-month change of the average rating at this level. Quantifies magnitude of credit change and enables portfolio-level migration analysis, stress testing sensitivity, and risk trend measurement.
+        <v xml:space="preserve">Directional indicator of external credit rating migration, derived from the sign of month-over-month rating notch changes in counterparty_rating_observation. Encoded as: -1 = Downgrade, 0 = Stable, +1 = Upgrade. At aggregate (desk/portfolio/segment) levels, determined by the sign of the average rating change steps across all counterparties in the LOB — consistent with the spec requirement that LOB-level status reflects the direction of the LOB-average rating movement, not a vote count of individual counterparty directions. No facility-level calculation (ratings are per counterparty).
 </v>
       </c>
       <c r="C104" t="str">
-        <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps)</v>
+        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable)</v>
       </c>
       <c r="D104" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_change_steps from counterparty_rating_observation for each facility as-of reporting date.
+        <v xml:space="preserve">Not directly applicable — ratings are per counterparty, not facility. Passthrough: assigns counterparty's external rating status to each of its facilities via facility_master.counterparty_id join.
 </v>
       </c>
       <c r="E104" t="str">
@@ -10108,63 +10425,63 @@
         <v>Raw</v>
       </c>
       <c r="J104" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_change_steps from counterparty_rating_observation for each facility as-of reporting date.
+        <v xml:space="preserve">Not directly applicable — ratings are per counterparty, not facility. Passthrough: assigns counterparty's external rating status to each of its facilities via facility_master.counterparty_id join.
 </v>
       </c>
       <c r="K104" t="str">
-        <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps) (facility)</v>
+        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable) (facility)</v>
       </c>
       <c r="L104" t="str">
         <v>Y</v>
       </c>
       <c r="M104" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N104" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per counterparty.
+        <v xml:space="preserve">AVG of external rating change steps per counterparty, then SIGN: &lt; 0 → Downgrade (-1), = 0 → Stable (0), &gt; 0 → Upgrade (+1). Averages across multiple agency observations (Moody's, S&amp;P, Fitch).
 </v>
       </c>
       <c r="O104" t="str">
-        <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps) (counterparty)</v>
+        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable) (counterparty)</v>
       </c>
       <c r="P104" t="str">
         <v>Y</v>
       </c>
       <c r="Q104" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R104" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per L3 desk segment.
+        <v xml:space="preserve">AVG of counterparty-level external rating change steps across all unique counterparties in the L3 desk segment, then SIGN to classify the desk-level migration direction.
 </v>
       </c>
       <c r="S104" t="str">
-        <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps) (desk)</v>
+        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable) (desk)</v>
       </c>
       <c r="T104" t="str">
         <v>Y</v>
       </c>
       <c r="U104" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V104" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per L2 portfolio segment.
+        <v xml:space="preserve">AVG of counterparty-level external rating change steps across all unique counterparties in the L2 portfolio segment (one hop up in EBT), then SIGN to classify portfolio migration direction.
 </v>
       </c>
       <c r="W104" t="str">
-        <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps) (portfolio)</v>
+        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable) (portfolio)</v>
       </c>
       <c r="X104" t="str">
         <v>Y</v>
       </c>
       <c r="Y104" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z104" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per L1 business segment segment.
+        <v xml:space="preserve">AVG of counterparty-level external rating change steps across all unique counterparties in the L1 business segment (two hops up in EBT), then SIGN to classify segment migration direction.
 </v>
       </c>
       <c r="AA104" t="str">
-        <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps) (business_segment)</v>
+        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable) (business_segment)</v>
       </c>
       <c r="AB104" t="str">
         <v/>
@@ -10172,17 +10489,17 @@
     </row>
     <row r="105" xml:space="preserve">
       <c r="A105" t="str">
-        <v>RSK-006</v>
+        <v>RSK-005</v>
       </c>
       <c r="B105" t="str" xml:space="preserve">
-        <v xml:space="preserve">Derived directional classification indicating whether the internal credit rating has changed month over month: upgraded (e.g. 3 to 1), downgraded (e.g. 1 to 3), or remained stable (remained costant month-over month) compared to the prior reporting period. Note when this is displayed at an aggregated Line of Business or portfolio level, it is determined by the month-over-month change of the average rating at this level. Provides migration trend insight and serves as an early warning indicator of credit quality movement to support proactive risk management and escalation decisions.
+        <v xml:space="preserve">Mean external rating notch change (month-over-month) expressed as a numeric step count. Positive values indicate upgrades (e.g., A→AA = +1), negative values indicate downgrades (e.g., B+→B- = -2). Sourced from counterparty_rating_observation.risk_rating_change_steps, filtered to external agency observations only (is_internal_flag = 'N'). At counterparty level: AVG across agency observations for that counterparty. At aggregate levels: AVG across unique counterparties in the LOB segment, consistent with spec requirement that LOB-level steps reflect the average rating at that level, not the sum.
 </v>
       </c>
       <c r="C105" t="str">
-        <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable)</v>
+        <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps)</v>
       </c>
       <c r="D105" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility as-of reporting date.
+        <v xml:space="preserve">Not directly applicable — ratings are per counterparty, not facility. Passthrough: assigns counterparty's AVG external rating change steps to each of its facilities via facility_master.counterparty_id join.
 </v>
       </c>
       <c r="E105" t="str">
@@ -10201,63 +10518,63 @@
         <v>Raw</v>
       </c>
       <c r="J105" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility as-of reporting date.
+        <v xml:space="preserve">Not directly applicable — ratings are per counterparty, not facility. Passthrough: assigns counterparty's AVG external rating change steps to each of its facilities via facility_master.counterparty_id join.
 </v>
       </c>
       <c r="K105" t="str">
-        <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable) (facility)</v>
+        <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps) (facility)</v>
       </c>
       <c r="L105" t="str">
         <v>Y</v>
       </c>
       <c r="M105" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N105" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_status per counterparty.
+        <v xml:space="preserve">AVG of external rating change steps per counterparty, across all agency observations (Moody's, S&amp;P, Fitch) for the reporting date.
 </v>
       </c>
       <c r="O105" t="str">
-        <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable) (counterparty)</v>
+        <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps) (counterparty)</v>
       </c>
       <c r="P105" t="str">
         <v>Y</v>
       </c>
       <c r="Q105" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R105" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_status per L3 desk segment.
+        <v xml:space="preserve">AVG of counterparty-level external rating change steps across all unique counterparties in the L3 desk segment. Each counterparty counted once per LOB (deduplicated via DISTINCT on counterparty_id + lob_segment_id from facility_master).
 </v>
       </c>
       <c r="S105" t="str">
-        <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable) (desk)</v>
+        <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps) (desk)</v>
       </c>
       <c r="T105" t="str">
         <v>Y</v>
       </c>
       <c r="U105" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V105" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_status per L2 portfolio segment.
+        <v xml:space="preserve">AVG of counterparty-level external rating change steps across all unique counterparties in the L2 portfolio segment (one hop up in EBT).
 </v>
       </c>
       <c r="W105" t="str">
-        <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable) (portfolio)</v>
+        <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps) (portfolio)</v>
       </c>
       <c r="X105" t="str">
         <v>Y</v>
       </c>
       <c r="Y105" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z105" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_status per L1 business segment segment.
+        <v xml:space="preserve">AVG of counterparty-level external rating change steps across all unique counterparties in the L1 business segment (two hops up in EBT).
 </v>
       </c>
       <c r="AA105" t="str">
-        <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable) (business_segment)</v>
+        <v>Risk Rating Status - External Change - Steps (e.g. AAA to A = -2 steps) (business_segment)</v>
       </c>
       <c r="AB105" t="str">
         <v/>
@@ -10265,17 +10582,17 @@
     </row>
     <row r="106" xml:space="preserve">
       <c r="A106" t="str">
-        <v>RSK-007</v>
+        <v>RSK-006</v>
       </c>
       <c r="B106" t="str" xml:space="preserve">
-        <v xml:space="preserve">Numerical representation of internal risk rating migration (month over month changes) expressed in notch movement (positive or negative). Positive step changes are identified when there is an upgrade, from 3 to 1and the step change is +2, where as the negative step change is identified when there is a downgrade from 5 to 8 and the step change is -3. Note when this is displayed at an aggregated Line of Business or portfolio level, it is determined by the month-over-month change of the average rating at this level. Quantifies magnitude of credit change and enables portfolio-level migration analysis, stress testing sensitivity, and risk trend measurement.
+        <v xml:space="preserve">Directional classification indicating whether the internal credit rating has changed month-over-month: Upgrade (positive notch movement), Downgrade (negative notch movement), or Stable (no change). At facility/counterparty level, reads the pre-computed risk_rating_status from the internal rating observation. At aggregate levels (desk, portfolio, business segment), derives the direction from the average of counterparty-level risk_rating_change_steps — each counterparty counted once per segment to avoid facility-count bias. Provides migration trend insight and serves as an early warning indicator of credit quality movement.
 </v>
       </c>
       <c r="C106" t="str">
-        <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps)</v>
+        <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable)</v>
       </c>
       <c r="D106" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_change_steps from counterparty_rating_observation for each facility as-of reporting date.
+        <v xml:space="preserve">Read risk_rating_status from internal counterparty_rating_observation. Each facility inherits its counterparty's internal rating status.
 </v>
       </c>
       <c r="E106" t="str">
@@ -10294,63 +10611,63 @@
         <v>Raw</v>
       </c>
       <c r="J106" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_change_steps from counterparty_rating_observation for each facility as-of reporting date.
+        <v xml:space="preserve">Read risk_rating_status from internal counterparty_rating_observation. Each facility inherits its counterparty's internal rating status.
 </v>
       </c>
       <c r="K106" t="str">
-        <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps) (facility)</v>
+        <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable) (facility)</v>
       </c>
       <c r="L106" t="str">
         <v>Y</v>
       </c>
       <c r="M106" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="N106" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per counterparty.
+        <v xml:space="preserve">Read risk_rating_status directly from internal counterparty_rating_observation.
 </v>
       </c>
       <c r="O106" t="str">
-        <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps) (counterparty)</v>
+        <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable) (counterparty)</v>
       </c>
       <c r="P106" t="str">
         <v>Y</v>
       </c>
       <c r="Q106" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R106" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per L3 desk segment.
+        <v xml:space="preserve">Average internal risk_rating_change_steps across distinct counterparties in the L3 desk segment, then classify: &gt;0 Upgrade, &lt;0 Downgrade, =0 Stable. Counterparties de-duplicated per segment to avoid facility-count bias.
 </v>
       </c>
       <c r="S106" t="str">
-        <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps) (desk)</v>
+        <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable) (desk)</v>
       </c>
       <c r="T106" t="str">
         <v>Y</v>
       </c>
       <c r="U106" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V106" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per L2 portfolio segment.
+        <v xml:space="preserve">Average internal risk_rating_change_steps across distinct counterparties in the L2 portfolio segment, then classify direction.
 </v>
       </c>
       <c r="W106" t="str">
-        <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps) (portfolio)</v>
+        <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable) (portfolio)</v>
       </c>
       <c r="X106" t="str">
         <v>Y</v>
       </c>
       <c r="Y106" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z106" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_change_steps per L1 business segment segment.
+        <v xml:space="preserve">Average internal risk_rating_change_steps across distinct counterparties in the L1 business segment, then classify direction.
 </v>
       </c>
       <c r="AA106" t="str">
-        <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps) (business_segment)</v>
+        <v>Risk Rating Status - Internal (e.g. Downgrade, Upgrade, Stable) (business_segment)</v>
       </c>
       <c r="AB106" t="str">
         <v/>
@@ -10358,17 +10675,17 @@
     </row>
     <row r="107" xml:space="preserve">
       <c r="A107" t="str">
-        <v>RSK-008</v>
+        <v>RSK-007</v>
       </c>
       <c r="B107" t="str" xml:space="preserve">
-        <v xml:space="preserve">Categorizes exposures by internal credit risk level into distribution buckets based on counterparty internal risk rating; enables monitoring of credit quality distribution, concentration, and deterioration via rating migration.
+        <v xml:space="preserve">Numerical representation of internal risk rating migration expressed in notch movement. Positive values indicate upgrades (e.g. rating 3 to 1 = +2 steps), negative values indicate downgrades (e.g. rating 5 to 8 = -3 steps), zero indicates stable. At facility/counterparty level, reads the pre-computed risk_rating_change_steps from the internal rating observation. At aggregate levels (desk, portfolio, business segment), computes the rounded average of counterparty-level change steps — each counterparty counted once per segment to avoid facility-count bias. Quantifies magnitude of credit migration for portfolio-level trend analysis and stress testing.
 </v>
       </c>
       <c r="C107" t="str">
-        <v>Internal Risk Rating Bucket</v>
+        <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps)</v>
       </c>
       <c r="D107" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read internal_risk_rating_bucket_code from facility_exposure_snapshot for each facility.
+        <v xml:space="preserve">Read risk_rating_change_steps from internal counterparty_rating_observation. Each facility inherits its counterparty's internal rating change magnitude.
 </v>
       </c>
       <c r="E107" t="str">
@@ -10387,63 +10704,63 @@
         <v>Raw</v>
       </c>
       <c r="J107" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read internal_risk_rating_bucket_code from facility_exposure_snapshot for each facility.
+        <v xml:space="preserve">Read risk_rating_change_steps from internal counterparty_rating_observation. Each facility inherits its counterparty's internal rating change magnitude.
 </v>
       </c>
       <c r="K107" t="str">
-        <v>Internal Risk Rating Bucket (facility)</v>
+        <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps) (facility)</v>
       </c>
       <c r="L107" t="str">
         <v>Y</v>
       </c>
       <c r="M107" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="N107" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating bucket per counterparty.
+        <v xml:space="preserve">Read risk_rating_change_steps directly from internal counterparty_rating_observation.
 </v>
       </c>
       <c r="O107" t="str">
-        <v>Internal Risk Rating Bucket (counterparty)</v>
+        <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps) (counterparty)</v>
       </c>
       <c r="P107" t="str">
         <v>Y</v>
       </c>
       <c r="Q107" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="R107" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating bucket per L3 desk segment.
+        <v xml:space="preserve">Rounded average of counterparty-level risk_rating_change_steps across distinct counterparties in the L3 desk segment. Counterparties de-duplicated per segment to avoid facility-count bias.
 </v>
       </c>
       <c r="S107" t="str">
-        <v>Internal Risk Rating Bucket (desk)</v>
+        <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps) (desk)</v>
       </c>
       <c r="T107" t="str">
         <v>Y</v>
       </c>
       <c r="U107" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="V107" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating bucket per L2 portfolio segment.
+        <v xml:space="preserve">Rounded average of counterparty-level risk_rating_change_steps across distinct counterparties in the L2 portfolio segment.
 </v>
       </c>
       <c r="W107" t="str">
-        <v>Internal Risk Rating Bucket (portfolio)</v>
+        <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps) (portfolio)</v>
       </c>
       <c r="X107" t="str">
         <v>Y</v>
       </c>
       <c r="Y107" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="Z107" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with risk rating bucket per L1 business segment.
+        <v xml:space="preserve">Rounded average of counterparty-level risk_rating_change_steps across distinct counterparties in the L1 business segment.
 </v>
       </c>
       <c r="AA107" t="str">
-        <v>Internal Risk Rating Bucket (business_segment)</v>
+        <v>Risk Rating Status - Internal Change - Steps (e.g. 1 to 3 = -3 steps) (business_segment)</v>
       </c>
       <c r="AB107" t="str">
         <v/>
@@ -10451,106 +10768,292 @@
     </row>
     <row r="108" xml:space="preserve">
       <c r="A108" t="str">
+        <v>RSK-008</v>
+      </c>
+      <c r="B108" t="str" xml:space="preserve">
+        <v xml:space="preserve">Categorizes exposures by internal credit risk level into distribution buckets based on counterparty internal risk rating; enables monitoring of credit quality distribution, concentration, and deterioration via rating migration.
+</v>
+      </c>
+      <c r="C108" t="str">
+        <v>Internal Risk Rating Bucket</v>
+      </c>
+      <c r="D108" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read internal_risk_rating_bucket_code from facility_exposure_snapshot for each facility.
+</v>
+      </c>
+      <c r="E108" t="str">
+        <v/>
+      </c>
+      <c r="F108" t="str">
+        <v/>
+      </c>
+      <c r="G108" t="str">
+        <v/>
+      </c>
+      <c r="H108" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I108" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J108" t="str" xml:space="preserve">
+        <v xml:space="preserve">Read internal_risk_rating_bucket_code from facility_exposure_snapshot for each facility.
+</v>
+      </c>
+      <c r="K108" t="str">
+        <v>Internal Risk Rating Bucket (facility)</v>
+      </c>
+      <c r="L108" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M108" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="N108" t="str" xml:space="preserve">
+        <v xml:space="preserve">COUNT of facilities with risk rating bucket per counterparty.
+</v>
+      </c>
+      <c r="O108" t="str">
+        <v>Internal Risk Rating Bucket (counterparty)</v>
+      </c>
+      <c r="P108" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q108" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="R108" t="str" xml:space="preserve">
+        <v xml:space="preserve">COUNT of facilities with risk rating bucket per L3 desk segment.
+</v>
+      </c>
+      <c r="S108" t="str">
+        <v>Internal Risk Rating Bucket (desk)</v>
+      </c>
+      <c r="T108" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U108" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="V108" t="str" xml:space="preserve">
+        <v xml:space="preserve">COUNT of facilities with risk rating bucket per L2 portfolio segment.
+</v>
+      </c>
+      <c r="W108" t="str">
+        <v>Internal Risk Rating Bucket (portfolio)</v>
+      </c>
+      <c r="X108" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y108" t="str">
+        <v>Agg</v>
+      </c>
+      <c r="Z108" t="str" xml:space="preserve">
+        <v xml:space="preserve">COUNT of facilities with risk rating bucket per L1 business segment.
+</v>
+      </c>
+      <c r="AA108" t="str">
+        <v>Internal Risk Rating Bucket (business_segment)</v>
+      </c>
+      <c r="AB108" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="109" xml:space="preserve">
+      <c r="A109" t="str">
         <v>RSK-009</v>
       </c>
-      <c r="B108" t="str" xml:space="preserve">
+      <c r="B109" t="str" xml:space="preserve">
         <v xml:space="preserve">Committed facility amount as a percentage of underlying collateral value. Higher LTV indicates greater loss severity risk in the event of default. A core risk metric for secured lending portfolios.
 </v>
       </c>
-      <c r="C108" t="str">
+      <c r="C109" t="str">
         <v>Loan-to-Value Ratio (%)</v>
       </c>
-      <c r="D108" t="str" xml:space="preserve">
+      <c r="D109" t="str" xml:space="preserve">
         <v xml:space="preserve">Aggregate collateral per facility (a facility may have multiple collateral assets),
 then compute LTV = committed_facility_amt / SUM(current_valuation_usd) * 100.
 </v>
       </c>
-      <c r="E108" t="str">
-        <v/>
-      </c>
-      <c r="F108" t="str">
-        <v/>
-      </c>
-      <c r="G108" t="str">
-        <v/>
-      </c>
-      <c r="H108" t="str">
-        <v>Y</v>
-      </c>
-      <c r="I108" t="str">
+      <c r="E109" t="str">
+        <v/>
+      </c>
+      <c r="F109" t="str">
+        <v/>
+      </c>
+      <c r="G109" t="str">
+        <v/>
+      </c>
+      <c r="H109" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I109" t="str">
         <v>Raw</v>
       </c>
-      <c r="J108" t="str" xml:space="preserve">
+      <c r="J109" t="str" xml:space="preserve">
         <v xml:space="preserve">Aggregate collateral per facility (a facility may have multiple collateral assets),
 then compute LTV = committed_facility_amt / SUM(current_valuation_usd) * 100.
 </v>
       </c>
-      <c r="K108" t="str">
+      <c r="K109" t="str">
         <v>Loan-to-Value Ratio (%) (facility)</v>
       </c>
-      <c r="L108" t="str">
-        <v>Y</v>
-      </c>
-      <c r="M108" t="str">
-        <v>Calc</v>
-      </c>
-      <c r="N108" t="str" xml:space="preserve">
+      <c r="L109" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M109" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="N109" t="str" xml:space="preserve">
         <v xml:space="preserve">SUM(committed_facility_amt) / SUM(current_valuation_usd) * 100.0
 per counterparty. Re-derives ratio from summed components.
 </v>
       </c>
-      <c r="O108" t="str">
+      <c r="O109" t="str">
         <v>Loan-to-Value Ratio (%) (counterparty)</v>
       </c>
-      <c r="P108" t="str">
-        <v>Y</v>
-      </c>
-      <c r="Q108" t="str">
-        <v>Calc</v>
-      </c>
-      <c r="R108" t="str" xml:space="preserve">
+      <c r="P109" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q109" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="R109" t="str" xml:space="preserve">
         <v xml:space="preserve">SUM(committed_facility_amt) / SUM(current_valuation_usd) * 100.0
 per L3 desk segment. Re-derives ratio from summed components.
 </v>
       </c>
-      <c r="S108" t="str">
+      <c r="S109" t="str">
         <v>Loan-to-Value Ratio (%) (desk)</v>
       </c>
-      <c r="T108" t="str">
-        <v>Y</v>
-      </c>
-      <c r="U108" t="str">
-        <v>Calc</v>
-      </c>
-      <c r="V108" t="str" xml:space="preserve">
+      <c r="T109" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U109" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="V109" t="str" xml:space="preserve">
         <v xml:space="preserve">SUM(committed_facility_amt) / SUM(current_valuation_usd) * 100.0
 per L2 portfolio segment. Re-derives ratio from summed components.
 </v>
       </c>
-      <c r="W108" t="str">
+      <c r="W109" t="str">
         <v>Loan-to-Value Ratio (%) (portfolio)</v>
       </c>
-      <c r="X108" t="str">
-        <v>Y</v>
-      </c>
-      <c r="Y108" t="str">
-        <v>Calc</v>
-      </c>
-      <c r="Z108" t="str" xml:space="preserve">
+      <c r="X109" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y109" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="Z109" t="str" xml:space="preserve">
         <v xml:space="preserve">SUM(committed_facility_amt) / SUM(current_valuation_usd) * 100.0
 per L1 business segment. Re-derives ratio from summed components.
 </v>
       </c>
-      <c r="AA108" t="str">
+      <c r="AA109" t="str">
         <v>Loan-to-Value Ratio (%) (business_segment)</v>
       </c>
-      <c r="AB108" t="str">
+      <c r="AB109" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="110" xml:space="preserve">
+      <c r="A110" t="str">
+        <v>RSK-010</v>
+      </c>
+      <c r="B110" t="str" xml:space="preserve">
+        <v xml:space="preserve">Internal risk rating expressed as a numeric notch value. At facility level, reads the internal_risk_rating from the latest facility risk snapshot and maps it to a numeric rating_value via the rating_scale_dim reference table. At counterparty level, maps the counterparty's internal_risk_rating to a numeric notch. At desk, portfolio, and business segment levels, computes the average rating notch across distinct counterparties in the segment, then rounds to the nearest integer for a representative rating grade. Lower values indicate better credit quality.
+</v>
+      </c>
+      <c r="C110" t="str">
+        <v>Internal Risk Rating</v>
+      </c>
+      <c r="D110" t="str" xml:space="preserve">
+        <v xml:space="preserve">For each facility, read the internal_risk_rating from the latest facility_risk_snapshot (MAX as_of_date), then join to rating_scale_dim to convert the rating string to a numeric rating_value (notch ordinal). Uses MIN(rating_value) to handle potential duplicate dim matches.
+</v>
+      </c>
+      <c r="E110" t="str">
+        <v/>
+      </c>
+      <c r="F110" t="str">
+        <v/>
+      </c>
+      <c r="G110" t="str">
+        <v/>
+      </c>
+      <c r="H110" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I110" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="J110" t="str" xml:space="preserve">
+        <v xml:space="preserve">For each facility, read the internal_risk_rating from the latest facility_risk_snapshot (MAX as_of_date), then join to rating_scale_dim to convert the rating string to a numeric rating_value (notch ordinal). Uses MIN(rating_value) to handle potential duplicate dim matches.
+</v>
+      </c>
+      <c r="K110" t="str">
+        <v>Internal Risk Rating (facility)</v>
+      </c>
+      <c r="L110" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M110" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="N110" t="str" xml:space="preserve">
+        <v xml:space="preserve">For each counterparty, read the internal_risk_rating from the counterparty table, then join to rating_scale_dim to convert to a numeric rating_value. Uses MIN(rating_value) for deduplication.
+</v>
+      </c>
+      <c r="O110" t="str">
+        <v>Internal Risk Rating (counterparty)</v>
+      </c>
+      <c r="P110" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q110" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="R110" t="str" xml:space="preserve">
+        <v xml:space="preserve">Average internal risk rating notch across distinct counterparties in each L3 desk segment. Inner query ensures each counterparty is counted once per segment (avoids weighting by facility count). Result is rounded to nearest integer for a representative rating grade. Uses EBT direct join for L3 desk lookup.
+</v>
+      </c>
+      <c r="S110" t="str">
+        <v>Internal Risk Rating (desk)</v>
+      </c>
+      <c r="T110" t="str">
+        <v>Y</v>
+      </c>
+      <c r="U110" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="V110" t="str" xml:space="preserve">
+        <v xml:space="preserve">Average internal risk rating notch across distinct counterparties per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id. Each counterparty counted once per portfolio for a true counterparty-level average, then rounded.
+</v>
+      </c>
+      <c r="W110" t="str">
+        <v>Internal Risk Rating (portfolio)</v>
+      </c>
+      <c r="X110" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Y110" t="str">
+        <v>Calc</v>
+      </c>
+      <c r="Z110" t="str" xml:space="preserve">
+        <v xml:space="preserve">Average internal risk rating notch across distinct counterparties per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1. Each counterparty counted once per business segment, averaged, and rounded to nearest integer for a representative segment rating grade.
+</v>
+      </c>
+      <c r="AA110" t="str">
+        <v>Internal Risk Rating (business_segment)</v>
+      </c>
+      <c r="AB110" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AB108"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AB110"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/metrics_dimensions_filled.xlsx
+++ b/data/metrics_dimensions_filled.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB108"/>
+  <dimension ref="A1:AB110"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -795,14 +795,14 @@
         <v>AMD-004</v>
       </c>
       <c r="B6" t="str" xml:space="preserve">
-        <v xml:space="preserve">Indicator that facility agreement has undergone amendment. Portfolio KPI (% Facilities with Amendments) signals restructuring activity.
+        <v xml:space="preserve">Percentage of active facilities that have undergone at least one contractual amendment. At facility level, returns a binary flag (1 = has amendment, 0 = no amendment). At counterparty and aggregate levels, computes the count-ratio: COUNT(amended facilities) / COUNT(total facilities) x 100. High amendment rates may signal portfolio stress, widespread restructuring activity, or covenant relief campaigns.
 </v>
       </c>
       <c r="C6" t="str">
-        <v>Amendment ID</v>
+        <v>Amendment Rate</v>
       </c>
       <c r="D6" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read amendment_event_id from amendment_event for each facility as-of reporting date.
+        <v xml:space="preserve">For each active facility, check whether any amendment_event records exist via LEFT JOIN. Returns 1 (has amendment) or 0 (no amendment). A facility is considered amended if it has at least one record in the amendment_event table regardless of amendment type or status.
 </v>
       </c>
       <c r="E6" t="str">
@@ -818,66 +818,66 @@
         <v>Y</v>
       </c>
       <c r="I6" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="J6" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read amendment_event_id from amendment_event for each facility as-of reporting date.
+        <v xml:space="preserve">For each active facility, check whether any amendment_event records exist via LEFT JOIN. Returns 1 (has amendment) or 0 (no amendment). A facility is considered amended if it has at least one record in the amendment_event table regardless of amendment type or status.
 </v>
       </c>
       <c r="K6" t="str">
-        <v>Amendment ID (facility)</v>
+        <v>Amendment Rate (facility)</v>
       </c>
       <c r="L6" t="str">
         <v>Y</v>
       </c>
       <c r="M6" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N6" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level amendment_event_id) per counterparty.
+        <v xml:space="preserve">Count-ratio: number of amended facilities divided by total active facilities for each counterparty, expressed as a percentage. Uses a DISTINCT subquery on amendment_event to avoid double-counting facilities with multiple amendments.
 </v>
       </c>
       <c r="O6" t="str">
-        <v>Amendment ID (counterparty)</v>
+        <v>Amendment Rate (counterparty)</v>
       </c>
       <c r="P6" t="str">
         <v>Y</v>
       </c>
       <c r="Q6" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R6" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level amendment_event_id per L3 desk segment.
+        <v xml:space="preserve">Count-ratio: percentage of amended facilities per L3 desk segment. Re-counts at segment level (never averages pre-computed ratios) to avoid Simpson's paradox. Uses EBT direct join for L3.
 </v>
       </c>
       <c r="S6" t="str">
-        <v>Amendment ID (desk)</v>
+        <v>Amendment Rate (desk)</v>
       </c>
       <c r="T6" t="str">
         <v>Y</v>
       </c>
       <c r="U6" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V6" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level amendment_event_id per L2 portfolio segment.
+        <v xml:space="preserve">Count-ratio: percentage of amended facilities per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id. Re-counts at portfolio level for mathematical consistency.
 </v>
       </c>
       <c r="W6" t="str">
-        <v>Amendment ID (portfolio)</v>
+        <v>Amendment Rate (portfolio)</v>
       </c>
       <c r="X6" t="str">
         <v>Y</v>
       </c>
       <c r="Y6" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z6" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level amendment_event_id per L1 business segment segment.
+        <v xml:space="preserve">Count-ratio: percentage of amended facilities per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1. Re-counts at segment level for mathematical consistency across the rollup hierarchy.
 </v>
       </c>
       <c r="AA6" t="str">
-        <v>Amendment ID (business_segment)</v>
+        <v>Amendment Rate (business_segment)</v>
       </c>
       <c r="AB6" t="str">
         <v/>
@@ -2766,11 +2766,21 @@
         <v>Undrawn Exposure ($)</v>
       </c>
       <c r="D26" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each active facility:
-1. SUM(funded_amount) from PRINCIPAL position_detail rows per facility
-2. Subtract from committed_facility_amt to get unfunded amount
-3. Multiply by COALESCE(bank_share_pct, 100) / 100 from facility_lender_allocation
-Ensures: Committed Exposure = Outstanding Exposure + Undrawn Exposure
+        <v xml:space="preserve">1. LOAD  l2.position  (pos)
+   WHERE pos.as_of_date = :as_of_date
+2. JOIN  l2.position_detail  (pdtl)
+   ON    pdtl.position_id = pos.position_id
+   AND   pdtl.detail_type = 'PRINCIPAL'
+3. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = pos.facility_id
+   WHERE fm.is_active_flag = 'Y'
+4. LEFT JOIN  l2.facility_lender_allocation  (fla)
+   ON    fla.facility_id = fm.facility_id
+   AND   fla.is_current_flag = 'Y'
+5. GROUP BY fm.facility_id
+6. COMPUTE
+   metric_value = (committed_facility_amt - SUM(funded_amount))
+                  * COALESCE(bank_share_pct, 100) / 100
 </v>
       </c>
       <c r="E26" t="str">
@@ -2789,11 +2799,21 @@
         <v>Calc</v>
       </c>
       <c r="J26" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each active facility:
-1. SUM(funded_amount) from PRINCIPAL position_detail rows per facility
-2. Subtract from committed_facility_amt to get unfunded amount
-3. Multiply by COALESCE(bank_share_pct, 100) / 100 from facility_lender_allocation
-Ensures: Committed Exposure = Outstanding Exposure + Undrawn Exposure
+        <v xml:space="preserve">1. LOAD  l2.position  (pos)
+   WHERE pos.as_of_date = :as_of_date
+2. JOIN  l2.position_detail  (pdtl)
+   ON    pdtl.position_id = pos.position_id
+   AND   pdtl.detail_type = 'PRINCIPAL'
+3. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = pos.facility_id
+   WHERE fm.is_active_flag = 'Y'
+4. LEFT JOIN  l2.facility_lender_allocation  (fla)
+   ON    fla.facility_id = fm.facility_id
+   AND   fla.is_current_flag = 'Y'
+5. GROUP BY fm.facility_id
+6. COMPUTE
+   metric_value = (committed_facility_amt - SUM(funded_amount))
+                  * COALESCE(bank_share_pct, 100) / 100
 </v>
       </c>
       <c r="K26" t="str">
@@ -2806,8 +2826,13 @@
         <v>Calc</v>
       </c>
       <c r="N26" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each counterparty, sum facility-level undrawn exposure weighted
-by participation_pct from facility_counterparty_participation.
+        <v xml:space="preserve">1. LOAD  facility-level undrawn exposure (subquery)
+2. JOIN  l2.facility_counterparty_participation  (fcp)
+   ON    fcp.facility_id = fac.facility_id
+   AND   fcp.is_current_flag = 'Y'
+3. GROUP BY fcp.counterparty_id
+4. COMPUTE
+   metric_value = SUM(facility_undrawn * participation_pct)
 </v>
       </c>
       <c r="O26" t="str">
@@ -2820,8 +2845,15 @@
         <v>Agg</v>
       </c>
       <c r="R26" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level undrawn exposure per L3 desk segment.
-Joins facility_master.lob_segment_id to enterprise_business_taxonomy.managed_segment_id.
+        <v xml:space="preserve">1. LOAD  facility-level undrawn exposure (subquery)
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = fac.facility_id
+3. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt)
+   ON    ebt.managed_segment_id = fm.lob_segment_id
+   AND   ebt.is_current_flag = 'Y'
+4. GROUP BY ebt.managed_segment_id
+5. COMPUTE
+   metric_value = SUM(facility_undrawn)
 </v>
       </c>
       <c r="S26" t="str">
@@ -2834,8 +2866,16 @@
         <v>Agg</v>
       </c>
       <c r="V26" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level undrawn exposure per L2 portfolio segment.
-Traverses L3 -&gt; L2 via parent_segment_id.
+        <v xml:space="preserve">1. LOAD  facility-level undrawn exposure (subquery)
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = fac.facility_id
+3. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l3)
+   ON    ebt_l3.managed_segment_id = fm.lob_segment_id
+4. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l2)
+   ON    ebt_l2.managed_segment_id = ebt_l3.parent_segment_id
+5. GROUP BY ebt_l2.managed_segment_id
+6. COMPUTE
+   metric_value = SUM(facility_undrawn)
 </v>
       </c>
       <c r="W26" t="str">
@@ -2848,8 +2888,18 @@
         <v>Agg</v>
       </c>
       <c r="Z26" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level undrawn exposure per L1 business segment.
-Traverses L3 -&gt; L2 -&gt; L1 via parent_segment_id chain.
+        <v xml:space="preserve">1. LOAD  facility-level undrawn exposure (subquery)
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = fac.facility_id
+3. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l3)
+   ON    ebt_l3.managed_segment_id = fm.lob_segment_id
+4. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l2)
+   ON    ebt_l2.managed_segment_id = ebt_l3.parent_segment_id
+5. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l1)
+   ON    ebt_l1.managed_segment_id = ebt_l2.parent_segment_id
+6. GROUP BY ebt_l1.managed_segment_id
+7. COMPUTE
+   metric_value = SUM(facility_undrawn)
 </v>
       </c>
       <c r="AA26" t="str">
@@ -2864,17 +2914,28 @@
         <v>EXP-018</v>
       </c>
       <c r="B27" t="str" xml:space="preserve">
-        <v xml:space="preserve">Bank-share-adjusted funded (drawn) exposure amount. Represents the portion of committed credit currently utilized by the borrower. Maps to FR Y-14Q Field 25 (Utilized Exposure Global, MDRM G075).
+        <v xml:space="preserve">Bank-share-adjusted funded (drawn) exposure amount. Represents the portion of committed credit currently utilized by the borrower. Maps to FR Y-14Q Field 25 (Utilized Exposure Global, MDRM G075). Counterparty level uses exposure_counterparty_attribution for risk-shifted attribution weighting per Basel III requirements.
 </v>
       </c>
       <c r="C27" t="str">
         <v>Outstanding Exposure ($)</v>
       </c>
       <c r="D27" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each active facility:
-1. Join position -&gt; position_detail on position_id (both as_of_date filtered)
-2. SUM(funded_amount) across all positions for the facility
-3. Multiply by COALESCE(bank_share_pct, 100) / 100 from facility_lender_allocation
+        <v xml:space="preserve">1. LOAD  l2.position  (pos)
+   WHERE pos.as_of_date = :as_of_date
+2. JOIN  l2.position_detail  (pdtl)
+   ON    pdtl.position_id = pos.position_id
+   AND   pdtl.detail_type = 'PRINCIPAL'
+3. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = pos.facility_id
+   WHERE fm.is_active_flag = 'Y'
+4. LEFT JOIN  l2.facility_lender_allocation  (fla)
+   ON    fla.facility_id = fm.facility_id
+   AND   fla.is_current_flag = 'Y'
+5. GROUP BY pos.facility_id
+6. COMPUTE
+   metric_value = SUM(funded_amount)
+                  * COALESCE(bank_share_pct, 100) / 100
 </v>
       </c>
       <c r="E27" t="str">
@@ -2893,10 +2954,21 @@
         <v>Calc</v>
       </c>
       <c r="J27" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each active facility:
-1. Join position -&gt; position_detail on position_id (both as_of_date filtered)
-2. SUM(funded_amount) across all positions for the facility
-3. Multiply by COALESCE(bank_share_pct, 100) / 100 from facility_lender_allocation
+        <v xml:space="preserve">1. LOAD  l2.position  (pos)
+   WHERE pos.as_of_date = :as_of_date
+2. JOIN  l2.position_detail  (pdtl)
+   ON    pdtl.position_id = pos.position_id
+   AND   pdtl.detail_type = 'PRINCIPAL'
+3. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = pos.facility_id
+   WHERE fm.is_active_flag = 'Y'
+4. LEFT JOIN  l2.facility_lender_allocation  (fla)
+   ON    fla.facility_id = fm.facility_id
+   AND   fla.is_current_flag = 'Y'
+5. GROUP BY pos.facility_id
+6. COMPUTE
+   metric_value = SUM(funded_amount)
+                  * COALESCE(bank_share_pct, 100) / 100
 </v>
       </c>
       <c r="K27" t="str">
@@ -2909,9 +2981,13 @@
         <v>Calc</v>
       </c>
       <c r="N27" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each counterparty, sum facility-level outstanding exposure weighted
-by participation_pct from facility_counterparty_participation.
-Uses contractual pro-rata basis per FR Y-14Q requirements.
+        <v xml:space="preserve">1. LOAD  facility-level outstanding exposure (subquery)
+2. JOIN  l2.exposure_counterparty_attribution  (eca)
+   ON    eca.facility_id = fac.facility_id
+   AND   eca.as_of_date = :as_of_date
+3. GROUP BY eca.counterparty_id
+4. COMPUTE
+   metric_value = SUM(facility_outstanding * attribution_pct)
 </v>
       </c>
       <c r="O27" t="str">
@@ -2924,8 +3000,15 @@
         <v>Agg</v>
       </c>
       <c r="R27" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level outstanding exposure per L3 desk segment.
-Joins facility_master.lob_segment_id to enterprise_business_taxonomy.managed_segment_id.
+        <v xml:space="preserve">1. LOAD  facility-level outstanding exposure (subquery)
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = fac.facility_id
+3. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt)
+   ON    ebt.managed_segment_id = fm.lob_segment_id
+   AND   ebt.is_current_flag = 'Y'
+4. GROUP BY ebt.managed_segment_id
+5. COMPUTE
+   metric_value = SUM(facility_outstanding)
 </v>
       </c>
       <c r="S27" t="str">
@@ -2938,8 +3021,16 @@
         <v>Agg</v>
       </c>
       <c r="V27" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level outstanding exposure per L2 portfolio segment.
-Traverses L3 -&gt; L2 via parent_segment_id.
+        <v xml:space="preserve">1. LOAD  facility-level outstanding exposure (subquery)
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = fac.facility_id
+3. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l3)
+   ON    ebt_l3.managed_segment_id = fm.lob_segment_id
+4. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l2)
+   ON    ebt_l2.managed_segment_id = ebt_l3.parent_segment_id
+5. GROUP BY ebt_l2.managed_segment_id
+6. COMPUTE
+   metric_value = SUM(facility_outstanding)
 </v>
       </c>
       <c r="W27" t="str">
@@ -2952,8 +3043,14 @@
         <v>Agg</v>
       </c>
       <c r="Z27" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level outstanding exposure per L1 business segment.
-Traverses L3 -&gt; L2 -&gt; L1 via parent_segment_id chain.
+        <v xml:space="preserve">1. LOAD  facility-level outstanding exposure (subquery)
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = fac.facility_id
+3. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l3, ebt_l2, ebt_l1)
+   Traverse L3 -&gt; L2 -&gt; L1 via parent_segment_id chain
+4. GROUP BY ebt_l1.managed_segment_id
+5. COMPUTE
+   metric_value = SUM(facility_outstanding)
 </v>
       </c>
       <c r="AA27" t="str">
@@ -2968,14 +3065,15 @@
         <v>EXP-019</v>
       </c>
       <c r="B28" t="str" xml:space="preserve">
-        <v xml:space="preserve">Maximum approved credit exposure authorized for the counterparty or Line of Business segment in USD. Represents formal risk appetite allocation and governance control threshold.
+        <v xml:space="preserve">Maximum approved credit exposure authorized for the counterparty or Line of Business segment in USD. Sourced directly from the limit_rule reference table. Represents formal risk appetite allocation and governance control threshold set by the Credit Risk Committee. Not applicable at individual facility level — limits are set at counterparty and organizational hierarchy levels.
 </v>
       </c>
       <c r="C28" t="str">
         <v>Exposure Limit ($)</v>
       </c>
       <c r="D28" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read limit_amt from lob_exposure_summary for each facility as-of reporting date.
+        <v xml:space="preserve">Not applicable — exposure limits are set at counterparty and
+organizational levels, not per individual facility. Returns NULL.
 </v>
       </c>
       <c r="E28" t="str">
@@ -2994,7 +3092,8 @@
         <v>Raw</v>
       </c>
       <c r="J28" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read limit_amt from lob_exposure_summary for each facility as-of reporting date.
+        <v xml:space="preserve">Not applicable — exposure limits are set at counterparty and
+organizational levels, not per individual facility. Returns NULL.
 </v>
       </c>
       <c r="K28" t="str">
@@ -3007,7 +3106,12 @@
         <v>Raw</v>
       </c>
       <c r="N28" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read limit_amt per counterparty.
+        <v xml:space="preserve">1. LOAD  l1.limit_rule  (lr)
+   WHERE lr.is_current_flag = 'Y'
+   AND   lr.counterparty_id IS NOT NULL
+2. GROUP BY lr.counterparty_id
+3. COMPUTE
+   metric_value = SUM(limit_amount_usd)
 </v>
       </c>
       <c r="O28" t="str">
@@ -3017,10 +3121,18 @@
         <v>Y</v>
       </c>
       <c r="Q28" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="R28" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level limit_amt per L3 desk segment.
+        <v xml:space="preserve">1. LOAD  l1.limit_rule  (lr)
+   WHERE lr.is_current_flag = 'Y'
+   AND   lr.lob_segment_id IS NOT NULL
+2. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt)
+   ON    ebt.managed_segment_id = lr.lob_segment_id
+   AND   ebt.is_current_flag = 'Y'
+3. GROUP BY lr.lob_segment_id
+4. COMPUTE
+   metric_value = SUM(limit_amount_usd)
 </v>
       </c>
       <c r="S28" t="str">
@@ -3030,10 +3142,18 @@
         <v>Y</v>
       </c>
       <c r="U28" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="V28" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level limit_amt per L2 portfolio segment.
+        <v xml:space="preserve">1. LOAD  l1.limit_rule  (lr)
+   WHERE lr.is_current_flag = 'Y'
+   AND   lr.lob_segment_id IS NOT NULL
+2. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt)
+   ON    ebt.managed_segment_id = lr.lob_segment_id
+   AND   ebt.is_current_flag = 'Y'
+3. GROUP BY lr.lob_segment_id
+4. COMPUTE
+   metric_value = SUM(limit_amount_usd)
 </v>
       </c>
       <c r="W28" t="str">
@@ -3043,10 +3163,18 @@
         <v>Y</v>
       </c>
       <c r="Y28" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="Z28" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level limit_amt per L1 business segment segment.
+        <v xml:space="preserve">1. LOAD  l1.limit_rule  (lr)
+   WHERE lr.is_current_flag = 'Y'
+   AND   lr.lob_segment_id IS NOT NULL
+2. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt)
+   ON    ebt.managed_segment_id = lr.lob_segment_id
+   AND   ebt.is_current_flag = 'Y'
+3. GROUP BY lr.lob_segment_id
+4. COMPUTE
+   metric_value = SUM(limit_amount_usd)
 </v>
       </c>
       <c r="AA28" t="str">
@@ -3061,14 +3189,25 @@
         <v>EXP-020</v>
       </c>
       <c r="B29" t="str" xml:space="preserve">
-        <v xml:space="preserve">The estimated exposure amount (in USD) expected to be outstanding if the borrower defaults.
+        <v xml:space="preserve">Estimated exposure amount outstanding if the borrower defaults, computed from L2 atomic inputs per Basel III: EAD = OB + CCF × Undrawn, where OB = drawn/funded amount, CCF = credit conversion factor from facility_risk_snapshot, and Undrawn = committed minus drawn from facility_exposure_snapshot. Bank-share adjusted via facility_exposure_snapshot. At counterparty level, weighted by participation_pct from facility_counterparty_participation per FR Y-14Q requirements.
 </v>
       </c>
       <c r="C29" t="str">
         <v>Exposure at Default ($)</v>
       </c>
       <c r="D29" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read exposure_at_default from credit_event_facility_link for each facility as-of reporting date.
+        <v xml:space="preserve">1. LOAD  l2.facility_exposure_snapshot  (fes)
+   WHERE fes.as_of_date = :as_of_date
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = fes.facility_id
+   WHERE fm.is_active_flag = 'Y'
+3. LEFT JOIN  l2.facility_risk_snapshot  (frs)
+   ON    frs.facility_id = fes.facility_id
+   AND   frs.as_of_date = fes.as_of_date
+4. GROUP BY fes.facility_id
+5. COMPUTE
+   metric_value = (drawn_amount + CCF * undrawn_amount)
+                  * bank_share_pct / 100
 </v>
       </c>
       <c r="E29" t="str">
@@ -3084,10 +3223,21 @@
         <v>Y</v>
       </c>
       <c r="I29" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="J29" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read exposure_at_default from credit_event_facility_link for each facility as-of reporting date.
+        <v xml:space="preserve">1. LOAD  l2.facility_exposure_snapshot  (fes)
+   WHERE fes.as_of_date = :as_of_date
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = fes.facility_id
+   WHERE fm.is_active_flag = 'Y'
+3. LEFT JOIN  l2.facility_risk_snapshot  (frs)
+   ON    frs.facility_id = fes.facility_id
+   AND   frs.as_of_date = fes.as_of_date
+4. GROUP BY fes.facility_id
+5. COMPUTE
+   metric_value = (drawn_amount + CCF * undrawn_amount)
+                  * bank_share_pct / 100
 </v>
       </c>
       <c r="K29" t="str">
@@ -3097,10 +3247,22 @@
         <v>Y</v>
       </c>
       <c r="M29" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N29" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level exposure_at_default per counterparty.
+        <v xml:space="preserve">1. LOAD  l2.facility_exposure_snapshot  (fes)
+   WHERE fes.as_of_date = :as_of_date
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = fes.facility_id
+3. LEFT JOIN  l2.facility_risk_snapshot  (frs)
+   ON    frs.facility_id = fes.facility_id
+4. JOIN  l2.facility_counterparty_participation  (fcp)
+   ON    fcp.facility_id = fes.facility_id
+   AND   fcp.is_current_flag = 'Y'
+5. GROUP BY fcp.counterparty_id
+6. COMPUTE
+   metric_value = SUM((drawn + CCF * undrawn) * bank_share / 100
+                  * participation_pct)
 </v>
       </c>
       <c r="O29" t="str">
@@ -3113,7 +3275,15 @@
         <v>Agg</v>
       </c>
       <c r="R29" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level exposure_at_default per L3 desk segment.
+        <v xml:space="preserve">1. LOAD  facility-level EAD (subquery)
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = fac.facility_id
+3. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt)
+   ON    ebt.managed_segment_id = fm.lob_segment_id
+   AND   ebt.is_current_flag = 'Y'
+4. GROUP BY ebt.managed_segment_id
+5. COMPUTE
+   metric_value = SUM(facility_ead)
 </v>
       </c>
       <c r="S29" t="str">
@@ -3126,7 +3296,13 @@
         <v>Agg</v>
       </c>
       <c r="V29" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level exposure_at_default per L2 portfolio segment.
+        <v xml:space="preserve">1. LOAD  facility-level EAD (subquery)
+2. JOIN  l2.facility_master  (fm)
+3. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l3, ebt_l2)
+   Traverse L3 -&gt; L2 via parent_segment_id
+4. GROUP BY ebt_l2.managed_segment_id
+5. COMPUTE
+   metric_value = SUM(facility_ead)
 </v>
       </c>
       <c r="W29" t="str">
@@ -3139,7 +3315,13 @@
         <v>Agg</v>
       </c>
       <c r="Z29" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level exposure_at_default per L1 business segment segment.
+        <v xml:space="preserve">1. LOAD  facility-level EAD (subquery)
+2. JOIN  l2.facility_master  (fm)
+3. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l3, ebt_l2, ebt_l1)
+   Traverse L3 -&gt; L2 -&gt; L1 via parent_segment_id chain
+4. GROUP BY ebt_l1.managed_segment_id
+5. COMPUTE
+   metric_value = SUM(facility_ead)
 </v>
       </c>
       <c r="AA29" t="str">
@@ -3154,14 +3336,14 @@
         <v>EXP-021</v>
       </c>
       <c r="B30" t="str" xml:space="preserve">
-        <v xml:space="preserve">Derived categorical classification (Sufficient, Approaching, Fully Utilized) of utilization level based on current drawn exposure relative to committed amount. Operational KPI providing early warning insight into limit pressure, liquidity usage, and potential capacity constraints.
+        <v xml:space="preserve">Derived categorical classification of utilization level based on current drawn exposure relative to committed amount. Maps facility utilization percentage against l1.utilization_status_dim threshold ranges to return status labels (e.g., Sufficient, Approaching, Fully Utilized). Operational KPI providing early warning insight into limit pressure, liquidity usage, and potential capacity constraints.
 </v>
       </c>
       <c r="C30" t="str">
-        <v>Facility Utilization Status (e.g., Sufficient, Approaching, Fully Utilized)</v>
+        <v>Utilization Status (Utilized Exposure to Committed Exposure)</v>
       </c>
       <c r="D30" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated utilization_status_code per facility.
+        <v xml:space="preserve">For each facility, compute utilization_pct from L2 atomic data (drawn_amount / committed_amount * 100), then match against l1.utilization_status_dim threshold ranges (utilization_min_pct &lt;= pct &lt; utilization_max_pct) to return status_name.
 </v>
       </c>
       <c r="E30" t="str">
@@ -3180,63 +3362,63 @@
         <v>Calc</v>
       </c>
       <c r="J30" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated utilization_status_code per facility.
+        <v xml:space="preserve">For each facility, compute utilization_pct from L2 atomic data (drawn_amount / committed_amount * 100), then match against l1.utilization_status_dim threshold ranges (utilization_min_pct &lt;= pct &lt; utilization_max_pct) to return status_name.
 </v>
       </c>
       <c r="K30" t="str">
-        <v>Facility Utilization Status (e.g., Sufficient, Approaching, Fully Utilized) (facility)</v>
+        <v>Utilization Status (Utilized Exposure to Committed Exposure) (facility)</v>
       </c>
       <c r="L30" t="str">
         <v>Y</v>
       </c>
       <c r="M30" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N30" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level utilization_status_code) per counterparty.
+        <v xml:space="preserve">Compute counterparty-level utilization pct via sum-ratio with FX conversion: SUM(drawn * fx) / SUM(committed * fx) * 100. Then look up status from utilization_status_dim threshold ranges.
 </v>
       </c>
       <c r="O30" t="str">
-        <v>Facility Utilization Status (e.g., Sufficient, Approaching, Fully Utilized) (counterparty)</v>
+        <v>Utilization Status (Utilized Exposure to Committed Exposure) (counterparty)</v>
       </c>
       <c r="P30" t="str">
         <v>Y</v>
       </c>
       <c r="Q30" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R30" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level utilization_status_code per L3 desk segment.
+        <v xml:space="preserve">Compute L3 desk-level utilization pct via sum-ratio with FX conversion, then look up status from utilization_status_dim threshold ranges.
 </v>
       </c>
       <c r="S30" t="str">
-        <v>Facility Utilization Status (e.g., Sufficient, Approaching, Fully Utilized) (desk)</v>
+        <v>Utilization Status (Utilized Exposure to Committed Exposure) (desk)</v>
       </c>
       <c r="T30" t="str">
         <v>Y</v>
       </c>
       <c r="U30" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V30" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level utilization_status_code per L2 portfolio segment.
+        <v xml:space="preserve">Compute L2 portfolio-level utilization pct via sum-ratio with FX conversion (one-hop EBT hierarchy), then look up status from utilization_status_dim threshold ranges.
 </v>
       </c>
       <c r="W30" t="str">
-        <v>Facility Utilization Status (e.g., Sufficient, Approaching, Fully Utilized) (portfolio)</v>
+        <v>Utilization Status (Utilized Exposure to Committed Exposure) (portfolio)</v>
       </c>
       <c r="X30" t="str">
         <v>Y</v>
       </c>
       <c r="Y30" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z30" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level utilization_status_code per L1 business segment segment.
+        <v xml:space="preserve">Compute L1 business segment-level utilization pct via sum-ratio with FX conversion (two-hop EBT hierarchy), then look up status from utilization_status_dim threshold ranges.
 </v>
       </c>
       <c r="AA30" t="str">
-        <v>Facility Utilization Status (e.g., Sufficient, Approaching, Fully Utilized) (business_segment)</v>
+        <v>Utilization Status (Utilized Exposure to Committed Exposure) (business_segment)</v>
       </c>
       <c r="AB30" t="str">
         <v/>
@@ -3340,14 +3522,14 @@
         <v>EXP-023</v>
       </c>
       <c r="B32" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure × LGD expressed in dollar terms weighted based on facility-level exposure. Derived loss severity metric estimating expected recovery-adjusted loss magnitude.
+        <v xml:space="preserve">Expected dollar loss given default. Computed as EAD (drawn amount, bank share) multiplied by LGD percentage from facility risk snapshot. Expressed in local currency at facility level and FX-converted to USD at aggregate levels. Quantifies loss severity per facility and across rollup hierarchy.
 </v>
       </c>
       <c r="C32" t="str">
         <v>Loss Given Default ($)</v>
       </c>
       <c r="D32" t="str" xml:space="preserve">
-        <v xml:space="preserve">EAD * LGD (in Percentage) for all facilities across Counterparties
+        <v xml:space="preserve">EAD (bank share) x LGD% per facility in local currency.
 </v>
       </c>
       <c r="E32" t="str">
@@ -3366,7 +3548,7 @@
         <v>Calc</v>
       </c>
       <c r="J32" t="str" xml:space="preserve">
-        <v xml:space="preserve">EAD * LGD (in Percentage) for all facilities across Counterparties
+        <v xml:space="preserve">EAD (bank share) x LGD% per facility in local currency.
 </v>
       </c>
       <c r="K32" t="str">
@@ -3379,7 +3561,7 @@
         <v>Agg</v>
       </c>
       <c r="N32" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level lgd_estimate per counterparty.
+        <v xml:space="preserve">SUM of facility-level LGD$ per counterparty, FX-converted to USD.
 </v>
       </c>
       <c r="O32" t="str">
@@ -3392,7 +3574,7 @@
         <v>Agg</v>
       </c>
       <c r="R32" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level lgd_estimate per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level LGD$ per L3 desk segment, FX-converted to USD.
 </v>
       </c>
       <c r="S32" t="str">
@@ -3405,7 +3587,7 @@
         <v>Agg</v>
       </c>
       <c r="V32" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level lgd_estimate per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level LGD$ per L2 portfolio segment, FX-converted to USD.
 </v>
       </c>
       <c r="W32" t="str">
@@ -3418,7 +3600,7 @@
         <v>Agg</v>
       </c>
       <c r="Z32" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level lgd_estimate per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level LGD$ per L1 business segment, FX-converted to USD.
 </v>
       </c>
       <c r="AA32" t="str">
@@ -3433,14 +3615,14 @@
         <v>EXP-024</v>
       </c>
       <c r="B33" t="str" xml:space="preserve">
-        <v xml:space="preserve">Status of credit limit (Active, Warning, Breach). Used to monitor risk appetite breaches and exposure governance compliance.
+        <v xml:space="preserve">Utilization-based limit compliance status. At facility level reads the pre-computed limit_status_code. At aggregate levels computes drawn-to- committed utilization percentage (FX-converted to USD) and maps to a status code via utilization_status_dim thresholds. Used for credit limit monitoring and risk appetite breach detection.
 </v>
       </c>
       <c r="C33" t="str">
         <v>Limit Status</v>
       </c>
       <c r="D33" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated limit_status_code per facility.
+        <v xml:space="preserve">Read pre-computed limit_status_code from facility_exposure_snapshot.
 </v>
       </c>
       <c r="E33" t="str">
@@ -3456,10 +3638,10 @@
         <v>Y</v>
       </c>
       <c r="I33" t="str">
-        <v>Calc</v>
+        <v>Raw</v>
       </c>
       <c r="J33" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated limit_status_code per facility.
+        <v xml:space="preserve">Read pre-computed limit_status_code from facility_exposure_snapshot.
 </v>
       </c>
       <c r="K33" t="str">
@@ -3469,10 +3651,10 @@
         <v>Y</v>
       </c>
       <c r="M33" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N33" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level limit_status_code per counterparty.
+        <v xml:space="preserve">Compute drawn-to-committed utilization % per counterparty (FX-converted), then map to status via utilization_status_dim thresholds.
 </v>
       </c>
       <c r="O33" t="str">
@@ -3482,10 +3664,10 @@
         <v>Y</v>
       </c>
       <c r="Q33" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R33" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level limit_status_code per L3 desk segment.
+        <v xml:space="preserve">Compute drawn-to-committed utilization % per L3 desk segment (FX-converted), then map to status via utilization_status_dim.
 </v>
       </c>
       <c r="S33" t="str">
@@ -3495,10 +3677,10 @@
         <v>Y</v>
       </c>
       <c r="U33" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V33" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level limit_status_code per L2 portfolio segment.
+        <v xml:space="preserve">Compute drawn-to-committed utilization % per L2 portfolio segment (FX-converted), then map to status via utilization_status_dim.
 </v>
       </c>
       <c r="W33" t="str">
@@ -3508,10 +3690,10 @@
         <v>Y</v>
       </c>
       <c r="Y33" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z33" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level limit_status_code per L1 business segment segment.
+        <v xml:space="preserve">Compute drawn-to-committed utilization % per L1 business segment (FX-converted), then map to status via utilization_status_dim.
 </v>
       </c>
       <c r="AA33" t="str">
@@ -3526,14 +3708,14 @@
         <v>EXP-025</v>
       </c>
       <c r="B34" t="str" xml:space="preserve">
-        <v xml:space="preserve">The average expected loss rate (percent of exposure) if default occurs, weighted across exposures (typically by EAD).
+        <v xml:space="preserve">Exposure-weighted average Loss Given Default rate expressed as a decimal fraction (e.g. 0.45 = 45%). At facility level, reads lgd_pct directly from facility_risk_snapshot. At aggregate levels, computes the commitment-adjusted weighted average: SUM(lgd_pct * outstanding_balance_amt) / SUM(committed_amount), with FX conversion for cross-currency portfolios. LGD represents the expected severity of loss if the obligor defaults, a key input to Expected Loss (EL = PD x LGD x EAD) under Basel III IRB.
 </v>
       </c>
       <c r="C34" t="str">
         <v>Loss Given Default (%)</v>
       </c>
       <c r="D34" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated lgd_pct per facility.
+        <v xml:space="preserve">Direct lookup of lgd_pct per facility from facility_risk_snapshot. No aggregation needed — facility-level LGD is a sourced atomic value.
 </v>
       </c>
       <c r="E34" t="str">
@@ -3549,10 +3731,10 @@
         <v>Y</v>
       </c>
       <c r="I34" t="str">
-        <v>Calc</v>
+        <v>Raw</v>
       </c>
       <c r="J34" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated lgd_pct per facility.
+        <v xml:space="preserve">Direct lookup of lgd_pct per facility from facility_risk_snapshot. No aggregation needed — facility-level LGD is a sourced atomic value.
 </v>
       </c>
       <c r="K34" t="str">
@@ -3565,7 +3747,7 @@
         <v>Avg</v>
       </c>
       <c r="N34" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of lgd_pct across counterparty facilities.
+        <v xml:space="preserve">Commitment-adjusted exposure-weighted LGD per counterparty: SUM(lgd_pct * outstanding_balance_amt * fx_rate) / NULLIF(SUM(committed_amount * fx_rate), 0). FX conversion ensures proper weighting across multi-currency facilities.
 </v>
       </c>
       <c r="O34" t="str">
@@ -3575,10 +3757,10 @@
         <v>Y</v>
       </c>
       <c r="Q34" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="R34" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level lgd_pct per L3 desk segment.
+        <v xml:space="preserve">Commitment-adjusted exposure-weighted LGD per L3 desk segment: SUM(lgd_pct * outstanding_balance_amt * fx_rate) / NULLIF(SUM(committed_amount * fx_rate), 0). Standard EBT hierarchy direct join for desk grouping.
 </v>
       </c>
       <c r="S34" t="str">
@@ -3588,10 +3770,10 @@
         <v>Y</v>
       </c>
       <c r="U34" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="V34" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level lgd_pct per L2 portfolio segment.
+        <v xml:space="preserve">Commitment-adjusted exposure-weighted LGD per L2 portfolio segment: SUM(lgd_pct * outstanding_balance_amt * fx_rate) / NULLIF(SUM(committed_amount * fx_rate), 0). One-hop EBT traversal for portfolio grouping.
 </v>
       </c>
       <c r="W34" t="str">
@@ -3601,10 +3783,10 @@
         <v>Y</v>
       </c>
       <c r="Y34" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="Z34" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level lgd_pct per L1 business segment segment.
+        <v xml:space="preserve">Commitment-adjusted exposure-weighted LGD per L1 business segment: SUM(lgd_pct * outstanding_balance_amt * fx_rate) / NULLIF(SUM(committed_amount * fx_rate), 0). Two-hop EBT traversal for business segment grouping.
 </v>
       </c>
       <c r="AA34" t="str">
@@ -3616,17 +3798,17 @@
     </row>
     <row r="35" xml:space="preserve">
       <c r="A35" t="str">
-        <v>EXP-026</v>
+        <v>EXP-027</v>
       </c>
       <c r="B35" t="str" xml:space="preserve">
-        <v xml:space="preserve">Loan to Value Ratio (%) metric.
+        <v xml:space="preserve">Net income computed from L2 atomic inputs: NOI (Net Operating Income, which equals Revenue minus Operating Expense) minus Interest Expense minus Expected Loss (PD × LGD × Committed Amount). Indicator of facility-level profitability.
 </v>
       </c>
       <c r="C35" t="str">
-        <v>Loan to Value Ratio (%)</v>
+        <v>Net Income ($)</v>
       </c>
       <c r="D35" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each DISTINCT (Facility_ID) lookup Collateral ID and SUM(Current_Colalteral_MV) THEN  [Commited_Facility_Amt] / [Current_Collateral_MV] × 100
+        <v xml:space="preserve">Net Income = NOI (Revenue - OpEx) - Interest Expense - Expected Loss (PD × LGD × Committed Amount). All sourced from L2 atomic tables.
 </v>
       </c>
       <c r="E35" t="str">
@@ -3645,11 +3827,11 @@
         <v>Calc</v>
       </c>
       <c r="J35" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each DISTINCT (Facility_ID) lookup Collateral ID and SUM(Current_Colalteral_MV) THEN  [Commited_Facility_Amt] / [Current_Collateral_MV] × 100
+        <v xml:space="preserve">Net Income = NOI (Revenue - OpEx) - Interest Expense - Expected Loss (PD × LGD × Committed Amount). All sourced from L2 atomic tables.
 </v>
       </c>
       <c r="K35" t="str">
-        <v>Loan to Value Ratio (%) (facility)</v>
+        <v>Net Income ($) (facility)</v>
       </c>
       <c r="L35" t="str">
         <v>Y</v>
@@ -3658,11 +3840,11 @@
         <v>Agg</v>
       </c>
       <c r="N35" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level ltv_pct per counterparty.
+        <v xml:space="preserve">SUM of facility-level net income per counterparty, FX-converted to USD.
 </v>
       </c>
       <c r="O35" t="str">
-        <v>Loan to Value Ratio (%) (counterparty)</v>
+        <v>Net Income ($) (counterparty)</v>
       </c>
       <c r="P35" t="str">
         <v>Y</v>
@@ -3671,11 +3853,11 @@
         <v>Agg</v>
       </c>
       <c r="R35" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level ltv_pct per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level net income per L3 desk segment, FX-converted to USD.
 </v>
       </c>
       <c r="S35" t="str">
-        <v>Loan to Value Ratio (%) (desk)</v>
+        <v>Net Income ($) (desk)</v>
       </c>
       <c r="T35" t="str">
         <v>Y</v>
@@ -3684,11 +3866,11 @@
         <v>Agg</v>
       </c>
       <c r="V35" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level ltv_pct per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level net income per L2 portfolio segment, FX-converted to USD.
 </v>
       </c>
       <c r="W35" t="str">
-        <v>Loan to Value Ratio (%) (portfolio)</v>
+        <v>Net Income ($) (portfolio)</v>
       </c>
       <c r="X35" t="str">
         <v>Y</v>
@@ -3697,11 +3879,11 @@
         <v>Agg</v>
       </c>
       <c r="Z35" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level ltv_pct per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level net income per L1 business segment, FX-converted to USD.
 </v>
       </c>
       <c r="AA35" t="str">
-        <v>Loan to Value Ratio (%) (business_segment)</v>
+        <v>Net Income ($) (business_segment)</v>
       </c>
       <c r="AB35" t="str">
         <v/>
@@ -3709,17 +3891,17 @@
     </row>
     <row r="36" xml:space="preserve">
       <c r="A36" t="str">
-        <v>EXP-027</v>
+        <v>EXP-028</v>
       </c>
       <c r="B36" t="str" xml:space="preserve">
-        <v xml:space="preserve">Profit after all expenses in USD. Indicator of borrower profitability and financial sustainability.
+        <v xml:space="preserve">Net Interest Income divided by Average Earning Assets. Core banking profitability measure assessing pricing effectiveness and lending margin. Sourced from L2 facility_profitability_snapshot atomic data.
 </v>
       </c>
       <c r="C36" t="str">
-        <v>Net Income ($)</v>
+        <v>Net Interest Margin (%)</v>
       </c>
       <c r="D36" t="str" xml:space="preserve">
-        <v xml:space="preserve">Revenue – Interest Expense – Operating Cost – EL
+        <v xml:space="preserve">(Interest Income - Interest Expense) / Average Earning Assets * 100.
 </v>
       </c>
       <c r="E36" t="str">
@@ -3738,63 +3920,63 @@
         <v>Calc</v>
       </c>
       <c r="J36" t="str" xml:space="preserve">
-        <v xml:space="preserve">Revenue – Interest Expense – Operating Cost – EL
+        <v xml:space="preserve">(Interest Income - Interest Expense) / Average Earning Assets * 100.
 </v>
       </c>
       <c r="K36" t="str">
-        <v>Net Income ($) (facility)</v>
+        <v>Net Interest Margin (%) (facility)</v>
       </c>
       <c r="L36" t="str">
         <v>Y</v>
       </c>
       <c r="M36" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N36" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level net_income_amt per counterparty.
+        <v xml:space="preserve">SUM(Net Interest Income) / SUM(Avg Earning Assets) * 100 per counterparty. Sum-ratio rollup preserves mathematical consistency.
 </v>
       </c>
       <c r="O36" t="str">
-        <v>Net Income ($) (counterparty)</v>
+        <v>Net Interest Margin (%) (counterparty)</v>
       </c>
       <c r="P36" t="str">
         <v>Y</v>
       </c>
       <c r="Q36" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R36" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level net_income_amt per L3 desk segment.
+        <v xml:space="preserve">SUM(Net Interest Income) / SUM(Avg Earning Assets) * 100 per L3 desk segment.
 </v>
       </c>
       <c r="S36" t="str">
-        <v>Net Income ($) (desk)</v>
+        <v>Net Interest Margin (%) (desk)</v>
       </c>
       <c r="T36" t="str">
         <v>Y</v>
       </c>
       <c r="U36" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V36" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level net_income_amt per L2 portfolio segment.
+        <v xml:space="preserve">SUM(Net Interest Income) / SUM(Avg Earning Assets) * 100 per L2 portfolio segment.
 </v>
       </c>
       <c r="W36" t="str">
-        <v>Net Income ($) (portfolio)</v>
+        <v>Net Interest Margin (%) (portfolio)</v>
       </c>
       <c r="X36" t="str">
         <v>Y</v>
       </c>
       <c r="Y36" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z36" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level net_income_amt per L1 business segment segment.
+        <v xml:space="preserve">SUM(Net Interest Income) / SUM(Avg Earning Assets) * 100 per L1 business segment.
 </v>
       </c>
       <c r="AA36" t="str">
-        <v>Net Income ($) (business_segment)</v>
+        <v>Net Interest Margin (%) (business_segment)</v>
       </c>
       <c r="AB36" t="str">
         <v/>
@@ -3802,17 +3984,17 @@
     </row>
     <row r="37" xml:space="preserve">
       <c r="A37" t="str">
-        <v>EXP-028</v>
+        <v>EXP-029</v>
       </c>
       <c r="B37" t="str" xml:space="preserve">
-        <v xml:space="preserve">Net Interest Income divided by earning assets. Calculated margin KPI assessing pricing effectiveness and lending profitability.
+        <v xml:space="preserve">Allocated operating or servicing cost associated with each facility. Direct-sum rollup at all aggregate levels with FX conversion to USD.
 </v>
       </c>
       <c r="C37" t="str">
-        <v>Net Interest Margin (%)</v>
+        <v>Operating Cost ($)</v>
       </c>
       <c r="D37" t="str" xml:space="preserve">
-        <v xml:space="preserve">(Interest Income - Interst Expense)/Average Earning Assets
+        <v xml:space="preserve">Read operating_expense_amt from facility_financial_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="E37" t="str">
@@ -3828,66 +4010,66 @@
         <v>Y</v>
       </c>
       <c r="I37" t="str">
-        <v>Calc</v>
+        <v>Raw</v>
       </c>
       <c r="J37" t="str" xml:space="preserve">
-        <v xml:space="preserve">(Interest Income - Interst Expense)/Average Earning Assets
+        <v xml:space="preserve">Read operating_expense_amt from facility_financial_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="K37" t="str">
-        <v>Net Interest Margin (%) (facility)</v>
+        <v>Operating Cost ($) (facility)</v>
       </c>
       <c r="L37" t="str">
         <v>Y</v>
       </c>
       <c r="M37" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="N37" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(net_interest_income) / SUM(avg_earning_assets) * 100.0 per counterparty.
+        <v xml:space="preserve">SUM of facility-level operating_expense_amt per counterparty, FX-converted to USD.
 </v>
       </c>
       <c r="O37" t="str">
-        <v>Net Interest Margin (%) (counterparty)</v>
+        <v>Operating Cost ($) (counterparty)</v>
       </c>
       <c r="P37" t="str">
         <v>Y</v>
       </c>
       <c r="Q37" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="R37" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(net_interest_income) / SUM(avg_earning_assets) * 100.0 per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level operating_expense_amt per L3 desk segment, FX-converted to USD.
 </v>
       </c>
       <c r="S37" t="str">
-        <v>Net Interest Margin (%) (desk)</v>
+        <v>Operating Cost ($) (desk)</v>
       </c>
       <c r="T37" t="str">
         <v>Y</v>
       </c>
       <c r="U37" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="V37" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(net_interest_income) / SUM(avg_earning_assets) * 100.0 per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level operating_expense_amt per L2 portfolio segment, FX-converted to USD.
 </v>
       </c>
       <c r="W37" t="str">
-        <v>Net Interest Margin (%) (portfolio)</v>
+        <v>Operating Cost ($) (portfolio)</v>
       </c>
       <c r="X37" t="str">
         <v>Y</v>
       </c>
       <c r="Y37" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="Z37" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(net_interest_income) / SUM(avg_earning_assets) * 100.0 per L1 business segment.
+        <v xml:space="preserve">SUM of facility-level operating_expense_amt per L1 business segment, FX-converted to USD.
 </v>
       </c>
       <c r="AA37" t="str">
-        <v>Net Interest Margin (%) (business_segment)</v>
+        <v>Operating Cost ($) (business_segment)</v>
       </c>
       <c r="AB37" t="str">
         <v/>
@@ -3895,17 +4077,18 @@
     </row>
     <row r="38" xml:space="preserve">
       <c r="A38" t="str">
-        <v>EXP-029</v>
+        <v>EXP-030</v>
       </c>
       <c r="B38" t="str" xml:space="preserve">
-        <v xml:space="preserve">Allocated operating or servicing cost associated with exposure.
+        <v xml:space="preserve">Model-estimated probability of default (PD) within the defined rating horizon. At facility level, sources the raw pd_pct from L2 facility_risk_snapshot. At aggregate levels, computes the exposure- weighted average: SUM(pd_pct × committed_amount) / SUM(committed_amount). This weighted-avg rollup avoids Simpson's paradox — never averages pre-computed PD rates. Core credit risk input supporting IRB capital modeling, expected loss estimation (EL = PD × LGD × EAD), stress testing, and risk appetite alignment.
 </v>
       </c>
       <c r="C38" t="str">
-        <v>Operating Cost ($)</v>
+        <v>Probability of Default (%)</v>
       </c>
       <c r="D38" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read operating_expense_amt from facility_financial_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Direct lookup of pd_pct from facility_risk_snapshot for each facility.
+Ingredients: pd_pct (L2 facility_risk_snapshot — raw model output)
 </v>
       </c>
       <c r="E38" t="str">
@@ -3924,37 +4107,47 @@
         <v>Raw</v>
       </c>
       <c r="J38" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read operating_expense_amt from facility_financial_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Direct lookup of pd_pct from facility_risk_snapshot for each facility.
+Ingredients: pd_pct (L2 facility_risk_snapshot — raw model output)
 </v>
       </c>
       <c r="K38" t="str">
-        <v>Operating Cost ($) (facility)</v>
+        <v>Probability of Default (%) (facility)</v>
       </c>
       <c r="L38" t="str">
         <v>Y</v>
       </c>
       <c r="M38" t="str">
-        <v>Raw</v>
+        <v>Avg</v>
       </c>
       <c r="N38" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read operating_expense_amt per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD pd_pct and committed_amount per facility
+  2. COMPUTE exposure-weighted average PD:
+     SUM(pd_pct × committed_amount) / SUM(committed_amount)
+Weighted-avg rollup ensures large-exposure facilities dominate the
+counterparty-level PD, avoiding equal-weight averaging bias.
 </v>
       </c>
       <c r="O38" t="str">
-        <v>Operating Cost ($) (counterparty)</v>
+        <v>Probability of Default (%) (counterparty)</v>
       </c>
       <c r="P38" t="str">
         <v>Y</v>
       </c>
       <c r="Q38" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="R38" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level operating_expense_amt per L3 desk segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOAD pd_pct and committed_amount per facility
+  2. JOIN l1.enterprise_business_taxonomy on lob_segment_id
+  3. COMPUTE SUM(pd_pct × committed_amount) / SUM(committed_amount)
+Weighted-avg rollup per desk.
 </v>
       </c>
       <c r="S38" t="str">
-        <v>Operating Cost ($) (desk)</v>
+        <v>Probability of Default (%) (desk)</v>
       </c>
       <c r="T38" t="str">
         <v>Y</v>
@@ -3963,11 +4156,15 @@
         <v>Avg</v>
       </c>
       <c r="V38" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level operating_expense_amt per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. COMPUTE SUM(pd_pct × committed_amount) / SUM(committed_amount)
+Weighted-avg rollup per portfolio. Per spec:
+Σ(probability_of_default × Outstanding_Exposure) / Σ(Total Committed Amount)
 </v>
       </c>
       <c r="W38" t="str">
-        <v>Operating Cost ($) (portfolio)</v>
+        <v>Probability of Default (%) (portfolio)</v>
       </c>
       <c r="X38" t="str">
         <v>Y</v>
@@ -3976,11 +4173,14 @@
         <v>Avg</v>
       </c>
       <c r="Z38" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level operating_expense_amt per L1 business segment segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. COMPUTE SUM(pd_pct × committed_amount) / SUM(committed_amount)
+Weighted-avg rollup per business segment.
 </v>
       </c>
       <c r="AA38" t="str">
-        <v>Operating Cost ($) (business_segment)</v>
+        <v>Probability of Default (%) (business_segment)</v>
       </c>
       <c r="AB38" t="str">
         <v/>
@@ -3988,17 +4188,17 @@
     </row>
     <row r="39" xml:space="preserve">
       <c r="A39" t="str">
-        <v>EXP-030</v>
+        <v>EXP-031</v>
       </c>
       <c r="B39" t="str" xml:space="preserve">
-        <v xml:space="preserve">Model-estimated probability of default within defined horizon. Core credit risk input supporting capital modeling, expected loss estimation, stress testing, and risk appetite alignment.
+        <v xml:space="preserve">Total facility-level revenue computed as Interest Income + Fee Income, adjusted for bank share percentage. Sourced from L2 atomic data in facility_profitability_snapshot (interest_income_amt, fee_income_amt) with bank share from facility_lender_allocation. Assesses scale of lending activity and income generation capacity.
 </v>
       </c>
       <c r="C39" t="str">
-        <v>Probability of Default (%)</v>
+        <v>Revenue ($)</v>
       </c>
       <c r="D39" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read pd_pct from facility_risk_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">[Facility Revenue] = (interest_income_amt + fee_income_amt) × bank_share_pct / 100. USD-converted for consistent reporting.
 </v>
       </c>
       <c r="E39" t="str">
@@ -4014,14 +4214,14 @@
         <v>Y</v>
       </c>
       <c r="I39" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="J39" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read pd_pct from facility_risk_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">[Facility Revenue] = (interest_income_amt + fee_income_amt) × bank_share_pct / 100. USD-converted for consistent reporting.
 </v>
       </c>
       <c r="K39" t="str">
-        <v>Probability of Default (%) (facility)</v>
+        <v>Revenue ($) (facility)</v>
       </c>
       <c r="L39" t="str">
         <v>Y</v>
@@ -4030,37 +4230,37 @@
         <v>Agg</v>
       </c>
       <c r="N39" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pd_pct per counterparty.
+        <v xml:space="preserve">SUM of facility-level revenue (bank-share-adjusted, USD-converted) per counterparty.
 </v>
       </c>
       <c r="O39" t="str">
-        <v>Probability of Default (%) (counterparty)</v>
+        <v>Revenue ($) (counterparty)</v>
       </c>
       <c r="P39" t="str">
         <v>Y</v>
       </c>
       <c r="Q39" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="R39" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level pd_pct per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level revenue (bank-share-adjusted, USD-converted) per L3 desk segment.
 </v>
       </c>
       <c r="S39" t="str">
-        <v>Probability of Default (%) (desk)</v>
+        <v>Revenue ($) (desk)</v>
       </c>
       <c r="T39" t="str">
         <v>Y</v>
       </c>
       <c r="U39" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="V39" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level pd_pct per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level revenue (bank-share-adjusted, USD-converted) per L2 portfolio segment via EBT hierarchy (one hop up).
 </v>
       </c>
       <c r="W39" t="str">
-        <v>Probability of Default (%) (portfolio)</v>
+        <v>Revenue ($) (portfolio)</v>
       </c>
       <c r="X39" t="str">
         <v>Y</v>
@@ -4069,11 +4269,11 @@
         <v>Agg</v>
       </c>
       <c r="Z39" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pd_pct per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level revenue (bank-share-adjusted, USD-converted) per L1 business segment via EBT hierarchy (two hops up).
 </v>
       </c>
       <c r="AA39" t="str">
-        <v>Probability of Default (%) (business_segment)</v>
+        <v>Revenue ($) (business_segment)</v>
       </c>
       <c r="AB39" t="str">
         <v/>
@@ -4081,17 +4281,17 @@
     </row>
     <row r="40" xml:space="preserve">
       <c r="A40" t="str">
-        <v>EXP-031</v>
+        <v>EXP-032</v>
       </c>
       <c r="B40" t="str" xml:space="preserve">
-        <v xml:space="preserve">Total income generated by the borrower or attributed to the facility in millions USD. Used to assess scale and repayment capacity.
+        <v xml:space="preserve">Original appraised value of pledged collateral securing exposure, in USD. At facility level, sums original_valuation_usd from collateral_snapshot weighted by the bank's syndication share (bank_share_pct from facility_lender_allocation). Rolls up additively through counterparty, desk, portfolio, and business segment via the standard EBT hierarchy. Supports recovery analysis and secured lending assessment.
 </v>
       </c>
       <c r="C40" t="str">
-        <v>Revenue ($)</v>
+        <v>Collateral Market Value at Origination ($)</v>
       </c>
       <c r="D40" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(revenue_amt) per facility from facility_financial_snapshot. Weighted by bank share percentage.
+        <v xml:space="preserve">SUM(original_valuation_usd * bank_share_pct / 100) per facility. Bank share defaults to 100% if no lender allocation record.
 </v>
       </c>
       <c r="E40" t="str">
@@ -4110,11 +4310,11 @@
         <v>Agg</v>
       </c>
       <c r="J40" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(revenue_amt) per facility from facility_financial_snapshot. Weighted by bank share percentage.
+        <v xml:space="preserve">SUM(original_valuation_usd * bank_share_pct / 100) per facility. Bank share defaults to 100% if no lender allocation record.
 </v>
       </c>
       <c r="K40" t="str">
-        <v>Revenue ($) (facility)</v>
+        <v>Collateral Market Value at Origination ($) (facility)</v>
       </c>
       <c r="L40" t="str">
         <v>Y</v>
@@ -4123,11 +4323,11 @@
         <v>Agg</v>
       </c>
       <c r="N40" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level revenue_amt per counterparty.
+        <v xml:space="preserve">SUM of facility-level collateral origination value per counterparty.
 </v>
       </c>
       <c r="O40" t="str">
-        <v>Revenue ($) (counterparty)</v>
+        <v>Collateral Market Value at Origination ($) (counterparty)</v>
       </c>
       <c r="P40" t="str">
         <v>Y</v>
@@ -4136,11 +4336,11 @@
         <v>Agg</v>
       </c>
       <c r="R40" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level revenue_amt per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level collateral origination value per L3 desk segment.
 </v>
       </c>
       <c r="S40" t="str">
-        <v>Revenue ($) (desk)</v>
+        <v>Collateral Market Value at Origination ($) (desk)</v>
       </c>
       <c r="T40" t="str">
         <v>Y</v>
@@ -4149,11 +4349,11 @@
         <v>Agg</v>
       </c>
       <c r="V40" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level revenue_amt per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level collateral origination value per L2 portfolio segment.
 </v>
       </c>
       <c r="W40" t="str">
-        <v>Revenue ($) (portfolio)</v>
+        <v>Collateral Market Value at Origination ($) (portfolio)</v>
       </c>
       <c r="X40" t="str">
         <v>Y</v>
@@ -4162,11 +4362,11 @@
         <v>Agg</v>
       </c>
       <c r="Z40" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level revenue_amt per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level collateral origination value per L1 business segment.
 </v>
       </c>
       <c r="AA40" t="str">
-        <v>Revenue ($) (business_segment)</v>
+        <v>Collateral Market Value at Origination ($) (business_segment)</v>
       </c>
       <c r="AB40" t="str">
         <v/>
@@ -4174,17 +4374,17 @@
     </row>
     <row r="41" xml:space="preserve">
       <c r="A41" t="str">
-        <v>EXP-032</v>
+        <v>EXP-033</v>
       </c>
       <c r="B41" t="str" xml:space="preserve">
-        <v xml:space="preserve">Original Appriased Value of pledged collateral securing exposure in USD. Supports recovery analysis and secured lending assessment.
+        <v xml:space="preserve">Count of distinct risk mitigant sub-types protecting exposure at each rollup level. Joins through the risk_mitigant_link bridge table to risk_mitigant_master and the risk_mitigant_type_dim taxonomy. Measures mitigation diversification — higher counts indicate broader collateral coverage across different sub-type categories (e.g. Sovereign Guarantee, Bank Guarantee, Cash Collateral, Real Estate, Equipment).
 </v>
       </c>
       <c r="C41" t="str">
-        <v>Collateral Market Value at Origination ($)</v>
+        <v>Risk Mitigant Sub Type</v>
       </c>
       <c r="D41" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(original_valuation_usd) per facility from collateral_snapshot. Weighted by bank share percentage.
+        <v xml:space="preserve">COUNT DISTINCT risk_mitigant_subtype_code per facility via risk_mitigant_link -&gt; risk_mitigant_master -&gt; risk_mitigant_type_dim. Only active mitigants with current link status.
 </v>
       </c>
       <c r="E41" t="str">
@@ -4203,11 +4403,11 @@
         <v>Agg</v>
       </c>
       <c r="J41" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(original_valuation_usd) per facility from collateral_snapshot. Weighted by bank share percentage.
+        <v xml:space="preserve">COUNT DISTINCT risk_mitigant_subtype_code per facility via risk_mitigant_link -&gt; risk_mitigant_master -&gt; risk_mitigant_type_dim. Only active mitigants with current link status.
 </v>
       </c>
       <c r="K41" t="str">
-        <v>Collateral Market Value at Origination ($) (facility)</v>
+        <v>Risk Mitigant Sub Type (facility)</v>
       </c>
       <c r="L41" t="str">
         <v>Y</v>
@@ -4216,11 +4416,11 @@
         <v>Agg</v>
       </c>
       <c r="N41" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level original_valuation_usd per counterparty.
+        <v xml:space="preserve">COUNT DISTINCT risk_mitigant_subtype_code across all facilities per counterparty.
 </v>
       </c>
       <c r="O41" t="str">
-        <v>Collateral Market Value at Origination ($) (counterparty)</v>
+        <v>Risk Mitigant Sub Type (counterparty)</v>
       </c>
       <c r="P41" t="str">
         <v>Y</v>
@@ -4229,11 +4429,11 @@
         <v>Agg</v>
       </c>
       <c r="R41" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level original_valuation_usd per L3 desk segment.
+        <v xml:space="preserve">COUNT DISTINCT risk_mitigant_subtype_code across all facilities per L3 desk segment.
 </v>
       </c>
       <c r="S41" t="str">
-        <v>Collateral Market Value at Origination ($) (desk)</v>
+        <v>Risk Mitigant Sub Type (desk)</v>
       </c>
       <c r="T41" t="str">
         <v>Y</v>
@@ -4242,11 +4442,11 @@
         <v>Agg</v>
       </c>
       <c r="V41" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level original_valuation_usd per L2 portfolio segment.
+        <v xml:space="preserve">COUNT DISTINCT risk_mitigant_subtype_code across all facilities per L2 portfolio segment.
 </v>
       </c>
       <c r="W41" t="str">
-        <v>Collateral Market Value at Origination ($) (portfolio)</v>
+        <v>Risk Mitigant Sub Type (portfolio)</v>
       </c>
       <c r="X41" t="str">
         <v>Y</v>
@@ -4255,11 +4455,11 @@
         <v>Agg</v>
       </c>
       <c r="Z41" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level original_valuation_usd per L1 business segment segment.
+        <v xml:space="preserve">COUNT DISTINCT risk_mitigant_subtype_code across all facilities per L1 business segment.
 </v>
       </c>
       <c r="AA41" t="str">
-        <v>Collateral Market Value at Origination ($) (business_segment)</v>
+        <v>Risk Mitigant Sub Type (business_segment)</v>
       </c>
       <c r="AB41" t="str">
         <v/>
@@ -4267,17 +4467,17 @@
     </row>
     <row r="42" xml:space="preserve">
       <c r="A42" t="str">
-        <v>EXP-033</v>
+        <v>EXP-034</v>
       </c>
       <c r="B42" t="str" xml:space="preserve">
-        <v xml:space="preserve">Sub-classification of risk mitigant or collateral type tied to the facility. Used for granular risk segmentation.
+        <v xml:space="preserve">Count of distinct risk mitigant parent categories protecting exposure at each rollup level. Joins through the risk_mitigant_link bridge table to risk_mitigant_master and the risk_mitigant_type_dim taxonomy, reading the mitigant_category field (e.g. Cash, Real Estate, Guarantee, Insurance, Equipment). Provides a higher-level view of mitigation diversification compared to EXP-033 (sub-type detail). Supports recovery assessment and CRM eligibility analysis.
 </v>
       </c>
       <c r="C42" t="str">
-        <v>Risk Mitigant Sub Type</v>
+        <v>Risk Mitigant Type</v>
       </c>
       <c r="D42" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(risk_mitigant_subtype_code) per facility from risk_mitigant_type_dim.
+        <v xml:space="preserve">COUNT DISTINCT mitigant_category per facility via risk_mitigant_link -&gt; risk_mitigant_master -&gt; risk_mitigant_type_dim. Only active mitigants with current link status.
 </v>
       </c>
       <c r="E42" t="str">
@@ -4296,24 +4496,24 @@
         <v>Agg</v>
       </c>
       <c r="J42" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(risk_mitigant_subtype_code) per facility from risk_mitigant_type_dim.
+        <v xml:space="preserve">COUNT DISTINCT mitigant_category per facility via risk_mitigant_link -&gt; risk_mitigant_master -&gt; risk_mitigant_type_dim. Only active mitigants with current link status.
 </v>
       </c>
       <c r="K42" t="str">
-        <v>Risk Mitigant Sub Type (facility)</v>
+        <v>Risk Mitigant Type (facility)</v>
       </c>
       <c r="L42" t="str">
         <v>Y</v>
       </c>
       <c r="M42" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="N42" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_mitigant_subtype_code per counterparty.
+        <v xml:space="preserve">COUNT DISTINCT mitigant_category across all facilities per counterparty.
 </v>
       </c>
       <c r="O42" t="str">
-        <v>Risk Mitigant Sub Type (counterparty)</v>
+        <v>Risk Mitigant Type (counterparty)</v>
       </c>
       <c r="P42" t="str">
         <v>Y</v>
@@ -4322,11 +4522,11 @@
         <v>Agg</v>
       </c>
       <c r="R42" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_mitigant_subtype_code per L3 desk segment.
+        <v xml:space="preserve">COUNT DISTINCT mitigant_category across all facilities per L3 desk segment.
 </v>
       </c>
       <c r="S42" t="str">
-        <v>Risk Mitigant Sub Type (desk)</v>
+        <v>Risk Mitigant Type (desk)</v>
       </c>
       <c r="T42" t="str">
         <v>Y</v>
@@ -4335,11 +4535,11 @@
         <v>Agg</v>
       </c>
       <c r="V42" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_mitigant_subtype_code per L2 portfolio segment.
+        <v xml:space="preserve">COUNT DISTINCT mitigant_category across all facilities per L2 portfolio segment.
 </v>
       </c>
       <c r="W42" t="str">
-        <v>Risk Mitigant Sub Type (portfolio)</v>
+        <v>Risk Mitigant Type (portfolio)</v>
       </c>
       <c r="X42" t="str">
         <v>Y</v>
@@ -4348,11 +4548,11 @@
         <v>Agg</v>
       </c>
       <c r="Z42" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_mitigant_subtype_code per L1 business segment segment.
+        <v xml:space="preserve">COUNT DISTINCT mitigant_category across all facilities per L1 business segment.
 </v>
       </c>
       <c r="AA42" t="str">
-        <v>Risk Mitigant Sub Type (business_segment)</v>
+        <v>Risk Mitigant Type (business_segment)</v>
       </c>
       <c r="AB42" t="str">
         <v/>
@@ -4360,17 +4560,17 @@
     </row>
     <row r="43" xml:space="preserve">
       <c r="A43" t="str">
-        <v>EXP-034</v>
+        <v>EXP-035</v>
       </c>
       <c r="B43" t="str" xml:space="preserve">
-        <v xml:space="preserve">Parent group of risk mitigation or collateral asset type (e.g., cash, aviation, guarantee). Used to assess recovery support mechanisms.
+        <v xml:space="preserve">Net Income divided by Total Assets (at counterparty level) or Committed Exposure bank-share (at facility level). Measures asset utilization efficiency and overall financial performance.
 </v>
       </c>
       <c r="C43" t="str">
-        <v>Risk Mitigant Type</v>
+        <v>Return on Assets (%)</v>
       </c>
       <c r="D43" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(risk_mitigant_id) per facility from risk_mitigant_master.
+        <v xml:space="preserve">Facility Net Income / Committed Exposure (Bank Share portion only).
 </v>
       </c>
       <c r="E43" t="str">
@@ -4386,66 +4586,66 @@
         <v>Y</v>
       </c>
       <c r="I43" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="J43" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(risk_mitigant_id) per facility from risk_mitigant_master.
+        <v xml:space="preserve">Facility Net Income / Committed Exposure (Bank Share portion only).
 </v>
       </c>
       <c r="K43" t="str">
-        <v>Risk Mitigant Type (facility)</v>
+        <v>Return on Assets (%) (facility)</v>
       </c>
       <c r="L43" t="str">
         <v>Y</v>
       </c>
       <c r="M43" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="N43" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_mitigant_id per counterparty.
+        <v xml:space="preserve">Counterparty Net Income / Total Assets * 100. Net income computed from revenue minus expenses.
 </v>
       </c>
       <c r="O43" t="str">
-        <v>Risk Mitigant Type (counterparty)</v>
+        <v>Return on Assets (%) (counterparty)</v>
       </c>
       <c r="P43" t="str">
         <v>Y</v>
       </c>
       <c r="Q43" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="R43" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_mitigant_id per L3 desk segment.
+        <v xml:space="preserve">Exposure-weighted average ROA per L3 desk segment.
 </v>
       </c>
       <c r="S43" t="str">
-        <v>Risk Mitigant Type (desk)</v>
+        <v>Return on Assets (%) (desk)</v>
       </c>
       <c r="T43" t="str">
         <v>Y</v>
       </c>
       <c r="U43" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="V43" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_mitigant_id per L2 portfolio segment.
+        <v xml:space="preserve">Exposure-weighted average ROA per L2 portfolio segment.
 </v>
       </c>
       <c r="W43" t="str">
-        <v>Risk Mitigant Type (portfolio)</v>
+        <v>Return on Assets (%) (portfolio)</v>
       </c>
       <c r="X43" t="str">
         <v>Y</v>
       </c>
       <c r="Y43" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="Z43" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_mitigant_id per L1 business segment segment.
+        <v xml:space="preserve">Exposure-weighted average ROA per L1 business segment.
 </v>
       </c>
       <c r="AA43" t="str">
-        <v>Risk Mitigant Type (business_segment)</v>
+        <v>Return on Assets (%) (business_segment)</v>
       </c>
       <c r="AB43" t="str">
         <v/>
@@ -4453,14 +4653,14 @@
     </row>
     <row r="44" xml:space="preserve">
       <c r="A44" t="str">
-        <v>EXP-035</v>
+        <v>EXP-036</v>
       </c>
       <c r="B44" t="str" xml:space="preserve">
-        <v xml:space="preserve">Net Income divided by Total Assets (at counterparty level) or Committed Exposure bank-share (at facility level). Measures asset utilization efficiency and overall financial performance.
+        <v xml:space="preserve">Net Income divided by Shareholders Equity. Profitability KPI measuring return generated on shareholder capital. At facility level uses committed exposure (bank share) as denominator proxy.
 </v>
       </c>
       <c r="C44" t="str">
-        <v>Return on Assets (%)</v>
+        <v>Return on Equity (%)</v>
       </c>
       <c r="D44" t="str" xml:space="preserve">
         <v xml:space="preserve">Facility Net Income / Committed Exposure (Bank Share portion only).
@@ -4486,7 +4686,7 @@
 </v>
       </c>
       <c r="K44" t="str">
-        <v>Return on Assets (%) (facility)</v>
+        <v>Return on Equity (%) (facility)</v>
       </c>
       <c r="L44" t="str">
         <v>Y</v>
@@ -4495,11 +4695,11 @@
         <v>Calc</v>
       </c>
       <c r="N44" t="str" xml:space="preserve">
-        <v xml:space="preserve">Counterparty Net Income / Total Assets * 100. Net income computed from revenue minus expenses.
+        <v xml:space="preserve">Counterparty Net Income / Shareholders Equity * 100. Net income computed from revenue minus expenses.
 </v>
       </c>
       <c r="O44" t="str">
-        <v>Return on Assets (%) (counterparty)</v>
+        <v>Return on Equity (%) (counterparty)</v>
       </c>
       <c r="P44" t="str">
         <v>Y</v>
@@ -4508,11 +4708,11 @@
         <v>Avg</v>
       </c>
       <c r="R44" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average ROA per L3 desk segment.
+        <v xml:space="preserve">Exposure-weighted average ROE per L3 desk segment.
 </v>
       </c>
       <c r="S44" t="str">
-        <v>Return on Assets (%) (desk)</v>
+        <v>Return on Equity (%) (desk)</v>
       </c>
       <c r="T44" t="str">
         <v>Y</v>
@@ -4521,11 +4721,11 @@
         <v>Avg</v>
       </c>
       <c r="V44" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average ROA per L2 portfolio segment.
+        <v xml:space="preserve">Exposure-weighted average ROE per L2 portfolio segment.
 </v>
       </c>
       <c r="W44" t="str">
-        <v>Return on Assets (%) (portfolio)</v>
+        <v>Return on Equity (%) (portfolio)</v>
       </c>
       <c r="X44" t="str">
         <v>Y</v>
@@ -4534,11 +4734,11 @@
         <v>Avg</v>
       </c>
       <c r="Z44" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average ROA per L1 business segment.
+        <v xml:space="preserve">Exposure-weighted average ROE per L1 business segment.
 </v>
       </c>
       <c r="AA44" t="str">
-        <v>Return on Assets (%) (business_segment)</v>
+        <v>Return on Equity (%) (business_segment)</v>
       </c>
       <c r="AB44" t="str">
         <v/>
@@ -4546,17 +4746,17 @@
     </row>
     <row r="45" xml:space="preserve">
       <c r="A45" t="str">
-        <v>EXP-036</v>
+        <v>EXP-037</v>
       </c>
       <c r="B45" t="str" xml:space="preserve">
-        <v xml:space="preserve">Net Income divided by Shareholders Equity. Profitability KPI measuring return generated on shareholder capital. At facility level uses committed exposure (bank share) as denominator proxy.
+        <v xml:space="preserve">Total principal and interest obligations due within reporting period. Facility level in local currency; counterparty and above converted to USD. Used in repayment capacity and covenant analysis.
 </v>
       </c>
       <c r="C45" t="str">
-        <v>Return on Equity (%)</v>
+        <v>Total Debt Service ($)</v>
       </c>
       <c r="D45" t="str" xml:space="preserve">
-        <v xml:space="preserve">Facility Net Income / Committed Exposure (Bank Share portion only).
+        <v xml:space="preserve">Interest Expense + Principal Payment from facility_financial_snapshot. Facility level stays in local currency (no FX conversion).
 </v>
       </c>
       <c r="E45" t="str">
@@ -4575,63 +4775,63 @@
         <v>Calc</v>
       </c>
       <c r="J45" t="str" xml:space="preserve">
-        <v xml:space="preserve">Facility Net Income / Committed Exposure (Bank Share portion only).
+        <v xml:space="preserve">Interest Expense + Principal Payment from facility_financial_snapshot. Facility level stays in local currency (no FX conversion).
 </v>
       </c>
       <c r="K45" t="str">
-        <v>Return on Equity (%) (facility)</v>
+        <v>Total Debt Service ($) (facility)</v>
       </c>
       <c r="L45" t="str">
         <v>Y</v>
       </c>
       <c r="M45" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="N45" t="str" xml:space="preserve">
-        <v xml:space="preserve">Counterparty Net Income / Shareholders Equity * 100. Net income computed from revenue minus expenses.
+        <v xml:space="preserve">SUM of facility-level TDS converted to USD per counterparty.
 </v>
       </c>
       <c r="O45" t="str">
-        <v>Return on Equity (%) (counterparty)</v>
+        <v>Total Debt Service ($) (counterparty)</v>
       </c>
       <c r="P45" t="str">
         <v>Y</v>
       </c>
       <c r="Q45" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="R45" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average ROE per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level TDS converted to USD per L3 desk segment.
 </v>
       </c>
       <c r="S45" t="str">
-        <v>Return on Equity (%) (desk)</v>
+        <v>Total Debt Service ($) (desk)</v>
       </c>
       <c r="T45" t="str">
         <v>Y</v>
       </c>
       <c r="U45" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="V45" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average ROE per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level TDS converted to USD per L2 portfolio segment.
 </v>
       </c>
       <c r="W45" t="str">
-        <v>Return on Equity (%) (portfolio)</v>
+        <v>Total Debt Service ($) (portfolio)</v>
       </c>
       <c r="X45" t="str">
         <v>Y</v>
       </c>
       <c r="Y45" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="Z45" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average ROE per L1 business segment.
+        <v xml:space="preserve">SUM of facility-level TDS converted to USD per L1 business segment.
 </v>
       </c>
       <c r="AA45" t="str">
-        <v>Return on Equity (%) (business_segment)</v>
+        <v>Total Debt Service ($) (business_segment)</v>
       </c>
       <c r="AB45" t="str">
         <v/>
@@ -4639,17 +4839,17 @@
     </row>
     <row r="46" xml:space="preserve">
       <c r="A46" t="str">
-        <v>EXP-037</v>
+        <v>EXP-038</v>
       </c>
       <c r="B46" t="str" xml:space="preserve">
-        <v xml:space="preserve">Total principal and interest obligations due within reporting period. Facility level in local currency; counterparty and above converted to USD. Used in repayment capacity and covenant analysis.
+        <v xml:space="preserve">Exposure divided by Exposure Limit. Calculated KPI measuring the proportion of approved capacity currently drawn, providing insight into liquidity usage and limit pressure.
 </v>
       </c>
       <c r="C46" t="str">
-        <v>Total Debt Service ($)</v>
+        <v>Utilization (%)</v>
       </c>
       <c r="D46" t="str" xml:space="preserve">
-        <v xml:space="preserve">Interest Expense + Principal Payment from facility_financial_snapshot. Facility level stays in local currency (no FX conversion).
+        <v xml:space="preserve">For each Distinct([Facility ID]), WHEN IS(MAX(AS_OF_DATE) AND [Facility_Active_Flag]="Y" Sum([Utilized Exposure] / [Committed_Facility_Amt])
 </v>
       </c>
       <c r="E46" t="str">
@@ -4668,63 +4868,63 @@
         <v>Calc</v>
       </c>
       <c r="J46" t="str" xml:space="preserve">
-        <v xml:space="preserve">Interest Expense + Principal Payment from facility_financial_snapshot. Facility level stays in local currency (no FX conversion).
+        <v xml:space="preserve">For each Distinct([Facility ID]), WHEN IS(MAX(AS_OF_DATE) AND [Facility_Active_Flag]="Y" Sum([Utilized Exposure] / [Committed_Facility_Amt])
 </v>
       </c>
       <c r="K46" t="str">
-        <v>Total Debt Service ($) (facility)</v>
+        <v>Utilization (%) (facility)</v>
       </c>
       <c r="L46" t="str">
         <v>Y</v>
       </c>
       <c r="M46" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N46" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level TDS converted to USD per counterparty.
+        <v xml:space="preserve">SUM(drawn_amount) / SUM(committed_amount) * 100.0 per counterparty.
 </v>
       </c>
       <c r="O46" t="str">
-        <v>Total Debt Service ($) (counterparty)</v>
+        <v>Utilization (%) (counterparty)</v>
       </c>
       <c r="P46" t="str">
         <v>Y</v>
       </c>
       <c r="Q46" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R46" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level TDS converted to USD per L3 desk segment.
+        <v xml:space="preserve">SUM(drawn_amount) / SUM(committed_amount) * 100.0 per L3 desk segment.
 </v>
       </c>
       <c r="S46" t="str">
-        <v>Total Debt Service ($) (desk)</v>
+        <v>Utilization (%) (desk)</v>
       </c>
       <c r="T46" t="str">
         <v>Y</v>
       </c>
       <c r="U46" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V46" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level TDS converted to USD per L2 portfolio segment.
+        <v xml:space="preserve">SUM(drawn_amount) / SUM(committed_amount) * 100.0 per L2 portfolio segment.
 </v>
       </c>
       <c r="W46" t="str">
-        <v>Total Debt Service ($) (portfolio)</v>
+        <v>Utilization (%) (portfolio)</v>
       </c>
       <c r="X46" t="str">
         <v>Y</v>
       </c>
       <c r="Y46" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z46" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level TDS converted to USD per L1 business segment.
+        <v xml:space="preserve">SUM(drawn_amount) / SUM(committed_amount) * 100.0 per L1 business segment.
 </v>
       </c>
       <c r="AA46" t="str">
-        <v>Total Debt Service ($) (business_segment)</v>
+        <v>Utilization (%) (business_segment)</v>
       </c>
       <c r="AB46" t="str">
         <v/>
@@ -4732,17 +4932,17 @@
     </row>
     <row r="47" xml:space="preserve">
       <c r="A47" t="str">
-        <v>EXP-038</v>
+        <v>EXP-039</v>
       </c>
       <c r="B47" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure divided by Exposure Limit. Calculated KPI measuring the proportion of approved capacity currently drawn, providing insight into liquidity usage and limit pressure.
+        <v xml:space="preserve">The currently drawn/outstanding amount (in USD) on the facility as of the reporting date.
 </v>
       </c>
       <c r="C47" t="str">
-        <v>Utilization (%)</v>
+        <v>Utilized Amount ($)</v>
       </c>
       <c r="D47" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Distinct([Facility ID]), WHEN IS(MAX(AS_OF_DATE) AND [Facility_Active_Flag]="Y" Sum([Utilized Exposure] / [Committed_Facility_Amt])
+        <v xml:space="preserve">Read utilized_amount_usd from limit_utilization_event for each facility as- of reporting date.
 </v>
       </c>
       <c r="E47" t="str">
@@ -4758,66 +4958,66 @@
         <v>Y</v>
       </c>
       <c r="I47" t="str">
-        <v>Calc</v>
+        <v>Raw</v>
       </c>
       <c r="J47" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each Distinct([Facility ID]), WHEN IS(MAX(AS_OF_DATE) AND [Facility_Active_Flag]="Y" Sum([Utilized Exposure] / [Committed_Facility_Amt])
+        <v xml:space="preserve">Read utilized_amount_usd from limit_utilization_event for each facility as- of reporting date.
 </v>
       </c>
       <c r="K47" t="str">
-        <v>Utilization (%) (facility)</v>
+        <v>Utilized Amount ($) (facility)</v>
       </c>
       <c r="L47" t="str">
         <v>Y</v>
       </c>
       <c r="M47" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="N47" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(drawn_amount) / SUM(committed_amount) * 100.0 per counterparty.
+        <v xml:space="preserve">SUM of facility-level utilized_amount_usd per counterparty.
 </v>
       </c>
       <c r="O47" t="str">
-        <v>Utilization (%) (counterparty)</v>
+        <v>Utilized Amount ($) (counterparty)</v>
       </c>
       <c r="P47" t="str">
         <v>Y</v>
       </c>
       <c r="Q47" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="R47" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(drawn_amount) / SUM(committed_amount) * 100.0 per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level utilized_amount_usd per L3 desk segment.
 </v>
       </c>
       <c r="S47" t="str">
-        <v>Utilization (%) (desk)</v>
+        <v>Utilized Amount ($) (desk)</v>
       </c>
       <c r="T47" t="str">
         <v>Y</v>
       </c>
       <c r="U47" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="V47" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(drawn_amount) / SUM(committed_amount) * 100.0 per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level utilized_amount_usd per L2 portfolio segment.
 </v>
       </c>
       <c r="W47" t="str">
-        <v>Utilization (%) (portfolio)</v>
+        <v>Utilized Amount ($) (portfolio)</v>
       </c>
       <c r="X47" t="str">
         <v>Y</v>
       </c>
       <c r="Y47" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="Z47" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(drawn_amount) / SUM(committed_amount) * 100.0 per L1 business segment.
+        <v xml:space="preserve">SUM of facility-level utilized_amount_usd per L1 business segment segment.
 </v>
       </c>
       <c r="AA47" t="str">
-        <v>Utilization (%) (business_segment)</v>
+        <v>Utilized Amount ($) (business_segment)</v>
       </c>
       <c r="AB47" t="str">
         <v/>
@@ -4825,17 +5025,18 @@
     </row>
     <row r="48" xml:space="preserve">
       <c r="A48" t="str">
-        <v>EXP-039</v>
+        <v>EXP-041</v>
       </c>
       <c r="B48" t="str" xml:space="preserve">
-        <v xml:space="preserve">The currently drawn/outstanding amount (in USD) on the facility as of the reporting date.
+        <v xml:space="preserve">Total interest earned on outstanding exposures during the reporting period. Sources from facility_profitability_snapshot.interest_income_amt (ETL'd from core banking, includes proper accrual and day-count per ASC 310-20). Bank-share-adjusted via facility_lender_allocation.
 </v>
       </c>
       <c r="C48" t="str">
-        <v>Utilized Amount ($)</v>
+        <v>Interest Income</v>
       </c>
       <c r="D48" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read utilized_amount_usd from limit_utilization_event for each facility as- of reporting date.
+        <v xml:space="preserve">SUM(interest_income_amt) per facility from facility_profitability_snapshot.
+Weighted by bank_share_pct from facility_lender_allocation.
 </v>
       </c>
       <c r="E48" t="str">
@@ -4851,27 +5052,29 @@
         <v>Y</v>
       </c>
       <c r="I48" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="J48" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read utilized_amount_usd from limit_utilization_event for each facility as- of reporting date.
+        <v xml:space="preserve">SUM(interest_income_amt) per facility from facility_profitability_snapshot.
+Weighted by bank_share_pct from facility_lender_allocation.
 </v>
       </c>
       <c r="K48" t="str">
-        <v>Utilized Amount ($) (facility)</v>
+        <v>Interest Income (facility)</v>
       </c>
       <c r="L48" t="str">
         <v>Y</v>
       </c>
       <c r="M48" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N48" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level utilized_amount_usd per counterparty.
+        <v xml:space="preserve">For each counterparty, sum facility-level interest income weighted
+by participation_pct from facility_counterparty_participation.
 </v>
       </c>
       <c r="O48" t="str">
-        <v>Utilized Amount ($) (counterparty)</v>
+        <v>Interest Income (counterparty)</v>
       </c>
       <c r="P48" t="str">
         <v>Y</v>
@@ -4880,11 +5083,11 @@
         <v>Agg</v>
       </c>
       <c r="R48" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level utilized_amount_usd per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level interest income per L3 desk segment.
 </v>
       </c>
       <c r="S48" t="str">
-        <v>Utilized Amount ($) (desk)</v>
+        <v>Interest Income (desk)</v>
       </c>
       <c r="T48" t="str">
         <v>Y</v>
@@ -4893,11 +5096,12 @@
         <v>Agg</v>
       </c>
       <c r="V48" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level utilized_amount_usd per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level interest income per L2 portfolio segment.
+Traverses L3 -&gt; L2 via parent_segment_id.
 </v>
       </c>
       <c r="W48" t="str">
-        <v>Utilized Amount ($) (portfolio)</v>
+        <v>Interest Income (portfolio)</v>
       </c>
       <c r="X48" t="str">
         <v>Y</v>
@@ -4906,11 +5110,12 @@
         <v>Agg</v>
       </c>
       <c r="Z48" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level utilized_amount_usd per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level interest income per L1 business segment.
+Traverses L3 -&gt; L2 -&gt; L1 via parent_segment_id chain.
 </v>
       </c>
       <c r="AA48" t="str">
-        <v>Utilized Amount ($) (business_segment)</v>
+        <v>Interest Income (business_segment)</v>
       </c>
       <c r="AB48" t="str">
         <v/>
@@ -4918,18 +5123,17 @@
     </row>
     <row r="49" xml:space="preserve">
       <c r="A49" t="str">
-        <v>EXP-041</v>
+        <v>EXP-042</v>
       </c>
       <c r="B49" t="str" xml:space="preserve">
-        <v xml:space="preserve">Total interest earned on outstanding exposures during the reporting period. Sources from facility_profitability_snapshot.interest_income_amt (ETL'd from core banking, includes proper accrual and day-count per ASC 310-20). Bank-share-adjusted via facility_lender_allocation.
+        <v xml:space="preserve">Total on-balance-sheet assets attributable to the reporting entity at a point in time.
 </v>
       </c>
       <c r="C49" t="str">
-        <v>Interest Income</v>
+        <v>Total Assets Amount</v>
       </c>
       <c r="D49" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(interest_income_amt) per facility from facility_profitability_snapshot.
-Weighted by bank_share_pct from facility_lender_allocation.
+        <v xml:space="preserve">SUM(total_assets_amt) per facility from counterparty_financial_snapshot. Weighted by bank share percentage.
 </v>
       </c>
       <c r="E49" t="str">
@@ -4948,26 +5152,24 @@
         <v>Agg</v>
       </c>
       <c r="J49" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(interest_income_amt) per facility from facility_profitability_snapshot.
-Weighted by bank_share_pct from facility_lender_allocation.
+        <v xml:space="preserve">SUM(total_assets_amt) per facility from counterparty_financial_snapshot. Weighted by bank share percentage.
 </v>
       </c>
       <c r="K49" t="str">
-        <v>Interest Income (facility)</v>
+        <v>Total Assets Amount (facility)</v>
       </c>
       <c r="L49" t="str">
         <v>Y</v>
       </c>
       <c r="M49" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="N49" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each counterparty, sum facility-level interest income weighted
-by participation_pct from facility_counterparty_participation.
+        <v xml:space="preserve">SUM of facility-level total_assets_amt per counterparty.
 </v>
       </c>
       <c r="O49" t="str">
-        <v>Interest Income (counterparty)</v>
+        <v>Total Assets Amount (counterparty)</v>
       </c>
       <c r="P49" t="str">
         <v>Y</v>
@@ -4976,11 +5178,11 @@
         <v>Agg</v>
       </c>
       <c r="R49" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level interest income per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level total_assets_amt per L3 desk segment.
 </v>
       </c>
       <c r="S49" t="str">
-        <v>Interest Income (desk)</v>
+        <v>Total Assets Amount (desk)</v>
       </c>
       <c r="T49" t="str">
         <v>Y</v>
@@ -4989,12 +5191,11 @@
         <v>Agg</v>
       </c>
       <c r="V49" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level interest income per L2 portfolio segment.
-Traverses L3 -&gt; L2 via parent_segment_id.
+        <v xml:space="preserve">SUM of facility-level total_assets_amt per L2 portfolio segment.
 </v>
       </c>
       <c r="W49" t="str">
-        <v>Interest Income (portfolio)</v>
+        <v>Total Assets Amount (portfolio)</v>
       </c>
       <c r="X49" t="str">
         <v>Y</v>
@@ -5003,12 +5204,11 @@
         <v>Agg</v>
       </c>
       <c r="Z49" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level interest income per L1 business segment.
-Traverses L3 -&gt; L2 -&gt; L1 via parent_segment_id chain.
+        <v xml:space="preserve">SUM of facility-level total_assets_amt per L1 business segment segment.
 </v>
       </c>
       <c r="AA49" t="str">
-        <v>Interest Income (business_segment)</v>
+        <v>Total Assets Amount (business_segment)</v>
       </c>
       <c r="AB49" t="str">
         <v/>
@@ -5016,17 +5216,17 @@
     </row>
     <row r="50" xml:space="preserve">
       <c r="A50" t="str">
-        <v>EXP-042</v>
+        <v>EXP-043</v>
       </c>
       <c r="B50" t="str" xml:space="preserve">
-        <v xml:space="preserve">Total on-balance-sheet assets attributable to the reporting entity at a point in time.
+        <v xml:space="preserve">Total shareholder capital allocated to the reporting unit.
 </v>
       </c>
       <c r="C50" t="str">
-        <v>Total Assets Amount</v>
+        <v>Total Equity amount</v>
       </c>
       <c r="D50" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(total_assets_amt) per facility from counterparty_financial_snapshot. Weighted by bank share percentage.
+        <v xml:space="preserve">SUM(allocated_equity_amt) per facility from facility_profitability_snapshot. Weighted by bank share percentage.
 </v>
       </c>
       <c r="E50" t="str">
@@ -5045,11 +5245,11 @@
         <v>Agg</v>
       </c>
       <c r="J50" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(total_assets_amt) per facility from counterparty_financial_snapshot. Weighted by bank share percentage.
+        <v xml:space="preserve">SUM(allocated_equity_amt) per facility from facility_profitability_snapshot. Weighted by bank share percentage.
 </v>
       </c>
       <c r="K50" t="str">
-        <v>Total Assets Amount (facility)</v>
+        <v>Total Equity amount (facility)</v>
       </c>
       <c r="L50" t="str">
         <v>Y</v>
@@ -5058,11 +5258,11 @@
         <v>Agg</v>
       </c>
       <c r="N50" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_assets_amt per counterparty.
+        <v xml:space="preserve">SUM of facility-level allocated_equity_amt per counterparty.
 </v>
       </c>
       <c r="O50" t="str">
-        <v>Total Assets Amount (counterparty)</v>
+        <v>Total Equity amount (counterparty)</v>
       </c>
       <c r="P50" t="str">
         <v>Y</v>
@@ -5071,11 +5271,11 @@
         <v>Agg</v>
       </c>
       <c r="R50" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_assets_amt per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level allocated_equity_amt per L3 desk segment.
 </v>
       </c>
       <c r="S50" t="str">
-        <v>Total Assets Amount (desk)</v>
+        <v>Total Equity amount (desk)</v>
       </c>
       <c r="T50" t="str">
         <v>Y</v>
@@ -5084,11 +5284,11 @@
         <v>Agg</v>
       </c>
       <c r="V50" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_assets_amt per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level allocated_equity_amt per L2 portfolio segment.
 </v>
       </c>
       <c r="W50" t="str">
-        <v>Total Assets Amount (portfolio)</v>
+        <v>Total Equity amount (portfolio)</v>
       </c>
       <c r="X50" t="str">
         <v>Y</v>
@@ -5097,11 +5297,11 @@
         <v>Agg</v>
       </c>
       <c r="Z50" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level total_assets_amt per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level allocated_equity_amt per L1 business segment segment.
 </v>
       </c>
       <c r="AA50" t="str">
-        <v>Total Assets Amount (business_segment)</v>
+        <v>Total Equity amount (business_segment)</v>
       </c>
       <c r="AB50" t="str">
         <v/>
@@ -5109,17 +5309,17 @@
     </row>
     <row r="51" xml:space="preserve">
       <c r="A51" t="str">
-        <v>EXP-043</v>
+        <v>EXP-044</v>
       </c>
       <c r="B51" t="str" xml:space="preserve">
-        <v xml:space="preserve">Total shareholder capital allocated to the reporting unit.
+        <v xml:space="preserve">Average balance of interest-generating assets over the reporting period.
 </v>
       </c>
       <c r="C51" t="str">
-        <v>Total Equity amount</v>
+        <v>Average Earning Assets Amount</v>
       </c>
       <c r="D51" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(allocated_equity_amt) per facility from facility_profitability_snapshot. Weighted by bank share percentage.
+        <v xml:space="preserve">Read avg_earning_assets_amt from facility_profitability_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="E51" t="str">
@@ -5135,27 +5335,27 @@
         <v>Y</v>
       </c>
       <c r="I51" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="J51" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(allocated_equity_amt) per facility from facility_profitability_snapshot. Weighted by bank share percentage.
+        <v xml:space="preserve">Read avg_earning_assets_amt from facility_profitability_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="K51" t="str">
-        <v>Total Equity amount (facility)</v>
+        <v>Average Earning Assets Amount (facility)</v>
       </c>
       <c r="L51" t="str">
         <v>Y</v>
       </c>
       <c r="M51" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="N51" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level allocated_equity_amt per counterparty.
+        <v xml:space="preserve">Exposure-weighted average of avg_earning_assets_amt across counterparty facilities.
 </v>
       </c>
       <c r="O51" t="str">
-        <v>Total Equity amount (counterparty)</v>
+        <v>Average Earning Assets Amount (counterparty)</v>
       </c>
       <c r="P51" t="str">
         <v>Y</v>
@@ -5164,24 +5364,24 @@
         <v>Agg</v>
       </c>
       <c r="R51" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level allocated_equity_amt per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level avg_earning_assets_amt per L3 desk segment.
 </v>
       </c>
       <c r="S51" t="str">
-        <v>Total Equity amount (desk)</v>
+        <v>Average Earning Assets Amount (desk)</v>
       </c>
       <c r="T51" t="str">
         <v>Y</v>
       </c>
       <c r="U51" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="V51" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level allocated_equity_amt per L2 portfolio segment.
+        <v xml:space="preserve">AVG of facility-level avg_earning_assets_amt per L2 portfolio segment.
 </v>
       </c>
       <c r="W51" t="str">
-        <v>Total Equity amount (portfolio)</v>
+        <v>Average Earning Assets Amount (portfolio)</v>
       </c>
       <c r="X51" t="str">
         <v>Y</v>
@@ -5190,11 +5390,11 @@
         <v>Agg</v>
       </c>
       <c r="Z51" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level allocated_equity_amt per L1 business segment segment.
+        <v xml:space="preserve">SUM of facility-level avg_earning_assets_amt per L1 business segment segment.
 </v>
       </c>
       <c r="AA51" t="str">
-        <v>Total Equity amount (business_segment)</v>
+        <v>Average Earning Assets Amount (business_segment)</v>
       </c>
       <c r="AB51" t="str">
         <v/>
@@ -5202,17 +5402,17 @@
     </row>
     <row r="52" xml:space="preserve">
       <c r="A52" t="str">
-        <v>EXP-044</v>
+        <v>EXP-045</v>
       </c>
       <c r="B52" t="str" xml:space="preserve">
-        <v xml:space="preserve">Average balance of interest-generating assets over the reporting period.
+        <v xml:space="preserve">Exposure-weighted average regulatory risk weight reflecting capital intensity.
 </v>
       </c>
       <c r="C52" t="str">
-        <v>Average Earning Assets Amount</v>
+        <v>Risk Weighted Average (%)</v>
       </c>
       <c r="D52" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read avg_earning_assets_amt from facility_profitability_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">SUM(RWA Amount)/SUM(Exposure)
 </v>
       </c>
       <c r="E52" t="str">
@@ -5228,66 +5428,66 @@
         <v>Y</v>
       </c>
       <c r="I52" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="J52" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read avg_earning_assets_amt from facility_profitability_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">SUM(RWA Amount)/SUM(Exposure)
 </v>
       </c>
       <c r="K52" t="str">
-        <v>Average Earning Assets Amount (facility)</v>
+        <v>Risk Weighted Average (%) (facility)</v>
       </c>
       <c r="L52" t="str">
         <v>Y</v>
       </c>
       <c r="M52" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="N52" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of avg_earning_assets_amt across counterparty facilities.
+        <v xml:space="preserve">SUM(rwa) / SUM(gross_exposure) * 100.0 per counterparty.
 </v>
       </c>
       <c r="O52" t="str">
-        <v>Average Earning Assets Amount (counterparty)</v>
+        <v>Risk Weighted Average (%) (counterparty)</v>
       </c>
       <c r="P52" t="str">
         <v>Y</v>
       </c>
       <c r="Q52" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R52" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level avg_earning_assets_amt per L3 desk segment.
+        <v xml:space="preserve">SUM(rwa) / SUM(gross_exposure) * 100.0 per L3 desk segment.
 </v>
       </c>
       <c r="S52" t="str">
-        <v>Average Earning Assets Amount (desk)</v>
+        <v>Risk Weighted Average (%) (desk)</v>
       </c>
       <c r="T52" t="str">
         <v>Y</v>
       </c>
       <c r="U52" t="str">
-        <v>Avg</v>
+        <v>Calc</v>
       </c>
       <c r="V52" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level avg_earning_assets_amt per L2 portfolio segment.
+        <v xml:space="preserve">SUM(rwa) / SUM(gross_exposure) * 100.0 per L2 portfolio segment.
 </v>
       </c>
       <c r="W52" t="str">
-        <v>Average Earning Assets Amount (portfolio)</v>
+        <v>Risk Weighted Average (%) (portfolio)</v>
       </c>
       <c r="X52" t="str">
         <v>Y</v>
       </c>
       <c r="Y52" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z52" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level avg_earning_assets_amt per L1 business segment segment.
+        <v xml:space="preserve">SUM(rwa) / SUM(gross_exposure) * 100.0 per L1 business segment.
 </v>
       </c>
       <c r="AA52" t="str">
-        <v>Average Earning Assets Amount (business_segment)</v>
+        <v>Risk Weighted Average (%) (business_segment)</v>
       </c>
       <c r="AB52" t="str">
         <v/>
@@ -5295,17 +5495,17 @@
     </row>
     <row r="53" xml:space="preserve">
       <c r="A53" t="str">
-        <v>EXP-045</v>
+        <v>EXP-046</v>
       </c>
       <c r="B53" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average regulatory risk weight reflecting capital intensity.
+        <v xml:space="preserve">Total risk-weighted assets calculated for regulatory capital purposes.
 </v>
       </c>
       <c r="C53" t="str">
-        <v>Risk Weighted Average (%)</v>
+        <v>Risk Weighted Average Amount ($)</v>
       </c>
       <c r="D53" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(RWA Amount)/SUM(Exposure)
+        <v xml:space="preserve">Exposure * Risk Weight %
 </v>
       </c>
       <c r="E53" t="str">
@@ -5324,63 +5524,63 @@
         <v>Calc</v>
       </c>
       <c r="J53" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(RWA Amount)/SUM(Exposure)
+        <v xml:space="preserve">Exposure * Risk Weight %
 </v>
       </c>
       <c r="K53" t="str">
-        <v>Risk Weighted Average (%) (facility)</v>
+        <v>Risk Weighted Average Amount ($) (facility)</v>
       </c>
       <c r="L53" t="str">
         <v>Y</v>
       </c>
       <c r="M53" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="N53" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(rwa) / SUM(gross_exposure) * 100.0 per counterparty.
+        <v xml:space="preserve">SUM of facility-level rwa_amt per counterparty.
 </v>
       </c>
       <c r="O53" t="str">
-        <v>Risk Weighted Average (%) (counterparty)</v>
+        <v>Risk Weighted Average Amount ($) (counterparty)</v>
       </c>
       <c r="P53" t="str">
         <v>Y</v>
       </c>
       <c r="Q53" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="R53" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(rwa) / SUM(gross_exposure) * 100.0 per L3 desk segment.
+        <v xml:space="preserve">SUM of facility-level rwa_amt per L3 desk segment.
 </v>
       </c>
       <c r="S53" t="str">
-        <v>Risk Weighted Average (%) (desk)</v>
+        <v>Risk Weighted Average Amount ($) (desk)</v>
       </c>
       <c r="T53" t="str">
         <v>Y</v>
       </c>
       <c r="U53" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="V53" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(rwa) / SUM(gross_exposure) * 100.0 per L2 portfolio segment.
+        <v xml:space="preserve">SUM of facility-level rwa_amt per L2 portfolio segment.
 </v>
       </c>
       <c r="W53" t="str">
-        <v>Risk Weighted Average (%) (portfolio)</v>
+        <v>Risk Weighted Average Amount ($) (portfolio)</v>
       </c>
       <c r="X53" t="str">
         <v>Y</v>
       </c>
       <c r="Y53" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="Z53" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(rwa) / SUM(gross_exposure) * 100.0 per L1 business segment.
+        <v xml:space="preserve">SUM of facility-level rwa_amt per L1 business segment.
 </v>
       </c>
       <c r="AA53" t="str">
-        <v>Risk Weighted Average (%) (business_segment)</v>
+        <v>Risk Weighted Average Amount ($) (business_segment)</v>
       </c>
       <c r="AB53" t="str">
         <v/>
@@ -5388,17 +5588,17 @@
     </row>
     <row r="54" xml:space="preserve">
       <c r="A54" t="str">
-        <v>EXP-046</v>
+        <v>EXP-047</v>
       </c>
       <c r="B54" t="str" xml:space="preserve">
-        <v xml:space="preserve">Total risk-weighted assets calculated for regulatory capital purposes.
+        <v xml:space="preserve">Indicates how well cash flow covers fixed, non-discretionary obligations; highlights ability to withstand earnings volatility and signals potential liquidity stress/default risk.
 </v>
       </c>
       <c r="C54" t="str">
-        <v>Risk Weighted Average Amount ($)</v>
+        <v>Fixed Cost Coverage Ratio (%)</v>
       </c>
       <c r="D54" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure * Risk Weight %
+        <v xml:space="preserve">Read fccr_value from lob_risk_ratio_summary for each facility as-of reporting date.
 </v>
       </c>
       <c r="E54" t="str">
@@ -5414,66 +5614,70 @@
         <v>Y</v>
       </c>
       <c r="I54" t="str">
-        <v>Calc</v>
+        <v>Raw</v>
       </c>
       <c r="J54" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure * Risk Weight %
+        <v xml:space="preserve">Read fccr_value from lob_risk_ratio_summary for each facility as-of reporting date.
 </v>
       </c>
       <c r="K54" t="str">
-        <v>Risk Weighted Average Amount ($) (facility)</v>
+        <v>Fixed Cost Coverage Ratio (%) (facility)</v>
       </c>
       <c r="L54" t="str">
         <v>Y</v>
       </c>
       <c r="M54" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N54" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level rwa_amt per counterparty.
+        <v xml:space="preserve">SUM(ebitda × fx_rate) / SUM(total_debt_service × fx_rate) per counterparty.
+Amounts converted to USD via l2.fx_rate before aggregation.
 </v>
       </c>
       <c r="O54" t="str">
-        <v>Risk Weighted Average Amount ($) (counterparty)</v>
+        <v>Fixed Cost Coverage Ratio (%) (counterparty)</v>
       </c>
       <c r="P54" t="str">
         <v>Y</v>
       </c>
       <c r="Q54" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R54" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level rwa_amt per L3 desk segment.
+        <v xml:space="preserve">SUM(ebitda × fx_rate) / SUM(total_debt_service × fx_rate) per L3 desk segment.
+Amounts converted to USD via l2.fx_rate before aggregation.
 </v>
       </c>
       <c r="S54" t="str">
-        <v>Risk Weighted Average Amount ($) (desk)</v>
+        <v>Fixed Cost Coverage Ratio (%) (desk)</v>
       </c>
       <c r="T54" t="str">
         <v>Y</v>
       </c>
       <c r="U54" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V54" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level rwa_amt per L2 portfolio segment.
+        <v xml:space="preserve">SUM(ebitda × fx_rate) / SUM(total_debt_service × fx_rate) per L2 portfolio segment.
+Amounts converted to USD via l2.fx_rate before aggregation.
 </v>
       </c>
       <c r="W54" t="str">
-        <v>Risk Weighted Average Amount ($) (portfolio)</v>
+        <v>Fixed Cost Coverage Ratio (%) (portfolio)</v>
       </c>
       <c r="X54" t="str">
         <v>Y</v>
       </c>
       <c r="Y54" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z54" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level rwa_amt per L1 business segment.
+        <v xml:space="preserve">SUM(ebitda × fx_rate) / SUM(total_debt_service × fx_rate) per L1 business segment.
+Amounts converted to USD via l2.fx_rate before aggregation.
 </v>
       </c>
       <c r="AA54" t="str">
-        <v>Risk Weighted Average Amount ($) (business_segment)</v>
+        <v>Fixed Cost Coverage Ratio (%) (business_segment)</v>
       </c>
       <c r="AB54" t="str">
         <v/>
@@ -5481,17 +5685,17 @@
     </row>
     <row r="55" xml:space="preserve">
       <c r="A55" t="str">
-        <v>EXP-047</v>
+        <v>EXP-048</v>
       </c>
       <c r="B55" t="str" xml:space="preserve">
-        <v xml:space="preserve">Indicates how well cash flow covers fixed, non-discretionary obligations; highlights ability to withstand earnings volatility and signals potential liquidity stress/default risk.
+        <v xml:space="preserve">Scheduled principal repayment obligation due for the contractual commitment.
 </v>
       </c>
       <c r="C55" t="str">
-        <v>Fixed Cost Coverage Ratio (%)</v>
+        <v>Principal Repayment Amount ($)</v>
       </c>
       <c r="D55" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read fccr_value from lob_risk_ratio_summary for each facility as-of reporting date.
+        <v xml:space="preserve">Read principal_payment_amt from facility_financial_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="E55" t="str">
@@ -5510,67 +5714,63 @@
         <v>Raw</v>
       </c>
       <c r="J55" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read fccr_value from lob_risk_ratio_summary for each facility as-of reporting date.
+        <v xml:space="preserve">Read principal_payment_amt from facility_financial_snapshot for each facility as-of reporting date.
 </v>
       </c>
       <c r="K55" t="str">
-        <v>Fixed Cost Coverage Ratio (%) (facility)</v>
+        <v>Principal Repayment Amount ($) (facility)</v>
       </c>
       <c r="L55" t="str">
         <v>Y</v>
       </c>
       <c r="M55" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="N55" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(ebitda × fx_rate) / SUM(total_debt_service × fx_rate) per counterparty.
-Amounts converted to USD via l2.fx_rate before aggregation.
+        <v xml:space="preserve">SUM(facility-level principal_payment_amt) per counterparty.
 </v>
       </c>
       <c r="O55" t="str">
-        <v>Fixed Cost Coverage Ratio (%) (counterparty)</v>
+        <v>Principal Repayment Amount ($) (counterparty)</v>
       </c>
       <c r="P55" t="str">
         <v>Y</v>
       </c>
       <c r="Q55" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="R55" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(ebitda × fx_rate) / SUM(total_debt_service × fx_rate) per L3 desk segment.
-Amounts converted to USD via l2.fx_rate before aggregation.
+        <v xml:space="preserve">SUM of facility-level principal_payment_amt per L3 desk segment.
 </v>
       </c>
       <c r="S55" t="str">
-        <v>Fixed Cost Coverage Ratio (%) (desk)</v>
+        <v>Principal Repayment Amount ($) (desk)</v>
       </c>
       <c r="T55" t="str">
         <v>Y</v>
       </c>
       <c r="U55" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="V55" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(ebitda × fx_rate) / SUM(total_debt_service × fx_rate) per L2 portfolio segment.
-Amounts converted to USD via l2.fx_rate before aggregation.
+        <v xml:space="preserve">SUM of facility-level principal_payment_amt per L2 portfolio segment.
 </v>
       </c>
       <c r="W55" t="str">
-        <v>Fixed Cost Coverage Ratio (%) (portfolio)</v>
+        <v>Principal Repayment Amount ($) (portfolio)</v>
       </c>
       <c r="X55" t="str">
         <v>Y</v>
       </c>
       <c r="Y55" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="Z55" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(ebitda × fx_rate) / SUM(total_debt_service × fx_rate) per L1 business segment.
-Amounts converted to USD via l2.fx_rate before aggregation.
+        <v xml:space="preserve">SUM of facility-level principal_payment_amt per L1 business segment segment.
 </v>
       </c>
       <c r="AA55" t="str">
-        <v>Fixed Cost Coverage Ratio (%) (business_segment)</v>
+        <v>Principal Repayment Amount ($) (business_segment)</v>
       </c>
       <c r="AB55" t="str">
         <v/>
@@ -5578,17 +5778,17 @@
     </row>
     <row r="56" xml:space="preserve">
       <c r="A56" t="str">
-        <v>EXP-048</v>
+        <v>EXP-049</v>
       </c>
       <c r="B56" t="str" xml:space="preserve">
-        <v xml:space="preserve">Scheduled principal repayment obligation due for the contractual commitment.
+        <v xml:space="preserve">Identifies facilities and counterparties with cross-entity exposure — where a single facility participates across multiple counterparties. At facility level, returns 1 if the facility has participations from more than one distinct counterparty in facility_counterparty_participation, 0 otherwise. At counterparty level, returns 1 if any of the counterparty's facilities have cross-entity participations. Flags complexity and concentration risk from intercompany exposure structures.
 </v>
       </c>
       <c r="C56" t="str">
-        <v>Principal Repayment Amount ($)</v>
+        <v>Cross Entity Exposure Flag</v>
       </c>
       <c r="D56" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read principal_payment_amt from facility_financial_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">For each facility, count the number of distinct counterparties in facility_counterparty_participation (current records only). If COUNT(DISTINCT counterparty_id) &gt; 1, the facility has cross-entity exposure (flag = 1). Otherwise flag = 0.
 </v>
       </c>
       <c r="E56" t="str">
@@ -5604,66 +5804,66 @@
         <v>Y</v>
       </c>
       <c r="I56" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="J56" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read principal_payment_amt from facility_financial_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">For each facility, count the number of distinct counterparties in facility_counterparty_participation (current records only). If COUNT(DISTINCT counterparty_id) &gt; 1, the facility has cross-entity exposure (flag = 1). Otherwise flag = 0.
 </v>
       </c>
       <c r="K56" t="str">
-        <v>Principal Repayment Amount ($) (facility)</v>
+        <v>Cross Entity Exposure Flag (facility)</v>
       </c>
       <c r="L56" t="str">
         <v>Y</v>
       </c>
       <c r="M56" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N56" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level principal_payment_amt) per counterparty.
+        <v xml:space="preserve">For each counterparty, check all of its facilities in the participation table. For each facility, determine if it has cross-entity exposure (multiple distinct counterparties). If ANY facility belonging to this counterparty has cross-entity exposure, the counterparty flag = 1. Uses MAX over the facility-level flags for correct boolean OR logic.
 </v>
       </c>
       <c r="O56" t="str">
-        <v>Principal Repayment Amount ($) (counterparty)</v>
+        <v>Cross Entity Exposure Flag (counterparty)</v>
       </c>
       <c r="P56" t="str">
         <v>Y</v>
       </c>
       <c r="Q56" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R56" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level principal_payment_amt per L3 desk segment.
+        <v xml:space="preserve">Not applicable — cross-entity exposure flag is a facility/counterparty level indicator. Desk-level analysis should use EXP-008 (Cross Entity Exposure Amount) for dollar-weighted concentration risk.
 </v>
       </c>
       <c r="S56" t="str">
-        <v>Principal Repayment Amount ($) (desk)</v>
+        <v>Cross Entity Exposure Flag (desk)</v>
       </c>
       <c r="T56" t="str">
         <v>Y</v>
       </c>
       <c r="U56" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V56" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level principal_payment_amt per L2 portfolio segment.
+        <v xml:space="preserve">Not applicable — cross-entity exposure flag is a facility/counterparty level indicator. Portfolio analysis should use EXP-008 for aggregate cross-entity exposure amounts.
 </v>
       </c>
       <c r="W56" t="str">
-        <v>Principal Repayment Amount ($) (portfolio)</v>
+        <v>Cross Entity Exposure Flag (portfolio)</v>
       </c>
       <c r="X56" t="str">
         <v>Y</v>
       </c>
       <c r="Y56" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z56" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level principal_payment_amt per L1 business segment segment.
+        <v xml:space="preserve">Not applicable — cross-entity exposure flag is a facility/counterparty level indicator. Segment analysis should use EXP-008 for aggregate cross-entity exposure amounts.
 </v>
       </c>
       <c r="AA56" t="str">
-        <v>Principal Repayment Amount ($) (business_segment)</v>
+        <v>Cross Entity Exposure Flag (business_segment)</v>
       </c>
       <c r="AB56" t="str">
         <v/>
@@ -5967,14 +6167,14 @@
         <v>PRC-004</v>
       </c>
       <c r="B60" t="str" xml:space="preserve">
-        <v xml:space="preserve">Fee percentage applied to committed or undrawn exposure. Calculated KPI supporting pricing adequacy and revenue optimization analysis.
+        <v xml:space="preserve">Fee percentage applied to committed or undrawn exposure. Sourced from l2.facility_pricing_snapshot at facility level. Supports pricing adequacy and revenue optimization analysis. Aggregate levels use exposure-weighted average with FX conversion to USD.
 </v>
       </c>
       <c r="C60" t="str">
         <v>Fee Rate (%)</v>
       </c>
       <c r="D60" t="str" xml:space="preserve">
-        <v xml:space="preserve">Fee Income / Average Balance
+        <v xml:space="preserve">Direct lookup of fee_rate_pct from l2.facility_pricing_snapshot.
 </v>
       </c>
       <c r="E60" t="str">
@@ -5990,10 +6190,10 @@
         <v>Y</v>
       </c>
       <c r="I60" t="str">
-        <v>Calc</v>
+        <v>Raw</v>
       </c>
       <c r="J60" t="str" xml:space="preserve">
-        <v xml:space="preserve">Fee Income / Average Balance
+        <v xml:space="preserve">Direct lookup of fee_rate_pct from l2.facility_pricing_snapshot.
 </v>
       </c>
       <c r="K60" t="str">
@@ -6006,7 +6206,7 @@
         <v>Avg</v>
       </c>
       <c r="N60" t="str" xml:space="preserve">
-        <v xml:space="preserve">Exposure-weighted average of fee_rate_pct across counterparty facilities.
+        <v xml:space="preserve">Supplementary (not in primary specification at counterparty level). Exposure-weighted average fee rate per counterparty with FX conversion: SUM(fee_rate * committed_amt * fx) / SUM(committed_amt * fx).
 </v>
       </c>
       <c r="O60" t="str">
@@ -6019,7 +6219,7 @@
         <v>Avg</v>
       </c>
       <c r="R60" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level fee_rate_pct per L3 desk segment.
+        <v xml:space="preserve">Supplementary. Exposure-weighted average fee rate per L3 desk segment with FX conversion.
 </v>
       </c>
       <c r="S60" t="str">
@@ -6032,7 +6232,7 @@
         <v>Avg</v>
       </c>
       <c r="V60" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level fee_rate_pct per L2 portfolio segment.
+        <v xml:space="preserve">Supplementary. Exposure-weighted average fee rate per L2 portfolio segment with FX conversion.
 </v>
       </c>
       <c r="W60" t="str">
@@ -6042,10 +6242,10 @@
         <v>Y</v>
       </c>
       <c r="Y60" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="Z60" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level fee_rate_pct per L1 business segment segment.
+        <v xml:space="preserve">Supplementary. Exposure-weighted average fee rate per L1 business segment with FX conversion.
 </v>
       </c>
       <c r="AA60" t="str">
@@ -6153,14 +6353,18 @@
         <v>PRC-006</v>
       </c>
       <c r="B62" t="str" xml:space="preserve">
-        <v xml:space="preserve">Pricing classification tier assigned to facility. Supports structured pricing strategy and yield segmentation.
+        <v xml:space="preserve">Pricing classification tier derived by range-joining the facility's spread (spread_bps from L2 facility_pricing_snapshot) against the pricing_tier_dim reference table (spread_min_bps/spread_max_bps). Returns the tier_ordinal at facility level and at aggregate levels classifies the exposure-weighted average spread into the corresponding tier. Supports pricing strategy segmentation, yield curve analysis, and risk-adjusted return monitoring.
 </v>
       </c>
       <c r="C62" t="str">
         <v>Pricing Tier</v>
       </c>
       <c r="D62" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read pricing_tier_code from facility_detail_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">For each facility:
+  1. LOAD spread_bps from l2.facility_pricing_snapshot
+  2. RANGE-JOIN against l1.pricing_tier_dim
+     WHERE spread_bps &gt;= spread_min_bps AND spread_bps &lt; spread_max_bps
+  3. RETURN tier_ordinal — the numeric tier classification
 </v>
       </c>
       <c r="E62" t="str">
@@ -6176,10 +6380,14 @@
         <v>Y</v>
       </c>
       <c r="I62" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="J62" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read pricing_tier_code from facility_detail_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">For each facility:
+  1. LOAD spread_bps from l2.facility_pricing_snapshot
+  2. RANGE-JOIN against l1.pricing_tier_dim
+     WHERE spread_bps &gt;= spread_min_bps AND spread_bps &lt; spread_max_bps
+  3. RETURN tier_ordinal — the numeric tier classification
 </v>
       </c>
       <c r="K62" t="str">
@@ -6189,10 +6397,15 @@
         <v>Y</v>
       </c>
       <c r="M62" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="N62" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read pricing_tier_code per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD spread_bps and committed_amount per facility
+  2. COMPUTE weighted average spread:
+     SUM(spread_bps × committed_amount) / SUM(committed_amount)
+  3. RANGE-JOIN weighted avg spread against l1.pricing_tier_dim
+  4. RETURN tier_ordinal for the counterparty's blended spread
 </v>
       </c>
       <c r="O62" t="str">
@@ -6202,10 +6415,13 @@
         <v>Y</v>
       </c>
       <c r="Q62" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R62" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pricing_tier_code per L3 desk segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. Compute exposure-weighted average spread across desk facilities
+  2. Classify against pricing_tier_dim ranges
+  3. RETURN tier_ordinal for the desk's blended spread
 </v>
       </c>
       <c r="S62" t="str">
@@ -6215,10 +6431,13 @@
         <v>Y</v>
       </c>
       <c r="U62" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V62" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pricing_tier_code per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. Compute exposure-weighted average spread
+  3. Classify against pricing_tier_dim ranges
 </v>
       </c>
       <c r="W62" t="str">
@@ -6228,10 +6447,13 @@
         <v>Y</v>
       </c>
       <c r="Y62" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z62" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pricing_tier_code per L1 business segment segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. Compute exposure-weighted average spread
+  3. Classify against pricing_tier_dim ranges
 </v>
       </c>
       <c r="AA62" t="str">
@@ -6432,14 +6654,16 @@
         <v>PRC-009</v>
       </c>
       <c r="B65" t="str" xml:space="preserve">
-        <v xml:space="preserve">Boolean indicator identifying whether the exposure was approved outside standard pricing policy thresholds at origination or amendment.
+        <v xml:space="preserve">Pricing exception effectiveness metric. At facility level, returns an ordinal encoding of the pricing_exception_status (APPROVED=3, PENDING=2, DENIED=1, NONE=0). At aggregate levels, computes the exception rate as COUNT(exception facilities) / COUNT(total facilities) × 100, following the count-ratio rollup pattern. Re-counts at each level to avoid Simpson's paradox. Complements PRC-003 (Exception Rate) with status-level detail for governance drill-down.
 </v>
       </c>
       <c r="C65" t="str">
-        <v>Pricing Exception Flag (Y/N)</v>
+        <v>Pricing Exception Status</v>
       </c>
       <c r="D65" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated pricing_exception_flag per facility.
+        <v xml:space="preserve">Ordinal encoding of pricing_exception_status per facility:
+  APPROVED = 3, PENDING = 2, DENIED = 1, NONE/NULL = 0.
+Ingredients: pricing_exception_status (L2 facility_pricing_snapshot)
 </v>
       </c>
       <c r="E65" t="str">
@@ -6458,63 +6682,79 @@
         <v>Calc</v>
       </c>
       <c r="J65" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated pricing_exception_flag per facility.
+        <v xml:space="preserve">Ordinal encoding of pricing_exception_status per facility:
+  APPROVED = 3, PENDING = 2, DENIED = 1, NONE/NULL = 0.
+Ingredients: pricing_exception_status (L2 facility_pricing_snapshot)
 </v>
       </c>
       <c r="K65" t="str">
-        <v>Pricing Exception Flag (Y/N) (facility)</v>
+        <v>Pricing Exception Status (facility)</v>
       </c>
       <c r="L65" t="str">
         <v>Y</v>
       </c>
       <c r="M65" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N65" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pricing_exception_flag per counterparty.
+        <v xml:space="preserve">For each counterparty:
+  1. LOAD is_pricing_exception_flag for all facilities
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup: re-counts from facility-level flags.
 </v>
       </c>
       <c r="O65" t="str">
-        <v>Pricing Exception Flag (Y/N) (counterparty)</v>
+        <v>Pricing Exception Status (counterparty)</v>
       </c>
       <c r="P65" t="str">
         <v>Y</v>
       </c>
       <c r="Q65" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R65" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pricing_exception_flag per L3 desk segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. JOIN l1.enterprise_business_taxonomy on lob_segment_id
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup per desk.
 </v>
       </c>
       <c r="S65" t="str">
-        <v>Pricing Exception Flag (Y/N) (desk)</v>
+        <v>Pricing Exception Status (desk)</v>
       </c>
       <c r="T65" t="str">
         <v>Y</v>
       </c>
       <c r="U65" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V65" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pricing_exception_flag per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup per portfolio. Drill-down returns exception
+facility details: Facility_ID, Facility_Name, Counterparty_ID,
+Counterparty_Name, Exception_Status, All_in_Rate.
 </v>
       </c>
       <c r="W65" t="str">
-        <v>Pricing Exception Flag (Y/N) (portfolio)</v>
+        <v>Pricing Exception Status (portfolio)</v>
       </c>
       <c r="X65" t="str">
         <v>Y</v>
       </c>
       <c r="Y65" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z65" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level pricing_exception_flag per L1 business segment segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. COMPUTE COUNT(exceptions) / COUNT(total facilities) × 100
+Count-ratio rollup per business segment.
 </v>
       </c>
       <c r="AA65" t="str">
-        <v>Pricing Exception Flag (Y/N) (business_segment)</v>
+        <v>Pricing Exception Status (business_segment)</v>
       </c>
       <c r="AB65" t="str">
         <v/>
@@ -6722,14 +6962,14 @@
         <v>REF-002</v>
       </c>
       <c r="B68" t="str" xml:space="preserve">
-        <v xml:space="preserve">Snapshot date of the dataset used for reporting and aggregation. Serves as the temporal reference point for all balances, risk metrics, and performance indicators.
+        <v xml:space="preserve">Snapshot date of the dataset used for reporting and aggregation. Serves as the temporal reference point for all balances, risk metrics, and performance indicators. At facility level, returns the as_of_date. At aggregate levels, returns MAX(as_of_date) — the latest reporting date for facilities in the segment.
 </v>
       </c>
       <c r="C68" t="str">
         <v>Reporting Period (As-of Date)</v>
       </c>
       <c r="D68" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read as_of_date from facility_exposure_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Read as_of_date from facility_exposure_snapshot for each facility.
 </v>
       </c>
       <c r="E68" t="str">
@@ -6748,7 +6988,7 @@
         <v>Raw</v>
       </c>
       <c r="J68" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read as_of_date from facility_exposure_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Read as_of_date from facility_exposure_snapshot for each facility.
 </v>
       </c>
       <c r="K68" t="str">
@@ -6758,10 +6998,10 @@
         <v>Y</v>
       </c>
       <c r="M68" t="str">
-        <v>Raw</v>
+        <v>Agg</v>
       </c>
       <c r="N68" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read as_of_date per counterparty.
+        <v xml:space="preserve">Latest reporting date per counterparty. MAX(as_of_date) — never SUM dates (mathematically invalid).
 </v>
       </c>
       <c r="O68" t="str">
@@ -6774,7 +7014,7 @@
         <v>Agg</v>
       </c>
       <c r="R68" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level as_of_date per L3 desk segment.
+        <v xml:space="preserve">Latest reporting date per L3 desk segment. MAX(as_of_date).
 </v>
       </c>
       <c r="S68" t="str">
@@ -6787,7 +7027,7 @@
         <v>Agg</v>
       </c>
       <c r="V68" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level as_of_date per L2 portfolio segment.
+        <v xml:space="preserve">Latest reporting date per L2 portfolio segment via EBT hierarchy (one hop up). MAX(as_of_date).
 </v>
       </c>
       <c r="W68" t="str">
@@ -6800,7 +7040,7 @@
         <v>Agg</v>
       </c>
       <c r="Z68" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level as_of_date per L1 business segment segment.
+        <v xml:space="preserve">Latest reporting date per L1 business segment via EBT hierarchy (two hops up). MAX(as_of_date).
 </v>
       </c>
       <c r="AA68" t="str">
@@ -7373,11 +7613,11 @@
         <v>REF-009</v>
       </c>
       <c r="B75" t="str" xml:space="preserve">
-        <v xml:space="preserve">Date on which loan or contract became legally effective. Sourced directly from facility_master. At aggregate levels, returns the earliest origination date (MIN) across constituent facilities — indicating the oldest vintage in the book. Key contract lifecycle tracking attribute for vintage analysis and portfolio seasoning assessment.
+        <v xml:space="preserve">Facility effective date sourced from facility_master origination_date. At facility and counterparty levels, returns the raw date (or earliest vintage via MIN). At portfolio level, pivots to facility lifecycle tracking: counts inactive facilities whose origination date falls within 90 days of the reporting date, identifying the upcoming pipeline of facilities about to start ("Starting 90d"). Key for vintage analysis, portfolio seasoning, and facility pipeline monitoring.
 </v>
       </c>
       <c r="C75" t="str">
-        <v>Contract Origination Date</v>
+        <v>Facility Origination Date</v>
       </c>
       <c r="D75" t="str" xml:space="preserve">
         <v xml:space="preserve">Direct lookup of origination_date from facility_master.
@@ -7405,7 +7645,7 @@
 </v>
       </c>
       <c r="K75" t="str">
-        <v>Contract Origination Date (facility)</v>
+        <v>Facility Origination Date (facility)</v>
       </c>
       <c r="L75" t="str">
         <v>Y</v>
@@ -7421,7 +7661,7 @@
 </v>
       </c>
       <c r="O75" t="str">
-        <v>Contract Origination Date (counterparty)</v>
+        <v>Facility Origination Date (counterparty)</v>
       </c>
       <c r="P75" t="str">
         <v>Y</v>
@@ -7437,22 +7677,26 @@
 </v>
       </c>
       <c r="S75" t="str">
-        <v>Contract Origination Date (desk)</v>
+        <v>Facility Origination Date (desk)</v>
       </c>
       <c r="T75" t="str">
         <v>Y</v>
       </c>
       <c r="U75" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V75" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each L2 Portfolio segment:
+        <v xml:space="preserve">Facility pipeline tracking for each L2 Portfolio segment:
   1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
-  2. COMPUTE MIN(origination_date) — earliest vintage in portfolio
+  2. FILTER inactive facilities (is_active_flag != 'Y')
+     whose origination_date is within 90 days of current date
+  3. COMPUTE COUNT(DISTINCT facility_id) — number of upcoming facilities
+Returns the count of facilities in the "Starting (90d)" pipeline.
+Business rule: facilities not yet active with origination within ±90 days.
 </v>
       </c>
       <c r="W75" t="str">
-        <v>Contract Origination Date (portfolio)</v>
+        <v>Facility Origination Date (portfolio)</v>
       </c>
       <c r="X75" t="str">
         <v>Y</v>
@@ -7467,7 +7711,7 @@
 </v>
       </c>
       <c r="AA75" t="str">
-        <v>Contract Origination Date (business_segment)</v>
+        <v>Facility Origination Date (business_segment)</v>
       </c>
       <c r="AB75" t="str">
         <v/>
@@ -7517,7 +7761,7 @@
         <v>Raw</v>
       </c>
       <c r="N76" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read facility_id per counterparty.
+        <v xml:space="preserve">Representative facility_id per counterparty (MIN).
 </v>
       </c>
       <c r="O76" t="str">
@@ -7527,10 +7771,10 @@
         <v>Y</v>
       </c>
       <c r="Q76" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="R76" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_id per L3 desk segment.
+        <v xml:space="preserve">Representative facility_id per L3 desk segment (MIN).
 </v>
       </c>
       <c r="S76" t="str">
@@ -7540,10 +7784,10 @@
         <v>Y</v>
       </c>
       <c r="U76" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="V76" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_id per L2 portfolio segment.
+        <v xml:space="preserve">Representative facility_id per L2 portfolio segment (MIN).
 </v>
       </c>
       <c r="W76" t="str">
@@ -7553,10 +7797,10 @@
         <v>Y</v>
       </c>
       <c r="Y76" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="Z76" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_id per L1 business segment segment.
+        <v xml:space="preserve">Representative facility_id per L1 business segment (MIN).
 </v>
       </c>
       <c r="AA76" t="str">
@@ -7610,7 +7854,7 @@
         <v>Raw</v>
       </c>
       <c r="N77" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read facility_name per counterparty.
+        <v xml:space="preserve">Representative facility_name per counterparty (MIN alphabetical).
 </v>
       </c>
       <c r="O77" t="str">
@@ -7620,10 +7864,10 @@
         <v>Y</v>
       </c>
       <c r="Q77" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="R77" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_name per L3 desk segment.
+        <v xml:space="preserve">Representative facility_name per L3 desk segment (MIN alphabetical).
 </v>
       </c>
       <c r="S77" t="str">
@@ -7633,10 +7877,10 @@
         <v>Y</v>
       </c>
       <c r="U77" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="V77" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_name per L2 portfolio segment.
+        <v xml:space="preserve">Representative facility_name per L2 portfolio segment (MIN alphabetical).
 </v>
       </c>
       <c r="W77" t="str">
@@ -7646,10 +7890,10 @@
         <v>Y</v>
       </c>
       <c r="Y77" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="Z77" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_name per L1 business segment segment.
+        <v xml:space="preserve">Representative facility_name per L1 business segment (MIN alphabetical).
 </v>
       </c>
       <c r="AA77" t="str">
@@ -7664,14 +7908,14 @@
         <v>REF-012</v>
       </c>
       <c r="B78" t="str" xml:space="preserve">
-        <v xml:space="preserve">Type of credit facility (e.g., Term Loan, Revolver, Letter of Credit). Enables product-level segmentation, risk concentration analysis, and performance benchmarking.
+        <v xml:space="preserve">Type of credit facility (e.g., Term Loan, Revolver, Letter of Credit). At facility level, returns the facility_type string directly. At counterparty and aggregate levels, returns the dominant facility type by drawn exposure weight using ROW_NUMBER. Enables product-level segmentation, risk concentration analysis, and performance benchmarking.
 </v>
       </c>
       <c r="C78" t="str">
         <v>Facility Type</v>
       </c>
       <c r="D78" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read facility_type from facility_exposure_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Direct lookup of facility_type from facility_master.
 </v>
       </c>
       <c r="E78" t="str">
@@ -7690,7 +7934,7 @@
         <v>Raw</v>
       </c>
       <c r="J78" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read facility_type from facility_exposure_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Direct lookup of facility_type from facility_master.
 </v>
       </c>
       <c r="K78" t="str">
@@ -7700,10 +7944,10 @@
         <v>Y</v>
       </c>
       <c r="M78" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N78" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level facility_type) per counterparty.
+        <v xml:space="preserve">Dominant facility type by drawn exposure weight per counterparty. ROW_NUMBER partitioned by counterparty, ordered by total bank-share-adjusted drawn amount descending.
 </v>
       </c>
       <c r="O78" t="str">
@@ -7713,10 +7957,10 @@
         <v>Y</v>
       </c>
       <c r="Q78" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R78" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_type per L3 desk segment.
+        <v xml:space="preserve">Dominant facility type by drawn exposure weight (USD-converted) per L3 desk segment. ROW_NUMBER partitioned by desk, ordered by total exposure descending.
 </v>
       </c>
       <c r="S78" t="str">
@@ -7726,10 +7970,10 @@
         <v>Y</v>
       </c>
       <c r="U78" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V78" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_type per L2 portfolio segment.
+        <v xml:space="preserve">Dominant facility type by drawn exposure weight (USD-converted) per L2 portfolio segment via EBT hierarchy (one hop up).
 </v>
       </c>
       <c r="W78" t="str">
@@ -7739,10 +7983,10 @@
         <v>Y</v>
       </c>
       <c r="Y78" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z78" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level facility_type per L1 business segment segment.
+        <v xml:space="preserve">Dominant facility type by drawn exposure weight (USD-converted) per L1 business segment via EBT hierarchy (two hops up).
 </v>
       </c>
       <c r="AA78" t="str">
@@ -7757,14 +8001,14 @@
         <v>REF-013</v>
       </c>
       <c r="B79" t="str" xml:space="preserve">
-        <v xml:space="preserve">A classification used for reporting purposes in the FR 2590 regulatory report pertaining to financial institutions' credit exposures.
+        <v xml:space="preserve">FR 2590 regulatory classification for each facility exposure. Reads the fr2590_category_code from the facility exposure snapshot and joins to the fr2590_category_dim reference table to return the human-readable category name. Used for FR 2590 supervisory reporting and exposure segmentation by product type. Facility-level only — categorical values cannot be meaningfully aggregated to higher organizational levels.
 </v>
       </c>
       <c r="C79" t="str">
         <v>FR2590 Category</v>
       </c>
       <c r="D79" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated fr2590_category_code per facility.
+        <v xml:space="preserve">For each facility, read the fr2590_category_code from the latest facility_exposure_snapshot, then join to fr2590_category_dim to return the human-readable category_name. Uses MAX(category_name) to handle any duplicate exposure rows per facility on the same reporting date.
 </v>
       </c>
       <c r="E79" t="str">
@@ -7783,7 +8027,7 @@
         <v>Calc</v>
       </c>
       <c r="J79" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated fr2590_category_code per facility.
+        <v xml:space="preserve">For each facility, read the fr2590_category_code from the latest facility_exposure_snapshot, then join to fr2590_category_dim to return the human-readable category_name. Uses MAX(category_name) to handle any duplicate exposure rows per facility on the same reporting date.
 </v>
       </c>
       <c r="K79" t="str">
@@ -7793,10 +8037,10 @@
         <v>Y</v>
       </c>
       <c r="M79" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N79" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level fr2590_category_code per counterparty.
+        <v xml:space="preserve">Not applicable — FR2590 category is a per-facility categorical classification that cannot be meaningfully aggregated to counterparty level. Use facility-level drill-down for category distribution.
 </v>
       </c>
       <c r="O79" t="str">
@@ -7806,10 +8050,10 @@
         <v>Y</v>
       </c>
       <c r="Q79" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R79" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level fr2590_category_code per L3 desk segment.
+        <v xml:space="preserve">Not applicable — FR2590 category is a per-facility categorical classification. Desk-level analysis should use facility-level data grouped by FR2590 category as a dimension.
 </v>
       </c>
       <c r="S79" t="str">
@@ -7819,10 +8063,10 @@
         <v>Y</v>
       </c>
       <c r="U79" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V79" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level fr2590_category_code per L2 portfolio segment.
+        <v xml:space="preserve">Not applicable — FR2590 category is a per-facility categorical classification. Portfolio-level reporting uses FR2590 as a grouping dimension, not as an aggregated metric.
 </v>
       </c>
       <c r="W79" t="str">
@@ -7832,10 +8076,10 @@
         <v>Y</v>
       </c>
       <c r="Y79" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z79" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level fr2590_category_code per L1 business segment segment.
+        <v xml:space="preserve">Not applicable — FR2590 category is a per-facility categorical classification. Business segment reporting uses FR2590 as a grouping dimension, not as an aggregated metric.
 </v>
       </c>
       <c r="AA79" t="str">
@@ -8036,14 +8280,14 @@
         <v>REF-016</v>
       </c>
       <c r="B82" t="str" xml:space="preserve">
-        <v xml:space="preserve">Legal entity booking or owning the exposure. Critical for regulatory capital and entity-level reporting.
+        <v xml:space="preserve">Booking legal entity for each facility exposure. At facility level returns the entity name from the legal_entity table. At aggregate levels returns the count of distinct booking entities for risk concentration analysis.
 </v>
       </c>
       <c r="C82" t="str">
         <v>Legal Entity</v>
       </c>
       <c r="D82" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of legal_name from counterparty.
+        <v xml:space="preserve">Lookup legal_entity_name from legal_entity table via facility_exposure_snapshot.legal_entity_id.
 </v>
       </c>
       <c r="E82" t="str">
@@ -8062,7 +8306,7 @@
         <v>Raw</v>
       </c>
       <c r="J82" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of legal_name from counterparty.
+        <v xml:space="preserve">Lookup legal_entity_name from legal_entity table via facility_exposure_snapshot.legal_entity_id.
 </v>
       </c>
       <c r="K82" t="str">
@@ -8072,10 +8316,10 @@
         <v>Y</v>
       </c>
       <c r="M82" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="N82" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of legal_name from counterparty.
+        <v xml:space="preserve">Count of distinct booking legal entities per counterparty.
 </v>
       </c>
       <c r="O82" t="str">
@@ -8085,10 +8329,10 @@
         <v>Y</v>
       </c>
       <c r="Q82" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R82" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level legal_name per L3 desk segment.
+        <v xml:space="preserve">Count of distinct booking legal entities per L3 desk segment.
 </v>
       </c>
       <c r="S82" t="str">
@@ -8098,10 +8342,10 @@
         <v>Y</v>
       </c>
       <c r="U82" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V82" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level legal_name per L2 portfolio segment.
+        <v xml:space="preserve">Count of distinct booking legal entities per L2 portfolio segment.
 </v>
       </c>
       <c r="W82" t="str">
@@ -8111,10 +8355,10 @@
         <v>Y</v>
       </c>
       <c r="Y82" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z82" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level legal_name per L1 business segment segment.
+        <v xml:space="preserve">Count of distinct booking legal entities per L1 business segment.
 </v>
       </c>
       <c r="AA82" t="str">
@@ -8129,14 +8373,14 @@
         <v>REF-017</v>
       </c>
       <c r="B83" t="str" xml:space="preserve">
-        <v xml:space="preserve">Unique identifier assigned to legal entity in enterprise systems.
+        <v xml:space="preserve">Unique identifier for the booking legal entity. At facility level returns the entity ID. At aggregate levels returns count of distinct booking entities for entity concentration tracking.
 </v>
       </c>
       <c r="C83" t="str">
         <v>Legal Entity ID</v>
       </c>
       <c r="D83" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read legal_entity_id from facility_exposure_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Read legal_entity_id from facility_exposure_snapshot for each facility.
 </v>
       </c>
       <c r="E83" t="str">
@@ -8155,7 +8399,7 @@
         <v>Raw</v>
       </c>
       <c r="J83" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read legal_entity_id from facility_exposure_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Read legal_entity_id from facility_exposure_snapshot for each facility.
 </v>
       </c>
       <c r="K83" t="str">
@@ -8165,10 +8409,10 @@
         <v>Y</v>
       </c>
       <c r="M83" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="N83" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read legal_entity_id per counterparty.
+        <v xml:space="preserve">Count of distinct booking legal entities per counterparty.
 </v>
       </c>
       <c r="O83" t="str">
@@ -8178,10 +8422,10 @@
         <v>Y</v>
       </c>
       <c r="Q83" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R83" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level legal_entity_id per L3 desk segment.
+        <v xml:space="preserve">Count of distinct booking legal entities per L3 desk segment.
 </v>
       </c>
       <c r="S83" t="str">
@@ -8191,10 +8435,10 @@
         <v>Y</v>
       </c>
       <c r="U83" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V83" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level legal_entity_id per L2 portfolio segment.
+        <v xml:space="preserve">Count of distinct booking legal entities per L2 portfolio segment.
 </v>
       </c>
       <c r="W83" t="str">
@@ -8204,10 +8448,10 @@
         <v>Y</v>
       </c>
       <c r="Y83" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z83" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level legal_entity_id per L1 business segment segment.
+        <v xml:space="preserve">Count of distinct booking legal entities per L1 business segment.
 </v>
       </c>
       <c r="AA83" t="str">
@@ -8222,14 +8466,14 @@
         <v>REF-018</v>
       </c>
       <c r="B84" t="str" xml:space="preserve">
-        <v xml:space="preserve">Line of Business classification associated with exposure.
+        <v xml:space="preserve">Line of Business classification code associated with each exposure. Returns the hierarchical parent path code from the enterprise_business_taxonomy for the segment directly assigned to each facility via lob_segment_id. Used to group and filter exposures by organizational business line.
 </v>
       </c>
       <c r="C84" t="str">
         <v>Line of Business Level Name</v>
       </c>
       <c r="D84" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
+        <v xml:space="preserve">Direct lookup of parent code from enterprise_business_taxonomy via facility_master.lob_segment_id.
 </v>
       </c>
       <c r="E84" t="str">
@@ -8248,7 +8492,7 @@
         <v>Raw</v>
       </c>
       <c r="J84" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
+        <v xml:space="preserve">Direct lookup of parent code from enterprise_business_taxonomy via facility_master.lob_segment_id.
 </v>
       </c>
       <c r="K84" t="str">
@@ -8261,7 +8505,7 @@
         <v>Raw</v>
       </c>
       <c r="N84" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read parent per counterparty.
+        <v xml:space="preserve">Deterministic selection (MIN) of parent code across all facilities belonging to the counterparty.
 </v>
       </c>
       <c r="O84" t="str">
@@ -8271,10 +8515,10 @@
         <v>Y</v>
       </c>
       <c r="Q84" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="R84" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level parent per L3 desk segment.
+        <v xml:space="preserve">Direct parent code lookup per L3 desk segment. Groups facilities by their assigned EBT segment and returns the segment parent code.
 </v>
       </c>
       <c r="S84" t="str">
@@ -8284,10 +8528,10 @@
         <v>Y</v>
       </c>
       <c r="U84" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="V84" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level parent per L2 portfolio segment.
+        <v xml:space="preserve">Parent code at L2 portfolio level via one-hop EBT traversal.
 </v>
       </c>
       <c r="W84" t="str">
@@ -8297,10 +8541,10 @@
         <v>Y</v>
       </c>
       <c r="Y84" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="Z84" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level parent per L1 business segment segment.
+        <v xml:space="preserve">Parent code at L1 business segment level via two-hop EBT traversal.
 </v>
       </c>
       <c r="AA84" t="str">
@@ -8315,14 +8559,14 @@
         <v>REF-019</v>
       </c>
       <c r="B85" t="str" xml:space="preserve">
-        <v xml:space="preserve">Level 1 Line of Business hierarchy. Enables top-level organizational risk aggregation, representing the Department (e.g. Commercial Real Estate, Corporate Banking)
+        <v xml:space="preserve">Level 1 (Department) Line of Business hierarchy code. For each facility, traverses two hops up from the assigned EBT segment via parent_segment_id to reach the L1 department node, returning its parent path code. Enables top-level organizational risk aggregation (e.g. Corporate Banking, Commercial Real Estate).
 </v>
       </c>
       <c r="C85" t="str">
-        <v>Line of Business  L1</v>
+        <v>Line of Business L1</v>
       </c>
       <c r="D85" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
+        <v xml:space="preserve">Traverse two hops up the EBT hierarchy from facility lob_segment_id to reach the L1 department ancestor and return its parent code.
 </v>
       </c>
       <c r="E85" t="str">
@@ -8341,11 +8585,11 @@
         <v>Raw</v>
       </c>
       <c r="J85" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
+        <v xml:space="preserve">Traverse two hops up the EBT hierarchy from facility lob_segment_id to reach the L1 department ancestor and return its parent code.
 </v>
       </c>
       <c r="K85" t="str">
-        <v>Line of Business  L1 (facility)</v>
+        <v>Line of Business L1 (facility)</v>
       </c>
       <c r="L85" t="str">
         <v>Y</v>
@@ -8354,50 +8598,50 @@
         <v>Raw</v>
       </c>
       <c r="N85" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read parent per counterparty.
+        <v xml:space="preserve">Deterministic selection (MIN) of L1 department parent code across all facilities belonging to the counterparty.
 </v>
       </c>
       <c r="O85" t="str">
-        <v>Line of Business  L1 (counterparty)</v>
+        <v>Line of Business L1 (counterparty)</v>
       </c>
       <c r="P85" t="str">
         <v>Y</v>
       </c>
       <c r="Q85" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="R85" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level parent per L3 desk segment.
+        <v xml:space="preserve">For each L3 desk, traverse two hops up to the L1 department ancestor and return its parent code.
 </v>
       </c>
       <c r="S85" t="str">
-        <v>Line of Business  L1 (desk)</v>
+        <v>Line of Business L1 (desk)</v>
       </c>
       <c r="T85" t="str">
         <v>Y</v>
       </c>
       <c r="U85" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="V85" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level parent per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 portfolio, traverse one hop up to the L1 department ancestor and return its parent code.
 </v>
       </c>
       <c r="W85" t="str">
-        <v>Line of Business  L1 (portfolio)</v>
+        <v>Line of Business L1 (portfolio)</v>
       </c>
       <c r="X85" t="str">
         <v>Y</v>
       </c>
       <c r="Y85" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="Z85" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level parent per L1 business segment segment.
+        <v xml:space="preserve">At L1 business segment level, the segment IS the L1 department. Return its own parent code directly.
 </v>
       </c>
       <c r="AA85" t="str">
-        <v>Line of Business  L1 (business_segment)</v>
+        <v>Line of Business L1 (business_segment)</v>
       </c>
       <c r="AB85" t="str">
         <v/>
@@ -8408,14 +8652,14 @@
         <v>REF-020</v>
       </c>
       <c r="B86" t="str" xml:space="preserve">
-        <v xml:space="preserve">Level 2 Line of Business hierarchy for intermediate aggregation and reporting, representing the Portfolio within the L1 LoB (e.g., CRE &gt; Office)
+        <v xml:space="preserve">Level 2 (Portfolio) Line of Business hierarchy code. For each facility, traverses one hop up from the assigned EBT segment via parent_segment_id to reach the L2 portfolio node, returning its parent path code. Enables detailed business segment analysis (e.g. CRE &gt; Office).
 </v>
       </c>
       <c r="C86" t="str">
         <v>Line of Business L2</v>
       </c>
       <c r="D86" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
+        <v xml:space="preserve">Traverse one hop up the EBT hierarchy from facility lob_segment_id to reach the L2 portfolio ancestor and return its parent code.
 </v>
       </c>
       <c r="E86" t="str">
@@ -8434,7 +8678,7 @@
         <v>Raw</v>
       </c>
       <c r="J86" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
+        <v xml:space="preserve">Traverse one hop up the EBT hierarchy from facility lob_segment_id to reach the L2 portfolio ancestor and return its parent code.
 </v>
       </c>
       <c r="K86" t="str">
@@ -8447,7 +8691,7 @@
         <v>Raw</v>
       </c>
       <c r="N86" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read parent per counterparty.
+        <v xml:space="preserve">Deterministic selection (MIN) of L2 portfolio parent code across all facilities belonging to the counterparty.
 </v>
       </c>
       <c r="O86" t="str">
@@ -8457,10 +8701,10 @@
         <v>Y</v>
       </c>
       <c r="Q86" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="R86" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level parent per L3 desk segment.
+        <v xml:space="preserve">For each L3 desk, traverse one hop up to the L2 portfolio ancestor and return its parent code.
 </v>
       </c>
       <c r="S86" t="str">
@@ -8470,10 +8714,10 @@
         <v>Y</v>
       </c>
       <c r="U86" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="V86" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level parent per L2 portfolio segment.
+        <v xml:space="preserve">At L2 portfolio level, the segment IS the L2 portfolio. Return its own parent code directly.
 </v>
       </c>
       <c r="W86" t="str">
@@ -8483,10 +8727,10 @@
         <v>Y</v>
       </c>
       <c r="Y86" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="Z86" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level parent per L1 business segment segment.
+        <v xml:space="preserve">For each L1 business segment, returns the L2 portfolio parent codes of child portfolios. Uses MIN for deterministic string selection.
 </v>
       </c>
       <c r="AA86" t="str">
@@ -8501,14 +8745,14 @@
         <v>REF-021</v>
       </c>
       <c r="B87" t="str" xml:space="preserve">
-        <v xml:space="preserve">Level 3 Line of Business hierarchy for detailed business segmentation, representing the Desk within the L2 LoB (e.g. CRE &gt; Office &gt; Lease Up Desk)
+        <v xml:space="preserve">Level 3 (Desk) Line of Business hierarchy code. Returns the parent path code of the EBT segment directly assigned to each facility via lob_segment_id. Represents the most granular organizational segment view (e.g. CRE &gt; Office &gt; Lease Up Desk).
 </v>
       </c>
       <c r="C87" t="str">
         <v>Line of Business L3</v>
       </c>
       <c r="D87" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
+        <v xml:space="preserve">Direct lookup of parent code from enterprise_business_taxonomy via facility_master.lob_segment_id. For L3-assigned facilities this returns the L3 desk parent code.
 </v>
       </c>
       <c r="E87" t="str">
@@ -8527,7 +8771,7 @@
         <v>Raw</v>
       </c>
       <c r="J87" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of parent from enterprise_business_taxonomy.
+        <v xml:space="preserve">Direct lookup of parent code from enterprise_business_taxonomy via facility_master.lob_segment_id. For L3-assigned facilities this returns the L3 desk parent code.
 </v>
       </c>
       <c r="K87" t="str">
@@ -8540,7 +8784,7 @@
         <v>Raw</v>
       </c>
       <c r="N87" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read parent per counterparty.
+        <v xml:space="preserve">Deterministic selection (MIN) of L3 desk parent code across all facilities belonging to the counterparty.
 </v>
       </c>
       <c r="O87" t="str">
@@ -8550,10 +8794,10 @@
         <v>Y</v>
       </c>
       <c r="Q87" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="R87" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level parent per L3 desk segment.
+        <v xml:space="preserve">Direct parent code lookup per L3 desk segment. The desk level IS the L3 level, so return the segment own parent code.
 </v>
       </c>
       <c r="S87" t="str">
@@ -8563,10 +8807,10 @@
         <v>Y</v>
       </c>
       <c r="U87" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="V87" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level parent per L2 portfolio segment.
+        <v xml:space="preserve">L3 desk parent codes rolled up to L2 portfolio level. Returns MIN of desk-level parent codes within each portfolio.
 </v>
       </c>
       <c r="W87" t="str">
@@ -8576,10 +8820,10 @@
         <v>Y</v>
       </c>
       <c r="Y87" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="Z87" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level parent per L1 business segment segment.
+        <v xml:space="preserve">L3 desk parent codes rolled up to L1 business segment level. Returns MIN of desk-level parent codes within each segment.
 </v>
       </c>
       <c r="AA87" t="str">
@@ -8594,7 +8838,7 @@
         <v>REF-022</v>
       </c>
       <c r="B88" t="str" xml:space="preserve">
-        <v xml:space="preserve">Contractual date on which the facility or loan is scheduled to mature. Used to assess duration exposure, refinancing risk, and liquidity planning.
+        <v xml:space="preserve">Contractual date on which the facility or loan is scheduled to mature. Used to assess duration exposure, refinancing risk, and liquidity planning. At aggregate levels, returns the nearest (MIN) maturity date as a risk indicator.
 </v>
       </c>
       <c r="C88" t="str">
@@ -8630,10 +8874,10 @@
         <v>Y</v>
       </c>
       <c r="M88" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N88" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level maturity_date) per counterparty.
+        <v xml:space="preserve">Nearest (MIN) maturity date across all facilities per counterparty.
 </v>
       </c>
       <c r="O88" t="str">
@@ -8643,10 +8887,10 @@
         <v>Y</v>
       </c>
       <c r="Q88" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R88" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level maturity_date per L3 desk segment.
+        <v xml:space="preserve">Nearest (MIN) maturity date across all facilities per L3 desk segment.
 </v>
       </c>
       <c r="S88" t="str">
@@ -8656,10 +8900,10 @@
         <v>Y</v>
       </c>
       <c r="U88" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V88" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level maturity_date per L2 portfolio segment.
+        <v xml:space="preserve">Nearest (MIN) maturity date across all facilities per L2 portfolio segment.
 </v>
       </c>
       <c r="W88" t="str">
@@ -8669,10 +8913,10 @@
         <v>Y</v>
       </c>
       <c r="Y88" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z88" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level maturity_date per L1 business segment segment.
+        <v xml:space="preserve">Nearest (MIN) maturity date across all facilities per L1 business segment.
 </v>
       </c>
       <c r="AA88" t="str">
@@ -8780,14 +9024,15 @@
         <v>REF-024</v>
       </c>
       <c r="B90" t="str" xml:space="preserve">
-        <v xml:space="preserve">Identifiers of counterparties participating in the credit structures or facility as multiple-borrowers. Enables exposure attribution and concentration analysis.
+        <v xml:space="preserve">Count of distinct counterparties participating in credit structures. At counterparty level, returns the counterparty identifier directly. At desk and higher levels, counts distinct counterparties per segment to measure borrower concentration and multi-borrower facility exposure. Enables concentration analysis, relationship tracking, and syndicated deal monitoring.
 </v>
       </c>
       <c r="C90" t="str">
         <v>Participating Counterparty IDs</v>
       </c>
       <c r="D90" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">Direct lookup of counterparty_id from facility_master for each facility.
+Returns the counterparty associated with the facility.
 </v>
       </c>
       <c r="E90" t="str">
@@ -8806,7 +9051,8 @@
         <v>Raw</v>
       </c>
       <c r="J90" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">Direct lookup of counterparty_id from facility_master for each facility.
+Returns the counterparty associated with the facility.
 </v>
       </c>
       <c r="K90" t="str">
@@ -8819,7 +9065,8 @@
         <v>Raw</v>
       </c>
       <c r="N90" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of counterparty_id from counterparty.
+        <v xml:space="preserve">Identity: returns counterparty_id for each active counterparty.
+Enables direct counterparty identification in drill-down views.
 </v>
       </c>
       <c r="O90" t="str">
@@ -8829,10 +9076,14 @@
         <v>Y</v>
       </c>
       <c r="Q90" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R90" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L3 desk segment.
+        <v xml:space="preserve">For each L3 Desk segment:
+  1. LOAD all facilities from l2.facility_master
+  2. JOIN l1.enterprise_business_taxonomy on lob_segment_id
+  3. COMPUTE COUNT(DISTINCT counterparty_id) — unique borrowers per desk
+Measures borrower concentration within each desk.
 </v>
       </c>
       <c r="S90" t="str">
@@ -8842,10 +9093,12 @@
         <v>Y</v>
       </c>
       <c r="U90" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V90" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L2 portfolio segment.
+        <v xml:space="preserve">For each L2 Portfolio segment:
+  1. Walk UP hierarchy: L3 desk → L2 portfolio via parent_segment_id
+  2. COMPUTE COUNT(DISTINCT counterparty_id) — unique borrowers per portfolio
 </v>
       </c>
       <c r="W90" t="str">
@@ -8855,10 +9108,12 @@
         <v>Y</v>
       </c>
       <c r="Y90" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z90" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level counterparty_id per L1 business segment segment.
+        <v xml:space="preserve">For each L1 Business Segment / LoB:
+  1. Walk UP hierarchy: L3 → L2 → L1 via parent_segment_id chain
+  2. COMPUTE COUNT(DISTINCT counterparty_id) — unique borrowers per segment
 </v>
       </c>
       <c r="AA90" t="str">
@@ -8873,14 +9128,14 @@
         <v>REF-025</v>
       </c>
       <c r="B91" t="str" xml:space="preserve">
-        <v xml:space="preserve">Product classification assigned to the contract offering. Supports product- level segmentation and performance analysis.
+        <v xml:space="preserve">Product classification from the Enterprise Product Taxonomy for each facility. At facility level, returns the product_name (e.g., Term Loan, Revolver, Letter of Credit). At aggregate levels, returns the dominant product by drawn exposure weight (bank-share-adjusted, USD-converted) using ROW_NUMBER to identify the highest-exposure product in the segment.
 </v>
       </c>
       <c r="C91" t="str">
         <v>Product</v>
       </c>
       <c r="D91" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(product_id) per facility from facility_exposure_snapshot.
+        <v xml:space="preserve">Product name lookup from enterprise_product_taxonomy via facility_exposure_snapshot.product_node_id.
 </v>
       </c>
       <c r="E91" t="str">
@@ -8896,10 +9151,10 @@
         <v>Y</v>
       </c>
       <c r="I91" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="J91" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(product_id) per facility from facility_exposure_snapshot.
+        <v xml:space="preserve">Product name lookup from enterprise_product_taxonomy via facility_exposure_snapshot.product_node_id.
 </v>
       </c>
       <c r="K91" t="str">
@@ -8909,10 +9164,10 @@
         <v>Y</v>
       </c>
       <c r="M91" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N91" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level product_id per counterparty.
+        <v xml:space="preserve">Dominant product by drawn exposure weight per counterparty. ROW_NUMBER partitioned by counterparty, ordered by total bank-share-adjusted drawn amount descending.
 </v>
       </c>
       <c r="O91" t="str">
@@ -8922,10 +9177,10 @@
         <v>Y</v>
       </c>
       <c r="Q91" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R91" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level product_id per L3 desk segment.
+        <v xml:space="preserve">Dominant product by drawn exposure weight (USD-converted) per L3 desk segment. ROW_NUMBER partitioned by desk, ordered by total exposure descending.
 </v>
       </c>
       <c r="S91" t="str">
@@ -8935,10 +9190,10 @@
         <v>Y</v>
       </c>
       <c r="U91" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V91" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level product_id per L2 portfolio segment.
+        <v xml:space="preserve">Dominant product by drawn exposure weight (USD-converted) per L2 portfolio segment via EBT hierarchy (one hop up).
 </v>
       </c>
       <c r="W91" t="str">
@@ -8948,10 +9203,10 @@
         <v>Y</v>
       </c>
       <c r="Y91" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z91" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level product_id per L1 business segment segment.
+        <v xml:space="preserve">Dominant product by drawn exposure weight (USD-converted) per L1 business segment via EBT hierarchy (two hops up).
 </v>
       </c>
       <c r="AA91" t="str">
@@ -8966,14 +9221,14 @@
         <v>REF-026</v>
       </c>
       <c r="B92" t="str" xml:space="preserve">
-        <v xml:space="preserve">Geographic region classification tied to location of deal origination, supporting portfolio segmentation and concentration monitoring.
+        <v xml:space="preserve">Geographic region classification derived from counterparty country of domicile. Join chain: counterparty.country_code -&gt; country_dim.region_code -&gt; region_dim.region_name. At facility level, returns the region name. At aggregate levels, returns the dominant region by drawn exposure weight (bank-share-adjusted, USD-converted) using ROW_NUMBER.
 </v>
       </c>
       <c r="C92" t="str">
         <v>Region</v>
       </c>
       <c r="D92" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of region_code from counterparty.
+        <v xml:space="preserve">Region name lookup via counterparty.country_code -&gt; country_dim -&gt; region_dim.region_name.
 </v>
       </c>
       <c r="E92" t="str">
@@ -8992,7 +9247,7 @@
         <v>Raw</v>
       </c>
       <c r="J92" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of region_code from counterparty.
+        <v xml:space="preserve">Region name lookup via counterparty.country_code -&gt; country_dim -&gt; region_dim.region_name.
 </v>
       </c>
       <c r="K92" t="str">
@@ -9002,10 +9257,10 @@
         <v>Y</v>
       </c>
       <c r="M92" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="N92" t="str" xml:space="preserve">
-        <v xml:space="preserve">Direct lookup of region_code from counterparty.
+        <v xml:space="preserve">Dominant region by drawn exposure weight per counterparty. ROW_NUMBER partitioned by counterparty, ordered by total bank-share-adjusted drawn amount descending.
 </v>
       </c>
       <c r="O92" t="str">
@@ -9015,10 +9270,10 @@
         <v>Y</v>
       </c>
       <c r="Q92" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R92" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level region_code per L3 desk segment.
+        <v xml:space="preserve">Dominant region by drawn exposure weight (USD-converted) per L3 desk segment. ROW_NUMBER partitioned by desk, ordered by total exposure descending.
 </v>
       </c>
       <c r="S92" t="str">
@@ -9028,10 +9283,10 @@
         <v>Y</v>
       </c>
       <c r="U92" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V92" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level region_code per L2 portfolio segment.
+        <v xml:space="preserve">Dominant region by drawn exposure weight (USD-converted) per L2 portfolio segment via EBT hierarchy (one hop up).
 </v>
       </c>
       <c r="W92" t="str">
@@ -9041,10 +9296,10 @@
         <v>Y</v>
       </c>
       <c r="Y92" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z92" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level region_code per L1 business segment segment.
+        <v xml:space="preserve">Dominant region by drawn exposure weight (USD-converted) per L1 business segment via EBT hierarchy (two hops up).
 </v>
       </c>
       <c r="AA92" t="str">
@@ -9245,14 +9500,14 @@
         <v>REF-029</v>
       </c>
       <c r="B95" t="str" xml:space="preserve">
-        <v xml:space="preserve">Represents “hard” equity after removing intangibles; reflects true loss- absorbing capacity, covenant strength, and resilience under downside scenarios.
+        <v xml:space="preserve">Counterparty tangible net worth (hard equity after removing intangibles). Reflects true loss-absorbing capacity, covenant strength, and resilience under downside scenarios. At facility level, returns the counterparty's TNW. At counterparty level, direct read. At aggregate levels, returns exposure-weighted average TNW — avoids invalid SUM of equity across unrelated counterparties (consolidation accounting violation).
 </v>
       </c>
       <c r="C95" t="str">
         <v>Tangible Net Worth</v>
       </c>
       <c r="D95" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read tangible_net_worth_usd from counterparty_financial_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Read tangible_net_worth_usd from counterparty_financial_snapshot for the counterparty behind each facility.
 </v>
       </c>
       <c r="E95" t="str">
@@ -9271,7 +9526,7 @@
         <v>Raw</v>
       </c>
       <c r="J95" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read tangible_net_worth_usd from counterparty_financial_snapshot for each facility as-of reporting date.
+        <v xml:space="preserve">Read tangible_net_worth_usd from counterparty_financial_snapshot for the counterparty behind each facility.
 </v>
       </c>
       <c r="K95" t="str">
@@ -9284,7 +9539,7 @@
         <v>Raw</v>
       </c>
       <c r="N95" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read tangible_net_worth_usd per counterparty.
+        <v xml:space="preserve">Direct read of tangible_net_worth_usd per counterparty.
 </v>
       </c>
       <c r="O95" t="str">
@@ -9294,10 +9549,10 @@
         <v>Y</v>
       </c>
       <c r="Q95" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="R95" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level tangible_net_worth_usd per L3 desk segment.
+        <v xml:space="preserve">Exposure-weighted average TNW per L3 desk segment. Weights by each counterparty's drawn exposure (bank-share-adjusted, USD-converted) in the segment. Avoids invalid SUM of equity across counterparties.
 </v>
       </c>
       <c r="S95" t="str">
@@ -9307,10 +9562,10 @@
         <v>Y</v>
       </c>
       <c r="U95" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="V95" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level tangible_net_worth_usd per L2 portfolio segment.
+        <v xml:space="preserve">Exposure-weighted average TNW per L2 portfolio segment via EBT hierarchy (one hop up).
 </v>
       </c>
       <c r="W95" t="str">
@@ -9320,10 +9575,10 @@
         <v>Y</v>
       </c>
       <c r="Y95" t="str">
-        <v>Agg</v>
+        <v>Avg</v>
       </c>
       <c r="Z95" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level tangible_net_worth_usd per L1 business segment segment.
+        <v xml:space="preserve">Exposure-weighted average TNW per L1 business segment via EBT hierarchy (two hops up).
 </v>
       </c>
       <c r="AA95" t="str">
@@ -9338,14 +9593,14 @@
         <v>REF-030</v>
       </c>
       <c r="B96" t="str" xml:space="preserve">
-        <v xml:space="preserve">Bucketing mechanism to calculate Maturity Dates supporting the identification of upcoming liquidations in the next 90 days
+        <v xml:space="preserve">Maturity time bucket for each facility based on days_until_maturity from the exposure snapshot, mapped to maturity_bucket_dim via range join (bucket_start_days &lt;= days &lt;= bucket_end_days). At facility level, returns the bucket_name. At aggregate levels, returns the dominant maturity bucket by drawn exposure weight. Supports maturity wall identification and concentration risk monitoring.
 </v>
       </c>
       <c r="C96" t="str">
         <v>Maturity Date Bucket</v>
       </c>
       <c r="D96" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated maturity_bucket_id per facility.
+        <v xml:space="preserve">Maturity bucket lookup from maturity_bucket_dim via range join on days_until_maturity. Returns bucket_name (e.g., "0-90 days", "91-180 days", "1-2 years").
 </v>
       </c>
       <c r="E96" t="str">
@@ -9361,10 +9616,10 @@
         <v>Y</v>
       </c>
       <c r="I96" t="str">
-        <v>Calc</v>
+        <v>Raw</v>
       </c>
       <c r="J96" t="str" xml:space="preserve">
-        <v xml:space="preserve">Calculated maturity_bucket_id per facility.
+        <v xml:space="preserve">Maturity bucket lookup from maturity_bucket_dim via range join on days_until_maturity. Returns bucket_name (e.g., "0-90 days", "91-180 days", "1-2 years").
 </v>
       </c>
       <c r="K96" t="str">
@@ -9374,10 +9629,10 @@
         <v>Y</v>
       </c>
       <c r="M96" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="N96" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM(facility-level maturity_bucket_id) per counterparty.
+        <v xml:space="preserve">Dominant maturity bucket by drawn exposure weight per counterparty. ROW_NUMBER partitioned by counterparty, ordered by total bank-share-adjusted drawn amount descending.
 </v>
       </c>
       <c r="O96" t="str">
@@ -9387,10 +9642,10 @@
         <v>Y</v>
       </c>
       <c r="Q96" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R96" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level maturity_bucket_id per L3 desk segment.
+        <v xml:space="preserve">Dominant maturity bucket by drawn exposure weight (USD-converted) per L3 desk segment. ROW_NUMBER partitioned by desk, ordered by total exposure descending.
 </v>
       </c>
       <c r="S96" t="str">
@@ -9400,10 +9655,10 @@
         <v>Y</v>
       </c>
       <c r="U96" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V96" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level maturity_bucket_id per L2 portfolio segment.
+        <v xml:space="preserve">Dominant maturity bucket by drawn exposure weight (USD-converted) per L2 portfolio segment via EBT hierarchy (one hop up).
 </v>
       </c>
       <c r="W96" t="str">
@@ -9413,10 +9668,10 @@
         <v>Y</v>
       </c>
       <c r="Y96" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z96" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level maturity_bucket_id per L1 business segment segment.
+        <v xml:space="preserve">Dominant maturity bucket by drawn exposure weight (USD-converted) per L1 business segment via EBT hierarchy (two hops up).
 </v>
       </c>
       <c r="AA96" t="str">
@@ -9707,17 +9962,17 @@
     </row>
     <row r="100" xml:space="preserve">
       <c r="A100" t="str">
-        <v>RSK-001</v>
+        <v>REF-034</v>
       </c>
       <c r="B100" t="str" xml:space="preserve">
-        <v xml:space="preserve">Risk rating tier derived from counterparty probability of default (PD). Each counterparty's pd_annual is matched against the risk_rating_tier_dim reference table (pd_min_pct / pd_max_pct boundaries) to assign a tier classification. At facility level, the tier is inherited from the owning counterparty. At aggregate levels, MAX (worst-case) tier ordinal is reported.
+        <v xml:space="preserve">Facility activity status indicator. At facility level, reads the is_active_flag from facility_master and returns 1 (active) or 0 (inactive). At counterparty level, returns 1 if any of the counterparty's facilities are active (boolean OR). Provides a baseline portfolio activity measure for CRO reporting and data quality monitoring.
 </v>
       </c>
       <c r="C100" t="str">
-        <v>Risk Rating Tier</v>
+        <v>Active Flag</v>
       </c>
       <c r="D100" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each facility, inherit the risk rating tier from the owning counterparty. Join facility_master to counterparty, then range-match counterparty pd_annual against risk_rating_tier_dim to derive the tier ordinal (display_order).
+        <v xml:space="preserve">Read is_active_flag from facility_master. Returns 1 if the facility is active (is_active_flag = 'Y'), 0 otherwise. No date filtering required as is_active_flag reflects current status.
 </v>
       </c>
       <c r="E100" t="str">
@@ -9733,66 +9988,66 @@
         <v>Y</v>
       </c>
       <c r="I100" t="str">
-        <v>Calc</v>
+        <v>Raw</v>
       </c>
       <c r="J100" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each facility, inherit the risk rating tier from the owning counterparty. Join facility_master to counterparty, then range-match counterparty pd_annual against risk_rating_tier_dim to derive the tier ordinal (display_order).
+        <v xml:space="preserve">Read is_active_flag from facility_master. Returns 1 if the facility is active (is_active_flag = 'Y'), 0 otherwise. No date filtering required as is_active_flag reflects current status.
 </v>
       </c>
       <c r="K100" t="str">
-        <v>Risk Rating Tier (facility)</v>
+        <v>Active Flag (facility)</v>
       </c>
       <c r="L100" t="str">
         <v>Y</v>
       </c>
       <c r="M100" t="str">
-        <v>Calc</v>
+        <v>Agg</v>
       </c>
       <c r="N100" t="str" xml:space="preserve">
-        <v xml:space="preserve">For each counterparty, look up pd_annual and range-match against risk_rating_tier_dim where pd_annual &gt;= pd_min_pct AND pd_annual &lt; pd_max_pct. Returns the tier ordinal (display_order). Counterparties with NULL PD receive tier 0 (unrated).
+        <v xml:space="preserve">For each counterparty, check if any of its facilities are active. Uses MAX over the facility-level boolean flags — if any facility is active (1), the counterparty is considered active (1). Returns 0 only if ALL facilities for the counterparty are inactive.
 </v>
       </c>
       <c r="O100" t="str">
-        <v>Risk Rating Tier (counterparty)</v>
+        <v>Active Flag (counterparty)</v>
       </c>
       <c r="P100" t="str">
         <v>Y</v>
       </c>
       <c r="Q100" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R100" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst-case (MAX) risk rating tier ordinal across all counterparties in the L3 desk segment. Higher ordinal = riskier tier. Full tier distribution available via counterparty-level drill-down.
+        <v xml:space="preserve">Not applicable — active flag is a facility/counterparty level indicator. Desk-level portfolio activity analysis should use count-based metrics or exposure-weighted activity rates.
 </v>
       </c>
       <c r="S100" t="str">
-        <v>Risk Rating Tier (desk)</v>
+        <v>Active Flag (desk)</v>
       </c>
       <c r="T100" t="str">
         <v>Y</v>
       </c>
       <c r="U100" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V100" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst-case (MAX) risk rating tier ordinal per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
+        <v xml:space="preserve">Not applicable — active flag is a facility/counterparty level indicator. Portfolio-level analysis should aggregate exposure amounts filtered by active status.
 </v>
       </c>
       <c r="W100" t="str">
-        <v>Risk Rating Tier (portfolio)</v>
+        <v>Active Flag (portfolio)</v>
       </c>
       <c r="X100" t="str">
         <v>Y</v>
       </c>
       <c r="Y100" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z100" t="str" xml:space="preserve">
-        <v xml:space="preserve">Worst-case (MAX) risk rating tier ordinal per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
+        <v xml:space="preserve">Not applicable — active flag is a facility/counterparty level indicator. Business segment analysis should aggregate exposure amounts filtered by active status.
 </v>
       </c>
       <c r="AA100" t="str">
-        <v>Risk Rating Tier (business_segment)</v>
+        <v>Active Flag (business_segment)</v>
       </c>
       <c r="AB100" t="str">
         <v/>
@@ -9800,17 +10055,17 @@
     </row>
     <row r="101" xml:space="preserve">
       <c r="A101" t="str">
-        <v>RSK-002</v>
+        <v>RSK-001</v>
       </c>
       <c r="B101" t="str" xml:space="preserve">
-        <v xml:space="preserve">Current external credit agency rating assigned to the obligor. Used for benchmarking, regulatory reporting, and external credit risk validation. Sourced based on external Rating provider (S&amp;P, Moodys, Fitch) - populated based on firm's preferred recognized rating provider.
+        <v xml:space="preserve">Risk rating tier derived from counterparty probability of default (PD). Each counterparty's pd_annual is matched against the risk_rating_tier_dim reference table (pd_min_pct / pd_max_pct boundaries) to assign a tier classification. At facility level, the tier is inherited from the owning counterparty. At aggregate levels, MAX (worst-case) tier ordinal is reported.
 </v>
       </c>
       <c r="C101" t="str">
-        <v>Risk Rating - External Rating</v>
+        <v>Risk Rating Tier</v>
       </c>
       <c r="D101" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read external_risk_rating from position for each facility as-of reporting date.
+        <v xml:space="preserve">For each facility, inherit the risk rating tier from the owning counterparty. Join facility_master to counterparty, then range-match counterparty pd_annual against risk_rating_tier_dim to derive the tier ordinal (display_order).
 </v>
       </c>
       <c r="E101" t="str">
@@ -9826,66 +10081,66 @@
         <v>Y</v>
       </c>
       <c r="I101" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="J101" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read external_risk_rating from position for each facility as-of reporting date.
+        <v xml:space="preserve">For each facility, inherit the risk rating tier from the owning counterparty. Join facility_master to counterparty, then range-match counterparty pd_annual against risk_rating_tier_dim to derive the tier ordinal (display_order).
 </v>
       </c>
       <c r="K101" t="str">
-        <v>Risk Rating - External Rating (facility)</v>
+        <v>Risk Rating Tier (facility)</v>
       </c>
       <c r="L101" t="str">
         <v>Y</v>
       </c>
       <c r="M101" t="str">
-        <v>Raw</v>
+        <v>Calc</v>
       </c>
       <c r="N101" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read external_risk_rating per counterparty.
+        <v xml:space="preserve">For each counterparty, look up pd_annual and range-match against risk_rating_tier_dim where pd_annual &gt;= pd_min_pct AND pd_annual &lt; pd_max_pct. Returns the tier ordinal (display_order). Counterparties with NULL PD receive tier 0 (unrated).
 </v>
       </c>
       <c r="O101" t="str">
-        <v>Risk Rating - External Rating (counterparty)</v>
+        <v>Risk Rating Tier (counterparty)</v>
       </c>
       <c r="P101" t="str">
         <v>Y</v>
       </c>
       <c r="Q101" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="R101" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level external_risk_rating per L3 desk segment.
+        <v xml:space="preserve">Worst-case (MAX) risk rating tier ordinal across all counterparties in the L3 desk segment. Higher ordinal = riskier tier. Full tier distribution available via counterparty-level drill-down.
 </v>
       </c>
       <c r="S101" t="str">
-        <v>Risk Rating - External Rating (desk)</v>
+        <v>Risk Rating Tier (desk)</v>
       </c>
       <c r="T101" t="str">
         <v>Y</v>
       </c>
       <c r="U101" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="V101" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level external_risk_rating per L2 portfolio segment.
+        <v xml:space="preserve">Worst-case (MAX) risk rating tier ordinal per L2 portfolio segment. Traverses EBT hierarchy L3 → L2 via parent_segment_id.
 </v>
       </c>
       <c r="W101" t="str">
-        <v>Risk Rating - External Rating (portfolio)</v>
+        <v>Risk Rating Tier (portfolio)</v>
       </c>
       <c r="X101" t="str">
         <v>Y</v>
       </c>
       <c r="Y101" t="str">
-        <v>Avg</v>
+        <v>Agg</v>
       </c>
       <c r="Z101" t="str" xml:space="preserve">
-        <v xml:space="preserve">AVG of facility-level external_risk_rating per L1 business segment segment.
+        <v xml:space="preserve">Worst-case (MAX) risk rating tier ordinal per L1 business segment. Full EBT hierarchy traversal L3 → L2 → L1.
 </v>
       </c>
       <c r="AA101" t="str">
-        <v>Risk Rating - External Rating (business_segment)</v>
+        <v>Risk Rating Tier (business_segment)</v>
       </c>
       <c r="AB101" t="str">
         <v/>
@@ -9893,17 +10148,26 @@
     </row>
     <row r="102" xml:space="preserve">
       <c r="A102" t="str">
-        <v>RSK-003</v>
+        <v>RSK-002</v>
       </c>
       <c r="B102" t="str" xml:space="preserve">
-        <v xml:space="preserve">The institution’s internally assigned credit risk grade for a borrower, facility, or exposure as of a given date, reflecting its assessment of default risk according to the firm’s internal rating scale/model.
+        <v xml:space="preserve">External credit agency rating expressed as a numeric notch value from the rating_scale_dim. At facility/counterparty levels, returns the raw notch of the external rating. At aggregate levels (desk, portfolio, segment), computes the exposure-weighted average notch across all positions, rounded to the nearest whole notch. Lower notch = better rating (e.g., 1=AAA, 21=D). Sourced from position.external_risk_rating, mapped to rating_scale_dim.rating_value.
 </v>
       </c>
       <c r="C102" t="str">
-        <v>Risk Rating - Internal Risk Rating</v>
+        <v>Risk Rating - External Rating</v>
       </c>
       <c r="D102" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read internal_risk_rating from facility_risk_snapshot for each facility.
+        <v xml:space="preserve">1. LOAD  l2.position  (pos)
+   WHERE pos.as_of_date = :as_of_date
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = pos.facility_id
+   WHERE fm.is_active_flag = 'Y'
+3. LEFT JOIN  l1.rating_scale_dim  (rs)
+   ON    rs.rating_notch = pos.external_risk_rating
+   AND   rs.is_current_flag = 'Y'
+4. COMPUTE
+   metric_value = rs.rating_value
 </v>
       </c>
       <c r="E102" t="str">
@@ -9922,63 +10186,108 @@
         <v>Raw</v>
       </c>
       <c r="J102" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read internal_risk_rating from facility_risk_snapshot for each facility.
+        <v xml:space="preserve">1. LOAD  l2.position  (pos)
+   WHERE pos.as_of_date = :as_of_date
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = pos.facility_id
+   WHERE fm.is_active_flag = 'Y'
+3. LEFT JOIN  l1.rating_scale_dim  (rs)
+   ON    rs.rating_notch = pos.external_risk_rating
+   AND   rs.is_current_flag = 'Y'
+4. COMPUTE
+   metric_value = rs.rating_value
 </v>
       </c>
       <c r="K102" t="str">
-        <v>Risk Rating - Internal Risk Rating (facility)</v>
+        <v>Risk Rating - External Rating (facility)</v>
       </c>
       <c r="L102" t="str">
         <v>Y</v>
       </c>
       <c r="M102" t="str">
-        <v>Agg</v>
+        <v>Raw</v>
       </c>
       <c r="N102" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with internal risk rating per counterparty.
+        <v xml:space="preserve">1. LOAD  l2.position  (pos)
+   WHERE pos.as_of_date = :as_of_date
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = pos.facility_id
+3. LEFT JOIN  l1.rating_scale_dim  (rs)
+   ON    rs.rating_notch = pos.external_risk_rating
+4. GROUP BY fm.counterparty_id
+5. COMPUTE
+   metric_value = ROUND(AVG(rating_value))
 </v>
       </c>
       <c r="O102" t="str">
-        <v>Risk Rating - Internal Risk Rating (counterparty)</v>
+        <v>Risk Rating - External Rating (counterparty)</v>
       </c>
       <c r="P102" t="str">
         <v>Y</v>
       </c>
       <c r="Q102" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="R102" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with internal risk rating per L3 desk segment.
+        <v xml:space="preserve">1. LOAD  l2.position  (pos)
+   WHERE pos.as_of_date = :as_of_date
+2. JOIN  l2.facility_master  (fm)
+   ON    fm.facility_id = pos.facility_id
+3. LEFT JOIN  l1.rating_scale_dim  (rs)
+   ON    rs.rating_notch = pos.external_risk_rating
+4. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt)
+   ON    ebt.managed_segment_id = fm.lob_segment_id
+5. GROUP BY ebt.managed_segment_id
+6. COMPUTE
+   metric_value = ROUND(AVG(rating_value))
 </v>
       </c>
       <c r="S102" t="str">
-        <v>Risk Rating - Internal Risk Rating (desk)</v>
+        <v>Risk Rating - External Rating (desk)</v>
       </c>
       <c r="T102" t="str">
         <v>Y</v>
       </c>
       <c r="U102" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="V102" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with internal risk rating per L2 portfolio segment.
+        <v xml:space="preserve">1. LOAD  l2.position  (pos)
+   WHERE pos.as_of_date = :as_of_date
+2. JOIN  l2.facility_master  (fm)
+3. LEFT JOIN  l1.rating_scale_dim  (rs)
+   ON    rs.rating_notch = pos.external_risk_rating
+4. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l3, ebt_l2)
+   Traverse L3 -&gt; L2 via parent_segment_id
+5. GROUP BY ebt_l2.managed_segment_id
+6. COMPUTE
+   metric_value = ROUND(AVG(rating_value))
 </v>
       </c>
       <c r="W102" t="str">
-        <v>Risk Rating - Internal Risk Rating (portfolio)</v>
+        <v>Risk Rating - External Rating (portfolio)</v>
       </c>
       <c r="X102" t="str">
         <v>Y</v>
       </c>
       <c r="Y102" t="str">
-        <v>Agg</v>
+        <v>Calc</v>
       </c>
       <c r="Z102" t="str" xml:space="preserve">
-        <v xml:space="preserve">COUNT of facilities with internal risk rating per L1 business segment.
+        <v xml:space="preserve">1. LOAD  l2.position  (pos)
+   WHERE pos.as_of_date = :as_of_date
+2. JOIN  l2.facility_master  (fm)
+3. LEFT JOIN  l1.rating_scale_dim  (rs)
+   ON    rs.rating_notch = pos.external_risk_rating
+4. LEFT JOIN  l1.enterprise_business_taxonomy  (ebt_l3, ebt_l2, ebt_l1)
+   Traverse L3 -&gt; L2 -&gt; L1 via parent_segment_id chain
+5. GROUP BY ebt_l1.managed_segment_id
+6. COMPUTE
+   metric_value = ROUND(AVG(rating_value))
 </v>
       </c>
       <c r="AA102" t="str">
-        <v>Risk Rating - Internal Risk Rating (business_segment)</v>
+        <v>Risk Rating - External Rating (business_segment)</v>
       </c>
       <c r="AB102" t="str">
         <v/>
@@ -9986,17 +10295,17 @@
     </row>
     <row r="103" xml:space="preserve">
       <c r="A103" t="str">
-        <v>RSK-004</v>
+        <v>RSK-003</v>
       </c>
       <c r="B103" t="str" xml:space="preserve">
-        <v xml:space="preserve">Derived directional indicator reflecting movement in external credit agency rating and changes month over month, which depicts the month-over-month change reflecting an upgrade (e.g. A to AA), downgrade (e.g., B+ to B-) or stable (remaing constant month over month), as compared to prior month reporting periods. Note when this is displayed at an aggregated Line of Business or portfolio level, it is determined by the month-over-month change of the average rating at this level. Supports benchmarking against market perception and helps validate internal risk assessment trends.
+        <v xml:space="preserve">The institution’s internally assigned credit risk grade for a borrower, facility, or exposure as of a given date, reflecting its assessment of default risk according to the firm’s internal rating scale/model.
 </v>
       </c>
       <c r="C103" t="str">
-        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable)</v>
+        <v>Risk Rating - Internal Risk Rating</v>
       </c>
       <c r="D103" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility as-of reporting date.
+        <v xml:space="preserve">Read internal_risk_rating from facility_risk_snapshot for each facility.
 </v>
       </c>
       <c r="E103" t="str">
@@ -10015,11 +10324,11 @@
         <v>Raw</v>
       </c>
       <c r="J103" t="str" xml:space="preserve">
-        <v xml:space="preserve">Read risk_rating_status from counterparty_rating_observation for each facility as-of reporting date.
+        <v xml:space="preserve">Read internal_risk_rating from facility_risk_snapshot for each facility.
 </v>
       </c>
       <c r="K103" t="str">
-        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable) (facility)</v>
+        <v>Risk Rating - Internal Risk Rating (facility)</v>
       </c>
       <c r="L103" t="str">
         <v>Y</v>
@@ -10028,11 +10337,11 @@
         <v>Agg</v>
       </c>
       <c r="N103" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_status per counterparty.
+        <v xml:space="preserve">COUNT of facilities with internal risk rating per counterparty.
 </v>
       </c>
       <c r="O103" t="str">
-        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable) (counterparty)</v>
+        <v>Risk Rating - Internal Risk Rating (counterparty)</v>
       </c>
       <c r="P103" t="str">
         <v>Y</v>
@@ -10041,11 +10350,11 @@
         <v>Agg</v>
       </c>
       <c r="R103" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_status per L3 desk segment.
+        <v xml:space="preserve">COUNT of facilities with internal risk rating per L3 desk segment.
 </v>
       </c>
       <c r="S103" t="str">
-        <v>Risk Rating Status - External (e.g. Downgrade, Upgrade, Stable) (desk)</v>
+        <v>Risk Rating - Internal Risk Rating (desk)</v>
       </c>
       <c r="T103" t="str">
         <v>Y</v>
@@ -10054,11 +10363,11 @@
         <v>Agg</v>
       </c>
       <c r="V103" t="str" xml:space="preserve">
-        <v xml:space="preserve">SUM of facility-level risk_rating_status per L2 portfolio segment.
+        <v xml:space="preserve">CO